--- a/liftpilot/docs/lista-verifica-normativa.xlsx
+++ b/liftpilot/docs/lista-verifica-normativa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Riepilogo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$111</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Voci'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -594,102 +594,106 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>modifiche e sostituzioni su ascensori elettrici esistenti non conformi alle direttive</t>
+          <t>modifiche e sostituzioni su ascensori elettrici esistenti non conformi alla Direttiva Ascensori: collaudo delle parti modificate</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>UNI 10411-11:2024</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>modifiche e sostituzioni su ascensori elettrici esistenti conformi alla 95/16/CE o alla 2014/33/UE: collaudo delle parti modificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
           <t>DM 236/1989</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>accessibilità: cabina e porta minime (8.1.12), per il progetto del vano</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Come compilare</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Nel foglio «Voci», per ogni riga confrontare il «Valore nel software» con il testo vigente del documento in «Dove verificare».</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
+          <t>Nel foglio «Voci», per ogni riga confrontare il «Valore nel software» con il testo vigente del documento in «Dove verificare».</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
           <t>Compilare solo le celle gialle: Esito (conforme / diverso / non applicabile), Valore corretto e Clausola esatta se diverso, Note, Verificato da, Data.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>La riga 2 è un ESEMPIO del formato: non è una voce e non entra nel riepilogo.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="B16" s="4" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Stati: «da verificare» = fonte secondaria; «stima» e «scelta del software» = decisioni del software da approvare o correggere; «derivazione» = meccanica elementare; «confermato» = due fonti indipendenti o un caso pubblicato riprodotto, da confrontare comunque con il testo; «prassi di cantiere» = indicazione di Panev Ascensori.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Ogni correzione viene riportata nel registro del software (argano/src/calc/norme.ts) e cambia insieme motore di calcolo, lista e relazione di calcolo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
+    <row r="18" ht="32" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>Ogni correzione viene riportata nel registro del software (liftpilot/src/calc/norme.ts) e cambia insieme motore di calcolo, lista e relazione di calcolo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>Non trascrivere il testo delle norme in questo file: basta il valore e il numero di clausola.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Legenda</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>celle da compilare</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Verifica complessiva</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Ingegnere (nome e cognome)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Iscrizione all'albo</t>
+          <t>Ingegnere (nome e cognome)</t>
         </is>
       </c>
       <c r="B24" s="7" t="n"/>
@@ -697,7 +701,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Iscrizione all'albo</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -705,10 +709,18 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t>Firma</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -722,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N96"/>
+  <dimension ref="A1:N111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3277,43 +3289,43 @@
       <c r="M54" s="11" t="n"/>
       <c r="N54" s="11" t="n"/>
     </row>
-    <row r="55" ht="43" customHeight="1">
+    <row r="55" ht="199" customHeight="1">
       <c r="A55" s="10" t="n">
         <v>53</v>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Vano: accessibilità (DM 236/1989)</t>
+          <t>Vano: distanze in pianta</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Edifici residenziali nuovi: cabina e porta minime</t>
+          <t>Pareti all'ultimo piano e in testata diverse dal piano principale</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>cabina larga 950 mm e profonda 1300 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (non verificata)</t>
+          <t>negli edifici esistenti le pareti del vano all'ultima fermata e in testata possono stare altrove che al piano principale: cabina, guide e contrappeso restano a piombo; la cabina con soglie e operatori delle porte e il contrappeso passano ad almeno 25 mm dalle pareti spostate (meno: «Attenzione»; dentro la parete: «Non conforme»); le porte di piano dell'ultima fermata restano in linea con la cabina e la parete non entra nel loro spessore, i piedi delle guide e la staffa a ponte non entrano nelle pareti; le staffe arrivano alla parete dove sta (le staffe Panev si verificano anche lì); la distanza dalla parete di fronte all'entrata (voce distanze.parete.entrata) vale anche in testata</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-20:2020, 5.2.5.3.1 (parete di fronte all'entrata); il resto scelta del software</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>sintesi pubblicate del DM 236/1989 (disabili.com, studiomadera.it), fonti secondarie concordi</t>
+          <t>scelta del software: il margine di marcia va confermato con l'installatore</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>pareti in testata diverse dal piano principale</t>
         </is>
       </c>
       <c r="I55" s="11" t="n"/>
@@ -3334,12 +3346,12 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Edifici non residenziali nuovi: cabina e porta minime</t>
+          <t>Edifici residenziali nuovi: cabina e porta minime</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>cabina larga 1100 mm e profonda 1400 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (non verificata)</t>
+          <t>cabina larga 950 mm e profonda 1300 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (non verificata)</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
@@ -3380,12 +3392,12 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Adeguamento di edifici esistenti: cabina e porta minime</t>
+          <t>Edifici non residenziali nuovi: cabina e porta minime</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>cabina larga 800 mm e profonda 1200 mm, porta di 750 mm sul lato corto; piattaforma davanti alla porta 1,40 × 1,40 m (non verificata)</t>
+          <t>cabina larga 1100 mm e profonda 1400 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (non verificata)</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
@@ -3421,37 +3433,37 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Vano: porte</t>
+          <t>Vano: accessibilità (DM 236/1989)</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Ingombro della porta di piano lungo la parete del vano</t>
+          <t>Adeguamento di edifici esistenti: cabina e porta minime</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>telescopica a 2 ante: 1,5·L + 110 mm; centrale a 2 ante: 2·L + 110 mm (L = luce netta)</t>
+          <t>cabina larga 800 mm e profonda 1200 mm, porta di 750 mm sul lato corto; piattaforma davanti alla porta 1,40 × 1,40 m (non verificata)</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>dato del fornitore delle porte</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>valori tipici: scelta del software da confermare con il fornitore</t>
+          <t>sintesi pubblicate del DM 236/1989 (disabili.com, studiomadera.it), fonti secondarie concordi</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>ingombro della porta di piano</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I58" s="11" t="n"/>
@@ -3461,7 +3473,7 @@
       <c r="M58" s="11" t="n"/>
       <c r="N58" s="11" t="n"/>
     </row>
-    <row r="59" ht="30" customHeight="1">
+    <row r="59" ht="43" customHeight="1">
       <c r="A59" s="10" t="n">
         <v>57</v>
       </c>
@@ -3472,32 +3484,32 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Larghezza della cabina rispetto alla porta</t>
+          <t>Ingombro della porta di piano lungo la parete del vano</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>larghezza interna ≥ luce della porta + 50 mm; profondità interna ≥ 800 mm</t>
+          <t>telescopica a 2 ante: 1,5·L + 110 mm; centrale a 2 ante: 2·L + 110 mm (L = luce netta)</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>dato del fornitore delle porte</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
+          <t>valori tipici: scelta del software da confermare con il fornitore</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
           <t>scelta del software</t>
         </is>
       </c>
-      <c r="G59" s="10" t="inlineStr">
-        <is>
-          <t>scelta del software</t>
-        </is>
-      </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>la cabina entra nel vano</t>
+          <t>ingombro della porta di piano</t>
         </is>
       </c>
       <c r="I59" s="11" t="n"/>
@@ -3507,7 +3519,7 @@
       <c r="M59" s="11" t="n"/>
       <c r="N59" s="11" t="n"/>
     </row>
-    <row r="60" ht="108" customHeight="1">
+    <row r="60" ht="30" customHeight="1">
       <c r="A60" s="10" t="n">
         <v>58</v>
       </c>
@@ -3518,32 +3530,32 @@
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Vano porta di piano e operatore della porta di cabina</t>
+          <t>Larghezza della cabina rispetto alla porta</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>vano nel muro: luce netta + 2 × 50 mm di portale; operatore della porta di cabina lungo 1,5·L + 50 mm con porta telescopica (il lato di chiusura 25 mm oltre la luce) e 2·L + 60 mm con porta centrale, profondo 150 mm, dentro il vano; con due accessi adiacenti gli operatori non devono sovrapporsi all'angolo tra le porte (altrimenti «Attenzione»: operatori da scegliere con il fornitore)</t>
+          <t>larghezza interna ≥ luce della porta + 50 mm; profondità interna ≥ 800 mm</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>dato del fornitore delle porte</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>cataloghi 2SG FLY 2AT (1,5·A + 40) e 2AO (2·A + 20), Fermator 40/10 VF (1,5·PL + 40/50; 2·PL + 50; chiusura a 25 mm dalla luce), letti da estratti di ricerca: presi i valori più lunghi, da confermare con il fornitore</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>ingombro della porta di piano; ingombro della seconda porta di piano; operatori delle porte adiacenti</t>
+          <t>la cabina entra nel vano</t>
         </is>
       </c>
       <c r="I60" s="11" t="n"/>
@@ -3553,43 +3565,43 @@
       <c r="M60" s="11" t="n"/>
       <c r="N60" s="11" t="n"/>
     </row>
-    <row r="61" ht="108" customHeight="1">
+    <row r="61" ht="212" customHeight="1">
       <c r="A61" s="10" t="n">
         <v>59</v>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Vano: ingombri tipici</t>
+          <t>Vano: porte</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Ingombri tipici nel vano (modificabili su ogni progetto)</t>
+          <t>Vano porta di piano e operatore della porta di cabina</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>profondità della porta di piano 80 mm; gioco tra le soglie 30 mm; porta di cabina 80 mm; pareti della cabina 35 mm; guide e staffe della cabina 165 mm per lato; cabina–contrappeso 60 mm; spessore del contrappeso 140 mm; guide e staffe del contrappeso 80 mm; cabina–parete di fondo 60 mm; punta della guida–cabina 30 mm; contrappeso laterale–piede della guida di cabina 85 mm</t>
+          <t>vano nel muro: luce netta + 2 × 50 mm di portale; operatore della porta di cabina lungo 1,5·L + 50 mm con porta telescopica (il lato di chiusura 25 mm oltre la luce) e 2·L + 60 mm con porta centrale, profondo 150 mm, dentro il vano; con il fornitore scelto: 2SG FLY/LIKE 1,5·L + 40 mm (telescopica) e 2·L + 20 mm (centrale), Fermator 40/10 1,5·L + 50 mm e 2·L + 50 mm; con due accessi adiacenti gli operatori non devono sovrapporsi all'angolo tra le porte (altrimenti «Attenzione»: operatori da scegliere con il fornitore)</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>dati del costruttore di guide, porte e cabina</t>
+          <t>dato del fornitore delle porte</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>valori tipici: scelta del software</t>
+          <t>cataloghi 2SG FLY 2AT (1,5·A + 40) e 2AO (2·A + 20), Fermator 40/10 VF (1,5·PL + 40/50; 2·PL + 50; chiusura a 25 mm dalla luce), letti da estratti di ricerca: presi i valori più lunghi, da confermare con il fornitore. Le formule con + 40 danno esattamente la lunghezza delle soglie Fermator di catalogo (2 ante telescopiche, luce 900: 1390 mm; 2 ante centrali, luce 700: 1440 mm): potrebbero essere la soglia e non la trave dell'operatore. Wittur, Prisma, Dapa e CMM: lunghezza dell'operatore non trovata</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>la cabina entra nel vano</t>
+          <t>ingombro della porta di piano; ingombro della seconda porta di piano; operatori delle porte adiacenti</t>
         </is>
       </c>
       <c r="I61" s="11" t="n"/>
@@ -3599,28 +3611,28 @@
       <c r="M61" s="11" t="n"/>
       <c r="N61" s="11" t="n"/>
     </row>
-    <row r="62" ht="108" customHeight="1">
+    <row r="62" ht="95" customHeight="1">
       <c r="A62" s="10" t="n">
         <v>60</v>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Vano: ingombri tipici</t>
+          <t>Vano: porte</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Contrappeso laterale</t>
+          <t>Bottoniera di piano</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>tra la parete e la guida della cabina, centrato sull'asse delle guide di cabina, con le sue guide alle estremità (pattini 20 mm) e la guida di cabina su una staffa a ponte; a 40 mm dalle zone delle porte; lunghezza in pianta da 400 a 900 mm (sotto 400 mm: «Attenzione»); con il contrappeso sul fondo, al massimo la larghezza tra le guide della cabina</t>
+          <t>accanto a ogni porta di piano, sul pianerottolo: per default a destra guardando la porta, il centro della pulsantiera a 150 mm dal vano della porta e i pulsanti a 1100 mm dal pavimento; pulsantiera di 120 × 300 mm, sporgente 15 mm dal muro; lato, distanza e altezza modificabili su ogni progetto</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>altezze e distanze dagli angoli per l'accessibilità da verificare (DM 236/1989, UNI EN 81-70)</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
@@ -3635,7 +3647,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>lunghezza del contrappeso</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I62" s="11" t="n"/>
@@ -3645,33 +3657,33 @@
       <c r="M62" s="11" t="n"/>
       <c r="N62" s="11" t="n"/>
     </row>
-    <row r="63" ht="147" customHeight="1">
+    <row r="63" ht="160" customHeight="1">
       <c r="A63" s="10" t="n">
         <v>61</v>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Vano: ingombri tipici</t>
+          <t>Vano: porte</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Arcata a zaino (due accessi adiacenti a 90°)</t>
+          <t>Imbotti della porta di piano (sostituzione con una luce più piccola)</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>entrambe le guide di cabina sulla parete opposta all'accesso laterale, con le lame affacciate lungo la parete (il momento della cabina a sbalzo va sulle facce delle lame); piedi delle guide a 20 mm dentro la profondità della piattaforma; contrappeso tra le guide, contro la parete, con le sue guide alle estremità e i piedi a 70 mm da quelli delle guide di cabina (staffe); la cabina a 10 mm dalle bride che tengono i piedi delle guide sulle staffe (bride forgiate della misura della guida, con la piastra oltre il piede)</t>
+          <t>quando la porta nuova ha una luce più piccola del vano esistente tra i marmi, gli imbotti laterali (a sinistra e a destra guardando la porta dal pianerottolo) e quello superiore coprono la differenza: distanza tra i marmi = imbotto sinistro + luce + 2 × 50 mm di portale + imbotto destro; altezza sotto il marmo superiore = altezza della luce + 60 mm di architrave del portale + imbotto superiore; gli stessi imbotti per tutte le porte di piano, in lamiera sul filo del muro verso il pianerottolo, disegnati in pianta, in sezione e nel 3D</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>dato del fornitore delle porte (imbotti su misura)</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (principio: cataloghi di arcate a zaino); disposizione da confermare con il fornitore dell'arcata</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
@@ -3691,43 +3703,43 @@
       <c r="M63" s="11" t="n"/>
       <c r="N63" s="11" t="n"/>
     </row>
-    <row r="64" ht="82" customHeight="1">
+    <row r="64" ht="199" customHeight="1">
       <c r="A64" s="10" t="n">
         <v>62</v>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Spazi di rifugio sul tetto di cabina e in fossa</t>
+          <t>Ingombri tipici nel vano (modificabili su ogni progetto) — pacchetto porta di catalogo (porta di cabina + gioco tra le soglie + porta di piano), da wittur.com: Hydra 210 mm a 2 ante telescopiche e 180 mm a 2 ante centrali, Hydra 3000 180 e 130, Augusta EVO 190 e 110, Sematic 2000 C-MOD 185 e 117, Fineline 115 e 85; Sematic 2000 B 255 e 165 (cabina 90 e 45, gioco 30, piano 135 e 90, da una copia della brochure). Con le porte scelte, i tre ingombri vanno portati alla somma del fornitore (oggi 80 + 30 + 80 = 190 mm)</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>tipo 1 (in piedi) 400 × 500 mm in pianta, alto 2000 mm; tipo 2 (accucciato) 500 × 700 mm, alto 1000 mm; tipo 3 (disteso, solo in fossa) 700 × 1000 mm, alto 500 mm; in testata con la cabina nella posizione più alta, in fossa con la cabina sugli ammortizzatori compressi</t>
+          <t>profondità della porta di piano 80 mm; gioco tra le soglie 30 mm; porta di cabina 80 mm; pareti della cabina 35 mm; guide e staffe della cabina 165 mm per lato; cabina–contrappeso 60 mm; spessore del contrappeso 140 mm; guide e staffe del contrappeso 80 mm; cabina–parete di fondo 60 mm; punta della guida–cabina 30 mm; contrappeso laterale–piede della guida di cabina 85 mm</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1 (Tabella 3)</t>
+          <t>dati del costruttore di guide, porte e cabina</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>valori tipici: scelta del software</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>spazio di rifugio in testata; spazio di rifugio in fossa</t>
+          <t>la cabina entra nel vano</t>
         </is>
       </c>
       <c r="I64" s="11" t="n"/>
@@ -3737,43 +3749,43 @@
       <c r="M64" s="11" t="n"/>
       <c r="N64" s="11" t="n"/>
     </row>
-    <row r="65" ht="56" customHeight="1">
+    <row r="65" ht="108" customHeight="1">
       <c r="A65" s="10" t="n">
         <v>63</v>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Posizione più alta della cabina</t>
+          <t>Contrappeso laterale</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>contrappeso sugli ammortizzatori completamente compressi, più il salto 0,035·v² m (v velocità nominale)</t>
+          <t>tra la parete e la guida della cabina, centrato sull'asse delle guide di cabina, con le sue guide alle estremità (pattini 20 mm) e la guida di cabina su una staffa a ponte; a 40 mm dalle zone delle porte; lunghezza in pianta da 400 a 900 mm (sotto 400 mm: «Attenzione»); con il contrappeso sul fondo, al massimo la larghezza tra le guide della cabina</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.6.1 (Tabella 2)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>spazio di rifugio in testata; distanze libere dal soffitto</t>
+          <t>lunghezza del contrappeso</t>
         </is>
       </c>
       <c r="I65" s="11" t="n"/>
@@ -3783,43 +3795,43 @@
       <c r="M65" s="11" t="n"/>
       <c r="N65" s="11" t="n"/>
     </row>
-    <row r="66" ht="56" customHeight="1">
+    <row r="66" ht="147" customHeight="1">
       <c r="A66" s="10" t="n">
         <v>64</v>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Distanze libere dal soffitto con la cabina nella posizione più alta</t>
+          <t>Arcata a zaino (due accessi adiacenti a 90°)</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>≥ 500 mm sopra le apparecchiature sul tetto di cabina (operatore); ≥ 100 mm sopra pattini, attacchi delle funi e traversa dell'arcata; ≥ 300 mm sopra il corrimano della balaustra</t>
+          <t>entrambe le guide di cabina sulla parete opposta all'accesso laterale, con le lame affacciate lungo la parete (il momento della cabina a sbalzo va sulle facce delle lame); piedi delle guide a 20 mm dentro la profondità della piattaforma; contrappeso tra le guide, contro la parete, con le sue guide alle estremità e i piedi a 70 mm da quelli delle guide di cabina (staffe); la cabina a 10 mm dalle bride che tengono i piedi delle guide sulle staffe (bride forgiate della misura della guida, con la piastra oltre il piede)</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>scelta del software (principio: cataloghi di arcate a zaino); disposizione da confermare con il fornitore dell'arcata</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>distanze libere dal soffitto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I66" s="11" t="n"/>
@@ -3829,43 +3841,43 @@
       <c r="M66" s="11" t="n"/>
       <c r="N66" s="11" t="n"/>
     </row>
-    <row r="67" ht="56" customHeight="1">
+    <row r="67" ht="212" customHeight="1">
       <c r="A67" s="10" t="n">
         <v>65</v>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Distanze in fossa con la cabina sugli ammortizzatori compressi</t>
+          <t>Nicchie nelle pareti del vano</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>≥ 500 mm dal pavimento della fossa alle parti più basse della cabina; grembiule alto ≥ 750 mm sotto la soglia di cabina, con ≥ 100 mm liberi dal pavimento della fossa</t>
+          <t>contrappeso in nicchia: il contrappeso con le sue guide sta nella nicchia della parete su cui corre, con almeno 20 mm tra le guide e i fianchi della nicchia (con le staffe Panev, lo spazio della piastra del supporto dietro il piede di ogni guida); la distanza dalla parete si misura dal fondo della nicchia e la cabina guadagna la sua profondità, senza scendere sotto gli ingombri delle guide; luce del vano in nicchia: una nicchia alta 400 mm per lampada, le lampade 1500 mm sopra ogni piano e l'ultima a 80 mm sotto il solaio; canalina in nicchia: dal fondo della fossa al solaio; ogni nicchia dentro la sua parete, fuori dai telai delle porte di piano e dalle altre nicchie, con almeno 50 mm di muro dietro; altrimenti «Non conforme»</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.8.2 e 5.4.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>scelta del software; la resistenza della parete con la nicchia va verificata dal progettista</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>spazio di rifugio in fossa; grembiule sugli ammortizzatori compressi</t>
+          <t>nicchie nelle pareti</t>
         </is>
       </c>
       <c r="I67" s="11" t="n"/>
@@ -3875,43 +3887,43 @@
       <c r="M67" s="11" t="n"/>
       <c r="N67" s="11" t="n"/>
     </row>
-    <row r="68" ht="56" customHeight="1">
+    <row r="68" ht="134" customHeight="1">
       <c r="A68" s="10" t="n">
         <v>66</v>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Balaustra sul tetto di cabina</t>
+          <t>Staffe delle guide del contrappeso (catalogo Panev)</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>richiesta se la distanza libera dal tetto alla parete supera 300 mm: alta 700 mm fino a 500 mm di distanza, 1100 mm oltre</t>
+          <t>per default il supporto Panev SU o SD con la guida SG, la guida serrata sulla flangia della SG da due bride N1: il supporto più corto il cui campo stampato prende la distanza della guida dalla parete (o dal fondo della nicchia) e la cui piastra sta sulla parete: SU, SD 150 e SD 220 lunghi 160 mm da 45 a 155 mm (SD 220 da 50), lunghi 180 mm da 45 a 195 mm, lunghi 200 mm da 45 a 215 mm; nessuno adatto: «Non conforme» (si possono scegliere staffe generiche, da dimensionare a parte)</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.7.4</t>
+          <t>catalogo staffe Panev 2026, pp. 20-59</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>catalogo del costruttore (panev/docs/catalogo-staffe-panev-2026.pdf)</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>balaustra sul tetto di cabina</t>
+          <t>staffe del catalogo per le guide del contrappeso</t>
         </is>
       </c>
       <c r="I68" s="11" t="n"/>
@@ -3921,33 +3933,33 @@
       <c r="M68" s="11" t="n"/>
       <c r="N68" s="11" t="n"/>
     </row>
-    <row r="69" ht="56" customHeight="1">
+    <row r="69" ht="212" customHeight="1">
       <c r="A69" s="10" t="n">
         <v>67</v>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Superficie dove una persona può stare sul tetto di cabina</t>
+          <t>Limitatore di velocità e tenditore (pianta, locale macchina, 3D) — per le RQ-A Montanari 0,15–3,0 m/s è il campo della famiglia: il limite di ogni taglia va letto sul manuale; delle basi pubblicate non è detto quale lato stia nel piano della puleggia (il lato lungo è disegnato in quel piano, come nel LK200). Tenditore a leva: lungo 700 mm (quota «A» del PFB R4KE per LK200 in un listino di rivenditore, senza definizione), puleggia a 255 mm dalla cerniera e blocco di 150 × 185 mm: scelte del software; le masse di 22 e 44 kg sono quelle delle tabelle PFB</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>area continua ≥ 0,12 m² con il lato minore ≥ 250 mm (disegnata 400 × 300 mm); sopra di essa deve esserci l'altezza dello spazio di rifugio</t>
+          <t>per velocità il più piccolo PFB che la regge: LK200 (Ø 200, fune 6) fino a 1,48 m/s, LK250 fino a 1,74, LK300 fino a 2,93, R12BF fino a 4,00; oppure il modello scelto se regge la velocità: PFB (LX, LK, R1, R10BF) o Montanari (RQ-A 200, 250 e 300, NOR fino a 1,50 m/s, RG 200 fino a 0,30). Disegnati nelle proporzioni del LK200 (alto 370 mm, base 220 × 165) salvo LX120 alto 178, R10BF 488 su base 460 × 196, R12BF 524 su base 520 × 116, R1-LR 344 su base 285 × 80. Tenditore in fossa sulla guida di cabina: a leva con 22 kg (come PFB R4K) o verticale con 44 kg (come PFB R4R)</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.3</t>
+          <t>dati del fornitore del limitatore</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>pagine pfb.it e montanarigiulio.com, schede di elevatorequipment.co.uk (altezze, basi), estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
@@ -3967,7 +3979,7 @@
       <c r="M69" s="11" t="n"/>
       <c r="N69" s="11" t="n"/>
     </row>
-    <row r="70" ht="56" customHeight="1">
+    <row r="70" ht="82" customHeight="1">
       <c r="A70" s="10" t="n">
         <v>68</v>
       </c>
@@ -3978,17 +3990,17 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Schermo del contrappeso in fossa</t>
+          <t>Spazi di rifugio sul tetto di cabina e in fossa</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>dal punto più basso del contrappeso sugli ammortizzatori compressi fino ad almeno 2000 mm sopra il pavimento della fossa</t>
+          <t>tipo 1 (in piedi) 400 × 500 mm in pianta, alto 2000 mm; tipo 2 (accucciato) 500 × 700 mm, alto 1000 mm; tipo 3 (disteso, solo in fossa) 700 × 1000 mm, alto 500 mm; in testata con la cabina nella posizione più alta, in fossa con la cabina sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.5.1</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1 (Tabella 3)</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -4003,7 +4015,7 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>spazio di rifugio in testata; spazio di rifugio in fossa</t>
         </is>
       </c>
       <c r="I70" s="11" t="n"/>
@@ -4024,17 +4036,17 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori ad accumulo di energia lineari (molle)</t>
+          <t>Posizione più alta della cabina</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>ammessi fino a 1 m/s; corsa ≥ 0,135·v² m e comunque ≥ 65 mm; extracorsa della cabina e del contrappeso ≥ 0 (nessun minimo nella norma)</t>
+          <t>contrappeso sugli ammortizzatori completamente compressi, più il salto 0,035·v² m (v velocità nominale)</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2.2</t>
+          <t>UNI EN 81-20:2020, 5.2.5.6.1 (Tabella 2)</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -4049,7 +4061,7 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso; extracorsa di cabina e contrappeso</t>
+          <t>spazio di rifugio in testata; distanze libere dal soffitto</t>
         </is>
       </c>
       <c r="I71" s="11" t="n"/>
@@ -4059,28 +4071,28 @@
       <c r="M71" s="11" t="n"/>
       <c r="N71" s="11" t="n"/>
     </row>
-    <row r="72" ht="69" customHeight="1">
+    <row r="72" ht="56" customHeight="1">
       <c r="A72" s="10" t="n">
         <v>70</v>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Distanze libere dal soffitto con la cabina nella posizione più alta</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>altezza libera delle zone di lavoro ≥ 2100 mm (1800 mm sui percorsi); davanti al quadro una superficie libera profonda ≥ 700 mm e larga ≥ 500 mm o quanto il quadro; porta di accesso ≥ 600 × 2000 mm</t>
+          <t>≥ 500 mm sopra le apparecchiature sul tetto di cabina (operatore); ≥ 100 mm sopra pattini, attacchi delle funi e traversa dell'arcata; ≥ 300 mm sopra il corrimano della balaustra</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.6.3.2.1 e 5.2.3</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.2</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -4095,7 +4107,7 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>altezza del locale macchina; superficie libera davanti al quadro; porta del locale macchina</t>
+          <t>distanze libere dal soffitto</t>
         </is>
       </c>
       <c r="I72" s="11" t="n"/>
@@ -4105,28 +4117,28 @@
       <c r="M72" s="11" t="n"/>
       <c r="N72" s="11" t="n"/>
     </row>
-    <row r="73" ht="69" customHeight="1">
+    <row r="73" ht="56" customHeight="1">
       <c r="A73" s="10" t="n">
         <v>71</v>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Illuminazione del vano e del locale del macchinario</t>
+          <t>Distanze in fossa con la cabina sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>vano: illuminazione fissa di almeno 50 lux a 1 m sopra il tetto della cabina e sopra il pavimento della fossa, 20 lux altrove; locale del macchinario: almeno 200 lux al pavimento nelle zone di lavoro</t>
+          <t>≥ 500 mm dal pavimento della fossa alle parti più basse della cabina; grembiule alto ≥ 750 mm sotto la soglia di cabina, con ≥ 100 mm liberi dal pavimento della fossa</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.4</t>
+          <t>UNI EN 81-20:2020, 5.2.5.8.2 e 5.4.5</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -4141,7 +4153,7 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>spazio di rifugio in fossa; grembiule sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="I73" s="11" t="n"/>
@@ -4157,22 +4169,22 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Temperatura dei locali del macchinario e degli armadi</t>
+          <t>Balaustra sul tetto di cabina</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>temperatura ambiente mantenuta tra +5 °C e +40 °C: ipotesi della norma, da garantire nell'edificio</t>
+          <t>richiesta se la distanza libera dal tetto alla parete supera 300 mm: alta 700 mm fino a 500 mm di distanza, 1100 mm oltre</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, introduzione (ipotesi)</t>
+          <t>UNI EN 81-20:2020, 5.4.7.4</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -4187,7 +4199,7 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>balaustra sul tetto di cabina</t>
         </is>
       </c>
       <c r="I74" s="11" t="n"/>
@@ -4197,33 +4209,33 @@
       <c r="M74" s="11" t="n"/>
       <c r="N74" s="11" t="n"/>
     </row>
-    <row r="75" ht="108" customHeight="1">
+    <row r="75" ht="56" customHeight="1">
       <c r="A75" s="10" t="n">
         <v>73</v>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Carichi sul pavimento della fossa</t>
+          <t>Superficie dove una persona può stare sul tetto di cabina</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
+          <t>area continua ≥ 0,12 m² con il lato minore ≥ 250 mm (disegnata 400 × 300 mm, modificabile sulla pianta in testata); sopra di essa deve esserci l'altezza dello spazio di rifugio</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.8; UNI EN 81-50:2020, 5.10</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.3</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi; sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
@@ -4233,7 +4245,7 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>superficie per stare sul tetto di cabina</t>
         </is>
       </c>
       <c r="I75" s="11" t="n"/>
@@ -4243,33 +4255,33 @@
       <c r="M75" s="11" t="n"/>
       <c r="N75" s="11" t="n"/>
     </row>
-    <row r="76" ht="108" customHeight="1">
+    <row r="76" ht="69" customHeight="1">
       <c r="A76" s="10" t="n">
         <v>74</v>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Spinte sulle guide di cabina</t>
+          <t>Schermo del contrappeso in fossa</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
+          <t>dal punto più basso del contrappeso sugli ammortizzatori compressi fino ad almeno 2000 mm sopra il pavimento della fossa (altezza dello schermo modificabile sul progetto, mai sotto questo valore)</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.10</t>
+          <t>UNI EN 81-20:2020, 5.2.5.5.1</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
@@ -4279,7 +4291,7 @@
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>protezione del contrappeso in fossa</t>
         </is>
       </c>
       <c r="I76" s="11" t="n"/>
@@ -4289,43 +4301,43 @@
       <c r="M76" s="11" t="n"/>
       <c r="N76" s="11" t="n"/>
     </row>
-    <row r="77" ht="82" customHeight="1">
+    <row r="77" ht="69" customHeight="1">
       <c r="A77" s="10" t="n">
         <v>75</v>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Carico della macchina sulla soletta</t>
+          <t>Ammortizzatori ad accumulo di energia lineari (molle)</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
+          <t>ammessi fino a 1 m/s; corsa ≥ 0,135·v² m e comunque ≥ 65 mm; extracorsa della cabina e del contrappeso ≥ 0 (nessun minimo nella norma)</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.8.2 (accumulo di energia, caratteristica lineare; sottoclausola da verificare sul testo)</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>prassi di cantiere</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso; extracorsa di cabina e contrappeso</t>
         </is>
       </c>
       <c r="I77" s="11" t="n"/>
@@ -4335,43 +4347,43 @@
       <c r="M77" s="11" t="n"/>
       <c r="N77" s="11" t="n"/>
     </row>
-    <row r="78" ht="43" customHeight="1">
+    <row r="78" ht="121" customHeight="1">
       <c r="A78" s="10" t="n">
         <v>76</v>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Massa dei cavi flessibili</t>
+          <t>Ammortizzatori ad accumulo di energia non lineari (tamponi in poliuretano)</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
+          <t>ammessi fino a 1 m/s come le molle; nessuna corsa minima da formula: il campo di masse del certificato di esame di tipo per la velocità deve comprendere, per ogni tampone, la cabina vuota e a pieno carico (o il contrappeso); «completamente compresso» vuol dire compresso del 90 % dell'altezza, quindi la corsa è 0,9·H negli spazi in fossa e in testata; tampone tipico alti 80 mm (P+S Diepocell D, Ø da 80 a 220 mm; ACLA AUTAN XL)</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.8.2 (caratteristica non lineare) e UNI EN 81-50:2020, 5.5 (esame di tipo); sottoclausole da verificare sul testo</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
+          <t>cataloghi P+S Diepocell (wwlift.de), ACLA AUTAN XL (acla.de), Stingl (corsa al 90 %); estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso</t>
         </is>
       </c>
       <c r="I78" s="11" t="n"/>
@@ -4381,43 +4393,43 @@
       <c r="M78" s="11" t="n"/>
       <c r="N78" s="11" t="n"/>
     </row>
-    <row r="79" ht="82" customHeight="1">
+    <row r="79" ht="95" customHeight="1">
       <c r="A79" s="10" t="n">
         <v>77</v>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Lunghezze stimate nel foglio dei dati</t>
+          <t>Ammortizzatori a dissipazione di energia (idraulici)</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
+          <t>a ogni velocità; corsa ≥ 0,0674·v² m (arresto per gravità al 115 % della velocità nominale); la corsa ridotta con il controllo del rallentamento non è considerata; ammortizzatori tipici: Oleo LSB10 fino a 1 m/s, alto 222,2 mm con corsa 73,4 mm; LSB16 fino a 1,6 m/s, alto 485,5 mm con corsa 173,5 mm</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.8.2 (dissipazione di energia; sottoclausola da verificare sul testo)</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>stima del software, da sostituire con le misure di cantiere</t>
+          <t>catalogo Oleo LSB e SEB (oleo.co.uk), estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso</t>
         </is>
       </c>
       <c r="I79" s="11" t="n"/>
@@ -4427,43 +4439,43 @@
       <c r="M79" s="11" t="n"/>
       <c r="N79" s="11" t="n"/>
     </row>
-    <row r="80" ht="43" customHeight="1">
+    <row r="80" ht="69" customHeight="1">
       <c r="A80" s="10" t="n">
         <v>78</v>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Dimensioni proposte della cabina</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
+          <t>altezza libera delle zone di lavoro ≥ 2100 mm (1800 mm sui percorsi); davanti al quadro una superficie libera profonda ≥ 700 mm e larga ≥ 500 mm o quanto il quadro; porta di accesso ≥ 600 × 2000 mm</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.2.6.3.2.1 e 5.2.3</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>altezza del locale macchina; superficie libera davanti al quadro; porta del locale macchina</t>
         </is>
       </c>
       <c r="I80" s="11" t="n"/>
@@ -4473,43 +4485,43 @@
       <c r="M80" s="11" t="n"/>
       <c r="N80" s="11" t="n"/>
     </row>
-    <row r="81" ht="134" customHeight="1">
+    <row r="81" ht="69" customHeight="1">
       <c r="A81" s="10" t="n">
         <v>79</v>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Quote della pianta fissate a mano</t>
+          <t>Illuminazione del vano e del locale del macchinario</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme»</t>
+          <t>vano: illuminazione fissa di almeno 50 lux a 1 m sopra il tetto della cabina e sopra il pavimento della fossa, 20 lux altrove; locale del macchinario: almeno 200 lux al pavimento nelle zone di lavoro</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.2.1.4</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I81" s="11" t="n"/>
@@ -4519,38 +4531,38 @@
       <c r="M81" s="11" t="n"/>
       <c r="N81" s="11" t="n"/>
     </row>
-    <row r="82" ht="82" customHeight="1">
+    <row r="82" ht="56" customHeight="1">
       <c r="A82" s="10" t="n">
         <v>80</v>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Limiti del modello del vano</t>
+          <t>Temperatura dei locali del macchinario e degli armadi</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
+          <t>temperatura ambiente mantenuta tra +5 °C e +40 °C: ipotesi della norma, da garantire nell'edificio</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, introduzione (ipotesi)</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>limite del modello attuale</t>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
@@ -4565,38 +4577,38 @@
       <c r="M82" s="11" t="n"/>
       <c r="N82" s="11" t="n"/>
     </row>
-    <row r="83" ht="56" customHeight="1">
+    <row r="83" ht="199" customHeight="1">
       <c r="A83" s="10" t="n">
         <v>81</v>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Corsa</t>
+          <t>Basamento dell'argano</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
+          <t>su spessori di livellamento sotto gli appoggi (l'asse della puleggia dove lo mette il software), su telaio di due profilati sul pavimento (tipico UPN 200, alto quanto il profilato come i telai bassi universali), su due putrelle da muro a muro che possono stare sollevate dal pavimento (tipiche IPE 200, appoggio nei muri 150 mm), su piastre d'acciaio sotto gli appoggi (tipiche 20 mm) o su plinto in calcestruzzo (tipico 250 mm); tamponi antivibranti di 30 mm sotto gli appoggi, salvo sugli spessori; telaio e plinto 100 mm oltre il telaio dell'argano a ogni estremità; l'altezza del basamento porta l'asse della puleggia, che il calcolo (tratto di fune oltre la corsa) e il 3D seguono</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio); scelta del costruttore</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>dati dei piani inseriti</t>
+          <t>telaio basso universale per argano alto 200 mm (lift-store.it); tamponi antivibranti 25–30 mm (catalogo Donati); piastre di 20 mm e plinto di 250–300 mm nella pratica di installazione (fonti estere, da confermare); estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
@@ -4611,43 +4623,43 @@
       <c r="M83" s="11" t="n"/>
       <c r="N83" s="11" t="n"/>
     </row>
-    <row r="84" ht="56" customHeight="1">
+    <row r="84" ht="134" customHeight="1">
       <c r="A84" s="10" t="n">
         <v>82</v>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Portata e velocità</t>
+          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
+          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.2.1</t>
+          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E); DPR 1497/1963, art. 5 (carichi fissi più 1,5 volte il carico statico delle funi; freccia ≤ 1/1500 della luce libera: regola storica, da confermare)</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>progetto del vano</t>
+          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
         </is>
       </c>
       <c r="I84" s="11" t="n"/>
@@ -4657,38 +4669,38 @@
       <c r="M84" s="11" t="n"/>
       <c r="N84" s="11" t="n"/>
     </row>
-    <row r="85" ht="69" customHeight="1">
+    <row r="85" ht="108" customHeight="1">
       <c r="A85" s="10" t="n">
         <v>83</v>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
+          <t>Carichi sul pavimento della fossa</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
+          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8; UNI EN 81-50:2020, 5.10</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>scelta del software, senza fonte</t>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi; sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
@@ -4703,38 +4715,38 @@
       <c r="M85" s="11" t="n"/>
       <c r="N85" s="11" t="n"/>
     </row>
-    <row r="86" ht="82" customHeight="1">
+    <row r="86" ht="108" customHeight="1">
       <c r="A86" s="10" t="n">
         <v>84</v>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Fune oltre la corsa (L0)</t>
+          <t>Spinte sulle guide di cabina</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale (macchina in basso o senza locale: fino al soffitto del vano)</t>
+          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.10</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
+          <t>sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
@@ -4749,38 +4761,38 @@
       <c r="M86" s="11" t="n"/>
       <c r="N86" s="11" t="n"/>
     </row>
-    <row r="87" ht="147" customHeight="1">
+    <row r="87" ht="82" customHeight="1">
       <c r="A87" s="10" t="n">
         <v>85</v>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
+          <t>Carico della macchina sulla soletta</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
+          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>pianta del vano</t>
+          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>prassi di cantiere</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
@@ -4795,38 +4807,38 @@
       <c r="M87" s="11" t="n"/>
       <c r="N87" s="11" t="n"/>
     </row>
-    <row r="88" ht="56" customHeight="1">
+    <row r="88" ht="43" customHeight="1">
       <c r="A88" s="10" t="n">
         <v>86</v>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
+          <t>Massa dei cavi flessibili</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>corsa + testata: la macchina al livello del piano più basso, le pulegge sotto il soffitto del vano</t>
+          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano</t>
+          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
@@ -4841,33 +4853,33 @@
       <c r="M88" s="11" t="n"/>
       <c r="N88" s="11" t="n"/>
     </row>
-    <row r="89" ht="134" customHeight="1">
+    <row r="89" ht="121" customHeight="1">
       <c r="A89" s="10" t="n">
         <v>87</v>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
+          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
+          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 8</t>
+          <t>regola di montaggio indicata dal committente</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo</t>
+          <t>scelta del committente</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
@@ -4887,38 +4899,38 @@
       <c r="M89" s="11" t="n"/>
       <c r="N89" s="11" t="n"/>
     </row>
-    <row r="90" ht="69" customHeight="1">
+    <row r="90" ht="82" customHeight="1">
       <c r="A90" s="10" t="n">
         <v>88</v>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
+          <t>Lunghezze stimate nel foglio dei dati</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
+          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo (src/calc/model.ts)</t>
+          <t>stima del software, da sostituire con le misure di cantiere</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
@@ -4933,28 +4945,28 @@
       <c r="M90" s="11" t="n"/>
       <c r="N90" s="11" t="n"/>
     </row>
-    <row r="91" ht="56" customHeight="1">
+    <row r="91" ht="43" customHeight="1">
       <c r="A91" s="10" t="n">
         <v>89</v>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
+          <t>Dimensioni proposte della cabina</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
+          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
-          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
@@ -4979,28 +4991,28 @@
       <c r="M91" s="11" t="n"/>
       <c r="N91" s="11" t="n"/>
     </row>
-    <row r="92" ht="69" customHeight="1">
+    <row r="92" ht="199" customHeight="1">
       <c r="A92" s="10" t="n">
         <v>90</v>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Limite di aderenza mostrato durante la marcia</t>
+          <t>Quote della pianta fissate a mano</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
+          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8), quello del contrappeso dentro la lunghezza del contrappeso</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
@@ -5015,7 +5027,7 @@
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
         </is>
       </c>
       <c r="I92" s="11" t="n"/>
@@ -5025,23 +5037,23 @@
       <c r="M92" s="11" t="n"/>
       <c r="N92" s="11" t="n"/>
     </row>
-    <row r="93" ht="43" customHeight="1">
+    <row r="93" ht="82" customHeight="1">
       <c r="A93" s="10" t="n">
         <v>91</v>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Tempi delle porte</t>
+          <t>Limiti del modello del vano</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
+          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
@@ -5051,7 +5063,7 @@
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (solo animazione)</t>
+          <t>limite del modello attuale</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
@@ -5071,38 +5083,38 @@
       <c r="M93" s="11" t="n"/>
       <c r="N93" s="11" t="n"/>
     </row>
-    <row r="94" ht="69" customHeight="1">
+    <row r="94" ht="56" customHeight="1">
       <c r="A94" s="10" t="n">
         <v>92</v>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa; la verifica della corsa resta quella della sezione</t>
+          <t>Corsa</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>velocità d'urto 1,15 volte la nominale; ammortizzatore lineare con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa); la cabina e il contrappeso si separano all'urto</t>
+          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>sintesi della norma di costruttori e organismi notificati (fonti secondarie)</t>
+          <t>dati dei piani inseriti</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
@@ -5123,32 +5135,32 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Cabina bloccata: rotazione in salita</t>
+          <t>Portata e velocità</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
+          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2</t>
+          <t>UNI EN 81-20:2020, 5.4.2.1</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo; velocità scelta dal software</t>
+          <t>progetto del vano</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
@@ -5163,38 +5175,38 @@
       <c r="M95" s="11" t="n"/>
       <c r="N95" s="11" t="n"/>
     </row>
-    <row r="96" ht="43" customHeight="1">
+    <row r="96" ht="160" customHeight="1">
       <c r="A96" s="10" t="n">
         <v>94</v>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Passo di campionamento</t>
+          <t>Normativa di collaudo e parti sostituite o modificate — il testo delle UNI 10411 del 2024 non è stato letto: le verifiche per parte e i requisiti per la sostituzione del macchinario (edizione 2021: freno in due elementi, temporizzatore, velocità eccessiva in salita, arresto entro 1 m dalla macchina, interruzione se il freno non si apre) vanno confermati sul testo vigente</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
+          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>schede UNI delle norme (scopo, data 31/10/2024); schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); sintesi secondarie; ricerca, capitoli 2.4 e 6.6</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
@@ -5209,10 +5221,700 @@
       <c r="M96" s="11" t="n"/>
       <c r="N96" s="11" t="n"/>
     </row>
+    <row r="97" ht="69" customHeight="1">
+      <c r="A97" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software, senza fonte</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t>stima</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I97" s="11" t="n"/>
+      <c r="J97" s="11" t="n"/>
+      <c r="K97" s="11" t="n"/>
+      <c r="L97" s="11" t="n"/>
+      <c r="M97" s="11" t="n"/>
+      <c r="N97" s="11" t="n"/>
+    </row>
+    <row r="98" ht="82" customHeight="1">
+      <c r="A98" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>Fune oltre la corsa (L0)</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale (macchina in basso o senza locale: fino al soffitto del vano)</t>
+        </is>
+      </c>
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H98" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="n"/>
+      <c r="J98" s="11" t="n"/>
+      <c r="K98" s="11" t="n"/>
+      <c r="L98" s="11" t="n"/>
+      <c r="M98" s="11" t="n"/>
+      <c r="N98" s="11" t="n"/>
+    </row>
+    <row r="99" ht="147" customHeight="1">
+      <c r="A99" s="10" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, capitolo 5.3</t>
+        </is>
+      </c>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>pianta del vano</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="inlineStr">
+        <is>
+          <t>derivazione</t>
+        </is>
+      </c>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="n"/>
+      <c r="J99" s="11" t="n"/>
+      <c r="K99" s="11" t="n"/>
+      <c r="L99" s="11" t="n"/>
+      <c r="M99" s="11" t="n"/>
+      <c r="N99" s="11" t="n"/>
+    </row>
+    <row r="100" ht="160" customHeight="1">
+      <c r="A100" s="10" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
+        </is>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>geometria delle funi</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="inlineStr">
+        <is>
+          <t>derivazione</t>
+        </is>
+      </c>
+      <c r="H100" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="n"/>
+      <c r="J100" s="11" t="n"/>
+      <c r="K100" s="11" t="n"/>
+      <c r="L100" s="11" t="n"/>
+      <c r="M100" s="11" t="n"/>
+      <c r="N100" s="11" t="n"/>
+    </row>
+    <row r="101" ht="56" customHeight="1">
+      <c r="A101" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
+        </is>
+      </c>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>dati verticali del vano</t>
+        </is>
+      </c>
+      <c r="G101" s="10" t="inlineStr">
+        <is>
+          <t>derivazione</t>
+        </is>
+      </c>
+      <c r="H101" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="n"/>
+      <c r="J101" s="11" t="n"/>
+      <c r="K101" s="11" t="n"/>
+      <c r="L101" s="11" t="n"/>
+      <c r="M101" s="11" t="n"/>
+      <c r="N101" s="11" t="n"/>
+    </row>
+    <row r="102" ht="238" customHeight="1">
+      <c r="A102" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso o pilastro pieno fino al terreno (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
+        </is>
+      </c>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>geometria ricostruita dal software</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H102" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="n"/>
+      <c r="J102" s="11" t="n"/>
+      <c r="K102" s="11" t="n"/>
+      <c r="L102" s="11" t="n"/>
+      <c r="M102" s="11" t="n"/>
+      <c r="N102" s="11" t="n"/>
+    </row>
+    <row r="103" ht="160" customHeight="1">
+      <c r="A103" s="10" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>Macchina proposta dal catalogo di un costruttore — i dati di catalogo vengono da estratti dei motori di ricerca, non dai documenti: vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
+        </is>
+      </c>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>estratti delle pagine dei costruttori (SICOR, Sassi, Montanari, GEM, FAER) e dei rivenditori, 1° ottobre 2026</t>
+        </is>
+      </c>
+      <c r="G103" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H103" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="n"/>
+      <c r="J103" s="11" t="n"/>
+      <c r="K103" s="11" t="n"/>
+      <c r="L103" s="11" t="n"/>
+      <c r="M103" s="11" t="n"/>
+      <c r="N103" s="11" t="n"/>
+    </row>
+    <row r="104" ht="134" customHeight="1">
+      <c r="A104" s="10" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, capitolo 8</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>motore di calcolo</t>
+        </is>
+      </c>
+      <c r="G104" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H104" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="n"/>
+      <c r="J104" s="11" t="n"/>
+      <c r="K104" s="11" t="n"/>
+      <c r="L104" s="11" t="n"/>
+      <c r="M104" s="11" t="n"/>
+      <c r="N104" s="11" t="n"/>
+    </row>
+    <row r="105" ht="69" customHeight="1">
+      <c r="A105" s="10" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
+        </is>
+      </c>
+      <c r="E105" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
+        </is>
+      </c>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>motore di calcolo (src/calc/model.ts)</t>
+        </is>
+      </c>
+      <c r="G105" s="10" t="inlineStr">
+        <is>
+          <t>derivazione</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="n"/>
+      <c r="J105" s="11" t="n"/>
+      <c r="K105" s="11" t="n"/>
+      <c r="L105" s="11" t="n"/>
+      <c r="M105" s="11" t="n"/>
+      <c r="N105" s="11" t="n"/>
+    </row>
+    <row r="106" ht="56" customHeight="1">
+      <c r="A106" s="10" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
+        </is>
+      </c>
+      <c r="E106" s="10" t="inlineStr">
+        <is>
+          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
+        </is>
+      </c>
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="G106" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H106" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="n"/>
+      <c r="J106" s="11" t="n"/>
+      <c r="K106" s="11" t="n"/>
+      <c r="L106" s="11" t="n"/>
+      <c r="M106" s="11" t="n"/>
+      <c r="N106" s="11" t="n"/>
+    </row>
+    <row r="107" ht="69" customHeight="1">
+      <c r="A107" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>Limite di aderenza mostrato durante la marcia</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
+        </is>
+      </c>
+      <c r="E107" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-50:2020, 5.11.2.2</t>
+        </is>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="G107" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H107" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="n"/>
+      <c r="J107" s="11" t="n"/>
+      <c r="K107" s="11" t="n"/>
+      <c r="L107" s="11" t="n"/>
+      <c r="M107" s="11" t="n"/>
+      <c r="N107" s="11" t="n"/>
+    </row>
+    <row r="108" ht="43" customHeight="1">
+      <c r="A108" s="10" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>Tempi delle porte</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software (solo animazione)</t>
+        </is>
+      </c>
+      <c r="G108" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H108" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="n"/>
+      <c r="J108" s="11" t="n"/>
+      <c r="K108" s="11" t="n"/>
+      <c r="L108" s="11" t="n"/>
+      <c r="M108" s="11" t="n"/>
+      <c r="N108" s="11" t="n"/>
+    </row>
+    <row r="109" ht="108" customHeight="1">
+      <c r="A109" s="10" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
+        </is>
+      </c>
+      <c r="E109" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-20:2020, 5.8.2</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>sintesi della norma di costruttori e organismi notificati (fonti secondarie)</t>
+        </is>
+      </c>
+      <c r="G109" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H109" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I109" s="11" t="n"/>
+      <c r="J109" s="11" t="n"/>
+      <c r="K109" s="11" t="n"/>
+      <c r="L109" s="11" t="n"/>
+      <c r="M109" s="11" t="n"/>
+      <c r="N109" s="11" t="n"/>
+    </row>
+    <row r="110" ht="56" customHeight="1">
+      <c r="A110" s="10" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>Cabina bloccata: rotazione in salita</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-50:2020, 5.11.2</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>motore di calcolo; velocità scelta dal software</t>
+        </is>
+      </c>
+      <c r="G110" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H110" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I110" s="11" t="n"/>
+      <c r="J110" s="11" t="n"/>
+      <c r="K110" s="11" t="n"/>
+      <c r="L110" s="11" t="n"/>
+      <c r="M110" s="11" t="n"/>
+      <c r="N110" s="11" t="n"/>
+    </row>
+    <row r="111" ht="43" customHeight="1">
+      <c r="A111" s="10" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>Passo di campionamento</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
+        </is>
+      </c>
+      <c r="E111" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="G111" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H111" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="n"/>
+      <c r="J111" s="11" t="n"/>
+      <c r="K111" s="11" t="n"/>
+      <c r="L111" s="11" t="n"/>
+      <c r="M111" s="11" t="n"/>
+      <c r="N111" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N96"/>
+  <autoFilter ref="A1:N111"/>
   <dataValidations count="1">
-    <dataValidation sqref="I3:I96" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
+    <dataValidation sqref="I3:I111" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
       <formula1>"conforme,diverso,non applicabile"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5255,7 +5957,7 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$96,"da verificare")</f>
+        <f>COUNTIF(Voci!$G$3:$G$111,"da verificare")</f>
         <v/>
       </c>
     </row>
@@ -5266,7 +5968,7 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$96,"confermato")</f>
+        <f>COUNTIF(Voci!$G$3:$G$111,"confermato")</f>
         <v/>
       </c>
     </row>
@@ -5277,7 +5979,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$96,"scelta del software")</f>
+        <f>COUNTIF(Voci!$G$3:$G$111,"scelta del software")</f>
         <v/>
       </c>
     </row>
@@ -5288,7 +5990,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$96,"stima")</f>
+        <f>COUNTIF(Voci!$G$3:$G$111,"stima")</f>
         <v/>
       </c>
     </row>
@@ -5299,7 +6001,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$96,"derivazione")</f>
+        <f>COUNTIF(Voci!$G$3:$G$111,"derivazione")</f>
         <v/>
       </c>
     </row>
@@ -5310,7 +6012,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$96,"prassi di cantiere")</f>
+        <f>COUNTIF(Voci!$G$3:$G$111,"prassi di cantiere")</f>
         <v/>
       </c>
     </row>
@@ -5321,7 +6023,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTA(Voci!$A$3:$A$96)</f>
+        <f>COUNTA(Voci!$A$3:$A$111)</f>
         <v/>
       </c>
     </row>
@@ -5339,7 +6041,7 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$96,"conforme")</f>
+        <f>COUNTIF(Voci!$I$3:$I$111,"conforme")</f>
         <v/>
       </c>
     </row>
@@ -5350,7 +6052,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$96,"diverso")</f>
+        <f>COUNTIF(Voci!$I$3:$I$111,"diverso")</f>
         <v/>
       </c>
     </row>
@@ -5361,7 +6063,7 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$96,"non applicabile")</f>
+        <f>COUNTIF(Voci!$I$3:$I$111,"non applicabile")</f>
         <v/>
       </c>
     </row>
@@ -5372,14 +6074,14 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>COUNTBLANK(Voci!$I$3:$I$96)</f>
+        <f>COUNTBLANK(Voci!$I$3:$I$111)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Conteggi sulle righe 3–96 del foglio «Voci» (la riga 2 è l'esempio).</t>
+          <t>Conteggi sulle righe 3–111 del foglio «Voci» (la riga 2 è l'esempio).</t>
         </is>
       </c>
     </row>

--- a/liftpilot/docs/lista-verifica-normativa.xlsx
+++ b/liftpilot/docs/lista-verifica-normativa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Riepilogo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$112</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Voci'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -660,7 +660,7 @@
     <row r="18" ht="32" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Ogni correzione viene riportata nel registro del software (liftpilot/src/calc/norme.ts) e cambia insieme motore di calcolo, lista e relazione di calcolo.</t>
+          <t>Ogni correzione viene riportata nel registro del software (argano/src/calc/norme.ts) e cambia insieme motore di calcolo, lista e relazione di calcolo.</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N111"/>
+  <dimension ref="A1:N112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4623,7 +4623,7 @@
       <c r="M83" s="11" t="n"/>
       <c r="N83" s="11" t="n"/>
     </row>
-    <row r="84" ht="134" customHeight="1">
+    <row r="84" ht="147" customHeight="1">
       <c r="A84" s="10" t="n">
         <v>82</v>
       </c>
@@ -4634,32 +4634,32 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
+          <t>Telaio sotto l'argano di un costruttore</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
+          <t>l'argano di catalogo poggia con i suoi piedi su un telaio di due travi sotto le file di fori, con antivibranti alle estremità e 40 mm oltre l'argano a ogni estremità; il telaio è alto quanto serve per tenere l'asse della puleggia dove lo tiene l'argano generico del software, almeno 80 mm e con il bordo della puleggia 30 mm sopra il suo piano d'appoggio (gli argani compatti hanno la puleggia a sbalzo, sotto il piano dei piedi); se l'argano non lo permette l'asse sale e il calcolo segue</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E); DPR 1497/1963, art. 5 (carichi fissi più 1,5 volte il carico statico delle funi; freccia ≤ 1/1500 della luce libera: regola storica, da confermare)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
+          <t>quote dei piedi, dei fori e dell'asse della puleggia dalle schede tecniche del costruttore; altezza del telaio scelta dal software, da adattare al telaio fornito</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I84" s="11" t="n"/>
@@ -4669,33 +4669,33 @@
       <c r="M84" s="11" t="n"/>
       <c r="N84" s="11" t="n"/>
     </row>
-    <row r="85" ht="108" customHeight="1">
+    <row r="85" ht="134" customHeight="1">
       <c r="A85" s="10" t="n">
         <v>83</v>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Carichi sul pavimento della fossa</t>
+          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
+          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.8; UNI EN 81-50:2020, 5.10</t>
+          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E); DPR 1497/1963, art. 5 (carichi fissi più 1,5 volte il carico statico delle funi; freccia ≤ 1/1500 della luce libera: regola storica, da confermare)</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi; sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
+          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
         </is>
       </c>
       <c r="I85" s="11" t="n"/>
@@ -4726,22 +4726,22 @@
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Spinte sulle guide di cabina</t>
+          <t>Carichi sul pavimento della fossa</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
+          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.10</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8; UNI EN 81-50:2020, 5.10</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi; sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
@@ -4761,7 +4761,7 @@
       <c r="M86" s="11" t="n"/>
       <c r="N86" s="11" t="n"/>
     </row>
-    <row r="87" ht="82" customHeight="1">
+    <row r="87" ht="108" customHeight="1">
       <c r="A87" s="10" t="n">
         <v>85</v>
       </c>
@@ -4772,27 +4772,27 @@
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Carico della macchina sulla soletta</t>
+          <t>Spinte sulle guide di cabina</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
+          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.10</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
+          <t>sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>prassi di cantiere</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
@@ -4807,7 +4807,7 @@
       <c r="M87" s="11" t="n"/>
       <c r="N87" s="11" t="n"/>
     </row>
-    <row r="88" ht="43" customHeight="1">
+    <row r="88" ht="82" customHeight="1">
       <c r="A88" s="10" t="n">
         <v>86</v>
       </c>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Massa dei cavi flessibili</t>
+          <t>Carico della macchina sulla soletta</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
+          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
+          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>prassi di cantiere</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
@@ -4853,7 +4853,7 @@
       <c r="M88" s="11" t="n"/>
       <c r="N88" s="11" t="n"/>
     </row>
-    <row r="89" ht="121" customHeight="1">
+    <row r="89" ht="43" customHeight="1">
       <c r="A89" s="10" t="n">
         <v>87</v>
       </c>
@@ -4864,27 +4864,27 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
+          <t>Massa dei cavi flessibili</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
+          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>regola di montaggio indicata dal committente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>scelta del committente</t>
+          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       <c r="M89" s="11" t="n"/>
       <c r="N89" s="11" t="n"/>
     </row>
-    <row r="90" ht="82" customHeight="1">
+    <row r="90" ht="121" customHeight="1">
       <c r="A90" s="10" t="n">
         <v>88</v>
       </c>
@@ -4910,27 +4910,27 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Lunghezze stimate nel foglio dei dati</t>
+          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
+          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>regola di montaggio indicata dal committente</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>stima del software, da sostituire con le misure di cantiere</t>
+          <t>scelta del committente</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
@@ -4945,23 +4945,23 @@
       <c r="M90" s="11" t="n"/>
       <c r="N90" s="11" t="n"/>
     </row>
-    <row r="91" ht="43" customHeight="1">
+    <row r="91" ht="82" customHeight="1">
       <c r="A91" s="10" t="n">
         <v>89</v>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Dimensioni proposte della cabina</t>
+          <t>Lunghezze stimate nel foglio dei dati</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
+          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima del software, da sostituire con le misure di cantiere</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
@@ -4991,7 +4991,7 @@
       <c r="M91" s="11" t="n"/>
       <c r="N91" s="11" t="n"/>
     </row>
-    <row r="92" ht="199" customHeight="1">
+    <row r="92" ht="43" customHeight="1">
       <c r="A92" s="10" t="n">
         <v>90</v>
       </c>
@@ -5002,12 +5002,12 @@
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Quote della pianta fissate a mano</t>
+          <t>Dimensioni proposte della cabina</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8), quello del contrappeso dentro la lunghezza del contrappeso</t>
+          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I92" s="11" t="n"/>
@@ -5037,7 +5037,7 @@
       <c r="M92" s="11" t="n"/>
       <c r="N92" s="11" t="n"/>
     </row>
-    <row r="93" ht="82" customHeight="1">
+    <row r="93" ht="199" customHeight="1">
       <c r="A93" s="10" t="n">
         <v>91</v>
       </c>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Limiti del modello del vano</t>
+          <t>Quote della pianta fissate a mano</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
+          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8), quello del contrappeso dentro la lunghezza del contrappeso</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>limite del modello attuale</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
         </is>
       </c>
       <c r="I93" s="11" t="n"/>
@@ -5083,23 +5083,23 @@
       <c r="M93" s="11" t="n"/>
       <c r="N93" s="11" t="n"/>
     </row>
-    <row r="94" ht="56" customHeight="1">
+    <row r="94" ht="82" customHeight="1">
       <c r="A94" s="10" t="n">
         <v>92</v>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Corsa</t>
+          <t>Limiti del modello del vano</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
+          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>dati dei piani inseriti</t>
+          <t>limite del modello attuale</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
@@ -5140,22 +5140,22 @@
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Portata e velocità</t>
+          <t>Corsa</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
+          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.2.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>progetto del vano</t>
+          <t>dati dei piani inseriti</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
@@ -5175,7 +5175,7 @@
       <c r="M95" s="11" t="n"/>
       <c r="N95" s="11" t="n"/>
     </row>
-    <row r="96" ht="160" customHeight="1">
+    <row r="96" ht="56" customHeight="1">
       <c r="A96" s="10" t="n">
         <v>94</v>
       </c>
@@ -5186,27 +5186,27 @@
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Normativa di collaudo e parti sostituite o modificate — il testo delle UNI 10411 del 2024 non è stato letto: le verifiche per parte e i requisiti per la sostituzione del macchinario (edizione 2021: freno in due elementi, temporizzatore, velocità eccessiva in salita, arresto entro 1 m dalla macchina, interruzione se il freno non si apre) vanno confermati sul testo vigente</t>
+          <t>Portata e velocità</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software</t>
+          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
+          <t>UNI EN 81-20:2020, 5.4.2.1</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>schede UNI delle norme (scopo, data 31/10/2024); schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); sintesi secondarie; ricerca, capitoli 2.4 e 6.6</t>
+          <t>progetto del vano</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
@@ -5221,7 +5221,7 @@
       <c r="M96" s="11" t="n"/>
       <c r="N96" s="11" t="n"/>
     </row>
-    <row r="97" ht="69" customHeight="1">
+    <row r="97" ht="160" customHeight="1">
       <c r="A97" s="10" t="n">
         <v>95</v>
       </c>
@@ -5232,27 +5232,27 @@
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
+          <t>Normativa di collaudo e parti sostituite o modificate — il testo delle UNI 10411 del 2024 non è stato letto: le verifiche per parte e i requisiti per la sostituzione del macchinario (edizione 2021: freno in due elementi, temporizzatore, velocità eccessiva in salita, arresto entro 1 m dalla macchina, interruzione se il freno non si apre) vanno confermati sul testo vigente</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
+          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
+          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>scelta del software, senza fonte</t>
+          <t>schede UNI delle norme (scopo, data 31/10/2024); schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); sintesi secondarie; ricerca, capitoli 2.4 e 6.6</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H97" s="10" t="inlineStr">
@@ -5267,7 +5267,7 @@
       <c r="M97" s="11" t="n"/>
       <c r="N97" s="11" t="n"/>
     </row>
-    <row r="98" ht="82" customHeight="1">
+    <row r="98" ht="69" customHeight="1">
       <c r="A98" s="10" t="n">
         <v>96</v>
       </c>
@@ -5278,27 +5278,27 @@
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Fune oltre la corsa (L0)</t>
+          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale (macchina in basso o senza locale: fino al soffitto del vano)</t>
+          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
+          <t>scelta del software, senza fonte</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
@@ -5313,7 +5313,7 @@
       <c r="M98" s="11" t="n"/>
       <c r="N98" s="11" t="n"/>
     </row>
-    <row r="99" ht="147" customHeight="1">
+    <row r="99" ht="82" customHeight="1">
       <c r="A99" s="10" t="n">
         <v>97</v>
       </c>
@@ -5324,27 +5324,27 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
+          <t>Fune oltre la corsa (L0)</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
+          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale (macchina in basso o senza locale: fino al soffitto del vano)</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>pianta del vano</t>
+          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H99" s="10" t="inlineStr">
@@ -5359,7 +5359,7 @@
       <c r="M99" s="11" t="n"/>
       <c r="N99" s="11" t="n"/>
     </row>
-    <row r="100" ht="160" customHeight="1">
+    <row r="100" ht="147" customHeight="1">
       <c r="A100" s="10" t="n">
         <v>98</v>
       </c>
@@ -5370,22 +5370,22 @@
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
+          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
+          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
+          <t>ricerca, capitolo 5.3</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>geometria delle funi</t>
+          <t>pianta del vano</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
@@ -5405,7 +5405,7 @@
       <c r="M100" s="11" t="n"/>
       <c r="N100" s="11" t="n"/>
     </row>
-    <row r="101" ht="56" customHeight="1">
+    <row r="101" ht="160" customHeight="1">
       <c r="A101" s="10" t="n">
         <v>99</v>
       </c>
@@ -5416,22 +5416,22 @@
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
+          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
+          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
+          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano</t>
+          <t>geometria delle funi</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
@@ -5451,7 +5451,7 @@
       <c r="M101" s="11" t="n"/>
       <c r="N101" s="11" t="n"/>
     </row>
-    <row r="102" ht="238" customHeight="1">
+    <row r="102" ht="56" customHeight="1">
       <c r="A102" s="10" t="n">
         <v>100</v>
       </c>
@@ -5462,27 +5462,27 @@
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso o pilastro pieno fino al terreno (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori</t>
+          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
+          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
+          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>geometria ricostruita dal software</t>
+          <t>dati verticali del vano</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H102" s="10" t="inlineStr">
@@ -5497,7 +5497,7 @@
       <c r="M102" s="11" t="n"/>
       <c r="N102" s="11" t="n"/>
     </row>
-    <row r="103" ht="160" customHeight="1">
+    <row r="103" ht="238" customHeight="1">
       <c r="A103" s="10" t="n">
         <v>101</v>
       </c>
@@ -5508,27 +5508,27 @@
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta dal catalogo di un costruttore — i dati di catalogo vengono da estratti dei motori di ricerca, non dai documenti: vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
+          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso o pilastro pieno fino al terreno (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo</t>
+          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
+          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>estratti delle pagine dei costruttori (SICOR, Sassi, Montanari, GEM, FAER) e dei rivenditori, 1° ottobre 2026</t>
+          <t>geometria ricostruita dal software</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
@@ -5543,7 +5543,7 @@
       <c r="M103" s="11" t="n"/>
       <c r="N103" s="11" t="n"/>
     </row>
-    <row r="104" ht="134" customHeight="1">
+    <row r="104" ht="186" customHeight="1">
       <c r="A104" s="10" t="n">
         <v>102</v>
       </c>
@@ -5554,27 +5554,27 @@
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
+          <t>Macchina proposta dal catalogo di un costruttore — i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
+          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo; i disegni e il 3D mostrano l'argano SICOR com'è (ingombri, piedi e fori, asse della puleggia, P ed E della scheda), sul telaio del software</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 8</t>
+          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo</t>
+          <t>SICOR: schede tecniche 2025 e modelli CAD scaricati da sicoritaly.com il 2 ottobre 2026 (solo le quote); Sassi, Montanari, GEM, FAER: estratti delle pagine dei costruttori e dei rivenditori, 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr">
@@ -5589,38 +5589,38 @@
       <c r="M104" s="11" t="n"/>
       <c r="N104" s="11" t="n"/>
     </row>
-    <row r="105" ht="69" customHeight="1">
+    <row r="105" ht="134" customHeight="1">
       <c r="A105" s="10" t="n">
         <v>103</v>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
+          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
+          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
         </is>
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
+          <t>ricerca, capitolo 8</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo (src/calc/model.ts)</t>
+          <t>motore di calcolo</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
@@ -5635,7 +5635,7 @@
       <c r="M105" s="11" t="n"/>
       <c r="N105" s="11" t="n"/>
     </row>
-    <row r="106" ht="56" customHeight="1">
+    <row r="106" ht="69" customHeight="1">
       <c r="A106" s="10" t="n">
         <v>104</v>
       </c>
@@ -5646,27 +5646,27 @@
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
+          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
+          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
+          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>motore di calcolo (src/calc/model.ts)</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
@@ -5681,7 +5681,7 @@
       <c r="M106" s="11" t="n"/>
       <c r="N106" s="11" t="n"/>
     </row>
-    <row r="107" ht="69" customHeight="1">
+    <row r="107" ht="56" customHeight="1">
       <c r="A107" s="10" t="n">
         <v>105</v>
       </c>
@@ -5692,17 +5692,17 @@
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Limite di aderenza mostrato durante la marcia</t>
+          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
+          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.2</t>
+          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
@@ -5727,7 +5727,7 @@
       <c r="M107" s="11" t="n"/>
       <c r="N107" s="11" t="n"/>
     </row>
-    <row r="108" ht="43" customHeight="1">
+    <row r="108" ht="69" customHeight="1">
       <c r="A108" s="10" t="n">
         <v>106</v>
       </c>
@@ -5738,22 +5738,22 @@
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Tempi delle porte</t>
+          <t>Limite di aderenza mostrato durante la marcia</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
+          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.2.2</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (solo animazione)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
@@ -5773,7 +5773,7 @@
       <c r="M108" s="11" t="n"/>
       <c r="N108" s="11" t="n"/>
     </row>
-    <row r="109" ht="108" customHeight="1">
+    <row r="109" ht="43" customHeight="1">
       <c r="A109" s="10" t="n">
         <v>107</v>
       </c>
@@ -5784,27 +5784,27 @@
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione</t>
+          <t>Tempi delle porte</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
+          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
         </is>
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>sintesi della norma di costruttori e organismi notificati (fonti secondarie)</t>
+          <t>scelta del software (solo animazione)</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H109" s="10" t="inlineStr">
@@ -5819,7 +5819,7 @@
       <c r="M109" s="11" t="n"/>
       <c r="N109" s="11" t="n"/>
     </row>
-    <row r="110" ht="56" customHeight="1">
+    <row r="110" ht="108" customHeight="1">
       <c r="A110" s="10" t="n">
         <v>108</v>
       </c>
@@ -5830,27 +5830,27 @@
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Cabina bloccata: rotazione in salita</t>
+          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
+          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2</t>
+          <t>UNI EN 81-20:2020, 5.8.2</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo; velocità scelta dal software</t>
+          <t>sintesi della norma di costruttori e organismi notificati (fonti secondarie)</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
@@ -5865,7 +5865,7 @@
       <c r="M110" s="11" t="n"/>
       <c r="N110" s="11" t="n"/>
     </row>
-    <row r="111" ht="43" customHeight="1">
+    <row r="111" ht="56" customHeight="1">
       <c r="A111" s="10" t="n">
         <v>109</v>
       </c>
@@ -5876,22 +5876,22 @@
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Passo di campionamento</t>
+          <t>Cabina bloccata: rotazione in salita</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
+          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.2</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>motore di calcolo; velocità scelta dal software</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
@@ -5911,10 +5911,56 @@
       <c r="M111" s="11" t="n"/>
       <c r="N111" s="11" t="n"/>
     </row>
+    <row r="112" ht="43" customHeight="1">
+      <c r="A112" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>Passo di campionamento</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
+        </is>
+      </c>
+      <c r="E112" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="G112" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H112" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I112" s="11" t="n"/>
+      <c r="J112" s="11" t="n"/>
+      <c r="K112" s="11" t="n"/>
+      <c r="L112" s="11" t="n"/>
+      <c r="M112" s="11" t="n"/>
+      <c r="N112" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N111"/>
+  <autoFilter ref="A1:N112"/>
   <dataValidations count="1">
-    <dataValidation sqref="I3:I111" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
+    <dataValidation sqref="I3:I112" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
       <formula1>"conforme,diverso,non applicabile"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5957,7 +6003,7 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$111,"da verificare")</f>
+        <f>COUNTIF(Voci!$G$3:$G$112,"da verificare")</f>
         <v/>
       </c>
     </row>
@@ -5968,7 +6014,7 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$111,"confermato")</f>
+        <f>COUNTIF(Voci!$G$3:$G$112,"confermato")</f>
         <v/>
       </c>
     </row>
@@ -5979,7 +6025,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$111,"scelta del software")</f>
+        <f>COUNTIF(Voci!$G$3:$G$112,"scelta del software")</f>
         <v/>
       </c>
     </row>
@@ -5990,7 +6036,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$111,"stima")</f>
+        <f>COUNTIF(Voci!$G$3:$G$112,"stima")</f>
         <v/>
       </c>
     </row>
@@ -6001,7 +6047,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$111,"derivazione")</f>
+        <f>COUNTIF(Voci!$G$3:$G$112,"derivazione")</f>
         <v/>
       </c>
     </row>
@@ -6012,7 +6058,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$111,"prassi di cantiere")</f>
+        <f>COUNTIF(Voci!$G$3:$G$112,"prassi di cantiere")</f>
         <v/>
       </c>
     </row>
@@ -6023,7 +6069,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTA(Voci!$A$3:$A$111)</f>
+        <f>COUNTA(Voci!$A$3:$A$112)</f>
         <v/>
       </c>
     </row>
@@ -6041,7 +6087,7 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$111,"conforme")</f>
+        <f>COUNTIF(Voci!$I$3:$I$112,"conforme")</f>
         <v/>
       </c>
     </row>
@@ -6052,7 +6098,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$111,"diverso")</f>
+        <f>COUNTIF(Voci!$I$3:$I$112,"diverso")</f>
         <v/>
       </c>
     </row>
@@ -6063,7 +6109,7 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$111,"non applicabile")</f>
+        <f>COUNTIF(Voci!$I$3:$I$112,"non applicabile")</f>
         <v/>
       </c>
     </row>
@@ -6074,14 +6120,14 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>COUNTBLANK(Voci!$I$3:$I$111)</f>
+        <f>COUNTBLANK(Voci!$I$3:$I$112)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Conteggi sulle righe 3–111 del foglio «Voci» (la riga 2 è l'esempio).</t>
+          <t>Conteggi sulle righe 3–112 del foglio «Voci» (la riga 2 è l'esempio).</t>
         </is>
       </c>
     </row>

--- a/liftpilot/docs/lista-verifica-normativa.xlsx
+++ b/liftpilot/docs/lista-verifica-normativa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Riepilogo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$113</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Voci'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N112"/>
+  <dimension ref="A1:N113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3611,7 +3611,7 @@
       <c r="M61" s="11" t="n"/>
       <c r="N61" s="11" t="n"/>
     </row>
-    <row r="62" ht="95" customHeight="1">
+    <row r="62" ht="134" customHeight="1">
       <c r="A62" s="10" t="n">
         <v>60</v>
       </c>
@@ -3622,32 +3622,32 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Bottoniera di piano</t>
+          <t>Porta di piano spostata rispetto alla porta di cabina (disassamento) — nel 3D la leva della serratura con i rulli resta in linea con l'accoppiatore della porta di cabina: con il disassamento va montata spostata sull'anta della porta di piano (da concordare con il fornitore delle porte)</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>accanto a ogni porta di piano, sul pianerottolo: per default a destra guardando la porta, il centro della pulsantiera a 150 mm dal vano della porta e i pulsanti a 1100 mm dal pavimento; pulsantiera di 120 × 300 mm, sporgente 15 mm dal muro; lato, distanza e altezza modificabili su ogni progetto</t>
+          <t>la luce netta della porta di piano sporge al massimo 50 mm per lato oltre quella della porta di cabina: con la stessa luce, disassamento ≤ 50 mm (oltre: «Non conforme»); lo stesso spostamento a tutti i piani, per ciascun accesso, con il vano nel muro, il portale, gli imbotti, la soglia sulle staffe e la bottoniera della porta di piano; il passaggio libero è la parte comune delle due luci (luce − disassamento), ed è quello verificato per l'accessibilità (DM 236/1989)</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>altezze e distanze dagli angoli per l'accessibilità da verificare (DM 236/1989, UNI EN 81-70)</t>
+          <t>UNI EN 81-20:2020, 5.3.2.2 (larghezza degli accessi; numero della clausola da confermare sul testo)</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>fonti secondarie: sintesi dei requisiti EN 81-20 dei costruttori letta tramite motore di ricerca (i documenti non erano raggiungibili); che la 5.3.2.1 sia l'altezza libera degli accessi (≥ 2 m) lo confermano le interpretazioni VDMA della serie EN 81 (DAfA 104, 16.09.2020)</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>disassamento della porta di piano A; disassamento della porta di piano B</t>
         </is>
       </c>
       <c r="I62" s="11" t="n"/>
@@ -3657,7 +3657,7 @@
       <c r="M62" s="11" t="n"/>
       <c r="N62" s="11" t="n"/>
     </row>
-    <row r="63" ht="160" customHeight="1">
+    <row r="63" ht="95" customHeight="1">
       <c r="A63" s="10" t="n">
         <v>61</v>
       </c>
@@ -3668,17 +3668,17 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Imbotti della porta di piano (sostituzione con una luce più piccola)</t>
+          <t>Bottoniera di piano</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>quando la porta nuova ha una luce più piccola del vano esistente tra i marmi, gli imbotti laterali (a sinistra e a destra guardando la porta dal pianerottolo) e quello superiore coprono la differenza: distanza tra i marmi = imbotto sinistro + luce + 2 × 50 mm di portale + imbotto destro; altezza sotto il marmo superiore = altezza della luce + 60 mm di architrave del portale + imbotto superiore; gli stessi imbotti per tutte le porte di piano, in lamiera sul filo del muro verso il pianerottolo, disegnati in pianta, in sezione e nel 3D</t>
+          <t>accanto a ogni porta di piano, sul pianerottolo: per default a destra guardando la porta, il centro della pulsantiera a 150 mm dal vano della porta e i pulsanti a 1100 mm dal pavimento; pulsantiera di 120 × 300 mm, sporgente 15 mm dal muro; lato, distanza e altezza modificabili su ogni progetto</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>dato del fornitore delle porte (imbotti su misura)</t>
+          <t>altezze e distanze dagli angoli per l'accessibilità da verificare (DM 236/1989, UNI EN 81-70)</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
@@ -3703,33 +3703,33 @@
       <c r="M63" s="11" t="n"/>
       <c r="N63" s="11" t="n"/>
     </row>
-    <row r="64" ht="199" customHeight="1">
+    <row r="64" ht="160" customHeight="1">
       <c r="A64" s="10" t="n">
         <v>62</v>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Vano: ingombri tipici</t>
+          <t>Vano: porte</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Ingombri tipici nel vano (modificabili su ogni progetto) — pacchetto porta di catalogo (porta di cabina + gioco tra le soglie + porta di piano), da wittur.com: Hydra 210 mm a 2 ante telescopiche e 180 mm a 2 ante centrali, Hydra 3000 180 e 130, Augusta EVO 190 e 110, Sematic 2000 C-MOD 185 e 117, Fineline 115 e 85; Sematic 2000 B 255 e 165 (cabina 90 e 45, gioco 30, piano 135 e 90, da una copia della brochure). Con le porte scelte, i tre ingombri vanno portati alla somma del fornitore (oggi 80 + 30 + 80 = 190 mm)</t>
+          <t>Imbotti della porta di piano (sostituzione con una luce più piccola)</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>profondità della porta di piano 80 mm; gioco tra le soglie 30 mm; porta di cabina 80 mm; pareti della cabina 35 mm; guide e staffe della cabina 165 mm per lato; cabina–contrappeso 60 mm; spessore del contrappeso 140 mm; guide e staffe del contrappeso 80 mm; cabina–parete di fondo 60 mm; punta della guida–cabina 30 mm; contrappeso laterale–piede della guida di cabina 85 mm</t>
+          <t>quando la porta nuova ha una luce più piccola del vano esistente tra i marmi, gli imbotti laterali (a sinistra e a destra guardando la porta dal pianerottolo) e quello superiore coprono la differenza: distanza tra i marmi = imbotto sinistro + luce + 2 × 50 mm di portale + imbotto destro; altezza sotto il marmo superiore = altezza della luce + 60 mm di architrave del portale + imbotto superiore; gli stessi imbotti per tutte le porte di piano, in lamiera sul filo del muro verso il pianerottolo, disegnati in pianta, in sezione e nel 3D</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>dati del costruttore di guide, porte e cabina</t>
+          <t>dato del fornitore delle porte (imbotti su misura)</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>valori tipici: scelta del software</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>la cabina entra nel vano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I64" s="11" t="n"/>
@@ -3749,7 +3749,7 @@
       <c r="M64" s="11" t="n"/>
       <c r="N64" s="11" t="n"/>
     </row>
-    <row r="65" ht="108" customHeight="1">
+    <row r="65" ht="199" customHeight="1">
       <c r="A65" s="10" t="n">
         <v>63</v>
       </c>
@@ -3760,32 +3760,32 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Contrappeso laterale</t>
+          <t>Ingombri tipici nel vano (modificabili su ogni progetto) — pacchetto porta di catalogo (porta di cabina + gioco tra le soglie + porta di piano), da wittur.com: Hydra 210 mm a 2 ante telescopiche e 180 mm a 2 ante centrali, Hydra 3000 180 e 130, Augusta EVO 190 e 110, Sematic 2000 C-MOD 185 e 117, Fineline 115 e 85; Sematic 2000 B 255 e 165 (cabina 90 e 45, gioco 30, piano 135 e 90, da una copia della brochure). Con le porte scelte, i tre ingombri vanno portati alla somma del fornitore (oggi 80 + 30 + 80 = 190 mm)</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>tra la parete e la guida della cabina, centrato sull'asse delle guide di cabina, con le sue guide alle estremità (pattini 20 mm) e la guida di cabina su una staffa a ponte; a 40 mm dalle zone delle porte; lunghezza in pianta da 400 a 900 mm (sotto 400 mm: «Attenzione»); con il contrappeso sul fondo, al massimo la larghezza tra le guide della cabina</t>
+          <t>profondità della porta di piano 80 mm; gioco tra le soglie 30 mm; porta di cabina 80 mm; pareti della cabina 35 mm; guide e staffe della cabina 165 mm per lato; cabina–contrappeso 60 mm; spessore del contrappeso 140 mm; guide e staffe del contrappeso 80 mm; cabina–parete di fondo 60 mm; punta della guida–cabina 30 mm; contrappeso laterale–piede della guida di cabina 85 mm</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>dati del costruttore di guide, porte e cabina</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
+          <t>valori tipici: scelta del software</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
           <t>scelta del software</t>
         </is>
       </c>
-      <c r="G65" s="10" t="inlineStr">
-        <is>
-          <t>scelta del software</t>
-        </is>
-      </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>lunghezza del contrappeso</t>
+          <t>la cabina entra nel vano</t>
         </is>
       </c>
       <c r="I65" s="11" t="n"/>
@@ -3795,7 +3795,7 @@
       <c r="M65" s="11" t="n"/>
       <c r="N65" s="11" t="n"/>
     </row>
-    <row r="66" ht="147" customHeight="1">
+    <row r="66" ht="108" customHeight="1">
       <c r="A66" s="10" t="n">
         <v>64</v>
       </c>
@@ -3806,12 +3806,12 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Arcata a zaino (due accessi adiacenti a 90°)</t>
+          <t>Contrappeso laterale</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>entrambe le guide di cabina sulla parete opposta all'accesso laterale, con le lame affacciate lungo la parete (il momento della cabina a sbalzo va sulle facce delle lame); piedi delle guide a 20 mm dentro la profondità della piattaforma; contrappeso tra le guide, contro la parete, con le sue guide alle estremità e i piedi a 70 mm da quelli delle guide di cabina (staffe); la cabina a 10 mm dalle bride che tengono i piedi delle guide sulle staffe (bride forgiate della misura della guida, con la piastra oltre il piede)</t>
+          <t>tra la parete e la guida della cabina, centrato sull'asse delle guide di cabina, con le sue guide alle estremità (pattini 20 mm) e la guida di cabina su una staffa a ponte; a 40 mm dalle zone delle porte; lunghezza in pianta da 400 a 900 mm (sotto 400 mm: «Attenzione»); con il contrappeso sul fondo, al massimo la larghezza tra le guide della cabina</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (principio: cataloghi di arcate a zaino); disposizione da confermare con il fornitore dell'arcata</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>lunghezza del contrappeso</t>
         </is>
       </c>
       <c r="I66" s="11" t="n"/>
@@ -3841,7 +3841,7 @@
       <c r="M66" s="11" t="n"/>
       <c r="N66" s="11" t="n"/>
     </row>
-    <row r="67" ht="212" customHeight="1">
+    <row r="67" ht="147" customHeight="1">
       <c r="A67" s="10" t="n">
         <v>65</v>
       </c>
@@ -3852,12 +3852,12 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Nicchie nelle pareti del vano</t>
+          <t>Arcata a zaino (due accessi adiacenti a 90°)</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>contrappeso in nicchia: il contrappeso con le sue guide sta nella nicchia della parete su cui corre, con almeno 20 mm tra le guide e i fianchi della nicchia (con le staffe Panev, lo spazio della piastra del supporto dietro il piede di ogni guida); la distanza dalla parete si misura dal fondo della nicchia e la cabina guadagna la sua profondità, senza scendere sotto gli ingombri delle guide; luce del vano in nicchia: una nicchia alta 400 mm per lampada, le lampade 1500 mm sopra ogni piano e l'ultima a 80 mm sotto il solaio; canalina in nicchia: dal fondo della fossa al solaio; ogni nicchia dentro la sua parete, fuori dai telai delle porte di piano e dalle altre nicchie, con almeno 50 mm di muro dietro; altrimenti «Non conforme»</t>
+          <t>entrambe le guide di cabina sulla parete opposta all'accesso laterale, con le lame affacciate lungo la parete (il momento della cabina a sbalzo va sulle facce delle lame); piedi delle guide a 20 mm dentro la profondità della piattaforma; contrappeso tra le guide, contro la parete, con le sue guide alle estremità e i piedi a 70 mm da quelli delle guide di cabina (staffe); la cabina a 10 mm dalle bride che tengono i piedi delle guide sulle staffe (bride forgiate della misura della guida, con la piastra oltre il piede)</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>scelta del software; la resistenza della parete con la nicchia va verificata dal progettista</t>
+          <t>scelta del software (principio: cataloghi di arcate a zaino); disposizione da confermare con il fornitore dell'arcata</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>nicchie nelle pareti</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I67" s="11" t="n"/>
@@ -3887,7 +3887,7 @@
       <c r="M67" s="11" t="n"/>
       <c r="N67" s="11" t="n"/>
     </row>
-    <row r="68" ht="134" customHeight="1">
+    <row r="68" ht="212" customHeight="1">
       <c r="A68" s="10" t="n">
         <v>66</v>
       </c>
@@ -3898,32 +3898,32 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Staffe delle guide del contrappeso (catalogo Panev)</t>
+          <t>Nicchie nelle pareti del vano</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>per default il supporto Panev SU o SD con la guida SG, la guida serrata sulla flangia della SG da due bride N1: il supporto più corto il cui campo stampato prende la distanza della guida dalla parete (o dal fondo della nicchia) e la cui piastra sta sulla parete: SU, SD 150 e SD 220 lunghi 160 mm da 45 a 155 mm (SD 220 da 50), lunghi 180 mm da 45 a 195 mm, lunghi 200 mm da 45 a 215 mm; nessuno adatto: «Non conforme» (si possono scegliere staffe generiche, da dimensionare a parte)</t>
+          <t>contrappeso in nicchia: il contrappeso con le sue guide sta nella nicchia della parete su cui corre, con almeno 20 mm tra le guide e i fianchi della nicchia (con le staffe Panev, lo spazio della piastra del supporto dietro il piede di ogni guida); la distanza dalla parete si misura dal fondo della nicchia e la cabina guadagna la sua profondità, senza scendere sotto gli ingombri delle guide; luce del vano in nicchia: una nicchia alta 400 mm per lampada, le lampade 1500 mm sopra ogni piano e l'ultima a 80 mm sotto il solaio; canalina in nicchia: dal fondo della fossa al solaio; ogni nicchia dentro la sua parete, fuori dai telai delle porte di piano e dalle altre nicchie, con almeno 50 mm di muro dietro; altrimenti «Non conforme»</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>catalogo staffe Panev 2026, pp. 20-59</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>catalogo del costruttore (panev/docs/catalogo-staffe-panev-2026.pdf)</t>
+          <t>scelta del software; la resistenza della parete con la nicchia va verificata dal progettista</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>staffe del catalogo per le guide del contrappeso</t>
+          <t>nicchie nelle pareti</t>
         </is>
       </c>
       <c r="I68" s="11" t="n"/>
@@ -3933,7 +3933,7 @@
       <c r="M68" s="11" t="n"/>
       <c r="N68" s="11" t="n"/>
     </row>
-    <row r="69" ht="212" customHeight="1">
+    <row r="69" ht="134" customHeight="1">
       <c r="A69" s="10" t="n">
         <v>67</v>
       </c>
@@ -3944,32 +3944,32 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Limitatore di velocità e tenditore (pianta, locale macchina, 3D) — per le RQ-A Montanari 0,15–3,0 m/s è il campo della famiglia: il limite di ogni taglia va letto sul manuale; delle basi pubblicate non è detto quale lato stia nel piano della puleggia (il lato lungo è disegnato in quel piano, come nel LK200). Tenditore a leva: lungo 700 mm (quota «A» del PFB R4KE per LK200 in un listino di rivenditore, senza definizione), puleggia a 255 mm dalla cerniera e blocco di 150 × 185 mm: scelte del software; le masse di 22 e 44 kg sono quelle delle tabelle PFB</t>
+          <t>Staffe delle guide del contrappeso (catalogo Panev)</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>per velocità il più piccolo PFB che la regge: LK200 (Ø 200, fune 6) fino a 1,48 m/s, LK250 fino a 1,74, LK300 fino a 2,93, R12BF fino a 4,00; oppure il modello scelto se regge la velocità: PFB (LX, LK, R1, R10BF) o Montanari (RQ-A 200, 250 e 300, NOR fino a 1,50 m/s, RG 200 fino a 0,30). Disegnati nelle proporzioni del LK200 (alto 370 mm, base 220 × 165) salvo LX120 alto 178, R10BF 488 su base 460 × 196, R12BF 524 su base 520 × 116, R1-LR 344 su base 285 × 80. Tenditore in fossa sulla guida di cabina: a leva con 22 kg (come PFB R4K) o verticale con 44 kg (come PFB R4R)</t>
+          <t>per default il supporto Panev SU o SD con la guida SG, la guida serrata sulla flangia della SG da due bride N1: il supporto più corto il cui campo stampato prende la distanza della guida dalla parete (o dal fondo della nicchia) e la cui piastra sta sulla parete: SU, SD 150 e SD 220 lunghi 160 mm da 45 a 155 mm (SD 220 da 50), lunghi 180 mm da 45 a 195 mm, lunghi 200 mm da 45 a 215 mm; nessuno adatto: «Non conforme» (si possono scegliere staffe generiche, da dimensionare a parte)</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>dati del fornitore del limitatore</t>
+          <t>catalogo staffe Panev 2026, pp. 20-59</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>pagine pfb.it e montanarigiulio.com, schede di elevatorequipment.co.uk (altezze, basi), estratti di ricerca del 1° ottobre 2026</t>
+          <t>catalogo del costruttore (panev/docs/catalogo-staffe-panev-2026.pdf)</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>staffe del catalogo per le guide del contrappeso</t>
         </is>
       </c>
       <c r="I69" s="11" t="n"/>
@@ -3979,33 +3979,33 @@
       <c r="M69" s="11" t="n"/>
       <c r="N69" s="11" t="n"/>
     </row>
-    <row r="70" ht="82" customHeight="1">
+    <row r="70" ht="212" customHeight="1">
       <c r="A70" s="10" t="n">
         <v>68</v>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Spazi di rifugio sul tetto di cabina e in fossa</t>
+          <t>Limitatore di velocità e tenditore (pianta, locale macchina, 3D) — per le RQ-A Montanari 0,15–3,0 m/s è il campo della famiglia: il limite di ogni taglia va letto sul manuale; delle basi pubblicate non è detto quale lato stia nel piano della puleggia (il lato lungo è disegnato in quel piano, come nel LK200). Tenditore a leva: lungo 700 mm (quota «A» del PFB R4KE per LK200 in un listino di rivenditore, senza definizione), puleggia a 255 mm dalla cerniera e blocco di 150 × 185 mm: scelte del software; le masse di 22 e 44 kg sono quelle delle tabelle PFB</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>tipo 1 (in piedi) 400 × 500 mm in pianta, alto 2000 mm; tipo 2 (accucciato) 500 × 700 mm, alto 1000 mm; tipo 3 (disteso, solo in fossa) 700 × 1000 mm, alto 500 mm; in testata con la cabina nella posizione più alta, in fossa con la cabina sugli ammortizzatori compressi</t>
+          <t>per velocità il più piccolo PFB che la regge: LK200 (Ø 200, fune 6) fino a 1,48 m/s, LK250 fino a 1,74, LK300 fino a 2,93, R12BF fino a 4,00; oppure il modello scelto se regge la velocità: PFB (LX, LK, R1, R10BF) o Montanari (RQ-A 200, 250 e 300, NOR fino a 1,50 m/s, RG 200 fino a 0,30). Disegnati nelle proporzioni del LK200 (alto 370 mm, base 220 × 165) salvo LX120 alto 178, R10BF 488 su base 460 × 196, R12BF 524 su base 520 × 116, R1-LR 344 su base 285 × 80. Tenditore in fossa sulla guida di cabina: a leva con 22 kg (come PFB R4K) o verticale con 44 kg (come PFB R4R)</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1 (Tabella 3)</t>
+          <t>dati del fornitore del limitatore</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>pagine pfb.it e montanarigiulio.com, schede di elevatorequipment.co.uk (altezze, basi), estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>spazio di rifugio in testata; spazio di rifugio in fossa</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I70" s="11" t="n"/>
@@ -4025,7 +4025,7 @@
       <c r="M70" s="11" t="n"/>
       <c r="N70" s="11" t="n"/>
     </row>
-    <row r="71" ht="56" customHeight="1">
+    <row r="71" ht="82" customHeight="1">
       <c r="A71" s="10" t="n">
         <v>69</v>
       </c>
@@ -4036,17 +4036,17 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Posizione più alta della cabina</t>
+          <t>Spazi di rifugio sul tetto di cabina e in fossa</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>contrappeso sugli ammortizzatori completamente compressi, più il salto 0,035·v² m (v velocità nominale)</t>
+          <t>tipo 1 (in piedi) 400 × 500 mm in pianta, alto 2000 mm; tipo 2 (accucciato) 500 × 700 mm, alto 1000 mm; tipo 3 (disteso, solo in fossa) 700 × 1000 mm, alto 500 mm; in testata con la cabina nella posizione più alta, in fossa con la cabina sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.6.1 (Tabella 2)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1 (Tabella 3)</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>spazio di rifugio in testata; distanze libere dal soffitto</t>
+          <t>spazio di rifugio in testata; spazio di rifugio in fossa</t>
         </is>
       </c>
       <c r="I71" s="11" t="n"/>
@@ -4082,17 +4082,17 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Distanze libere dal soffitto con la cabina nella posizione più alta</t>
+          <t>Posizione più alta della cabina</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>≥ 500 mm sopra le apparecchiature sul tetto di cabina (operatore); ≥ 100 mm sopra pattini, attacchi delle funi e traversa dell'arcata; ≥ 300 mm sopra il corrimano della balaustra</t>
+          <t>contrappeso sugli ammortizzatori completamente compressi, più il salto 0,035·v² m (v velocità nominale)</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.2</t>
+          <t>UNI EN 81-20:2020, 5.2.5.6.1 (Tabella 2)</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>distanze libere dal soffitto</t>
+          <t>spazio di rifugio in testata; distanze libere dal soffitto</t>
         </is>
       </c>
       <c r="I72" s="11" t="n"/>
@@ -4128,17 +4128,17 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Distanze in fossa con la cabina sugli ammortizzatori compressi</t>
+          <t>Distanze libere dal soffitto con la cabina nella posizione più alta</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>≥ 500 mm dal pavimento della fossa alle parti più basse della cabina; grembiule alto ≥ 750 mm sotto la soglia di cabina, con ≥ 100 mm liberi dal pavimento della fossa</t>
+          <t>≥ 500 mm sopra le apparecchiature sul tetto di cabina (operatore); ≥ 100 mm sopra pattini, attacchi delle funi e traversa dell'arcata; ≥ 300 mm sopra il corrimano della balaustra</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.8.2 e 5.4.5</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.2</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>spazio di rifugio in fossa; grembiule sugli ammortizzatori compressi</t>
+          <t>distanze libere dal soffitto</t>
         </is>
       </c>
       <c r="I73" s="11" t="n"/>
@@ -4174,17 +4174,17 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Balaustra sul tetto di cabina</t>
+          <t>Distanze in fossa con la cabina sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>richiesta se la distanza libera dal tetto alla parete supera 300 mm: alta 700 mm fino a 500 mm di distanza, 1100 mm oltre</t>
+          <t>≥ 500 mm dal pavimento della fossa alle parti più basse della cabina; grembiule alto ≥ 750 mm sotto la soglia di cabina, con ≥ 100 mm liberi dal pavimento della fossa</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.7.4</t>
+          <t>UNI EN 81-20:2020, 5.2.5.8.2 e 5.4.5</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>balaustra sul tetto di cabina</t>
+          <t>spazio di rifugio in fossa; grembiule sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="I74" s="11" t="n"/>
@@ -4220,17 +4220,17 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Superficie dove una persona può stare sul tetto di cabina</t>
+          <t>Balaustra sul tetto di cabina</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>area continua ≥ 0,12 m² con il lato minore ≥ 250 mm (disegnata 400 × 300 mm, modificabile sulla pianta in testata); sopra di essa deve esserci l'altezza dello spazio di rifugio</t>
+          <t>richiesta se la distanza libera dal tetto alla parete supera 300 mm: alta 700 mm fino a 500 mm di distanza, 1100 mm oltre</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.3</t>
+          <t>UNI EN 81-20:2020, 5.4.7.4</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>superficie per stare sul tetto di cabina</t>
+          <t>balaustra sul tetto di cabina</t>
         </is>
       </c>
       <c r="I75" s="11" t="n"/>
@@ -4255,7 +4255,7 @@
       <c r="M75" s="11" t="n"/>
       <c r="N75" s="11" t="n"/>
     </row>
-    <row r="76" ht="69" customHeight="1">
+    <row r="76" ht="56" customHeight="1">
       <c r="A76" s="10" t="n">
         <v>74</v>
       </c>
@@ -4266,17 +4266,17 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Schermo del contrappeso in fossa</t>
+          <t>Superficie dove una persona può stare sul tetto di cabina</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>dal punto più basso del contrappeso sugli ammortizzatori compressi fino ad almeno 2000 mm sopra il pavimento della fossa (altezza dello schermo modificabile sul progetto, mai sotto questo valore)</t>
+          <t>area continua ≥ 0,12 m² con il lato minore ≥ 250 mm (disegnata 400 × 300 mm, modificabile sulla pianta in testata); sopra di essa deve esserci l'altezza dello spazio di rifugio</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.5.1</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.3</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>protezione del contrappeso in fossa</t>
+          <t>superficie per stare sul tetto di cabina</t>
         </is>
       </c>
       <c r="I76" s="11" t="n"/>
@@ -4312,17 +4312,17 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori ad accumulo di energia lineari (molle)</t>
+          <t>Schermo del contrappeso in fossa</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>ammessi fino a 1 m/s; corsa ≥ 0,135·v² m e comunque ≥ 65 mm; extracorsa della cabina e del contrappeso ≥ 0 (nessun minimo nella norma)</t>
+          <t>dal punto più basso del contrappeso sugli ammortizzatori compressi fino ad almeno 2000 mm sopra il pavimento della fossa (altezza dello schermo modificabile sul progetto, mai sotto questo valore)</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2 (accumulo di energia, caratteristica lineare; sottoclausola da verificare sul testo)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.5.1</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso; extracorsa di cabina e contrappeso</t>
+          <t>protezione del contrappeso in fossa</t>
         </is>
       </c>
       <c r="I77" s="11" t="n"/>
@@ -4347,7 +4347,7 @@
       <c r="M77" s="11" t="n"/>
       <c r="N77" s="11" t="n"/>
     </row>
-    <row r="78" ht="121" customHeight="1">
+    <row r="78" ht="69" customHeight="1">
       <c r="A78" s="10" t="n">
         <v>76</v>
       </c>
@@ -4358,22 +4358,22 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori ad accumulo di energia non lineari (tamponi in poliuretano)</t>
+          <t>Ammortizzatori ad accumulo di energia lineari (molle)</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>ammessi fino a 1 m/s come le molle; nessuna corsa minima da formula: il campo di masse del certificato di esame di tipo per la velocità deve comprendere, per ogni tampone, la cabina vuota e a pieno carico (o il contrappeso); «completamente compresso» vuol dire compresso del 90 % dell'altezza, quindi la corsa è 0,9·H negli spazi in fossa e in testata; tampone tipico alti 80 mm (P+S Diepocell D, Ø da 80 a 220 mm; ACLA AUTAN XL)</t>
+          <t>ammessi fino a 1 m/s; corsa ≥ 0,135·v² m e comunque ≥ 65 mm; extracorsa della cabina e del contrappeso ≥ 0 (nessun minimo nella norma)</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2 (caratteristica non lineare) e UNI EN 81-50:2020, 5.5 (esame di tipo); sottoclausole da verificare sul testo</t>
+          <t>UNI EN 81-20:2020, 5.8.2 (accumulo di energia, caratteristica lineare; sottoclausola da verificare sul testo)</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>cataloghi P+S Diepocell (wwlift.de), ACLA AUTAN XL (acla.de), Stingl (corsa al 90 %); estratti di ricerca del 1° ottobre 2026</t>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso</t>
+          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso; extracorsa di cabina e contrappeso</t>
         </is>
       </c>
       <c r="I78" s="11" t="n"/>
@@ -4393,7 +4393,7 @@
       <c r="M78" s="11" t="n"/>
       <c r="N78" s="11" t="n"/>
     </row>
-    <row r="79" ht="95" customHeight="1">
+    <row r="79" ht="121" customHeight="1">
       <c r="A79" s="10" t="n">
         <v>77</v>
       </c>
@@ -4404,22 +4404,22 @@
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori a dissipazione di energia (idraulici)</t>
+          <t>Ammortizzatori ad accumulo di energia non lineari (tamponi in poliuretano)</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>a ogni velocità; corsa ≥ 0,0674·v² m (arresto per gravità al 115 % della velocità nominale); la corsa ridotta con il controllo del rallentamento non è considerata; ammortizzatori tipici: Oleo LSB10 fino a 1 m/s, alto 222,2 mm con corsa 73,4 mm; LSB16 fino a 1,6 m/s, alto 485,5 mm con corsa 173,5 mm</t>
+          <t>ammessi fino a 1 m/s come le molle; nessuna corsa minima da formula: il campo di masse del certificato di esame di tipo per la velocità deve comprendere, per ogni tampone, la cabina vuota e a pieno carico (o il contrappeso); «completamente compresso» vuol dire compresso del 90 % dell'altezza, quindi la corsa è 0,9·H negli spazi in fossa e in testata; tampone tipico alti 80 mm (P+S Diepocell D, Ø da 80 a 220 mm; ACLA AUTAN XL)</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2 (dissipazione di energia; sottoclausola da verificare sul testo)</t>
+          <t>UNI EN 81-20:2020, 5.8.2 (caratteristica non lineare) e UNI EN 81-50:2020, 5.5 (esame di tipo); sottoclausole da verificare sul testo</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>catalogo Oleo LSB e SEB (oleo.co.uk), estratti di ricerca del 1° ottobre 2026</t>
+          <t>cataloghi P+S Diepocell (wwlift.de), ACLA AUTAN XL (acla.de), Stingl (corsa al 90 %); estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
@@ -4439,33 +4439,33 @@
       <c r="M79" s="11" t="n"/>
       <c r="N79" s="11" t="n"/>
     </row>
-    <row r="80" ht="69" customHeight="1">
+    <row r="80" ht="95" customHeight="1">
       <c r="A80" s="10" t="n">
         <v>78</v>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Ammortizzatori a dissipazione di energia (idraulici)</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>altezza libera delle zone di lavoro ≥ 2100 mm (1800 mm sui percorsi); davanti al quadro una superficie libera profonda ≥ 700 mm e larga ≥ 500 mm o quanto il quadro; porta di accesso ≥ 600 × 2000 mm</t>
+          <t>a ogni velocità; corsa ≥ 0,0674·v² m (arresto per gravità al 115 % della velocità nominale); la corsa ridotta con il controllo del rallentamento non è considerata; ammortizzatori tipici: Oleo LSB10 fino a 1 m/s, alto 222,2 mm con corsa 73,4 mm; LSB16 fino a 1,6 m/s, alto 485,5 mm con corsa 173,5 mm</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.6.3.2.1 e 5.2.3</t>
+          <t>UNI EN 81-20:2020, 5.8.2 (dissipazione di energia; sottoclausola da verificare sul testo)</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>catalogo Oleo LSB e SEB (oleo.co.uk), estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>altezza del locale macchina; superficie libera davanti al quadro; porta del locale macchina</t>
+          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso</t>
         </is>
       </c>
       <c r="I80" s="11" t="n"/>
@@ -4496,17 +4496,17 @@
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Illuminazione del vano e del locale del macchinario</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>vano: illuminazione fissa di almeno 50 lux a 1 m sopra il tetto della cabina e sopra il pavimento della fossa, 20 lux altrove; locale del macchinario: almeno 200 lux al pavimento nelle zone di lavoro</t>
+          <t>altezza libera delle zone di lavoro ≥ 2100 mm (1800 mm sui percorsi); davanti al quadro una superficie libera profonda ≥ 700 mm e larga ≥ 500 mm o quanto il quadro; porta di accesso ≥ 600 × 2000 mm</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.4</t>
+          <t>UNI EN 81-20:2020, 5.2.6.3.2.1 e 5.2.3</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>altezza del locale macchina; superficie libera davanti al quadro; porta del locale macchina</t>
         </is>
       </c>
       <c r="I81" s="11" t="n"/>
@@ -4531,7 +4531,7 @@
       <c r="M81" s="11" t="n"/>
       <c r="N81" s="11" t="n"/>
     </row>
-    <row r="82" ht="56" customHeight="1">
+    <row r="82" ht="69" customHeight="1">
       <c r="A82" s="10" t="n">
         <v>80</v>
       </c>
@@ -4542,17 +4542,17 @@
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Temperatura dei locali del macchinario e degli armadi</t>
+          <t>Illuminazione del vano e del locale del macchinario</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>temperatura ambiente mantenuta tra +5 °C e +40 °C: ipotesi della norma, da garantire nell'edificio</t>
+          <t>vano: illuminazione fissa di almeno 50 lux a 1 m sopra il tetto della cabina e sopra il pavimento della fossa, 20 lux altrove; locale del macchinario: almeno 200 lux al pavimento nelle zone di lavoro</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, introduzione (ipotesi)</t>
+          <t>UNI EN 81-20:2020, 5.2.1.4</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
@@ -4577,7 +4577,7 @@
       <c r="M82" s="11" t="n"/>
       <c r="N82" s="11" t="n"/>
     </row>
-    <row r="83" ht="199" customHeight="1">
+    <row r="83" ht="56" customHeight="1">
       <c r="A83" s="10" t="n">
         <v>81</v>
       </c>
@@ -4588,27 +4588,27 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Basamento dell'argano</t>
+          <t>Temperatura dei locali del macchinario e degli armadi</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>su spessori di livellamento sotto gli appoggi (l'asse della puleggia dove lo mette il software), su telaio di due profilati sul pavimento (tipico UPN 200, alto quanto il profilato come i telai bassi universali), su due putrelle da muro a muro che possono stare sollevate dal pavimento (tipiche IPE 200, appoggio nei muri 150 mm), su piastre d'acciaio sotto gli appoggi (tipiche 20 mm) o su plinto in calcestruzzo (tipico 250 mm); tamponi antivibranti di 30 mm sotto gli appoggi, salvo sugli spessori; telaio e plinto 100 mm oltre il telaio dell'argano a ogni estremità; l'altezza del basamento porta l'asse della puleggia, che il calcolo (tratto di fune oltre la corsa) e il 3D seguono</t>
+          <t>temperatura ambiente mantenuta tra +5 °C e +40 °C: ipotesi della norma, da garantire nell'edificio</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio); scelta del costruttore</t>
+          <t>UNI EN 81-20:2020, introduzione (ipotesi)</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>telaio basso universale per argano alto 200 mm (lift-store.it); tamponi antivibranti 25–30 mm (catalogo Donati); piastre di 20 mm e plinto di 250–300 mm nella pratica di installazione (fonti estere, da confermare); estratti di ricerca del 1° ottobre 2026</t>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
@@ -4623,7 +4623,7 @@
       <c r="M83" s="11" t="n"/>
       <c r="N83" s="11" t="n"/>
     </row>
-    <row r="84" ht="147" customHeight="1">
+    <row r="84" ht="199" customHeight="1">
       <c r="A84" s="10" t="n">
         <v>82</v>
       </c>
@@ -4634,22 +4634,22 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Telaio sotto l'argano di un costruttore</t>
+          <t>Basamento dell'argano</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>l'argano di catalogo poggia con i suoi piedi su un telaio di due travi sotto le file di fori, con antivibranti alle estremità e 40 mm oltre l'argano a ogni estremità; il telaio è alto quanto serve per tenere l'asse della puleggia dove lo tiene l'argano generico del software, almeno 80 mm e con il bordo della puleggia 30 mm sopra il suo piano d'appoggio (gli argani compatti hanno la puleggia a sbalzo, sotto il piano dei piedi); se l'argano non lo permette l'asse sale e il calcolo segue</t>
+          <t>su spessori di livellamento sotto gli appoggi (l'asse della puleggia dove lo mette il software), su telaio di due profilati sul pavimento (tipico UPN 200, alto quanto il profilato come i telai bassi universali), su due putrelle da muro a muro che possono stare sollevate dal pavimento (tipiche IPE 200, appoggio nei muri 150 mm), su piastre d'acciaio sotto gli appoggi (tipiche 20 mm) o su plinto in calcestruzzo (tipico 250 mm); tamponi antivibranti di 30 mm sotto gli appoggi, salvo sugli spessori; telaio e plinto 100 mm oltre il telaio dell'argano a ogni estremità; l'altezza del basamento porta l'asse della puleggia, che il calcolo (tratto di fune oltre la corsa) e il 3D seguono</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio); scelta del costruttore</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>quote dei piedi, dei fori e dell'asse della puleggia dalle schede tecniche del costruttore; altezza del telaio scelta dal software, da adattare al telaio fornito</t>
+          <t>telaio basso universale per argano alto 200 mm (lift-store.it); tamponi antivibranti 25–30 mm (catalogo Donati); piastre di 20 mm e plinto di 250–300 mm nella pratica di installazione (fonti estere, da confermare); estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
@@ -4669,7 +4669,7 @@
       <c r="M84" s="11" t="n"/>
       <c r="N84" s="11" t="n"/>
     </row>
-    <row r="85" ht="134" customHeight="1">
+    <row r="85" ht="147" customHeight="1">
       <c r="A85" s="10" t="n">
         <v>83</v>
       </c>
@@ -4680,32 +4680,32 @@
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
+          <t>Telaio sotto l'argano di un costruttore</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
+          <t>l'argano di catalogo poggia con i suoi piedi su un telaio di due travi sotto le file di fori, con antivibranti alle estremità e 40 mm oltre l'argano a ogni estremità; il telaio è alto quanto serve per tenere l'asse della puleggia dove lo tiene l'argano generico del software, almeno 80 mm e con il bordo della puleggia 30 mm sopra il suo piano d'appoggio (gli argani compatti hanno la puleggia a sbalzo, sotto il piano dei piedi); se l'argano non lo permette l'asse sale e il calcolo segue</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E); DPR 1497/1963, art. 5 (carichi fissi più 1,5 volte il carico statico delle funi; freccia ≤ 1/1500 della luce libera: regola storica, da confermare)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
+          <t>quote dei piedi, dei fori e dell'asse della puleggia dalle schede tecniche del costruttore; altezza del telaio scelta dal software, da adattare al telaio fornito</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I85" s="11" t="n"/>
@@ -4715,33 +4715,33 @@
       <c r="M85" s="11" t="n"/>
       <c r="N85" s="11" t="n"/>
     </row>
-    <row r="86" ht="108" customHeight="1">
+    <row r="86" ht="134" customHeight="1">
       <c r="A86" s="10" t="n">
         <v>84</v>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Carichi sul pavimento della fossa</t>
+          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
+          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.8; UNI EN 81-50:2020, 5.10</t>
+          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E); DPR 1497/1963, art. 5 (carichi fissi più 1,5 volte il carico statico delle funi; freccia ≤ 1/1500 della luce libera: regola storica, da confermare)</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi; sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
+          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
         </is>
       </c>
       <c r="I86" s="11" t="n"/>
@@ -4772,22 +4772,22 @@
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Spinte sulle guide di cabina</t>
+          <t>Carichi sul pavimento della fossa</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
+          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.10</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8; UNI EN 81-50:2020, 5.10</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi; sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
@@ -4807,7 +4807,7 @@
       <c r="M87" s="11" t="n"/>
       <c r="N87" s="11" t="n"/>
     </row>
-    <row r="88" ht="82" customHeight="1">
+    <row r="88" ht="108" customHeight="1">
       <c r="A88" s="10" t="n">
         <v>86</v>
       </c>
@@ -4818,27 +4818,27 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Carico della macchina sulla soletta</t>
+          <t>Spinte sulle guide di cabina</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
+          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.10</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
+          <t>sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>prassi di cantiere</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
@@ -4853,7 +4853,7 @@
       <c r="M88" s="11" t="n"/>
       <c r="N88" s="11" t="n"/>
     </row>
-    <row r="89" ht="43" customHeight="1">
+    <row r="89" ht="82" customHeight="1">
       <c r="A89" s="10" t="n">
         <v>87</v>
       </c>
@@ -4864,12 +4864,12 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Massa dei cavi flessibili</t>
+          <t>Carico della macchina sulla soletta</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
+          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
+          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>prassi di cantiere</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       <c r="M89" s="11" t="n"/>
       <c r="N89" s="11" t="n"/>
     </row>
-    <row r="90" ht="121" customHeight="1">
+    <row r="90" ht="43" customHeight="1">
       <c r="A90" s="10" t="n">
         <v>88</v>
       </c>
@@ -4910,27 +4910,27 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
+          <t>Massa dei cavi flessibili</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
+          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>regola di montaggio indicata dal committente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>scelta del committente</t>
+          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
@@ -4945,7 +4945,7 @@
       <c r="M90" s="11" t="n"/>
       <c r="N90" s="11" t="n"/>
     </row>
-    <row r="91" ht="82" customHeight="1">
+    <row r="91" ht="121" customHeight="1">
       <c r="A91" s="10" t="n">
         <v>89</v>
       </c>
@@ -4956,27 +4956,27 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Lunghezze stimate nel foglio dei dati</t>
+          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
+          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>regola di montaggio indicata dal committente</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>stima del software, da sostituire con le misure di cantiere</t>
+          <t>scelta del committente</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
@@ -4991,23 +4991,23 @@
       <c r="M91" s="11" t="n"/>
       <c r="N91" s="11" t="n"/>
     </row>
-    <row r="92" ht="43" customHeight="1">
+    <row r="92" ht="82" customHeight="1">
       <c r="A92" s="10" t="n">
         <v>90</v>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Dimensioni proposte della cabina</t>
+          <t>Lunghezze stimate nel foglio dei dati</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
+          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima del software, da sostituire con le misure di cantiere</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
@@ -5037,7 +5037,7 @@
       <c r="M92" s="11" t="n"/>
       <c r="N92" s="11" t="n"/>
     </row>
-    <row r="93" ht="199" customHeight="1">
+    <row r="93" ht="43" customHeight="1">
       <c r="A93" s="10" t="n">
         <v>91</v>
       </c>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Quote della pianta fissate a mano</t>
+          <t>Dimensioni proposte della cabina</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8), quello del contrappeso dentro la lunghezza del contrappeso</t>
+          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I93" s="11" t="n"/>
@@ -5083,7 +5083,7 @@
       <c r="M93" s="11" t="n"/>
       <c r="N93" s="11" t="n"/>
     </row>
-    <row r="94" ht="82" customHeight="1">
+    <row r="94" ht="199" customHeight="1">
       <c r="A94" s="10" t="n">
         <v>92</v>
       </c>
@@ -5094,12 +5094,12 @@
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Limiti del modello del vano</t>
+          <t>Quote della pianta fissate a mano</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
+          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8), quello del contrappeso dentro la lunghezza del contrappeso</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>limite del modello attuale</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
         </is>
       </c>
       <c r="I94" s="11" t="n"/>
@@ -5129,23 +5129,23 @@
       <c r="M94" s="11" t="n"/>
       <c r="N94" s="11" t="n"/>
     </row>
-    <row r="95" ht="56" customHeight="1">
+    <row r="95" ht="82" customHeight="1">
       <c r="A95" s="10" t="n">
         <v>93</v>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Corsa</t>
+          <t>Limiti del modello del vano</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
+          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>dati dei piani inseriti</t>
+          <t>limite del modello attuale</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
@@ -5186,22 +5186,22 @@
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Portata e velocità</t>
+          <t>Corsa</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
+          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.2.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>progetto del vano</t>
+          <t>dati dei piani inseriti</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
@@ -5221,7 +5221,7 @@
       <c r="M96" s="11" t="n"/>
       <c r="N96" s="11" t="n"/>
     </row>
-    <row r="97" ht="160" customHeight="1">
+    <row r="97" ht="56" customHeight="1">
       <c r="A97" s="10" t="n">
         <v>95</v>
       </c>
@@ -5232,27 +5232,27 @@
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Normativa di collaudo e parti sostituite o modificate — il testo delle UNI 10411 del 2024 non è stato letto: le verifiche per parte e i requisiti per la sostituzione del macchinario (edizione 2021: freno in due elementi, temporizzatore, velocità eccessiva in salita, arresto entro 1 m dalla macchina, interruzione se il freno non si apre) vanno confermati sul testo vigente</t>
+          <t>Portata e velocità</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software</t>
+          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
+          <t>UNI EN 81-20:2020, 5.4.2.1</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>schede UNI delle norme (scopo, data 31/10/2024); schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); sintesi secondarie; ricerca, capitoli 2.4 e 6.6</t>
+          <t>progetto del vano</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H97" s="10" t="inlineStr">
@@ -5267,7 +5267,7 @@
       <c r="M97" s="11" t="n"/>
       <c r="N97" s="11" t="n"/>
     </row>
-    <row r="98" ht="69" customHeight="1">
+    <row r="98" ht="160" customHeight="1">
       <c r="A98" s="10" t="n">
         <v>96</v>
       </c>
@@ -5278,27 +5278,27 @@
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
+          <t>Normativa di collaudo e parti sostituite o modificate — il testo delle UNI 10411 del 2024 non è stato letto: le verifiche per parte e i requisiti per la sostituzione del macchinario (edizione 2021: freno in due elementi, temporizzatore, velocità eccessiva in salita, arresto entro 1 m dalla macchina, interruzione se il freno non si apre) vanno confermati sul testo vigente</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
+          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
+          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>scelta del software, senza fonte</t>
+          <t>schede UNI delle norme (scopo, data 31/10/2024); schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); sintesi secondarie; ricerca, capitoli 2.4 e 6.6</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
@@ -5313,7 +5313,7 @@
       <c r="M98" s="11" t="n"/>
       <c r="N98" s="11" t="n"/>
     </row>
-    <row r="99" ht="82" customHeight="1">
+    <row r="99" ht="69" customHeight="1">
       <c r="A99" s="10" t="n">
         <v>97</v>
       </c>
@@ -5324,27 +5324,27 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Fune oltre la corsa (L0)</t>
+          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale (macchina in basso o senza locale: fino al soffitto del vano)</t>
+          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
+          <t>scelta del software, senza fonte</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H99" s="10" t="inlineStr">
@@ -5359,7 +5359,7 @@
       <c r="M99" s="11" t="n"/>
       <c r="N99" s="11" t="n"/>
     </row>
-    <row r="100" ht="147" customHeight="1">
+    <row r="100" ht="82" customHeight="1">
       <c r="A100" s="10" t="n">
         <v>98</v>
       </c>
@@ -5370,27 +5370,27 @@
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
+          <t>Fune oltre la corsa (L0)</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
+          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale (macchina in basso o senza locale: fino al soffitto del vano)</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>pianta del vano</t>
+          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H100" s="10" t="inlineStr">
@@ -5405,7 +5405,7 @@
       <c r="M100" s="11" t="n"/>
       <c r="N100" s="11" t="n"/>
     </row>
-    <row r="101" ht="160" customHeight="1">
+    <row r="101" ht="147" customHeight="1">
       <c r="A101" s="10" t="n">
         <v>99</v>
       </c>
@@ -5416,22 +5416,22 @@
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
+          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
+          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
+          <t>ricerca, capitolo 5.3</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>geometria delle funi</t>
+          <t>pianta del vano</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
@@ -5451,7 +5451,7 @@
       <c r="M101" s="11" t="n"/>
       <c r="N101" s="11" t="n"/>
     </row>
-    <row r="102" ht="56" customHeight="1">
+    <row r="102" ht="160" customHeight="1">
       <c r="A102" s="10" t="n">
         <v>100</v>
       </c>
@@ -5462,22 +5462,22 @@
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
+          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
+          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
+          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano</t>
+          <t>geometria delle funi</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
@@ -5497,7 +5497,7 @@
       <c r="M102" s="11" t="n"/>
       <c r="N102" s="11" t="n"/>
     </row>
-    <row r="103" ht="238" customHeight="1">
+    <row r="103" ht="56" customHeight="1">
       <c r="A103" s="10" t="n">
         <v>101</v>
       </c>
@@ -5508,27 +5508,27 @@
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso o pilastro pieno fino al terreno (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori</t>
+          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
+          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
+          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>geometria ricostruita dal software</t>
+          <t>dati verticali del vano</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
@@ -5543,7 +5543,7 @@
       <c r="M103" s="11" t="n"/>
       <c r="N103" s="11" t="n"/>
     </row>
-    <row r="104" ht="186" customHeight="1">
+    <row r="104" ht="238" customHeight="1">
       <c r="A104" s="10" t="n">
         <v>102</v>
       </c>
@@ -5554,27 +5554,27 @@
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta dal catalogo di un costruttore — i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
+          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso o pilastro pieno fino al terreno (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo; i disegni e il 3D mostrano l'argano SICOR com'è (ingombri, piedi e fori, asse della puleggia, P ed E della scheda), sul telaio del software</t>
+          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
+          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>SICOR: schede tecniche 2025 e modelli CAD scaricati da sicoritaly.com il 2 ottobre 2026 (solo le quote); Sassi, Montanari, GEM, FAER: estratti delle pagine dei costruttori e dei rivenditori, 1° ottobre 2026</t>
+          <t>geometria ricostruita dal software</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr">
@@ -5589,7 +5589,7 @@
       <c r="M104" s="11" t="n"/>
       <c r="N104" s="11" t="n"/>
     </row>
-    <row r="105" ht="134" customHeight="1">
+    <row r="105" ht="186" customHeight="1">
       <c r="A105" s="10" t="n">
         <v>103</v>
       </c>
@@ -5600,27 +5600,27 @@
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
+          <t>Macchina proposta dal catalogo di un costruttore — i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
+          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo; i disegni e il 3D mostrano l'argano SICOR com'è (ingombri, piedi e fori, asse della puleggia, P ed E della scheda), sul telaio del software</t>
         </is>
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 8</t>
+          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo</t>
+          <t>SICOR: schede tecniche 2025 e modelli CAD scaricati da sicoritaly.com il 2 ottobre 2026 (solo le quote); Sassi, Montanari, GEM, FAER: estratti delle pagine dei costruttori e dei rivenditori, 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
@@ -5635,38 +5635,38 @@
       <c r="M105" s="11" t="n"/>
       <c r="N105" s="11" t="n"/>
     </row>
-    <row r="106" ht="69" customHeight="1">
+    <row r="106" ht="134" customHeight="1">
       <c r="A106" s="10" t="n">
         <v>104</v>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
+          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
+          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
+          <t>ricerca, capitolo 8</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo (src/calc/model.ts)</t>
+          <t>motore di calcolo</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
@@ -5681,7 +5681,7 @@
       <c r="M106" s="11" t="n"/>
       <c r="N106" s="11" t="n"/>
     </row>
-    <row r="107" ht="56" customHeight="1">
+    <row r="107" ht="69" customHeight="1">
       <c r="A107" s="10" t="n">
         <v>105</v>
       </c>
@@ -5692,27 +5692,27 @@
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
+          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
+          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
+          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>motore di calcolo (src/calc/model.ts)</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
@@ -5727,7 +5727,7 @@
       <c r="M107" s="11" t="n"/>
       <c r="N107" s="11" t="n"/>
     </row>
-    <row r="108" ht="69" customHeight="1">
+    <row r="108" ht="56" customHeight="1">
       <c r="A108" s="10" t="n">
         <v>106</v>
       </c>
@@ -5738,17 +5738,17 @@
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Limite di aderenza mostrato durante la marcia</t>
+          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
+          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.2</t>
+          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
@@ -5773,7 +5773,7 @@
       <c r="M108" s="11" t="n"/>
       <c r="N108" s="11" t="n"/>
     </row>
-    <row r="109" ht="43" customHeight="1">
+    <row r="109" ht="69" customHeight="1">
       <c r="A109" s="10" t="n">
         <v>107</v>
       </c>
@@ -5784,22 +5784,22 @@
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Tempi delle porte</t>
+          <t>Limite di aderenza mostrato durante la marcia</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
+          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
         </is>
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.2.2</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (solo animazione)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
@@ -5819,7 +5819,7 @@
       <c r="M109" s="11" t="n"/>
       <c r="N109" s="11" t="n"/>
     </row>
-    <row r="110" ht="108" customHeight="1">
+    <row r="110" ht="43" customHeight="1">
       <c r="A110" s="10" t="n">
         <v>108</v>
       </c>
@@ -5830,27 +5830,27 @@
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione</t>
+          <t>Tempi delle porte</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
+          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>sintesi della norma di costruttori e organismi notificati (fonti secondarie)</t>
+          <t>scelta del software (solo animazione)</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
@@ -5865,7 +5865,7 @@
       <c r="M110" s="11" t="n"/>
       <c r="N110" s="11" t="n"/>
     </row>
-    <row r="111" ht="56" customHeight="1">
+    <row r="111" ht="108" customHeight="1">
       <c r="A111" s="10" t="n">
         <v>109</v>
       </c>
@@ -5876,27 +5876,27 @@
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Cabina bloccata: rotazione in salita</t>
+          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
+          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2</t>
+          <t>UNI EN 81-20:2020, 5.8.2</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo; velocità scelta dal software</t>
+          <t>sintesi della norma di costruttori e organismi notificati (fonti secondarie)</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H111" s="10" t="inlineStr">
@@ -5911,7 +5911,7 @@
       <c r="M111" s="11" t="n"/>
       <c r="N111" s="11" t="n"/>
     </row>
-    <row r="112" ht="43" customHeight="1">
+    <row r="112" ht="56" customHeight="1">
       <c r="A112" s="10" t="n">
         <v>110</v>
       </c>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Passo di campionamento</t>
+          <t>Cabina bloccata: rotazione in salita</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
+          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.2</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>motore di calcolo; velocità scelta dal software</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
@@ -5957,10 +5957,56 @@
       <c r="M112" s="11" t="n"/>
       <c r="N112" s="11" t="n"/>
     </row>
+    <row r="113" ht="43" customHeight="1">
+      <c r="A113" s="10" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>Passo di campionamento</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
+        </is>
+      </c>
+      <c r="E113" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="G113" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H113" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="n"/>
+      <c r="J113" s="11" t="n"/>
+      <c r="K113" s="11" t="n"/>
+      <c r="L113" s="11" t="n"/>
+      <c r="M113" s="11" t="n"/>
+      <c r="N113" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N112"/>
+  <autoFilter ref="A1:N113"/>
   <dataValidations count="1">
-    <dataValidation sqref="I3:I112" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
+    <dataValidation sqref="I3:I113" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
       <formula1>"conforme,diverso,non applicabile"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6003,7 +6049,7 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$112,"da verificare")</f>
+        <f>COUNTIF(Voci!$G$3:$G$113,"da verificare")</f>
         <v/>
       </c>
     </row>
@@ -6014,7 +6060,7 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$112,"confermato")</f>
+        <f>COUNTIF(Voci!$G$3:$G$113,"confermato")</f>
         <v/>
       </c>
     </row>
@@ -6025,7 +6071,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$112,"scelta del software")</f>
+        <f>COUNTIF(Voci!$G$3:$G$113,"scelta del software")</f>
         <v/>
       </c>
     </row>
@@ -6036,7 +6082,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$112,"stima")</f>
+        <f>COUNTIF(Voci!$G$3:$G$113,"stima")</f>
         <v/>
       </c>
     </row>
@@ -6047,7 +6093,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$112,"derivazione")</f>
+        <f>COUNTIF(Voci!$G$3:$G$113,"derivazione")</f>
         <v/>
       </c>
     </row>
@@ -6058,7 +6104,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$112,"prassi di cantiere")</f>
+        <f>COUNTIF(Voci!$G$3:$G$113,"prassi di cantiere")</f>
         <v/>
       </c>
     </row>
@@ -6069,7 +6115,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTA(Voci!$A$3:$A$112)</f>
+        <f>COUNTA(Voci!$A$3:$A$113)</f>
         <v/>
       </c>
     </row>
@@ -6087,7 +6133,7 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$112,"conforme")</f>
+        <f>COUNTIF(Voci!$I$3:$I$113,"conforme")</f>
         <v/>
       </c>
     </row>
@@ -6098,7 +6144,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$112,"diverso")</f>
+        <f>COUNTIF(Voci!$I$3:$I$113,"diverso")</f>
         <v/>
       </c>
     </row>
@@ -6109,7 +6155,7 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$112,"non applicabile")</f>
+        <f>COUNTIF(Voci!$I$3:$I$113,"non applicabile")</f>
         <v/>
       </c>
     </row>
@@ -6120,14 +6166,14 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>COUNTBLANK(Voci!$I$3:$I$112)</f>
+        <f>COUNTBLANK(Voci!$I$3:$I$113)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Conteggi sulle righe 3–112 del foglio «Voci» (la riga 2 è l'esempio).</t>
+          <t>Conteggi sulle righe 3–113 del foglio «Voci» (la riga 2 è l'esempio).</t>
         </is>
       </c>
     </row>

--- a/liftpilot/docs/lista-verifica-normativa.xlsx
+++ b/liftpilot/docs/lista-verifica-normativa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Riepilogo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$166</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Voci'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -660,7 +660,7 @@
     <row r="18" ht="32" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Ogni correzione viene riportata nel registro del software (argano/src/calc/norme.ts) e cambia insieme motore di calcolo, lista e relazione di calcolo.</t>
+          <t>Ogni correzione viene riportata nel registro del software (liftpilot/src/calc/norme.ts) e cambia insieme motore di calcolo, lista e relazione di calcolo.</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N113"/>
+  <dimension ref="A1:N166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1633,7 +1633,7 @@
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="11" t="n"/>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="43" customHeight="1">
       <c r="A19" s="10" t="n">
         <v>17</v>
       </c>
@@ -1654,17 +1654,17 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Direttiva 2014/33/UE, Allegato I; UNI EN 81-20:2020, 5.5</t>
+          <t>DPR 162/1999, All. I 1.3 (Direttiva 2014/33/UE, All. I); UNI EN 81-20:2020, 5.5</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>fonte secondaria</t>
+          <t>DPR 162/1999 consolidato (Normattiva), letto il 2026-10-02 (ricerca, cap. 16), All. I 1.3</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
@@ -2737,7 +2737,7 @@
       <c r="M42" s="11" t="n"/>
       <c r="N42" s="11" t="n"/>
     </row>
-    <row r="43" ht="43" customHeight="1">
+    <row r="43" ht="69" customHeight="1">
       <c r="A43" s="10" t="n">
         <v>41</v>
       </c>
@@ -2753,22 +2753,22 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>adeguamento della parte sostituita, comunicazione al Comune e al soggetto delle verifiche, verifica straordinaria prima del servizio</t>
+          <t>modifica costruttiva (art. 2 c.1 lett. cc), n. 5): adeguamento della parte sostituita e delle altre parti interessate, comunicazione al Comune e al soggetto delle verifiche periodiche, verifica straordinaria prima del servizio</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., art. 2 (dopo il DPR 23/2017) e art. 14</t>
+          <t>DPR 162/1999 e s.m.i., art. 2 c.1 lett. cc), art. 12 c.4–5, art. 14 c.3</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>testi consolidati non ufficiali; fonti secondarie concordi</t>
+          <t>DPR 162/1999 consolidato (Normattiva), letto il 2026-10-02 (ricerca, cap. 16), §3.2</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
@@ -3335,7 +3335,7 @@
       <c r="M55" s="11" t="n"/>
       <c r="N55" s="11" t="n"/>
     </row>
-    <row r="56" ht="43" customHeight="1">
+    <row r="56" ht="56" customHeight="1">
       <c r="A56" s="10" t="n">
         <v>54</v>
       </c>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>cabina larga 950 mm e profonda 1300 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (non verificata)</t>
+          <t>cabina larga 950 mm e profonda 1300 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (fuori dal vano: da verificare in sito)</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>sintesi pubblicate del DM 236/1989 (disabili.com, studiomadera.it), fonti secondarie concordi</t>
+          <t>DM 236/1989, 8.1.12, letto per intero su Normattiva il 2026-10-02 (ricerca, cap. 16, §4.1)</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
@@ -3381,7 +3381,7 @@
       <c r="M56" s="11" t="n"/>
       <c r="N56" s="11" t="n"/>
     </row>
-    <row r="57" ht="43" customHeight="1">
+    <row r="57" ht="56" customHeight="1">
       <c r="A57" s="10" t="n">
         <v>55</v>
       </c>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>cabina larga 1100 mm e profonda 1400 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (non verificata)</t>
+          <t>cabina larga 1100 mm e profonda 1400 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (fuori dal vano: da verificare in sito)</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>sintesi pubblicate del DM 236/1989 (disabili.com, studiomadera.it), fonti secondarie concordi</t>
+          <t>DM 236/1989, 8.1.12, letto per intero su Normattiva il 2026-10-02 (ricerca, cap. 16, §4.1)</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
@@ -3427,7 +3427,7 @@
       <c r="M57" s="11" t="n"/>
       <c r="N57" s="11" t="n"/>
     </row>
-    <row r="58" ht="43" customHeight="1">
+    <row r="58" ht="56" customHeight="1">
       <c r="A58" s="10" t="n">
         <v>56</v>
       </c>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>cabina larga 800 mm e profonda 1200 mm, porta di 750 mm sul lato corto; piattaforma davanti alla porta 1,40 × 1,40 m (non verificata)</t>
+          <t>cabina larga 800 mm e profonda 1200 mm, porta di 750 mm sul lato corto; piattaforma davanti alla porta 1,40 × 1,40 m (fuori dal vano: da verificare in sito)</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>sintesi pubblicate del DM 236/1989 (disabili.com, studiomadera.it), fonti secondarie concordi</t>
+          <t>DM 236/1989, 8.1.12, letto per intero su Normattiva il 2026-10-02 (ricerca, cap. 16, §4.1)</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
@@ -3565,7 +3565,7 @@
       <c r="M60" s="11" t="n"/>
       <c r="N60" s="11" t="n"/>
     </row>
-    <row r="61" ht="212" customHeight="1">
+    <row r="61" ht="342" customHeight="1">
       <c r="A61" s="10" t="n">
         <v>59</v>
       </c>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>vano nel muro: luce netta + 2 × 50 mm di portale; operatore della porta di cabina lungo 1,5·L + 50 mm con porta telescopica (il lato di chiusura 25 mm oltre la luce) e 2·L + 60 mm con porta centrale, profondo 150 mm, dentro il vano; con il fornitore scelto: 2SG FLY/LIKE 1,5·L + 40 mm (telescopica) e 2·L + 20 mm (centrale), Fermator 40/10 1,5·L + 50 mm e 2·L + 50 mm; con due accessi adiacenti gli operatori non devono sovrapporsi all'angolo tra le porte (altrimenti «Attenzione»: operatori da scegliere con il fornitore)</t>
+          <t>vano nel muro: luce netta + 2 × 50 mm di portale; operatore della porta di cabina lungo 1,5·L + 50 mm con porta telescopica (il lato di chiusura 25 mm oltre la luce) e 2·L + 60 mm con porta centrale, profondo 220 mm, dentro il vano; con il fornitore scelto: 2SG FLY/LIKE 1,5·L + 40 mm (telescopica) e 2·L + 20 mm (centrale), profondo 220 mm; Fermator 40/10 1,5·L + 50 mm e 2·L + 50 mm, profondo 144 mm; Dapa LOWER 1,5·L + 47 mm e 2·L + 50 mm, profondo 217 mm; con due accessi adiacenti gli operatori non devono sovrapporsi all'angolo tra le porte (altrimenti «Attenzione»: operatori da scegliere con il fornitore)</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>cataloghi 2SG FLY 2AT (1,5·A + 40) e 2AO (2·A + 20), Fermator 40/10 VF (1,5·PL + 40/50; 2·PL + 50; chiusura a 25 mm dalla luce), letti da estratti di ricerca: presi i valori più lunghi, da confermare con il fornitore. Le formule con + 40 danno esattamente la lunghezza delle soglie Fermator di catalogo (2 ante telescopiche, luce 900: 1390 mm; 2 ante centrali, luce 700: 1440 mm): potrebbero essere la soglia e non la trave dell'operatore. Wittur, Prisma, Dapa e CMM: lunghezza dell'operatore non trovata</t>
+          <t>schede PDF 2SG FLY 2AT (ingombro massimo 1,5·A + 10; soglia 1,5·A + 20, + 40 con l'extracorsa: presa la più lunga) e 2AO (2·A + 20), profondità 220 letta sul disegno; catalogo tecnico Dapa LOWER (1,5·AP + 47, 2·AP + 50, profondità 217); Fermator 40/10 PM in copie presso terzi (1,5·PL + 50 e 2·PL + 50, le soglie + 40; profondità 120–144 sul disegno, con le staffe 183–280; chiusura a 15 mm dalla luce, il software ne tiene 25); Wittur Hydra Plus da una copia del catalogo Selcom (1,5·PL + 25 e 2·PL + 50, profondo 200); letti il 2 ottobre 2026 (research/argano-geared/18-porte-limitatori-tenditori-tutti.md). Il generico è l'inviluppo: il più lungo (Fermator, Dapa) e il più profondo (2SG FLY). Hydra Plus può superarlo dove la sua quota GM supera la GW; Prisma e CMM: lunghezza e profondità non trovate</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
@@ -3933,7 +3933,7 @@
       <c r="M68" s="11" t="n"/>
       <c r="N68" s="11" t="n"/>
     </row>
-    <row r="69" ht="134" customHeight="1">
+    <row r="69" ht="329" customHeight="1">
       <c r="A69" s="10" t="n">
         <v>67</v>
       </c>
@@ -3949,17 +3949,17 @@
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>per default il supporto Panev SU o SD con la guida SG, la guida serrata sulla flangia della SG da due bride N1: il supporto più corto il cui campo stampato prende la distanza della guida dalla parete (o dal fondo della nicchia) e la cui piastra sta sulla parete: SU, SD 150 e SD 220 lunghi 160 mm da 45 a 155 mm (SD 220 da 50), lunghi 180 mm da 45 a 195 mm, lunghi 200 mm da 45 a 215 mm; nessuno adatto: «Non conforme» (si possono scegliere staffe generiche, da dimensionare a parte)</t>
+          <t>per default il supporto Panev SU o SD con la guida SG, la guida serrata sulla flangia della SG da due bride N1: il supporto più corto il cui campo stampato prende la distanza della guida dalla parete (o dal fondo della nicchia) e la cui piastra sta sulla parete: SU, SD 150 e SD 220 lunghi 160 mm da 45 a 155 mm (SD 220 da 50), lunghi 180 mm da 45 a 195 mm, lunghi 200 mm da 45 a 215 mm; quando nessuno sta, vicino a un angolo, il supporto scorrevole SC sulla parete dietro il piede della guida con la SG lungo la parete: la flangia della SG da 2 mm oltre il bordo dell'SC fino a 70, 88, 130 e 140 mm dalla parete per SC 50, 60, 80 e 90, l'asse della guida entro il campo stampato da un'estremità dell'SC (lunghi 200 mm: 210, 213, 215 e 215 mm; lunghi 220 mm: 235, 235, 255 e 235 mm), fuori dai telai delle porte e dalle nicchie. Il progettista può scegliere l'articolo a mano (se non prende la guida: «Non conforme») o una soluzione su disegno esecutivo, SC 50 170 + SG 225 50 a misura o SN 60 65 + SN 65 200 + BRACCIO 160 190 all'angolo del vano: «Da verificare» sul disegno; nessuno adatto: «Non conforme» (si possono scegliere staffe generiche, da dimensionare a parte)</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>catalogo staffe Panev 2026, pp. 20-59</t>
+          <t>catalogo staffe Panev 2026, pp. 20-62</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>catalogo del costruttore (panev/docs/catalogo-staffe-panev-2026.pdf)</t>
+          <t>catalogo del costruttore (panev/docs/catalogo-staffe-panev-2026.pdf); le corse dell'SC lontano dalla parete lette sui disegni di montaggio (pp. 41-55)</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
@@ -3979,7 +3979,7 @@
       <c r="M69" s="11" t="n"/>
       <c r="N69" s="11" t="n"/>
     </row>
-    <row r="70" ht="212" customHeight="1">
+    <row r="70" ht="121" customHeight="1">
       <c r="A70" s="10" t="n">
         <v>68</v>
       </c>
@@ -3990,27 +3990,27 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Limitatore di velocità e tenditore (pianta, locale macchina, 3D) — per le RQ-A Montanari 0,15–3,0 m/s è il campo della famiglia: il limite di ogni taglia va letto sul manuale; delle basi pubblicate non è detto quale lato stia nel piano della puleggia (il lato lungo è disegnato in quel piano, come nel LK200). Tenditore a leva: lungo 700 mm (quota «A» del PFB R4KE per LK200 in un listino di rivenditore, senza definizione), puleggia a 255 mm dalla cerniera e blocco di 150 × 185 mm: scelte del software; le masse di 22 e 44 kg sono quelle delle tabelle PFB</t>
+          <t>Staffe delle porte di piano (catalogo Panev)</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>per velocità il più piccolo PFB che la regge: LK200 (Ø 200, fune 6) fino a 1,48 m/s, LK250 fino a 1,74, LK300 fino a 2,93, R12BF fino a 4,00; oppure il modello scelto se regge la velocità: PFB (LX, LK, R1, R10BF) o Montanari (RQ-A 200, 250 e 300, NOR fino a 1,50 m/s, RG 200 fino a 0,30). Disegnati nelle proporzioni del LK200 (alto 370 mm, base 220 × 165) salvo LX120 alto 178, R10BF 488 su base 460 × 196, R12BF 524 su base 520 × 116, R1-LR 344 su base 285 × 80. Tenditore in fossa sulla guida di cabina: a leva con 22 kg (come PFB R4K) o verticale con 44 kg (come PFB R4R)</t>
+          <t>sotto ogni soglia di piano la coppia A + B della stessa sezione (65, 45 o 37 mm: le serie non sono intercambiabili): per default A 65 170 7 + B 65 320 (5 mm, regolazione ±8°), oppure quella scelta dal progettista; la piastra A tagliata alla profondità della soglia, 4 mm prima del suo bordo (se la piastra è più corta della soglia: da verificare); una coppia ogni 400 mm della luce, almeno tre, le estreme a 10 mm dai bordi della luce</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>dati del fornitore del limitatore</t>
+          <t>catalogo staffe Panev 2026, pp. 14-18 (coppie) e p. 05 (taglio della piastra)</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>pagine pfb.it e montanarigiulio.com, schede di elevatorequipment.co.uk (altezze, basi), estratti di ricerca del 1° ottobre 2026</t>
+          <t>catalogo del costruttore (panev/docs/catalogo-staffe-panev-2026.pdf); il passo e il numero minimo sono scelta del software</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
@@ -4025,33 +4025,33 @@
       <c r="M70" s="11" t="n"/>
       <c r="N70" s="11" t="n"/>
     </row>
-    <row r="71" ht="82" customHeight="1">
+    <row r="71" ht="355" customHeight="1">
       <c r="A71" s="10" t="n">
         <v>69</v>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Spazi di rifugio sul tetto di cabina e in fossa</t>
+          <t>Limitatore di velocità e tenditore (pianta, locale macchina, 3D) — il disegno unico delle LK200–LK315 dà due altezze non spiegate (230 e 415 mm; un rivenditore scrive 370): è presa la maggiore. Per Bode la velocità nominale massima è nostra: la velocità di scatto massima diviso 1,15 (scatto ≥ 115 % della nominale), del GB 8 con 1,49 m/s del disegno invece dei 2,04 della brochure. Per le RQ-A e le RC Montanari 0,15–3,0 e 1,60–4,2 m/s sono i campi della famiglia: il limite di ogni taglia va letto sul manuale. Delle basi pubblicate non sempre è detto quale lato stia nel piano della puleggia (il lato lungo è disegnato in quel piano, come nel LK200). Tenditore a leva: lungo 700 mm (quota «A» del PFB R4KE per LK200 in un listino di rivenditore, senza definizione), puleggia a 255 mm dalla cerniera e blocco di 150 × 185 mm: scelte del software; le masse di 22 e 44 kg sono quelle delle tabelle PFB (tenditori R4K e R4R per LK200, confermate dalla brochure)</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>tipo 1 (in piedi) 400 × 500 mm in pianta, alto 2000 mm; tipo 2 (accucciato) 500 × 700 mm, alto 1000 mm; tipo 3 (disteso, solo in fossa) 700 × 1000 mm, alto 500 mm; in testata con la cabina nella posizione più alta, in fossa con la cabina sugli ammortizzatori compressi</t>
+          <t>per velocità il più piccolo PFB che la regge: LK200 (Ø 200, fune 6) fino a 1,48 m/s, LK250 fino a 1,74, LK300 fino a 2,93, R12BF fino a 4,00; oppure il modello scelto se regge la velocità: PFB (LX, LK, R1, R3LR, R5, R6, R10BF), Bode (GB 7 fino a 2,98 m/s, GB 8 fino a 1,29), Dynatech (VEGA 200 fino a 2,40), Wittur (OL20 fino a 1,75, OL35 fino a 3,00, EOS fino a 2,50, OL100 fino a 10,00) o Montanari (RQ-A 200, 250 e 300, RC 200 e 300, NOR fino a 1,50 m/s, RG 200 fino a 0,30). Con le quote dei disegni dei costruttori (altezza totale, tra parentesi l'asse dalla base): LK200, LK250, LK300 e LK315 415 (165) su base 220 × 165 (LK315 220 × 130); LX120 178 (70,5), LK120 270 (71), LX150 274 (86), LX180 322 (107), LX200 349 (110); R1 344 (190,5) su base 285 × 80; R3LR 348 (157); R5 261 (120); R6 335 (168); R10BF 488 (303) su base 460 × 196; R12BF 524 (337) su base 520 × 116; Bode GB 7 360 (205) e GB 8 315 (205); Dynatech VEGA 200 332 (199,5); Wittur e Montanari nelle proporzioni del software (Ø 200: alto 370, asse a 240). Tenditore in fossa sulla guida di cabina: a leva con 22 kg (come PFB R4K) o verticale con 44 kg (come PFB R4R)</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1 (Tabella 3)</t>
+          <t>dati del fornitore del limitatore</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>manuali d'uso PFB con i disegni quotati (download.pfb.it), brochure Bode e Wittur, manuale Dynatech VEGA e disegni Bode in copia presso un rivenditore (elevatorequipment.co.uk), letti il 2 ottobre 2026; basi delle LK da un listino di rivenditore; Montanari da estratti di ricerca del 1° ottobre 2026 (research/argano-geared/18-porte-limitatori-tenditori-tutti.md)</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>spazio di rifugio in testata; spazio di rifugio in fossa</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="11" t="n"/>
@@ -4071,7 +4071,7 @@
       <c r="M71" s="11" t="n"/>
       <c r="N71" s="11" t="n"/>
     </row>
-    <row r="72" ht="56" customHeight="1">
+    <row r="72" ht="82" customHeight="1">
       <c r="A72" s="10" t="n">
         <v>70</v>
       </c>
@@ -4082,17 +4082,17 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Posizione più alta della cabina</t>
+          <t>Spazi di rifugio sul tetto di cabina e in fossa</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>contrappeso sugli ammortizzatori completamente compressi, più il salto 0,035·v² m (v velocità nominale)</t>
+          <t>tipo 1 (in piedi) 400 × 500 mm in pianta, alto 2000 mm; tipo 2 (accucciato) 500 × 700 mm, alto 1000 mm; tipo 3 (disteso, solo in fossa) 700 × 1000 mm, alto 500 mm; in testata con la cabina nella posizione più alta, in fossa con la cabina sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.6.1 (Tabella 2)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1 (Tabella 3)</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>spazio di rifugio in testata; distanze libere dal soffitto</t>
+          <t>spazio di rifugio in testata; spazio di rifugio in fossa</t>
         </is>
       </c>
       <c r="I72" s="11" t="n"/>
@@ -4128,17 +4128,17 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Distanze libere dal soffitto con la cabina nella posizione più alta</t>
+          <t>Posizione più alta della cabina</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>≥ 500 mm sopra le apparecchiature sul tetto di cabina (operatore); ≥ 100 mm sopra pattini, attacchi delle funi e traversa dell'arcata; ≥ 300 mm sopra il corrimano della balaustra</t>
+          <t>contrappeso sugli ammortizzatori completamente compressi, più il salto 0,035·v² m (v velocità nominale)</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.2</t>
+          <t>UNI EN 81-20:2020, 5.2.5.6.1 (Tabella 2)</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>distanze libere dal soffitto</t>
+          <t>spazio di rifugio in testata; distanze libere dal soffitto</t>
         </is>
       </c>
       <c r="I73" s="11" t="n"/>
@@ -4174,17 +4174,17 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Distanze in fossa con la cabina sugli ammortizzatori compressi</t>
+          <t>Distanze libere dal soffitto con la cabina nella posizione più alta</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>≥ 500 mm dal pavimento della fossa alle parti più basse della cabina; grembiule alto ≥ 750 mm sotto la soglia di cabina, con ≥ 100 mm liberi dal pavimento della fossa</t>
+          <t>≥ 500 mm sopra le apparecchiature sul tetto di cabina (operatore); ≥ 100 mm sopra pattini, attacchi delle funi e traversa dell'arcata; ≥ 300 mm sopra il corrimano della balaustra</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.8.2 e 5.4.5</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.2</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>spazio di rifugio in fossa; grembiule sugli ammortizzatori compressi</t>
+          <t>distanze libere dal soffitto</t>
         </is>
       </c>
       <c r="I74" s="11" t="n"/>
@@ -4220,17 +4220,17 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Balaustra sul tetto di cabina</t>
+          <t>Distanze in fossa con la cabina sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>richiesta se la distanza libera dal tetto alla parete supera 300 mm: alta 700 mm fino a 500 mm di distanza, 1100 mm oltre</t>
+          <t>≥ 500 mm dal pavimento della fossa alle parti più basse della cabina; grembiule alto ≥ 750 mm sotto la soglia di cabina, con ≥ 100 mm liberi dal pavimento della fossa</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.7.4</t>
+          <t>UNI EN 81-20:2020, 5.2.5.8.2 e 5.4.5</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>balaustra sul tetto di cabina</t>
+          <t>spazio di rifugio in fossa; grembiule sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="I75" s="11" t="n"/>
@@ -4266,17 +4266,17 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Superficie dove una persona può stare sul tetto di cabina</t>
+          <t>Balaustra sul tetto di cabina</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>area continua ≥ 0,12 m² con il lato minore ≥ 250 mm (disegnata 400 × 300 mm, modificabile sulla pianta in testata); sopra di essa deve esserci l'altezza dello spazio di rifugio</t>
+          <t>richiesta se la distanza libera dal tetto alla parete supera 300 mm: alta 700 mm fino a 500 mm di distanza, 1100 mm oltre</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.3</t>
+          <t>UNI EN 81-20:2020, 5.4.7.4</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>superficie per stare sul tetto di cabina</t>
+          <t>balaustra sul tetto di cabina</t>
         </is>
       </c>
       <c r="I76" s="11" t="n"/>
@@ -4301,7 +4301,7 @@
       <c r="M76" s="11" t="n"/>
       <c r="N76" s="11" t="n"/>
     </row>
-    <row r="77" ht="69" customHeight="1">
+    <row r="77" ht="56" customHeight="1">
       <c r="A77" s="10" t="n">
         <v>75</v>
       </c>
@@ -4312,17 +4312,17 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Schermo del contrappeso in fossa</t>
+          <t>Superficie dove una persona può stare sul tetto di cabina</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>dal punto più basso del contrappeso sugli ammortizzatori compressi fino ad almeno 2000 mm sopra il pavimento della fossa (altezza dello schermo modificabile sul progetto, mai sotto questo valore)</t>
+          <t>area continua ≥ 0,12 m² con il lato minore ≥ 250 mm (disegnata 400 × 300 mm, modificabile sulla pianta in testata); sopra di essa deve esserci l'altezza dello spazio di rifugio</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.5.1</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.3</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>protezione del contrappeso in fossa</t>
+          <t>superficie per stare sul tetto di cabina</t>
         </is>
       </c>
       <c r="I77" s="11" t="n"/>
@@ -4358,17 +4358,17 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori ad accumulo di energia lineari (molle)</t>
+          <t>Schermo del contrappeso in fossa</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>ammessi fino a 1 m/s; corsa ≥ 0,135·v² m e comunque ≥ 65 mm; extracorsa della cabina e del contrappeso ≥ 0 (nessun minimo nella norma)</t>
+          <t>dal punto più basso del contrappeso sugli ammortizzatori compressi fino ad almeno 2000 mm sopra il pavimento della fossa (altezza dello schermo modificabile sul progetto, mai sotto questo valore)</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2 (accumulo di energia, caratteristica lineare; sottoclausola da verificare sul testo)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.5.1</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso; extracorsa di cabina e contrappeso</t>
+          <t>protezione del contrappeso in fossa</t>
         </is>
       </c>
       <c r="I78" s="11" t="n"/>
@@ -4393,7 +4393,7 @@
       <c r="M78" s="11" t="n"/>
       <c r="N78" s="11" t="n"/>
     </row>
-    <row r="79" ht="121" customHeight="1">
+    <row r="79" ht="69" customHeight="1">
       <c r="A79" s="10" t="n">
         <v>77</v>
       </c>
@@ -4404,22 +4404,22 @@
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori ad accumulo di energia non lineari (tamponi in poliuretano)</t>
+          <t>Ammortizzatori ad accumulo di energia lineari (molle)</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>ammessi fino a 1 m/s come le molle; nessuna corsa minima da formula: il campo di masse del certificato di esame di tipo per la velocità deve comprendere, per ogni tampone, la cabina vuota e a pieno carico (o il contrappeso); «completamente compresso» vuol dire compresso del 90 % dell'altezza, quindi la corsa è 0,9·H negli spazi in fossa e in testata; tampone tipico alti 80 mm (P+S Diepocell D, Ø da 80 a 220 mm; ACLA AUTAN XL)</t>
+          <t>ammessi fino a 1 m/s; corsa ≥ 0,135·v² m e comunque ≥ 65 mm; extracorsa della cabina e del contrappeso ≥ 0 (nessun minimo nella norma)</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2 (caratteristica non lineare) e UNI EN 81-50:2020, 5.5 (esame di tipo); sottoclausole da verificare sul testo</t>
+          <t>UNI EN 81-20:2020, 5.8.2 (accumulo di energia, caratteristica lineare; sottoclausola da verificare sul testo)</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>cataloghi P+S Diepocell (wwlift.de), ACLA AUTAN XL (acla.de), Stingl (corsa al 90 %); estratti di ricerca del 1° ottobre 2026</t>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso</t>
+          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso; extracorsa di cabina e contrappeso</t>
         </is>
       </c>
       <c r="I79" s="11" t="n"/>
@@ -4439,7 +4439,7 @@
       <c r="M79" s="11" t="n"/>
       <c r="N79" s="11" t="n"/>
     </row>
-    <row r="80" ht="95" customHeight="1">
+    <row r="80" ht="121" customHeight="1">
       <c r="A80" s="10" t="n">
         <v>78</v>
       </c>
@@ -4450,22 +4450,22 @@
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori a dissipazione di energia (idraulici)</t>
+          <t>Ammortizzatori ad accumulo di energia non lineari (tamponi in poliuretano)</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>a ogni velocità; corsa ≥ 0,0674·v² m (arresto per gravità al 115 % della velocità nominale); la corsa ridotta con il controllo del rallentamento non è considerata; ammortizzatori tipici: Oleo LSB10 fino a 1 m/s, alto 222,2 mm con corsa 73,4 mm; LSB16 fino a 1,6 m/s, alto 485,5 mm con corsa 173,5 mm</t>
+          <t>ammessi fino a 1 m/s come le molle; nessuna corsa minima da formula: il campo di masse del certificato di esame di tipo per la velocità deve comprendere, per ogni tampone, la cabina vuota e a pieno carico (o il contrappeso); «completamente compresso» vuol dire compresso del 90 % dell'altezza, quindi la corsa è 0,9·H negli spazi in fossa e in testata; tampone tipico alti 80 mm (P+S Diepocell D, Ø da 80 a 220 mm; ACLA AUTAN XL)</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2 (dissipazione di energia; sottoclausola da verificare sul testo)</t>
+          <t>UNI EN 81-20:2020, 5.8.2 (caratteristica non lineare) e UNI EN 81-50:2020, 5.5 (esame di tipo); sottoclausole da verificare sul testo</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>catalogo Oleo LSB e SEB (oleo.co.uk), estratti di ricerca del 1° ottobre 2026</t>
+          <t>cataloghi P+S Diepocell (wwlift.de), ACLA AUTAN XL (acla.de), Stingl (corsa al 90 %); estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
@@ -4485,33 +4485,33 @@
       <c r="M80" s="11" t="n"/>
       <c r="N80" s="11" t="n"/>
     </row>
-    <row r="81" ht="69" customHeight="1">
+    <row r="81" ht="95" customHeight="1">
       <c r="A81" s="10" t="n">
         <v>79</v>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Ammortizzatori a dissipazione di energia (idraulici)</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>altezza libera delle zone di lavoro ≥ 2100 mm (1800 mm sui percorsi); davanti al quadro una superficie libera profonda ≥ 700 mm e larga ≥ 500 mm o quanto il quadro; porta di accesso ≥ 600 × 2000 mm</t>
+          <t>a ogni velocità; corsa ≥ 0,0674·v² m (arresto per gravità al 115 % della velocità nominale); la corsa ridotta con il controllo del rallentamento non è considerata; ammortizzatori tipici: Oleo LSB10 fino a 1 m/s, alto 222,2 mm con corsa 73,4 mm; LSB16 fino a 1,6 m/s, alto 485,5 mm con corsa 173,5 mm</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.6.3.2.1 e 5.2.3</t>
+          <t>UNI EN 81-20:2020, 5.8.2 (dissipazione di energia; sottoclausola da verificare sul testo)</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>catalogo Oleo LSB e SEB (oleo.co.uk), estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>altezza del locale macchina; superficie libera davanti al quadro; porta del locale macchina</t>
+          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso</t>
         </is>
       </c>
       <c r="I81" s="11" t="n"/>
@@ -4542,17 +4542,17 @@
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Illuminazione del vano e del locale del macchinario</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>vano: illuminazione fissa di almeno 50 lux a 1 m sopra il tetto della cabina e sopra il pavimento della fossa, 20 lux altrove; locale del macchinario: almeno 200 lux al pavimento nelle zone di lavoro</t>
+          <t>altezza libera delle zone di lavoro ≥ 2100 mm (1800 mm sui percorsi); davanti al quadro una superficie libera profonda ≥ 700 mm e larga ≥ 500 mm o quanto il quadro; porta di accesso ≥ 600 × 2000 mm</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.4</t>
+          <t>UNI EN 81-20:2020, 5.2.6.3.2.1 e 5.2.3</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>altezza del locale macchina; superficie libera davanti al quadro; porta del locale macchina</t>
         </is>
       </c>
       <c r="I82" s="11" t="n"/>
@@ -4577,7 +4577,7 @@
       <c r="M82" s="11" t="n"/>
       <c r="N82" s="11" t="n"/>
     </row>
-    <row r="83" ht="56" customHeight="1">
+    <row r="83" ht="69" customHeight="1">
       <c r="A83" s="10" t="n">
         <v>81</v>
       </c>
@@ -4588,17 +4588,17 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Temperatura dei locali del macchinario e degli armadi</t>
+          <t>Illuminazione del vano e del locale del macchinario</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>temperatura ambiente mantenuta tra +5 °C e +40 °C: ipotesi della norma, da garantire nell'edificio</t>
+          <t>vano: illuminazione fissa di almeno 50 lux a 1 m sopra il tetto della cabina e sopra il pavimento della fossa, 20 lux altrove; locale del macchinario: almeno 200 lux al pavimento nelle zone di lavoro</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, introduzione (ipotesi)</t>
+          <t>UNI EN 81-20:2020, 5.2.1.4</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
@@ -4623,7 +4623,7 @@
       <c r="M83" s="11" t="n"/>
       <c r="N83" s="11" t="n"/>
     </row>
-    <row r="84" ht="199" customHeight="1">
+    <row r="84" ht="56" customHeight="1">
       <c r="A84" s="10" t="n">
         <v>82</v>
       </c>
@@ -4634,27 +4634,27 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Basamento dell'argano</t>
+          <t>Temperatura dei locali del macchinario e degli armadi</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>su spessori di livellamento sotto gli appoggi (l'asse della puleggia dove lo mette il software), su telaio di due profilati sul pavimento (tipico UPN 200, alto quanto il profilato come i telai bassi universali), su due putrelle da muro a muro che possono stare sollevate dal pavimento (tipiche IPE 200, appoggio nei muri 150 mm), su piastre d'acciaio sotto gli appoggi (tipiche 20 mm) o su plinto in calcestruzzo (tipico 250 mm); tamponi antivibranti di 30 mm sotto gli appoggi, salvo sugli spessori; telaio e plinto 100 mm oltre il telaio dell'argano a ogni estremità; l'altezza del basamento porta l'asse della puleggia, che il calcolo (tratto di fune oltre la corsa) e il 3D seguono</t>
+          <t>temperatura ambiente mantenuta tra +5 °C e +40 °C: ipotesi della norma, da garantire nell'edificio</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio); scelta del costruttore</t>
+          <t>UNI EN 81-20:2020, introduzione (ipotesi)</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>telaio basso universale per argano alto 200 mm (lift-store.it); tamponi antivibranti 25–30 mm (catalogo Donati); piastre di 20 mm e plinto di 250–300 mm nella pratica di installazione (fonti estere, da confermare); estratti di ricerca del 1° ottobre 2026</t>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
@@ -4669,7 +4669,7 @@
       <c r="M84" s="11" t="n"/>
       <c r="N84" s="11" t="n"/>
     </row>
-    <row r="85" ht="147" customHeight="1">
+    <row r="85" ht="199" customHeight="1">
       <c r="A85" s="10" t="n">
         <v>83</v>
       </c>
@@ -4680,22 +4680,22 @@
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Telaio sotto l'argano di un costruttore</t>
+          <t>Basamento dell'argano</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>l'argano di catalogo poggia con i suoi piedi su un telaio di due travi sotto le file di fori, con antivibranti alle estremità e 40 mm oltre l'argano a ogni estremità; il telaio è alto quanto serve per tenere l'asse della puleggia dove lo tiene l'argano generico del software, almeno 80 mm e con il bordo della puleggia 30 mm sopra il suo piano d'appoggio (gli argani compatti hanno la puleggia a sbalzo, sotto il piano dei piedi); se l'argano non lo permette l'asse sale e il calcolo segue</t>
+          <t>su spessori di livellamento sotto gli appoggi (l'asse della puleggia dove lo mette il software), su telaio di due profilati sul pavimento (tipico UPN 200, alto quanto il profilato come i telai bassi universali), su due putrelle da muro a muro che possono stare sollevate dal pavimento (tipiche IPE 200, appoggio nei muri 150 mm), su piastre d'acciaio sotto gli appoggi (tipiche 20 mm) o su plinto in calcestruzzo (tipico 250 mm); tamponi antivibranti di 30 mm sotto gli appoggi, salvo sugli spessori; telaio e plinto 100 mm oltre il telaio dell'argano a ogni estremità; l'altezza del basamento porta l'asse della puleggia, che il calcolo (tratto di fune oltre la corsa) e il 3D seguono</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio); scelta del costruttore</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>quote dei piedi, dei fori e dell'asse della puleggia dalle schede tecniche del costruttore; altezza del telaio scelta dal software, da adattare al telaio fornito</t>
+          <t>telaio basso universale per argano alto 200 mm (lift-store.it); tamponi antivibranti 25–30 mm (catalogo Donati); piastre di 20 mm e plinto di 250–300 mm nella pratica di installazione (fonti estere, da confermare); estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
@@ -4715,7 +4715,7 @@
       <c r="M85" s="11" t="n"/>
       <c r="N85" s="11" t="n"/>
     </row>
-    <row r="86" ht="134" customHeight="1">
+    <row r="86" ht="147" customHeight="1">
       <c r="A86" s="10" t="n">
         <v>84</v>
       </c>
@@ -4726,32 +4726,32 @@
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
+          <t>Telaio sotto l'argano di un costruttore</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
+          <t>l'argano di catalogo poggia con i suoi piedi su un telaio di due travi sotto le file di fori, con antivibranti alle estremità e 40 mm oltre l'argano a ogni estremità; il telaio è alto quanto serve per tenere l'asse della puleggia dove lo tiene l'argano generico del software, almeno 80 mm e con il bordo della puleggia 30 mm sopra il suo piano d'appoggio (gli argani compatti hanno la puleggia a sbalzo, sotto il piano dei piedi); se l'argano non lo permette l'asse sale e il calcolo segue</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E); DPR 1497/1963, art. 5 (carichi fissi più 1,5 volte il carico statico delle funi; freccia ≤ 1/1500 della luce libera: regola storica, da confermare)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
+          <t>quote dei piedi, dei fori e dell'asse della puleggia dalle schede tecniche del costruttore; altezza del telaio scelta dal software, da adattare al telaio fornito</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I86" s="11" t="n"/>
@@ -4761,33 +4761,33 @@
       <c r="M86" s="11" t="n"/>
       <c r="N86" s="11" t="n"/>
     </row>
-    <row r="87" ht="108" customHeight="1">
+    <row r="87" ht="134" customHeight="1">
       <c r="A87" s="10" t="n">
         <v>85</v>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Carichi sul pavimento della fossa</t>
+          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
+          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.8; UNI EN 81-50:2020, 5.10</t>
+          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E), §3.1.4 (carichi del macchinario); DPR 1497/1963, art. 5.1–5.2 (carichi fissi più 1,5 volte il carico statico delle funi, sicurezza ≥ 6, freccia ≤ 1/1500 della luce libera: regola storica degli impianti esistenti, letta su Normattiva)</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi; sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
+          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
         </is>
       </c>
       <c r="I87" s="11" t="n"/>
@@ -4818,22 +4818,22 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Spinte sulle guide di cabina</t>
+          <t>Carichi sul pavimento della fossa</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
+          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.10</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8; UNI EN 81-50:2020, 5.10</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi; sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
@@ -4853,7 +4853,7 @@
       <c r="M88" s="11" t="n"/>
       <c r="N88" s="11" t="n"/>
     </row>
-    <row r="89" ht="82" customHeight="1">
+    <row r="89" ht="108" customHeight="1">
       <c r="A89" s="10" t="n">
         <v>87</v>
       </c>
@@ -4864,27 +4864,27 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Carico della macchina sulla soletta</t>
+          <t>Spinte sulle guide di cabina</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
+          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.10</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
+          <t>sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>prassi di cantiere</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       <c r="M89" s="11" t="n"/>
       <c r="N89" s="11" t="n"/>
     </row>
-    <row r="90" ht="43" customHeight="1">
+    <row r="90" ht="82" customHeight="1">
       <c r="A90" s="10" t="n">
         <v>88</v>
       </c>
@@ -4910,12 +4910,12 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Massa dei cavi flessibili</t>
+          <t>Carico della macchina sulla soletta</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
+          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
+          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>prassi di cantiere</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
@@ -4945,7 +4945,7 @@
       <c r="M90" s="11" t="n"/>
       <c r="N90" s="11" t="n"/>
     </row>
-    <row r="91" ht="121" customHeight="1">
+    <row r="91" ht="43" customHeight="1">
       <c r="A91" s="10" t="n">
         <v>89</v>
       </c>
@@ -4956,27 +4956,27 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
+          <t>Massa dei cavi flessibili</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
+          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
-          <t>regola di montaggio indicata dal committente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>scelta del committente</t>
+          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
@@ -4991,7 +4991,7 @@
       <c r="M91" s="11" t="n"/>
       <c r="N91" s="11" t="n"/>
     </row>
-    <row r="92" ht="82" customHeight="1">
+    <row r="92" ht="121" customHeight="1">
       <c r="A92" s="10" t="n">
         <v>90</v>
       </c>
@@ -5002,27 +5002,27 @@
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Lunghezze stimate nel foglio dei dati</t>
+          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
+          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>regola di montaggio indicata dal committente</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>stima del software, da sostituire con le misure di cantiere</t>
+          <t>scelta del committente</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
@@ -5037,23 +5037,23 @@
       <c r="M92" s="11" t="n"/>
       <c r="N92" s="11" t="n"/>
     </row>
-    <row r="93" ht="43" customHeight="1">
+    <row r="93" ht="82" customHeight="1">
       <c r="A93" s="10" t="n">
         <v>91</v>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Dimensioni proposte della cabina</t>
+          <t>Lunghezze stimate nel foglio dei dati</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
+          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima del software, da sostituire con le misure di cantiere</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
@@ -5083,7 +5083,7 @@
       <c r="M93" s="11" t="n"/>
       <c r="N93" s="11" t="n"/>
     </row>
-    <row r="94" ht="199" customHeight="1">
+    <row r="94" ht="43" customHeight="1">
       <c r="A94" s="10" t="n">
         <v>92</v>
       </c>
@@ -5094,12 +5094,12 @@
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Quote della pianta fissate a mano</t>
+          <t>Dimensioni proposte della cabina</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8), quello del contrappeso dentro la lunghezza del contrappeso</t>
+          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I94" s="11" t="n"/>
@@ -5129,7 +5129,7 @@
       <c r="M94" s="11" t="n"/>
       <c r="N94" s="11" t="n"/>
     </row>
-    <row r="95" ht="82" customHeight="1">
+    <row r="95" ht="199" customHeight="1">
       <c r="A95" s="10" t="n">
         <v>93</v>
       </c>
@@ -5140,12 +5140,12 @@
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Limiti del modello del vano</t>
+          <t>Quote della pianta fissate a mano</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
+          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8), quello del contrappeso dentro la lunghezza del contrappeso</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>limite del modello attuale</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
         </is>
       </c>
       <c r="I95" s="11" t="n"/>
@@ -5175,23 +5175,23 @@
       <c r="M95" s="11" t="n"/>
       <c r="N95" s="11" t="n"/>
     </row>
-    <row r="96" ht="56" customHeight="1">
+    <row r="96" ht="82" customHeight="1">
       <c r="A96" s="10" t="n">
         <v>94</v>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Corsa</t>
+          <t>Limiti del modello del vano</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
+          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>dati dei piani inseriti</t>
+          <t>limite del modello attuale</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
@@ -5232,22 +5232,22 @@
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Portata e velocità</t>
+          <t>Corsa</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
+          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.2.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>progetto del vano</t>
+          <t>dati dei piani inseriti</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
@@ -5267,7 +5267,7 @@
       <c r="M97" s="11" t="n"/>
       <c r="N97" s="11" t="n"/>
     </row>
-    <row r="98" ht="160" customHeight="1">
+    <row r="98" ht="56" customHeight="1">
       <c r="A98" s="10" t="n">
         <v>96</v>
       </c>
@@ -5278,27 +5278,27 @@
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Normativa di collaudo e parti sostituite o modificate — il testo delle UNI 10411 del 2024 non è stato letto: le verifiche per parte e i requisiti per la sostituzione del macchinario (edizione 2021: freno in due elementi, temporizzatore, velocità eccessiva in salita, arresto entro 1 m dalla macchina, interruzione se il freno non si apre) vanno confermati sul testo vigente</t>
+          <t>Portata e velocità</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software</t>
+          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
+          <t>UNI EN 81-20:2020, 5.4.2.1</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>schede UNI delle norme (scopo, data 31/10/2024); schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); sintesi secondarie; ricerca, capitoli 2.4 e 6.6</t>
+          <t>progetto del vano</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
@@ -5313,7 +5313,7 @@
       <c r="M98" s="11" t="n"/>
       <c r="N98" s="11" t="n"/>
     </row>
-    <row r="99" ht="69" customHeight="1">
+    <row r="99" ht="303" customHeight="1">
       <c r="A99" s="10" t="n">
         <v>97</v>
       </c>
@@ -5324,27 +5324,27 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
+          <t>Normativa di collaudo e parti sostituite o modificate — il testo delle UNI 10411 del 2024 non è stato letto: le verifiche per parte e i requisiti per la sostituzione del macchinario (edizione 2021: freno in due elementi, temporizzatore, velocità eccessiva in salita, arresto entro 1 m dalla macchina, interruzione se il freno non si apre) vanno confermati sul testo vigente</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
+          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software. Alla norma base si aggiungono le norme compatibili (matrice della ricerca, cap. 16 §5.2): sull'impianto nuovo le EN 81 supplementari (21, 28, 58, 70, 71, 72, 73, 76, 77), sulla modifica la EN 81-20/50 intera, le EN 81-28, 58, 73 e il miglioramento (80, 82, 83), su entrambi DM 236/1989, antincendio (DM 15/09/2005 o Codice V.3) e NTC 2018 (con le verifiche delle putrelle). Ogni norma ha il suo esito («non calcolata» se il software non ne calcola verifiche) e i suoi punti da verificare in sito nella relazione, con gli adempimenti del DPR 162/1999</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
+          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>scelta del software, senza fonte</t>
+          <t>schede UNI delle norme (scopo, data 31/10/2024); schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); sintesi secondarie; ricerca, capitoli 2.4 e 6.6</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H99" s="10" t="inlineStr">
@@ -5359,7 +5359,7 @@
       <c r="M99" s="11" t="n"/>
       <c r="N99" s="11" t="n"/>
     </row>
-    <row r="100" ht="82" customHeight="1">
+    <row r="100" ht="69" customHeight="1">
       <c r="A100" s="10" t="n">
         <v>98</v>
       </c>
@@ -5370,27 +5370,27 @@
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Fune oltre la corsa (L0)</t>
+          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale (macchina in basso o senza locale: fino al soffitto del vano)</t>
+          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
+          <t>scelta del software, senza fonte</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H100" s="10" t="inlineStr">
@@ -5405,7 +5405,7 @@
       <c r="M100" s="11" t="n"/>
       <c r="N100" s="11" t="n"/>
     </row>
-    <row r="101" ht="147" customHeight="1">
+    <row r="101" ht="82" customHeight="1">
       <c r="A101" s="10" t="n">
         <v>99</v>
       </c>
@@ -5416,27 +5416,27 @@
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
+          <t>Fune oltre la corsa (L0)</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
+          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale (macchina in basso o senza locale: fino al soffitto del vano)</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>pianta del vano</t>
+          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H101" s="10" t="inlineStr">
@@ -5451,7 +5451,7 @@
       <c r="M101" s="11" t="n"/>
       <c r="N101" s="11" t="n"/>
     </row>
-    <row r="102" ht="160" customHeight="1">
+    <row r="102" ht="147" customHeight="1">
       <c r="A102" s="10" t="n">
         <v>100</v>
       </c>
@@ -5462,22 +5462,22 @@
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
+          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
+          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
+          <t>ricerca, capitolo 5.3</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>geometria delle funi</t>
+          <t>pianta del vano</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
@@ -5497,7 +5497,7 @@
       <c r="M102" s="11" t="n"/>
       <c r="N102" s="11" t="n"/>
     </row>
-    <row r="103" ht="56" customHeight="1">
+    <row r="103" ht="160" customHeight="1">
       <c r="A103" s="10" t="n">
         <v>101</v>
       </c>
@@ -5508,22 +5508,22 @@
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
+          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
+          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
+          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano</t>
+          <t>geometria delle funi</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
@@ -5543,7 +5543,7 @@
       <c r="M103" s="11" t="n"/>
       <c r="N103" s="11" t="n"/>
     </row>
-    <row r="104" ht="238" customHeight="1">
+    <row r="104" ht="56" customHeight="1">
       <c r="A104" s="10" t="n">
         <v>102</v>
       </c>
@@ -5554,27 +5554,27 @@
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso o pilastro pieno fino al terreno (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori</t>
+          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
+          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
+          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>geometria ricostruita dal software</t>
+          <t>dati verticali del vano</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr">
@@ -5589,7 +5589,7 @@
       <c r="M104" s="11" t="n"/>
       <c r="N104" s="11" t="n"/>
     </row>
-    <row r="105" ht="186" customHeight="1">
+    <row r="105" ht="238" customHeight="1">
       <c r="A105" s="10" t="n">
         <v>103</v>
       </c>
@@ -5600,27 +5600,27 @@
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta dal catalogo di un costruttore — i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
+          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso o pilastro pieno fino al terreno (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo; i disegni e il 3D mostrano l'argano SICOR com'è (ingombri, piedi e fori, asse della puleggia, P ed E della scheda), sul telaio del software</t>
+          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
         </is>
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
+          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>SICOR: schede tecniche 2025 e modelli CAD scaricati da sicoritaly.com il 2 ottobre 2026 (solo le quote); Sassi, Montanari, GEM, FAER: estratti delle pagine dei costruttori e dei rivenditori, 1° ottobre 2026</t>
+          <t>geometria ricostruita dal software</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
@@ -5635,7 +5635,7 @@
       <c r="M105" s="11" t="n"/>
       <c r="N105" s="11" t="n"/>
     </row>
-    <row r="106" ht="134" customHeight="1">
+    <row r="106" ht="186" customHeight="1">
       <c r="A106" s="10" t="n">
         <v>104</v>
       </c>
@@ -5646,27 +5646,27 @@
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
+          <t>Macchina proposta dal catalogo di un costruttore — i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
+          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo; i disegni e il 3D mostrano l'argano SICOR com'è (ingombri, piedi e fori, asse della puleggia, P ed E della scheda), sul telaio del software</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 8</t>
+          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo</t>
+          <t>SICOR: schede tecniche 2025 e modelli CAD scaricati da sicoritaly.com il 2 ottobre 2026 (solo le quote); Sassi, Montanari, GEM, FAER: estratti delle pagine dei costruttori e dei rivenditori, 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
@@ -5681,38 +5681,38 @@
       <c r="M106" s="11" t="n"/>
       <c r="N106" s="11" t="n"/>
     </row>
-    <row r="107" ht="69" customHeight="1">
+    <row r="107" ht="134" customHeight="1">
       <c r="A107" s="10" t="n">
         <v>105</v>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
+          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
+          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
+          <t>ricerca, capitolo 8</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo (src/calc/model.ts)</t>
+          <t>motore di calcolo</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
@@ -5727,7 +5727,7 @@
       <c r="M107" s="11" t="n"/>
       <c r="N107" s="11" t="n"/>
     </row>
-    <row r="108" ht="56" customHeight="1">
+    <row r="108" ht="69" customHeight="1">
       <c r="A108" s="10" t="n">
         <v>106</v>
       </c>
@@ -5738,27 +5738,27 @@
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
+          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
+          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
+          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>motore di calcolo (src/calc/model.ts)</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H108" s="10" t="inlineStr">
@@ -5773,7 +5773,7 @@
       <c r="M108" s="11" t="n"/>
       <c r="N108" s="11" t="n"/>
     </row>
-    <row r="109" ht="69" customHeight="1">
+    <row r="109" ht="56" customHeight="1">
       <c r="A109" s="10" t="n">
         <v>107</v>
       </c>
@@ -5784,17 +5784,17 @@
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Limite di aderenza mostrato durante la marcia</t>
+          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
+          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
         </is>
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.2</t>
+          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
@@ -5819,7 +5819,7 @@
       <c r="M109" s="11" t="n"/>
       <c r="N109" s="11" t="n"/>
     </row>
-    <row r="110" ht="43" customHeight="1">
+    <row r="110" ht="69" customHeight="1">
       <c r="A110" s="10" t="n">
         <v>108</v>
       </c>
@@ -5830,22 +5830,22 @@
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Tempi delle porte</t>
+          <t>Limite di aderenza mostrato durante la marcia</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
+          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.2.2</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (solo animazione)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
@@ -5865,7 +5865,7 @@
       <c r="M110" s="11" t="n"/>
       <c r="N110" s="11" t="n"/>
     </row>
-    <row r="111" ht="108" customHeight="1">
+    <row r="111" ht="43" customHeight="1">
       <c r="A111" s="10" t="n">
         <v>109</v>
       </c>
@@ -5876,27 +5876,27 @@
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione</t>
+          <t>Tempi delle porte</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
+          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>sintesi della norma di costruttori e organismi notificati (fonti secondarie)</t>
+          <t>scelta del software (solo animazione)</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H111" s="10" t="inlineStr">
@@ -5911,7 +5911,7 @@
       <c r="M111" s="11" t="n"/>
       <c r="N111" s="11" t="n"/>
     </row>
-    <row r="112" ht="56" customHeight="1">
+    <row r="112" ht="108" customHeight="1">
       <c r="A112" s="10" t="n">
         <v>110</v>
       </c>
@@ -5922,27 +5922,27 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Cabina bloccata: rotazione in salita</t>
+          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
+          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2</t>
+          <t>UNI EN 81-20:2020, 5.8.2</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo; velocità scelta dal software</t>
+          <t>sintesi della norma di costruttori e organismi notificati (fonti secondarie)</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
@@ -5957,7 +5957,7 @@
       <c r="M112" s="11" t="n"/>
       <c r="N112" s="11" t="n"/>
     </row>
-    <row r="113" ht="43" customHeight="1">
+    <row r="113" ht="56" customHeight="1">
       <c r="A113" s="10" t="n">
         <v>111</v>
       </c>
@@ -5968,22 +5968,22 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Passo di campionamento</t>
+          <t>Cabina bloccata: rotazione in salita</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
+          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.2</t>
         </is>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>motore di calcolo; velocità scelta dal software</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
@@ -6003,10 +6003,2448 @@
       <c r="M113" s="11" t="n"/>
       <c r="N113" s="11" t="n"/>
     </row>
+    <row r="114" ht="43" customHeight="1">
+      <c r="A114" s="10" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
+          <t>Passo di campionamento</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
+        </is>
+      </c>
+      <c r="E114" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F114" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="G114" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H114" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I114" s="11" t="n"/>
+      <c r="J114" s="11" t="n"/>
+      <c r="K114" s="11" t="n"/>
+      <c r="L114" s="11" t="n"/>
+      <c r="M114" s="11" t="n"/>
+      <c r="N114" s="11" t="n"/>
+    </row>
+    <row r="115" ht="56" customHeight="1">
+      <c r="A115" s="10" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+        </is>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, art. 4-bis</t>
+        </is>
+      </c>
+      <c r="D115" s="10" t="inlineStr">
+        <is>
+          <t>progetto, fabbricazione, installazione e prove conformi all'All. I; documentazione tecnica e dichiarazione di conformità conservate per 10 anni</t>
+        </is>
+      </c>
+      <c r="E115" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, art. 4-bis</t>
+        </is>
+      </c>
+      <c r="F115" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G115" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H115" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I115" s="11" t="n"/>
+      <c r="J115" s="11" t="n"/>
+      <c r="K115" s="11" t="n"/>
+      <c r="L115" s="11" t="n"/>
+      <c r="M115" s="11" t="n"/>
+      <c r="N115" s="11" t="n"/>
+    </row>
+    <row r="116" ht="56" customHeight="1">
+      <c r="A116" s="10" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, artt. 6-bis e 7 c.3</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="inlineStr">
+        <is>
+          <t>procedura con un organismo notificato (All. V, VIII, X, XI o XII); marcatura CE in cabina con il numero dell'organismo</t>
+        </is>
+      </c>
+      <c r="E116" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, artt. 6-bis e 7 c.3</t>
+        </is>
+      </c>
+      <c r="F116" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G116" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H116" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I116" s="11" t="n"/>
+      <c r="J116" s="11" t="n"/>
+      <c r="K116" s="11" t="n"/>
+      <c r="L116" s="11" t="n"/>
+      <c r="M116" s="11" t="n"/>
+      <c r="N116" s="11" t="n"/>
+    </row>
+    <row r="117" ht="56" customHeight="1">
+      <c r="A117" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+        </is>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, art. 12 c.1–3</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>comunicazione al Comune entro 60 giorni dalla dichiarazione di conformità (oltre: con il verbale di una verifica straordinaria di attivazione); matricola entro 30 giorni</t>
+        </is>
+      </c>
+      <c r="E117" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, art. 12 c.1–3</t>
+        </is>
+      </c>
+      <c r="F117" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G117" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H117" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="n"/>
+      <c r="J117" s="11" t="n"/>
+      <c r="K117" s="11" t="n"/>
+      <c r="L117" s="11" t="n"/>
+      <c r="M117" s="11" t="n"/>
+      <c r="N117" s="11" t="n"/>
+    </row>
+    <row r="118" ht="56" customHeight="1">
+      <c r="A118" s="10" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>verifiche periodiche ogni 2 anni; controllo dei dispositivi di sicurezza, delle funi e dell'isolamento almeno ogni 6 mesi; targa in cabina</t>
+        </is>
+      </c>
+      <c r="E118" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
+        </is>
+      </c>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G118" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H118" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I118" s="11" t="n"/>
+      <c r="J118" s="11" t="n"/>
+      <c r="K118" s="11" t="n"/>
+      <c r="L118" s="11" t="n"/>
+      <c r="M118" s="11" t="n"/>
+      <c r="N118" s="11" t="n"/>
+    </row>
+    <row r="119" ht="43" customHeight="1">
+      <c r="A119" s="10" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>la modifica è costruttiva: la sostituzione del macchinario ne è il caso n. 5)</t>
+        </is>
+      </c>
+      <c r="E119" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
+        </is>
+      </c>
+      <c r="F119" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G119" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H119" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I119" s="11" t="n"/>
+      <c r="J119" s="11" t="n"/>
+      <c r="K119" s="11" t="n"/>
+      <c r="L119" s="11" t="n"/>
+      <c r="M119" s="11" t="n"/>
+      <c r="N119" s="11" t="n"/>
+    </row>
+    <row r="120" ht="43" customHeight="1">
+      <c r="A120" s="10" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, art. 12 c.4</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>prima della comunicazione, adeguamento della parte modificata o sostituita e delle altre parti interessate</t>
+        </is>
+      </c>
+      <c r="E120" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, art. 12 c.4</t>
+        </is>
+      </c>
+      <c r="F120" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G120" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H120" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I120" s="11" t="n"/>
+      <c r="J120" s="11" t="n"/>
+      <c r="K120" s="11" t="n"/>
+      <c r="L120" s="11" t="n"/>
+      <c r="M120" s="11" t="n"/>
+      <c r="N120" s="11" t="n"/>
+    </row>
+    <row r="121" ht="43" customHeight="1">
+      <c r="A121" s="10" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, art. 12 c.4–5</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>comunicazione al Comune e al soggetto delle verifiche periodiche; l'impianto non resta in esercizio senza le comunicazioni aggiornate</t>
+        </is>
+      </c>
+      <c r="E121" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, art. 12 c.4–5</t>
+        </is>
+      </c>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G121" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H121" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I121" s="11" t="n"/>
+      <c r="J121" s="11" t="n"/>
+      <c r="K121" s="11" t="n"/>
+      <c r="L121" s="11" t="n"/>
+      <c r="M121" s="11" t="n"/>
+      <c r="N121" s="11" t="n"/>
+    </row>
+    <row r="122" ht="56" customHeight="1">
+      <c r="A122" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, art. 14 c.3</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>verifica straordinaria da uno dei soggetti dell'art. 13 c.1, di norma limitata ai controlli sulle modifiche, con la documentazione delle modifiche e dei componenti sostituiti</t>
+        </is>
+      </c>
+      <c r="E122" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, art. 14 c.3</t>
+        </is>
+      </c>
+      <c r="F122" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G122" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H122" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I122" s="11" t="n"/>
+      <c r="J122" s="11" t="n"/>
+      <c r="K122" s="11" t="n"/>
+      <c r="L122" s="11" t="n"/>
+      <c r="M122" s="11" t="n"/>
+      <c r="N122" s="11" t="n"/>
+    </row>
+    <row r="123" ht="56" customHeight="1">
+      <c r="A123" s="10" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>prove dell'organismo notificato: funzionamento a vuoto e a pieno carico, in mancanza di energia, prova statica a 1,25 volte la portata e controllo che non restino deformazioni</t>
+        </is>
+      </c>
+      <c r="E123" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
+        </is>
+      </c>
+      <c r="F123" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G123" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H123" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I123" s="11" t="n"/>
+      <c r="J123" s="11" t="n"/>
+      <c r="K123" s="11" t="n"/>
+      <c r="L123" s="11" t="n"/>
+      <c r="M123" s="11" t="n"/>
+      <c r="N123" s="11" t="n"/>
+    </row>
+    <row r="124" ht="56" customHeight="1">
+      <c r="A124" s="10" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>documentazione tecnica con i risultati dei calcoli di progetto, le relazioni sulle prove e l'elenco delle norme armonizzate applicate, anche in parte</t>
+        </is>
+      </c>
+      <c r="E124" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
+        </is>
+      </c>
+      <c r="F124" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G124" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H124" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I124" s="11" t="n"/>
+      <c r="J124" s="11" t="n"/>
+      <c r="K124" s="11" t="n"/>
+      <c r="L124" s="11" t="n"/>
+      <c r="M124" s="11" t="n"/>
+      <c r="N124" s="11" t="n"/>
+    </row>
+    <row r="125" ht="56" customHeight="1">
+      <c r="A125" s="10" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>per gli ascensori dichiarati conformi dal 20/01/2027: requisiti dell'All. III del Regolamento macchine (tra cui 1.1.9 e 1.2.1), con una valutazione aggiuntiva per i requisiti nuovi o cambiati</t>
+        </is>
+      </c>
+      <c r="E125" s="10" t="inlineStr">
+        <is>
+          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
+        </is>
+      </c>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G125" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H125" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I125" s="11" t="n"/>
+      <c r="J125" s="11" t="n"/>
+      <c r="K125" s="11" t="n"/>
+      <c r="L125" s="11" t="n"/>
+      <c r="M125" s="11" t="n"/>
+      <c r="N125" s="11" t="n"/>
+    </row>
+    <row r="126" ht="56" customHeight="1">
+      <c r="A126" s="10" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI 10411-1:2024</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>UNI 10411-1:2024, scopo</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t>ascensori elettrici a frizione non conformi alla 95/16/CE né alla 2014/33/UE; esclude le modifiche che cambiano le misure antincendio (valgono il DM 15/09/2005 o il Codice V.3)</t>
+        </is>
+      </c>
+      <c r="E126" s="10" t="inlineStr">
+        <is>
+          <t>UNI 10411-1:2024, scopo</t>
+        </is>
+      </c>
+      <c r="F126" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G126" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H126" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I126" s="11" t="n"/>
+      <c r="J126" s="11" t="n"/>
+      <c r="K126" s="11" t="n"/>
+      <c r="L126" s="11" t="n"/>
+      <c r="M126" s="11" t="n"/>
+      <c r="N126" s="11" t="n"/>
+    </row>
+    <row r="127" ht="56" customHeight="1">
+      <c r="A127" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI 10411-11:2024</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>UNI 10411-11:2024, scopo</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t>ascensori elettrici a frizione conformi alla Direttiva Ascensori; esclude le modifiche che cambiano le misure antincendio (valgono il DM 15/09/2005 o il Codice V.3)</t>
+        </is>
+      </c>
+      <c r="E127" s="10" t="inlineStr">
+        <is>
+          <t>UNI 10411-11:2024, scopo</t>
+        </is>
+      </c>
+      <c r="F127" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G127" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H127" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="n"/>
+      <c r="J127" s="11" t="n"/>
+      <c r="K127" s="11" t="n"/>
+      <c r="L127" s="11" t="n"/>
+      <c r="M127" s="11" t="n"/>
+      <c r="N127" s="11" t="n"/>
+    </row>
+    <row r="128" ht="56" customHeight="1">
+      <c r="A128" s="10" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-21:2022, scopo</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>impianto nuovo o sostituzione completa in un edificio esistente; non copre le modifiche parziali (letto sull'edizione 2018)</t>
+        </is>
+      </c>
+      <c r="E128" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-21:2022, scopo</t>
+        </is>
+      </c>
+      <c r="F128" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G128" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H128" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I128" s="11" t="n"/>
+      <c r="J128" s="11" t="n"/>
+      <c r="K128" s="11" t="n"/>
+      <c r="L128" s="11" t="n"/>
+      <c r="M128" s="11" t="n"/>
+      <c r="N128" s="11" t="n"/>
+    </row>
+    <row r="129" ht="82" customHeight="1">
+      <c r="A129" s="10" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="inlineStr">
+        <is>
+          <t>spazi di rifugio ridotti solo con l'accordo preventivo: in edificio esistente PEC al Ministero con la certificazione dell'organismo prima dell'installazione (Procedura 2: dichiarazione dei punti della EN 81-21 applicati); la EN 81-21 da sola non giustifica la deroga</t>
+        </is>
+      </c>
+      <c r="E129" s="10" t="inlineStr">
+        <is>
+          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
+        </is>
+      </c>
+      <c r="F129" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G129" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H129" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I129" s="11" t="n"/>
+      <c r="J129" s="11" t="n"/>
+      <c r="K129" s="11" t="n"/>
+      <c r="L129" s="11" t="n"/>
+      <c r="M129" s="11" t="n"/>
+      <c r="N129" s="11" t="n"/>
+    </row>
+    <row r="130" ht="56" customHeight="1">
+      <c r="A130" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-28:2022</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="inlineStr">
+        <is>
+          <t>teleallarme verso un servizio di soccorso: requisiti da verificare sul testo della norma; il suo uso sugli impianti esistenti non è stato verificato</t>
+        </is>
+      </c>
+      <c r="E130" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-28:2022</t>
+        </is>
+      </c>
+      <c r="F130" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G130" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H130" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I130" s="11" t="n"/>
+      <c r="J130" s="11" t="n"/>
+      <c r="K130" s="11" t="n"/>
+      <c r="L130" s="11" t="n"/>
+      <c r="M130" s="11" t="n"/>
+      <c r="N130" s="11" t="n"/>
+    </row>
+    <row r="131" ht="69" customHeight="1">
+      <c r="A131" s="10" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-58:2022 (resistenza al fuoco delle porte di piano)</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
+        </is>
+      </c>
+      <c r="D131" s="10" t="inlineStr">
+        <is>
+          <t>porte di piano resistenti al fuoco (classi E, EI, EW) provate secondo la norma, quando fanno parte della compartimentazione del vano; sostituirle con modelli diversi è una modifica sostanziale ai fini antincendio</t>
+        </is>
+      </c>
+      <c r="E131" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
+        </is>
+      </c>
+      <c r="F131" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G131" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H131" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I131" s="11" t="n"/>
+      <c r="J131" s="11" t="n"/>
+      <c r="K131" s="11" t="n"/>
+      <c r="L131" s="11" t="n"/>
+      <c r="M131" s="11" t="n"/>
+      <c r="N131" s="11" t="n"/>
+    </row>
+    <row r="132" ht="69" customHeight="1">
+      <c r="A132" s="10" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-70:2022, 5.3.1</t>
+        </is>
+      </c>
+      <c r="D132" s="10" t="inlineStr">
+        <is>
+          <t>tipi di cabina (larghezza × profondità, luce della porta): 1) 1000 × 1300, 800; 2) 1100 × 1400, 900; 3) 1100 × 2100, 900; 4) 1600 × 1400 o 1400 × 1600, 900; 5) 2000 × 1400 o 1400 × 2000, 1100 mm</t>
+        </is>
+      </c>
+      <c r="E132" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-70:2022, 5.3.1</t>
+        </is>
+      </c>
+      <c r="F132" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G132" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H132" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="n"/>
+      <c r="J132" s="11" t="n"/>
+      <c r="K132" s="11" t="n"/>
+      <c r="L132" s="11" t="n"/>
+      <c r="M132" s="11" t="n"/>
+      <c r="N132" s="11" t="n"/>
+    </row>
+    <row r="133" ht="69" customHeight="1">
+      <c r="A133" s="10" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+        </is>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
+        </is>
+      </c>
+      <c r="D133" s="10" t="inlineStr">
+        <is>
+          <t>specchio nei tipi 1–3; finiture che riducono le misure nominali al massimo di 15 mm per parete; segnale acustico regolabile 35–65 dB(A), fino a 80 in ambienti rumorosi; contrasto di Michelson con la A1:2022</t>
+        </is>
+      </c>
+      <c r="E133" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
+        </is>
+      </c>
+      <c r="F133" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G133" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H133" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I133" s="11" t="n"/>
+      <c r="J133" s="11" t="n"/>
+      <c r="K133" s="11" t="n"/>
+      <c r="L133" s="11" t="n"/>
+      <c r="M133" s="11" t="n"/>
+      <c r="N133" s="11" t="n"/>
+    </row>
+    <row r="134" ht="43" customHeight="1">
+      <c r="A134" s="10" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-70:2022, scopo</t>
+        </is>
+      </c>
+      <c r="D134" s="10" t="inlineStr">
+        <is>
+          <t>si usa con la UNI EN 81-20:2020; per gli impianti esistenti vale la UNI EN 81-82</t>
+        </is>
+      </c>
+      <c r="E134" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-70:2022, scopo</t>
+        </is>
+      </c>
+      <c r="F134" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G134" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H134" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="n"/>
+      <c r="J134" s="11" t="n"/>
+      <c r="K134" s="11" t="n"/>
+      <c r="L134" s="11" t="n"/>
+      <c r="M134" s="11" t="n"/>
+      <c r="N134" s="11" t="n"/>
+    </row>
+    <row r="135" ht="43" customHeight="1">
+      <c r="A135" s="10" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-71 (ascensori antivandalo)</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-71</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>categoria antivandalo da concordare con il committente; per la presunzione di conformità vale l'edizione 2005+A1:2006</t>
+        </is>
+      </c>
+      <c r="E135" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-71</t>
+        </is>
+      </c>
+      <c r="F135" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G135" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H135" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I135" s="11" t="n"/>
+      <c r="J135" s="11" t="n"/>
+      <c r="K135" s="11" t="n"/>
+      <c r="L135" s="11" t="n"/>
+      <c r="M135" s="11" t="n"/>
+      <c r="N135" s="11" t="n"/>
+    </row>
+    <row r="136" ht="108" customHeight="1">
+      <c r="A136" s="10" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 7; Codice V.3.3.4</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>ascensore antincendio: tutti i piani serviti; vano e porte di piano almeno REI 60; cabina interna almeno 1,10 × 2,10 m con accesso sul lato corto; botola sul tetto almeno 0,50 × 0,70 m; area dedicata almeno 5 m² a ogni piano; luce d'emergenza almeno 5 lux con 1 h di autonomia; IPX3 dove arriva l'acqua; linea dedicata con alimentazione di sicurezza</t>
+        </is>
+      </c>
+      <c r="E136" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 7; Codice V.3.3.4</t>
+        </is>
+      </c>
+      <c r="F136" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G136" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H136" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="n"/>
+      <c r="J136" s="11" t="n"/>
+      <c r="K136" s="11" t="n"/>
+      <c r="L136" s="11" t="n"/>
+      <c r="M136" s="11" t="n"/>
+      <c r="N136" s="11" t="n"/>
+    </row>
+    <row r="137" ht="56" customHeight="1">
+      <c r="A137" s="10" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+        </is>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>Codice S.10, Tab. S.10-2</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t>alimentazione di sicurezza dell'ascensore antincendio: interruzione al massimo 15 s, autonomia oltre 30 min</t>
+        </is>
+      </c>
+      <c r="E137" s="10" t="inlineStr">
+        <is>
+          <t>Codice S.10, Tab. S.10-2</t>
+        </is>
+      </c>
+      <c r="F137" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G137" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H137" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I137" s="11" t="n"/>
+      <c r="J137" s="11" t="n"/>
+      <c r="K137" s="11" t="n"/>
+      <c r="L137" s="11" t="n"/>
+      <c r="M137" s="11" t="n"/>
+      <c r="N137" s="11" t="n"/>
+    </row>
+    <row r="138" ht="56" customHeight="1">
+      <c r="A138" s="10" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-72:2020</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>requisiti propri della norma (cabina, tempi, protezione dall'acqua) da verificare sul testo</t>
+        </is>
+      </c>
+      <c r="E138" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-72:2020</t>
+        </is>
+      </c>
+      <c r="F138" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G138" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H138" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="n"/>
+      <c r="J138" s="11" t="n"/>
+      <c r="K138" s="11" t="n"/>
+      <c r="L138" s="11" t="n"/>
+      <c r="M138" s="11" t="n"/>
+      <c r="N138" s="11" t="n"/>
+    </row>
+    <row r="139" ht="56" customHeight="1">
+      <c r="A139" s="10" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
+        </is>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
+        </is>
+      </c>
+      <c r="D139" s="10" t="inlineStr">
+        <is>
+          <t>su comando della rivelazione incendio la cabina va al piano prestabilito e lascia uscire i passeggeri; con il Codice l'ascensore «dovrebbe» essere conforme alla UNI EN 81-73</t>
+        </is>
+      </c>
+      <c r="E139" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
+        </is>
+      </c>
+      <c r="F139" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G139" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H139" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="n"/>
+      <c r="J139" s="11" t="n"/>
+      <c r="K139" s="11" t="n"/>
+      <c r="L139" s="11" t="n"/>
+      <c r="M139" s="11" t="n"/>
+      <c r="N139" s="11" t="n"/>
+    </row>
+    <row r="140" ht="56" customHeight="1">
+      <c r="A140" s="10" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-73:2020</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="inlineStr">
+        <is>
+          <t>segnali e comportamento della manovra da verificare sul testo; la norma serve anche da base per migliorare gli esistenti</t>
+        </is>
+      </c>
+      <c r="E140" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-73:2020</t>
+        </is>
+      </c>
+      <c r="F140" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G140" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H140" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="n"/>
+      <c r="J140" s="11" t="n"/>
+      <c r="K140" s="11" t="n"/>
+      <c r="L140" s="11" t="n"/>
+      <c r="M140" s="11" t="n"/>
+      <c r="N140" s="11" t="n"/>
+    </row>
+    <row r="141" ht="69" customHeight="1">
+      <c r="A141" s="10" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-76:2025 (evacuazione delle persone con disabilità)</t>
+        </is>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-76:2025</t>
+        </is>
+      </c>
+      <c r="D141" s="10" t="inlineStr">
+        <is>
+          <t>evacuazione delle persone con disabilità con l'ascensore: requisiti aggiuntivi alla EN 81-20 (manovra, alimentazione) da verificare sul testo</t>
+        </is>
+      </c>
+      <c r="E141" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-76:2025</t>
+        </is>
+      </c>
+      <c r="F141" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G141" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H141" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I141" s="11" t="n"/>
+      <c r="J141" s="11" t="n"/>
+      <c r="K141" s="11" t="n"/>
+      <c r="L141" s="11" t="n"/>
+      <c r="M141" s="11" t="n"/>
+      <c r="N141" s="11" t="n"/>
+    </row>
+    <row r="142" ht="56" customHeight="1">
+      <c r="A142" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-77:2022, 1</t>
+        </is>
+      </c>
+      <c r="D142" s="10" t="inlineStr">
+        <is>
+          <t>con accelerazione di progetto a_d fino a 1 m/s² nessuna prescrizione specifica; a_d e la posizione dei rilevatori si concordano con il progettista dell'edificio</t>
+        </is>
+      </c>
+      <c r="E142" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-77:2022, 1</t>
+        </is>
+      </c>
+      <c r="F142" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G142" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H142" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I142" s="11" t="n"/>
+      <c r="J142" s="11" t="n"/>
+      <c r="K142" s="11" t="n"/>
+      <c r="L142" s="11" t="n"/>
+      <c r="M142" s="11" t="n"/>
+      <c r="N142" s="11" t="n"/>
+    </row>
+    <row r="143" ht="95" customHeight="1">
+      <c r="A143" s="10" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
+        </is>
+      </c>
+      <c r="D143" s="10" t="inlineStr">
+        <is>
+          <t>oltre 1 m/s²: massa della cabina nei calcoli (5.4.1), ritegni della cabina (5.4.2) e del contrappeso (5.5), protezione delle pulegge (5.6.1), tensioni e frecce delle guide (5.8.2, All. D), rilevazione e modo sismico (5.10.3, 5.10.4); soglie delle categorie dell'All. A da verificare sul testo</t>
+        </is>
+      </c>
+      <c r="E143" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
+        </is>
+      </c>
+      <c r="F143" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G143" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H143" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I143" s="11" t="n"/>
+      <c r="J143" s="11" t="n"/>
+      <c r="K143" s="11" t="n"/>
+      <c r="L143" s="11" t="n"/>
+      <c r="M143" s="11" t="n"/>
+      <c r="N143" s="11" t="n"/>
+    </row>
+    <row r="144" ht="43" customHeight="1">
+      <c r="A144" s="10" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-77:2022, 0.3</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>non si applica agli impianti installati prima della sua pubblicazione</t>
+        </is>
+      </c>
+      <c r="E144" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-77:2022, 0.3</t>
+        </is>
+      </c>
+      <c r="F144" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G144" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H144" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I144" s="11" t="n"/>
+      <c r="J144" s="11" t="n"/>
+      <c r="K144" s="11" t="n"/>
+      <c r="L144" s="11" t="n"/>
+      <c r="M144" s="11" t="n"/>
+      <c r="N144" s="11" t="n"/>
+    </row>
+    <row r="145" ht="69" customHeight="1">
+      <c r="A145" s="10" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
+        </is>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-80:2019</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>analisi dei rischi dell'impianto esistente e piano di miglioramento per priorità, scelta volontaria del proprietario</t>
+        </is>
+      </c>
+      <c r="E145" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-80:2019</t>
+        </is>
+      </c>
+      <c r="F145" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G145" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H145" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I145" s="11" t="n"/>
+      <c r="J145" s="11" t="n"/>
+      <c r="K145" s="11" t="n"/>
+      <c r="L145" s="11" t="n"/>
+      <c r="M145" s="11" t="n"/>
+      <c r="N145" s="11" t="n"/>
+    </row>
+    <row r="146" ht="56" customHeight="1">
+      <c r="A146" s="10" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-82:2026 (accessibilità degli esistenti)</t>
+        </is>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-82:2026</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="inlineStr">
+        <is>
+          <t>miglioramento dell'accessibilità di un impianto esistente secondo i requisiti della EN 81-70</t>
+        </is>
+      </c>
+      <c r="E146" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-82:2026</t>
+        </is>
+      </c>
+      <c r="F146" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G146" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H146" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I146" s="11" t="n"/>
+      <c r="J146" s="11" t="n"/>
+      <c r="K146" s="11" t="n"/>
+      <c r="L146" s="11" t="n"/>
+      <c r="M146" s="11" t="n"/>
+      <c r="N146" s="11" t="n"/>
+    </row>
+    <row r="147" ht="56" customHeight="1">
+      <c r="A147" s="10" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-83:2026 (antivandalo degli esistenti)</t>
+        </is>
+      </c>
+      <c r="C147" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-83:2026</t>
+        </is>
+      </c>
+      <c r="D147" s="10" t="inlineStr">
+        <is>
+          <t>miglioramento della resistenza agli atti vandalici di un impianto esistente secondo la EN 81-71:2022 (voce 1.2 della Tab. A.1 della EN 81-80)</t>
+        </is>
+      </c>
+      <c r="E147" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-83:2026</t>
+        </is>
+      </c>
+      <c r="F147" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G147" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H147" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I147" s="11" t="n"/>
+      <c r="J147" s="11" t="n"/>
+      <c r="K147" s="11" t="n"/>
+      <c r="L147" s="11" t="n"/>
+      <c r="M147" s="11" t="n"/>
+      <c r="N147" s="11" t="n"/>
+    </row>
+    <row r="148" ht="56" customHeight="1">
+      <c r="A148" s="10" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+        </is>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12</t>
+        </is>
+      </c>
+      <c r="D148" s="10" t="inlineStr">
+        <is>
+          <t>piattaforma di distribuzione davanti alla porta di cabina: 1,50 × 1,50 m negli edifici nuovi, 1,40 × 1,40 m nell'adeguamento (fuori dal vano: in sito)</t>
+        </is>
+      </c>
+      <c r="E148" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12</t>
+        </is>
+      </c>
+      <c r="F148" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G148" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H148" s="10" t="inlineStr">
+        <is>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+        </is>
+      </c>
+      <c r="I148" s="11" t="n"/>
+      <c r="J148" s="11" t="n"/>
+      <c r="K148" s="11" t="n"/>
+      <c r="L148" s="11" t="n"/>
+      <c r="M148" s="11" t="n"/>
+      <c r="N148" s="11" t="n"/>
+    </row>
+    <row r="149" ht="56" customHeight="1">
+      <c r="A149" s="10" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+        </is>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12</t>
+        </is>
+      </c>
+      <c r="D149" s="10" t="inlineStr">
+        <is>
+          <t>porte di cabina e di piano a scorrimento automatico (nell'adeguamento la porta di piano può essere a battente se ad apertura automatica); porte aperte almeno 8 s, chiusura in almeno 4 s</t>
+        </is>
+      </c>
+      <c r="E149" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12</t>
+        </is>
+      </c>
+      <c r="F149" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G149" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H149" s="10" t="inlineStr">
+        <is>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+        </is>
+      </c>
+      <c r="I149" s="11" t="n"/>
+      <c r="J149" s="11" t="n"/>
+      <c r="K149" s="11" t="n"/>
+      <c r="L149" s="11" t="n"/>
+      <c r="M149" s="11" t="n"/>
+      <c r="N149" s="11" t="n"/>
+    </row>
+    <row r="150" ht="43" customHeight="1">
+      <c r="A150" s="10" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+        </is>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12</t>
+        </is>
+      </c>
+      <c r="D150" s="10" t="inlineStr">
+        <is>
+          <t>arresto ai piani con autolivellamento entro ± 2 cm; sosta ai piani con le porte chiuse</t>
+        </is>
+      </c>
+      <c r="E150" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12</t>
+        </is>
+      </c>
+      <c r="F150" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G150" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H150" s="10" t="inlineStr">
+        <is>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+        </is>
+      </c>
+      <c r="I150" s="11" t="n"/>
+      <c r="J150" s="11" t="n"/>
+      <c r="K150" s="11" t="n"/>
+      <c r="L150" s="11" t="n"/>
+      <c r="M150" s="11" t="n"/>
+      <c r="N150" s="11" t="n"/>
+    </row>
+    <row r="151" ht="56" customHeight="1">
+      <c r="A151" s="10" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+        </is>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
+        </is>
+      </c>
+      <c r="D151" s="10" t="inlineStr">
+        <is>
+          <t>pulsanti di cabina e di piano: il più alto tra 1,10 e 1,40 m, misurato all'asse del comando; bottoniera di cabina su una parete laterale ad almeno 0,35 m dalla porta</t>
+        </is>
+      </c>
+      <c r="E151" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
+        </is>
+      </c>
+      <c r="F151" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G151" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H151" s="10" t="inlineStr">
+        <is>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+        </is>
+      </c>
+      <c r="I151" s="11" t="n"/>
+      <c r="J151" s="11" t="n"/>
+      <c r="K151" s="11" t="n"/>
+      <c r="L151" s="11" t="n"/>
+      <c r="M151" s="11" t="n"/>
+      <c r="N151" s="11" t="n"/>
+    </row>
+    <row r="152" ht="95" customHeight="1">
+      <c r="A152" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
+        </is>
+      </c>
+      <c r="D152" s="10" t="inlineStr">
+        <is>
+          <t>citofono in cabina tra 1,10 e 1,30 m; luce d'emergenza con almeno 3 h di autonomia; campanello d'allarme e segnale luminoso di allarme ricevuto; arresto e inversione della chiusura; segnale acustico d'arrivo; numeri in rilievo e Braille, targa Braille di piano; sedile ribaltabile dove possibile</t>
+        </is>
+      </c>
+      <c r="E152" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
+        </is>
+      </c>
+      <c r="F152" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G152" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H152" s="10" t="inlineStr">
+        <is>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+        </is>
+      </c>
+      <c r="I152" s="11" t="n"/>
+      <c r="J152" s="11" t="n"/>
+      <c r="K152" s="11" t="n"/>
+      <c r="L152" s="11" t="n"/>
+      <c r="M152" s="11" t="n"/>
+      <c r="N152" s="11" t="n"/>
+    </row>
+    <row r="153" ht="56" customHeight="1">
+      <c r="A153" s="10" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="inlineStr">
+        <is>
+          <t>ascensore obbligatorio oltre il terzo livello (contati interrati e porticati); negli immobili con più di tre livelli fuori terra un ascensore per ogni scala principale</t>
+        </is>
+      </c>
+      <c r="E153" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
+        </is>
+      </c>
+      <c r="F153" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G153" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H153" s="10" t="inlineStr">
+        <is>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+        </is>
+      </c>
+      <c r="I153" s="11" t="n"/>
+      <c r="J153" s="11" t="n"/>
+      <c r="K153" s="11" t="n"/>
+      <c r="L153" s="11" t="n"/>
+      <c r="M153" s="11" t="n"/>
+      <c r="N153" s="11" t="n"/>
+    </row>
+    <row r="154" ht="56" customHeight="1">
+      <c r="A154" s="10" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="inlineStr">
+        <is>
+          <t>nelle ristrutturazioni deroghe per impossibilità tecnica strutturale o impiantistica (privati: concesse dal Sindaco); edifici vincolati: deroga se le opere pregiudicano il bene</t>
+        </is>
+      </c>
+      <c r="E154" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+        </is>
+      </c>
+      <c r="F154" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G154" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H154" s="10" t="inlineStr">
+        <is>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+        </is>
+      </c>
+      <c r="I154" s="11" t="n"/>
+      <c r="J154" s="11" t="n"/>
+      <c r="K154" s="11" t="n"/>
+      <c r="L154" s="11" t="n"/>
+      <c r="M154" s="11" t="n"/>
+      <c r="N154" s="11" t="n"/>
+    </row>
+    <row r="155" ht="69" customHeight="1">
+      <c r="A155" s="10" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C155" s="10" t="inlineStr">
+        <is>
+          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+        </is>
+      </c>
+      <c r="D155" s="10" t="inlineStr">
+        <is>
+          <t>il progettista applica il DM 15/09/2005 oppure la RTV V.3 del Codice: dove si usa il Codice il DM 2005 non si applica</t>
+        </is>
+      </c>
+      <c r="E155" s="10" t="inlineStr">
+        <is>
+          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+        </is>
+      </c>
+      <c r="F155" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G155" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H155" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I155" s="11" t="n"/>
+      <c r="J155" s="11" t="n"/>
+      <c r="K155" s="11" t="n"/>
+      <c r="L155" s="11" t="n"/>
+      <c r="M155" s="11" t="n"/>
+      <c r="N155" s="11" t="n"/>
+    </row>
+    <row r="156" ht="95" customHeight="1">
+      <c r="A156" s="10" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, art. 1 c.2</t>
+        </is>
+      </c>
+      <c r="D156" s="10" t="inlineStr">
+        <is>
+          <t>sugli impianti esistenti vale per le modifiche sostanziali: nuovo impianto; più fermate o altro azionamento; pareti del vano, porte di piano, locale macchine o pulegge sostituiti con materiali, modelli, dimensioni o criteri diversi; solai o scale rifatti che coinvolgono l'impianto; sopraelevazione; cambio di destinazione d'uso</t>
+        </is>
+      </c>
+      <c r="E156" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, art. 1 c.2</t>
+        </is>
+      </c>
+      <c r="F156" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G156" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H156" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I156" s="11" t="n"/>
+      <c r="J156" s="11" t="n"/>
+      <c r="K156" s="11" t="n"/>
+      <c r="L156" s="11" t="n"/>
+      <c r="M156" s="11" t="n"/>
+      <c r="N156" s="11" t="n"/>
+    </row>
+    <row r="157" ht="69" customHeight="1">
+      <c r="A157" s="10" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+        </is>
+      </c>
+      <c r="D157" s="10" t="inlineStr">
+        <is>
+          <t>tipo di vano: aperto, protetto o a prova di fumo (Codice: classi da SA a SE)</t>
+        </is>
+      </c>
+      <c r="E157" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+        </is>
+      </c>
+      <c r="F157" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G157" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H157" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I157" s="11" t="n"/>
+      <c r="J157" s="11" t="n"/>
+      <c r="K157" s="11" t="n"/>
+      <c r="L157" s="11" t="n"/>
+      <c r="M157" s="11" t="n"/>
+      <c r="N157" s="11" t="n"/>
+    </row>
+    <row r="158" ht="69" customHeight="1">
+      <c r="A158" s="10" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 2</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="inlineStr">
+        <is>
+          <t>pareti del vano, locale macchine e pulegge, setti e arcata non combustibili; pareti, pavimento e tetto della cabina in classe di reazione al fuoco non oltre 1</t>
+        </is>
+      </c>
+      <c r="E158" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 2</t>
+        </is>
+      </c>
+      <c r="F158" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G158" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H158" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I158" s="11" t="n"/>
+      <c r="J158" s="11" t="n"/>
+      <c r="K158" s="11" t="n"/>
+      <c r="L158" s="11" t="n"/>
+      <c r="M158" s="11" t="n"/>
+      <c r="N158" s="11" t="n"/>
+    </row>
+    <row r="159" ht="82" customHeight="1">
+      <c r="A159" s="10" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 5</t>
+        </is>
+      </c>
+      <c r="D159" s="10" t="inlineStr">
+        <is>
+          <t>aerazione permanente in alto verso spazi scoperti di almeno il 3 % della pianta (vano almeno 0,20 m², locale macchine o pulegge almeno 0,05 m²), con una protezione che non lascia passare una sfera oltre 15 mm; non serve se il vano è aperto su spazi scoperti</t>
+        </is>
+      </c>
+      <c r="E159" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 5</t>
+        </is>
+      </c>
+      <c r="F159" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G159" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H159" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I159" s="11" t="n"/>
+      <c r="J159" s="11" t="n"/>
+      <c r="K159" s="11" t="n"/>
+      <c r="L159" s="11" t="n"/>
+      <c r="M159" s="11" t="n"/>
+      <c r="N159" s="11" t="n"/>
+    </row>
+    <row r="160" ht="69" customHeight="1">
+      <c r="A160" s="10" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+        </is>
+      </c>
+      <c r="D160" s="10" t="inlineStr">
+        <is>
+          <t>estintore 21A89BC vicino all'accesso al macchinario; richiamo della cabina al piano prestabilito su comando della rivelazione quando la compartimentazione lo richiede</t>
+        </is>
+      </c>
+      <c r="E160" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+        </is>
+      </c>
+      <c r="F160" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G160" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H160" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I160" s="11" t="n"/>
+      <c r="J160" s="11" t="n"/>
+      <c r="K160" s="11" t="n"/>
+      <c r="L160" s="11" t="n"/>
+      <c r="M160" s="11" t="n"/>
+      <c r="N160" s="11" t="n"/>
+    </row>
+    <row r="161" ht="69" customHeight="1">
+      <c r="A161" s="10" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>Codice S.9, Tab. S.9-3</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="inlineStr">
+        <is>
+          <t>piani tra 32 e 54 m: almeno un ascensore antincendio; oltre 54 m: almeno uno di soccorso; interrati tra −10 e −15 m: antincendio; sotto −15 m: soccorso</t>
+        </is>
+      </c>
+      <c r="E161" s="10" t="inlineStr">
+        <is>
+          <t>Codice S.9, Tab. S.9-3</t>
+        </is>
+      </c>
+      <c r="F161" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G161" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H161" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I161" s="11" t="n"/>
+      <c r="J161" s="11" t="n"/>
+      <c r="K161" s="11" t="n"/>
+      <c r="L161" s="11" t="n"/>
+      <c r="M161" s="11" t="n"/>
+      <c r="N161" s="11" t="n"/>
+    </row>
+    <row r="162" ht="43" customHeight="1">
+      <c r="A162" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §3.1.4</t>
+        </is>
+      </c>
+      <c r="D162" s="10" t="inlineStr">
+        <is>
+          <t>carichi del macchinario valutati caso per caso sui massimi prevedibili e riportati nel progetto e nel collaudo statico</t>
+        </is>
+      </c>
+      <c r="E162" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §3.1.4</t>
+        </is>
+      </c>
+      <c r="F162" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G162" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H162" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I162" s="11" t="n"/>
+      <c r="J162" s="11" t="n"/>
+      <c r="K162" s="11" t="n"/>
+      <c r="L162" s="11" t="n"/>
+      <c r="M162" s="11" t="n"/>
+      <c r="N162" s="11" t="n"/>
+    </row>
+    <row r="163" ht="43" customHeight="1">
+      <c r="A163" s="10" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §8.4.1</t>
+        </is>
+      </c>
+      <c r="D163" s="10" t="inlineStr">
+        <is>
+          <t>su un edificio esistente l'intervento è locale: verifica limitata alle parti interessate, senza ridurre la sicurezza preesistente</t>
+        </is>
+      </c>
+      <c r="E163" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §8.4.1</t>
+        </is>
+      </c>
+      <c r="F163" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G163" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H163" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I163" s="11" t="n"/>
+      <c r="J163" s="11" t="n"/>
+      <c r="K163" s="11" t="n"/>
+      <c r="L163" s="11" t="n"/>
+      <c r="M163" s="11" t="n"/>
+      <c r="N163" s="11" t="n"/>
+    </row>
+    <row r="164" ht="43" customHeight="1">
+      <c r="A164" s="10" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C164" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §11.4.1</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="inlineStr">
+        <is>
+          <t>ancoranti per uso strutturale qualificati; con azioni sismiche categoria C2 per tutte le classi d'uso</t>
+        </is>
+      </c>
+      <c r="E164" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §11.4.1</t>
+        </is>
+      </c>
+      <c r="F164" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G164" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H164" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I164" s="11" t="n"/>
+      <c r="J164" s="11" t="n"/>
+      <c r="K164" s="11" t="n"/>
+      <c r="L164" s="11" t="n"/>
+      <c r="M164" s="11" t="n"/>
+      <c r="N164" s="11" t="n"/>
+    </row>
+    <row r="165" ht="108" customHeight="1">
+      <c r="A165" s="10" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C165" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §7.2.3–7.2.4</t>
+        </is>
+      </c>
+      <c r="D165" s="10" t="inlineStr">
+        <is>
+          <t>forza sismica sull'elemento non strutturale Fa = Sa·Wa/qa; nessun vincolo ad attrito; studio specifico oltre il 30 % del carico permanente del solaio o il 10 % di quello dell'intera struttura; progetto antisismico dell'impianto del produttore, dei collegamenti dell'installatore, dei solai e delle pareti d'ancoraggio del progettista strutturale</t>
+        </is>
+      </c>
+      <c r="E165" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §7.2.3–7.2.4</t>
+        </is>
+      </c>
+      <c r="F165" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G165" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H165" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I165" s="11" t="n"/>
+      <c r="J165" s="11" t="n"/>
+      <c r="K165" s="11" t="n"/>
+      <c r="L165" s="11" t="n"/>
+      <c r="M165" s="11" t="n"/>
+      <c r="N165" s="11" t="n"/>
+    </row>
+    <row r="166" ht="43" customHeight="1">
+      <c r="A166" s="10" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C166" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="inlineStr">
+        <is>
+          <t>impianti: stabilità allo SLV per tutte le classi d'uso; nelle classi III e IV anche funzionamento allo SLO</t>
+        </is>
+      </c>
+      <c r="E166" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+        </is>
+      </c>
+      <c r="F166" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G166" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H166" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I166" s="11" t="n"/>
+      <c r="J166" s="11" t="n"/>
+      <c r="K166" s="11" t="n"/>
+      <c r="L166" s="11" t="n"/>
+      <c r="M166" s="11" t="n"/>
+      <c r="N166" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N113"/>
+  <autoFilter ref="A1:N166"/>
   <dataValidations count="1">
-    <dataValidation sqref="I3:I113" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
+    <dataValidation sqref="I3:I166" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
       <formula1>"conforme,diverso,non applicabile"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6049,7 +8487,7 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$113,"da verificare")</f>
+        <f>COUNTIF(Voci!$G$3:$G$166,"da verificare")</f>
         <v/>
       </c>
     </row>
@@ -6060,7 +8498,7 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$113,"confermato")</f>
+        <f>COUNTIF(Voci!$G$3:$G$166,"confermato")</f>
         <v/>
       </c>
     </row>
@@ -6071,7 +8509,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$113,"scelta del software")</f>
+        <f>COUNTIF(Voci!$G$3:$G$166,"scelta del software")</f>
         <v/>
       </c>
     </row>
@@ -6082,7 +8520,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$113,"stima")</f>
+        <f>COUNTIF(Voci!$G$3:$G$166,"stima")</f>
         <v/>
       </c>
     </row>
@@ -6093,7 +8531,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$113,"derivazione")</f>
+        <f>COUNTIF(Voci!$G$3:$G$166,"derivazione")</f>
         <v/>
       </c>
     </row>
@@ -6104,7 +8542,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$113,"prassi di cantiere")</f>
+        <f>COUNTIF(Voci!$G$3:$G$166,"prassi di cantiere")</f>
         <v/>
       </c>
     </row>
@@ -6115,7 +8553,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTA(Voci!$A$3:$A$113)</f>
+        <f>COUNTA(Voci!$A$3:$A$166)</f>
         <v/>
       </c>
     </row>
@@ -6133,7 +8571,7 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$113,"conforme")</f>
+        <f>COUNTIF(Voci!$I$3:$I$166,"conforme")</f>
         <v/>
       </c>
     </row>
@@ -6144,7 +8582,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$113,"diverso")</f>
+        <f>COUNTIF(Voci!$I$3:$I$166,"diverso")</f>
         <v/>
       </c>
     </row>
@@ -6155,7 +8593,7 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$113,"non applicabile")</f>
+        <f>COUNTIF(Voci!$I$3:$I$166,"non applicabile")</f>
         <v/>
       </c>
     </row>
@@ -6166,14 +8604,14 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>COUNTBLANK(Voci!$I$3:$I$113)</f>
+        <f>COUNTBLANK(Voci!$I$3:$I$166)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Conteggi sulle righe 3–113 del foglio «Voci» (la riga 2 è l'esempio).</t>
+          <t>Conteggi sulle righe 3–166 del foglio «Voci» (la riga 2 è l'esempio).</t>
         </is>
       </c>
     </row>

--- a/liftpilot/docs/lista-verifica-normativa.xlsx
+++ b/liftpilot/docs/lista-verifica-normativa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Riepilogo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$167</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Voci'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N166"/>
+  <dimension ref="A1:N167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4669,7 +4669,7 @@
       <c r="M84" s="11" t="n"/>
       <c r="N84" s="11" t="n"/>
     </row>
-    <row r="85" ht="199" customHeight="1">
+    <row r="85" ht="225" customHeight="1">
       <c r="A85" s="10" t="n">
         <v>83</v>
       </c>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>su spessori di livellamento sotto gli appoggi (l'asse della puleggia dove lo mette il software), su telaio di due profilati sul pavimento (tipico UPN 200, alto quanto il profilato come i telai bassi universali), su due putrelle da muro a muro che possono stare sollevate dal pavimento (tipiche IPE 200, appoggio nei muri 150 mm), su piastre d'acciaio sotto gli appoggi (tipiche 20 mm) o su plinto in calcestruzzo (tipico 250 mm); tamponi antivibranti di 30 mm sotto gli appoggi, salvo sugli spessori; telaio e plinto 100 mm oltre il telaio dell'argano a ogni estremità; l'altezza del basamento porta l'asse della puleggia, che il calcolo (tratto di fune oltre la corsa) e il 3D seguono</t>
+          <t>su spessori di livellamento sotto gli appoggi (l'asse della puleggia dove lo mette il software), su telaio di due profilati sul pavimento (tipico UPN 200, alto quanto il profilato come i telai bassi universali), su due putrelle da muro a muro che possono stare sollevate dal pavimento (tipiche IPE 200, appoggio nei muri 150 mm), su piastre d'acciaio sotto gli appoggi (tipiche 20 mm) o su plinto in calcestruzzo (tipico 250 mm), o — con un rinvio — sul telaio con rinvio (locale.rinvio); tamponi antivibranti di 30 mm sotto gli appoggi, salvo sugli spessori e sul telaio con rinvio (antivibranti sotto le gambe); telaio e plinto 100 mm oltre il telaio dell'argano a ogni estremità; l'altezza del basamento porta l'asse della puleggia, che il calcolo (tratto di fune oltre la corsa) e il 3D seguono</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
@@ -4761,7 +4761,7 @@
       <c r="M86" s="11" t="n"/>
       <c r="N86" s="11" t="n"/>
     </row>
-    <row r="87" ht="134" customHeight="1">
+    <row r="87" ht="303" customHeight="1">
       <c r="A87" s="10" t="n">
         <v>85</v>
       </c>
@@ -4772,32 +4772,32 @@
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
+          <t>Puleggia di rinvio nel locale del macchinario</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
+          <t>con l'argano in alto il rinvio sta sempre nel locale del macchinario, mai nel vano: nel telaio dell'argano (il basamento che il software prende quando c'è un rinvio), con l'asse del rinvio a 320 mm dal pavimento (il bordo almeno 60 mm sopra il pavimento: Dp/2 + 60 oltre Ø 520), il piano del telaio a 736 mm (almeno 176 mm sopra il rinvio), gambe di tubo quadro da 80 mm su antivibranti da 28 mm, travi UPN 160, 100 mm oltre l'argano e il rinvio a ogni estremità, largo almeno 655 mm; con un argano SICOR che ha il suo telaio a catalogo (SV110 e SH110B XTE0517/XTE0516, SH130 e SH130G XTE3022/XTE3023, SH140 XTE6026/XTE6027, SH160 XTE5708, SH190 XTE3988) le quote del costruttore: asse del rinvio, asse della puleggia (A), piano del telaio (A − B), calata del contrappeso entro L max dall'asse della puleggia (verifica di avvertimento: oltre, telaio su misura); h del calcolo = asse della puleggia − asse del rinvio, dx dalla pianta; con un altro basamento scelto il rinvio sta su un supporto proprio sul pavimento, alla stessa altezza; una h inserita a mano che porta il rinvio sotto il pavimento è segnalata</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E), §3.1.4 (carichi del macchinario); DPR 1497/1963, art. 5.1–5.2 (carichi fissi più 1,5 volte il carico statico delle funi, sicurezza ≥ 6, freccia ≤ 1/1500 della luce libera: regola storica degli impianti esistenti, letta su Normattiva)</t>
+          <t>regola del committente (Panev): il rinvio sta nel telaio del locale macchine, mai nel vano; UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio)</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
+          <t>brochure Geared SICOR, aprile 2026, pp. 16, 23, 41, 47, 58, 68 e 80 (telai «top machine with diverting pulley for CSW wrapping»), letta il 2 ottobre 2026; i telai «corti» MR21, MR26 e MR35 portano il rinvio sotto il pavimento (Hmin = Dt/2 + 75) e non sono usati; le quote del telaio del software sono quelle dei telai SICOR, da adattare al telaio fornito</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>calata del contrappeso nel telaio con rinvio del costruttore</t>
         </is>
       </c>
       <c r="I87" s="11" t="n"/>
@@ -4807,33 +4807,33 @@
       <c r="M87" s="11" t="n"/>
       <c r="N87" s="11" t="n"/>
     </row>
-    <row r="88" ht="108" customHeight="1">
+    <row r="88" ht="134" customHeight="1">
       <c r="A88" s="10" t="n">
         <v>86</v>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Carichi sul pavimento della fossa</t>
+          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
+          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.8; UNI EN 81-50:2020, 5.10</t>
+          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E), §3.1.4 (carichi del macchinario); DPR 1497/1963, art. 5.1–5.2 (carichi fissi più 1,5 volte il carico statico delle funi, sicurezza ≥ 6, freccia ≤ 1/1500 della luce libera: regola storica degli impianti esistenti, letta su Normattiva)</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi; sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
+          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
         </is>
       </c>
       <c r="I88" s="11" t="n"/>
@@ -4864,22 +4864,22 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Spinte sulle guide di cabina</t>
+          <t>Carichi sul pavimento della fossa</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
+          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.10</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8; UNI EN 81-50:2020, 5.10</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi; sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       <c r="M89" s="11" t="n"/>
       <c r="N89" s="11" t="n"/>
     </row>
-    <row r="90" ht="82" customHeight="1">
+    <row r="90" ht="108" customHeight="1">
       <c r="A90" s="10" t="n">
         <v>88</v>
       </c>
@@ -4910,27 +4910,27 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Carico della macchina sulla soletta</t>
+          <t>Spinte sulle guide di cabina</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
+          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.10</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
+          <t>sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>prassi di cantiere</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
@@ -4945,7 +4945,7 @@
       <c r="M90" s="11" t="n"/>
       <c r="N90" s="11" t="n"/>
     </row>
-    <row r="91" ht="43" customHeight="1">
+    <row r="91" ht="82" customHeight="1">
       <c r="A91" s="10" t="n">
         <v>89</v>
       </c>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Massa dei cavi flessibili</t>
+          <t>Carico della macchina sulla soletta</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
+          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
+          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>prassi di cantiere</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
@@ -4991,7 +4991,7 @@
       <c r="M91" s="11" t="n"/>
       <c r="N91" s="11" t="n"/>
     </row>
-    <row r="92" ht="121" customHeight="1">
+    <row r="92" ht="43" customHeight="1">
       <c r="A92" s="10" t="n">
         <v>90</v>
       </c>
@@ -5002,27 +5002,27 @@
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
+          <t>Massa dei cavi flessibili</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
+          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>regola di montaggio indicata dal committente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>scelta del committente</t>
+          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
@@ -5037,7 +5037,7 @@
       <c r="M92" s="11" t="n"/>
       <c r="N92" s="11" t="n"/>
     </row>
-    <row r="93" ht="82" customHeight="1">
+    <row r="93" ht="121" customHeight="1">
       <c r="A93" s="10" t="n">
         <v>91</v>
       </c>
@@ -5048,27 +5048,27 @@
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Lunghezze stimate nel foglio dei dati</t>
+          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
+          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>regola di montaggio indicata dal committente</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>stima del software, da sostituire con le misure di cantiere</t>
+          <t>scelta del committente</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
@@ -5083,23 +5083,23 @@
       <c r="M93" s="11" t="n"/>
       <c r="N93" s="11" t="n"/>
     </row>
-    <row r="94" ht="43" customHeight="1">
+    <row r="94" ht="82" customHeight="1">
       <c r="A94" s="10" t="n">
         <v>92</v>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Dimensioni proposte della cabina</t>
+          <t>Lunghezze stimate nel foglio dei dati</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
+          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima del software, da sostituire con le misure di cantiere</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
@@ -5129,7 +5129,7 @@
       <c r="M94" s="11" t="n"/>
       <c r="N94" s="11" t="n"/>
     </row>
-    <row r="95" ht="199" customHeight="1">
+    <row r="95" ht="43" customHeight="1">
       <c r="A95" s="10" t="n">
         <v>93</v>
       </c>
@@ -5140,12 +5140,12 @@
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Quote della pianta fissate a mano</t>
+          <t>Dimensioni proposte della cabina</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8), quello del contrappeso dentro la lunghezza del contrappeso</t>
+          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I95" s="11" t="n"/>
@@ -5175,7 +5175,7 @@
       <c r="M95" s="11" t="n"/>
       <c r="N95" s="11" t="n"/>
     </row>
-    <row r="96" ht="82" customHeight="1">
+    <row r="96" ht="199" customHeight="1">
       <c r="A96" s="10" t="n">
         <v>94</v>
       </c>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Limiti del modello del vano</t>
+          <t>Quote della pianta fissate a mano</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
+          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8), quello del contrappeso dentro la lunghezza del contrappeso</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>limite del modello attuale</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
         </is>
       </c>
       <c r="I96" s="11" t="n"/>
@@ -5221,23 +5221,23 @@
       <c r="M96" s="11" t="n"/>
       <c r="N96" s="11" t="n"/>
     </row>
-    <row r="97" ht="56" customHeight="1">
+    <row r="97" ht="82" customHeight="1">
       <c r="A97" s="10" t="n">
         <v>95</v>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Corsa</t>
+          <t>Limiti del modello del vano</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
+          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>dati dei piani inseriti</t>
+          <t>limite del modello attuale</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H97" s="10" t="inlineStr">
@@ -5278,22 +5278,22 @@
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Portata e velocità</t>
+          <t>Corsa</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
+          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.2.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>progetto del vano</t>
+          <t>dati dei piani inseriti</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
@@ -5313,7 +5313,7 @@
       <c r="M98" s="11" t="n"/>
       <c r="N98" s="11" t="n"/>
     </row>
-    <row r="99" ht="303" customHeight="1">
+    <row r="99" ht="56" customHeight="1">
       <c r="A99" s="10" t="n">
         <v>97</v>
       </c>
@@ -5324,27 +5324,27 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Normativa di collaudo e parti sostituite o modificate — il testo delle UNI 10411 del 2024 non è stato letto: le verifiche per parte e i requisiti per la sostituzione del macchinario (edizione 2021: freno in due elementi, temporizzatore, velocità eccessiva in salita, arresto entro 1 m dalla macchina, interruzione se il freno non si apre) vanno confermati sul testo vigente</t>
+          <t>Portata e velocità</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software. Alla norma base si aggiungono le norme compatibili (matrice della ricerca, cap. 16 §5.2): sull'impianto nuovo le EN 81 supplementari (21, 28, 58, 70, 71, 72, 73, 76, 77), sulla modifica la EN 81-20/50 intera, le EN 81-28, 58, 73 e il miglioramento (80, 82, 83), su entrambi DM 236/1989, antincendio (DM 15/09/2005 o Codice V.3) e NTC 2018 (con le verifiche delle putrelle). Ogni norma ha il suo esito («non calcolata» se il software non ne calcola verifiche) e i suoi punti da verificare in sito nella relazione, con gli adempimenti del DPR 162/1999</t>
+          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
+          <t>UNI EN 81-20:2020, 5.4.2.1</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>schede UNI delle norme (scopo, data 31/10/2024); schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); sintesi secondarie; ricerca, capitoli 2.4 e 6.6</t>
+          <t>progetto del vano</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H99" s="10" t="inlineStr">
@@ -5359,7 +5359,7 @@
       <c r="M99" s="11" t="n"/>
       <c r="N99" s="11" t="n"/>
     </row>
-    <row r="100" ht="69" customHeight="1">
+    <row r="100" ht="303" customHeight="1">
       <c r="A100" s="10" t="n">
         <v>98</v>
       </c>
@@ -5370,27 +5370,27 @@
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
+          <t>Normativa di collaudo e parti sostituite o modificate — il testo delle UNI 10411 del 2024 non è stato letto: le verifiche per parte e i requisiti per la sostituzione del macchinario (edizione 2021: freno in due elementi, temporizzatore, velocità eccessiva in salita, arresto entro 1 m dalla macchina, interruzione se il freno non si apre) vanno confermati sul testo vigente</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
+          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software. Alla norma base si aggiungono le norme compatibili (matrice della ricerca, cap. 16 §5.2): sull'impianto nuovo le EN 81 supplementari (21, 28, 58, 70, 71, 72, 73, 76, 77), sulla modifica la EN 81-20/50 intera, le EN 81-28, 58, 73 e il miglioramento (80, 82, 83), su entrambi DM 236/1989, antincendio (DM 15/09/2005 o Codice V.3) e NTC 2018 (con le verifiche delle putrelle). Ogni norma ha il suo esito («non calcolata» se il software non ne calcola verifiche) e i suoi punti da verificare in sito nella relazione, con gli adempimenti del DPR 162/1999</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
+          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>scelta del software, senza fonte</t>
+          <t>schede UNI delle norme (scopo, data 31/10/2024); schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); sintesi secondarie; ricerca, capitoli 2.4 e 6.6</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H100" s="10" t="inlineStr">
@@ -5405,7 +5405,7 @@
       <c r="M100" s="11" t="n"/>
       <c r="N100" s="11" t="n"/>
     </row>
-    <row r="101" ht="82" customHeight="1">
+    <row r="101" ht="69" customHeight="1">
       <c r="A101" s="10" t="n">
         <v>99</v>
       </c>
@@ -5416,27 +5416,27 @@
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Fune oltre la corsa (L0)</t>
+          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale (macchina in basso o senza locale: fino al soffitto del vano)</t>
+          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
+          <t>scelta del software, senza fonte</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H101" s="10" t="inlineStr">
@@ -5451,7 +5451,7 @@
       <c r="M101" s="11" t="n"/>
       <c r="N101" s="11" t="n"/>
     </row>
-    <row r="102" ht="147" customHeight="1">
+    <row r="102" ht="82" customHeight="1">
       <c r="A102" s="10" t="n">
         <v>100</v>
       </c>
@@ -5462,27 +5462,27 @@
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
+          <t>Fune oltre la corsa (L0)</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
+          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale (macchina in basso o senza locale: fino al soffitto del vano)</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>pianta del vano</t>
+          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H102" s="10" t="inlineStr">
@@ -5497,7 +5497,7 @@
       <c r="M102" s="11" t="n"/>
       <c r="N102" s="11" t="n"/>
     </row>
-    <row r="103" ht="160" customHeight="1">
+    <row r="103" ht="147" customHeight="1">
       <c r="A103" s="10" t="n">
         <v>101</v>
       </c>
@@ -5508,22 +5508,22 @@
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
+          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
+          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
+          <t>ricerca, capitolo 5.3</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>geometria delle funi</t>
+          <t>pianta del vano</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
@@ -5543,7 +5543,7 @@
       <c r="M103" s="11" t="n"/>
       <c r="N103" s="11" t="n"/>
     </row>
-    <row r="104" ht="56" customHeight="1">
+    <row r="104" ht="160" customHeight="1">
       <c r="A104" s="10" t="n">
         <v>102</v>
       </c>
@@ -5554,22 +5554,22 @@
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
+          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
+          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
+          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano</t>
+          <t>geometria delle funi</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
@@ -5589,7 +5589,7 @@
       <c r="M104" s="11" t="n"/>
       <c r="N104" s="11" t="n"/>
     </row>
-    <row r="105" ht="238" customHeight="1">
+    <row r="105" ht="56" customHeight="1">
       <c r="A105" s="10" t="n">
         <v>103</v>
       </c>
@@ -5600,27 +5600,27 @@
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso o pilastro pieno fino al terreno (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori</t>
+          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
+          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
         </is>
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
+          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>geometria ricostruita dal software</t>
+          <t>dati verticali del vano</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
@@ -5635,7 +5635,7 @@
       <c r="M105" s="11" t="n"/>
       <c r="N105" s="11" t="n"/>
     </row>
-    <row r="106" ht="186" customHeight="1">
+    <row r="106" ht="238" customHeight="1">
       <c r="A106" s="10" t="n">
         <v>104</v>
       </c>
@@ -5646,27 +5646,27 @@
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta dal catalogo di un costruttore — i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
+          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso o pilastro pieno fino al terreno (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo; i disegni e il 3D mostrano l'argano SICOR com'è (ingombri, piedi e fori, asse della puleggia, P ed E della scheda), sul telaio del software</t>
+          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
+          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>SICOR: schede tecniche 2025 e modelli CAD scaricati da sicoritaly.com il 2 ottobre 2026 (solo le quote); Sassi, Montanari, GEM, FAER: estratti delle pagine dei costruttori e dei rivenditori, 1° ottobre 2026</t>
+          <t>geometria ricostruita dal software</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
@@ -5681,7 +5681,7 @@
       <c r="M106" s="11" t="n"/>
       <c r="N106" s="11" t="n"/>
     </row>
-    <row r="107" ht="134" customHeight="1">
+    <row r="107" ht="186" customHeight="1">
       <c r="A107" s="10" t="n">
         <v>105</v>
       </c>
@@ -5692,27 +5692,27 @@
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
+          <t>Macchina proposta dal catalogo di un costruttore — i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
+          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo; i disegni e il 3D mostrano l'argano SICOR com'è (ingombri, piedi e fori, asse della puleggia, P ed E della scheda), sul telaio del software</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 8</t>
+          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo</t>
+          <t>SICOR: schede tecniche 2025 e modelli CAD scaricati da sicoritaly.com il 2 ottobre 2026 (solo le quote); Sassi, Montanari, GEM, FAER: estratti delle pagine dei costruttori e dei rivenditori, 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
@@ -5727,38 +5727,38 @@
       <c r="M107" s="11" t="n"/>
       <c r="N107" s="11" t="n"/>
     </row>
-    <row r="108" ht="69" customHeight="1">
+    <row r="108" ht="134" customHeight="1">
       <c r="A108" s="10" t="n">
         <v>106</v>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
+          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
+          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
+          <t>ricerca, capitolo 8</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo (src/calc/model.ts)</t>
+          <t>motore di calcolo</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H108" s="10" t="inlineStr">
@@ -5773,7 +5773,7 @@
       <c r="M108" s="11" t="n"/>
       <c r="N108" s="11" t="n"/>
     </row>
-    <row r="109" ht="56" customHeight="1">
+    <row r="109" ht="69" customHeight="1">
       <c r="A109" s="10" t="n">
         <v>107</v>
       </c>
@@ -5784,27 +5784,27 @@
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
+          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
+          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
         </is>
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
+          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>motore di calcolo (src/calc/model.ts)</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H109" s="10" t="inlineStr">
@@ -5819,7 +5819,7 @@
       <c r="M109" s="11" t="n"/>
       <c r="N109" s="11" t="n"/>
     </row>
-    <row r="110" ht="69" customHeight="1">
+    <row r="110" ht="56" customHeight="1">
       <c r="A110" s="10" t="n">
         <v>108</v>
       </c>
@@ -5830,17 +5830,17 @@
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Limite di aderenza mostrato durante la marcia</t>
+          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
+          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.2</t>
+          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
@@ -5865,7 +5865,7 @@
       <c r="M110" s="11" t="n"/>
       <c r="N110" s="11" t="n"/>
     </row>
-    <row r="111" ht="43" customHeight="1">
+    <row r="111" ht="69" customHeight="1">
       <c r="A111" s="10" t="n">
         <v>109</v>
       </c>
@@ -5876,22 +5876,22 @@
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Tempi delle porte</t>
+          <t>Limite di aderenza mostrato durante la marcia</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
+          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.2.2</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (solo animazione)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
@@ -5911,7 +5911,7 @@
       <c r="M111" s="11" t="n"/>
       <c r="N111" s="11" t="n"/>
     </row>
-    <row r="112" ht="108" customHeight="1">
+    <row r="112" ht="43" customHeight="1">
       <c r="A112" s="10" t="n">
         <v>110</v>
       </c>
@@ -5922,27 +5922,27 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione</t>
+          <t>Tempi delle porte</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
+          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>sintesi della norma di costruttori e organismi notificati (fonti secondarie)</t>
+          <t>scelta del software (solo animazione)</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
@@ -5957,7 +5957,7 @@
       <c r="M112" s="11" t="n"/>
       <c r="N112" s="11" t="n"/>
     </row>
-    <row r="113" ht="56" customHeight="1">
+    <row r="113" ht="108" customHeight="1">
       <c r="A113" s="10" t="n">
         <v>111</v>
       </c>
@@ -5968,27 +5968,27 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Cabina bloccata: rotazione in salita</t>
+          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
+          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2</t>
+          <t>UNI EN 81-20:2020, 5.8.2</t>
         </is>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo; velocità scelta dal software</t>
+          <t>sintesi della norma di costruttori e organismi notificati (fonti secondarie)</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
@@ -6003,7 +6003,7 @@
       <c r="M113" s="11" t="n"/>
       <c r="N113" s="11" t="n"/>
     </row>
-    <row r="114" ht="43" customHeight="1">
+    <row r="114" ht="56" customHeight="1">
       <c r="A114" s="10" t="n">
         <v>112</v>
       </c>
@@ -6014,22 +6014,22 @@
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Passo di campionamento</t>
+          <t>Cabina bloccata: rotazione in salita</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
+          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.2</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>motore di calcolo; velocità scelta dal software</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
@@ -6049,38 +6049,38 @@
       <c r="M114" s="11" t="n"/>
       <c r="N114" s="11" t="n"/>
     </row>
-    <row r="115" ht="56" customHeight="1">
+    <row r="115" ht="43" customHeight="1">
       <c r="A115" s="10" t="n">
         <v>113</v>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 4-bis</t>
+          <t>Passo di campionamento</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>progetto, fabbricazione, installazione e prove conformi all'All. I; documentazione tecnica e dichiarazione di conformità conservate per 10 anni</t>
+          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
         </is>
       </c>
       <c r="E115" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 4-bis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H115" s="10" t="inlineStr">
@@ -6106,17 +6106,17 @@
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 6-bis e 7 c.3</t>
+          <t>DPR 162/1999, art. 4-bis</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>procedura con un organismo notificato (All. V, VIII, X, XI o XII); marcatura CE in cabina con il numero dell'organismo</t>
+          <t>progetto, fabbricazione, installazione e prove conformi all'All. I; documentazione tecnica e dichiarazione di conformità conservate per 10 anni</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 6-bis e 7 c.3</t>
+          <t>DPR 162/1999, art. 4-bis</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
@@ -6152,17 +6152,17 @@
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.1–3</t>
+          <t>DPR 162/1999, artt. 6-bis e 7 c.3</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>comunicazione al Comune entro 60 giorni dalla dichiarazione di conformità (oltre: con il verbale di una verifica straordinaria di attivazione); matricola entro 30 giorni</t>
+          <t>procedura con un organismo notificato (All. V, VIII, X, XI o XII); marcatura CE in cabina con il numero dell'organismo</t>
         </is>
       </c>
       <c r="E117" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.1–3</t>
+          <t>DPR 162/1999, artt. 6-bis e 7 c.3</t>
         </is>
       </c>
       <c r="F117" s="10" t="inlineStr">
@@ -6198,17 +6198,17 @@
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
+          <t>DPR 162/1999, art. 12 c.1–3</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>verifiche periodiche ogni 2 anni; controllo dei dispositivi di sicurezza, delle funi e dell'isolamento almeno ogni 6 mesi; targa in cabina</t>
+          <t>comunicazione al Comune entro 60 giorni dalla dichiarazione di conformità (oltre: con il verbale di una verifica straordinaria di attivazione); matricola entro 30 giorni</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
+          <t>DPR 162/1999, art. 12 c.1–3</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
@@ -6233,28 +6233,28 @@
       <c r="M118" s="11" t="n"/>
       <c r="N118" s="11" t="n"/>
     </row>
-    <row r="119" ht="43" customHeight="1">
+    <row r="119" ht="56" customHeight="1">
       <c r="A119" s="10" t="n">
         <v>117</v>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
+          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>la modifica è costruttiva: la sostituzione del macchinario ne è il caso n. 5)</t>
+          <t>verifiche periodiche ogni 2 anni; controllo dei dispositivi di sicurezza, delle funi e dell'isolamento almeno ogni 6 mesi; targa in cabina</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
+          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
@@ -6290,17 +6290,17 @@
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4</t>
+          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>prima della comunicazione, adeguamento della parte modificata o sostituita e delle altre parti interessate</t>
+          <t>la modifica è costruttiva: la sostituzione del macchinario ne è il caso n. 5)</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4</t>
+          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
@@ -6336,17 +6336,17 @@
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4–5</t>
+          <t>DPR 162/1999, art. 12 c.4</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>comunicazione al Comune e al soggetto delle verifiche periodiche; l'impianto non resta in esercizio senza le comunicazioni aggiornate</t>
+          <t>prima della comunicazione, adeguamento della parte modificata o sostituita e delle altre parti interessate</t>
         </is>
       </c>
       <c r="E121" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4–5</t>
+          <t>DPR 162/1999, art. 12 c.4</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
@@ -6371,7 +6371,7 @@
       <c r="M121" s="11" t="n"/>
       <c r="N121" s="11" t="n"/>
     </row>
-    <row r="122" ht="56" customHeight="1">
+    <row r="122" ht="43" customHeight="1">
       <c r="A122" s="10" t="n">
         <v>120</v>
       </c>
@@ -6382,17 +6382,17 @@
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 14 c.3</t>
+          <t>DPR 162/1999, art. 12 c.4–5</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>verifica straordinaria da uno dei soggetti dell'art. 13 c.1, di norma limitata ai controlli sulle modifiche, con la documentazione delle modifiche e dei componenti sostituiti</t>
+          <t>comunicazione al Comune e al soggetto delle verifiche periodiche; l'impianto non resta in esercizio senza le comunicazioni aggiornate</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 14 c.3</t>
+          <t>DPR 162/1999, art. 12 c.4–5</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
@@ -6423,22 +6423,22 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
+          <t>DPR 162/1999, art. 14 c.3</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>prove dell'organismo notificato: funzionamento a vuoto e a pieno carico, in mancanza di energia, prova statica a 1,25 volte la portata e controllo che non restino deformazioni</t>
+          <t>verifica straordinaria da uno dei soggetti dell'art. 13 c.1, di norma limitata ai controlli sulle modifiche, con la documentazione delle modifiche e dei componenti sostituiti</t>
         </is>
       </c>
       <c r="E123" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
+          <t>DPR 162/1999, art. 14 c.3</t>
         </is>
       </c>
       <c r="F123" s="10" t="inlineStr">
@@ -6474,17 +6474,17 @@
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
+          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>documentazione tecnica con i risultati dei calcoli di progetto, le relazioni sulle prove e l'elenco delle norme armonizzate applicate, anche in parte</t>
+          <t>prove dell'organismo notificato: funzionamento a vuoto e a pieno carico, in mancanza di energia, prova statica a 1,25 volte la portata e controllo che non restino deformazioni</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
+          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
@@ -6520,17 +6520,17 @@
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
+          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>per gli ascensori dichiarati conformi dal 20/01/2027: requisiti dell'All. III del Regolamento macchine (tra cui 1.1.9 e 1.2.1), con una valutazione aggiuntiva per i requisiti nuovi o cambiati</t>
+          <t>documentazione tecnica con i risultati dei calcoli di progetto, le relazioni sulle prove e l'elenco delle norme armonizzate applicate, anche in parte</t>
         </is>
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
+          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
@@ -6561,22 +6561,22 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-1:2024</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, scopo</t>
+          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>ascensori elettrici a frizione non conformi alla 95/16/CE né alla 2014/33/UE; esclude le modifiche che cambiano le misure antincendio (valgono il DM 15/09/2005 o il Codice V.3)</t>
+          <t>per gli ascensori dichiarati conformi dal 20/01/2027: requisiti dell'All. III del Regolamento macchine (tra cui 1.1.9 e 1.2.1), con una valutazione aggiuntiva per i requisiti nuovi o cambiati</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, scopo</t>
+          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
@@ -6607,22 +6607,22 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-11:2024</t>
+          <t>Collaudo: UNI 10411-1:2024</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, scopo</t>
+          <t>UNI 10411-1:2024, scopo</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>ascensori elettrici a frizione conformi alla Direttiva Ascensori; esclude le modifiche che cambiano le misure antincendio (valgono il DM 15/09/2005 o il Codice V.3)</t>
+          <t>ascensori elettrici a frizione non conformi alla 95/16/CE né alla 2014/33/UE; esclude le modifiche che cambiano le misure antincendio (valgono il DM 15/09/2005 o il Codice V.3)</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, scopo</t>
+          <t>UNI 10411-1:2024, scopo</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
@@ -6653,22 +6653,22 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
+          <t>Collaudo: UNI 10411-11:2024</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-21:2022, scopo</t>
+          <t>UNI 10411-11:2024, scopo</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>impianto nuovo o sostituzione completa in un edificio esistente; non copre le modifiche parziali (letto sull'edizione 2018)</t>
+          <t>ascensori elettrici a frizione conformi alla Direttiva Ascensori; esclude le modifiche che cambiano le misure antincendio (valgono il DM 15/09/2005 o il Codice V.3)</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-21:2022, scopo</t>
+          <t>UNI 10411-11:2024, scopo</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="G128" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H128" s="10" t="inlineStr">
@@ -6693,7 +6693,7 @@
       <c r="M128" s="11" t="n"/>
       <c r="N128" s="11" t="n"/>
     </row>
-    <row r="129" ht="82" customHeight="1">
+    <row r="129" ht="56" customHeight="1">
       <c r="A129" s="10" t="n">
         <v>127</v>
       </c>
@@ -6704,17 +6704,17 @@
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
+          <t>UNI EN 81-21:2022, scopo</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>spazi di rifugio ridotti solo con l'accordo preventivo: in edificio esistente PEC al Ministero con la certificazione dell'organismo prima dell'installazione (Procedura 2: dichiarazione dei punti della EN 81-21 applicati); la EN 81-21 da sola non giustifica la deroga</t>
+          <t>impianto nuovo o sostituzione completa in un edificio esistente; non copre le modifiche parziali (letto sull'edizione 2018)</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
+          <t>UNI EN 81-21:2022, scopo</t>
         </is>
       </c>
       <c r="F129" s="10" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G129" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H129" s="10" t="inlineStr">
@@ -6739,28 +6739,28 @@
       <c r="M129" s="11" t="n"/>
       <c r="N129" s="11" t="n"/>
     </row>
-    <row r="130" ht="56" customHeight="1">
+    <row r="130" ht="82" customHeight="1">
       <c r="A130" s="10" t="n">
         <v>128</v>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
+          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-28:2022</t>
+          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>teleallarme verso un servizio di soccorso: requisiti da verificare sul testo della norma; il suo uso sugli impianti esistenti non è stato verificato</t>
+          <t>spazi di rifugio ridotti solo con l'accordo preventivo: in edificio esistente PEC al Ministero con la certificazione dell'organismo prima dell'installazione (Procedura 2: dichiarazione dei punti della EN 81-21 applicati); la EN 81-21 da sola non giustifica la deroga</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-28:2022</t>
+          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="G130" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H130" s="10" t="inlineStr">
@@ -6785,28 +6785,28 @@
       <c r="M130" s="11" t="n"/>
       <c r="N130" s="11" t="n"/>
     </row>
-    <row r="131" ht="69" customHeight="1">
+    <row r="131" ht="56" customHeight="1">
       <c r="A131" s="10" t="n">
         <v>129</v>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-58:2022 (resistenza al fuoco delle porte di piano)</t>
+          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
+          <t>UNI EN 81-28:2022</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>porte di piano resistenti al fuoco (classi E, EI, EW) provate secondo la norma, quando fanno parte della compartimentazione del vano; sostituirle con modelli diversi è una modifica sostanziale ai fini antincendio</t>
+          <t>teleallarme verso un servizio di soccorso: requisiti da verificare sul testo della norma; il suo uso sugli impianti esistenti non è stato verificato</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
+          <t>UNI EN 81-28:2022</t>
         </is>
       </c>
       <c r="F131" s="10" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="G131" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H131" s="10" t="inlineStr">
@@ -6837,22 +6837,22 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+          <t>Collaudo: UNI EN 81-58:2022 (resistenza al fuoco delle porte di piano)</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.1</t>
+          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>tipi di cabina (larghezza × profondità, luce della porta): 1) 1000 × 1300, 800; 2) 1100 × 1400, 900; 3) 1100 × 2100, 900; 4) 1600 × 1400 o 1400 × 1600, 900; 5) 2000 × 1400 o 1400 × 2000, 1100 mm</t>
+          <t>porte di piano resistenti al fuoco (classi E, EI, EW) provate secondo la norma, quando fanno parte della compartimentazione del vano; sostituirle con modelli diversi è una modifica sostanziale ai fini antincendio</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.1</t>
+          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H132" s="10" t="inlineStr">
@@ -6888,17 +6888,17 @@
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
+          <t>UNI EN 81-70:2022, 5.3.1</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>specchio nei tipi 1–3; finiture che riducono le misure nominali al massimo di 15 mm per parete; segnale acustico regolabile 35–65 dB(A), fino a 80 in ambienti rumorosi; contrasto di Michelson con la A1:2022</t>
+          <t>tipi di cabina (larghezza × profondità, luce della porta): 1) 1000 × 1300, 800; 2) 1100 × 1400, 900; 3) 1100 × 2100, 900; 4) 1600 × 1400 o 1400 × 1600, 900; 5) 2000 × 1400 o 1400 × 2000, 1100 mm</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
+          <t>UNI EN 81-70:2022, 5.3.1</t>
         </is>
       </c>
       <c r="F133" s="10" t="inlineStr">
@@ -6923,7 +6923,7 @@
       <c r="M133" s="11" t="n"/>
       <c r="N133" s="11" t="n"/>
     </row>
-    <row r="134" ht="43" customHeight="1">
+    <row r="134" ht="69" customHeight="1">
       <c r="A134" s="10" t="n">
         <v>132</v>
       </c>
@@ -6934,17 +6934,17 @@
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, scopo</t>
+          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>si usa con la UNI EN 81-20:2020; per gli impianti esistenti vale la UNI EN 81-82</t>
+          <t>specchio nei tipi 1–3; finiture che riducono le misure nominali al massimo di 15 mm per parete; segnale acustico regolabile 35–65 dB(A), fino a 80 in ambienti rumorosi; contrasto di Michelson con la A1:2022</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, scopo</t>
+          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="G134" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H134" s="10" t="inlineStr">
@@ -6975,22 +6975,22 @@
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-71 (ascensori antivandalo)</t>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-71</t>
+          <t>UNI EN 81-70:2022, scopo</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>categoria antivandalo da concordare con il committente; per la presunzione di conformità vale l'edizione 2005+A1:2006</t>
+          <t>si usa con la UNI EN 81-20:2020; per gli impianti esistenti vale la UNI EN 81-82</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-71</t>
+          <t>UNI EN 81-70:2022, scopo</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
@@ -7015,28 +7015,28 @@
       <c r="M135" s="11" t="n"/>
       <c r="N135" s="11" t="n"/>
     </row>
-    <row r="136" ht="108" customHeight="1">
+    <row r="136" ht="43" customHeight="1">
       <c r="A136" s="10" t="n">
         <v>134</v>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+          <t>Collaudo: UNI EN 81-71 (ascensori antivandalo)</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 7; Codice V.3.3.4</t>
+          <t>UNI EN 81-71</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>ascensore antincendio: tutti i piani serviti; vano e porte di piano almeno REI 60; cabina interna almeno 1,10 × 2,10 m con accesso sul lato corto; botola sul tetto almeno 0,50 × 0,70 m; area dedicata almeno 5 m² a ogni piano; luce d'emergenza almeno 5 lux con 1 h di autonomia; IPX3 dove arriva l'acqua; linea dedicata con alimentazione di sicurezza</t>
+          <t>categoria antivandalo da concordare con il committente; per la presunzione di conformità vale l'edizione 2005+A1:2006</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 7; Codice V.3.3.4</t>
+          <t>UNI EN 81-71</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
@@ -7061,7 +7061,7 @@
       <c r="M136" s="11" t="n"/>
       <c r="N136" s="11" t="n"/>
     </row>
-    <row r="137" ht="56" customHeight="1">
+    <row r="137" ht="108" customHeight="1">
       <c r="A137" s="10" t="n">
         <v>135</v>
       </c>
@@ -7072,17 +7072,17 @@
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Codice S.10, Tab. S.10-2</t>
+          <t>DM 15/09/2005, punto 7; Codice V.3.3.4</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>alimentazione di sicurezza dell'ascensore antincendio: interruzione al massimo 15 s, autonomia oltre 30 min</t>
+          <t>ascensore antincendio: tutti i piani serviti; vano e porte di piano almeno REI 60; cabina interna almeno 1,10 × 2,10 m con accesso sul lato corto; botola sul tetto almeno 0,50 × 0,70 m; area dedicata almeno 5 m² a ogni piano; luce d'emergenza almeno 5 lux con 1 h di autonomia; IPX3 dove arriva l'acqua; linea dedicata con alimentazione di sicurezza</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>Codice S.10, Tab. S.10-2</t>
+          <t>DM 15/09/2005, punto 7; Codice V.3.3.4</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
@@ -7118,17 +7118,17 @@
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-72:2020</t>
+          <t>Codice S.10, Tab. S.10-2</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>requisiti propri della norma (cabina, tempi, protezione dall'acqua) da verificare sul testo</t>
+          <t>alimentazione di sicurezza dell'ascensore antincendio: interruzione al massimo 15 s, autonomia oltre 30 min</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-72:2020</t>
+          <t>Codice S.10, Tab. S.10-2</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="G138" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H138" s="10" t="inlineStr">
@@ -7159,22 +7159,22 @@
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
+          <t>UNI EN 81-72:2020</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>su comando della rivelazione incendio la cabina va al piano prestabilito e lascia uscire i passeggeri; con il Codice l'ascensore «dovrebbe» essere conforme alla UNI EN 81-73</t>
+          <t>requisiti propri della norma (cabina, tempi, protezione dall'acqua) da verificare sul testo</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
+          <t>UNI EN 81-72:2020</t>
         </is>
       </c>
       <c r="F139" s="10" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="G139" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H139" s="10" t="inlineStr">
@@ -7210,17 +7210,17 @@
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-73:2020</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>segnali e comportamento della manovra da verificare sul testo; la norma serve anche da base per migliorare gli esistenti</t>
+          <t>su comando della rivelazione incendio la cabina va al piano prestabilito e lascia uscire i passeggeri; con il Codice l'ascensore «dovrebbe» essere conforme alla UNI EN 81-73</t>
         </is>
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-73:2020</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
         </is>
       </c>
       <c r="F140" s="10" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="G140" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H140" s="10" t="inlineStr">
@@ -7245,28 +7245,28 @@
       <c r="M140" s="11" t="n"/>
       <c r="N140" s="11" t="n"/>
     </row>
-    <row r="141" ht="69" customHeight="1">
+    <row r="141" ht="56" customHeight="1">
       <c r="A141" s="10" t="n">
         <v>139</v>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-76:2025 (evacuazione delle persone con disabilità)</t>
+          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-76:2025</t>
+          <t>UNI EN 81-73:2020</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>evacuazione delle persone con disabilità con l'ascensore: requisiti aggiuntivi alla EN 81-20 (manovra, alimentazione) da verificare sul testo</t>
+          <t>segnali e comportamento della manovra da verificare sul testo; la norma serve anche da base per migliorare gli esistenti</t>
         </is>
       </c>
       <c r="E141" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-76:2025</t>
+          <t>UNI EN 81-73:2020</t>
         </is>
       </c>
       <c r="F141" s="10" t="inlineStr">
@@ -7291,28 +7291,28 @@
       <c r="M141" s="11" t="n"/>
       <c r="N141" s="11" t="n"/>
     </row>
-    <row r="142" ht="56" customHeight="1">
+    <row r="142" ht="69" customHeight="1">
       <c r="A142" s="10" t="n">
         <v>140</v>
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-76:2025 (evacuazione delle persone con disabilità)</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 1</t>
+          <t>UNI EN 81-76:2025</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>con accelerazione di progetto a_d fino a 1 m/s² nessuna prescrizione specifica; a_d e la posizione dei rilevatori si concordano con il progettista dell'edificio</t>
+          <t>evacuazione delle persone con disabilità con l'ascensore: requisiti aggiuntivi alla EN 81-20 (manovra, alimentazione) da verificare sul testo</t>
         </is>
       </c>
       <c r="E142" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 1</t>
+          <t>UNI EN 81-76:2025</t>
         </is>
       </c>
       <c r="F142" s="10" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="G142" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H142" s="10" t="inlineStr">
@@ -7337,7 +7337,7 @@
       <c r="M142" s="11" t="n"/>
       <c r="N142" s="11" t="n"/>
     </row>
-    <row r="143" ht="95" customHeight="1">
+    <row r="143" ht="56" customHeight="1">
       <c r="A143" s="10" t="n">
         <v>141</v>
       </c>
@@ -7348,17 +7348,17 @@
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
+          <t>UNI EN 81-77:2022, 1</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>oltre 1 m/s²: massa della cabina nei calcoli (5.4.1), ritegni della cabina (5.4.2) e del contrappeso (5.5), protezione delle pulegge (5.6.1), tensioni e frecce delle guide (5.8.2, All. D), rilevazione e modo sismico (5.10.3, 5.10.4); soglie delle categorie dell'All. A da verificare sul testo</t>
+          <t>con accelerazione di progetto a_d fino a 1 m/s² nessuna prescrizione specifica; a_d e la posizione dei rilevatori si concordano con il progettista dell'edificio</t>
         </is>
       </c>
       <c r="E143" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
+          <t>UNI EN 81-77:2022, 1</t>
         </is>
       </c>
       <c r="F143" s="10" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="G143" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H143" s="10" t="inlineStr">
@@ -7383,7 +7383,7 @@
       <c r="M143" s="11" t="n"/>
       <c r="N143" s="11" t="n"/>
     </row>
-    <row r="144" ht="43" customHeight="1">
+    <row r="144" ht="95" customHeight="1">
       <c r="A144" s="10" t="n">
         <v>142</v>
       </c>
@@ -7394,17 +7394,17 @@
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 0.3</t>
+          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>non si applica agli impianti installati prima della sua pubblicazione</t>
+          <t>oltre 1 m/s²: massa della cabina nei calcoli (5.4.1), ritegni della cabina (5.4.2) e del contrappeso (5.5), protezione delle pulegge (5.6.1), tensioni e frecce delle guide (5.8.2, All. D), rilevazione e modo sismico (5.10.3, 5.10.4); soglie delle categorie dell'All. A da verificare sul testo</t>
         </is>
       </c>
       <c r="E144" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 0.3</t>
+          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
         </is>
       </c>
       <c r="F144" s="10" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="G144" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H144" s="10" t="inlineStr">
@@ -7429,28 +7429,28 @@
       <c r="M144" s="11" t="n"/>
       <c r="N144" s="11" t="n"/>
     </row>
-    <row r="145" ht="69" customHeight="1">
+    <row r="145" ht="43" customHeight="1">
       <c r="A145" s="10" t="n">
         <v>143</v>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-80:2019</t>
+          <t>UNI EN 81-77:2022, 0.3</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>analisi dei rischi dell'impianto esistente e piano di miglioramento per priorità, scelta volontaria del proprietario</t>
+          <t>non si applica agli impianti installati prima della sua pubblicazione</t>
         </is>
       </c>
       <c r="E145" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-80:2019</t>
+          <t>UNI EN 81-77:2022, 0.3</t>
         </is>
       </c>
       <c r="F145" s="10" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="G145" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H145" s="10" t="inlineStr">
@@ -7475,28 +7475,28 @@
       <c r="M145" s="11" t="n"/>
       <c r="N145" s="11" t="n"/>
     </row>
-    <row r="146" ht="56" customHeight="1">
+    <row r="146" ht="69" customHeight="1">
       <c r="A146" s="10" t="n">
         <v>144</v>
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-82:2026 (accessibilità degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-82:2026</t>
+          <t>UNI EN 81-80:2019</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>miglioramento dell'accessibilità di un impianto esistente secondo i requisiti della EN 81-70</t>
+          <t>analisi dei rischi dell'impianto esistente e piano di miglioramento per priorità, scelta volontaria del proprietario</t>
         </is>
       </c>
       <c r="E146" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-82:2026</t>
+          <t>UNI EN 81-80:2019</t>
         </is>
       </c>
       <c r="F146" s="10" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="G146" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H146" s="10" t="inlineStr">
@@ -7527,22 +7527,22 @@
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-83:2026 (antivandalo degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-82:2026 (accessibilità degli esistenti)</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-83:2026</t>
+          <t>UNI EN 81-82:2026</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>miglioramento della resistenza agli atti vandalici di un impianto esistente secondo la EN 81-71:2022 (voce 1.2 della Tab. A.1 della EN 81-80)</t>
+          <t>miglioramento dell'accessibilità di un impianto esistente secondo i requisiti della EN 81-70</t>
         </is>
       </c>
       <c r="E147" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-83:2026</t>
+          <t>UNI EN 81-82:2026</t>
         </is>
       </c>
       <c r="F147" s="10" t="inlineStr">
@@ -7573,22 +7573,22 @@
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-83:2026 (antivandalo degli esistenti)</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-83:2026</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>piattaforma di distribuzione davanti alla porta di cabina: 1,50 × 1,50 m negli edifici nuovi, 1,40 × 1,40 m nell'adeguamento (fuori dal vano: in sito)</t>
+          <t>miglioramento della resistenza agli atti vandalici di un impianto esistente secondo la EN 81-71:2022 (voce 1.2 della Tab. A.1 della EN 81-80)</t>
         </is>
       </c>
       <c r="E148" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-83:2026</t>
         </is>
       </c>
       <c r="F148" s="10" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="H148" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I148" s="11" t="n"/>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>porte di cabina e di piano a scorrimento automatico (nell'adeguamento la porta di piano può essere a battente se ad apertura automatica); porte aperte almeno 8 s, chiusura in almeno 4 s</t>
+          <t>piattaforma di distribuzione davanti alla porta di cabina: 1,50 × 1,50 m negli edifici nuovi, 1,40 × 1,40 m nell'adeguamento (fuori dal vano: in sito)</t>
         </is>
       </c>
       <c r="E149" s="10" t="inlineStr">
@@ -7659,7 +7659,7 @@
       <c r="M149" s="11" t="n"/>
       <c r="N149" s="11" t="n"/>
     </row>
-    <row r="150" ht="43" customHeight="1">
+    <row r="150" ht="56" customHeight="1">
       <c r="A150" s="10" t="n">
         <v>148</v>
       </c>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>arresto ai piani con autolivellamento entro ± 2 cm; sosta ai piani con le porte chiuse</t>
+          <t>porte di cabina e di piano a scorrimento automatico (nell'adeguamento la porta di piano può essere a battente se ad apertura automatica); porte aperte almeno 8 s, chiusura in almeno 4 s</t>
         </is>
       </c>
       <c r="E150" s="10" t="inlineStr">
@@ -7705,7 +7705,7 @@
       <c r="M150" s="11" t="n"/>
       <c r="N150" s="11" t="n"/>
     </row>
-    <row r="151" ht="56" customHeight="1">
+    <row r="151" ht="43" customHeight="1">
       <c r="A151" s="10" t="n">
         <v>149</v>
       </c>
@@ -7716,17 +7716,17 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>pulsanti di cabina e di piano: il più alto tra 1,10 e 1,40 m, misurato all'asse del comando; bottoniera di cabina su una parete laterale ad almeno 0,35 m dalla porta</t>
+          <t>arresto ai piani con autolivellamento entro ± 2 cm; sosta ai piani con le porte chiuse</t>
         </is>
       </c>
       <c r="E151" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F151" s="10" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="G151" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H151" s="10" t="inlineStr">
@@ -7751,7 +7751,7 @@
       <c r="M151" s="11" t="n"/>
       <c r="N151" s="11" t="n"/>
     </row>
-    <row r="152" ht="95" customHeight="1">
+    <row r="152" ht="56" customHeight="1">
       <c r="A152" s="10" t="n">
         <v>150</v>
       </c>
@@ -7762,17 +7762,17 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
+          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>citofono in cabina tra 1,10 e 1,30 m; luce d'emergenza con almeno 3 h di autonomia; campanello d'allarme e segnale luminoso di allarme ricevuto; arresto e inversione della chiusura; segnale acustico d'arrivo; numeri in rilievo e Braille, targa Braille di piano; sedile ribaltabile dove possibile</t>
+          <t>pulsanti di cabina e di piano: il più alto tra 1,10 e 1,40 m, misurato all'asse del comando; bottoniera di cabina su una parete laterale ad almeno 0,35 m dalla porta</t>
         </is>
       </c>
       <c r="E152" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
+          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
         </is>
       </c>
       <c r="F152" s="10" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="G152" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H152" s="10" t="inlineStr">
@@ -7797,7 +7797,7 @@
       <c r="M152" s="11" t="n"/>
       <c r="N152" s="11" t="n"/>
     </row>
-    <row r="153" ht="56" customHeight="1">
+    <row r="153" ht="95" customHeight="1">
       <c r="A153" s="10" t="n">
         <v>151</v>
       </c>
@@ -7808,17 +7808,17 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
+          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>ascensore obbligatorio oltre il terzo livello (contati interrati e porticati); negli immobili con più di tre livelli fuori terra un ascensore per ogni scala principale</t>
+          <t>citofono in cabina tra 1,10 e 1,30 m; luce d'emergenza con almeno 3 h di autonomia; campanello d'allarme e segnale luminoso di allarme ricevuto; arresto e inversione della chiusura; segnale acustico d'arrivo; numeri in rilievo e Braille, targa Braille di piano; sedile ribaltabile dove possibile</t>
         </is>
       </c>
       <c r="E153" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
+          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
         </is>
       </c>
       <c r="F153" s="10" t="inlineStr">
@@ -7854,17 +7854,17 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>nelle ristrutturazioni deroghe per impossibilità tecnica strutturale o impiantistica (privati: concesse dal Sindaco); edifici vincolati: deroga se le opere pregiudicano il bene</t>
+          <t>ascensore obbligatorio oltre il terzo livello (contati interrati e porticati); negli immobili con più di tre livelli fuori terra un ascensore per ogni scala principale</t>
         </is>
       </c>
       <c r="E154" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
         </is>
       </c>
       <c r="F154" s="10" t="inlineStr">
@@ -7889,28 +7889,28 @@
       <c r="M154" s="11" t="n"/>
       <c r="N154" s="11" t="n"/>
     </row>
-    <row r="155" ht="69" customHeight="1">
+    <row r="155" ht="56" customHeight="1">
       <c r="A155" s="10" t="n">
         <v>153</v>
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>il progettista applica il DM 15/09/2005 oppure la RTV V.3 del Codice: dove si usa il Codice il DM 2005 non si applica</t>
+          <t>nelle ristrutturazioni deroghe per impossibilità tecnica strutturale o impiantistica (privati: concesse dal Sindaco); edifici vincolati: deroga se le opere pregiudicano il bene</t>
         </is>
       </c>
       <c r="E155" s="10" t="inlineStr">
         <is>
-          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
         </is>
       </c>
       <c r="F155" s="10" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="H155" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I155" s="11" t="n"/>
@@ -7935,7 +7935,7 @@
       <c r="M155" s="11" t="n"/>
       <c r="N155" s="11" t="n"/>
     </row>
-    <row r="156" ht="95" customHeight="1">
+    <row r="156" ht="69" customHeight="1">
       <c r="A156" s="10" t="n">
         <v>154</v>
       </c>
@@ -7946,17 +7946,17 @@
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, art. 1 c.2</t>
+          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>sugli impianti esistenti vale per le modifiche sostanziali: nuovo impianto; più fermate o altro azionamento; pareti del vano, porte di piano, locale macchine o pulegge sostituiti con materiali, modelli, dimensioni o criteri diversi; solai o scale rifatti che coinvolgono l'impianto; sopraelevazione; cambio di destinazione d'uso</t>
+          <t>il progettista applica il DM 15/09/2005 oppure la RTV V.3 del Codice: dove si usa il Codice il DM 2005 non si applica</t>
         </is>
       </c>
       <c r="E156" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, art. 1 c.2</t>
+          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
         </is>
       </c>
       <c r="F156" s="10" t="inlineStr">
@@ -7981,7 +7981,7 @@
       <c r="M156" s="11" t="n"/>
       <c r="N156" s="11" t="n"/>
     </row>
-    <row r="157" ht="69" customHeight="1">
+    <row r="157" ht="95" customHeight="1">
       <c r="A157" s="10" t="n">
         <v>155</v>
       </c>
@@ -7992,17 +7992,17 @@
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+          <t>DM 15/09/2005, art. 1 c.2</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>tipo di vano: aperto, protetto o a prova di fumo (Codice: classi da SA a SE)</t>
+          <t>sugli impianti esistenti vale per le modifiche sostanziali: nuovo impianto; più fermate o altro azionamento; pareti del vano, porte di piano, locale macchine o pulegge sostituiti con materiali, modelli, dimensioni o criteri diversi; solai o scale rifatti che coinvolgono l'impianto; sopraelevazione; cambio di destinazione d'uso</t>
         </is>
       </c>
       <c r="E157" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+          <t>DM 15/09/2005, art. 1 c.2</t>
         </is>
       </c>
       <c r="F157" s="10" t="inlineStr">
@@ -8038,17 +8038,17 @@
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 2</t>
+          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>pareti del vano, locale macchine e pulegge, setti e arcata non combustibili; pareti, pavimento e tetto della cabina in classe di reazione al fuoco non oltre 1</t>
+          <t>tipo di vano: aperto, protetto o a prova di fumo (Codice: classi da SA a SE)</t>
         </is>
       </c>
       <c r="E158" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 2</t>
+          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
         </is>
       </c>
       <c r="F158" s="10" t="inlineStr">
@@ -8073,7 +8073,7 @@
       <c r="M158" s="11" t="n"/>
       <c r="N158" s="11" t="n"/>
     </row>
-    <row r="159" ht="82" customHeight="1">
+    <row r="159" ht="69" customHeight="1">
       <c r="A159" s="10" t="n">
         <v>157</v>
       </c>
@@ -8084,17 +8084,17 @@
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 5</t>
+          <t>DM 15/09/2005, punto 2</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>aerazione permanente in alto verso spazi scoperti di almeno il 3 % della pianta (vano almeno 0,20 m², locale macchine o pulegge almeno 0,05 m²), con una protezione che non lascia passare una sfera oltre 15 mm; non serve se il vano è aperto su spazi scoperti</t>
+          <t>pareti del vano, locale macchine e pulegge, setti e arcata non combustibili; pareti, pavimento e tetto della cabina in classe di reazione al fuoco non oltre 1</t>
         </is>
       </c>
       <c r="E159" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 5</t>
+          <t>DM 15/09/2005, punto 2</t>
         </is>
       </c>
       <c r="F159" s="10" t="inlineStr">
@@ -8119,7 +8119,7 @@
       <c r="M159" s="11" t="n"/>
       <c r="N159" s="11" t="n"/>
     </row>
-    <row r="160" ht="69" customHeight="1">
+    <row r="160" ht="82" customHeight="1">
       <c r="A160" s="10" t="n">
         <v>158</v>
       </c>
@@ -8130,17 +8130,17 @@
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+          <t>DM 15/09/2005, punto 5</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>estintore 21A89BC vicino all'accesso al macchinario; richiamo della cabina al piano prestabilito su comando della rivelazione quando la compartimentazione lo richiede</t>
+          <t>aerazione permanente in alto verso spazi scoperti di almeno il 3 % della pianta (vano almeno 0,20 m², locale macchine o pulegge almeno 0,05 m²), con una protezione che non lascia passare una sfera oltre 15 mm; non serve se il vano è aperto su spazi scoperti</t>
         </is>
       </c>
       <c r="E160" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+          <t>DM 15/09/2005, punto 5</t>
         </is>
       </c>
       <c r="F160" s="10" t="inlineStr">
@@ -8176,17 +8176,17 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>Codice S.9, Tab. S.9-3</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>piani tra 32 e 54 m: almeno un ascensore antincendio; oltre 54 m: almeno uno di soccorso; interrati tra −10 e −15 m: antincendio; sotto −15 m: soccorso</t>
+          <t>estintore 21A89BC vicino all'accesso al macchinario; richiamo della cabina al piano prestabilito su comando della rivelazione quando la compartimentazione lo richiede</t>
         </is>
       </c>
       <c r="E161" s="10" t="inlineStr">
         <is>
-          <t>Codice S.9, Tab. S.9-3</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
         </is>
       </c>
       <c r="F161" s="10" t="inlineStr">
@@ -8211,28 +8211,28 @@
       <c r="M161" s="11" t="n"/>
       <c r="N161" s="11" t="n"/>
     </row>
-    <row r="162" ht="43" customHeight="1">
+    <row r="162" ht="69" customHeight="1">
       <c r="A162" s="10" t="n">
         <v>160</v>
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §3.1.4</t>
+          <t>Codice S.9, Tab. S.9-3</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>carichi del macchinario valutati caso per caso sui massimi prevedibili e riportati nel progetto e nel collaudo statico</t>
+          <t>piani tra 32 e 54 m: almeno un ascensore antincendio; oltre 54 m: almeno uno di soccorso; interrati tra −10 e −15 m: antincendio; sotto −15 m: soccorso</t>
         </is>
       </c>
       <c r="E162" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §3.1.4</t>
+          <t>Codice S.9, Tab. S.9-3</t>
         </is>
       </c>
       <c r="F162" s="10" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="H162" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I162" s="11" t="n"/>
@@ -8268,17 +8268,17 @@
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §8.4.1</t>
+          <t>NTC 2018, §3.1.4</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>su un edificio esistente l'intervento è locale: verifica limitata alle parti interessate, senza ridurre la sicurezza preesistente</t>
+          <t>carichi del macchinario valutati caso per caso sui massimi prevedibili e riportati nel progetto e nel collaudo statico</t>
         </is>
       </c>
       <c r="E163" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §8.4.1</t>
+          <t>NTC 2018, §3.1.4</t>
         </is>
       </c>
       <c r="F163" s="10" t="inlineStr">
@@ -8314,17 +8314,17 @@
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §11.4.1</t>
+          <t>NTC 2018, §8.4.1</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>ancoranti per uso strutturale qualificati; con azioni sismiche categoria C2 per tutte le classi d'uso</t>
+          <t>su un edificio esistente l'intervento è locale: verifica limitata alle parti interessate, senza ridurre la sicurezza preesistente</t>
         </is>
       </c>
       <c r="E164" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §11.4.1</t>
+          <t>NTC 2018, §8.4.1</t>
         </is>
       </c>
       <c r="F164" s="10" t="inlineStr">
@@ -8349,7 +8349,7 @@
       <c r="M164" s="11" t="n"/>
       <c r="N164" s="11" t="n"/>
     </row>
-    <row r="165" ht="108" customHeight="1">
+    <row r="165" ht="43" customHeight="1">
       <c r="A165" s="10" t="n">
         <v>163</v>
       </c>
@@ -8360,17 +8360,17 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §7.2.3–7.2.4</t>
+          <t>NTC 2018, §11.4.1</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>forza sismica sull'elemento non strutturale Fa = Sa·Wa/qa; nessun vincolo ad attrito; studio specifico oltre il 30 % del carico permanente del solaio o il 10 % di quello dell'intera struttura; progetto antisismico dell'impianto del produttore, dei collegamenti dell'installatore, dei solai e delle pareti d'ancoraggio del progettista strutturale</t>
+          <t>ancoranti per uso strutturale qualificati; con azioni sismiche categoria C2 per tutte le classi d'uso</t>
         </is>
       </c>
       <c r="E165" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §7.2.3–7.2.4</t>
+          <t>NTC 2018, §11.4.1</t>
         </is>
       </c>
       <c r="F165" s="10" t="inlineStr">
@@ -8395,7 +8395,7 @@
       <c r="M165" s="11" t="n"/>
       <c r="N165" s="11" t="n"/>
     </row>
-    <row r="166" ht="43" customHeight="1">
+    <row r="166" ht="108" customHeight="1">
       <c r="A166" s="10" t="n">
         <v>164</v>
       </c>
@@ -8406,17 +8406,17 @@
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+          <t>NTC 2018, §7.2.3–7.2.4</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>impianti: stabilità allo SLV per tutte le classi d'uso; nelle classi III e IV anche funzionamento allo SLO</t>
+          <t>forza sismica sull'elemento non strutturale Fa = Sa·Wa/qa; nessun vincolo ad attrito; studio specifico oltre il 30 % del carico permanente del solaio o il 10 % di quello dell'intera struttura; progetto antisismico dell'impianto del produttore, dei collegamenti dell'installatore, dei solai e delle pareti d'ancoraggio del progettista strutturale</t>
         </is>
       </c>
       <c r="E166" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+          <t>NTC 2018, §7.2.3–7.2.4</t>
         </is>
       </c>
       <c r="F166" s="10" t="inlineStr">
@@ -8441,10 +8441,56 @@
       <c r="M166" s="11" t="n"/>
       <c r="N166" s="11" t="n"/>
     </row>
+    <row r="167" ht="43" customHeight="1">
+      <c r="A167" s="10" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C167" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+        </is>
+      </c>
+      <c r="D167" s="10" t="inlineStr">
+        <is>
+          <t>impianti: stabilità allo SLV per tutte le classi d'uso; nelle classi III e IV anche funzionamento allo SLO</t>
+        </is>
+      </c>
+      <c r="E167" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+        </is>
+      </c>
+      <c r="F167" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G167" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H167" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I167" s="11" t="n"/>
+      <c r="J167" s="11" t="n"/>
+      <c r="K167" s="11" t="n"/>
+      <c r="L167" s="11" t="n"/>
+      <c r="M167" s="11" t="n"/>
+      <c r="N167" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N166"/>
+  <autoFilter ref="A1:N167"/>
   <dataValidations count="1">
-    <dataValidation sqref="I3:I166" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
+    <dataValidation sqref="I3:I167" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
       <formula1>"conforme,diverso,non applicabile"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8487,7 +8533,7 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$166,"da verificare")</f>
+        <f>COUNTIF(Voci!$G$3:$G$167,"da verificare")</f>
         <v/>
       </c>
     </row>
@@ -8498,7 +8544,7 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$166,"confermato")</f>
+        <f>COUNTIF(Voci!$G$3:$G$167,"confermato")</f>
         <v/>
       </c>
     </row>
@@ -8509,7 +8555,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$166,"scelta del software")</f>
+        <f>COUNTIF(Voci!$G$3:$G$167,"scelta del software")</f>
         <v/>
       </c>
     </row>
@@ -8520,7 +8566,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$166,"stima")</f>
+        <f>COUNTIF(Voci!$G$3:$G$167,"stima")</f>
         <v/>
       </c>
     </row>
@@ -8531,7 +8577,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$166,"derivazione")</f>
+        <f>COUNTIF(Voci!$G$3:$G$167,"derivazione")</f>
         <v/>
       </c>
     </row>
@@ -8542,7 +8588,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$166,"prassi di cantiere")</f>
+        <f>COUNTIF(Voci!$G$3:$G$167,"prassi di cantiere")</f>
         <v/>
       </c>
     </row>
@@ -8553,7 +8599,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTA(Voci!$A$3:$A$166)</f>
+        <f>COUNTA(Voci!$A$3:$A$167)</f>
         <v/>
       </c>
     </row>
@@ -8571,7 +8617,7 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$166,"conforme")</f>
+        <f>COUNTIF(Voci!$I$3:$I$167,"conforme")</f>
         <v/>
       </c>
     </row>
@@ -8582,7 +8628,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$166,"diverso")</f>
+        <f>COUNTIF(Voci!$I$3:$I$167,"diverso")</f>
         <v/>
       </c>
     </row>
@@ -8593,7 +8639,7 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$166,"non applicabile")</f>
+        <f>COUNTIF(Voci!$I$3:$I$167,"non applicabile")</f>
         <v/>
       </c>
     </row>
@@ -8604,14 +8650,14 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>COUNTBLANK(Voci!$I$3:$I$166)</f>
+        <f>COUNTBLANK(Voci!$I$3:$I$167)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Conteggi sulle righe 3–166 del foglio «Voci» (la riga 2 è l'esempio).</t>
+          <t>Conteggi sulle righe 3–167 del foglio «Voci» (la riga 2 è l'esempio).</t>
         </is>
       </c>
     </row>

--- a/liftpilot/docs/lista-verifica-normativa.xlsx
+++ b/liftpilot/docs/lista-verifica-normativa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Riepilogo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$168</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Voci'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N167"/>
+  <dimension ref="A1:N168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4818,32 +4818,32 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
+          <t>L'argano dentro il locale del macchinario</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
+          <t>l'argano sul suo basamento — con il telaio del rinvio o con il supporto del rinvio — sta dentro il locale in pianta e sotto il soffitto: la distanza minima dai muri e dal soffitto non è negativa; ingombri dalle quote del costruttore per gli argani disegnati com'è, dall'argano generico del software (scalato alla puleggia) per gli altri; la puleggia di rinvio sul suo supporto sotto l'argano libera il basamento dell'argano sopra di essa (solo le putrelle sollevate la scavalcano)</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E), §3.1.4 (carichi del macchinario); DPR 1497/1963, art. 5.1–5.2 (carichi fissi più 1,5 volte il carico statico delle funi, sicurezza ≥ 6, freccia ≤ 1/1500 della luce libera: regola storica degli impianti esistenti, letta su Normattiva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
+          <t>geometria del progetto: la pianta e l'altezza del locale inserite, gli ingombri dell'argano e del basamento</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>argano dentro il locale (muri e soffitto); puleggia di rinvio sul suo supporto sotto l'argano</t>
         </is>
       </c>
       <c r="I88" s="11" t="n"/>
@@ -4853,33 +4853,33 @@
       <c r="M88" s="11" t="n"/>
       <c r="N88" s="11" t="n"/>
     </row>
-    <row r="89" ht="108" customHeight="1">
+    <row r="89" ht="134" customHeight="1">
       <c r="A89" s="10" t="n">
         <v>87</v>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Carichi sul pavimento della fossa</t>
+          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
+          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.8; UNI EN 81-50:2020, 5.10</t>
+          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E), §3.1.4 (carichi del macchinario); DPR 1497/1963, art. 5.1–5.2 (carichi fissi più 1,5 volte il carico statico delle funi, sicurezza ≥ 6, freccia ≤ 1/1500 della luce libera: regola storica degli impianti esistenti, letta su Normattiva)</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi; sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
+          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
         </is>
       </c>
       <c r="I89" s="11" t="n"/>
@@ -4910,22 +4910,22 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Spinte sulle guide di cabina</t>
+          <t>Carichi sul pavimento della fossa</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
+          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.10</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8; UNI EN 81-50:2020, 5.10</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi; sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
@@ -4945,7 +4945,7 @@
       <c r="M90" s="11" t="n"/>
       <c r="N90" s="11" t="n"/>
     </row>
-    <row r="91" ht="82" customHeight="1">
+    <row r="91" ht="108" customHeight="1">
       <c r="A91" s="10" t="n">
         <v>89</v>
       </c>
@@ -4956,27 +4956,27 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Carico della macchina sulla soletta</t>
+          <t>Spinte sulle guide di cabina</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
+          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.10</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
+          <t>sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>prassi di cantiere</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
@@ -4991,7 +4991,7 @@
       <c r="M91" s="11" t="n"/>
       <c r="N91" s="11" t="n"/>
     </row>
-    <row r="92" ht="43" customHeight="1">
+    <row r="92" ht="82" customHeight="1">
       <c r="A92" s="10" t="n">
         <v>90</v>
       </c>
@@ -5002,12 +5002,12 @@
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Massa dei cavi flessibili</t>
+          <t>Carico della macchina sulla soletta</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
+          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
+          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>prassi di cantiere</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
@@ -5037,7 +5037,7 @@
       <c r="M92" s="11" t="n"/>
       <c r="N92" s="11" t="n"/>
     </row>
-    <row r="93" ht="121" customHeight="1">
+    <row r="93" ht="43" customHeight="1">
       <c r="A93" s="10" t="n">
         <v>91</v>
       </c>
@@ -5048,27 +5048,27 @@
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
+          <t>Massa dei cavi flessibili</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
+          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
-          <t>regola di montaggio indicata dal committente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>scelta del committente</t>
+          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
@@ -5083,7 +5083,7 @@
       <c r="M93" s="11" t="n"/>
       <c r="N93" s="11" t="n"/>
     </row>
-    <row r="94" ht="82" customHeight="1">
+    <row r="94" ht="121" customHeight="1">
       <c r="A94" s="10" t="n">
         <v>92</v>
       </c>
@@ -5094,27 +5094,27 @@
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Lunghezze stimate nel foglio dei dati</t>
+          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
+          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>regola di montaggio indicata dal committente</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>stima del software, da sostituire con le misure di cantiere</t>
+          <t>scelta del committente</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
@@ -5129,23 +5129,23 @@
       <c r="M94" s="11" t="n"/>
       <c r="N94" s="11" t="n"/>
     </row>
-    <row r="95" ht="43" customHeight="1">
+    <row r="95" ht="82" customHeight="1">
       <c r="A95" s="10" t="n">
         <v>93</v>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Dimensioni proposte della cabina</t>
+          <t>Lunghezze stimate nel foglio dei dati</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
+          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima del software, da sostituire con le misure di cantiere</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
@@ -5175,7 +5175,7 @@
       <c r="M95" s="11" t="n"/>
       <c r="N95" s="11" t="n"/>
     </row>
-    <row r="96" ht="199" customHeight="1">
+    <row r="96" ht="43" customHeight="1">
       <c r="A96" s="10" t="n">
         <v>94</v>
       </c>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Quote della pianta fissate a mano</t>
+          <t>Dimensioni proposte della cabina</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8), quello del contrappeso dentro la lunghezza del contrappeso</t>
+          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I96" s="11" t="n"/>
@@ -5221,7 +5221,7 @@
       <c r="M96" s="11" t="n"/>
       <c r="N96" s="11" t="n"/>
     </row>
-    <row r="97" ht="82" customHeight="1">
+    <row r="97" ht="199" customHeight="1">
       <c r="A97" s="10" t="n">
         <v>95</v>
       </c>
@@ -5232,12 +5232,12 @@
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Limiti del modello del vano</t>
+          <t>Quote della pianta fissate a mano</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
+          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8), quello del contrappeso dentro la lunghezza del contrappeso</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>limite del modello attuale</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
         </is>
       </c>
       <c r="I97" s="11" t="n"/>
@@ -5267,23 +5267,23 @@
       <c r="M97" s="11" t="n"/>
       <c r="N97" s="11" t="n"/>
     </row>
-    <row r="98" ht="56" customHeight="1">
+    <row r="98" ht="82" customHeight="1">
       <c r="A98" s="10" t="n">
         <v>96</v>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Corsa</t>
+          <t>Limiti del modello del vano</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
+          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>dati dei piani inseriti</t>
+          <t>limite del modello attuale</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
@@ -5324,22 +5324,22 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Portata e velocità</t>
+          <t>Corsa</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
+          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.2.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>progetto del vano</t>
+          <t>dati dei piani inseriti</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
@@ -5359,7 +5359,7 @@
       <c r="M99" s="11" t="n"/>
       <c r="N99" s="11" t="n"/>
     </row>
-    <row r="100" ht="303" customHeight="1">
+    <row r="100" ht="56" customHeight="1">
       <c r="A100" s="10" t="n">
         <v>98</v>
       </c>
@@ -5370,27 +5370,27 @@
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Normativa di collaudo e parti sostituite o modificate — il testo delle UNI 10411 del 2024 non è stato letto: le verifiche per parte e i requisiti per la sostituzione del macchinario (edizione 2021: freno in due elementi, temporizzatore, velocità eccessiva in salita, arresto entro 1 m dalla macchina, interruzione se il freno non si apre) vanno confermati sul testo vigente</t>
+          <t>Portata e velocità</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software. Alla norma base si aggiungono le norme compatibili (matrice della ricerca, cap. 16 §5.2): sull'impianto nuovo le EN 81 supplementari (21, 28, 58, 70, 71, 72, 73, 76, 77), sulla modifica la EN 81-20/50 intera, le EN 81-28, 58, 73 e il miglioramento (80, 82, 83), su entrambi DM 236/1989, antincendio (DM 15/09/2005 o Codice V.3) e NTC 2018 (con le verifiche delle putrelle). Ogni norma ha il suo esito («non calcolata» se il software non ne calcola verifiche) e i suoi punti da verificare in sito nella relazione, con gli adempimenti del DPR 162/1999</t>
+          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
+          <t>UNI EN 81-20:2020, 5.4.2.1</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>schede UNI delle norme (scopo, data 31/10/2024); schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); sintesi secondarie; ricerca, capitoli 2.4 e 6.6</t>
+          <t>progetto del vano</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H100" s="10" t="inlineStr">
@@ -5405,7 +5405,7 @@
       <c r="M100" s="11" t="n"/>
       <c r="N100" s="11" t="n"/>
     </row>
-    <row r="101" ht="69" customHeight="1">
+    <row r="101" ht="303" customHeight="1">
       <c r="A101" s="10" t="n">
         <v>99</v>
       </c>
@@ -5416,27 +5416,27 @@
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
+          <t>Normativa di collaudo e parti sostituite o modificate — il testo delle UNI 10411 del 2024 non è stato letto: le verifiche per parte e i requisiti per la sostituzione del macchinario (edizione 2021: freno in due elementi, temporizzatore, velocità eccessiva in salita, arresto entro 1 m dalla macchina, interruzione se il freno non si apre) vanno confermati sul testo vigente</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
+          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software. Alla norma base si aggiungono le norme compatibili (matrice della ricerca, cap. 16 §5.2): sull'impianto nuovo le EN 81 supplementari (21, 28, 58, 70, 71, 72, 73, 76, 77), sulla modifica la EN 81-20/50 intera, le EN 81-28, 58, 73 e il miglioramento (80, 82, 83), su entrambi DM 236/1989, antincendio (DM 15/09/2005 o Codice V.3) e NTC 2018 (con le verifiche delle putrelle). Ogni norma ha il suo esito («non calcolata» se il software non ne calcola verifiche) e i suoi punti da verificare in sito nella relazione, con gli adempimenti del DPR 162/1999</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
+          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>scelta del software, senza fonte</t>
+          <t>schede UNI delle norme (scopo, data 31/10/2024); schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); sintesi secondarie; ricerca, capitoli 2.4 e 6.6</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H101" s="10" t="inlineStr">
@@ -5451,7 +5451,7 @@
       <c r="M101" s="11" t="n"/>
       <c r="N101" s="11" t="n"/>
     </row>
-    <row r="102" ht="82" customHeight="1">
+    <row r="102" ht="69" customHeight="1">
       <c r="A102" s="10" t="n">
         <v>100</v>
       </c>
@@ -5462,27 +5462,27 @@
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Fune oltre la corsa (L0)</t>
+          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale (macchina in basso o senza locale: fino al soffitto del vano)</t>
+          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
+          <t>scelta del software, senza fonte</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H102" s="10" t="inlineStr">
@@ -5497,7 +5497,7 @@
       <c r="M102" s="11" t="n"/>
       <c r="N102" s="11" t="n"/>
     </row>
-    <row r="103" ht="147" customHeight="1">
+    <row r="103" ht="108" customHeight="1">
       <c r="A103" s="10" t="n">
         <v>101</v>
       </c>
@@ -5508,27 +5508,27 @@
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
+          <t>Fune oltre la corsa (L0)</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
+          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale; con la puleggia di rinvio, l'asse sul basamento o sul telaio che la porta (voce locale.rinvio); macchina in basso o senza locale: fino al soffitto del vano</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>pianta del vano</t>
+          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
@@ -5543,7 +5543,7 @@
       <c r="M103" s="11" t="n"/>
       <c r="N103" s="11" t="n"/>
     </row>
-    <row r="104" ht="160" customHeight="1">
+    <row r="104" ht="147" customHeight="1">
       <c r="A104" s="10" t="n">
         <v>102</v>
       </c>
@@ -5554,22 +5554,22 @@
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
+          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
+          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
+          <t>ricerca, capitolo 5.3</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>geometria delle funi</t>
+          <t>pianta del vano</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
@@ -5589,7 +5589,7 @@
       <c r="M104" s="11" t="n"/>
       <c r="N104" s="11" t="n"/>
     </row>
-    <row r="105" ht="56" customHeight="1">
+    <row r="105" ht="160" customHeight="1">
       <c r="A105" s="10" t="n">
         <v>103</v>
       </c>
@@ -5600,22 +5600,22 @@
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
+          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
+          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
         </is>
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
+          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano</t>
+          <t>geometria delle funi</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
@@ -5635,7 +5635,7 @@
       <c r="M105" s="11" t="n"/>
       <c r="N105" s="11" t="n"/>
     </row>
-    <row r="106" ht="238" customHeight="1">
+    <row r="106" ht="56" customHeight="1">
       <c r="A106" s="10" t="n">
         <v>104</v>
       </c>
@@ -5646,27 +5646,27 @@
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso o pilastro pieno fino al terreno (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori</t>
+          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
+          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
+          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>geometria ricostruita dal software</t>
+          <t>dati verticali del vano</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
@@ -5681,7 +5681,7 @@
       <c r="M106" s="11" t="n"/>
       <c r="N106" s="11" t="n"/>
     </row>
-    <row r="107" ht="186" customHeight="1">
+    <row r="107" ht="238" customHeight="1">
       <c r="A107" s="10" t="n">
         <v>105</v>
       </c>
@@ -5692,27 +5692,27 @@
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta dal catalogo di un costruttore — i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
+          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso o pilastro pieno fino al terreno (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo; i disegni e il 3D mostrano l'argano SICOR com'è (ingombri, piedi e fori, asse della puleggia, P ed E della scheda), sul telaio del software</t>
+          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
+          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>SICOR: schede tecniche 2025 e modelli CAD scaricati da sicoritaly.com il 2 ottobre 2026 (solo le quote); Sassi, Montanari, GEM, FAER: estratti delle pagine dei costruttori e dei rivenditori, 1° ottobre 2026</t>
+          <t>geometria ricostruita dal software</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
@@ -5727,7 +5727,7 @@
       <c r="M107" s="11" t="n"/>
       <c r="N107" s="11" t="n"/>
     </row>
-    <row r="108" ht="134" customHeight="1">
+    <row r="108" ht="186" customHeight="1">
       <c r="A108" s="10" t="n">
         <v>106</v>
       </c>
@@ -5738,27 +5738,27 @@
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
+          <t>Macchina proposta dal catalogo di un costruttore — i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
+          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo; i disegni e il 3D mostrano l'argano SICOR com'è (ingombri, piedi e fori, asse della puleggia, P ed E della scheda), sul telaio del software</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 8</t>
+          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo</t>
+          <t>SICOR: schede tecniche 2025 e modelli CAD scaricati da sicoritaly.com il 2 ottobre 2026 (solo le quote); Sassi, Montanari, GEM, FAER: estratti delle pagine dei costruttori e dei rivenditori, 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H108" s="10" t="inlineStr">
@@ -5773,38 +5773,38 @@
       <c r="M108" s="11" t="n"/>
       <c r="N108" s="11" t="n"/>
     </row>
-    <row r="109" ht="69" customHeight="1">
+    <row r="109" ht="134" customHeight="1">
       <c r="A109" s="10" t="n">
         <v>107</v>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
+          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
+          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
         </is>
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
+          <t>ricerca, capitolo 8</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo (src/calc/model.ts)</t>
+          <t>motore di calcolo</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H109" s="10" t="inlineStr">
@@ -5819,7 +5819,7 @@
       <c r="M109" s="11" t="n"/>
       <c r="N109" s="11" t="n"/>
     </row>
-    <row r="110" ht="56" customHeight="1">
+    <row r="110" ht="69" customHeight="1">
       <c r="A110" s="10" t="n">
         <v>108</v>
       </c>
@@ -5830,27 +5830,27 @@
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
+          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
+          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
+          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>motore di calcolo (src/calc/model.ts)</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
@@ -5865,7 +5865,7 @@
       <c r="M110" s="11" t="n"/>
       <c r="N110" s="11" t="n"/>
     </row>
-    <row r="111" ht="69" customHeight="1">
+    <row r="111" ht="56" customHeight="1">
       <c r="A111" s="10" t="n">
         <v>109</v>
       </c>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Limite di aderenza mostrato durante la marcia</t>
+          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
+          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.2</t>
+          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
@@ -5911,7 +5911,7 @@
       <c r="M111" s="11" t="n"/>
       <c r="N111" s="11" t="n"/>
     </row>
-    <row r="112" ht="43" customHeight="1">
+    <row r="112" ht="69" customHeight="1">
       <c r="A112" s="10" t="n">
         <v>110</v>
       </c>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Tempi delle porte</t>
+          <t>Limite di aderenza mostrato durante la marcia</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
+          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.2.2</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (solo animazione)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
@@ -5957,7 +5957,7 @@
       <c r="M112" s="11" t="n"/>
       <c r="N112" s="11" t="n"/>
     </row>
-    <row r="113" ht="108" customHeight="1">
+    <row r="113" ht="43" customHeight="1">
       <c r="A113" s="10" t="n">
         <v>111</v>
       </c>
@@ -5968,27 +5968,27 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione</t>
+          <t>Tempi delle porte</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
+          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>sintesi della norma di costruttori e organismi notificati (fonti secondarie)</t>
+          <t>scelta del software (solo animazione)</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
@@ -6003,7 +6003,7 @@
       <c r="M113" s="11" t="n"/>
       <c r="N113" s="11" t="n"/>
     </row>
-    <row r="114" ht="56" customHeight="1">
+    <row r="114" ht="108" customHeight="1">
       <c r="A114" s="10" t="n">
         <v>112</v>
       </c>
@@ -6014,27 +6014,27 @@
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Cabina bloccata: rotazione in salita</t>
+          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
+          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2</t>
+          <t>UNI EN 81-20:2020, 5.8.2</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo; velocità scelta dal software</t>
+          <t>sintesi della norma di costruttori e organismi notificati (fonti secondarie)</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
@@ -6049,7 +6049,7 @@
       <c r="M114" s="11" t="n"/>
       <c r="N114" s="11" t="n"/>
     </row>
-    <row r="115" ht="43" customHeight="1">
+    <row r="115" ht="56" customHeight="1">
       <c r="A115" s="10" t="n">
         <v>113</v>
       </c>
@@ -6060,22 +6060,22 @@
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Passo di campionamento</t>
+          <t>Cabina bloccata: rotazione in salita</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
+          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
         </is>
       </c>
       <c r="E115" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.2</t>
         </is>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>motore di calcolo; velocità scelta dal software</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
@@ -6095,38 +6095,38 @@
       <c r="M115" s="11" t="n"/>
       <c r="N115" s="11" t="n"/>
     </row>
-    <row r="116" ht="56" customHeight="1">
+    <row r="116" ht="43" customHeight="1">
       <c r="A116" s="10" t="n">
         <v>114</v>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 4-bis</t>
+          <t>Passo di campionamento</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>progetto, fabbricazione, installazione e prove conformi all'All. I; documentazione tecnica e dichiarazione di conformità conservate per 10 anni</t>
+          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 4-bis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G116" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H116" s="10" t="inlineStr">
@@ -6152,17 +6152,17 @@
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 6-bis e 7 c.3</t>
+          <t>DPR 162/1999, art. 4-bis</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>procedura con un organismo notificato (All. V, VIII, X, XI o XII); marcatura CE in cabina con il numero dell'organismo</t>
+          <t>progetto, fabbricazione, installazione e prove conformi all'All. I; documentazione tecnica e dichiarazione di conformità conservate per 10 anni</t>
         </is>
       </c>
       <c r="E117" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 6-bis e 7 c.3</t>
+          <t>DPR 162/1999, art. 4-bis</t>
         </is>
       </c>
       <c r="F117" s="10" t="inlineStr">
@@ -6198,17 +6198,17 @@
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.1–3</t>
+          <t>DPR 162/1999, artt. 6-bis e 7 c.3</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>comunicazione al Comune entro 60 giorni dalla dichiarazione di conformità (oltre: con il verbale di una verifica straordinaria di attivazione); matricola entro 30 giorni</t>
+          <t>procedura con un organismo notificato (All. V, VIII, X, XI o XII); marcatura CE in cabina con il numero dell'organismo</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.1–3</t>
+          <t>DPR 162/1999, artt. 6-bis e 7 c.3</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
@@ -6244,17 +6244,17 @@
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
+          <t>DPR 162/1999, art. 12 c.1–3</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>verifiche periodiche ogni 2 anni; controllo dei dispositivi di sicurezza, delle funi e dell'isolamento almeno ogni 6 mesi; targa in cabina</t>
+          <t>comunicazione al Comune entro 60 giorni dalla dichiarazione di conformità (oltre: con il verbale di una verifica straordinaria di attivazione); matricola entro 30 giorni</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
+          <t>DPR 162/1999, art. 12 c.1–3</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
@@ -6279,28 +6279,28 @@
       <c r="M119" s="11" t="n"/>
       <c r="N119" s="11" t="n"/>
     </row>
-    <row r="120" ht="43" customHeight="1">
+    <row r="120" ht="56" customHeight="1">
       <c r="A120" s="10" t="n">
         <v>118</v>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
+          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>la modifica è costruttiva: la sostituzione del macchinario ne è il caso n. 5)</t>
+          <t>verifiche periodiche ogni 2 anni; controllo dei dispositivi di sicurezza, delle funi e dell'isolamento almeno ogni 6 mesi; targa in cabina</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
+          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
@@ -6336,17 +6336,17 @@
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4</t>
+          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>prima della comunicazione, adeguamento della parte modificata o sostituita e delle altre parti interessate</t>
+          <t>la modifica è costruttiva: la sostituzione del macchinario ne è il caso n. 5)</t>
         </is>
       </c>
       <c r="E121" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4</t>
+          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
@@ -6382,17 +6382,17 @@
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4–5</t>
+          <t>DPR 162/1999, art. 12 c.4</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>comunicazione al Comune e al soggetto delle verifiche periodiche; l'impianto non resta in esercizio senza le comunicazioni aggiornate</t>
+          <t>prima della comunicazione, adeguamento della parte modificata o sostituita e delle altre parti interessate</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4–5</t>
+          <t>DPR 162/1999, art. 12 c.4</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
@@ -6417,7 +6417,7 @@
       <c r="M122" s="11" t="n"/>
       <c r="N122" s="11" t="n"/>
     </row>
-    <row r="123" ht="56" customHeight="1">
+    <row r="123" ht="43" customHeight="1">
       <c r="A123" s="10" t="n">
         <v>121</v>
       </c>
@@ -6428,17 +6428,17 @@
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 14 c.3</t>
+          <t>DPR 162/1999, art. 12 c.4–5</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>verifica straordinaria da uno dei soggetti dell'art. 13 c.1, di norma limitata ai controlli sulle modifiche, con la documentazione delle modifiche e dei componenti sostituiti</t>
+          <t>comunicazione al Comune e al soggetto delle verifiche periodiche; l'impianto non resta in esercizio senza le comunicazioni aggiornate</t>
         </is>
       </c>
       <c r="E123" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 14 c.3</t>
+          <t>DPR 162/1999, art. 12 c.4–5</t>
         </is>
       </c>
       <c r="F123" s="10" t="inlineStr">
@@ -6469,22 +6469,22 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
+          <t>DPR 162/1999, art. 14 c.3</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>prove dell'organismo notificato: funzionamento a vuoto e a pieno carico, in mancanza di energia, prova statica a 1,25 volte la portata e controllo che non restino deformazioni</t>
+          <t>verifica straordinaria da uno dei soggetti dell'art. 13 c.1, di norma limitata ai controlli sulle modifiche, con la documentazione delle modifiche e dei componenti sostituiti</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
+          <t>DPR 162/1999, art. 14 c.3</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
@@ -6520,17 +6520,17 @@
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
+          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>documentazione tecnica con i risultati dei calcoli di progetto, le relazioni sulle prove e l'elenco delle norme armonizzate applicate, anche in parte</t>
+          <t>prove dell'organismo notificato: funzionamento a vuoto e a pieno carico, in mancanza di energia, prova statica a 1,25 volte la portata e controllo che non restino deformazioni</t>
         </is>
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
+          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
@@ -6566,17 +6566,17 @@
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
+          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>per gli ascensori dichiarati conformi dal 20/01/2027: requisiti dell'All. III del Regolamento macchine (tra cui 1.1.9 e 1.2.1), con una valutazione aggiuntiva per i requisiti nuovi o cambiati</t>
+          <t>documentazione tecnica con i risultati dei calcoli di progetto, le relazioni sulle prove e l'elenco delle norme armonizzate applicate, anche in parte</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
+          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
@@ -6607,22 +6607,22 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-1:2024</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, scopo</t>
+          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>ascensori elettrici a frizione non conformi alla 95/16/CE né alla 2014/33/UE; esclude le modifiche che cambiano le misure antincendio (valgono il DM 15/09/2005 o il Codice V.3)</t>
+          <t>per gli ascensori dichiarati conformi dal 20/01/2027: requisiti dell'All. III del Regolamento macchine (tra cui 1.1.9 e 1.2.1), con una valutazione aggiuntiva per i requisiti nuovi o cambiati</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, scopo</t>
+          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
@@ -6653,22 +6653,22 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-11:2024</t>
+          <t>Collaudo: UNI 10411-1:2024</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, scopo</t>
+          <t>UNI 10411-1:2024, scopo</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>ascensori elettrici a frizione conformi alla Direttiva Ascensori; esclude le modifiche che cambiano le misure antincendio (valgono il DM 15/09/2005 o il Codice V.3)</t>
+          <t>ascensori elettrici a frizione non conformi alla 95/16/CE né alla 2014/33/UE; esclude le modifiche che cambiano le misure antincendio (valgono il DM 15/09/2005 o il Codice V.3)</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, scopo</t>
+          <t>UNI 10411-1:2024, scopo</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
@@ -6699,22 +6699,22 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
+          <t>Collaudo: UNI 10411-11:2024</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-21:2022, scopo</t>
+          <t>UNI 10411-11:2024, scopo</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>impianto nuovo o sostituzione completa in un edificio esistente; non copre le modifiche parziali (letto sull'edizione 2018)</t>
+          <t>ascensori elettrici a frizione conformi alla Direttiva Ascensori; esclude le modifiche che cambiano le misure antincendio (valgono il DM 15/09/2005 o il Codice V.3)</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-21:2022, scopo</t>
+          <t>UNI 10411-11:2024, scopo</t>
         </is>
       </c>
       <c r="F129" s="10" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G129" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H129" s="10" t="inlineStr">
@@ -6739,7 +6739,7 @@
       <c r="M129" s="11" t="n"/>
       <c r="N129" s="11" t="n"/>
     </row>
-    <row r="130" ht="82" customHeight="1">
+    <row r="130" ht="56" customHeight="1">
       <c r="A130" s="10" t="n">
         <v>128</v>
       </c>
@@ -6750,17 +6750,17 @@
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
+          <t>UNI EN 81-21:2022, scopo</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>spazi di rifugio ridotti solo con l'accordo preventivo: in edificio esistente PEC al Ministero con la certificazione dell'organismo prima dell'installazione (Procedura 2: dichiarazione dei punti della EN 81-21 applicati); la EN 81-21 da sola non giustifica la deroga</t>
+          <t>impianto nuovo o sostituzione completa in un edificio esistente; non copre le modifiche parziali (letto sull'edizione 2018)</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
+          <t>UNI EN 81-21:2022, scopo</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="G130" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H130" s="10" t="inlineStr">
@@ -6785,28 +6785,28 @@
       <c r="M130" s="11" t="n"/>
       <c r="N130" s="11" t="n"/>
     </row>
-    <row r="131" ht="56" customHeight="1">
+    <row r="131" ht="82" customHeight="1">
       <c r="A131" s="10" t="n">
         <v>129</v>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
+          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-28:2022</t>
+          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>teleallarme verso un servizio di soccorso: requisiti da verificare sul testo della norma; il suo uso sugli impianti esistenti non è stato verificato</t>
+          <t>spazi di rifugio ridotti solo con l'accordo preventivo: in edificio esistente PEC al Ministero con la certificazione dell'organismo prima dell'installazione (Procedura 2: dichiarazione dei punti della EN 81-21 applicati); la EN 81-21 da sola non giustifica la deroga</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-28:2022</t>
+          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
         </is>
       </c>
       <c r="F131" s="10" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="G131" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H131" s="10" t="inlineStr">
@@ -6831,28 +6831,28 @@
       <c r="M131" s="11" t="n"/>
       <c r="N131" s="11" t="n"/>
     </row>
-    <row r="132" ht="69" customHeight="1">
+    <row r="132" ht="56" customHeight="1">
       <c r="A132" s="10" t="n">
         <v>130</v>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-58:2022 (resistenza al fuoco delle porte di piano)</t>
+          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
+          <t>UNI EN 81-28:2022</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>porte di piano resistenti al fuoco (classi E, EI, EW) provate secondo la norma, quando fanno parte della compartimentazione del vano; sostituirle con modelli diversi è una modifica sostanziale ai fini antincendio</t>
+          <t>teleallarme verso un servizio di soccorso: requisiti da verificare sul testo della norma; il suo uso sugli impianti esistenti non è stato verificato</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
+          <t>UNI EN 81-28:2022</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H132" s="10" t="inlineStr">
@@ -6883,22 +6883,22 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+          <t>Collaudo: UNI EN 81-58:2022 (resistenza al fuoco delle porte di piano)</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.1</t>
+          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>tipi di cabina (larghezza × profondità, luce della porta): 1) 1000 × 1300, 800; 2) 1100 × 1400, 900; 3) 1100 × 2100, 900; 4) 1600 × 1400 o 1400 × 1600, 900; 5) 2000 × 1400 o 1400 × 2000, 1100 mm</t>
+          <t>porte di piano resistenti al fuoco (classi E, EI, EW) provate secondo la norma, quando fanno parte della compartimentazione del vano; sostituirle con modelli diversi è una modifica sostanziale ai fini antincendio</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.1</t>
+          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
         </is>
       </c>
       <c r="F133" s="10" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="G133" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H133" s="10" t="inlineStr">
@@ -6934,17 +6934,17 @@
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
+          <t>UNI EN 81-70:2022, 5.3.1</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>specchio nei tipi 1–3; finiture che riducono le misure nominali al massimo di 15 mm per parete; segnale acustico regolabile 35–65 dB(A), fino a 80 in ambienti rumorosi; contrasto di Michelson con la A1:2022</t>
+          <t>tipi di cabina (larghezza × profondità, luce della porta): 1) 1000 × 1300, 800; 2) 1100 × 1400, 900; 3) 1100 × 2100, 900; 4) 1600 × 1400 o 1400 × 1600, 900; 5) 2000 × 1400 o 1400 × 2000, 1100 mm</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
+          <t>UNI EN 81-70:2022, 5.3.1</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
@@ -6969,7 +6969,7 @@
       <c r="M134" s="11" t="n"/>
       <c r="N134" s="11" t="n"/>
     </row>
-    <row r="135" ht="43" customHeight="1">
+    <row r="135" ht="69" customHeight="1">
       <c r="A135" s="10" t="n">
         <v>133</v>
       </c>
@@ -6980,17 +6980,17 @@
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, scopo</t>
+          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>si usa con la UNI EN 81-20:2020; per gli impianti esistenti vale la UNI EN 81-82</t>
+          <t>specchio nei tipi 1–3; finiture che riducono le misure nominali al massimo di 15 mm per parete; segnale acustico regolabile 35–65 dB(A), fino a 80 in ambienti rumorosi; contrasto di Michelson con la A1:2022</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, scopo</t>
+          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="G135" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H135" s="10" t="inlineStr">
@@ -7021,22 +7021,22 @@
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-71 (ascensori antivandalo)</t>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-71</t>
+          <t>UNI EN 81-70:2022, scopo</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>categoria antivandalo da concordare con il committente; per la presunzione di conformità vale l'edizione 2005+A1:2006</t>
+          <t>si usa con la UNI EN 81-20:2020; per gli impianti esistenti vale la UNI EN 81-82</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-71</t>
+          <t>UNI EN 81-70:2022, scopo</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
@@ -7061,28 +7061,28 @@
       <c r="M136" s="11" t="n"/>
       <c r="N136" s="11" t="n"/>
     </row>
-    <row r="137" ht="108" customHeight="1">
+    <row r="137" ht="43" customHeight="1">
       <c r="A137" s="10" t="n">
         <v>135</v>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+          <t>Collaudo: UNI EN 81-71 (ascensori antivandalo)</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 7; Codice V.3.3.4</t>
+          <t>UNI EN 81-71</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>ascensore antincendio: tutti i piani serviti; vano e porte di piano almeno REI 60; cabina interna almeno 1,10 × 2,10 m con accesso sul lato corto; botola sul tetto almeno 0,50 × 0,70 m; area dedicata almeno 5 m² a ogni piano; luce d'emergenza almeno 5 lux con 1 h di autonomia; IPX3 dove arriva l'acqua; linea dedicata con alimentazione di sicurezza</t>
+          <t>categoria antivandalo da concordare con il committente; per la presunzione di conformità vale l'edizione 2005+A1:2006</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 7; Codice V.3.3.4</t>
+          <t>UNI EN 81-71</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
@@ -7107,7 +7107,7 @@
       <c r="M137" s="11" t="n"/>
       <c r="N137" s="11" t="n"/>
     </row>
-    <row r="138" ht="56" customHeight="1">
+    <row r="138" ht="108" customHeight="1">
       <c r="A138" s="10" t="n">
         <v>136</v>
       </c>
@@ -7118,17 +7118,17 @@
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Codice S.10, Tab. S.10-2</t>
+          <t>DM 15/09/2005, punto 7; Codice V.3.3.4</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>alimentazione di sicurezza dell'ascensore antincendio: interruzione al massimo 15 s, autonomia oltre 30 min</t>
+          <t>ascensore antincendio: tutti i piani serviti; vano e porte di piano almeno REI 60; cabina interna almeno 1,10 × 2,10 m con accesso sul lato corto; botola sul tetto almeno 0,50 × 0,70 m; area dedicata almeno 5 m² a ogni piano; luce d'emergenza almeno 5 lux con 1 h di autonomia; IPX3 dove arriva l'acqua; linea dedicata con alimentazione di sicurezza</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>Codice S.10, Tab. S.10-2</t>
+          <t>DM 15/09/2005, punto 7; Codice V.3.3.4</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
@@ -7164,17 +7164,17 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-72:2020</t>
+          <t>Codice S.10, Tab. S.10-2</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>requisiti propri della norma (cabina, tempi, protezione dall'acqua) da verificare sul testo</t>
+          <t>alimentazione di sicurezza dell'ascensore antincendio: interruzione al massimo 15 s, autonomia oltre 30 min</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-72:2020</t>
+          <t>Codice S.10, Tab. S.10-2</t>
         </is>
       </c>
       <c r="F139" s="10" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="G139" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H139" s="10" t="inlineStr">
@@ -7205,22 +7205,22 @@
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
+          <t>UNI EN 81-72:2020</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>su comando della rivelazione incendio la cabina va al piano prestabilito e lascia uscire i passeggeri; con il Codice l'ascensore «dovrebbe» essere conforme alla UNI EN 81-73</t>
+          <t>requisiti propri della norma (cabina, tempi, protezione dall'acqua) da verificare sul testo</t>
         </is>
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
+          <t>UNI EN 81-72:2020</t>
         </is>
       </c>
       <c r="F140" s="10" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="G140" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H140" s="10" t="inlineStr">
@@ -7256,17 +7256,17 @@
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-73:2020</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>segnali e comportamento della manovra da verificare sul testo; la norma serve anche da base per migliorare gli esistenti</t>
+          <t>su comando della rivelazione incendio la cabina va al piano prestabilito e lascia uscire i passeggeri; con il Codice l'ascensore «dovrebbe» essere conforme alla UNI EN 81-73</t>
         </is>
       </c>
       <c r="E141" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-73:2020</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
         </is>
       </c>
       <c r="F141" s="10" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="G141" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H141" s="10" t="inlineStr">
@@ -7291,28 +7291,28 @@
       <c r="M141" s="11" t="n"/>
       <c r="N141" s="11" t="n"/>
     </row>
-    <row r="142" ht="69" customHeight="1">
+    <row r="142" ht="56" customHeight="1">
       <c r="A142" s="10" t="n">
         <v>140</v>
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-76:2025 (evacuazione delle persone con disabilità)</t>
+          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-76:2025</t>
+          <t>UNI EN 81-73:2020</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>evacuazione delle persone con disabilità con l'ascensore: requisiti aggiuntivi alla EN 81-20 (manovra, alimentazione) da verificare sul testo</t>
+          <t>segnali e comportamento della manovra da verificare sul testo; la norma serve anche da base per migliorare gli esistenti</t>
         </is>
       </c>
       <c r="E142" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-76:2025</t>
+          <t>UNI EN 81-73:2020</t>
         </is>
       </c>
       <c r="F142" s="10" t="inlineStr">
@@ -7337,28 +7337,28 @@
       <c r="M142" s="11" t="n"/>
       <c r="N142" s="11" t="n"/>
     </row>
-    <row r="143" ht="56" customHeight="1">
+    <row r="143" ht="69" customHeight="1">
       <c r="A143" s="10" t="n">
         <v>141</v>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-76:2025 (evacuazione delle persone con disabilità)</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 1</t>
+          <t>UNI EN 81-76:2025</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>con accelerazione di progetto a_d fino a 1 m/s² nessuna prescrizione specifica; a_d e la posizione dei rilevatori si concordano con il progettista dell'edificio</t>
+          <t>evacuazione delle persone con disabilità con l'ascensore: requisiti aggiuntivi alla EN 81-20 (manovra, alimentazione) da verificare sul testo</t>
         </is>
       </c>
       <c r="E143" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 1</t>
+          <t>UNI EN 81-76:2025</t>
         </is>
       </c>
       <c r="F143" s="10" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="G143" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H143" s="10" t="inlineStr">
@@ -7383,7 +7383,7 @@
       <c r="M143" s="11" t="n"/>
       <c r="N143" s="11" t="n"/>
     </row>
-    <row r="144" ht="95" customHeight="1">
+    <row r="144" ht="56" customHeight="1">
       <c r="A144" s="10" t="n">
         <v>142</v>
       </c>
@@ -7394,17 +7394,17 @@
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
+          <t>UNI EN 81-77:2022, 1</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>oltre 1 m/s²: massa della cabina nei calcoli (5.4.1), ritegni della cabina (5.4.2) e del contrappeso (5.5), protezione delle pulegge (5.6.1), tensioni e frecce delle guide (5.8.2, All. D), rilevazione e modo sismico (5.10.3, 5.10.4); soglie delle categorie dell'All. A da verificare sul testo</t>
+          <t>con accelerazione di progetto a_d fino a 1 m/s² nessuna prescrizione specifica; a_d e la posizione dei rilevatori si concordano con il progettista dell'edificio</t>
         </is>
       </c>
       <c r="E144" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
+          <t>UNI EN 81-77:2022, 1</t>
         </is>
       </c>
       <c r="F144" s="10" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="G144" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H144" s="10" t="inlineStr">
@@ -7429,7 +7429,7 @@
       <c r="M144" s="11" t="n"/>
       <c r="N144" s="11" t="n"/>
     </row>
-    <row r="145" ht="43" customHeight="1">
+    <row r="145" ht="95" customHeight="1">
       <c r="A145" s="10" t="n">
         <v>143</v>
       </c>
@@ -7440,17 +7440,17 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 0.3</t>
+          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>non si applica agli impianti installati prima della sua pubblicazione</t>
+          <t>oltre 1 m/s²: massa della cabina nei calcoli (5.4.1), ritegni della cabina (5.4.2) e del contrappeso (5.5), protezione delle pulegge (5.6.1), tensioni e frecce delle guide (5.8.2, All. D), rilevazione e modo sismico (5.10.3, 5.10.4); soglie delle categorie dell'All. A da verificare sul testo</t>
         </is>
       </c>
       <c r="E145" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 0.3</t>
+          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
         </is>
       </c>
       <c r="F145" s="10" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="G145" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H145" s="10" t="inlineStr">
@@ -7475,28 +7475,28 @@
       <c r="M145" s="11" t="n"/>
       <c r="N145" s="11" t="n"/>
     </row>
-    <row r="146" ht="69" customHeight="1">
+    <row r="146" ht="43" customHeight="1">
       <c r="A146" s="10" t="n">
         <v>144</v>
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-80:2019</t>
+          <t>UNI EN 81-77:2022, 0.3</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>analisi dei rischi dell'impianto esistente e piano di miglioramento per priorità, scelta volontaria del proprietario</t>
+          <t>non si applica agli impianti installati prima della sua pubblicazione</t>
         </is>
       </c>
       <c r="E146" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-80:2019</t>
+          <t>UNI EN 81-77:2022, 0.3</t>
         </is>
       </c>
       <c r="F146" s="10" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="G146" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H146" s="10" t="inlineStr">
@@ -7521,28 +7521,28 @@
       <c r="M146" s="11" t="n"/>
       <c r="N146" s="11" t="n"/>
     </row>
-    <row r="147" ht="56" customHeight="1">
+    <row r="147" ht="69" customHeight="1">
       <c r="A147" s="10" t="n">
         <v>145</v>
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-82:2026 (accessibilità degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-82:2026</t>
+          <t>UNI EN 81-80:2019</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>miglioramento dell'accessibilità di un impianto esistente secondo i requisiti della EN 81-70</t>
+          <t>analisi dei rischi dell'impianto esistente e piano di miglioramento per priorità, scelta volontaria del proprietario</t>
         </is>
       </c>
       <c r="E147" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-82:2026</t>
+          <t>UNI EN 81-80:2019</t>
         </is>
       </c>
       <c r="F147" s="10" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="G147" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H147" s="10" t="inlineStr">
@@ -7573,22 +7573,22 @@
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-83:2026 (antivandalo degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-82:2026 (accessibilità degli esistenti)</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-83:2026</t>
+          <t>UNI EN 81-82:2026</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>miglioramento della resistenza agli atti vandalici di un impianto esistente secondo la EN 81-71:2022 (voce 1.2 della Tab. A.1 della EN 81-80)</t>
+          <t>miglioramento dell'accessibilità di un impianto esistente secondo i requisiti della EN 81-70</t>
         </is>
       </c>
       <c r="E148" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-83:2026</t>
+          <t>UNI EN 81-82:2026</t>
         </is>
       </c>
       <c r="F148" s="10" t="inlineStr">
@@ -7619,22 +7619,22 @@
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-83:2026 (antivandalo degli esistenti)</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-83:2026</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>piattaforma di distribuzione davanti alla porta di cabina: 1,50 × 1,50 m negli edifici nuovi, 1,40 × 1,40 m nell'adeguamento (fuori dal vano: in sito)</t>
+          <t>miglioramento della resistenza agli atti vandalici di un impianto esistente secondo la EN 81-71:2022 (voce 1.2 della Tab. A.1 della EN 81-80)</t>
         </is>
       </c>
       <c r="E149" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-83:2026</t>
         </is>
       </c>
       <c r="F149" s="10" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="H149" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I149" s="11" t="n"/>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>porte di cabina e di piano a scorrimento automatico (nell'adeguamento la porta di piano può essere a battente se ad apertura automatica); porte aperte almeno 8 s, chiusura in almeno 4 s</t>
+          <t>piattaforma di distribuzione davanti alla porta di cabina: 1,50 × 1,50 m negli edifici nuovi, 1,40 × 1,40 m nell'adeguamento (fuori dal vano: in sito)</t>
         </is>
       </c>
       <c r="E150" s="10" t="inlineStr">
@@ -7705,7 +7705,7 @@
       <c r="M150" s="11" t="n"/>
       <c r="N150" s="11" t="n"/>
     </row>
-    <row r="151" ht="43" customHeight="1">
+    <row r="151" ht="56" customHeight="1">
       <c r="A151" s="10" t="n">
         <v>149</v>
       </c>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>arresto ai piani con autolivellamento entro ± 2 cm; sosta ai piani con le porte chiuse</t>
+          <t>porte di cabina e di piano a scorrimento automatico (nell'adeguamento la porta di piano può essere a battente se ad apertura automatica); porte aperte almeno 8 s, chiusura in almeno 4 s</t>
         </is>
       </c>
       <c r="E151" s="10" t="inlineStr">
@@ -7751,7 +7751,7 @@
       <c r="M151" s="11" t="n"/>
       <c r="N151" s="11" t="n"/>
     </row>
-    <row r="152" ht="56" customHeight="1">
+    <row r="152" ht="43" customHeight="1">
       <c r="A152" s="10" t="n">
         <v>150</v>
       </c>
@@ -7762,17 +7762,17 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>pulsanti di cabina e di piano: il più alto tra 1,10 e 1,40 m, misurato all'asse del comando; bottoniera di cabina su una parete laterale ad almeno 0,35 m dalla porta</t>
+          <t>arresto ai piani con autolivellamento entro ± 2 cm; sosta ai piani con le porte chiuse</t>
         </is>
       </c>
       <c r="E152" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F152" s="10" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="G152" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H152" s="10" t="inlineStr">
@@ -7797,7 +7797,7 @@
       <c r="M152" s="11" t="n"/>
       <c r="N152" s="11" t="n"/>
     </row>
-    <row r="153" ht="95" customHeight="1">
+    <row r="153" ht="56" customHeight="1">
       <c r="A153" s="10" t="n">
         <v>151</v>
       </c>
@@ -7808,17 +7808,17 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
+          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>citofono in cabina tra 1,10 e 1,30 m; luce d'emergenza con almeno 3 h di autonomia; campanello d'allarme e segnale luminoso di allarme ricevuto; arresto e inversione della chiusura; segnale acustico d'arrivo; numeri in rilievo e Braille, targa Braille di piano; sedile ribaltabile dove possibile</t>
+          <t>pulsanti di cabina e di piano: il più alto tra 1,10 e 1,40 m, misurato all'asse del comando; bottoniera di cabina su una parete laterale ad almeno 0,35 m dalla porta</t>
         </is>
       </c>
       <c r="E153" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
+          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
         </is>
       </c>
       <c r="F153" s="10" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="G153" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H153" s="10" t="inlineStr">
@@ -7843,7 +7843,7 @@
       <c r="M153" s="11" t="n"/>
       <c r="N153" s="11" t="n"/>
     </row>
-    <row r="154" ht="56" customHeight="1">
+    <row r="154" ht="95" customHeight="1">
       <c r="A154" s="10" t="n">
         <v>152</v>
       </c>
@@ -7854,17 +7854,17 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
+          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>ascensore obbligatorio oltre il terzo livello (contati interrati e porticati); negli immobili con più di tre livelli fuori terra un ascensore per ogni scala principale</t>
+          <t>citofono in cabina tra 1,10 e 1,30 m; luce d'emergenza con almeno 3 h di autonomia; campanello d'allarme e segnale luminoso di allarme ricevuto; arresto e inversione della chiusura; segnale acustico d'arrivo; numeri in rilievo e Braille, targa Braille di piano; sedile ribaltabile dove possibile</t>
         </is>
       </c>
       <c r="E154" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
+          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
         </is>
       </c>
       <c r="F154" s="10" t="inlineStr">
@@ -7900,17 +7900,17 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>nelle ristrutturazioni deroghe per impossibilità tecnica strutturale o impiantistica (privati: concesse dal Sindaco); edifici vincolati: deroga se le opere pregiudicano il bene</t>
+          <t>ascensore obbligatorio oltre il terzo livello (contati interrati e porticati); negli immobili con più di tre livelli fuori terra un ascensore per ogni scala principale</t>
         </is>
       </c>
       <c r="E155" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
         </is>
       </c>
       <c r="F155" s="10" t="inlineStr">
@@ -7935,28 +7935,28 @@
       <c r="M155" s="11" t="n"/>
       <c r="N155" s="11" t="n"/>
     </row>
-    <row r="156" ht="69" customHeight="1">
+    <row r="156" ht="56" customHeight="1">
       <c r="A156" s="10" t="n">
         <v>154</v>
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>il progettista applica il DM 15/09/2005 oppure la RTV V.3 del Codice: dove si usa il Codice il DM 2005 non si applica</t>
+          <t>nelle ristrutturazioni deroghe per impossibilità tecnica strutturale o impiantistica (privati: concesse dal Sindaco); edifici vincolati: deroga se le opere pregiudicano il bene</t>
         </is>
       </c>
       <c r="E156" s="10" t="inlineStr">
         <is>
-          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
         </is>
       </c>
       <c r="F156" s="10" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="H156" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I156" s="11" t="n"/>
@@ -7981,7 +7981,7 @@
       <c r="M156" s="11" t="n"/>
       <c r="N156" s="11" t="n"/>
     </row>
-    <row r="157" ht="95" customHeight="1">
+    <row r="157" ht="69" customHeight="1">
       <c r="A157" s="10" t="n">
         <v>155</v>
       </c>
@@ -7992,17 +7992,17 @@
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, art. 1 c.2</t>
+          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>sugli impianti esistenti vale per le modifiche sostanziali: nuovo impianto; più fermate o altro azionamento; pareti del vano, porte di piano, locale macchine o pulegge sostituiti con materiali, modelli, dimensioni o criteri diversi; solai o scale rifatti che coinvolgono l'impianto; sopraelevazione; cambio di destinazione d'uso</t>
+          <t>il progettista applica il DM 15/09/2005 oppure la RTV V.3 del Codice: dove si usa il Codice il DM 2005 non si applica</t>
         </is>
       </c>
       <c r="E157" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, art. 1 c.2</t>
+          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
         </is>
       </c>
       <c r="F157" s="10" t="inlineStr">
@@ -8027,7 +8027,7 @@
       <c r="M157" s="11" t="n"/>
       <c r="N157" s="11" t="n"/>
     </row>
-    <row r="158" ht="69" customHeight="1">
+    <row r="158" ht="95" customHeight="1">
       <c r="A158" s="10" t="n">
         <v>156</v>
       </c>
@@ -8038,17 +8038,17 @@
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+          <t>DM 15/09/2005, art. 1 c.2</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>tipo di vano: aperto, protetto o a prova di fumo (Codice: classi da SA a SE)</t>
+          <t>sugli impianti esistenti vale per le modifiche sostanziali: nuovo impianto; più fermate o altro azionamento; pareti del vano, porte di piano, locale macchine o pulegge sostituiti con materiali, modelli, dimensioni o criteri diversi; solai o scale rifatti che coinvolgono l'impianto; sopraelevazione; cambio di destinazione d'uso</t>
         </is>
       </c>
       <c r="E158" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+          <t>DM 15/09/2005, art. 1 c.2</t>
         </is>
       </c>
       <c r="F158" s="10" t="inlineStr">
@@ -8084,17 +8084,17 @@
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 2</t>
+          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>pareti del vano, locale macchine e pulegge, setti e arcata non combustibili; pareti, pavimento e tetto della cabina in classe di reazione al fuoco non oltre 1</t>
+          <t>tipo di vano: aperto, protetto o a prova di fumo (Codice: classi da SA a SE)</t>
         </is>
       </c>
       <c r="E159" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 2</t>
+          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
         </is>
       </c>
       <c r="F159" s="10" t="inlineStr">
@@ -8119,7 +8119,7 @@
       <c r="M159" s="11" t="n"/>
       <c r="N159" s="11" t="n"/>
     </row>
-    <row r="160" ht="82" customHeight="1">
+    <row r="160" ht="69" customHeight="1">
       <c r="A160" s="10" t="n">
         <v>158</v>
       </c>
@@ -8130,17 +8130,17 @@
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 5</t>
+          <t>DM 15/09/2005, punto 2</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>aerazione permanente in alto verso spazi scoperti di almeno il 3 % della pianta (vano almeno 0,20 m², locale macchine o pulegge almeno 0,05 m²), con una protezione che non lascia passare una sfera oltre 15 mm; non serve se il vano è aperto su spazi scoperti</t>
+          <t>pareti del vano, locale macchine e pulegge, setti e arcata non combustibili; pareti, pavimento e tetto della cabina in classe di reazione al fuoco non oltre 1</t>
         </is>
       </c>
       <c r="E160" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 5</t>
+          <t>DM 15/09/2005, punto 2</t>
         </is>
       </c>
       <c r="F160" s="10" t="inlineStr">
@@ -8165,7 +8165,7 @@
       <c r="M160" s="11" t="n"/>
       <c r="N160" s="11" t="n"/>
     </row>
-    <row r="161" ht="69" customHeight="1">
+    <row r="161" ht="82" customHeight="1">
       <c r="A161" s="10" t="n">
         <v>159</v>
       </c>
@@ -8176,17 +8176,17 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+          <t>DM 15/09/2005, punto 5</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>estintore 21A89BC vicino all'accesso al macchinario; richiamo della cabina al piano prestabilito su comando della rivelazione quando la compartimentazione lo richiede</t>
+          <t>aerazione permanente in alto verso spazi scoperti di almeno il 3 % della pianta (vano almeno 0,20 m², locale macchine o pulegge almeno 0,05 m²), con una protezione che non lascia passare una sfera oltre 15 mm; non serve se il vano è aperto su spazi scoperti</t>
         </is>
       </c>
       <c r="E161" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+          <t>DM 15/09/2005, punto 5</t>
         </is>
       </c>
       <c r="F161" s="10" t="inlineStr">
@@ -8222,17 +8222,17 @@
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>Codice S.9, Tab. S.9-3</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>piani tra 32 e 54 m: almeno un ascensore antincendio; oltre 54 m: almeno uno di soccorso; interrati tra −10 e −15 m: antincendio; sotto −15 m: soccorso</t>
+          <t>estintore 21A89BC vicino all'accesso al macchinario; richiamo della cabina al piano prestabilito su comando della rivelazione quando la compartimentazione lo richiede</t>
         </is>
       </c>
       <c r="E162" s="10" t="inlineStr">
         <is>
-          <t>Codice S.9, Tab. S.9-3</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
         </is>
       </c>
       <c r="F162" s="10" t="inlineStr">
@@ -8257,28 +8257,28 @@
       <c r="M162" s="11" t="n"/>
       <c r="N162" s="11" t="n"/>
     </row>
-    <row r="163" ht="43" customHeight="1">
+    <row r="163" ht="69" customHeight="1">
       <c r="A163" s="10" t="n">
         <v>161</v>
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §3.1.4</t>
+          <t>Codice S.9, Tab. S.9-3</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>carichi del macchinario valutati caso per caso sui massimi prevedibili e riportati nel progetto e nel collaudo statico</t>
+          <t>piani tra 32 e 54 m: almeno un ascensore antincendio; oltre 54 m: almeno uno di soccorso; interrati tra −10 e −15 m: antincendio; sotto −15 m: soccorso</t>
         </is>
       </c>
       <c r="E163" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §3.1.4</t>
+          <t>Codice S.9, Tab. S.9-3</t>
         </is>
       </c>
       <c r="F163" s="10" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="H163" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I163" s="11" t="n"/>
@@ -8314,17 +8314,17 @@
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §8.4.1</t>
+          <t>NTC 2018, §3.1.4</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>su un edificio esistente l'intervento è locale: verifica limitata alle parti interessate, senza ridurre la sicurezza preesistente</t>
+          <t>carichi del macchinario valutati caso per caso sui massimi prevedibili e riportati nel progetto e nel collaudo statico</t>
         </is>
       </c>
       <c r="E164" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §8.4.1</t>
+          <t>NTC 2018, §3.1.4</t>
         </is>
       </c>
       <c r="F164" s="10" t="inlineStr">
@@ -8360,17 +8360,17 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §11.4.1</t>
+          <t>NTC 2018, §8.4.1</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>ancoranti per uso strutturale qualificati; con azioni sismiche categoria C2 per tutte le classi d'uso</t>
+          <t>su un edificio esistente l'intervento è locale: verifica limitata alle parti interessate, senza ridurre la sicurezza preesistente</t>
         </is>
       </c>
       <c r="E165" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §11.4.1</t>
+          <t>NTC 2018, §8.4.1</t>
         </is>
       </c>
       <c r="F165" s="10" t="inlineStr">
@@ -8395,7 +8395,7 @@
       <c r="M165" s="11" t="n"/>
       <c r="N165" s="11" t="n"/>
     </row>
-    <row r="166" ht="108" customHeight="1">
+    <row r="166" ht="43" customHeight="1">
       <c r="A166" s="10" t="n">
         <v>164</v>
       </c>
@@ -8406,17 +8406,17 @@
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §7.2.3–7.2.4</t>
+          <t>NTC 2018, §11.4.1</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>forza sismica sull'elemento non strutturale Fa = Sa·Wa/qa; nessun vincolo ad attrito; studio specifico oltre il 30 % del carico permanente del solaio o il 10 % di quello dell'intera struttura; progetto antisismico dell'impianto del produttore, dei collegamenti dell'installatore, dei solai e delle pareti d'ancoraggio del progettista strutturale</t>
+          <t>ancoranti per uso strutturale qualificati; con azioni sismiche categoria C2 per tutte le classi d'uso</t>
         </is>
       </c>
       <c r="E166" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §7.2.3–7.2.4</t>
+          <t>NTC 2018, §11.4.1</t>
         </is>
       </c>
       <c r="F166" s="10" t="inlineStr">
@@ -8441,7 +8441,7 @@
       <c r="M166" s="11" t="n"/>
       <c r="N166" s="11" t="n"/>
     </row>
-    <row r="167" ht="43" customHeight="1">
+    <row r="167" ht="108" customHeight="1">
       <c r="A167" s="10" t="n">
         <v>165</v>
       </c>
@@ -8452,17 +8452,17 @@
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+          <t>NTC 2018, §7.2.3–7.2.4</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>impianti: stabilità allo SLV per tutte le classi d'uso; nelle classi III e IV anche funzionamento allo SLO</t>
+          <t>forza sismica sull'elemento non strutturale Fa = Sa·Wa/qa; nessun vincolo ad attrito; studio specifico oltre il 30 % del carico permanente del solaio o il 10 % di quello dell'intera struttura; progetto antisismico dell'impianto del produttore, dei collegamenti dell'installatore, dei solai e delle pareti d'ancoraggio del progettista strutturale</t>
         </is>
       </c>
       <c r="E167" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+          <t>NTC 2018, §7.2.3–7.2.4</t>
         </is>
       </c>
       <c r="F167" s="10" t="inlineStr">
@@ -8487,10 +8487,56 @@
       <c r="M167" s="11" t="n"/>
       <c r="N167" s="11" t="n"/>
     </row>
+    <row r="168" ht="43" customHeight="1">
+      <c r="A168" s="10" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C168" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+        </is>
+      </c>
+      <c r="D168" s="10" t="inlineStr">
+        <is>
+          <t>impianti: stabilità allo SLV per tutte le classi d'uso; nelle classi III e IV anche funzionamento allo SLO</t>
+        </is>
+      </c>
+      <c r="E168" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+        </is>
+      </c>
+      <c r="F168" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G168" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H168" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I168" s="11" t="n"/>
+      <c r="J168" s="11" t="n"/>
+      <c r="K168" s="11" t="n"/>
+      <c r="L168" s="11" t="n"/>
+      <c r="M168" s="11" t="n"/>
+      <c r="N168" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N167"/>
+  <autoFilter ref="A1:N168"/>
   <dataValidations count="1">
-    <dataValidation sqref="I3:I167" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
+    <dataValidation sqref="I3:I168" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
       <formula1>"conforme,diverso,non applicabile"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8533,7 +8579,7 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$167,"da verificare")</f>
+        <f>COUNTIF(Voci!$G$3:$G$168,"da verificare")</f>
         <v/>
       </c>
     </row>
@@ -8544,7 +8590,7 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$167,"confermato")</f>
+        <f>COUNTIF(Voci!$G$3:$G$168,"confermato")</f>
         <v/>
       </c>
     </row>
@@ -8555,7 +8601,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$167,"scelta del software")</f>
+        <f>COUNTIF(Voci!$G$3:$G$168,"scelta del software")</f>
         <v/>
       </c>
     </row>
@@ -8566,7 +8612,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$167,"stima")</f>
+        <f>COUNTIF(Voci!$G$3:$G$168,"stima")</f>
         <v/>
       </c>
     </row>
@@ -8577,7 +8623,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$167,"derivazione")</f>
+        <f>COUNTIF(Voci!$G$3:$G$168,"derivazione")</f>
         <v/>
       </c>
     </row>
@@ -8588,7 +8634,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$167,"prassi di cantiere")</f>
+        <f>COUNTIF(Voci!$G$3:$G$168,"prassi di cantiere")</f>
         <v/>
       </c>
     </row>
@@ -8599,7 +8645,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTA(Voci!$A$3:$A$167)</f>
+        <f>COUNTA(Voci!$A$3:$A$168)</f>
         <v/>
       </c>
     </row>
@@ -8617,7 +8663,7 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$167,"conforme")</f>
+        <f>COUNTIF(Voci!$I$3:$I$168,"conforme")</f>
         <v/>
       </c>
     </row>
@@ -8628,7 +8674,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$167,"diverso")</f>
+        <f>COUNTIF(Voci!$I$3:$I$168,"diverso")</f>
         <v/>
       </c>
     </row>
@@ -8639,7 +8685,7 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$167,"non applicabile")</f>
+        <f>COUNTIF(Voci!$I$3:$I$168,"non applicabile")</f>
         <v/>
       </c>
     </row>
@@ -8650,14 +8696,14 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>COUNTBLANK(Voci!$I$3:$I$167)</f>
+        <f>COUNTBLANK(Voci!$I$3:$I$168)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Conteggi sulle righe 3–167 del foglio «Voci» (la riga 2 è l'esempio).</t>
+          <t>Conteggi sulle righe 3–168 del foglio «Voci» (la riga 2 è l'esempio).</t>
         </is>
       </c>
     </row>

--- a/liftpilot/docs/lista-verifica-normativa.xlsx
+++ b/liftpilot/docs/lista-verifica-normativa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Riepilogo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$193</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Voci'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N168"/>
+  <dimension ref="A1:N193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,17 +913,17 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>T1/T2 ≤ e^(f·α) al caricamento e in frenatura di emergenza; T1/T2 ≥ e^(f·α) con cabina bloccata</t>
+          <t>T1/T2 ≤ e^(f·α) al caricamento e in frenatura di emergenza; T1/T2 ≥ e^(f·α) con contrappeso o cabina bloccati (cabina vuota nella posizione più alta e in quella più bassa)</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11</t>
+          <t>UNI EN 81-50:2020, 5.11.2.1 e 5.11.2.2.3</t>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>Mellor; Elevator World; Scientific Reports 2025</t>
+          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 39–40</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2 (sottoclausola da individuare)</t>
+          <t>UNI EN 81-50:2020, 5.11.2.3.2</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>fonti secondarie concordi</t>
+          <t>BS EN 81-50:2020, estratto pubblico del testo, p. 50</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
@@ -1010,17 +1010,17 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2</t>
+          <t>UNI EN 81-50:2020, 5.11.2.3.2</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>fonti secondarie concordi</t>
+          <t>BS EN 81-50:2020, estratto pubblico del testo, p. 50 (v_f: velocità delle funi alla velocità nominale della cabina)</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Coefficiente di attrito, cabina bloccata</t>
+          <t>Coefficiente di attrito, contrappeso o cabina bloccati</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2</t>
+          <t>UNI EN 81-50:2020, 5.11.2.3.2</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>fonti secondarie concordi</t>
+          <t>BS EN 81-50:2020, estratto pubblico del testo, p. 50</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -1081,7 +1081,7 @@
       <c r="M6" s="11" t="n"/>
       <c r="N6" s="11" t="n"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="95" customHeight="1">
       <c r="A7" s="10" t="n">
         <v>5</v>
       </c>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Carico della verifica di caricamento — Il campione cita anche il peso dei dispositivi di movimentazione, dove usati: non modellato.</t>
+          <t>Carico della verifica di caricamento — La norma aggiunge il peso dei dispositivi di movimentazione, dove usati negli ascensori per merci e persone: non modellato. Le due posizioni della cabina sono quelle più sfavorevoli che il software verifica.</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -1102,17 +1102,17 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.3.2</t>
+          <t>UNI EN 81-50:2020, 5.11.3</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>campione BSI di EN 81-50:2020 (p. 50)</t>
+          <t>BS EN 81-50:2020, estratto pubblico del testo, p. 52 (al caricamento e con la cabina bloccata a = 0)</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>0,5 m/s²; 0,8 m/s² con ammortizzatori a corsa ridotta</t>
+          <t>almeno 0,5 m/s²</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>fonti secondarie; 0,8 m/s² da EN 81-1 secondo una fonte secondaria</t>
+          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 40</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -1173,7 +1173,7 @@
       <c r="M8" s="11" t="n"/>
       <c r="N8" s="11" t="n"/>
     </row>
-    <row r="9" ht="43" customHeight="1">
+    <row r="9" ht="160" customHeight="1">
       <c r="A9" s="10" t="n">
         <v>7</v>
       </c>
@@ -1184,22 +1184,22 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Combinazioni della frenatura di emergenza</t>
+          <t>Decelerazione della verifica di frenatura con ammortizzatori a corsa ridotta — La UNI EN 81-50:2020 non dà un numero: con ammortizzatori a corsa ridotta la decelerazione è la minima che porta cabina e contrappeso alla velocità di progetto degli ammortizzatori, mai sotto 0,5 m/s². Il software tiene 0,8 m/s², il valore della UNI EN 81-1: l'ingegnere lo sostituisce con quello calcolato dai dati degli ammortizzatori.</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>cabina vuota e con portata × in discesa e in salita × in basso e in alto; conta la peggiore per verso</t>
+          <t>0,8 m/s²</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.2.2</t>
+          <t>UNI EN 81-1:2008, M.2.1.2; UNI EN 81-50:2020, 5.11.2.2.2</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>derivazione (copertura completa dei casi)</t>
+          <t>UNI EN 81-1:2008, testo della norma fornito dal cliente, letto il 2026-10-06, p. 167; UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 40</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -1219,7 +1219,7 @@
       <c r="M9" s="11" t="n"/>
       <c r="N9" s="11" t="n"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="43" customHeight="1">
       <c r="A10" s="10" t="n">
         <v>8</v>
       </c>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Aderenza alla decelerazione reale del freno — Se la lettura è confermata diventa un esito; nell'esempio B del capitolo 7 cambia 1,005 in 4,17.</t>
+          <t>Combinazioni della frenatura di emergenza</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Seconda verifica con la decelerazione data dal freno (tutti i gruppi, mai sotto il minimo); oggi solo avviso</t>
+          <t>cabina vuota e con portata × in discesa e in salita × in basso e in alto; conta la peggiore per verso</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.2.2 (lettura da decidere sul testo)</t>
+          <t>UNI EN 81-50:2020, 5.11.2.2.2</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>fonti secondarie: "ogni parte con la sua decelerazione"</t>
+          <t>derivazione (copertura completa dei casi)</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>aderenza alla decelerazione reale (avviso)</t>
+          <t>aderenza in frenatura, in discesa; aderenza in frenatura, in salita</t>
         </is>
       </c>
       <c r="I10" s="11" t="n"/>
@@ -1265,7 +1265,7 @@
       <c r="M10" s="11" t="n"/>
       <c r="N10" s="11" t="n"/>
     </row>
-    <row r="11" ht="69" customHeight="1">
+    <row r="11" ht="121" customHeight="1">
       <c r="A11" s="10" t="n">
         <v>9</v>
       </c>
@@ -1276,22 +1276,22 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Soglia di attenzione sull'utilizzo dell'aderenza</t>
+          <t>Aderenza alla decelerazione reale del freno — La norma vuole ogni massa in moto con la sua accelerazione e una decelerazione di calcolo mai sotto 0,5 m/s²; non dice con quanti gruppi del freno. Se contarla come esito lo decide l'ingegnere: nell'esempio B del capitolo 7 l'utilizzo passa da 1,005 a 4,17.</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>utilizzo &gt; 0,97 → «Attenzione»</t>
+          <t>Seconda verifica con la decelerazione data dal freno (tutti i gruppi, mai sotto il minimo); oggi solo avviso</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.2.2.2</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (margine per incertezza su masse e bilanciamento)</t>
+          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 40</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>aderenza al caricamento; aderenza in frenatura, in discesa; aderenza in frenatura, in salita; aderenza alla decelerazione reale (avviso)</t>
+          <t>aderenza alla decelerazione reale (avviso)</t>
         </is>
       </c>
       <c r="I11" s="11" t="n"/>
@@ -1311,43 +1311,43 @@
       <c r="M11" s="11" t="n"/>
       <c r="N11" s="11" t="n"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="69" customHeight="1">
       <c r="A12" s="10" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Gole</t>
+          <t>Aderenza</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Fattore di gola, semicircolare con o senza sottosquadro</t>
+          <t>Soglia di attenzione sull'utilizzo dell'aderenza</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>f = μ·4·(cos(γ/2) − sin(β/2)) / (π − β − γ − sin β + sin γ); senza sottosquadro β = 0</t>
+          <t>utilizzo &gt; 0,97 → «Attenzione»</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.3 (ex EN 81-1 Allegato M)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>fonti secondarie; controllo di coerenza con Mellor</t>
+          <t>scelta del software (margine per incertezza su masse e bilanciamento)</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>aderenza al caricamento; aderenza in frenatura, in discesa; aderenza in frenatura, in salita; cabina bloccata</t>
+          <t>aderenza al caricamento; aderenza in frenatura, in discesa; aderenza in frenatura, in salita; aderenza alla decelerazione reale (avviso)</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -1368,27 +1368,27 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Fattore di gola a V</t>
+          <t>Fattore di gola, semicircolare con o senza sottosquadro</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>temprata (e ogni gola a V con cabina bloccata): f = μ / sin(γ/2); non temprata: f = μ·4·(1 − sin(β/2)) / (π − β − sin β)</t>
+          <t>f = μ·4·(cos(γ/2) − sin(β/2)) / (π − β − γ − sin β + sin γ); senza sottosquadro β = 0</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.3</t>
+          <t>UNI EN 81-50:2020, 5.11.2.3.1.1</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>fonti secondarie; controllo di coerenza con Mellor</t>
+          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 40–41</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
@@ -1403,7 +1403,7 @@
       <c r="M13" s="11" t="n"/>
       <c r="N13" s="11" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" ht="69" customHeight="1">
       <c r="A14" s="10" t="n">
         <v>12</v>
       </c>
@@ -1414,32 +1414,32 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Limite del sottosquadro</t>
+          <t>Fattore di gola a V — la norma dà f = μ / sin(γ/2) per il contrappeso bloccato; il software la usa anche per la cabina bloccata nella posizione più bassa (5.11.2.2.3)</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>β ≤ 106° (oltre: KO)</t>
+          <t>non temprata, al caricamento e in frenatura: f = μ·4·(1 − sin(β/2)) / (π − β − sin β); temprata, e ogni gola a V con il contrappeso o la cabina bloccati: f = μ / sin(γ/2)</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.3 (valore di EN 81-1)</t>
+          <t>UNI EN 81-50:2020, 5.11.2.3.1.2</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>fonte secondaria su EN 81-1</t>
+          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 41</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>geometria della gola</t>
+          <t>aderenza al caricamento; aderenza in frenatura, in discesa; aderenza in frenatura, in salita; cabina bloccata</t>
         </is>
       </c>
       <c r="I14" s="11" t="n"/>
@@ -1449,7 +1449,7 @@
       <c r="M14" s="11" t="n"/>
       <c r="N14" s="11" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1">
+    <row r="15" ht="56" customHeight="1">
       <c r="A15" s="10" t="n">
         <v>13</v>
       </c>
@@ -1460,27 +1460,27 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Sottosquadro raccomandato</t>
+          <t>Limite del sottosquadro — fino alla versione 1.1.0 del motore il limite era 106°, il valore raccomandato della UNI EN 81-1 (M.2.2.1)</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>β ≤ 90° (oltre: «Attenzione»)</t>
+          <t>β ≤ 105° (1,83 rad; oltre: KO)</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.2.3.1.1 e 5.11.2.3.1.2</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Montanari, documento tecnico del costruttore</t>
+          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 40–41</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -1495,7 +1495,7 @@
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="11" t="n"/>
     </row>
-    <row r="16" ht="43" customHeight="1">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="10" t="n">
         <v>14</v>
       </c>
@@ -1506,22 +1506,22 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Angolo minimo della gola a V</t>
+          <t>Sottosquadro raccomandato</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>γ ≥ 35° (sotto: KO)</t>
+          <t>β ≤ 90° (oltre: «Attenzione»)</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12 (tabella di N_equiv(t))</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>la tabella usata parte da 35°; Montanari: γ ≥ 32°, consigliato 35–40°</t>
+          <t>Montanari, documento tecnico del costruttore</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -1541,33 +1541,33 @@
       <c r="M16" s="11" t="n"/>
       <c r="N16" s="11" t="n"/>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="56" customHeight="1">
       <c r="A17" s="10" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Funi</t>
+          <t>Gole</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Rapporto D/d della puleggia di trazione</t>
+          <t>Angolo minimo della gola a V</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>D/d ≥ 40</t>
+          <t>γ ≥ 35° (sotto: KO)</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.5.2.1</t>
+          <t>UNI EN 81-50:2020, 5.11.2.3.1.2</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>ELA 2026 e fonti concordi</t>
+          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 41; Montanari consiglia 35–40°</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>D/d della puleggia</t>
+          <t>geometria della gola</t>
         </is>
       </c>
       <c r="I17" s="11" t="n"/>
@@ -1587,43 +1587,43 @@
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="11" t="n"/>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="43" customHeight="1">
       <c r="A18" s="10" t="n">
         <v>16</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Funi</t>
+          <t>Gole</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Rapporto D/d delle pulegge di rinvio</t>
+          <t>Angolo minimo della gola semicircolare</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Dp/d ≥ 40</t>
+          <t>γ ≥ 25° (0,44 rad; sotto: «Attenzione»: la norma lo raccomanda, non lo impone)</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.5.2.1</t>
+          <t>UNI EN 81-50:2020, 5.11.2.3.1.1</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>fonti secondarie</t>
+          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 40–41</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Dp/d dei rinvii</t>
+          <t>geometria della gola</t>
         </is>
       </c>
       <c r="I18" s="11" t="n"/>
@@ -1644,22 +1644,22 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Numero minimo di funi</t>
+          <t>Rapporto D/d della puleggia di trazione</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>almeno 2 funi indipendenti, ciascuna con il suo attacco</t>
+          <t>D/d ≥ 40</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. I 1.3 (Direttiva 2014/33/UE, All. I); UNI EN 81-20:2020, 5.5</t>
+          <t>UNI EN 81-20:2020, 5.5.2.1</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 consolidato (Normattiva), letto il 2026-10-02 (ricerca, cap. 16), All. I 1.3</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 74</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>numero e diametro delle funi</t>
+          <t>D/d della puleggia</t>
         </is>
       </c>
       <c r="I19" s="11" t="n"/>
@@ -1679,7 +1679,7 @@
       <c r="M19" s="11" t="n"/>
       <c r="N19" s="11" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="82" customHeight="1">
       <c r="A20" s="10" t="n">
         <v>18</v>
       </c>
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Diametro nominale minimo</t>
+          <t>Rapporto D/d delle pulegge di rinvio</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>d ≥ 8 mm (salvo approvazione di un organismo notificato)</t>
+          <t>Dp/d ≥ 40</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.5</t>
+          <t>UNI EN 81-20:2020, 5.5.2.1; UNI 10411-1:2024, 14.3</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>fonti secondarie</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 74; UNI 10411-1:2024, testo della norma fornito dal cliente, letto il 2026-10-06, p. 14</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>numero e diametro delle funi</t>
+          <t>Dp/d dei rinvii</t>
         </is>
       </c>
       <c r="I20" s="11" t="n"/>
@@ -1725,7 +1725,7 @@
       <c r="M20" s="11" t="n"/>
       <c r="N20" s="11" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1">
+    <row r="21" ht="95" customHeight="1">
       <c r="A21" s="10" t="n">
         <v>19</v>
       </c>
@@ -1736,32 +1736,32 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Coefficiente di sicurezza minimo</t>
+          <t>Numero minimo di funi</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>12 con tre o più funi; 16 con due funi</t>
+          <t>almeno 2 funi indipendenti, ciascuna con il suo attacco</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.5</t>
+          <t>DPR 162/1999, All. I 1.3 (Direttiva 2014/33/UE, All. I); UNI EN 81-20:2020, 5.5</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>fonti secondarie</t>
+          <t>DPR 162/1999 consolidato (Normattiva), letto il 2026-10-02, e Direttiva 2014/33/UE nel testo ufficiale italiano (EUR-Lex, fornito dal cliente), letto il 2026-10-04 (ricerca, cap. 16): All. I 1.3</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>coefficiente di sicurezza delle funi</t>
+          <t>numero e diametro delle funi</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
@@ -1782,22 +1782,22 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Coefficiente di sicurezza richiesto S_f</t>
+          <t>Diametro nominale minimo</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>S_f = 10^[2,6834 − log10(695,85·10^6·N_equiv/(D/d)^8,567) / log10(77,09·(D/d)^−2,894)]</t>
+          <t>d ≥ 8 mm</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12 (ex EN 81-1 Allegato N)</t>
+          <t>UNI EN 81-20:2020, 5.5.1.2 a)</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>riprodotto su due casi pubblicati (liftdesign.it S_f 16,69; Mellor)</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 74</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>coefficiente di sicurezza delle funi</t>
+          <t>numero e diametro delle funi</t>
         </is>
       </c>
       <c r="I22" s="11" t="n"/>
@@ -1817,7 +1817,7 @@
       <c r="M22" s="11" t="n"/>
       <c r="N22" s="11" t="n"/>
     </row>
-    <row r="23" ht="69" customHeight="1">
+    <row r="23" ht="108" customHeight="1">
       <c r="A23" s="10" t="n">
         <v>21</v>
       </c>
@@ -1828,27 +1828,27 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>N_equiv delle pulegge — Da confermare anche quando una flessione conta come inversa (distanza tra le pulegge): oggi la classifica il progettista.</t>
+          <t>Coefficiente di sicurezza minimo — Con la trazione vale anche il valore calcolato secondo la UNI EN 81-50:2020, 5.12 (il maggiore dei due). Con la UNI 10411-1:2024 (14.1) 12 e 16 possono sostituire quel calcolo solo con la verifica della pressione nelle gole (appendice D.2).</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>N_equiv(p) = K_p·(N_ps + 4·N_pr), K_p = (D/Dp)^4</t>
+          <t>12 con tre o più funi; 16 con due funi</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12</t>
+          <t>UNI EN 81-20:2020, 5.5.2.2 a)–b); UNI 10411-1:2024, 14.1 c)–d)</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>fonti secondarie</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 74–75; UNI 10411-1:2024, testo della norma fornito dal cliente, letto il 2026-10-06, p. 13</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -1863,7 +1863,7 @@
       <c r="M23" s="11" t="n"/>
       <c r="N23" s="11" t="n"/>
     </row>
-    <row r="24" ht="30" customHeight="1">
+    <row r="24" ht="43" customHeight="1">
       <c r="A24" s="10" t="n">
         <v>22</v>
       </c>
@@ -1874,22 +1874,22 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>N_equiv(t) della gola: valori confermati</t>
+          <t>Coefficiente di sicurezza richiesto S_f</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>U senza sottosquadro 1; U β 105° 15,2; V γ 35° 18,5</t>
+          <t>S_f = 10^[2,6834 − log10(695,85·10^6·N_equiv/(D/d)^8,567) / log10(77,09·(D/d)^−2,894)]</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12, tabella 2</t>
+          <t>UNI EN 81-50:2020, 5.12 (ex EN 81-1 Allegato N)</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>fonti concordi</t>
+          <t>riprodotto su due casi pubblicati (liftdesign.it S_f 16,69; Mellor)</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -1909,7 +1909,7 @@
       <c r="M24" s="11" t="n"/>
       <c r="N24" s="11" t="n"/>
     </row>
-    <row r="25" ht="43" customHeight="1">
+    <row r="25" ht="121" customHeight="1">
       <c r="A25" s="10" t="n">
         <v>23</v>
       </c>
@@ -1920,27 +1920,27 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>N_equiv(t) della gola: altri valori (provvisori)</t>
+          <t>N_equiv delle pulegge — D è il diametro della puleggia di frizione, Dp la media delle altre pulegge. La flessione è inversa solo tra due pulegge consecutive ad assi fissi, con i punti di contatto a meno di 200·d e i piani di flessione ruotati di oltre 120°: la classifica il progettista.</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>β 75° 2,5; 80° 3,0; 85° 3,8; 90° 5,0; 95° 6,7; 100° 10,0 · γ 36° 15,2; 38° 10,5; 40° 7,1; 42° 5,6; 45° 4,0</t>
+          <t>N_equiv(p) = K_p·(N_ps + 4·N_pr), K_p = (D/Dp)^4</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12, tabella 2</t>
+          <t>UNI EN 81-50:2020, 5.12.2.3</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>fonti secondarie (β 90° indiretto); gli altri non verificati</t>
+          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 46</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -1955,7 +1955,7 @@
       <c r="M25" s="11" t="n"/>
       <c r="N25" s="11" t="n"/>
     </row>
-    <row r="26" ht="43" customHeight="1">
+    <row r="26" ht="56" customHeight="1">
       <c r="A26" s="10" t="n">
         <v>24</v>
       </c>
@@ -1966,27 +1966,27 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Uso della tabella di N_equiv(t)</t>
+          <t>N_equiv(t) della gola</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>nessuna interpolazione: punto più sfavorevole (β superiore, γ inferiore); oltre 105° estrapolazione dall'ultimo tratto, segnalata</t>
+          <t>U senza sottosquadro 1 · U con sottosquadro: β 75° 2,5; 80° 3,0; 85° 3,8; 90° 5,0; 95° 6,7; 100° 10,0; 105° 15,2 · V: γ 35° 18,5; 36° 16,0; 38° 12,0; 40° 10,0; 42° 8,0; 45° 6,5; 50° 5,0</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12</t>
+          <t>UNI EN 81-50:2020, 5.12.2.2, tabella 2</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>scelta prudente del software (la tabella non dà una regola)</t>
+          <t>BS EN 81-50:2020, estratto pubblico del testo, p. 55 (i valori della gola a V differiscono da quelli della EN 81-1)</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
@@ -2001,7 +2001,7 @@
       <c r="M26" s="11" t="n"/>
       <c r="N26" s="11" t="n"/>
     </row>
-    <row r="27" ht="43" customHeight="1">
+    <row r="27" ht="56" customHeight="1">
       <c r="A27" s="10" t="n">
         <v>25</v>
       </c>
@@ -2012,27 +2012,27 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Tiro massimo per fune</t>
+          <t>Angoli tra i punti della tabella di N_equiv(t)</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>cabina con portata ferma al piano più basso; con la macchina in basso sul primo tratto verso la testata</t>
+          <t>interpolazione lineare tra i due punti vicini</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12</t>
+          <t>UNI EN 81-50:2020, 5.12.2.2</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>definizione di EN 81-1 da fonte secondaria</t>
+          <t>BS EN 81-50:2020, estratto pubblico del testo, p. 55 (la norma consente l'interpolazione lineare)</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
@@ -2047,7 +2047,7 @@
       <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
     </row>
-    <row r="28" ht="43" customHeight="1">
+    <row r="28" ht="82" customHeight="1">
       <c r="A28" s="10" t="n">
         <v>26</v>
       </c>
@@ -2058,32 +2058,32 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Stima di carico di rottura e massa delle funi</t>
+          <t>Angoli fuori dalla tabella di N_equiv(t)</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>8×19 Seale anima tessile 1570 N/mm²: 8 mm = 30,4 kN e 0,215 kg/m, poi in proporzione a d²</t>
+          <t>U: sotto 75° il valore di 75°, oltre 105° estrapolazione dall'ultimo tratto, segnalata · V: oltre 50° il valore di 50°</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.12.2.2</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>tabella Pfeifer 8×19S NFC; usata solo con il pulsante di stima e nella proposta libera</t>
+          <t>scelta prudente del software (la tabella si ferma a quegli angoli; N_equiv cresce con β e cala con γ, quindi il valore dell'estremo sta dal lato della sicurezza)</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>coefficiente di sicurezza delle funi</t>
         </is>
       </c>
       <c r="I28" s="11" t="n"/>
@@ -2093,43 +2093,43 @@
       <c r="M28" s="11" t="n"/>
       <c r="N28" s="11" t="n"/>
     </row>
-    <row r="29" ht="30" customHeight="1">
+    <row r="29" ht="56" customHeight="1">
       <c r="A29" s="10" t="n">
         <v>27</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Freno</t>
+          <t>Funi</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Gruppi meccanici del freno</t>
+          <t>Tiro massimo per fune — Con la macchina in basso il tiro sul primo tratto verso la testata è una derivazione del software.</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>almeno 2</t>
+          <t>cabina con portata ferma al piano più basso; con la macchina in basso sul primo tratto verso la testata</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.9.2.2; UNI 10411-1:2024</t>
+          <t>UNI EN 81-20:2020, 5.5.2.2 (definizione); UNI EN 81-50:2020, 5.12.1</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI 10411-1:2021 e fonti secondarie</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 74–75</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>gruppi del freno</t>
+          <t>coefficiente di sicurezza delle funi</t>
         </is>
       </c>
       <c r="I29" s="11" t="n"/>
@@ -2139,43 +2139,43 @@
       <c r="M29" s="11" t="n"/>
       <c r="N29" s="11" t="n"/>
     </row>
-    <row r="30" ht="30" customHeight="1">
+    <row r="30" ht="43" customHeight="1">
       <c r="A30" s="10" t="n">
         <v>28</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Freno</t>
+          <t>Funi</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Freno, tutti i gruppi</t>
+          <t>Stima di carico di rottura e massa delle funi</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>arresta la cabina in discesa a velocità nominale con 1,25·Q</t>
+          <t>8×19 Seale anima tessile 1570 N/mm²: 8 mm = 30,4 kN e 0,215 kg/m, poi in proporzione a d²</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.9.2.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>due ricerche indipendenti, stessa formulazione</t>
+          <t>tabella Pfeifer 8×19S NFC; usata solo con il pulsante di stima e nella proposta libera</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>freno, tutti i gruppi</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I30" s="11" t="n"/>
@@ -2185,7 +2185,7 @@
       <c r="M30" s="11" t="n"/>
       <c r="N30" s="11" t="n"/>
     </row>
-    <row r="31" ht="30" customHeight="1">
+    <row r="31" ht="82" customHeight="1">
       <c r="A31" s="10" t="n">
         <v>29</v>
       </c>
@@ -2196,32 +2196,32 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Freno, un solo gruppo</t>
+          <t>Gruppi meccanici del freno</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>rallenta, arresta e tiene la cabina con portata in discesa e la cabina vuota in salita</t>
+          <t>almeno 2</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.9.2.2; UNI 10411-1:2024</t>
+          <t>UNI EN 81-20:2020, 5.9.2.2.2.1; UNI 10411-1:2024, 14.1 a)</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI 10411-1:2021</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 100; UNI 10411-1:2024, testo della norma fornito dal cliente, letto il 2026-10-06, p. 13</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>freno, un gruppo in discesa; freno, un gruppo a vuoto in salita</t>
+          <t>gruppi del freno</t>
         </is>
       </c>
       <c r="I31" s="11" t="n"/>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Attrito del riduttore nel fabbisogno del freno</t>
+          <t>Freno, tutti i gruppi</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>non conteggiato (η_i = 1): a favore di sicurezza</t>
+          <t>arresta la cabina in discesa a velocità nominale con 1,25·Q</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.9.2.2.2.1</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>scelta prudente del software</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 100</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>freno, tutti i gruppi; freno, un gruppo in discesa; freno, un gruppo a vuoto in salita</t>
+          <t>freno, tutti i gruppi</t>
         </is>
       </c>
       <c r="I32" s="11" t="n"/>
@@ -2277,7 +2277,7 @@
       <c r="M32" s="11" t="n"/>
       <c r="N32" s="11" t="n"/>
     </row>
-    <row r="33" ht="30" customHeight="1">
+    <row r="33" ht="82" customHeight="1">
       <c r="A33" s="10" t="n">
         <v>31</v>
       </c>
@@ -2288,32 +2288,32 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Decelerazione massima del freno</t>
+          <t>Freno, un solo gruppo — La UNI 10411-1:2024 (11.1.4) e la UNI EN 81-1 chiedono a un solo gruppo di rallentare la cabina carica in discesa; il software applica la richiesta più completa della UNI EN 81-20.</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>≤ 1 g (oltre: «Attenzione»), da confrontare con paracadute e ammortizzatori</t>
+          <t>rallenta, arresta e tiene la cabina con portata in discesa e la cabina vuota in salita</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.9.2.2</t>
+          <t>UNI EN 81-20:2020, 5.9.2.2.2.1; UNI 10411-1:2024, 14.1 a)</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>fonte secondaria</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 100; UNI 10411-1:2024, testo della norma fornito dal cliente, letto il 2026-10-06, p. 13</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>decelerazione massima del freno</t>
+          <t>freno, un gruppo in discesa; freno, un gruppo a vuoto in salita</t>
         </is>
       </c>
       <c r="I33" s="11" t="n"/>
@@ -2323,23 +2323,23 @@
       <c r="M33" s="11" t="n"/>
       <c r="N33" s="11" t="n"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="43" customHeight="1">
       <c r="A34" s="10" t="n">
         <v>32</v>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Riduttore e motore</t>
+          <t>Freno</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Rendimento inverso del riduttore se non dato — Da sostituire con il valore del costruttore: la decelerazione reale del freno ne dipende molto.</t>
+          <t>Attrito del riduttore nel fabbisogno del freno</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>η_i ≈ 2 − 1/η_d (0 = irreversibile)</t>
+          <t>non conteggiato (η_i = 1): a favore di sicurezza</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -2349,17 +2349,17 @@
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>approssimazione della teoria della vite senza fine</t>
+          <t>scelta prudente del software</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>aderenza alla decelerazione reale (avviso); decelerazione massima del freno</t>
+          <t>freno, tutti i gruppi; freno, un gruppo in discesa; freno, un gruppo a vuoto in salita</t>
         </is>
       </c>
       <c r="I34" s="11" t="n"/>
@@ -2369,43 +2369,43 @@
       <c r="M34" s="11" t="n"/>
       <c r="N34" s="11" t="n"/>
     </row>
-    <row r="35" ht="43" customHeight="1">
+    <row r="35" ht="108" customHeight="1">
       <c r="A35" s="10" t="n">
         <v>33</v>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Riduttore e motore</t>
+          <t>Freno</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Coppia di accelerazione</t>
+          <t>Decelerazione massima del freno — La norma non dà un numero per il freno: ne confronta la decelerazione media con quella del paracadute e dell'urto sugli ammortizzatori, che hanno 1 gn come limite. Il confronto vero è con i dati dei componenti montati.</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>≤ 2 volte la coppia nominale (oltre: «Attenzione»; nella proposta: criterio di scelta del motore)</t>
+          <t>≤ 1 g (oltre: «Attenzione»), da confrontare con paracadute e ammortizzatori</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.9.2.2.2.1 (non oltre il paracadute o l'urto sugli ammortizzatori); 1 gn in 5.6.2.1.3 e 5.8.2</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>scelta del software; il limite vero è quello di motore e inverter</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 81, 98–100</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>coppia di accelerazione</t>
+          <t>decelerazione massima del freno</t>
         </is>
       </c>
       <c r="I35" s="11" t="n"/>
@@ -2415,7 +2415,7 @@
       <c r="M35" s="11" t="n"/>
       <c r="N35" s="11" t="n"/>
     </row>
-    <row r="36" ht="30" customHeight="1">
+    <row r="36" ht="56" customHeight="1">
       <c r="A36" s="10" t="n">
         <v>34</v>
       </c>
@@ -2426,12 +2426,12 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Soglia di attenzione sui limiti del costruttore</t>
+          <t>Rendimento inverso del riduttore se non dato — Da sostituire con il valore del costruttore: la decelerazione reale del freno ne dipende molto.</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>oltre il 98% del limite di catalogo (albero, coppia in uscita) → «Attenzione»</t>
+          <t>η_i ≈ 2 − 1/η_d (0 = irreversibile)</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>approssimazione della teoria della vite senza fine</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>carico sull'albero; coppia in uscita</t>
+          <t>aderenza alla decelerazione reale (avviso); decelerazione massima del freno</t>
         </is>
       </c>
       <c r="I36" s="11" t="n"/>
@@ -2472,12 +2472,12 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Potenza statica del motore</t>
+          <t>Coppia di accelerazione</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>P_st = ΔF·v_f / (η_d·η_vano) ≤ P_n, con ΔF il maggiore tra cabina carica in salita dal basso e vuota in discesa dall'alto</t>
+          <t>≤ 2 volte la coppia nominale (oltre: «Attenzione»; nella proposta: criterio di scelta del motore)</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
@@ -2487,17 +2487,17 @@
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software; il limite vero è quello di motore e inverter</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>potenza del motore</t>
+          <t>coppia di accelerazione</t>
         </is>
       </c>
       <c r="I37" s="11" t="n"/>
@@ -2518,32 +2518,32 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Coppia massima in uscita dal riduttore</t>
+          <t>Soglia di attenzione sui limiti del costruttore</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>M_p = ΔF·D/2 + J·i·α_m, confrontata con il valore di catalogo se inserito</t>
+          <t>oltre il 98% del limite di catalogo (albero, coppia in uscita) → «Attenzione»</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>dato del costruttore</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>coppia in uscita</t>
+          <t>carico sull'albero; coppia in uscita</t>
         </is>
       </c>
       <c r="I38" s="11" t="n"/>
@@ -2553,7 +2553,7 @@
       <c r="M38" s="11" t="n"/>
       <c r="N38" s="11" t="n"/>
     </row>
-    <row r="39" ht="30" customHeight="1">
+    <row r="39" ht="43" customHeight="1">
       <c r="A39" s="10" t="n">
         <v>37</v>
       </c>
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Tolleranza tra velocità reale e nominale</t>
+          <t>Potenza statica del motore</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>non verificata: il software mostra la velocità reale e la frequenza per la nominale</t>
+          <t>P_st = ΔF·v_f / (η_d·η_vano) ≤ P_n, con ΔF il maggiore tra cabina carica in salita dal basso e vuota in discesa dall'alto</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>da individuare (UNI EN 81-20:2020 o UNI 10411-1:2024)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>non trovata nelle fonti consultate</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>potenza del motore</t>
         </is>
       </c>
       <c r="I39" s="11" t="n"/>
@@ -2605,37 +2605,37 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Manovra di emergenza</t>
+          <t>Riduttore e motore</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Forza massima al volantino</t>
+          <t>Coppia massima in uscita dal riduttore</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>≤ 400 N, altrimenti manovra elettrica di emergenza</t>
+          <t>M_p = ΔF·D/2 + J·i·α_m, confrontata con il valore di catalogo se inserito</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020 (clausola da individuare)</t>
+          <t>dato del costruttore</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Elevator World; stesso valore in EN 81-1</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>forza al volantino</t>
+          <t>coppia in uscita</t>
         </is>
       </c>
       <c r="I40" s="11" t="n"/>
@@ -2645,43 +2645,43 @@
       <c r="M40" s="11" t="n"/>
       <c r="N40" s="11" t="n"/>
     </row>
-    <row r="41" ht="30" customHeight="1">
+    <row r="41" ht="82" customHeight="1">
       <c r="A41" s="10" t="n">
         <v>39</v>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Albero e ancoraggi</t>
+          <t>Riduttore e motore</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Carico sull'albero della puleggia</t>
+          <t>Tolleranza tra velocità reale e nominale — Con la UNI 10411-1:2024 (15.1) una velocità oltre il 5 % sopra quella originale è un aumento della velocità nominale (punti 15.2–15.15).</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>risultante dei tiri con 1,25·Q al piano più basso, confrontata con il limite del costruttore</t>
+          <t>con metà portata a metà corsa, in salita e in discesa, non oltre il 5 % sopra la nominale (buona pratica: non oltre l'8 % sotto); non verificata: il software mostra la velocità reale e la frequenza per la nominale</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>dato del costruttore</t>
+          <t>UNI EN 81-20:2020, 5.9.2.4; UNI 10411-1:2024, 15.1</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>derivazione; definizione del costruttore da confermare</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 102; UNI 10411-1:2024, testo della norma fornito dal cliente, letto il 2026-10-06, p. 14</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>carico sull'albero</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I41" s="11" t="n"/>
@@ -2691,43 +2691,43 @@
       <c r="M41" s="11" t="n"/>
       <c r="N41" s="11" t="n"/>
     </row>
-    <row r="42" ht="30" customHeight="1">
+    <row r="42" ht="69" customHeight="1">
       <c r="A42" s="10" t="n">
         <v>40</v>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Albero e ancoraggi</t>
+          <t>Manovra di emergenza</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Sollevamento netto sugli ancoraggi (macchina in basso)</t>
+          <t>Forza massima al volantino — Il mezzo meccanico è ammesso solo se la forza per portare la cabina a una fermata non supera 150 N (5.9.2.3.1 a)): non verificato dal software.</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>carico verso l'alto meno la massa della macchina: da verificare con il progettista strutturale</t>
+          <t>≤ 400 N, altrimenti manovra elettrica di emergenza</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.9.2.3.3 (400 N) e 5.9.2.3.1 a) (150 N)</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 101–102</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>sollevamento netto</t>
+          <t>forza al volantino</t>
         </is>
       </c>
       <c r="I42" s="11" t="n"/>
@@ -2737,43 +2737,43 @@
       <c r="M42" s="11" t="n"/>
       <c r="N42" s="11" t="n"/>
     </row>
-    <row r="43" ht="69" customHeight="1">
+    <row r="43" ht="56" customHeight="1">
       <c r="A43" s="10" t="n">
         <v>41</v>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Sostituzione (Italia)</t>
+          <t>Albero e ancoraggi</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>La sostituzione del macchinario è una modifica costruttiva</t>
+          <t>Carico sull'albero della puleggia</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>modifica costruttiva (art. 2 c.1 lett. cc), n. 5): adeguamento della parte sostituita e delle altre parti interessate, comunicazione al Comune e al soggetto delle verifiche periodiche, verifica straordinaria prima del servizio</t>
+          <t>risultante dei tiri con 1,25·Q al piano più basso, confrontata con il limite del costruttore</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., art. 2 c.1 lett. cc), art. 12 c.4–5, art. 14 c.3</t>
+          <t>dato del costruttore; 1,25·Q come nella verifica di caricamento (UNI EN 81-50:2020, 5.11.2.2.1)</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 consolidato (Normattiva), letto il 2026-10-02 (ricerca, cap. 16), §3.2</t>
+          <t>derivazione; la definizione del carico va confermata con il costruttore</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>carico sull'albero</t>
         </is>
       </c>
       <c r="I43" s="11" t="n"/>
@@ -2789,37 +2789,37 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Sostituzione (Italia)</t>
+          <t>Albero e ancoraggi</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Adeguamenti richiesti per la sostituzione del macchinario</t>
+          <t>Sollevamento netto sugli ancoraggi (macchina in basso)</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>elenco del capitolo 6.6 della ricerca (tra cui freno a due gruppi)</t>
+          <t>carico verso l'alto meno la massa della macchina: da verificare con il progettista strutturale</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>sintesi pubblicate della UNI 10411-1:2021 (edizione superata)</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>gruppi del freno</t>
+          <t>sollevamento netto</t>
         </is>
       </c>
       <c r="I44" s="11" t="n"/>
@@ -2829,7 +2829,7 @@
       <c r="M44" s="11" t="n"/>
       <c r="N44" s="11" t="n"/>
     </row>
-    <row r="45" ht="43" customHeight="1">
+    <row r="45" ht="69" customHeight="1">
       <c r="A45" s="10" t="n">
         <v>43</v>
       </c>
@@ -2840,27 +2840,27 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Funi nella sostituzione</t>
+          <t>La sostituzione del macchinario è una modifica costruttiva</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>di norma funi nuove con lo stesso numero e diametro di quelle montate; la proposta le tiene fisse</t>
+          <t>modifica costruttiva (art. 2 c.1 lett. cc), n. 5): adeguamento della parte sostituita e delle altre parti interessate, comunicazione al Comune e al soggetto delle verifiche periodiche, verifica straordinaria prima del servizio</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DPR 162/1999 e s.m.i., art. 2 c.1 lett. cc), art. 12 c.4–5, art. 14 c.3</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>indicazione di Panev Ascensori (29 settembre 2026)</t>
+          <t>DPR 162/1999 consolidato (Normattiva), letto il 2026-10-02 (ricerca, cap. 16), §3.2</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>prassi di cantiere</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
@@ -2875,43 +2875,43 @@
       <c r="M45" s="11" t="n"/>
       <c r="N45" s="11" t="n"/>
     </row>
-    <row r="46" ht="30" customHeight="1">
+    <row r="46" ht="212" customHeight="1">
       <c r="A46" s="10" t="n">
         <v>44</v>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Modello di calcolo</t>
+          <t>Sostituzione (Italia)</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Accelerazione di gravità</t>
+          <t>Adeguamenti richiesti per la sostituzione del macchinario</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>g = 9,81 m/s² (anche come limite di 1 g)</t>
+          <t>UNI 10411-1:2024, punto 14: macchina secondo la UNI EN 81-20 (5.9.1 e 5.9.2, freno in due gruppi) o la UNI EN 81-1:2010, con aderenza e coefficiente di sicurezza delle funi (14.1); D/d ≥ 40 (14.3); temporizzatore della UNI EN 81-20 (5.9.2.7), arresto prima che la cabina in salita tocchi la velocità di intervento del limitatore, ACOP e UCM esistenti che funzionano ancora, arresto vicino alla macchina, pulegge secondo la 5.5.7, interruzione se il freno non si apre (14.4 a)–g)). UNI 10411-11:2024, punto 14: macchina come l'originale, altrimenti UNI EN 81-20 5.9.1–5.9.2 con le verifiche della norma di origine o della UNI EN 81-20 e la valutazione 4.3 (14.1); UCM esistenti che funzionano ancora e interruzione se il freno non si apre (14.3)</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020 (simboli)</t>
+          <t>UNI 10411-1:2024, 14.1–14.4; UNI 10411-11:2024, 14.1–14.3</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>valore d'uso nei calcoli degli ascensori</t>
+          <t>UNI 10411-1:2024, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 13–14; UNI 10411-11:2024, testo della norma fornito dal cliente, letto il 2026-10-06, p. 12</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>gruppi del freno</t>
         </is>
       </c>
       <c r="I46" s="11" t="n"/>
@@ -2921,43 +2921,43 @@
       <c r="M46" s="11" t="n"/>
       <c r="N46" s="11" t="n"/>
     </row>
-    <row r="47" ht="69" customHeight="1">
+    <row r="47" ht="43" customHeight="1">
       <c r="A47" s="10" t="n">
         <v>45</v>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Modello di calcolo</t>
+          <t>Sostituzione (Italia)</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Tiri con il metodo del percorso della fune</t>
+          <t>Funi nella sostituzione</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>masse e funi di ogni tratto, inerzia delle pulegge di rinvio; attrito di guide e pulegge trascurato in aderenza</t>
+          <t>di norma funi nuove con lo stesso numero e diametro di quelle montate; la proposta le tiene fisse</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>derivazione; il conteggio dell'inerzia delle pulegge va confermato</t>
+          <t>indicazione di Panev Ascensori (29 settembre 2026)</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>prassi di cantiere</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>aderenza al caricamento; aderenza in frenatura, in discesa; aderenza in frenatura, in salita; aderenza alla decelerazione reale (avviso); cabina bloccata</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I47" s="11" t="n"/>
@@ -2967,7 +2967,7 @@
       <c r="M47" s="11" t="n"/>
       <c r="N47" s="11" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="43" customHeight="1">
       <c r="A48" s="10" t="n">
         <v>46</v>
       </c>
@@ -2978,27 +2978,27 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Compensazione e cavo flessibile</t>
+          <t>Accelerazione di gravità</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>non modellati a parte: la loro massa sul lato cabina entra in P</t>
+          <t>g = 9,81 m/s² (anche come limite di 1 g)</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8.5 (g_n = 9,81 m/s²)</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>limite del modello attuale</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 27</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
@@ -3013,7 +3013,7 @@
       <c r="M48" s="11" t="n"/>
       <c r="N48" s="11" t="n"/>
     </row>
-    <row r="49" ht="30" customHeight="1">
+    <row r="49" ht="173" customHeight="1">
       <c r="A49" s="10" t="n">
         <v>47</v>
       </c>
@@ -3024,32 +3024,32 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Analisi di sensibilità</t>
+          <t>Tiri con il metodo del percorso della fune — Confermati sul testo: le masse per lato, il fattore (r² + 2)/3 delle funi, il termine delle pulegge di rinvio e l'attrito trascurato. Da verificare: in taglia 2:1 le pulegge di cabina e di contrappeso (termine III della norma) non sono contate; con la macchina in basso il tratto tra macchina e pulegge in testata usa r·a, dove il testo stampa a (la forma stampata coincide con quella fisica solo a 1:1).</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>P ±10%; k ±0,05 se il carico di equilibrio non è misurato</t>
+          <t>masse e funi di ogni tratto, inerzia delle pulegge di rinvio; attrito di guide e pulegge trascurato in aderenza</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.3</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (incertezza tipica del rilievo)</t>
+          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 43–44</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>aderenza al caricamento; aderenza in frenatura, in discesa; aderenza in frenatura, in salita; aderenza alla decelerazione reale (avviso); cabina bloccata</t>
         </is>
       </c>
       <c r="I49" s="11" t="n"/>
@@ -3059,43 +3059,43 @@
       <c r="M49" s="11" t="n"/>
       <c r="N49" s="11" t="n"/>
     </row>
-    <row r="50" ht="134" customHeight="1">
+    <row r="50" ht="30" customHeight="1">
       <c r="A50" s="10" t="n">
         <v>48</v>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Vano: cabina e portata</t>
+          <t>Modello di calcolo</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Superficie utile massima della cabina per portata — la superficie è calcolata come larghezza × profondità interne, senza nicchie né rientranze della porta</t>
+          <t>Compensazione e cavo flessibile</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>100 kg 0,37 m²; 180 kg 0,58; 225 kg 0,70; 300 kg 0,90; 375 kg 1,10; 400 kg 1,17; 450 kg 1,30; 525 kg 1,45; 600 kg 1,60; 630 kg 1,66; 675 kg 1,75; 750 kg 1,90; 800 kg 2,00; 825 kg 2,05; 900 kg 2,20; 975 kg 2,35; 1000 kg 2,40; 1050 kg 2,50; 1125 kg 2,65; 1200 kg 2,80; 1250 kg 2,90; 1275 kg 2,95; 1350 kg 3,10; 1425 kg 3,25; 1500 kg 3,40; 1600 kg 3,56; 2000 kg 4,20; 2500 kg 5,00; oltre 2500 kg +0,16 m² ogni 100 kg; interpolazione lineare</t>
+          <t>non modellati a parte: la loro massa sul lato cabina entra in P</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.2.1 (Tabella 6)</t>
+          <t>UNI EN 81-50:2020, 5.11</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>Elevator World, «Rated Load and Maximum Available Car Area» (fonte secondaria); valori della EN 81-1 (Tabella 1.1)</t>
+          <t>limite del modello attuale</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>superficie della cabina per la portata</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I50" s="11" t="n"/>
@@ -3105,38 +3105,38 @@
       <c r="M50" s="11" t="n"/>
       <c r="N50" s="11" t="n"/>
     </row>
-    <row r="51" ht="95" customHeight="1">
+    <row r="51" ht="30" customHeight="1">
       <c r="A51" s="10" t="n">
         <v>49</v>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Vano: cabina e portata</t>
+          <t>Modello di calcolo</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Numero di passeggeri</t>
+          <t>Analisi di sensibilità</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>il minore tra Q/75 arrotondato per difetto e il numero ammesso dalla superficie: 1 persona 0,28 m²; 2 0,49; 3 0,60; 4 0,79; 5 0,98; 6 1,17; 7 1,31; 8 1,45; 9 1,59; 10 1,73; 11 1,87; 12 2,01; 13 2,15; 14 2,29; 15 2,43; 16 2,57; 17 2,71; 18 2,85; 19 2,99; 20 3,13; oltre 20 +0,115 m² per persona</t>
+          <t>P ±10%; k ±0,05 se il carico di equilibrio non è misurato</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.2 (Tabella 8)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>valori della EN 81-1 (Tabella 1.2), edizione superata</t>
+          <t>scelta del software (incertezza tipica del rilievo)</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
@@ -3151,43 +3151,43 @@
       <c r="M51" s="11" t="n"/>
       <c r="N51" s="11" t="n"/>
     </row>
-    <row r="52" ht="43" customHeight="1">
+    <row r="52" ht="134" customHeight="1">
       <c r="A52" s="10" t="n">
         <v>50</v>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Vano: distanze in pianta</t>
+          <t>Vano: cabina e portata</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Parete del vano di fronte all'entrata della cabina</t>
+          <t>Superficie utile massima della cabina per portata — la norma misura la superficie a 1 m dal pavimento tra le pareti strutturali, senza finiture (5.4.2.1.2), conta le nicchie e conta per intero la rientranza dell'ingresso profonda più di 100 mm (5.4.2.1.3); il software usa larghezza × profondità interne: nicchie e rientranze vanno aggiunte a mano</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>distanza orizzontale dalla soglia o dal telaio della porta di cabina ≤ 150 mm (qui: profondità della porta di piano + gioco tra le soglie)</t>
+          <t>100 kg 0,37 m²; 180 kg 0,58; 225 kg 0,70; 300 kg 0,90; 375 kg 1,10; 400 kg 1,17; 450 kg 1,30; 525 kg 1,45; 600 kg 1,60; 630 kg 1,66; 675 kg 1,75; 750 kg 1,90; 800 kg 2,00; 825 kg 2,05; 900 kg 2,20; 975 kg 2,35; 1000 kg 2,40; 1050 kg 2,50; 1125 kg 2,65; 1200 kg 2,80; 1250 kg 2,90; 1275 kg 2,95; 1350 kg 3,10; 1425 kg 3,25; 1500 kg 3,40; 1600 kg 3,56; 2000 kg 4,20; 2500 kg 5,00; oltre 2500 kg +0,16 m² ogni 100 kg; interpolazione lineare</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.3.1</t>
+          <t>UNI EN 81-20:2020, 5.4.2.1.1 (Prospetto 6)</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>schede EN 81-20 dei costruttori (KONE), fonti secondarie</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 63–64</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>parete di fronte all'entrata</t>
+          <t>superficie della cabina per la portata</t>
         </is>
       </c>
       <c r="I52" s="11" t="n"/>
@@ -3197,43 +3197,43 @@
       <c r="M52" s="11" t="n"/>
       <c r="N52" s="11" t="n"/>
     </row>
-    <row r="53" ht="43" customHeight="1">
+    <row r="53" ht="95" customHeight="1">
       <c r="A53" s="10" t="n">
         <v>51</v>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Vano: distanze in pianta</t>
+          <t>Vano: cabina e portata</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Gioco tra soglia di cabina e soglia di piano</t>
+          <t>Numero di passeggeri</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>distanza orizzontale ≤ 35 mm</t>
+          <t>il minore tra Q/75 arrotondato per difetto e il numero ammesso dalla superficie: 1 persona 0,28 m²; 2 0,49; 3 0,60; 4 0,79; 5 0,98; 6 1,17; 7 1,31; 8 1,45; 9 1,59; 10 1,73; 11 1,87; 12 2,01; 13 2,15; 14 2,29; 15 2,43; 16 2,57; 17 2,71; 18 2,85; 19 2,99; 20 3,13; oltre 20 +0,115 m² per persona</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020 (clausola da individuare; 11.2.3 nella EN 81-1)</t>
+          <t>UNI EN 81-20:2020, 5.4.2.3.1 (Prospetto 8)</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>fonti secondarie concordi</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 66</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>gioco tra le soglie</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I53" s="11" t="n"/>
@@ -3243,7 +3243,7 @@
       <c r="M53" s="11" t="n"/>
       <c r="N53" s="11" t="n"/>
     </row>
-    <row r="54" ht="30" customHeight="1">
+    <row r="54" ht="108" customHeight="1">
       <c r="A54" s="10" t="n">
         <v>52</v>
       </c>
@@ -3254,32 +3254,32 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Distanza tra cabina e contrappeso</t>
+          <t>Parete del vano di fronte all'entrata della cabina — le deroghe della norma (fino a 0,20 m per un tratto alto non più di 0,50 m o con porte verticali di ascensori per merci; nessun limite con la porta di cabina bloccata meccanicamente) non sono usate: la verifica è più severa</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>≥ 50 mm tra la cabina con i suoi componenti e il contrappeso con i suoi</t>
+          <t>distanza orizzontale dalla soglia o dal telaio della porta di cabina ≤ 150 mm (qui: profondità della porta di piano + gioco tra le soglie)</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.5.1</t>
+          <t>UNI EN 81-20:2020, 5.2.5.3.1</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>schede EN 81-20 dei costruttori (KONE), fonti secondarie</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 33</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>distanza cabina–contrappeso</t>
+          <t>parete di fronte all'entrata</t>
         </is>
       </c>
       <c r="I54" s="11" t="n"/>
@@ -3289,7 +3289,7 @@
       <c r="M54" s="11" t="n"/>
       <c r="N54" s="11" t="n"/>
     </row>
-    <row r="55" ht="199" customHeight="1">
+    <row r="55" ht="43" customHeight="1">
       <c r="A55" s="10" t="n">
         <v>53</v>
       </c>
@@ -3300,32 +3300,32 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Pareti all'ultimo piano e in testata diverse dal piano principale</t>
+          <t>Gioco tra soglia di cabina e soglia di piano</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>negli edifici esistenti le pareti del vano all'ultima fermata e in testata possono stare altrove che al piano principale: cabina, guide e contrappeso restano a piombo; la cabina con soglie e operatori delle porte e il contrappeso passano ad almeno 25 mm dalle pareti spostate (meno: «Attenzione»; dentro la parete: «Non conforme»); le porte di piano dell'ultima fermata restano in linea con la cabina e la parete non entra nel loro spessore, i piedi delle guide e la staffa a ponte non entrano nelle pareti; le staffe arrivano alla parete dove sta (le staffe Panev si verificano anche lì); la distanza dalla parete di fronte all'entrata (voce distanze.parete.entrata) vale anche in testata</t>
+          <t>distanza orizzontale ≤ 35 mm</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.3.1 (parete di fronte all'entrata); il resto scelta del software</t>
+          <t>UNI EN 81-20:2020, 5.3.4.1 (figura 3); 11.2.2 nella UNI EN 81-1 (1999, 2008)</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>scelta del software: il margine di marcia va confermato con l'installatore</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 50</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>pareti in testata diverse dal piano principale</t>
+          <t>gioco tra le soglie</t>
         </is>
       </c>
       <c r="I55" s="11" t="n"/>
@@ -3335,33 +3335,33 @@
       <c r="M55" s="11" t="n"/>
       <c r="N55" s="11" t="n"/>
     </row>
-    <row r="56" ht="56" customHeight="1">
+    <row r="56" ht="69" customHeight="1">
       <c r="A56" s="10" t="n">
         <v>54</v>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Vano: accessibilità (DM 236/1989)</t>
+          <t>Vano: distanze in pianta</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Edifici residenziali nuovi: cabina e porta minime</t>
+          <t>Distanza tra cabina e contrappeso — il software misura tra le sagome di cabina e contrappeso: pattini e staffe non sono nel modello della pianta</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>cabina larga 950 mm e profonda 1300 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (fuori dal vano: da verificare in sito)</t>
+          <t>≥ 50 mm tra la cabina con i suoi componenti e il contrappeso con i suoi</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-20:2020, 5.2.5.5.1 h)</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12, letto per intero su Normattiva il 2026-10-02 (ricerca, cap. 16, §4.1)</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 35</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>distanza cabina–contrappeso</t>
         </is>
       </c>
       <c r="I56" s="11" t="n"/>
@@ -3381,43 +3381,43 @@
       <c r="M56" s="11" t="n"/>
       <c r="N56" s="11" t="n"/>
     </row>
-    <row r="57" ht="56" customHeight="1">
+    <row r="57" ht="199" customHeight="1">
       <c r="A57" s="10" t="n">
         <v>55</v>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Vano: accessibilità (DM 236/1989)</t>
+          <t>Vano: distanze in pianta</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Edifici non residenziali nuovi: cabina e porta minime</t>
+          <t>Pareti all'ultimo piano e in testata diverse dal piano principale</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>cabina larga 1100 mm e profonda 1400 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (fuori dal vano: da verificare in sito)</t>
+          <t>negli edifici esistenti le pareti del vano all'ultima fermata e in testata possono stare altrove che al piano principale: cabina, guide e contrappeso restano a piombo; la cabina con soglie e operatori delle porte e il contrappeso passano ad almeno 25 mm dalle pareti spostate (meno: «Attenzione»; dentro la parete: «Non conforme»); le porte di piano dell'ultima fermata restano in linea con la cabina e la parete non entra nel loro spessore, i piedi delle guide e la staffa a ponte non entrano nelle pareti; le staffe arrivano alla parete dove sta (le staffe Panev si verificano anche lì); la distanza dalla parete di fronte all'entrata (voce distanze.parete.entrata) vale anche in testata</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-20:2020, 5.2.5.3.1 (parete di fronte all'entrata); il resto scelta del software</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12, letto per intero su Normattiva il 2026-10-02 (ricerca, cap. 16, §4.1)</t>
+          <t>scelta del software: il margine di marcia va confermato con l'installatore</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>pareti in testata diverse dal piano principale</t>
         </is>
       </c>
       <c r="I57" s="11" t="n"/>
@@ -3438,12 +3438,12 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Adeguamento di edifici esistenti: cabina e porta minime</t>
+          <t>Edifici residenziali nuovi: cabina e porta minime</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>cabina larga 800 mm e profonda 1200 mm, porta di 750 mm sul lato corto; piattaforma davanti alla porta 1,40 × 1,40 m (fuori dal vano: da verificare in sito)</t>
+          <t>cabina larga 950 mm e profonda 1300 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (fuori dal vano: da verificare in sito)</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
@@ -3473,43 +3473,43 @@
       <c r="M58" s="11" t="n"/>
       <c r="N58" s="11" t="n"/>
     </row>
-    <row r="59" ht="43" customHeight="1">
+    <row r="59" ht="56" customHeight="1">
       <c r="A59" s="10" t="n">
         <v>57</v>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Vano: porte</t>
+          <t>Vano: accessibilità (DM 236/1989)</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Ingombro della porta di piano lungo la parete del vano</t>
+          <t>Edifici non residenziali nuovi: cabina e porta minime</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>telescopica a 2 ante: 1,5·L + 110 mm; centrale a 2 ante: 2·L + 110 mm (L = luce netta)</t>
+          <t>cabina larga 1100 mm e profonda 1400 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (fuori dal vano: da verificare in sito)</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>dato del fornitore delle porte</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>valori tipici: scelta del software da confermare con il fornitore</t>
+          <t>DM 236/1989, 8.1.12, letto per intero su Normattiva il 2026-10-02 (ricerca, cap. 16, §4.1)</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>ingombro della porta di piano</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I59" s="11" t="n"/>
@@ -3519,43 +3519,43 @@
       <c r="M59" s="11" t="n"/>
       <c r="N59" s="11" t="n"/>
     </row>
-    <row r="60" ht="30" customHeight="1">
+    <row r="60" ht="56" customHeight="1">
       <c r="A60" s="10" t="n">
         <v>58</v>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Vano: porte</t>
+          <t>Vano: accessibilità (DM 236/1989)</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Larghezza della cabina rispetto alla porta</t>
+          <t>Adeguamento di edifici esistenti: cabina e porta minime</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>larghezza interna ≥ luce della porta + 50 mm; profondità interna ≥ 800 mm</t>
+          <t>cabina larga 800 mm e profonda 1200 mm, porta di 750 mm sul lato corto; piattaforma davanti alla porta 1,40 × 1,40 m (fuori dal vano: da verificare in sito)</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>DM 236/1989, 8.1.12, letto per intero su Normattiva il 2026-10-02 (ricerca, cap. 16, §4.1)</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>la cabina entra nel vano</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I60" s="11" t="n"/>
@@ -3565,7 +3565,7 @@
       <c r="M60" s="11" t="n"/>
       <c r="N60" s="11" t="n"/>
     </row>
-    <row r="61" ht="342" customHeight="1">
+    <row r="61" ht="43" customHeight="1">
       <c r="A61" s="10" t="n">
         <v>59</v>
       </c>
@@ -3576,12 +3576,12 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Vano porta di piano e operatore della porta di cabina</t>
+          <t>Ingombro della porta di piano lungo la parete del vano</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>vano nel muro: luce netta + 2 × 50 mm di portale; operatore della porta di cabina lungo 1,5·L + 50 mm con porta telescopica (il lato di chiusura 25 mm oltre la luce) e 2·L + 60 mm con porta centrale, profondo 220 mm, dentro il vano; con il fornitore scelto: 2SG FLY/LIKE 1,5·L + 40 mm (telescopica) e 2·L + 20 mm (centrale), profondo 220 mm; Fermator 40/10 1,5·L + 50 mm e 2·L + 50 mm, profondo 144 mm; Dapa LOWER 1,5·L + 47 mm e 2·L + 50 mm, profondo 217 mm; con due accessi adiacenti gli operatori non devono sovrapporsi all'angolo tra le porte (altrimenti «Attenzione»: operatori da scegliere con il fornitore)</t>
+          <t>telescopica a 2 ante: 1,5·L + 110 mm; centrale a 2 ante: 2·L + 110 mm (L = luce netta)</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
@@ -3591,17 +3591,17 @@
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>schede PDF 2SG FLY 2AT (ingombro massimo 1,5·A + 10; soglia 1,5·A + 20, + 40 con l'extracorsa: presa la più lunga) e 2AO (2·A + 20), profondità 220 letta sul disegno; catalogo tecnico Dapa LOWER (1,5·AP + 47, 2·AP + 50, profondità 217); Fermator 40/10 PM in copie presso terzi (1,5·PL + 50 e 2·PL + 50, le soglie + 40; profondità 120–144 sul disegno, con le staffe 183–280; chiusura a 15 mm dalla luce, il software ne tiene 25); Wittur Hydra Plus da una copia del catalogo Selcom (1,5·PL + 25 e 2·PL + 50, profondo 200); letti il 2 ottobre 2026 (research/argano-geared/18-porte-limitatori-tenditori-tutti.md). Il generico è l'inviluppo: il più lungo (Fermator, Dapa) e il più profondo (2SG FLY). Hydra Plus può superarlo dove la sua quota GM supera la GW; Prisma e CMM: lunghezza e profondità non trovate</t>
+          <t>valori tipici: scelta del software da confermare con il fornitore</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>ingombro della porta di piano; ingombro della seconda porta di piano; operatori delle porte adiacenti</t>
+          <t>ingombro della porta di piano</t>
         </is>
       </c>
       <c r="I61" s="11" t="n"/>
@@ -3611,7 +3611,7 @@
       <c r="M61" s="11" t="n"/>
       <c r="N61" s="11" t="n"/>
     </row>
-    <row r="62" ht="134" customHeight="1">
+    <row r="62" ht="30" customHeight="1">
       <c r="A62" s="10" t="n">
         <v>60</v>
       </c>
@@ -3622,32 +3622,32 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Porta di piano spostata rispetto alla porta di cabina (disassamento) — nel 3D la leva della serratura con i rulli resta in linea con l'accoppiatore della porta di cabina: con il disassamento va montata spostata sull'anta della porta di piano (da concordare con il fornitore delle porte)</t>
+          <t>Larghezza della cabina rispetto alla porta</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>la luce netta della porta di piano sporge al massimo 50 mm per lato oltre quella della porta di cabina: con la stessa luce, disassamento ≤ 50 mm (oltre: «Non conforme»); lo stesso spostamento a tutti i piani, per ciascun accesso, con il vano nel muro, il portale, gli imbotti, la soglia sulle staffe e la bottoniera della porta di piano; il passaggio libero è la parte comune delle due luci (luce − disassamento), ed è quello verificato per l'accessibilità (DM 236/1989)</t>
+          <t>larghezza interna ≥ luce della porta + 50 mm; profondità interna ≥ 800 mm</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.3.2.2 (larghezza degli accessi; numero della clausola da confermare sul testo)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>fonti secondarie: sintesi dei requisiti EN 81-20 dei costruttori letta tramite motore di ricerca (i documenti non erano raggiungibili); che la 5.3.2.1 sia l'altezza libera degli accessi (≥ 2 m) lo confermano le interpretazioni VDMA della serie EN 81 (DAfA 104, 16.09.2020)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>disassamento della porta di piano A; disassamento della porta di piano B</t>
+          <t>la cabina entra nel vano</t>
         </is>
       </c>
       <c r="I62" s="11" t="n"/>
@@ -3657,7 +3657,7 @@
       <c r="M62" s="11" t="n"/>
       <c r="N62" s="11" t="n"/>
     </row>
-    <row r="63" ht="95" customHeight="1">
+    <row r="63" ht="342" customHeight="1">
       <c r="A63" s="10" t="n">
         <v>61</v>
       </c>
@@ -3668,32 +3668,32 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Bottoniera di piano</t>
+          <t>Vano porta di piano e operatore della porta di cabina</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>accanto a ogni porta di piano, sul pianerottolo: per default a destra guardando la porta, il centro della pulsantiera a 150 mm dal vano della porta e i pulsanti a 1100 mm dal pavimento; pulsantiera di 120 × 300 mm, sporgente 15 mm dal muro; lato, distanza e altezza modificabili su ogni progetto</t>
+          <t>vano nel muro: luce netta + 2 × 50 mm di portale; operatore della porta di cabina lungo 1,5·L + 50 mm con porta telescopica (il lato di chiusura 25 mm oltre la luce) e 2·L + 60 mm con porta centrale, profondo 220 mm, dentro il vano; con il fornitore scelto: 2SG FLY/LIKE 1,5·L + 40 mm (telescopica) e 2·L + 20 mm (centrale), profondo 220 mm; Fermator 40/10 1,5·L + 50 mm e 2·L + 50 mm, profondo 144 mm; Dapa LOWER 1,5·L + 47 mm e 2·L + 50 mm, profondo 217 mm; con due accessi adiacenti gli operatori non devono sovrapporsi all'angolo tra le porte (altrimenti «Attenzione»: operatori da scegliere con il fornitore)</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>altezze e distanze dagli angoli per l'accessibilità da verificare (DM 236/1989, UNI EN 81-70)</t>
+          <t>dato del fornitore delle porte</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>schede PDF 2SG FLY 2AT (ingombro massimo 1,5·A + 10; soglia 1,5·A + 20, + 40 con l'extracorsa: presa la più lunga) e 2AO (2·A + 20), profondità 220 letta sul disegno; catalogo tecnico Dapa LOWER (1,5·AP + 47, 2·AP + 50, profondità 217); Fermator 40/10 PM in copie presso terzi (1,5·PL + 50 e 2·PL + 50, le soglie + 40; profondità 120–144 sul disegno, con le staffe 183–280; chiusura a 15 mm dalla luce, il software ne tiene 25); Wittur Hydra Plus da una copia del catalogo Selcom (1,5·PL + 25 e 2·PL + 50, profondo 200); letti il 2 ottobre 2026 (research/argano-geared/18-porte-limitatori-tenditori-tutti.md). Il generico è l'inviluppo: il più lungo (Fermator, Dapa) e il più profondo (2SG FLY). Hydra Plus può superarlo dove la sua quota GM supera la GW; Prisma e CMM: lunghezza e profondità non trovate</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ingombro della porta di piano; ingombro della seconda porta di piano; operatori delle porte adiacenti</t>
         </is>
       </c>
       <c r="I63" s="11" t="n"/>
@@ -3703,7 +3703,7 @@
       <c r="M63" s="11" t="n"/>
       <c r="N63" s="11" t="n"/>
     </row>
-    <row r="64" ht="160" customHeight="1">
+    <row r="64" ht="134" customHeight="1">
       <c r="A64" s="10" t="n">
         <v>62</v>
       </c>
@@ -3714,32 +3714,32 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Imbotti della porta di piano (sostituzione con una luce più piccola)</t>
+          <t>Porta di piano spostata rispetto alla porta di cabina (disassamento) — nel 3D la leva della serratura con i rulli resta in linea con l'accoppiatore della porta di cabina: con il disassamento va montata spostata sull'anta della porta di piano (da concordare con il fornitore delle porte)</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>quando la porta nuova ha una luce più piccola del vano esistente tra i marmi, gli imbotti laterali (a sinistra e a destra guardando la porta dal pianerottolo) e quello superiore coprono la differenza: distanza tra i marmi = imbotto sinistro + luce + 2 × 50 mm di portale + imbotto destro; altezza sotto il marmo superiore = altezza della luce + 60 mm di architrave del portale + imbotto superiore; gli stessi imbotti per tutte le porte di piano, in lamiera sul filo del muro verso il pianerottolo, disegnati in pianta, in sezione e nel 3D</t>
+          <t>la luce netta della porta di piano sporge al massimo 50 mm per lato oltre quella della porta di cabina: con la stessa luce, disassamento ≤ 50 mm (oltre: «Non conforme»); lo stesso spostamento a tutti i piani, per ciascun accesso, con il vano nel muro, il portale, gli imbotti, la soglia sulle staffe e la bottoniera della porta di piano; il passaggio libero è la parte comune delle due luci (luce − disassamento), ed è quello verificato per l'accessibilità (DM 236/1989)</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>dato del fornitore delle porte (imbotti su misura)</t>
+          <t>UNI EN 81-20:2020, 5.3.2.2</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 49</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>disassamento della porta di piano A; disassamento della porta di piano B</t>
         </is>
       </c>
       <c r="I64" s="11" t="n"/>
@@ -3749,33 +3749,33 @@
       <c r="M64" s="11" t="n"/>
       <c r="N64" s="11" t="n"/>
     </row>
-    <row r="65" ht="199" customHeight="1">
+    <row r="65" ht="95" customHeight="1">
       <c r="A65" s="10" t="n">
         <v>63</v>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Vano: ingombri tipici</t>
+          <t>Vano: porte</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Ingombri tipici nel vano (modificabili su ogni progetto) — pacchetto porta di catalogo (porta di cabina + gioco tra le soglie + porta di piano), da wittur.com: Hydra 210 mm a 2 ante telescopiche e 180 mm a 2 ante centrali, Hydra 3000 180 e 130, Augusta EVO 190 e 110, Sematic 2000 C-MOD 185 e 117, Fineline 115 e 85; Sematic 2000 B 255 e 165 (cabina 90 e 45, gioco 30, piano 135 e 90, da una copia della brochure). Con le porte scelte, i tre ingombri vanno portati alla somma del fornitore (oggi 80 + 30 + 80 = 190 mm)</t>
+          <t>Bottoniera di piano</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>profondità della porta di piano 80 mm; gioco tra le soglie 30 mm; porta di cabina 80 mm; pareti della cabina 35 mm; guide e staffe della cabina 165 mm per lato; cabina–contrappeso 60 mm; spessore del contrappeso 140 mm; guide e staffe del contrappeso 80 mm; cabina–parete di fondo 60 mm; punta della guida–cabina 30 mm; contrappeso laterale–piede della guida di cabina 85 mm</t>
+          <t>accanto a ogni porta di piano, sul pianerottolo: per default a destra guardando la porta, il centro della pulsantiera a 150 mm dal vano della porta e i pulsanti a 1100 mm dal pavimento; pulsantiera di 120 × 300 mm, sporgente 15 mm dal muro; lato, distanza e altezza modificabili su ogni progetto</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>dati del costruttore di guide, porte e cabina</t>
+          <t>altezze e distanze dagli angoli per l'accessibilità da verificare (DM 236/1989, UNI EN 81-70)</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>valori tipici: scelta del software</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>la cabina entra nel vano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I65" s="11" t="n"/>
@@ -3795,28 +3795,28 @@
       <c r="M65" s="11" t="n"/>
       <c r="N65" s="11" t="n"/>
     </row>
-    <row r="66" ht="108" customHeight="1">
+    <row r="66" ht="186" customHeight="1">
       <c r="A66" s="10" t="n">
         <v>64</v>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Vano: ingombri tipici</t>
+          <t>Vano: porte</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Contrappeso laterale</t>
+          <t>Imbotti della porta di piano (sostituzione con una luce più piccola)</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>tra la parete e la guida della cabina, centrato sull'asse delle guide di cabina, con le sue guide alle estremità (pattini 20 mm) e la guida di cabina su una staffa a ponte; a 40 mm dalle zone delle porte; lunghezza in pianta da 400 a 900 mm (sotto 400 mm: «Attenzione»); con il contrappeso sul fondo, al massimo la larghezza tra le guide della cabina</t>
+          <t>quando la porta nuova ha una luce più piccola del vano esistente tra i marmi, gli imbotti laterali (a sinistra e a destra guardando la porta dal pianerottolo) e quello superiore coprono la differenza: distanza tra i marmi = imbotto sinistro + luce + 2 × 50 mm di portale + imbotto destro; altezza sotto il marmo superiore = altezza della luce + 60 mm di architrave del portale + imbotto superiore (con il telaio proprio della porta, i suoi montanti e il suo frontalino al posto del portale); gli stessi imbotti per tutte le porte di piano, in lamiera sul filo del muro verso il pianerottolo, disegnati in pianta, in sezione e nel 3D</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>dato del fornitore delle porte (imbotti su misura)</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>lunghezza del contrappeso</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I66" s="11" t="n"/>
@@ -3841,33 +3841,33 @@
       <c r="M66" s="11" t="n"/>
       <c r="N66" s="11" t="n"/>
     </row>
-    <row r="67" ht="147" customHeight="1">
+    <row r="67" ht="316" customHeight="1">
       <c r="A67" s="10" t="n">
         <v>65</v>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Vano: ingombri tipici</t>
+          <t>Vano: porte</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Arcata a zaino (due accessi adiacenti a 90°)</t>
+          <t>Telaio proprio delle porte di piano</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>entrambe le guide di cabina sulla parete opposta all'accesso laterale, con le lame affacciate lungo la parete (il momento della cabina a sbalzo va sulle facce delle lame); piedi delle guide a 20 mm dentro la profondità della piattaforma; contrappeso tra le guide, contro la parete, con le sue guide alle estremità e i piedi a 70 mm da quelli delle guide di cabina (staffe); la cabina a 10 mm dalle bride che tengono i piedi delle guide sulle staffe (bride forgiate della misura della guida, con la piastra oltre il piede)</t>
+          <t>a scelta del progettista, al posto del portale (2 × 50 mm, architrave 60 mm): il telaio della porta, uguale a tutti i piani, per default il telaio standard con montanti da 120 mm a tutta altezza, frontalino da 220 mm sopra la luce tra i montanti e spessore 50 mm; montanti, frontalino e spessore modificabili su ogni progetto, montanti e frontalino da 25 mm (telai su misura). Il telaio sta tutto nel vano di corsa, contro la parete e sulla soglia: soglia e sospensione della porta sono fissate al telaio e le coppie Panev (sotto la soglia e sopra la sospensione) lo tengono alla parete; il vano nel muro è il suo ingombro esterno (luce + 2 montanti, altezza della luce + frontalino), gli imbotti stanno sul pavimento del pianerottolo. Lo spessore del telaio è dentro la profondità della porta di piano: le ante scorrono dietro il telaio, il binario più vicino alla parete (68 mm prima del bordo della soglia nelle porte telescopiche, 30 mm nelle centrali) almeno a filo del telaio, altrimenti «Attenzione» (si aumenta la profondità della porta di piano). Disegnato in pianta, in sezione e nel 3D; la bottoniera si misura dal bordo del vano nel muro</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>dato del fornitore delle porte</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (principio: cataloghi di arcate a zaino); disposizione da confermare con il fornitore dell'arcata</t>
+          <t>2SG, pagina del telaio standard (montanti 120, frontalino 220, spessore 50; lamiera autoportante 1/1,2 mm; montaggio sul pavimento finito, staffe e tasselli per il muro) e disegno del telaio (larghezza luce + 240) letti il 2 ottobre 2026; telai di dimensioni speciali con montanti e frontalino da 25 mm (research/argano-geared/14-porte-e-soglie.md, 18-porte-limitatori-tenditori-tutti.md). Il telaio nel vano di corsa con soglia e sospensione fissate, tenuto dalle coppie Panev, il vano nel muro della misura del telaio, lo spessore dentro la profondità della porta e gli imbotti sul pavimento del pianerottolo: indicazione del cliente (4 ottobre 2026)</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>le ante della porta di piano dietro il suo telaio</t>
         </is>
       </c>
       <c r="I67" s="11" t="n"/>
@@ -3887,7 +3887,7 @@
       <c r="M67" s="11" t="n"/>
       <c r="N67" s="11" t="n"/>
     </row>
-    <row r="68" ht="212" customHeight="1">
+    <row r="68" ht="199" customHeight="1">
       <c r="A68" s="10" t="n">
         <v>66</v>
       </c>
@@ -3898,22 +3898,22 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Nicchie nelle pareti del vano</t>
+          <t>Ingombri tipici nel vano (modificabili su ogni progetto) — pacchetto porta di catalogo (porta di cabina + gioco tra le soglie + porta di piano), da wittur.com: Hydra 210 mm a 2 ante telescopiche e 180 mm a 2 ante centrali, Hydra 3000 180 e 130, Augusta EVO 190 e 110, Sematic 2000 C-MOD 185 e 117, Fineline 115 e 85; Sematic 2000 B 255 e 165 (cabina 90 e 45, gioco 30, piano 135 e 90, da una copia della brochure). Con le porte scelte, i tre ingombri vanno portati alla somma del fornitore (oggi 80 + 30 + 80 = 190 mm)</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>contrappeso in nicchia: il contrappeso con le sue guide sta nella nicchia della parete su cui corre, con almeno 20 mm tra le guide e i fianchi della nicchia (con le staffe Panev, lo spazio della piastra del supporto dietro il piede di ogni guida); la distanza dalla parete si misura dal fondo della nicchia e la cabina guadagna la sua profondità, senza scendere sotto gli ingombri delle guide; luce del vano in nicchia: una nicchia alta 400 mm per lampada, le lampade 1500 mm sopra ogni piano e l'ultima a 80 mm sotto il solaio; canalina in nicchia: dal fondo della fossa al solaio; ogni nicchia dentro la sua parete, fuori dai telai delle porte di piano e dalle altre nicchie, con almeno 50 mm di muro dietro; altrimenti «Non conforme»</t>
+          <t>profondità della porta di piano 80 mm; gioco tra le soglie 30 mm; porta di cabina 80 mm; pareti della cabina 35 mm; guide e staffe della cabina 165 mm per lato; cabina–contrappeso 60 mm; spessore del contrappeso 140 mm; guide e staffe del contrappeso 80 mm; cabina–parete di fondo 60 mm; punta della guida–cabina 30 mm; contrappeso laterale–piede della guida di cabina 85 mm</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>dati del costruttore di guide, porte e cabina</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>scelta del software; la resistenza della parete con la nicchia va verificata dal progettista</t>
+          <t>valori tipici: scelta del software</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>nicchie nelle pareti</t>
+          <t>la cabina entra nel vano</t>
         </is>
       </c>
       <c r="I68" s="11" t="n"/>
@@ -3933,7 +3933,7 @@
       <c r="M68" s="11" t="n"/>
       <c r="N68" s="11" t="n"/>
     </row>
-    <row r="69" ht="329" customHeight="1">
+    <row r="69" ht="108" customHeight="1">
       <c r="A69" s="10" t="n">
         <v>67</v>
       </c>
@@ -3944,32 +3944,32 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Staffe delle guide del contrappeso (catalogo Panev)</t>
+          <t>Contrappeso laterale</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>per default il supporto Panev SU o SD con la guida SG, la guida serrata sulla flangia della SG da due bride N1: il supporto più corto il cui campo stampato prende la distanza della guida dalla parete (o dal fondo della nicchia) e la cui piastra sta sulla parete: SU, SD 150 e SD 220 lunghi 160 mm da 45 a 155 mm (SD 220 da 50), lunghi 180 mm da 45 a 195 mm, lunghi 200 mm da 45 a 215 mm; quando nessuno sta, vicino a un angolo, il supporto scorrevole SC sulla parete dietro il piede della guida con la SG lungo la parete: la flangia della SG da 2 mm oltre il bordo dell'SC fino a 70, 88, 130 e 140 mm dalla parete per SC 50, 60, 80 e 90, l'asse della guida entro il campo stampato da un'estremità dell'SC (lunghi 200 mm: 210, 213, 215 e 215 mm; lunghi 220 mm: 235, 235, 255 e 235 mm), fuori dai telai delle porte e dalle nicchie. Il progettista può scegliere l'articolo a mano (se non prende la guida: «Non conforme») o una soluzione su disegno esecutivo, SC 50 170 + SG 225 50 a misura o SN 60 65 + SN 65 200 + BRACCIO 160 190 all'angolo del vano: «Da verificare» sul disegno; nessuno adatto: «Non conforme» (si possono scegliere staffe generiche, da dimensionare a parte)</t>
+          <t>tra la parete e la guida della cabina, centrato sull'asse delle guide di cabina, con le sue guide alle estremità (pattini 20 mm) e la guida di cabina su una staffa a ponte; a 40 mm dalle zone delle porte; lunghezza in pianta da 400 a 900 mm (sotto 400 mm: «Attenzione»); con il contrappeso sul fondo, al massimo la larghezza tra le guide della cabina</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>catalogo staffe Panev 2026, pp. 20-62</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>catalogo del costruttore (panev/docs/catalogo-staffe-panev-2026.pdf); le corse dell'SC lontano dalla parete lette sui disegni di montaggio (pp. 41-55)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>staffe del catalogo per le guide del contrappeso</t>
+          <t>lunghezza del contrappeso</t>
         </is>
       </c>
       <c r="I69" s="11" t="n"/>
@@ -3979,7 +3979,7 @@
       <c r="M69" s="11" t="n"/>
       <c r="N69" s="11" t="n"/>
     </row>
-    <row r="70" ht="121" customHeight="1">
+    <row r="70" ht="147" customHeight="1">
       <c r="A70" s="10" t="n">
         <v>68</v>
       </c>
@@ -3990,22 +3990,22 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Staffe delle porte di piano (catalogo Panev)</t>
+          <t>Arcata a zaino (due accessi adiacenti a 90°)</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>sotto ogni soglia di piano la coppia A + B della stessa sezione (65, 45 o 37 mm: le serie non sono intercambiabili): per default A 65 170 7 + B 65 320 (5 mm, regolazione ±8°), oppure quella scelta dal progettista; la piastra A tagliata alla profondità della soglia, 4 mm prima del suo bordo (se la piastra è più corta della soglia: da verificare); una coppia ogni 400 mm della luce, almeno tre, le estreme a 10 mm dai bordi della luce</t>
+          <t>entrambe le guide di cabina sulla parete opposta all'accesso laterale, con le lame affacciate lungo la parete (il momento della cabina a sbalzo va sulle facce delle lame); piedi delle guide a 20 mm dentro la profondità della piattaforma; contrappeso tra le guide, contro la parete, con le sue guide alle estremità e i piedi a 70 mm da quelli delle guide di cabina (staffe); la cabina a 10 mm dalle bride che tengono i piedi delle guide sulle staffe (bride forgiate della misura della guida, con la piastra oltre il piede)</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>catalogo staffe Panev 2026, pp. 14-18 (coppie) e p. 05 (taglio della piastra)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>catalogo del costruttore (panev/docs/catalogo-staffe-panev-2026.pdf); il passo e il numero minimo sono scelta del software</t>
+          <t>scelta del software (principio: cataloghi di arcate a zaino); disposizione da confermare con il fornitore dell'arcata</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
@@ -4025,7 +4025,7 @@
       <c r="M70" s="11" t="n"/>
       <c r="N70" s="11" t="n"/>
     </row>
-    <row r="71" ht="355" customHeight="1">
+    <row r="71" ht="212" customHeight="1">
       <c r="A71" s="10" t="n">
         <v>69</v>
       </c>
@@ -4036,32 +4036,32 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Limitatore di velocità e tenditore (pianta, locale macchina, 3D) — il disegno unico delle LK200–LK315 dà due altezze non spiegate (230 e 415 mm; un rivenditore scrive 370): è presa la maggiore. Per Bode la velocità nominale massima è nostra: la velocità di scatto massima diviso 1,15 (scatto ≥ 115 % della nominale), del GB 8 con 1,49 m/s del disegno invece dei 2,04 della brochure. Per le RQ-A e le RC Montanari 0,15–3,0 e 1,60–4,2 m/s sono i campi della famiglia: il limite di ogni taglia va letto sul manuale. Delle basi pubblicate non sempre è detto quale lato stia nel piano della puleggia (il lato lungo è disegnato in quel piano, come nel LK200). Tenditore a leva: lungo 700 mm (quota «A» del PFB R4KE per LK200 in un listino di rivenditore, senza definizione), puleggia a 255 mm dalla cerniera e blocco di 150 × 185 mm: scelte del software; le masse di 22 e 44 kg sono quelle delle tabelle PFB (tenditori R4K e R4R per LK200, confermate dalla brochure)</t>
+          <t>Nicchie nelle pareti del vano</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>per velocità il più piccolo PFB che la regge: LK200 (Ø 200, fune 6) fino a 1,48 m/s, LK250 fino a 1,74, LK300 fino a 2,93, R12BF fino a 4,00; oppure il modello scelto se regge la velocità: PFB (LX, LK, R1, R3LR, R5, R6, R10BF), Bode (GB 7 fino a 2,98 m/s, GB 8 fino a 1,29), Dynatech (VEGA 200 fino a 2,40), Wittur (OL20 fino a 1,75, OL35 fino a 3,00, EOS fino a 2,50, OL100 fino a 10,00) o Montanari (RQ-A 200, 250 e 300, RC 200 e 300, NOR fino a 1,50 m/s, RG 200 fino a 0,30). Con le quote dei disegni dei costruttori (altezza totale, tra parentesi l'asse dalla base): LK200, LK250, LK300 e LK315 415 (165) su base 220 × 165 (LK315 220 × 130); LX120 178 (70,5), LK120 270 (71), LX150 274 (86), LX180 322 (107), LX200 349 (110); R1 344 (190,5) su base 285 × 80; R3LR 348 (157); R5 261 (120); R6 335 (168); R10BF 488 (303) su base 460 × 196; R12BF 524 (337) su base 520 × 116; Bode GB 7 360 (205) e GB 8 315 (205); Dynatech VEGA 200 332 (199,5); Wittur e Montanari nelle proporzioni del software (Ø 200: alto 370, asse a 240). Tenditore in fossa sulla guida di cabina: a leva con 22 kg (come PFB R4K) o verticale con 44 kg (come PFB R4R)</t>
+          <t>contrappeso in nicchia: il contrappeso con le sue guide sta nella nicchia della parete su cui corre, con almeno 20 mm tra le guide e i fianchi della nicchia (con le staffe Panev, lo spazio della piastra del supporto dietro il piede di ogni guida); la distanza dalla parete si misura dal fondo della nicchia e la cabina guadagna la sua profondità, senza scendere sotto gli ingombri delle guide; luce del vano in nicchia: una nicchia alta 400 mm per lampada, le lampade 1500 mm sopra ogni piano e l'ultima a 80 mm sotto il solaio; canalina in nicchia: dal fondo della fossa al solaio; ogni nicchia dentro la sua parete, fuori dai telai delle porte di piano e dalle altre nicchie, con almeno 50 mm di muro dietro; altrimenti «Non conforme»</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>dati del fornitore del limitatore</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>manuali d'uso PFB con i disegni quotati (download.pfb.it), brochure Bode e Wittur, manuale Dynatech VEGA e disegni Bode in copia presso un rivenditore (elevatorequipment.co.uk), letti il 2 ottobre 2026; basi delle LK da un listino di rivenditore; Montanari da estratti di ricerca del 1° ottobre 2026 (research/argano-geared/18-porte-limitatori-tenditori-tutti.md)</t>
+          <t>scelta del software; la resistenza della parete con la nicchia va verificata dal progettista</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>nicchie nelle pareti</t>
         </is>
       </c>
       <c r="I71" s="11" t="n"/>
@@ -4071,43 +4071,43 @@
       <c r="M71" s="11" t="n"/>
       <c r="N71" s="11" t="n"/>
     </row>
-    <row r="72" ht="82" customHeight="1">
+    <row r="72" ht="329" customHeight="1">
       <c r="A72" s="10" t="n">
         <v>70</v>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Spazi di rifugio sul tetto di cabina e in fossa</t>
+          <t>Staffe delle guide del contrappeso (catalogo Panev)</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>tipo 1 (in piedi) 400 × 500 mm in pianta, alto 2000 mm; tipo 2 (accucciato) 500 × 700 mm, alto 1000 mm; tipo 3 (disteso, solo in fossa) 700 × 1000 mm, alto 500 mm; in testata con la cabina nella posizione più alta, in fossa con la cabina sugli ammortizzatori compressi</t>
+          <t>per default il supporto Panev SU o SD con la guida SG, la guida serrata sulla flangia della SG da due bride N1: il supporto più corto il cui campo stampato prende la distanza della guida dalla parete (o dal fondo della nicchia) e la cui piastra sta sulla parete: SU, SD 150 e SD 220 lunghi 160 mm da 45 a 155 mm (SD 220 da 50), lunghi 180 mm da 45 a 195 mm, lunghi 200 mm da 45 a 215 mm; quando nessuno sta, vicino a un angolo, il supporto scorrevole SC sulla parete dietro il piede della guida con la SG lungo la parete: la flangia della SG da 2 mm oltre il bordo dell'SC fino a 70, 88, 130 e 140 mm dalla parete per SC 50, 60, 80 e 90, l'asse della guida entro il campo stampato da un'estremità dell'SC (lunghi 200 mm: 210, 213, 215 e 215 mm; lunghi 220 mm: 235, 235, 255 e 235 mm), fuori dai telai delle porte e dalle nicchie. Il progettista può scegliere l'articolo a mano (se non prende la guida: «Non conforme») o una soluzione su disegno esecutivo, SC 50 170 + SG 225 50 a misura o SN 60 65 + SN 65 200 + BRACCIO 160 190 all'angolo del vano: «Da verificare» sul disegno; nessuno adatto: «Non conforme» (si possono scegliere staffe generiche, da dimensionare a parte)</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1 (Tabella 3)</t>
+          <t>catalogo staffe Panev 2026, pp. 20-62</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>catalogo del costruttore (panev/docs/catalogo-staffe-panev-2026.pdf); le corse dell'SC lontano dalla parete lette sui disegni di montaggio (pp. 41-55)</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>spazio di rifugio in testata; spazio di rifugio in fossa</t>
+          <t>staffe del catalogo per le guide del contrappeso</t>
         </is>
       </c>
       <c r="I72" s="11" t="n"/>
@@ -4117,43 +4117,43 @@
       <c r="M72" s="11" t="n"/>
       <c r="N72" s="11" t="n"/>
     </row>
-    <row r="73" ht="56" customHeight="1">
+    <row r="73" ht="407" customHeight="1">
       <c r="A73" s="10" t="n">
         <v>71</v>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Posizione più alta della cabina</t>
+          <t>Staffe delle porte di piano (catalogo Panev)</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>contrappeso sugli ammortizzatori completamente compressi, più il salto 0,035·v² m (v velocità nominale)</t>
+          <t>sotto ogni soglia di piano la coppia A + B della stessa sezione (65, 45 o 37 mm: le serie non sono intercambiabili): per default A 65 170 7 + B 65 320 (5 mm, regolazione ±8°), oppure quella scelta dal progettista; la piastra A tagliata alla profondità della soglia, 4 mm prima del suo bordo (se la piastra è più corta della soglia: da verificare); una coppia ogni 400 mm della luce, almeno tre, le estreme a 10 mm dai bordi della luce. Sopra ogni porta di piano la stessa coppia capovolta: B sulla parete sopra il vano con lo snodo in basso, la sospensione della porta appesa sotto la piattaforma di A con bulloni nei suoi fori, A tagliata come sotto la soglia; una coppia ogni 400 mm lungo la sospensione (la corsa delle ante e 30 mm per parte), almeno tre, le estreme a 10 mm dalle sue estremità; se le coppie della soglia del piano sopra arrivano alla stessa altezza, quella che cadrebbe su una di esse si sposta accanto (la faccia di B e 10 mm), dentro la sospensione. Con il telaio proprio della porta le coppie tengono il telaio, a cui sono fissate soglia e sospensione (porte.telaio). B vuole il muro dalla sommità della sospensione (230 mm sopra la luce) in su: se il vano nel muro (telaio o marmi) sale più in alto, o la coppia arriva alla soglia del piano sopra, a quel piano le coppie sopra la porta non sono poste né contate, e la verifica lo segnala come «Attenzione» (il fissaggio della sospensione va definito con il costruttore della porta)</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.6.1 (Tabella 2)</t>
+          <t>catalogo staffe Panev 2026, pp. 14-18 (coppie), p. 05 (taglio della piastra) e p. 04 (soglia o elemento portante della porta di piano)</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>catalogo del costruttore (panev/docs/catalogo-staffe-panev-2026.pdf); il passo, il numero minimo, il montaggio capovolto sopra la porta e lo spostamento sono scelta del software (il montaggio sopra la porta va confermato con il costruttore della porta)</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>spazio di rifugio in testata; distanze libere dal soffitto</t>
+          <t>staffe Panev sopra le porte di piano: muro tra il vano della porta e la soglia del piano sopra</t>
         </is>
       </c>
       <c r="I73" s="11" t="n"/>
@@ -4163,43 +4163,43 @@
       <c r="M73" s="11" t="n"/>
       <c r="N73" s="11" t="n"/>
     </row>
-    <row r="74" ht="56" customHeight="1">
+    <row r="74" ht="355" customHeight="1">
       <c r="A74" s="10" t="n">
         <v>72</v>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Distanze libere dal soffitto con la cabina nella posizione più alta</t>
+          <t>Limitatore di velocità e tenditore (pianta, locale macchina, 3D) — il disegno unico delle LK200–LK315 dà due altezze non spiegate (230 e 415 mm; un rivenditore scrive 370): è presa la maggiore. Per Bode la velocità nominale massima è nostra: la velocità di scatto massima diviso 1,15 (scatto ≥ 115 % della nominale), del GB 8 con 1,49 m/s del disegno invece dei 2,04 della brochure. Per le RQ-A e le RC Montanari 0,15–3,0 e 1,60–4,2 m/s sono i campi della famiglia: il limite di ogni taglia va letto sul manuale. Delle basi pubblicate non sempre è detto quale lato stia nel piano della puleggia (il lato lungo è disegnato in quel piano, come nel LK200). Tenditore a leva: lungo 700 mm (quota «A» del PFB R4KE per LK200 in un listino di rivenditore, senza definizione), puleggia a 255 mm dalla cerniera e blocco di 150 × 185 mm: scelte del software; le masse di 22 e 44 kg sono quelle delle tabelle PFB (tenditori R4K e R4R per LK200, confermate dalla brochure)</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>≥ 500 mm sopra le apparecchiature sul tetto di cabina (operatore); ≥ 100 mm sopra pattini, attacchi delle funi e traversa dell'arcata; ≥ 300 mm sopra il corrimano della balaustra</t>
+          <t>per velocità il più piccolo PFB che la regge: LK200 (Ø 200, fune 6) fino a 1,48 m/s, LK250 fino a 1,74, LK300 fino a 2,93, R12BF fino a 4,00; oppure il modello scelto se regge la velocità: PFB (LX, LK, R1, R3LR, R5, R6, R10BF), Bode (GB 7 fino a 2,98 m/s, GB 8 fino a 1,29), Dynatech (VEGA 200 fino a 2,40), Wittur (OL20 fino a 1,75, OL35 fino a 3,00, EOS fino a 2,50, OL100 fino a 10,00) o Montanari (RQ-A 200, 250 e 300, RC 200 e 300, NOR fino a 1,50 m/s, RG 200 fino a 0,30). Con le quote dei disegni dei costruttori (altezza totale, tra parentesi l'asse dalla base): LK200, LK250, LK300 e LK315 415 (165) su base 220 × 165 (LK315 220 × 130); LX120 178 (70,5), LK120 270 (71), LX150 274 (86), LX180 322 (107), LX200 349 (110); R1 344 (190,5) su base 285 × 80; R3LR 348 (157); R5 261 (120); R6 335 (168); R10BF 488 (303) su base 460 × 196; R12BF 524 (337) su base 520 × 116; Bode GB 7 360 (205) e GB 8 315 (205); Dynatech VEGA 200 332 (199,5); Wittur e Montanari nelle proporzioni del software (Ø 200: alto 370, asse a 240). Tenditore in fossa sulla guida di cabina: a leva con 22 kg (come PFB R4K) o verticale con 44 kg (come PFB R4R)</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.2</t>
+          <t>dati del fornitore del limitatore; dalla norma solo lo scatto ≥ 115 % della velocità nominale (UNI EN 81-20:2020, 5.6.2.2.1.1 a))</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>manuali d'uso PFB con i disegni quotati (download.pfb.it), brochure Bode e Wittur, manuale Dynatech VEGA e disegni Bode in copia presso un rivenditore (elevatorequipment.co.uk), letti il 2 ottobre 2026; basi delle LK da un listino di rivenditore; Montanari da estratti di ricerca del 1° ottobre 2026 (research/argano-geared/18-porte-limitatori-tenditori-tutti.md)</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>distanze libere dal soffitto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I74" s="11" t="n"/>
@@ -4209,7 +4209,7 @@
       <c r="M74" s="11" t="n"/>
       <c r="N74" s="11" t="n"/>
     </row>
-    <row r="75" ht="56" customHeight="1">
+    <row r="75" ht="82" customHeight="1">
       <c r="A75" s="10" t="n">
         <v>73</v>
       </c>
@@ -4220,32 +4220,32 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Distanze in fossa con la cabina sugli ammortizzatori compressi</t>
+          <t>Spazi di rifugio sul tetto di cabina e in fossa</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>≥ 500 mm dal pavimento della fossa alle parti più basse della cabina; grembiule alto ≥ 750 mm sotto la soglia di cabina, con ≥ 100 mm liberi dal pavimento della fossa</t>
+          <t>tipo 1 (in piedi) 400 × 500 mm in pianta, alto 2000 mm; tipo 2 (accucciato) 500 × 700 mm, alto 1000 mm; tipo 3 (disteso, solo in fossa) 700 × 1000 mm, alto 500 mm; in testata con la cabina nella posizione più alta, in fossa con la cabina sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.8.2 e 5.4.5</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1 (Prospetto 3) e 5.2.5.8.1 (Prospetto 4)</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 37–40</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>spazio di rifugio in fossa; grembiule sugli ammortizzatori compressi</t>
+          <t>spazio di rifugio in testata; spazio di rifugio in fossa</t>
         </is>
       </c>
       <c r="I75" s="11" t="n"/>
@@ -4255,7 +4255,7 @@
       <c r="M75" s="11" t="n"/>
       <c r="N75" s="11" t="n"/>
     </row>
-    <row r="76" ht="56" customHeight="1">
+    <row r="76" ht="95" customHeight="1">
       <c r="A76" s="10" t="n">
         <v>74</v>
       </c>
@@ -4266,32 +4266,32 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Balaustra sul tetto di cabina</t>
+          <t>Posizione più alta della cabina — vale per gli ascensori a frizione; le riduzioni di 5.2.5.6.1.2 (rallentamento controllato) e 5.2.5.6.1.3 (puleggia tenditrice con antirimbalzo) non sono usate: la verifica è più severa</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>richiesta se la distanza libera dal tetto alla parete supera 300 mm: alta 700 mm fino a 500 mm di distanza, 1100 mm oltre</t>
+          <t>contrappeso sugli ammortizzatori completamente compressi, più il salto 0,035·v² m (v velocità nominale)</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.7.4</t>
+          <t>UNI EN 81-20:2020, 5.2.5.6.1.1 (Prospetto 2)</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 36</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>balaustra sul tetto di cabina</t>
+          <t>spazio di rifugio in testata; distanze libere dal soffitto</t>
         </is>
       </c>
       <c r="I76" s="11" t="n"/>
@@ -4301,7 +4301,7 @@
       <c r="M76" s="11" t="n"/>
       <c r="N76" s="11" t="n"/>
     </row>
-    <row r="77" ht="56" customHeight="1">
+    <row r="77" ht="147" customHeight="1">
       <c r="A77" s="10" t="n">
         <v>75</v>
       </c>
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Superficie dove una persona può stare sul tetto di cabina</t>
+          <t>Distanze libere dal soffitto con la cabina nella posizione più alta — I valori 500, 100 e 300 mm sono confermati. Da concordare con l'organismo: il software dà alla traversa dell'arcata i 100 mm di b) (il testo nomina traversa o architrave e parti di porte verticali; se non vale per l'arcata servono i 500 mm di a)); non verifica i 500 mm in obliquo oltre i 400 mm dal corrimano (c) 2)).</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>area continua ≥ 0,12 m² con il lato minore ≥ 250 mm (disegnata 400 × 300 mm, modificabile sulla pianta in testata); sopra di essa deve esserci l'altezza dello spazio di rifugio</t>
+          <t>≥ 500 mm sopra le apparecchiature sul tetto di cabina (operatore); ≥ 100 mm sopra pattini, attacchi delle funi e traversa dell'arcata; ≥ 300 mm sopra il corrimano della balaustra</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.3</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.2 a)–c)</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 38</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>superficie per stare sul tetto di cabina</t>
+          <t>distanze libere dal soffitto</t>
         </is>
       </c>
       <c r="I77" s="11" t="n"/>
@@ -4347,7 +4347,7 @@
       <c r="M77" s="11" t="n"/>
       <c r="N77" s="11" t="n"/>
     </row>
-    <row r="78" ht="69" customHeight="1">
+    <row r="78" ht="108" customHeight="1">
       <c r="A78" s="10" t="n">
         <v>76</v>
       </c>
@@ -4358,32 +4358,32 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Schermo del contrappeso in fossa</t>
+          <t>Parte più alta della cabina sotto ciò che pende sopra — fino alla versione 1.17.0 del motore del progetto la puleggia di cabina era verificata a 100 mm; i 100 mm della traversa sono la stessa lettura di spazi.testata.parti</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>dal punto più basso del contrappeso sugli ammortizzatori compressi fino ad almeno 2000 mm sopra il pavimento della fossa (altezza dello schermo modificabile sul progetto, mai sotto questo valore)</t>
+          <t>con la cabina nella posizione più alta: a 2:1 la puleggia di cabina (Dp + 30 mm sopra la traversa) è un'apparecchiatura sul tetto, distanza libera ≥ 500 mm dal soffitto o dalle pulegge appese; a 1:1 con la macchina in basso la traversa sotto le pulegge appese al solaio (asse a Dp/2 + 120 mm sotto il soffitto), distanza libera ≥ 100 mm, quella della traversa</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.5.1</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.2 a) e b)</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 38</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>protezione del contrappeso in fossa</t>
+          <t>parte più alta della cabina sotto ciò che pende sopra</t>
         </is>
       </c>
       <c r="I78" s="11" t="n"/>
@@ -4393,7 +4393,7 @@
       <c r="M78" s="11" t="n"/>
       <c r="N78" s="11" t="n"/>
     </row>
-    <row r="79" ht="69" customHeight="1">
+    <row r="79" ht="134" customHeight="1">
       <c r="A79" s="10" t="n">
         <v>77</v>
       </c>
@@ -4404,32 +4404,32 @@
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori ad accumulo di energia lineari (molle)</t>
+          <t>Ammortizzatori e spazio di rifugio in fossa, in pianta</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>ammessi fino a 1 m/s; corsa ≥ 0,135·v² m e comunque ≥ 65 mm; extracorsa della cabina e del contrappeso ≥ 0 (nessun minimo nella norma)</t>
+          <t>lo spazio di rifugio in fossa resta libero dagli ammortizzatori di cabina: il software lo mette sotto il centro della cabina o, se un piatto vi entra, nel posto libero più vicino sotto l'interno della cabina; due o più ammortizzatori di cabina a 160 mm dai fianchi della piattaforma, più in fuori finché i piatti escono dalla pianta del rifugio, sempre sotto la piattaforma; la verifica vale anche per quelli messi dal software (margine ≥ 0)</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2 (accumulo di energia, caratteristica lineare; sottoclausola da verificare sul testo)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.8.1</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>scelta del software sul modello della fossa (posizioni tipiche, da confermare con i dati del fornitore degli ammortizzatori)</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso; extracorsa di cabina e contrappeso</t>
+          <t>ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
         </is>
       </c>
       <c r="I79" s="11" t="n"/>
@@ -4439,7 +4439,7 @@
       <c r="M79" s="11" t="n"/>
       <c r="N79" s="11" t="n"/>
     </row>
-    <row r="80" ht="121" customHeight="1">
+    <row r="80" ht="82" customHeight="1">
       <c r="A80" s="10" t="n">
         <v>78</v>
       </c>
@@ -4450,32 +4450,32 @@
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori ad accumulo di energia non lineari (tamponi in poliuretano)</t>
+          <t>Distanze in fossa con la cabina sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>ammessi fino a 1 m/s come le molle; nessuna corsa minima da formula: il campo di masse del certificato di esame di tipo per la velocità deve comprendere, per ogni tampone, la cabina vuota e a pieno carico (o il contrappeso); «completamente compresso» vuol dire compresso del 90 % dell'altezza, quindi la corsa è 0,9·H negli spazi in fossa e in testata; tampone tipico alti 80 mm (P+S Diepocell D, Ø da 80 a 220 mm; ACLA AUTAN XL)</t>
+          <t>≥ 500 mm dal pavimento della fossa alle parti più basse della cabina; grembiule sotto la soglia di cabina: tratto verticale ≥ 750 mm, poi uno smusso a ≥ 60° sull'orizzontale con proiezione orizzontale ≥ 20 mm (circa 35 mm più in basso), con ≥ 100 mm liberi dal pavimento della fossa</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2 (caratteristica non lineare) e UNI EN 81-50:2020, 5.5 (esame di tipo); sottoclausole da verificare sul testo</t>
+          <t>UNI EN 81-20:2020, 5.2.5.8.2 a) e 5.4.5.1–5.4.5.2</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>cataloghi P+S Diepocell (wwlift.de), ACLA AUTAN XL (acla.de), Stingl (corsa al 90 %); estratti di ricerca del 1° ottobre 2026</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 40–41, 69</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso</t>
+          <t>spazio di rifugio in fossa; grembiule sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="I80" s="11" t="n"/>
@@ -4485,7 +4485,7 @@
       <c r="M80" s="11" t="n"/>
       <c r="N80" s="11" t="n"/>
     </row>
-    <row r="81" ht="95" customHeight="1">
+    <row r="81" ht="108" customHeight="1">
       <c r="A81" s="10" t="n">
         <v>79</v>
       </c>
@@ -4496,32 +4496,32 @@
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori a dissipazione di energia (idraulici)</t>
+          <t>Balaustra sul tetto di cabina — fino alla versione 2.12.0 del motore del vano il software misurava i 500 mm dal bordo del tetto; la norma vuole la balaustra entro 150 mm dal bordo: se è più interna, la distanza cresce e può servire l'altezza maggiore</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>a ogni velocità; corsa ≥ 0,0674·v² m (arresto per gravità al 115 % della velocità nominale); la corsa ridotta con il controllo del rallentamento non è considerata; ammortizzatori tipici: Oleo LSB10 fino a 1 m/s, alto 222,2 mm con corsa 73,4 mm; LSB16 fino a 1,6 m/s, alto 485,5 mm con corsa 173,5 mm</t>
+          <t>richiesta se dal bordo esterno del tetto alla parete ci sono più di 300 mm; alta 700 mm se dal bordo interno del corrimano alla parete ci sono fino a 500 mm, 1100 mm oltre; il corrimano (30 mm) con la faccia esterna a 100 mm dal bordo del tetto, come nel 3D</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2 (dissipazione di energia; sottoclausola da verificare sul testo)</t>
+          <t>UNI EN 81-20:2020, 5.4.7.2 b) e 5.4.7.4 b)–c)</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>catalogo Oleo LSB e SEB (oleo.co.uk), estratti di ricerca del 1° ottobre 2026</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 70–72</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso</t>
+          <t>balaustra sul tetto di cabina</t>
         </is>
       </c>
       <c r="I81" s="11" t="n"/>
@@ -4531,43 +4531,43 @@
       <c r="M81" s="11" t="n"/>
       <c r="N81" s="11" t="n"/>
     </row>
-    <row r="82" ht="69" customHeight="1">
+    <row r="82" ht="56" customHeight="1">
       <c r="A82" s="10" t="n">
         <v>80</v>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Superficie dove una persona può stare sul tetto di cabina</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>altezza libera delle zone di lavoro ≥ 2100 mm (1800 mm sui percorsi); davanti al quadro una superficie libera profonda ≥ 700 mm e larga ≥ 500 mm o quanto il quadro; porta di accesso ≥ 600 × 2000 mm</t>
+          <t>area continua ≥ 0,12 m² con il lato minore oltre 250 mm (disegnata 400 × 300 mm, modificabile sulla pianta in testata); sopra di essa deve esserci l'altezza dello spazio di rifugio</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.6.3.2.1 e 5.2.3</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.3</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 39</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>altezza del locale macchina; superficie libera davanti al quadro; porta del locale macchina</t>
+          <t>superficie per stare sul tetto di cabina</t>
         </is>
       </c>
       <c r="I82" s="11" t="n"/>
@@ -4577,43 +4577,43 @@
       <c r="M82" s="11" t="n"/>
       <c r="N82" s="11" t="n"/>
     </row>
-    <row r="83" ht="69" customHeight="1">
+    <row r="83" ht="212" customHeight="1">
       <c r="A83" s="10" t="n">
         <v>81</v>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Illuminazione del vano e del locale del macchinario</t>
+          <t>Altezza libera degli accessi e della cabina — negli impianti esistenti (DPR 1497/1963, artt. 24, 27 e 29, non riletto) le porte possono essere alte 1,90 m e la cabina 2,00 m; con la sola sostituzione della macchina le altezze restano (parti esistenti); la UNI 10411-1:2024 ammette porte di piano nuove non più basse delle esistenti (19.1), una cabina nuova sotto 2 m se non più bassa dell'esistente e mai sotto 1,90 m (22 m)) e accessi di cabina mai sotto 1,80 m (22 n)), con avvertimenti: il software non conosce le esistenti e segnala ogni porta sotto 2000 mm</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>vano: illuminazione fissa di almeno 50 lux a 1 m sopra il tetto della cabina e sopra il pavimento della fossa, 20 lux altrove; locale del macchinario: almeno 200 lux al pavimento nelle zone di lavoro</t>
+          <t>luce netta in altezza delle porte di piano e di cabina ≥ 2000 mm; altezza libera interna della cabina ≥ 2000 mm</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.4</t>
+          <t>UNI EN 81-20:2020, 5.3.2.1 e 5.4.1</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 49, 63; 2 m anche in DM 587/1987 (UNI EN 81-1), 7.3.1, 8.1.1 e 8.1.2</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>altezza libera degli accessi; altezza libera interna della cabina</t>
         </is>
       </c>
       <c r="I83" s="11" t="n"/>
@@ -4623,43 +4623,43 @@
       <c r="M83" s="11" t="n"/>
       <c r="N83" s="11" t="n"/>
     </row>
-    <row r="84" ht="56" customHeight="1">
+    <row r="84" ht="108" customHeight="1">
       <c r="A84" s="10" t="n">
         <v>82</v>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Temperatura dei locali del macchinario e degli armadi</t>
+          <t>Corsa guidata del contrappeso in testata</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>temperatura ambiente mantenuta tra +5 °C e +40 °C: ipotesi della norma, da garantire nell'edificio</t>
+          <t>con la cabina sugli ammortizzatori completamente compressi le guide del contrappeso lo guidano ancora per almeno 0,1 + 0,035·v² m (v velocità nominale): dalla sommità del contrappeso, salito della corsa sotto la cabina (extracorsa e corsa degli ammortizzatori), alla sommità delle guide, che il software pone 50 mm sotto la soletta (voce foglio.stime)</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, introduzione (ipotesi)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.6.2 e 5.2.5.6.1.1 (Prospetto 2: cabina sugli ammortizzatori compressi più 0,035·v²); stesso valore in UNI EN 81-1 (1999, 2008), 5.7.1.2</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 36; UNI EN 81-1:2008, testo della norma fornito dal cliente, letto il 2026-10-06, p. 27</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>corsa guidata del contrappeso in testata</t>
         </is>
       </c>
       <c r="I84" s="11" t="n"/>
@@ -4669,43 +4669,43 @@
       <c r="M84" s="11" t="n"/>
       <c r="N84" s="11" t="n"/>
     </row>
-    <row r="85" ht="225" customHeight="1">
+    <row r="85" ht="95" customHeight="1">
       <c r="A85" s="10" t="n">
         <v>83</v>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Basamento dell'argano</t>
+          <t>Schermo del contrappeso in fossa — non verificati: il bordo inferiore dello schermo a non più di 300 mm dal fondo della fossa (5.2.5.5.1 c)) e la protezione dello spazio oltre 300 mm tra guide del contrappeso e parete (e))</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>su spessori di livellamento sotto gli appoggi (l'asse della puleggia dove lo mette il software), su telaio di due profilati sul pavimento (tipico UPN 200, alto quanto il profilato come i telai bassi universali), su due putrelle da muro a muro che possono stare sollevate dal pavimento (tipiche IPE 200, appoggio nei muri 150 mm), su piastre d'acciaio sotto gli appoggi (tipiche 20 mm) o su plinto in calcestruzzo (tipico 250 mm), o — con un rinvio — sul telaio con rinvio (locale.rinvio); tamponi antivibranti di 30 mm sotto gli appoggi, salvo sugli spessori e sul telaio con rinvio (antivibranti sotto le gambe); telaio e plinto 100 mm oltre il telaio dell'argano a ogni estremità; l'altezza del basamento porta l'asse della puleggia, che il calcolo (tratto di fune oltre la corsa) e il 3D seguono</t>
+          <t>dal punto più basso del contrappeso sugli ammortizzatori compressi fino ad almeno 2000 mm sopra il pavimento della fossa (altezza dello schermo modificabile sul progetto, mai sotto questo valore)</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio); scelta del costruttore</t>
+          <t>UNI EN 81-20:2020, 5.2.5.5.1 b)</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>telaio basso universale per argano alto 200 mm (lift-store.it); tamponi antivibranti 25–30 mm (catalogo Donati); piastre di 20 mm e plinto di 250–300 mm nella pratica di installazione (fonti estere, da confermare); estratti di ricerca del 1° ottobre 2026</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 35</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>protezione del contrappeso in fossa</t>
         </is>
       </c>
       <c r="I85" s="11" t="n"/>
@@ -4715,43 +4715,43 @@
       <c r="M85" s="11" t="n"/>
       <c r="N85" s="11" t="n"/>
     </row>
-    <row r="86" ht="147" customHeight="1">
+    <row r="86" ht="95" customHeight="1">
       <c r="A86" s="10" t="n">
         <v>84</v>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Telaio sotto l'argano di un costruttore</t>
+          <t>Ammortizzatori ad accumulo di energia lineari (molle)</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>l'argano di catalogo poggia con i suoi piedi su un telaio di due travi sotto le file di fori, con antivibranti alle estremità e 40 mm oltre l'argano a ogni estremità; il telaio è alto quanto serve per tenere l'asse della puleggia dove lo tiene l'argano generico del software, almeno 80 mm e con il bordo della puleggia 30 mm sopra il suo piano d'appoggio (gli argani compatti hanno la puleggia a sbalzo, sotto il piano dei piedi); se l'argano non lo permette l'asse sale e il calcolo segue</t>
+          <t>ammessi fino a 1 m/s; corsa ≥ 0,135·v² m e comunque ≥ 65 mm; extracorsa della cabina e del contrappeso ≥ 0 (nessun minimo nella norma)</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.8.1.5 (fino a 1 m/s) e 5.8.2.1.1.1 (corsa); nessuna extracorsa minima in metri: l'interruttore di extracorsa interviene prima che la cabina o il contrappeso tocchino gli ammortizzatori (5.12.2.1)</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>quote dei piedi, dei fori e dell'asse della puleggia dalle schede tecniche del costruttore; altezza del telaio scelta dal software, da adattare al telaio fornito</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 98, 131</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso; extracorsa di cabina e contrappeso</t>
         </is>
       </c>
       <c r="I86" s="11" t="n"/>
@@ -4761,43 +4761,43 @@
       <c r="M86" s="11" t="n"/>
       <c r="N86" s="11" t="n"/>
     </row>
-    <row r="87" ht="303" customHeight="1">
+    <row r="87" ht="134" customHeight="1">
       <c r="A87" s="10" t="n">
         <v>85</v>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Puleggia di rinvio nel locale del macchinario</t>
+          <t>Ammortizzatori ad accumulo di energia non lineari (tamponi in poliuretano) — il tampone tipico alto 80 mm è un dato di catalogo, non della norma: va sostituito con quello montato</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>con l'argano in alto il rinvio sta sempre nel locale del macchinario, mai nel vano: nel telaio dell'argano (il basamento che il software prende quando c'è un rinvio), con l'asse del rinvio a 320 mm dal pavimento (il bordo almeno 60 mm sopra il pavimento: Dp/2 + 60 oltre Ø 520), il piano del telaio a 736 mm (almeno 176 mm sopra il rinvio), gambe di tubo quadro da 80 mm su antivibranti da 28 mm, travi UPN 160, 100 mm oltre l'argano e il rinvio a ogni estremità, largo almeno 655 mm; con un argano SICOR che ha il suo telaio a catalogo (SV110 e SH110B XTE0517/XTE0516, SH130 e SH130G XTE3022/XTE3023, SH140 XTE6026/XTE6027, SH160 XTE5708, SH190 XTE3988) le quote del costruttore: asse del rinvio, asse della puleggia (A), piano del telaio (A − B), calata del contrappeso entro L max dall'asse della puleggia (verifica di avvertimento: oltre, telaio su misura); h del calcolo = asse della puleggia − asse del rinvio, dx dalla pianta; con un altro basamento scelto il rinvio sta su un supporto proprio sul pavimento, alla stessa altezza; una h inserita a mano che porta il rinvio sotto il pavimento è segnalata</t>
+          <t>ammessi fino a 1 m/s come le molle; nessuna corsa minima da formula: il campo di masse del certificato di esame di tipo per la velocità deve comprendere, per ogni tampone, la cabina vuota e a pieno carico (o il contrappeso); «completamente compresso» vuol dire compresso del 90 % dell'altezza, quindi la corsa è 0,9·H negli spazi in fossa e in testata; tampone tipico alti 80 mm (P+S Diepocell D, Ø da 80 a 220 mm; ACLA AUTAN XL)</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>regola del committente (Panev): il rinvio sta nel telaio del locale macchine, mai nel vano; UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio)</t>
+          <t>UNI EN 81-20:2020, 5.8.1.5, 5.8.1.7, 5.8.2.1.2.1 e 5.8.2.1.2.2 (compresso al 90 %); UNI EN 81-50:2020, 5.5.4 (esame di tipo)</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>brochure Geared SICOR, aprile 2026, pp. 16, 23, 41, 47, 58, 68 e 80 (telai «top machine with diverting pulley for CSW wrapping»), letta il 2 ottobre 2026; i telai «corti» MR21, MR26 e MR35 portano il rinvio sotto il pavimento (Hmin = Dt/2 + 75) e non sono usati; le quote del telaio del software sono quelle dei telai SICOR, da adattare al telaio fornito</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 98–99; UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 24; il tampone tipico dai cataloghi P+S Diepocell (wwlift.de) e ACLA AUTAN XL (acla.de), estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>calata del contrappeso nel telaio con rinvio del costruttore</t>
+          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso</t>
         </is>
       </c>
       <c r="I87" s="11" t="n"/>
@@ -4807,43 +4807,43 @@
       <c r="M87" s="11" t="n"/>
       <c r="N87" s="11" t="n"/>
     </row>
-    <row r="88" ht="134" customHeight="1">
+    <row r="88" ht="95" customHeight="1">
       <c r="A88" s="10" t="n">
         <v>86</v>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>L'argano dentro il locale del macchinario</t>
+          <t>Ammortizzatori a dissipazione di energia (idraulici) — gli ammortizzatori Oleo sono dati di catalogo, non della norma: vanno sostituiti con quelli montati</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>l'argano sul suo basamento — con il telaio del rinvio o con il supporto del rinvio — sta dentro il locale in pianta e sotto il soffitto: la distanza minima dai muri e dal soffitto non è negativa; ingombri dalle quote del costruttore per gli argani disegnati com'è, dall'argano generico del software (scalato alla puleggia) per gli altri; la puleggia di rinvio sul suo supporto sotto l'argano libera il basamento dell'argano sopra di essa (solo le putrelle sollevate la scavalcano)</t>
+          <t>a ogni velocità; corsa ≥ 0,0674·v² m (arresto per gravità al 115 % della velocità nominale); la corsa ridotta con il controllo del rallentamento non è considerata; ammortizzatori tipici: Oleo LSB10 fino a 1 m/s, alto 222,2 mm con corsa 73,4 mm; LSB16 fino a 1,6 m/s, alto 485,5 mm con corsa 173,5 mm</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.8.1.6 e 5.8.2.2.1 (corsa); la corsa ridotta di 5.8.2.2.2 non è usata</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>geometria del progetto: la pianta e l'altezza del locale inserite, gli ingombri dell'argano e del basamento</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 99; gli ammortizzatori tipici dal catalogo Oleo LSB e SEB (oleo.co.uk), estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>argano dentro il locale (muri e soffitto); puleggia di rinvio sul suo supporto sotto l'argano</t>
+          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso</t>
         </is>
       </c>
       <c r="I88" s="11" t="n"/>
@@ -4853,7 +4853,7 @@
       <c r="M88" s="11" t="n"/>
       <c r="N88" s="11" t="n"/>
     </row>
-    <row r="89" ht="134" customHeight="1">
+    <row r="89" ht="121" customHeight="1">
       <c r="A89" s="10" t="n">
         <v>87</v>
       </c>
@@ -4864,32 +4864,32 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
+          <t>Locale del macchinario — non verificati: i percorsi larghi almeno 0,50 m e lo spazio di 0,30 m sopra le parti rotanti (5.2.6.3.2.2)</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
+          <t>altezza libera delle zone di lavoro ≥ 2100 mm (1800 mm sui percorsi); davanti al quadro una superficie libera profonda ≥ 700 mm e larga ≥ 500 mm o quanto il quadro; per la manutenzione delle parti in movimento e la manovra di emergenza una superficie libera di almeno 500 × 600 mm (il software la cerca accanto all'argano, sul lato più libero, fino a muri e quadro); porta di accesso ≥ 600 × 2000 mm</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E), §3.1.4 (carichi del macchinario); DPR 1497/1963, art. 5.1–5.2 (carichi fissi più 1,5 volte il carico statico delle funi, sicurezza ≥ 6, freccia ≤ 1/1500 della luce libera: regola storica degli impianti esistenti, letta su Normattiva)</t>
+          <t>UNI EN 81-20:2020, 5.2.6.3.2.1 (2,10 m e superfici libere), 5.2.6.3.2.2 (1,80 m sui percorsi) e 5.2.3.2 a) (porta)</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 29, 43; le superfici libere anche in UNI EN 81-1:1999, 6.3.2.1 (edizione 2008: 6.3.3.1)</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>altezza del locale macchina; superficie libera davanti al quadro; superficie libera accanto all'argano; porta del locale macchina</t>
         </is>
       </c>
       <c r="I89" s="11" t="n"/>
@@ -4899,38 +4899,38 @@
       <c r="M89" s="11" t="n"/>
       <c r="N89" s="11" t="n"/>
     </row>
-    <row r="90" ht="108" customHeight="1">
+    <row r="90" ht="69" customHeight="1">
       <c r="A90" s="10" t="n">
         <v>88</v>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Carichi sul pavimento della fossa</t>
+          <t>Illuminazione del vano e del locale del macchinario</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
+          <t>vano: illuminazione fissa di almeno 50 lux a 1 m sopra il tetto della cabina e sopra il pavimento della fossa, 20 lux altrove; locale del macchinario: almeno 200 lux al pavimento nelle zone di lavoro</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.8; UNI EN 81-50:2020, 5.10</t>
+          <t>UNI EN 81-20:2020, 5.2.1.4.1 a)–c) e 5.2.1.4.2</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi; sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 25</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
@@ -4945,38 +4945,38 @@
       <c r="M90" s="11" t="n"/>
       <c r="N90" s="11" t="n"/>
     </row>
-    <row r="91" ht="108" customHeight="1">
+    <row r="91" ht="43" customHeight="1">
       <c r="A91" s="10" t="n">
         <v>89</v>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Spinte sulle guide di cabina</t>
+          <t>Temperatura dei locali del macchinario e degli armadi</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
+          <t>temperatura ambiente mantenuta tra +5 °C e +40 °C: ipotesi della norma, da garantire nell'edificio</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.10</t>
+          <t>UNI EN 81-20:2020, 0.4.16 (ipotesi della norma, vale anche per il vano)</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 14</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
@@ -4991,38 +4991,38 @@
       <c r="M91" s="11" t="n"/>
       <c r="N91" s="11" t="n"/>
     </row>
-    <row r="92" ht="82" customHeight="1">
+    <row r="92" ht="225" customHeight="1">
       <c r="A92" s="10" t="n">
         <v>90</v>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Carico della macchina sulla soletta</t>
+          <t>Basamento dell'argano</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
+          <t>su spessori di livellamento sotto gli appoggi (l'asse della puleggia dove lo mette il software), su telaio di due profilati sul pavimento (tipico UPN 200, alto quanto il profilato come i telai bassi universali), su due putrelle da muro a muro che possono stare sollevate dal pavimento (tipiche IPE 200, appoggio nei muri 150 mm), su piastre d'acciaio sotto gli appoggi (tipiche 20 mm) o su plinto in calcestruzzo (tipico 250 mm), o — con un rinvio — sul telaio con rinvio (locale.rinvio); tamponi antivibranti di 30 mm sotto gli appoggi, salvo sugli spessori e sul telaio con rinvio (antivibranti sotto le gambe); telaio e plinto 100 mm oltre il telaio dell'argano a ogni estremità; l'altezza del basamento porta l'asse della puleggia, che il calcolo (tratto di fune oltre la corsa) e il 3D seguono</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio); scelta del costruttore</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
+          <t>telaio basso universale per argano alto 200 mm (lift-store.it); tamponi antivibranti 25–30 mm (catalogo Donati); piastre di 20 mm e plinto di 250–300 mm nella pratica di installazione (fonti estere, da confermare); estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>prassi di cantiere</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
@@ -5037,23 +5037,23 @@
       <c r="M92" s="11" t="n"/>
       <c r="N92" s="11" t="n"/>
     </row>
-    <row r="93" ht="43" customHeight="1">
+    <row r="93" ht="147" customHeight="1">
       <c r="A93" s="10" t="n">
         <v>91</v>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Massa dei cavi flessibili</t>
+          <t>Telaio sotto l'argano di un costruttore</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
+          <t>l'argano di catalogo poggia con i suoi piedi su un telaio di due travi sotto le file di fori, con antivibranti alle estremità e 40 mm oltre l'argano a ogni estremità; il telaio è alto quanto serve per tenere l'asse della puleggia dove lo tiene l'argano generico del software, almeno 80 mm e con il bordo della puleggia 30 mm sopra il suo piano d'appoggio (gli argani compatti hanno la puleggia a sbalzo, sotto il piano dei piedi); se l'argano non lo permette l'asse sale e il calcolo segue</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
+          <t>quote dei piedi, dei fori e dell'asse della puleggia dalle schede tecniche del costruttore; altezza del telaio scelta dal software, da adattare al telaio fornito</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
@@ -5083,33 +5083,33 @@
       <c r="M93" s="11" t="n"/>
       <c r="N93" s="11" t="n"/>
     </row>
-    <row r="94" ht="121" customHeight="1">
+    <row r="94" ht="303" customHeight="1">
       <c r="A94" s="10" t="n">
         <v>92</v>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
+          <t>Puleggia di rinvio nel locale del macchinario</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
+          <t>con l'argano in alto il rinvio sta sempre nel locale del macchinario, mai nel vano: nel telaio dell'argano (il basamento che il software prende quando c'è un rinvio), con l'asse del rinvio a 320 mm dal pavimento (il bordo almeno 60 mm sopra il pavimento: Dp/2 + 60 oltre Ø 520), il piano del telaio a 736 mm (almeno 176 mm sopra il rinvio), gambe di tubo quadro da 80 mm su antivibranti da 28 mm, travi UPN 160, 100 mm oltre l'argano e il rinvio a ogni estremità, largo almeno 655 mm; con un argano SICOR che ha il suo telaio a catalogo (SV110 e SH110B XTE0517/XTE0516, SH130 e SH130G XTE3022/XTE3023, SH140 XTE6026/XTE6027, SH160 XTE5708, SH190 XTE3988) le quote del costruttore: asse del rinvio, asse della puleggia (A), piano del telaio (A − B), calata del contrappeso entro L max dall'asse della puleggia (verifica di avvertimento: oltre, telaio su misura); h del calcolo = asse della puleggia − asse del rinvio, dx dalla pianta; con un altro basamento scelto il rinvio sta su un supporto proprio sul pavimento, alla stessa altezza; una h inserita a mano che porta il rinvio sotto il pavimento è segnalata</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>regola di montaggio indicata dal committente</t>
+          <t>regola del committente (Panev): il rinvio sta nel telaio del locale macchine, mai nel vano; UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio)</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>scelta del committente</t>
+          <t>brochure Geared SICOR, aprile 2026, pp. 16, 23, 41, 47, 58, 68 e 80 (telai «top machine with diverting pulley for CSW wrapping»), letta il 2 ottobre 2026; i telai «corti» MR21, MR26 e MR35 portano il rinvio sotto il pavimento (Hmin = Dt/2 + 75) e non sono usati; le quote del telaio del software sono quelle dei telai SICOR, da adattare al telaio fornito</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>calata del contrappeso nel telaio con rinvio del costruttore</t>
         </is>
       </c>
       <c r="I94" s="11" t="n"/>
@@ -5129,23 +5129,23 @@
       <c r="M94" s="11" t="n"/>
       <c r="N94" s="11" t="n"/>
     </row>
-    <row r="95" ht="82" customHeight="1">
+    <row r="95" ht="134" customHeight="1">
       <c r="A95" s="10" t="n">
         <v>93</v>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Lunghezze stimate nel foglio dei dati</t>
+          <t>L'argano dentro il locale del macchinario</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
+          <t>l'argano sul suo basamento — con il telaio del rinvio o con il supporto del rinvio — sta dentro il locale in pianta e sotto il soffitto: la distanza minima dai muri e dal soffitto non è negativa; ingombri dalle quote del costruttore per gli argani disegnati com'è, dall'argano generico del software (scalato alla puleggia) per gli altri; la puleggia di rinvio sul suo supporto sotto l'argano libera il basamento dell'argano sopra di essa (solo le putrelle sollevate la scavalcano)</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
@@ -5155,17 +5155,17 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>stima del software, da sostituire con le misure di cantiere</t>
+          <t>geometria del progetto: la pianta e l'altezza del locale inserite, gli ingombri dell'argano e del basamento</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>argano dentro il locale (muri e soffitto); puleggia di rinvio sul suo supporto sotto l'argano</t>
         </is>
       </c>
       <c r="I95" s="11" t="n"/>
@@ -5175,43 +5175,43 @@
       <c r="M95" s="11" t="n"/>
       <c r="N95" s="11" t="n"/>
     </row>
-    <row r="96" ht="43" customHeight="1">
+    <row r="96" ht="134" customHeight="1">
       <c r="A96" s="10" t="n">
         <v>94</v>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Dimensioni proposte della cabina</t>
+          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
+          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E), §3.1.4 (carichi del macchinario); DPR 1497/1963, art. 5.1–5.2 (carichi fissi più 1,5 volte il carico statico delle funi, sicurezza ≥ 6, freccia ≤ 1/1500 della luce libera: regola storica degli impianti esistenti, letta su Normattiva)</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
         </is>
       </c>
       <c r="I96" s="11" t="n"/>
@@ -5221,23 +5221,23 @@
       <c r="M96" s="11" t="n"/>
       <c r="N96" s="11" t="n"/>
     </row>
-    <row r="97" ht="199" customHeight="1">
+    <row r="97" ht="147" customHeight="1">
       <c r="A97" s="10" t="n">
         <v>95</v>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Quote della pianta fissate a mano</t>
+          <t>Sostituzione dell'argano: calate esistenti e calate della nuova macchina</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8), quello del contrappeso dentro la lunghezza del contrappeso</t>
+          <t>nella sola sostituzione dell'argano la cabina e il contrappeso restano dove sono: le funi della nuova macchina devono scendere sulle calate esistenti, rilevate nel locale dall'angolo interno del vano. La distanza tra le calate data dal calcolo (rinvio: D/2 + dx ± Dp/2, più Dp in taglia 2:1; tiro diretto: il diametro della puleggia esistente, se inserita, altrimenti della nuova, più Dp in taglia 2:1) e quella misurata differiscono al più di 10 mm; oltre, il calcolo va ripetuto con la geometria misurata (dx, puleggia esistente)</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
@@ -5247,17 +5247,17 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
+          <t>tolleranza scelta dal software per il rilievo in sito (le funi a qualche metro dal basamento): da confermare con l'installatore</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
           <t>scelta del software</t>
         </is>
       </c>
-      <c r="G97" s="10" t="inlineStr">
-        <is>
-          <t>scelta del software</t>
-        </is>
-      </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
+          <t>sostituzione: calate della nuova macchina sulle calate esistenti</t>
         </is>
       </c>
       <c r="I97" s="11" t="n"/>
@@ -5267,38 +5267,38 @@
       <c r="M97" s="11" t="n"/>
       <c r="N97" s="11" t="n"/>
     </row>
-    <row r="98" ht="82" customHeight="1">
+    <row r="98" ht="108" customHeight="1">
       <c r="A98" s="10" t="n">
         <v>96</v>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Limiti del modello del vano</t>
+          <t>Carichi sul pavimento della fossa — non calcolato: con spazi accessibili sotto il vano (5.2.5.4) il contrappeso ha il paracadute, sotto le sue guide va anche k1·g·M_cw/n e il fondo della fossa regge almeno 5000 N/m²</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
+          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8.4–5.2.1.8.6, 5.7.2.3.5 e Prospetto 14 (k1)</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>limite del modello attuale</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 27, 94–96</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
@@ -5313,38 +5313,38 @@
       <c r="M98" s="11" t="n"/>
       <c r="N98" s="11" t="n"/>
     </row>
-    <row r="99" ht="56" customHeight="1">
+    <row r="99" ht="108" customHeight="1">
       <c r="A99" s="10" t="n">
         <v>97</v>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Corsa</t>
+          <t>Spinte sulle guide di cabina — h, la distanza tra i pattini, è una stima del software (l'ingombro verticale dell'arcata)</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
+          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, appendice C (informativa), C.2.1.1 e C.2.2.1; UNI EN 81-20:2020, 5.7.2.3.4 (portata su 3/4 della superficie: 1/8) e Prospetto 14 (k1; k2 = 1,2)</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>dati dei piani inseriti</t>
+          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 77–79; UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 94–96</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H99" s="10" t="inlineStr">
@@ -5359,38 +5359,38 @@
       <c r="M99" s="11" t="n"/>
       <c r="N99" s="11" t="n"/>
     </row>
-    <row r="100" ht="56" customHeight="1">
+    <row r="100" ht="82" customHeight="1">
       <c r="A100" s="10" t="n">
         <v>98</v>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Portata e velocità</t>
+          <t>Carico della macchina sulla soletta</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
+          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.2.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>progetto del vano</t>
+          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>prassi di cantiere</t>
         </is>
       </c>
       <c r="H100" s="10" t="inlineStr">
@@ -5405,38 +5405,38 @@
       <c r="M100" s="11" t="n"/>
       <c r="N100" s="11" t="n"/>
     </row>
-    <row r="101" ht="303" customHeight="1">
+    <row r="101" ht="43" customHeight="1">
       <c r="A101" s="10" t="n">
         <v>99</v>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Normativa di collaudo e parti sostituite o modificate — il testo delle UNI 10411 del 2024 non è stato letto: le verifiche per parte e i requisiti per la sostituzione del macchinario (edizione 2021: freno in due elementi, temporizzatore, velocità eccessiva in salita, arresto entro 1 m dalla macchina, interruzione se il freno non si apre) vanno confermati sul testo vigente</t>
+          <t>Massa dei cavi flessibili</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software. Alla norma base si aggiungono le norme compatibili (matrice della ricerca, cap. 16 §5.2): sull'impianto nuovo le EN 81 supplementari (21, 28, 58, 70, 71, 72, 73, 76, 77), sulla modifica la EN 81-20/50 intera, le EN 81-28, 58, 73 e il miglioramento (80, 82, 83), su entrambi DM 236/1989, antincendio (DM 15/09/2005 o Codice V.3) e NTC 2018 (con le verifiche delle putrelle). Ogni norma ha il suo esito («non calcolata» se il software non ne calcola verifiche) e i suoi punti da verificare in sito nella relazione, con gli adempimenti del DPR 162/1999</t>
+          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>schede UNI delle norme (scopo, data 31/10/2024); schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); sintesi secondarie; ricerca, capitoli 2.4 e 6.6</t>
+          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H101" s="10" t="inlineStr">
@@ -5451,38 +5451,38 @@
       <c r="M101" s="11" t="n"/>
       <c r="N101" s="11" t="n"/>
     </row>
-    <row r="102" ht="69" customHeight="1">
+    <row r="102" ht="121" customHeight="1">
       <c r="A102" s="10" t="n">
         <v>100</v>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
+          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
+          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
+          <t>regola di montaggio indicata dal committente</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>scelta del software, senza fonte</t>
+          <t>scelta del committente</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H102" s="10" t="inlineStr">
@@ -5497,23 +5497,23 @@
       <c r="M102" s="11" t="n"/>
       <c r="N102" s="11" t="n"/>
     </row>
-    <row r="103" ht="108" customHeight="1">
+    <row r="103" ht="82" customHeight="1">
       <c r="A103" s="10" t="n">
         <v>101</v>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Fune oltre la corsa (L0)</t>
+          <t>Lunghezze stimate nel foglio dei dati</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale; con la puleggia di rinvio, l'asse sul basamento o sul telaio che la porta (voce locale.rinvio); macchina in basso o senza locale: fino al soffitto del vano</t>
+          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
+          <t>stima del software, da sostituire con le misure di cantiere</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
@@ -5543,43 +5543,43 @@
       <c r="M103" s="11" t="n"/>
       <c r="N103" s="11" t="n"/>
     </row>
-    <row r="104" ht="147" customHeight="1">
+    <row r="104" ht="290" customHeight="1">
       <c r="A104" s="10" t="n">
         <v>102</v>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
+          <t>Verifica delle guide di cabina — Confermati sul testo i coefficienti, le formule e i limiti. Da verificare il carico al piano: la UNI EN 81-20:2020 (5.7.2.3.6) lo lega al tipo di ascensore, 0,4·g·Q per persone, 0,6·g·Q per merci, 0,85·g·Q con dispositivi di movimentazione pesanti; il software usa la regola della UNI EN 81-1 (0,6·g·Q da 2500 kg, appendice G.2.5) perché il tipo di ascensore non è tra i dati. La formula di ω per Rm 370 è data da λ 20 a 250: sotto 20 il software usa la stessa formula. Non contate: la spinta di scorrimento delle staffe (assestamento dell'edificio), le apparecchiature appese alle guide, le frecce di staffe ed edificio (la norma vuole la somma entro il limite) e le guide del contrappeso</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
+          <t>tra due staffe (l = distanza massima tra le staffe della guida) con le spinte della voce guide.spinte, portata spostata di 1/8 della cabina in un senso e poi nell'altro: flessione M = 3·F·l/16, σm = σx + σy; intervento del paracadute: forza verticale Fv = k1·g·(P+Q)/n più il peso della guida, carico di punta con il metodo omega (λ = l/i con il raggio d'inerzia minore √(I/A), λ ≤ 250; acciaio Rm 370: ω = 0,0001292·λ^1,89 + 1 fino a λ 60, 0,00004627·λ^2,14 + 1 fino a 85, 0,00001711·λ^2,35 + 1,04 fino a 115, 0,00016887·λ^2 fino a 250), σ = σm + Fv/A e σc = σk + 0,9·σm; marcia: k2 = 1,2 e il peso della guida; carico al piano: cabina vuota e Fs = 0,4·g·Q (0,6·g·Q da 2500 kg) al centro della soglia di cabina, a ogni accesso; flessione della suola σF = 1,85·Fx/c² (pattini a rotelle); frecce δx = 0,7·Fx·l³/(48·E·Iy) e δy = 0,7·Fy·l³/(48·E·Ix) ≤ 5 mm. Tensione ammissibile Rm/St con St = 2,25 in marcia e al carico, 1,8 all'intervento del paracadute (allungamento A5 &gt; 12 %): con Rm 370 N/mm², 164,4 e 205,6 N/mm²</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3</t>
+          <t>UNI EN 81-50:2020, 5.10.2–5.10.6; UNI EN 81-20:2020, 5.7.2.3.5, 5.7.2.3.6, 5.7.4.5 (Prospetto 15), 5.7.4.6 e Prospetto 14</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>pianta del vano</t>
+          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 35–39; UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 94–97; Rm 370 è scelta del software (il valore più basso)</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tensioni nelle guide di cabina; flessione della suola delle guide di cabina; frecce delle guide di cabina</t>
         </is>
       </c>
       <c r="I104" s="11" t="n"/>
@@ -5589,38 +5589,38 @@
       <c r="M104" s="11" t="n"/>
       <c r="N104" s="11" t="n"/>
     </row>
-    <row r="105" ht="160" customHeight="1">
+    <row r="105" ht="147" customHeight="1">
       <c r="A105" s="10" t="n">
         <v>103</v>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
+          <t>Sezioni delle guide di cabina</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
+          <t>area, momenti d'inerzia e moduli di resistenza minimi attorno all'asse parallelo alla suola (x) e all'asse di simmetria (y), spessore c del collo tra lama e suola, per ogni profilo del software; raggi d'inerzia calcolati come √(I/A)</t>
         </is>
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
+          <t>ISO 7465:2007 (ora ISO 8100-33:2022); EN 10055:1995 per il T 70×70×8 laminato</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>geometria delle funi</t>
+          <t>tabella ISO 7465:2007 stampata da Savera (Standard Savera Guide, Rev 03/10; assi e c dalla Rev 08.26), anteprime ISO 7465:1997 e ISO 8100-33:2022 (correzione dei raggi del T127-1/B, stampati nel 2007 uguali ai moduli), EN 10055:1995, Tabella 1. La EN 10055 non ha il T 45: al T 45×45×5 il software dà la sezione del T45/A, delle stesse misure</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
@@ -5635,43 +5635,43 @@
       <c r="M105" s="11" t="n"/>
       <c r="N105" s="11" t="n"/>
     </row>
-    <row r="106" ht="56" customHeight="1">
+    <row r="106" ht="82" customHeight="1">
       <c r="A106" s="10" t="n">
         <v>104</v>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
+          <t>Tipo di paracadute per la velocità nominale</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
+          <t>istantaneo (anche a rulli imprigionati) fino a 0,63 m/s; oltre, progressivo (la UNI EN 81-20 non ha più l'istantaneo con effetto ammortizzato fino a 1 m/s); il tipo viene dai dati dell'impianto (se manca: progressivo, con la nota sul foglio)</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
+          <t>UNI EN 81-20:2020, 5.6.2.1.2.1; la regola precedente in UNI EN 81-1 (1999, 2008), 9.8.2.1</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 81; UNI EN 81-1:2008, testo della norma fornito dal cliente, letto il 2026-10-06, p. 58</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tipo di paracadute per la velocità</t>
         </is>
       </c>
       <c r="I106" s="11" t="n"/>
@@ -5681,33 +5681,33 @@
       <c r="M106" s="11" t="n"/>
       <c r="N106" s="11" t="n"/>
     </row>
-    <row r="107" ht="238" customHeight="1">
+    <row r="107" ht="43" customHeight="1">
       <c r="A107" s="10" t="n">
         <v>105</v>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso o pilastro pieno fino al terreno (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori</t>
+          <t>Dimensioni proposte della cabina</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
+          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>geometria ricostruita dal software</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
@@ -5727,43 +5727,43 @@
       <c r="M107" s="11" t="n"/>
       <c r="N107" s="11" t="n"/>
     </row>
-    <row r="108" ht="186" customHeight="1">
+    <row r="108" ht="225" customHeight="1">
       <c r="A108" s="10" t="n">
         <v>106</v>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta dal catalogo di un costruttore — i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
+          <t>Quote della pianta fissate a mano</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo; i disegni e il 3D mostrano l'argano SICOR com'è (ingombri, piedi e fori, asse della puleggia, P ed E della scheda), sul telaio del software</t>
+          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8.1), quello del contrappeso dentro la lunghezza del contrappeso (la stessa verifica vale per quelli messi dal software: ammortizzatori.posizione)</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>SICOR: schede tecniche 2025 e modelli CAD scaricati da sicoritaly.com il 2 ottobre 2026 (solo le quote); Sassi, Montanari, GEM, FAER: estratti delle pagine dei costruttori e dei rivenditori, 1° ottobre 2026</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H108" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
         </is>
       </c>
       <c r="I108" s="11" t="n"/>
@@ -5773,33 +5773,33 @@
       <c r="M108" s="11" t="n"/>
       <c r="N108" s="11" t="n"/>
     </row>
-    <row r="109" ht="134" customHeight="1">
+    <row r="109" ht="82" customHeight="1">
       <c r="A109" s="10" t="n">
         <v>107</v>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
+          <t>Limiti del modello del vano</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
+          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
         </is>
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo</t>
+          <t>limite del modello attuale</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
@@ -5819,38 +5819,38 @@
       <c r="M109" s="11" t="n"/>
       <c r="N109" s="11" t="n"/>
     </row>
-    <row r="110" ht="69" customHeight="1">
+    <row r="110" ht="186" customHeight="1">
       <c r="A110" s="10" t="n">
         <v>108</v>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
+          <t>Verifiche che il software non calcola</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
+          <t>da fare a parte, con i dati dei fornitori: sollecitazioni e frecce delle staffe e delle guide del contrappeso (UNI EN 81-50:2020, 5.10: il software verifica le guide di cabina, sul foglio 1 delle tavole); puleggia del contrappeso in taglia 2:1 sotto il soffitto; paracadute del contrappeso con spazi accessibili sotto il vano; distanza tra le parti fisse più alte della fossa e quelle più basse della cabina sugli ammortizzatori; sporgenze nel vano oltre 150 mm senza balaustra; locale della macchina in basso (dimensioni e spazi di manovra: il software non lo disegna); movimento incontrollato della cabina (UCM) e velocità eccessiva in salita con la nuova macchina</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
+          <t>UNI EN 81-20:2020: guide e staffe 5.7.2–5.7.4 (con UNI EN 81-50:2020, 5.10); distanze in testata 5.2.5.7.2; spazi accessibili sotto il vano 5.2.5.4; parti fisse in fossa 5.2.5.8.2; sporgenze oltre 0,15 m 5.2.5.2.2.2; locale del macchinario 5.2.6.3; velocità eccessiva in salita 5.6.6; movimento incontrollato 5.6.7</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo (src/calc/model.ts)</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 31–43, 89–97; analisi delle lacune del 2026-10-03</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
@@ -5871,32 +5871,32 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
+          <t>Corsa</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
+          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>dati dei piani inseriti</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H111" s="10" t="inlineStr">
@@ -5911,38 +5911,38 @@
       <c r="M111" s="11" t="n"/>
       <c r="N111" s="11" t="n"/>
     </row>
-    <row r="112" ht="69" customHeight="1">
+    <row r="112" ht="56" customHeight="1">
       <c r="A112" s="10" t="n">
         <v>110</v>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Limite di aderenza mostrato durante la marcia</t>
+          <t>Portata e velocità</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
+          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.2</t>
+          <t>UNI EN 81-20:2020, 5.4.2.1</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>progetto del vano</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
@@ -5957,33 +5957,33 @@
       <c r="M112" s="11" t="n"/>
       <c r="N112" s="11" t="n"/>
     </row>
-    <row r="113" ht="43" customHeight="1">
+    <row r="113" ht="316" customHeight="1">
       <c r="A113" s="10" t="n">
         <v>111</v>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Tempi delle porte</t>
+          <t>Normativa di collaudo e parti sostituite o modificate — lo scopo delle due UNI 10411 e i requisiti per la sostituzione del macchinario (punto 14) sono letti sul testo (voce sostituzione.adeguamenti); quali verifiche riguardano ciascuna parte e la matrice delle norme compatibili sono una lettura del software, da approvare dall'ingegnere</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
+          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico a frizione non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (a frizione, conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software. Alla norma base si aggiungono le norme compatibili (matrice della ricerca, cap. 16 §5.2): sull'impianto nuovo le EN 81 supplementari (21, 28, 58, 70, 71, 72, 73, 76, 77), sulla modifica la EN 81-20/50 intera, le EN 81-28, 58, 73 e il miglioramento (80, 82, 83), su entrambi DM 236/1989, antincendio (DM 15/09/2005 o Codice V.3) e NTC 2018 (con le verifiche delle putrelle). Ogni norma ha il suo esito («non calcolata» se il software non ne calcola verifiche) e i suoi punti da verificare in sito nella relazione, con gli adempimenti del DPR 162/1999</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (solo animazione)</t>
+          <t>UNI 10411-1:2024, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 5, 13–14; UNI 10411-11:2024, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 5, 12; schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); ricerca, capitoli 2.4 e 6.6</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
@@ -6003,38 +6003,38 @@
       <c r="M113" s="11" t="n"/>
       <c r="N113" s="11" t="n"/>
     </row>
-    <row r="114" ht="108" customHeight="1">
+    <row r="114" ht="160" customHeight="1">
       <c r="A114" s="10" t="n">
         <v>112</v>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione</t>
+          <t>Rifacimento con l'arcata esistente — il DPR 162/1999 elenca le modifiche costruttive ma non dice quando l'insieme diventa una sostituzione completa: la qualificazione dell'intervento la conferma il tecnico incaricato con il soggetto che esegue la verifica straordinaria</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
+          <t>si sostituiscono tutte le parti tranne l'arcata, che resta: le sostituzioni sono modifiche costruttive dell'impianto esistente, che si collauda secondo UNI 10411-1:2024 o UNI 10411-11:2024 e non come impianto nuovo; le verifiche che riguardano solo l'arcata (il tipo di paracadute, se la velocità non cambia) sono riportate come «esistente». La sostituzione completa dell'ascensore, arcata compresa, si collauda come impianto nuovo (UNI EN 81-20:2020 e UNI EN 81-50:2020; negli edifici esistenti anche la UNI EN 81-21:2022, supplementare)</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2</t>
+          <t>DPR 162/1999 e s.m.i., art. 2 c.1 lett. cc), art. 12 c.4, art. 14 c.3; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-21:2022 (scopo)</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>sintesi della norma di costruttori e organismi notificati (fonti secondarie)</t>
+          <t>indicazione del cliente (5 ottobre 2026): prassi di lasciare l'arcata; ricerca, capitolo 16 §3.2 e §5.3</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>prassi di cantiere</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
@@ -6049,38 +6049,38 @@
       <c r="M114" s="11" t="n"/>
       <c r="N114" s="11" t="n"/>
     </row>
-    <row r="115" ht="56" customHeight="1">
+    <row r="115" ht="69" customHeight="1">
       <c r="A115" s="10" t="n">
         <v>113</v>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Cabina bloccata: rotazione in salita</t>
+          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
+          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
         </is>
       </c>
       <c r="E115" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2</t>
+          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
         </is>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo; velocità scelta dal software</t>
+          <t>scelta del software, senza fonte</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H115" s="10" t="inlineStr">
@@ -6095,23 +6095,23 @@
       <c r="M115" s="11" t="n"/>
       <c r="N115" s="11" t="n"/>
     </row>
-    <row r="116" ht="43" customHeight="1">
+    <row r="116" ht="108" customHeight="1">
       <c r="A116" s="10" t="n">
         <v>114</v>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Passo di campionamento</t>
+          <t>Fune oltre la corsa (L0)</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
+          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale; con la puleggia di rinvio, l'asse sul basamento o sul telaio che la porta (voce locale.rinvio); macchina in basso o senza locale: fino al soffitto del vano</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
         </is>
       </c>
       <c r="G116" s="10" t="inlineStr">
@@ -6141,38 +6141,38 @@
       <c r="M116" s="11" t="n"/>
       <c r="N116" s="11" t="n"/>
     </row>
-    <row r="117" ht="56" customHeight="1">
+    <row r="117" ht="147" customHeight="1">
       <c r="A117" s="10" t="n">
         <v>115</v>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 4-bis</t>
+          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>progetto, fabbricazione, installazione e prove conformi all'All. I; documentazione tecnica e dichiarazione di conformità conservate per 10 anni</t>
+          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
         </is>
       </c>
       <c r="E117" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 4-bis</t>
+          <t>ricerca, capitolo 5.3</t>
         </is>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>pianta del vano</t>
         </is>
       </c>
       <c r="G117" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
@@ -6187,38 +6187,38 @@
       <c r="M117" s="11" t="n"/>
       <c r="N117" s="11" t="n"/>
     </row>
-    <row r="118" ht="56" customHeight="1">
+    <row r="118" ht="160" customHeight="1">
       <c r="A118" s="10" t="n">
         <v>116</v>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 6-bis e 7 c.3</t>
+          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>procedura con un organismo notificato (All. V, VIII, X, XI o XII); marcatura CE in cabina con il numero dell'organismo</t>
+          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 6-bis e 7 c.3</t>
+          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>geometria delle funi</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H118" s="10" t="inlineStr">
@@ -6239,32 +6239,32 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.1–3</t>
+          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>comunicazione al Comune entro 60 giorni dalla dichiarazione di conformità (oltre: con il verbale di una verifica straordinaria di attivazione); matricola entro 30 giorni</t>
+          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.1–3</t>
+          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>dati verticali del vano</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H119" s="10" t="inlineStr">
@@ -6279,38 +6279,38 @@
       <c r="M119" s="11" t="n"/>
       <c r="N119" s="11" t="n"/>
     </row>
-    <row r="120" ht="56" customHeight="1">
+    <row r="120" ht="238" customHeight="1">
       <c r="A120" s="10" t="n">
         <v>118</v>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
+          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso — la EN 81-20 non ammette più il pilastro pieno fino al terreno — (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>verifiche periodiche ogni 2 anni; controllo dei dispositivi di sicurezza, delle funi e dell'isolamento almeno ogni 6 mesi; targa in cabina</t>
+          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
+          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>geometria ricostruita dal software</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H120" s="10" t="inlineStr">
@@ -6325,38 +6325,38 @@
       <c r="M120" s="11" t="n"/>
       <c r="N120" s="11" t="n"/>
     </row>
-    <row r="121" ht="43" customHeight="1">
+    <row r="121" ht="238" customHeight="1">
       <c r="A121" s="10" t="n">
         <v>119</v>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
+          <t>Macchina proposta dal catalogo di un costruttore — la tolleranza sul rapporto è una scelta del software: la velocità reale con l'inverter deve restare entro il 5 % sopra la nominale (UNI EN 81-20:2020, 5.9.2.4); i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>la modifica è costruttiva: la sostituzione del macchinario ne è il caso n. 5)</t>
+          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo; i disegni e il 3D mostrano l'argano SICOR com'è (ingombri, piedi e fori, asse della puleggia, P ed E della scheda), sul telaio del software</t>
         </is>
       </c>
       <c r="E121" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
+          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>SICOR: schede tecniche 2025 e modelli CAD scaricati da sicoritaly.com il 2 ottobre 2026 (solo le quote); Sassi, Montanari, GEM, FAER: estratti delle pagine dei costruttori e dei rivenditori, 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H121" s="10" t="inlineStr">
@@ -6371,38 +6371,38 @@
       <c r="M121" s="11" t="n"/>
       <c r="N121" s="11" t="n"/>
     </row>
-    <row r="122" ht="43" customHeight="1">
+    <row r="122" ht="134" customHeight="1">
       <c r="A122" s="10" t="n">
         <v>120</v>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4</t>
+          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>prima della comunicazione, adeguamento della parte modificata o sostituita e delle altre parti interessate</t>
+          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4</t>
+          <t>ricerca, capitolo 8</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>motore di calcolo</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H122" s="10" t="inlineStr">
@@ -6417,38 +6417,38 @@
       <c r="M122" s="11" t="n"/>
       <c r="N122" s="11" t="n"/>
     </row>
-    <row r="123" ht="43" customHeight="1">
+    <row r="123" ht="69" customHeight="1">
       <c r="A123" s="10" t="n">
         <v>121</v>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4–5</t>
+          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>comunicazione al Comune e al soggetto delle verifiche periodiche; l'impianto non resta in esercizio senza le comunicazioni aggiornate</t>
+          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
         </is>
       </c>
       <c r="E123" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4–5</t>
+          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
         </is>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>motore di calcolo (src/calc/model.ts)</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H123" s="10" t="inlineStr">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 14 c.3</t>
+          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>verifica straordinaria da uno dei soggetti dell'art. 13 c.1, di norma limitata ai controlli sulle modifiche, con la documentazione delle modifiche e dei componenti sostituiti</t>
+          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 14 c.3</t>
+          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H124" s="10" t="inlineStr">
@@ -6509,38 +6509,38 @@
       <c r="M124" s="11" t="n"/>
       <c r="N124" s="11" t="n"/>
     </row>
-    <row r="125" ht="56" customHeight="1">
+    <row r="125" ht="69" customHeight="1">
       <c r="A125" s="10" t="n">
         <v>123</v>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
+          <t>Limite di aderenza mostrato durante la marcia</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>prove dell'organismo notificato: funzionamento a vuoto e a pieno carico, in mancanza di energia, prova statica a 1,25 volte la portata e controllo che non restino deformazioni</t>
+          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
         </is>
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
+          <t>UNI EN 81-50:2020, 5.11.2.2</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H125" s="10" t="inlineStr">
@@ -6555,38 +6555,38 @@
       <c r="M125" s="11" t="n"/>
       <c r="N125" s="11" t="n"/>
     </row>
-    <row r="126" ht="56" customHeight="1">
+    <row r="126" ht="43" customHeight="1">
       <c r="A126" s="10" t="n">
         <v>124</v>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
+          <t>Tempi delle porte</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>documentazione tecnica con i risultati dei calcoli di progetto, le relazioni sulle prove e l'elenco delle norme armonizzate applicate, anche in parte</t>
+          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>scelta del software (solo animazione)</t>
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H126" s="10" t="inlineStr">
@@ -6601,38 +6601,38 @@
       <c r="M126" s="11" t="n"/>
       <c r="N126" s="11" t="n"/>
     </row>
-    <row r="127" ht="56" customHeight="1">
+    <row r="127" ht="108" customHeight="1">
       <c r="A127" s="10" t="n">
         <v>125</v>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
+          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>per gli ascensori dichiarati conformi dal 20/01/2027: requisiti dell'All. III del Regolamento macchine (tra cui 1.1.9 e 1.2.1), con una valutazione aggiuntiva per i requisiti nuovi o cambiati</t>
+          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr">
         <is>
-          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
+          <t>UNI EN 81-20:2020, 5.8.2.1.1.1–5.8.2.1.1.2 (urto al 115 %; corsa piena con un carico statico tra 2,5 e 4 volte: il software prende 4), 5.8.2.1.2.2 (90 %), 5.8.2.2.1 e 5.8.2.2.3 a)</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 98–99</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H127" s="10" t="inlineStr">
@@ -6653,32 +6653,32 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-1:2024</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, scopo</t>
+          <t>Cabina bloccata: rotazione in salita</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>ascensori elettrici a frizione non conformi alla 95/16/CE né alla 2014/33/UE; esclude le modifiche che cambiano le misure antincendio (valgono il DM 15/09/2005 o il Codice V.3)</t>
+          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, scopo</t>
+          <t>UNI EN 81-50:2020, 5.11.2</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>motore di calcolo; velocità scelta dal software</t>
         </is>
       </c>
       <c r="G128" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H128" s="10" t="inlineStr">
@@ -6693,38 +6693,38 @@
       <c r="M128" s="11" t="n"/>
       <c r="N128" s="11" t="n"/>
     </row>
-    <row r="129" ht="56" customHeight="1">
+    <row r="129" ht="43" customHeight="1">
       <c r="A129" s="10" t="n">
         <v>127</v>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-11:2024</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, scopo</t>
+          <t>Passo di campionamento</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>ascensori elettrici a frizione conformi alla Direttiva Ascensori; esclude le modifiche che cambiano le misure antincendio (valgono il DM 15/09/2005 o il Codice V.3)</t>
+          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, scopo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G129" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H129" s="10" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-21:2022, scopo</t>
+          <t>DPR 162/1999, art. 4-bis</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>impianto nuovo o sostituzione completa in un edificio esistente; non copre le modifiche parziali (letto sull'edizione 2018)</t>
+          <t>progetto, fabbricazione, installazione e prove conformi all'All. I; documentazione tecnica e dichiarazione di conformità conservate per 10 anni</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-21:2022, scopo</t>
+          <t>DPR 162/1999, art. 4-bis</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="G130" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H130" s="10" t="inlineStr">
@@ -6785,28 +6785,28 @@
       <c r="M130" s="11" t="n"/>
       <c r="N130" s="11" t="n"/>
     </row>
-    <row r="131" ht="82" customHeight="1">
+    <row r="131" ht="56" customHeight="1">
       <c r="A131" s="10" t="n">
         <v>129</v>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
+          <t>DPR 162/1999, artt. 6-bis e 7 c.3</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>spazi di rifugio ridotti solo con l'accordo preventivo: in edificio esistente PEC al Ministero con la certificazione dell'organismo prima dell'installazione (Procedura 2: dichiarazione dei punti della EN 81-21 applicati); la EN 81-21 da sola non giustifica la deroga</t>
+          <t>procedura con un organismo notificato (All. V, VIII, X, XI o XII); marcatura CE in cabina con il numero dell'organismo</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
+          <t>DPR 162/1999, artt. 6-bis e 7 c.3</t>
         </is>
       </c>
       <c r="F131" s="10" t="inlineStr">
@@ -6837,22 +6837,22 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-28:2022</t>
+          <t>DPR 162/1999, art. 12 c.1–3</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>teleallarme verso un servizio di soccorso: requisiti da verificare sul testo della norma; il suo uso sugli impianti esistenti non è stato verificato</t>
+          <t>comunicazione al Comune entro 60 giorni dalla dichiarazione di conformità (oltre: con il verbale di una verifica straordinaria di attivazione); matricola entro 30 giorni</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-28:2022</t>
+          <t>DPR 162/1999, art. 12 c.1–3</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H132" s="10" t="inlineStr">
@@ -6877,28 +6877,28 @@
       <c r="M132" s="11" t="n"/>
       <c r="N132" s="11" t="n"/>
     </row>
-    <row r="133" ht="69" customHeight="1">
+    <row r="133" ht="56" customHeight="1">
       <c r="A133" s="10" t="n">
         <v>131</v>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-58:2022 (resistenza al fuoco delle porte di piano)</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
+          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>porte di piano resistenti al fuoco (classi E, EI, EW) provate secondo la norma, quando fanno parte della compartimentazione del vano; sostituirle con modelli diversi è una modifica sostanziale ai fini antincendio</t>
+          <t>verifiche periodiche ogni 2 anni; controllo dei dispositivi di sicurezza, delle funi e dell'isolamento almeno ogni 6 mesi; targa in cabina</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
+          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
         </is>
       </c>
       <c r="F133" s="10" t="inlineStr">
@@ -6923,28 +6923,28 @@
       <c r="M133" s="11" t="n"/>
       <c r="N133" s="11" t="n"/>
     </row>
-    <row r="134" ht="69" customHeight="1">
+    <row r="134" ht="43" customHeight="1">
       <c r="A134" s="10" t="n">
         <v>132</v>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.1</t>
+          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>tipi di cabina (larghezza × profondità, luce della porta): 1) 1000 × 1300, 800; 2) 1100 × 1400, 900; 3) 1100 × 2100, 900; 4) 1600 × 1400 o 1400 × 1600, 900; 5) 2000 × 1400 o 1400 × 2000, 1100 mm</t>
+          <t>la modifica è costruttiva: la sostituzione del macchinario ne è il caso n. 5)</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.1</t>
+          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="G134" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H134" s="10" t="inlineStr">
@@ -6969,28 +6969,28 @@
       <c r="M134" s="11" t="n"/>
       <c r="N134" s="11" t="n"/>
     </row>
-    <row r="135" ht="69" customHeight="1">
+    <row r="135" ht="43" customHeight="1">
       <c r="A135" s="10" t="n">
         <v>133</v>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
+          <t>DPR 162/1999, art. 12 c.4</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>specchio nei tipi 1–3; finiture che riducono le misure nominali al massimo di 15 mm per parete; segnale acustico regolabile 35–65 dB(A), fino a 80 in ambienti rumorosi; contrasto di Michelson con la A1:2022</t>
+          <t>prima della comunicazione, adeguamento della parte modificata o sostituita e delle altre parti interessate</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
+          <t>DPR 162/1999, art. 12 c.4</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="G135" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H135" s="10" t="inlineStr">
@@ -7021,22 +7021,22 @@
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, scopo</t>
+          <t>DPR 162/1999, art. 12 c.4–5</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>si usa con la UNI EN 81-20:2020; per gli impianti esistenti vale la UNI EN 81-82</t>
+          <t>comunicazione al Comune e al soggetto delle verifiche periodiche; l'impianto non resta in esercizio senza le comunicazioni aggiornate</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, scopo</t>
+          <t>DPR 162/1999, art. 12 c.4–5</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
@@ -7061,28 +7061,28 @@
       <c r="M136" s="11" t="n"/>
       <c r="N136" s="11" t="n"/>
     </row>
-    <row r="137" ht="43" customHeight="1">
+    <row r="137" ht="56" customHeight="1">
       <c r="A137" s="10" t="n">
         <v>135</v>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-71 (ascensori antivandalo)</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-71</t>
+          <t>DPR 162/1999, art. 14 c.3</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>categoria antivandalo da concordare con il committente; per la presunzione di conformità vale l'edizione 2005+A1:2006</t>
+          <t>verifica straordinaria da uno dei soggetti dell'art. 13 c.1, di norma limitata ai controlli sulle modifiche, con la documentazione delle modifiche e dei componenti sostituiti</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-71</t>
+          <t>DPR 162/1999, art. 14 c.3</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
@@ -7107,28 +7107,28 @@
       <c r="M137" s="11" t="n"/>
       <c r="N137" s="11" t="n"/>
     </row>
-    <row r="138" ht="108" customHeight="1">
+    <row r="138" ht="56" customHeight="1">
       <c r="A138" s="10" t="n">
         <v>136</v>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 7; Codice V.3.3.4</t>
+          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>ascensore antincendio: tutti i piani serviti; vano e porte di piano almeno REI 60; cabina interna almeno 1,10 × 2,10 m con accesso sul lato corto; botola sul tetto almeno 0,50 × 0,70 m; area dedicata almeno 5 m² a ogni piano; luce d'emergenza almeno 5 lux con 1 h di autonomia; IPX3 dove arriva l'acqua; linea dedicata con alimentazione di sicurezza</t>
+          <t>prove dell'organismo notificato: funzionamento a vuoto e a pieno carico, in mancanza di energia, prova statica a 1,25 volte la portata e controllo che non restino deformazioni</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 7; Codice V.3.3.4</t>
+          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
@@ -7159,22 +7159,22 @@
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Codice S.10, Tab. S.10-2</t>
+          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>alimentazione di sicurezza dell'ascensore antincendio: interruzione al massimo 15 s, autonomia oltre 30 min</t>
+          <t>documentazione tecnica con i risultati dei calcoli di progetto, le relazioni sulle prove e l'elenco delle norme armonizzate applicate, anche in parte</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr">
         <is>
-          <t>Codice S.10, Tab. S.10-2</t>
+          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
         </is>
       </c>
       <c r="F139" s="10" t="inlineStr">
@@ -7205,22 +7205,22 @@
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-72:2020</t>
+          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>requisiti propri della norma (cabina, tempi, protezione dall'acqua) da verificare sul testo</t>
+          <t>per gli ascensori dichiarati conformi dal 20/01/2027: requisiti dell'All. III del Regolamento macchine (tra cui 1.1.9 e 1.2.1), con una valutazione aggiuntiva per i requisiti nuovi o cambiati</t>
         </is>
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-72:2020</t>
+          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
         </is>
       </c>
       <c r="F140" s="10" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="G140" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H140" s="10" t="inlineStr">
@@ -7245,28 +7245,28 @@
       <c r="M140" s="11" t="n"/>
       <c r="N140" s="11" t="n"/>
     </row>
-    <row r="141" ht="56" customHeight="1">
+    <row r="141" ht="82" customHeight="1">
       <c r="A141" s="10" t="n">
         <v>139</v>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
+          <t>UNI EN 81-50:2020, 5.12.1 e 5.12.2.1</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>su comando della rivelazione incendio la cabina va al piano prestabilito e lascia uscire i passeggeri; con il Codice l'ascensore «dovrebbe» essere conforme alla UNI EN 81-73</t>
+          <t>il metodo del coefficiente di sicurezza delle funi vale solo per pulegge di acciaio o ghisa e funi d'acciaio secondo EN 12385-5; la flessione è semplice se il raggio della gola non supera 0,53 volte il diametro della fune: rilevare il materiale della puleggia e il raggio delle gole</t>
         </is>
       </c>
       <c r="E141" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
+          <t>UNI EN 81-50:2020, 5.12.1 e 5.12.2.1</t>
         </is>
       </c>
       <c r="F141" s="10" t="inlineStr">
@@ -7291,28 +7291,28 @@
       <c r="M141" s="11" t="n"/>
       <c r="N141" s="11" t="n"/>
     </row>
-    <row r="142" ht="56" customHeight="1">
+    <row r="142" ht="43" customHeight="1">
       <c r="A142" s="10" t="n">
         <v>140</v>
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-73:2020</t>
+          <t>UNI EN 81-20:2020, 5.6.2.2.1.2</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>segnali e comportamento della manovra da verificare sul testo; la norma serve anche da base per migliorare gli esistenti</t>
+          <t>tempo di risposta del limitatore di velocità: i suoi punti d'intervento distano al massimo 250 mm di corsa della fune del limitatore</t>
         </is>
       </c>
       <c r="E142" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-73:2020</t>
+          <t>UNI EN 81-20:2020, 5.6.2.2.1.2</t>
         </is>
       </c>
       <c r="F142" s="10" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="G142" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H142" s="10" t="inlineStr">
@@ -7337,28 +7337,28 @@
       <c r="M142" s="11" t="n"/>
       <c r="N142" s="11" t="n"/>
     </row>
-    <row r="143" ht="69" customHeight="1">
+    <row r="143" ht="56" customHeight="1">
       <c r="A143" s="10" t="n">
         <v>141</v>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-76:2025 (evacuazione delle persone con disabilità)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-76:2025</t>
+          <t>UNI EN 81-20:2020, 5.8.2.1.2.1 e 5.8.2.2.3</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>evacuazione delle persone con disabilità con l'ascensore: requisiti aggiuntivi alla EN 81-20 (manovra, alimentazione) da verificare sul testo</t>
+          <t>ammortizzatori (dato del fornitore): decelerazione non oltre 1 gn, sopra 2,5 gn al massimo per 0,04 s; per quelli ad accumulo non lineari anche picco non oltre 6 gn e rimbalzo non oltre 1 m/s</t>
         </is>
       </c>
       <c r="E143" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-76:2025</t>
+          <t>UNI EN 81-20:2020, 5.8.2.1.2.1 e 5.8.2.2.3</t>
         </is>
       </c>
       <c r="F143" s="10" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="G143" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H143" s="10" t="inlineStr">
@@ -7383,28 +7383,28 @@
       <c r="M143" s="11" t="n"/>
       <c r="N143" s="11" t="n"/>
     </row>
-    <row r="144" ht="56" customHeight="1">
+    <row r="144" ht="69" customHeight="1">
       <c r="A144" s="10" t="n">
         <v>142</v>
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 1</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>con accelerazione di progetto a_d fino a 1 m/s² nessuna prescrizione specifica; a_d e la posizione dei rilevatori si concordano con il progettista dell'edificio</t>
+          <t>cartello sopra o accanto allo schermo del contrappeso (5.2.5.5.1) con il gioco massimo ammesso tra contrappeso e ammortizzatore con la cabina al piano più alto, per conservare gli spazi in testata</t>
         </is>
       </c>
       <c r="E144" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 1</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1</t>
         </is>
       </c>
       <c r="F144" s="10" t="inlineStr">
@@ -7429,28 +7429,28 @@
       <c r="M144" s="11" t="n"/>
       <c r="N144" s="11" t="n"/>
     </row>
-    <row r="145" ht="95" customHeight="1">
+    <row r="145" ht="43" customHeight="1">
       <c r="A145" s="10" t="n">
         <v>143</v>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
+          <t>UNI EN 81-20:2020, 5.2.2.4</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>oltre 1 m/s²: massa della cabina nei calcoli (5.4.1), ritegni della cabina (5.4.2) e del contrappeso (5.5), protezione delle pulegge (5.6.1), tensioni e frecce delle guide (5.8.2, All. D), rilevazione e modo sismico (5.10.3, 5.10.4); soglie delle categorie dell'All. A da verificare sul testo</t>
+          <t>fossa più profonda di 2,50 m: porta di accesso; fino a 2,50 m porta di accesso oppure scala dentro il vano (appendice F)</t>
         </is>
       </c>
       <c r="E145" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
+          <t>UNI EN 81-20:2020, 5.2.2.4</t>
         </is>
       </c>
       <c r="F145" s="10" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="G145" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H145" s="10" t="inlineStr">
@@ -7481,22 +7481,22 @@
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 0.3</t>
+          <t>UNI EN 81-20:2020, 5.2.1.5.1 b)</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>non si applica agli impianti installati prima della sua pubblicazione</t>
+          <t>in fossa un commutatore di ispezione fisso, manovrabile da non oltre 0,30 m da uno spazio di rifugio</t>
         </is>
       </c>
       <c r="E146" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 0.3</t>
+          <t>UNI EN 81-20:2020, 5.2.1.5.1 b)</t>
         </is>
       </c>
       <c r="F146" s="10" t="inlineStr">
@@ -7521,28 +7521,28 @@
       <c r="M146" s="11" t="n"/>
       <c r="N146" s="11" t="n"/>
     </row>
-    <row r="147" ht="69" customHeight="1">
+    <row r="147" ht="43" customHeight="1">
       <c r="A147" s="10" t="n">
         <v>145</v>
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-80:2019</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>analisi dei rischi dell'impianto esistente e piano di miglioramento per priorità, scelta volontaria del proprietario</t>
+          <t>uno spazio di rifugio per ogni persona, tutti dello stesso tipo e senza sovrapposizioni; cartello con il numero di persone ammesse e la postura</t>
         </is>
       </c>
       <c r="E147" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-80:2019</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1</t>
         </is>
       </c>
       <c r="F147" s="10" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="G147" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H147" s="10" t="inlineStr">
@@ -7567,28 +7567,28 @@
       <c r="M147" s="11" t="n"/>
       <c r="N147" s="11" t="n"/>
     </row>
-    <row r="148" ht="56" customHeight="1">
+    <row r="148" ht="69" customHeight="1">
       <c r="A148" s="10" t="n">
         <v>146</v>
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-82:2026 (accessibilità degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-82:2026</t>
+          <t>UNI EN 81-20:2020, 5.2.1.4.1</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>miglioramento dell'accessibilità di un impianto esistente secondo i requisiti della EN 81-70</t>
+          <t>illuminazione del vano: almeno 50 lux a 1 m sopra il tetto della cabina nella sua proiezione e a 1 m sopra il fondo della fossa dove si sta, si lavora o si passa tra le zone di lavoro; almeno 20 lux altrove</t>
         </is>
       </c>
       <c r="E148" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-82:2026</t>
+          <t>UNI EN 81-20:2020, 5.2.1.4.1</t>
         </is>
       </c>
       <c r="F148" s="10" t="inlineStr">
@@ -7619,22 +7619,22 @@
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-83:2026 (antivandalo degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-83:2026</t>
+          <t>UNI EN 81-20:2020, 5.4.10.1 e 5.4.10.4</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>miglioramento della resistenza agli atti vandalici di un impianto esistente secondo la EN 81-71:2022 (voce 1.2 della Tab. A.1 della EN 81-80)</t>
+          <t>luce in cabina almeno 100 lux sui comandi e a 1 m dal pavimento; luce di emergenza di almeno 5 lux per un'ora presso gli allarmi in cabina e sul tetto e al centro di cabina e tetto, a 1 m</t>
         </is>
       </c>
       <c r="E149" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-83:2026</t>
+          <t>UNI EN 81-20:2020, 5.4.10.1 e 5.4.10.4</t>
         </is>
       </c>
       <c r="F149" s="10" t="inlineStr">
@@ -7659,28 +7659,28 @@
       <c r="M149" s="11" t="n"/>
       <c r="N149" s="11" t="n"/>
     </row>
-    <row r="150" ht="56" customHeight="1">
+    <row r="150" ht="43" customHeight="1">
       <c r="A150" s="10" t="n">
         <v>148</v>
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-20:2020, 5.4.4</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>piattaforma di distribuzione davanti alla porta di cabina: 1,50 × 1,50 m negli edifici nuovi, 1,40 × 1,40 m nell'adeguamento (fuori dal vano: in sito)</t>
+          <t>materiali della cabina secondo EN 13501-1: pavimento Cfl-s2, pareti C-s2,d1, soffitto C-s2,d0</t>
         </is>
       </c>
       <c r="E150" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-20:2020, 5.4.4</t>
         </is>
       </c>
       <c r="F150" s="10" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="H150" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I150" s="11" t="n"/>
@@ -7705,28 +7705,28 @@
       <c r="M150" s="11" t="n"/>
       <c r="N150" s="11" t="n"/>
     </row>
-    <row r="151" ht="56" customHeight="1">
+    <row r="151" ht="108" customHeight="1">
       <c r="A151" s="10" t="n">
         <v>149</v>
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-20:2020, 5.3.5.3.2, 5.3.5.3.4, 5.3.6.2.2.1 b) e 5.3.15.2 b)</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>porte di cabina e di piano a scorrimento automatico (nell'adeguamento la porta di piano può essere a battente se ad apertura automatica); porte aperte almeno 8 s, chiusura in almeno 4 s</t>
+          <t>pannelli delle porte con i dispositivi di ritenuta e le prove a pendolo (morbido da 800 mm; rigido da 500 mm sui pannelli in vetro); sulle porte automatiche un dispositivo di protezione che copre da 25 a 1600 mm sopra la soglia e rileva ostacoli di 50 mm; fuori dalla zona di sbloccaggio la porta di cabina, spinta con 1000 N, non si apre più di 50 mm</t>
         </is>
       </c>
       <c r="E151" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-20:2020, 5.3.5.3.2, 5.3.5.3.4, 5.3.6.2.2.1 b) e 5.3.15.2 b)</t>
         </is>
       </c>
       <c r="F151" s="10" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="H151" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I151" s="11" t="n"/>
@@ -7751,28 +7751,28 @@
       <c r="M151" s="11" t="n"/>
       <c r="N151" s="11" t="n"/>
     </row>
-    <row r="152" ht="43" customHeight="1">
+    <row r="152" ht="56" customHeight="1">
       <c r="A152" s="10" t="n">
         <v>150</v>
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI 10411-1:2024</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI 10411-1:2024, scopo</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>arresto ai piani con autolivellamento entro ± 2 cm; sosta ai piani con le porte chiuse</t>
+          <t>ascensori elettrici a frizione non conformi alla 95/16/CE né alla 2014/33/UE; esclude le modifiche che cambiano le misure antincendio (valgono il DM 15/09/2005 o il Codice V.3)</t>
         </is>
       </c>
       <c r="E152" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI 10411-1:2024, scopo</t>
         </is>
       </c>
       <c r="F152" s="10" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="H152" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I152" s="11" t="n"/>
@@ -7803,22 +7803,22 @@
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI 10411-11:2024</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
+          <t>UNI 10411-11:2024, scopo</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>pulsanti di cabina e di piano: il più alto tra 1,10 e 1,40 m, misurato all'asse del comando; bottoniera di cabina su una parete laterale ad almeno 0,35 m dalla porta</t>
+          <t>ascensori elettrici a frizione conformi alla Direttiva Ascensori; esclude le modifiche che cambiano le misure antincendio (valgono il DM 15/09/2005 o il Codice V.3)</t>
         </is>
       </c>
       <c r="E153" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
+          <t>UNI 10411-11:2024, scopo</t>
         </is>
       </c>
       <c r="F153" s="10" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="G153" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I153" s="11" t="n"/>
@@ -7843,28 +7843,28 @@
       <c r="M153" s="11" t="n"/>
       <c r="N153" s="11" t="n"/>
     </row>
-    <row r="154" ht="95" customHeight="1">
+    <row r="154" ht="108" customHeight="1">
       <c r="A154" s="10" t="n">
         <v>152</v>
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI 10411-11:2024</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
+          <t>UNI 10411-11:2024, 14.3 a) e App. A (14); UNI EN 81-20:2020, 5.6.6.2 e 5.6.7.3</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>citofono in cabina tra 1,10 e 1,30 m; luce d'emergenza con almeno 3 h di autonomia; campanello d'allarme e segnale luminoso di allarme ricevuto; arresto e inversione della chiusura; segnale acustico d'arrivo; numeri in rilievo e Braille, targa Braille di piano; sedile ribaltabile dove possibile</t>
+          <t>cambiando la macchina con protezioni ACOP o UCM esistenti: la modifica ne deve garantire il funzionamento, con una relazione sulla compatibilità della nuova macchina, oppure nuovi dispositivi con certificato di esame di tipo e dichiarazione di conformità; il freno della macchina vale come organo d'arresto solo se ridondante e autocontrollato</t>
         </is>
       </c>
       <c r="E154" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
+          <t>UNI 10411-11:2024, 14.3 a) e App. A (14); UNI EN 81-20:2020, 5.6.6.2 e 5.6.7.3</t>
         </is>
       </c>
       <c r="F154" s="10" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="H154" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I154" s="11" t="n"/>
@@ -7889,28 +7889,28 @@
       <c r="M154" s="11" t="n"/>
       <c r="N154" s="11" t="n"/>
     </row>
-    <row r="155" ht="56" customHeight="1">
+    <row r="155" ht="69" customHeight="1">
       <c r="A155" s="10" t="n">
         <v>153</v>
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
+          <t>UNI EN 81-21:2022, 1</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>ascensore obbligatorio oltre il terzo livello (contati interrati e porticati); negli immobili con più di tre livelli fuori terra un ascensore per ogni scala principale</t>
+          <t>ascensori installati in un edificio esistente quando vincoli dell'edificio impediscono di soddisfare alcuni requisiti della UNI EN 81-20:2020; non si applica agli ascensori installati prima della sua pubblicazione</t>
         </is>
       </c>
       <c r="E155" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
+          <t>UNI EN 81-21:2022, 1</t>
         </is>
       </c>
       <c r="F155" s="10" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="H155" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I155" s="11" t="n"/>
@@ -7935,28 +7935,28 @@
       <c r="M155" s="11" t="n"/>
       <c r="N155" s="11" t="n"/>
     </row>
-    <row r="156" ht="56" customHeight="1">
+    <row r="156" ht="82" customHeight="1">
       <c r="A156" s="10" t="n">
         <v>154</v>
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>nelle ristrutturazioni deroghe per impossibilità tecnica strutturale o impiantistica (privati: concesse dal Sindaco); edifici vincolati: deroga se le opere pregiudicano il bene</t>
+          <t>spazi di rifugio ridotti solo con l'accordo preventivo: in edificio esistente PEC al Ministero con la certificazione dell'organismo prima dell'installazione (Procedura 2: dichiarazione dei punti della EN 81-21 applicati); la EN 81-21 da sola non giustifica la deroga</t>
         </is>
       </c>
       <c r="E156" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
         </is>
       </c>
       <c r="F156" s="10" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="H156" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I156" s="11" t="n"/>
@@ -7987,22 +7987,22 @@
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+          <t>UNI EN 81-28:2022</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>il progettista applica il DM 15/09/2005 oppure la RTV V.3 del Codice: dove si usa il Codice il DM 2005 non si applica</t>
+          <t>teleallarme verso un servizio di soccorso: requisiti da verificare sul testo della norma (la UNI EN 81-28:2004 letta si applica agli impianti montati dopo la sua pubblicazione e vale da riferimento per gli esistenti, punto 1)</t>
         </is>
       </c>
       <c r="E157" s="10" t="inlineStr">
         <is>
-          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+          <t>UNI EN 81-28:2022</t>
         </is>
       </c>
       <c r="F157" s="10" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="G157" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H157" s="10" t="inlineStr">
@@ -8027,28 +8027,28 @@
       <c r="M157" s="11" t="n"/>
       <c r="N157" s="11" t="n"/>
     </row>
-    <row r="158" ht="95" customHeight="1">
+    <row r="158" ht="69" customHeight="1">
       <c r="A158" s="10" t="n">
         <v>156</v>
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: UNI EN 81-58:2022 (resistenza al fuoco delle porte di piano)</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, art. 1 c.2</t>
+          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>sugli impianti esistenti vale per le modifiche sostanziali: nuovo impianto; più fermate o altro azionamento; pareti del vano, porte di piano, locale macchine o pulegge sostituiti con materiali, modelli, dimensioni o criteri diversi; solai o scale rifatti che coinvolgono l'impianto; sopraelevazione; cambio di destinazione d'uso</t>
+          <t>porte di piano resistenti al fuoco (classi E, EI, EW) provate secondo la norma, quando fanno parte della compartimentazione del vano; sostituirle con modelli diversi è una modifica sostanziale ai fini antincendio</t>
         </is>
       </c>
       <c r="E158" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, art. 1 c.2</t>
+          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
         </is>
       </c>
       <c r="F158" s="10" t="inlineStr">
@@ -8073,28 +8073,28 @@
       <c r="M158" s="11" t="n"/>
       <c r="N158" s="11" t="n"/>
     </row>
-    <row r="159" ht="69" customHeight="1">
+    <row r="159" ht="95" customHeight="1">
       <c r="A159" s="10" t="n">
         <v>157</v>
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+          <t>UNI EN 81-70:2022, 5.3.1</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>tipo di vano: aperto, protetto o a prova di fumo (Codice: classi da SA a SE)</t>
+          <t>tipi di cabina (larghezza × profondità, luce della porta): 1) 1000 × 1300, 800; 2) 1100 × 1400, 900; 3) 1100 × 2100, 900; 4) 1600 × 1400 o 1400 × 1600, 900; 5) 2000 × 1400 o 1400 × 2000, 1100 mm (la UNI EN 81-70:2005 letta, Prospetto 1, ha tre tipi: 1000 × 1250, 1100 × 1400 e 2000 × 1400 mm)</t>
         </is>
       </c>
       <c r="E159" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+          <t>UNI EN 81-70:2022, 5.3.1</t>
         </is>
       </c>
       <c r="F159" s="10" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="G159" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H159" s="10" t="inlineStr">
@@ -8119,28 +8119,28 @@
       <c r="M159" s="11" t="n"/>
       <c r="N159" s="11" t="n"/>
     </row>
-    <row r="160" ht="69" customHeight="1">
+    <row r="160" ht="95" customHeight="1">
       <c r="A160" s="10" t="n">
         <v>158</v>
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 2</t>
+          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>pareti del vano, locale macchine e pulegge, setti e arcata non combustibili; pareti, pavimento e tetto della cabina in classe di reazione al fuoco non oltre 1</t>
+          <t>specchio nei tipi 1–3; finiture che riducono le misure nominali al massimo di 15 mm per parete; segnale acustico regolabile 35–65 dB(A), fino a 80 in ambienti rumorosi; contrasto di Michelson con la A1:2022 (nella UNI EN 81-70:2005 letta: specchio nei tipi 1 e 2, 15 mm, 35–65 dB(A); non ci sono gli 80 dB(A) né il contrasto di Michelson)</t>
         </is>
       </c>
       <c r="E160" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 2</t>
+          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
         </is>
       </c>
       <c r="F160" s="10" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="G160" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H160" s="10" t="inlineStr">
@@ -8165,28 +8165,28 @@
       <c r="M160" s="11" t="n"/>
       <c r="N160" s="11" t="n"/>
     </row>
-    <row r="161" ht="82" customHeight="1">
+    <row r="161" ht="43" customHeight="1">
       <c r="A161" s="10" t="n">
         <v>159</v>
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 5</t>
+          <t>UNI EN 81-70:2022, scopo</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>aerazione permanente in alto verso spazi scoperti di almeno il 3 % della pianta (vano almeno 0,20 m², locale macchine o pulegge almeno 0,05 m²), con una protezione che non lascia passare una sfera oltre 15 mm; non serve se il vano è aperto su spazi scoperti</t>
+          <t>si usa con la UNI EN 81-20:2020; per gli impianti esistenti vale la UNI EN 81-82</t>
         </is>
       </c>
       <c r="E161" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 5</t>
+          <t>UNI EN 81-70:2022, scopo</t>
         </is>
       </c>
       <c r="F161" s="10" t="inlineStr">
@@ -8211,28 +8211,28 @@
       <c r="M161" s="11" t="n"/>
       <c r="N161" s="11" t="n"/>
     </row>
-    <row r="162" ht="69" customHeight="1">
+    <row r="162" ht="43" customHeight="1">
       <c r="A162" s="10" t="n">
         <v>160</v>
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: UNI EN 81-71 (ascensori antivandalo)</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+          <t>UNI EN 81-71</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>estintore 21A89BC vicino all'accesso al macchinario; richiamo della cabina al piano prestabilito su comando della rivelazione quando la compartimentazione lo richiede</t>
+          <t>categoria antivandalo da concordare con il committente; per la presunzione di conformità vale l'edizione 2005+A1:2006</t>
         </is>
       </c>
       <c r="E162" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+          <t>UNI EN 81-71</t>
         </is>
       </c>
       <c r="F162" s="10" t="inlineStr">
@@ -8257,28 +8257,28 @@
       <c r="M162" s="11" t="n"/>
       <c r="N162" s="11" t="n"/>
     </row>
-    <row r="163" ht="69" customHeight="1">
+    <row r="163" ht="108" customHeight="1">
       <c r="A163" s="10" t="n">
         <v>161</v>
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>Codice S.9, Tab. S.9-3</t>
+          <t>DM 15/09/2005, punto 7; Codice V.3.3.4</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>piani tra 32 e 54 m: almeno un ascensore antincendio; oltre 54 m: almeno uno di soccorso; interrati tra −10 e −15 m: antincendio; sotto −15 m: soccorso</t>
+          <t>ascensore antincendio: tutti i piani serviti; vano e porte di piano almeno REI 60; cabina interna almeno 1,10 × 2,10 m con accesso sul lato corto; botola sul tetto almeno 0,50 × 0,70 m; area dedicata almeno 5 m² a ogni piano; luce d'emergenza almeno 5 lux con 1 h di autonomia; IPX3 dove arriva l'acqua; linea dedicata con alimentazione di sicurezza</t>
         </is>
       </c>
       <c r="E163" s="10" t="inlineStr">
         <is>
-          <t>Codice S.9, Tab. S.9-3</t>
+          <t>DM 15/09/2005, punto 7; Codice V.3.3.4</t>
         </is>
       </c>
       <c r="F163" s="10" t="inlineStr">
@@ -8303,28 +8303,28 @@
       <c r="M163" s="11" t="n"/>
       <c r="N163" s="11" t="n"/>
     </row>
-    <row r="164" ht="43" customHeight="1">
+    <row r="164" ht="56" customHeight="1">
       <c r="A164" s="10" t="n">
         <v>162</v>
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §3.1.4</t>
+          <t>Codice S.10, Tab. S.10-2</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>carichi del macchinario valutati caso per caso sui massimi prevedibili e riportati nel progetto e nel collaudo statico</t>
+          <t>alimentazione di sicurezza dell'ascensore antincendio: interruzione al massimo 15 s, autonomia oltre 30 min</t>
         </is>
       </c>
       <c r="E164" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §3.1.4</t>
+          <t>Codice S.10, Tab. S.10-2</t>
         </is>
       </c>
       <c r="F164" s="10" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="H164" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I164" s="11" t="n"/>
@@ -8349,28 +8349,28 @@
       <c r="M164" s="11" t="n"/>
       <c r="N164" s="11" t="n"/>
     </row>
-    <row r="165" ht="43" customHeight="1">
+    <row r="165" ht="56" customHeight="1">
       <c r="A165" s="10" t="n">
         <v>163</v>
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §8.4.1</t>
+          <t>UNI EN 81-72:2020</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>su un edificio esistente l'intervento è locale: verifica limitata alle parti interessate, senza ridurre la sicurezza preesistente</t>
+          <t>requisiti propri della norma (cabina, tempi, protezione dall'acqua) da verificare sul testo</t>
         </is>
       </c>
       <c r="E165" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §8.4.1</t>
+          <t>UNI EN 81-72:2020</t>
         </is>
       </c>
       <c r="F165" s="10" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="G165" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H165" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I165" s="11" t="n"/>
@@ -8395,28 +8395,28 @@
       <c r="M165" s="11" t="n"/>
       <c r="N165" s="11" t="n"/>
     </row>
-    <row r="166" ht="43" customHeight="1">
+    <row r="166" ht="56" customHeight="1">
       <c r="A166" s="10" t="n">
         <v>164</v>
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §11.4.1</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>ancoranti per uso strutturale qualificati; con azioni sismiche categoria C2 per tutte le classi d'uso</t>
+          <t>su comando della rivelazione incendio la cabina va al piano prestabilito e lascia uscire i passeggeri; con il Codice l'ascensore «dovrebbe» essere conforme alla UNI EN 81-73</t>
         </is>
       </c>
       <c r="E166" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §11.4.1</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
         </is>
       </c>
       <c r="F166" s="10" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="H166" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I166" s="11" t="n"/>
@@ -8441,28 +8441,28 @@
       <c r="M166" s="11" t="n"/>
       <c r="N166" s="11" t="n"/>
     </row>
-    <row r="167" ht="108" customHeight="1">
+    <row r="167" ht="56" customHeight="1">
       <c r="A167" s="10" t="n">
         <v>165</v>
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §7.2.3–7.2.4</t>
+          <t>UNI EN 81-73:2020</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>forza sismica sull'elemento non strutturale Fa = Sa·Wa/qa; nessun vincolo ad attrito; studio specifico oltre il 30 % del carico permanente del solaio o il 10 % di quello dell'intera struttura; progetto antisismico dell'impianto del produttore, dei collegamenti dell'installatore, dei solai e delle pareti d'ancoraggio del progettista strutturale</t>
+          <t>segnali e comportamento della manovra da verificare sul testo; la norma serve anche da base per migliorare gli esistenti (così la UNI EN 81-73:2005 letta, punto 1)</t>
         </is>
       </c>
       <c r="E167" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §7.2.3–7.2.4</t>
+          <t>UNI EN 81-73:2020</t>
         </is>
       </c>
       <c r="F167" s="10" t="inlineStr">
@@ -8472,12 +8472,12 @@
       </c>
       <c r="G167" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H167" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I167" s="11" t="n"/>
@@ -8487,28 +8487,28 @@
       <c r="M167" s="11" t="n"/>
       <c r="N167" s="11" t="n"/>
     </row>
-    <row r="168" ht="43" customHeight="1">
+    <row r="168" ht="69" customHeight="1">
       <c r="A168" s="10" t="n">
         <v>166</v>
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-76:2025 (evacuazione delle persone con disabilità)</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+          <t>UNI EN 81-76:2025</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>impianti: stabilità allo SLV per tutte le classi d'uso; nelle classi III e IV anche funzionamento allo SLO</t>
+          <t>evacuazione delle persone con disabilità con l'ascensore: requisiti aggiuntivi alla EN 81-20 (manovra, alimentazione) da verificare sul testo</t>
         </is>
       </c>
       <c r="E168" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+          <t>UNI EN 81-76:2025</t>
         </is>
       </c>
       <c r="F168" s="10" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="G168" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H168" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I168" s="11" t="n"/>
@@ -8533,10 +8533,1160 @@
       <c r="M168" s="11" t="n"/>
       <c r="N168" s="11" t="n"/>
     </row>
+    <row r="169" ht="56" customHeight="1">
+      <c r="A169" s="10" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C169" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-77:2022, 1</t>
+        </is>
+      </c>
+      <c r="D169" s="10" t="inlineStr">
+        <is>
+          <t>con accelerazione di progetto a_d fino a 1 m/s² nessuna prescrizione specifica; a_d e la posizione dei rilevatori si concordano con il progettista dell'edificio</t>
+        </is>
+      </c>
+      <c r="E169" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-77:2022, 1</t>
+        </is>
+      </c>
+      <c r="F169" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G169" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H169" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I169" s="11" t="n"/>
+      <c r="J169" s="11" t="n"/>
+      <c r="K169" s="11" t="n"/>
+      <c r="L169" s="11" t="n"/>
+      <c r="M169" s="11" t="n"/>
+      <c r="N169" s="11" t="n"/>
+    </row>
+    <row r="170" ht="95" customHeight="1">
+      <c r="A170" s="10" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C170" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="inlineStr">
+        <is>
+          <t>oltre 1 m/s²: massa della cabina nei calcoli (5.4.1), ritegni della cabina (5.4.2) e del contrappeso (5.5), protezione delle pulegge (5.6.1), tensioni e frecce delle guide (5.8.2, All. D), rilevazione e modo sismico (5.10.3, 5.10.4); soglie delle categorie dell'All. A da verificare sul testo</t>
+        </is>
+      </c>
+      <c r="E170" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
+        </is>
+      </c>
+      <c r="F170" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G170" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H170" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I170" s="11" t="n"/>
+      <c r="J170" s="11" t="n"/>
+      <c r="K170" s="11" t="n"/>
+      <c r="L170" s="11" t="n"/>
+      <c r="M170" s="11" t="n"/>
+      <c r="N170" s="11" t="n"/>
+    </row>
+    <row r="171" ht="43" customHeight="1">
+      <c r="A171" s="10" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-77:2022, 0.3</t>
+        </is>
+      </c>
+      <c r="D171" s="10" t="inlineStr">
+        <is>
+          <t>non si applica agli impianti installati prima della sua pubblicazione</t>
+        </is>
+      </c>
+      <c r="E171" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-77:2022, 0.3</t>
+        </is>
+      </c>
+      <c r="F171" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G171" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H171" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I171" s="11" t="n"/>
+      <c r="J171" s="11" t="n"/>
+      <c r="K171" s="11" t="n"/>
+      <c r="L171" s="11" t="n"/>
+      <c r="M171" s="11" t="n"/>
+      <c r="N171" s="11" t="n"/>
+    </row>
+    <row r="172" ht="69" customHeight="1">
+      <c r="A172" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
+        </is>
+      </c>
+      <c r="C172" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-80:2019</t>
+        </is>
+      </c>
+      <c r="D172" s="10" t="inlineStr">
+        <is>
+          <t>analisi dei rischi dell'impianto esistente e piano di miglioramento per priorità, scelta volontaria del proprietario (così le UNI EN 81-80:2004 e 2009 lette, punto 1 e appendice A)</t>
+        </is>
+      </c>
+      <c r="E172" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-80:2019</t>
+        </is>
+      </c>
+      <c r="F172" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G172" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H172" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I172" s="11" t="n"/>
+      <c r="J172" s="11" t="n"/>
+      <c r="K172" s="11" t="n"/>
+      <c r="L172" s="11" t="n"/>
+      <c r="M172" s="11" t="n"/>
+      <c r="N172" s="11" t="n"/>
+    </row>
+    <row r="173" ht="56" customHeight="1">
+      <c r="A173" s="10" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-82:2026 (accessibilità degli esistenti)</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-82:2026</t>
+        </is>
+      </c>
+      <c r="D173" s="10" t="inlineStr">
+        <is>
+          <t>miglioramento dell'accessibilità di un impianto esistente secondo i requisiti della EN 81-70</t>
+        </is>
+      </c>
+      <c r="E173" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-82:2026</t>
+        </is>
+      </c>
+      <c r="F173" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G173" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H173" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I173" s="11" t="n"/>
+      <c r="J173" s="11" t="n"/>
+      <c r="K173" s="11" t="n"/>
+      <c r="L173" s="11" t="n"/>
+      <c r="M173" s="11" t="n"/>
+      <c r="N173" s="11" t="n"/>
+    </row>
+    <row r="174" ht="56" customHeight="1">
+      <c r="A174" s="10" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: UNI EN 81-83:2026 (antivandalo degli esistenti)</t>
+        </is>
+      </c>
+      <c r="C174" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-83:2026</t>
+        </is>
+      </c>
+      <c r="D174" s="10" t="inlineStr">
+        <is>
+          <t>miglioramento della resistenza agli atti vandalici di un impianto esistente secondo la EN 81-71:2022 (voce 1.2 della Tab. A.1 della EN 81-80)</t>
+        </is>
+      </c>
+      <c r="E174" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-83:2026</t>
+        </is>
+      </c>
+      <c r="F174" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G174" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H174" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I174" s="11" t="n"/>
+      <c r="J174" s="11" t="n"/>
+      <c r="K174" s="11" t="n"/>
+      <c r="L174" s="11" t="n"/>
+      <c r="M174" s="11" t="n"/>
+      <c r="N174" s="11" t="n"/>
+    </row>
+    <row r="175" ht="56" customHeight="1">
+      <c r="A175" s="10" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+        </is>
+      </c>
+      <c r="C175" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12</t>
+        </is>
+      </c>
+      <c r="D175" s="10" t="inlineStr">
+        <is>
+          <t>piattaforma di distribuzione davanti alla porta di cabina: 1,50 × 1,50 m negli edifici nuovi, 1,40 × 1,40 m nell'adeguamento (fuori dal vano: in sito)</t>
+        </is>
+      </c>
+      <c r="E175" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12</t>
+        </is>
+      </c>
+      <c r="F175" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G175" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H175" s="10" t="inlineStr">
+        <is>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+        </is>
+      </c>
+      <c r="I175" s="11" t="n"/>
+      <c r="J175" s="11" t="n"/>
+      <c r="K175" s="11" t="n"/>
+      <c r="L175" s="11" t="n"/>
+      <c r="M175" s="11" t="n"/>
+      <c r="N175" s="11" t="n"/>
+    </row>
+    <row r="176" ht="56" customHeight="1">
+      <c r="A176" s="10" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+        </is>
+      </c>
+      <c r="C176" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12</t>
+        </is>
+      </c>
+      <c r="D176" s="10" t="inlineStr">
+        <is>
+          <t>porte di cabina e di piano a scorrimento automatico (nell'adeguamento la porta di piano può essere a battente se ad apertura automatica); porte aperte almeno 8 s, chiusura in almeno 4 s</t>
+        </is>
+      </c>
+      <c r="E176" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12</t>
+        </is>
+      </c>
+      <c r="F176" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G176" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H176" s="10" t="inlineStr">
+        <is>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+        </is>
+      </c>
+      <c r="I176" s="11" t="n"/>
+      <c r="J176" s="11" t="n"/>
+      <c r="K176" s="11" t="n"/>
+      <c r="L176" s="11" t="n"/>
+      <c r="M176" s="11" t="n"/>
+      <c r="N176" s="11" t="n"/>
+    </row>
+    <row r="177" ht="43" customHeight="1">
+      <c r="A177" s="10" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+        </is>
+      </c>
+      <c r="C177" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12</t>
+        </is>
+      </c>
+      <c r="D177" s="10" t="inlineStr">
+        <is>
+          <t>arresto ai piani con autolivellamento entro ± 2 cm; sosta ai piani con le porte chiuse</t>
+        </is>
+      </c>
+      <c r="E177" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12</t>
+        </is>
+      </c>
+      <c r="F177" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G177" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H177" s="10" t="inlineStr">
+        <is>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+        </is>
+      </c>
+      <c r="I177" s="11" t="n"/>
+      <c r="J177" s="11" t="n"/>
+      <c r="K177" s="11" t="n"/>
+      <c r="L177" s="11" t="n"/>
+      <c r="M177" s="11" t="n"/>
+      <c r="N177" s="11" t="n"/>
+    </row>
+    <row r="178" ht="56" customHeight="1">
+      <c r="A178" s="10" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+        </is>
+      </c>
+      <c r="C178" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
+        </is>
+      </c>
+      <c r="D178" s="10" t="inlineStr">
+        <is>
+          <t>pulsanti di cabina e di piano: il più alto tra 1,10 e 1,40 m, misurato all'asse del comando; bottoniera di cabina su una parete laterale ad almeno 0,35 m dalla porta</t>
+        </is>
+      </c>
+      <c r="E178" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
+        </is>
+      </c>
+      <c r="F178" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G178" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H178" s="10" t="inlineStr">
+        <is>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+        </is>
+      </c>
+      <c r="I178" s="11" t="n"/>
+      <c r="J178" s="11" t="n"/>
+      <c r="K178" s="11" t="n"/>
+      <c r="L178" s="11" t="n"/>
+      <c r="M178" s="11" t="n"/>
+      <c r="N178" s="11" t="n"/>
+    </row>
+    <row r="179" ht="95" customHeight="1">
+      <c r="A179" s="10" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+        </is>
+      </c>
+      <c r="C179" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
+        </is>
+      </c>
+      <c r="D179" s="10" t="inlineStr">
+        <is>
+          <t>citofono in cabina tra 1,10 e 1,30 m; luce d'emergenza con almeno 3 h di autonomia; campanello d'allarme e segnale luminoso di allarme ricevuto; arresto e inversione della chiusura; segnale acustico d'arrivo; numeri in rilievo e Braille, targa Braille di piano; sedile ribaltabile dove possibile</t>
+        </is>
+      </c>
+      <c r="E179" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
+        </is>
+      </c>
+      <c r="F179" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G179" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H179" s="10" t="inlineStr">
+        <is>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+        </is>
+      </c>
+      <c r="I179" s="11" t="n"/>
+      <c r="J179" s="11" t="n"/>
+      <c r="K179" s="11" t="n"/>
+      <c r="L179" s="11" t="n"/>
+      <c r="M179" s="11" t="n"/>
+      <c r="N179" s="11" t="n"/>
+    </row>
+    <row r="180" ht="56" customHeight="1">
+      <c r="A180" s="10" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+        </is>
+      </c>
+      <c r="C180" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
+        </is>
+      </c>
+      <c r="D180" s="10" t="inlineStr">
+        <is>
+          <t>ascensore obbligatorio oltre il terzo livello (contati interrati e porticati); negli immobili con più di tre livelli fuori terra un ascensore per ogni scala principale</t>
+        </is>
+      </c>
+      <c r="E180" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
+        </is>
+      </c>
+      <c r="F180" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G180" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H180" s="10" t="inlineStr">
+        <is>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+        </is>
+      </c>
+      <c r="I180" s="11" t="n"/>
+      <c r="J180" s="11" t="n"/>
+      <c r="K180" s="11" t="n"/>
+      <c r="L180" s="11" t="n"/>
+      <c r="M180" s="11" t="n"/>
+      <c r="N180" s="11" t="n"/>
+    </row>
+    <row r="181" ht="56" customHeight="1">
+      <c r="A181" s="10" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+        </is>
+      </c>
+      <c r="C181" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+        </is>
+      </c>
+      <c r="D181" s="10" t="inlineStr">
+        <is>
+          <t>nelle ristrutturazioni deroghe per impossibilità tecnica strutturale o impiantistica (privati: concesse dal Sindaco); edifici vincolati: deroga se le opere pregiudicano il bene</t>
+        </is>
+      </c>
+      <c r="E181" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+        </is>
+      </c>
+      <c r="F181" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G181" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H181" s="10" t="inlineStr">
+        <is>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+        </is>
+      </c>
+      <c r="I181" s="11" t="n"/>
+      <c r="J181" s="11" t="n"/>
+      <c r="K181" s="11" t="n"/>
+      <c r="L181" s="11" t="n"/>
+      <c r="M181" s="11" t="n"/>
+      <c r="N181" s="11" t="n"/>
+    </row>
+    <row r="182" ht="69" customHeight="1">
+      <c r="A182" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C182" s="10" t="inlineStr">
+        <is>
+          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="inlineStr">
+        <is>
+          <t>il progettista applica il DM 15/09/2005 oppure la RTV V.3 del Codice: dove si usa il Codice il DM 2005 non si applica</t>
+        </is>
+      </c>
+      <c r="E182" s="10" t="inlineStr">
+        <is>
+          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+        </is>
+      </c>
+      <c r="F182" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G182" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H182" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I182" s="11" t="n"/>
+      <c r="J182" s="11" t="n"/>
+      <c r="K182" s="11" t="n"/>
+      <c r="L182" s="11" t="n"/>
+      <c r="M182" s="11" t="n"/>
+      <c r="N182" s="11" t="n"/>
+    </row>
+    <row r="183" ht="95" customHeight="1">
+      <c r="A183" s="10" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C183" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, art. 1 c.2</t>
+        </is>
+      </c>
+      <c r="D183" s="10" t="inlineStr">
+        <is>
+          <t>sugli impianti esistenti vale per le modifiche sostanziali: nuovo impianto; più fermate o altro azionamento; pareti del vano, porte di piano, locale macchine o pulegge sostituiti con materiali, modelli, dimensioni o criteri diversi; solai o scale rifatti che coinvolgono l'impianto; sopraelevazione; cambio di destinazione d'uso</t>
+        </is>
+      </c>
+      <c r="E183" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, art. 1 c.2</t>
+        </is>
+      </c>
+      <c r="F183" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G183" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H183" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I183" s="11" t="n"/>
+      <c r="J183" s="11" t="n"/>
+      <c r="K183" s="11" t="n"/>
+      <c r="L183" s="11" t="n"/>
+      <c r="M183" s="11" t="n"/>
+      <c r="N183" s="11" t="n"/>
+    </row>
+    <row r="184" ht="69" customHeight="1">
+      <c r="A184" s="10" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C184" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+        </is>
+      </c>
+      <c r="D184" s="10" t="inlineStr">
+        <is>
+          <t>tipo di vano: aperto, protetto o a prova di fumo (Codice: classi da SA a SE)</t>
+        </is>
+      </c>
+      <c r="E184" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+        </is>
+      </c>
+      <c r="F184" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G184" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H184" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I184" s="11" t="n"/>
+      <c r="J184" s="11" t="n"/>
+      <c r="K184" s="11" t="n"/>
+      <c r="L184" s="11" t="n"/>
+      <c r="M184" s="11" t="n"/>
+      <c r="N184" s="11" t="n"/>
+    </row>
+    <row r="185" ht="69" customHeight="1">
+      <c r="A185" s="10" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C185" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 2</t>
+        </is>
+      </c>
+      <c r="D185" s="10" t="inlineStr">
+        <is>
+          <t>pareti del vano, locale macchine e pulegge, setti e arcata non combustibili; pareti, pavimento e tetto della cabina in classe di reazione al fuoco non oltre 1</t>
+        </is>
+      </c>
+      <c r="E185" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 2</t>
+        </is>
+      </c>
+      <c r="F185" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G185" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H185" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I185" s="11" t="n"/>
+      <c r="J185" s="11" t="n"/>
+      <c r="K185" s="11" t="n"/>
+      <c r="L185" s="11" t="n"/>
+      <c r="M185" s="11" t="n"/>
+      <c r="N185" s="11" t="n"/>
+    </row>
+    <row r="186" ht="82" customHeight="1">
+      <c r="A186" s="10" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C186" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 5</t>
+        </is>
+      </c>
+      <c r="D186" s="10" t="inlineStr">
+        <is>
+          <t>aerazione permanente in alto verso spazi scoperti di almeno il 3 % della pianta (vano almeno 0,20 m², locale macchine o pulegge almeno 0,05 m²), con una protezione che non lascia passare una sfera oltre 15 mm; non serve se il vano è aperto su spazi scoperti</t>
+        </is>
+      </c>
+      <c r="E186" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 5</t>
+        </is>
+      </c>
+      <c r="F186" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G186" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H186" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I186" s="11" t="n"/>
+      <c r="J186" s="11" t="n"/>
+      <c r="K186" s="11" t="n"/>
+      <c r="L186" s="11" t="n"/>
+      <c r="M186" s="11" t="n"/>
+      <c r="N186" s="11" t="n"/>
+    </row>
+    <row r="187" ht="69" customHeight="1">
+      <c r="A187" s="10" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C187" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+        </is>
+      </c>
+      <c r="D187" s="10" t="inlineStr">
+        <is>
+          <t>estintore 21A89BC vicino all'accesso al macchinario; richiamo della cabina al piano prestabilito su comando della rivelazione quando la compartimentazione lo richiede</t>
+        </is>
+      </c>
+      <c r="E187" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+        </is>
+      </c>
+      <c r="F187" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G187" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H187" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I187" s="11" t="n"/>
+      <c r="J187" s="11" t="n"/>
+      <c r="K187" s="11" t="n"/>
+      <c r="L187" s="11" t="n"/>
+      <c r="M187" s="11" t="n"/>
+      <c r="N187" s="11" t="n"/>
+    </row>
+    <row r="188" ht="69" customHeight="1">
+      <c r="A188" s="10" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C188" s="10" t="inlineStr">
+        <is>
+          <t>Codice S.9, Tab. S.9-3</t>
+        </is>
+      </c>
+      <c r="D188" s="10" t="inlineStr">
+        <is>
+          <t>piani tra 32 e 54 m: almeno un ascensore antincendio; oltre 54 m: almeno uno di soccorso; interrati tra −10 e −15 m: antincendio; sotto −15 m: soccorso</t>
+        </is>
+      </c>
+      <c r="E188" s="10" t="inlineStr">
+        <is>
+          <t>Codice S.9, Tab. S.9-3</t>
+        </is>
+      </c>
+      <c r="F188" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G188" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H188" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I188" s="11" t="n"/>
+      <c r="J188" s="11" t="n"/>
+      <c r="K188" s="11" t="n"/>
+      <c r="L188" s="11" t="n"/>
+      <c r="M188" s="11" t="n"/>
+      <c r="N188" s="11" t="n"/>
+    </row>
+    <row r="189" ht="43" customHeight="1">
+      <c r="A189" s="10" t="n">
+        <v>187</v>
+      </c>
+      <c r="B189" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C189" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §3.1.4</t>
+        </is>
+      </c>
+      <c r="D189" s="10" t="inlineStr">
+        <is>
+          <t>carichi del macchinario valutati caso per caso sui massimi prevedibili e riportati nel progetto e nel collaudo statico</t>
+        </is>
+      </c>
+      <c r="E189" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §3.1.4</t>
+        </is>
+      </c>
+      <c r="F189" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G189" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H189" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I189" s="11" t="n"/>
+      <c r="J189" s="11" t="n"/>
+      <c r="K189" s="11" t="n"/>
+      <c r="L189" s="11" t="n"/>
+      <c r="M189" s="11" t="n"/>
+      <c r="N189" s="11" t="n"/>
+    </row>
+    <row r="190" ht="43" customHeight="1">
+      <c r="A190" s="10" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C190" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §8.4.1</t>
+        </is>
+      </c>
+      <c r="D190" s="10" t="inlineStr">
+        <is>
+          <t>su un edificio esistente l'intervento è locale: verifica limitata alle parti interessate, senza ridurre la sicurezza preesistente</t>
+        </is>
+      </c>
+      <c r="E190" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §8.4.1</t>
+        </is>
+      </c>
+      <c r="F190" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G190" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H190" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I190" s="11" t="n"/>
+      <c r="J190" s="11" t="n"/>
+      <c r="K190" s="11" t="n"/>
+      <c r="L190" s="11" t="n"/>
+      <c r="M190" s="11" t="n"/>
+      <c r="N190" s="11" t="n"/>
+    </row>
+    <row r="191" ht="43" customHeight="1">
+      <c r="A191" s="10" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C191" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §11.4.1</t>
+        </is>
+      </c>
+      <c r="D191" s="10" t="inlineStr">
+        <is>
+          <t>ancoranti per uso strutturale qualificati; con azioni sismiche categoria C2 per tutte le classi d'uso</t>
+        </is>
+      </c>
+      <c r="E191" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §11.4.1</t>
+        </is>
+      </c>
+      <c r="F191" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G191" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H191" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I191" s="11" t="n"/>
+      <c r="J191" s="11" t="n"/>
+      <c r="K191" s="11" t="n"/>
+      <c r="L191" s="11" t="n"/>
+      <c r="M191" s="11" t="n"/>
+      <c r="N191" s="11" t="n"/>
+    </row>
+    <row r="192" ht="108" customHeight="1">
+      <c r="A192" s="10" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C192" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §7.2.3–7.2.4</t>
+        </is>
+      </c>
+      <c r="D192" s="10" t="inlineStr">
+        <is>
+          <t>forza sismica sull'elemento non strutturale Fa = Sa·Wa/qa; nessun vincolo ad attrito; studio specifico oltre il 30 % del carico permanente del solaio o il 10 % di quello dell'intera struttura; progetto antisismico dell'impianto del produttore, dei collegamenti dell'installatore, dei solai e delle pareti d'ancoraggio del progettista strutturale</t>
+        </is>
+      </c>
+      <c r="E192" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §7.2.3–7.2.4</t>
+        </is>
+      </c>
+      <c r="F192" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G192" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H192" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I192" s="11" t="n"/>
+      <c r="J192" s="11" t="n"/>
+      <c r="K192" s="11" t="n"/>
+      <c r="L192" s="11" t="n"/>
+      <c r="M192" s="11" t="n"/>
+      <c r="N192" s="11" t="n"/>
+    </row>
+    <row r="193" ht="43" customHeight="1">
+      <c r="A193" s="10" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C193" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+        </is>
+      </c>
+      <c r="D193" s="10" t="inlineStr">
+        <is>
+          <t>impianti: stabilità allo SLV per tutte le classi d'uso; nelle classi III e IV anche funzionamento allo SLO</t>
+        </is>
+      </c>
+      <c r="E193" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+        </is>
+      </c>
+      <c r="F193" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G193" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H193" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I193" s="11" t="n"/>
+      <c r="J193" s="11" t="n"/>
+      <c r="K193" s="11" t="n"/>
+      <c r="L193" s="11" t="n"/>
+      <c r="M193" s="11" t="n"/>
+      <c r="N193" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N168"/>
+  <autoFilter ref="A1:N193"/>
   <dataValidations count="1">
-    <dataValidation sqref="I3:I168" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
+    <dataValidation sqref="I3:I193" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
       <formula1>"conforme,diverso,non applicabile"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8579,7 +9729,7 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$168,"da verificare")</f>
+        <f>COUNTIF(Voci!$G$3:$G$193,"da verificare")</f>
         <v/>
       </c>
     </row>
@@ -8590,7 +9740,7 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$168,"confermato")</f>
+        <f>COUNTIF(Voci!$G$3:$G$193,"confermato")</f>
         <v/>
       </c>
     </row>
@@ -8601,7 +9751,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$168,"scelta del software")</f>
+        <f>COUNTIF(Voci!$G$3:$G$193,"scelta del software")</f>
         <v/>
       </c>
     </row>
@@ -8612,7 +9762,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$168,"stima")</f>
+        <f>COUNTIF(Voci!$G$3:$G$193,"stima")</f>
         <v/>
       </c>
     </row>
@@ -8623,7 +9773,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$168,"derivazione")</f>
+        <f>COUNTIF(Voci!$G$3:$G$193,"derivazione")</f>
         <v/>
       </c>
     </row>
@@ -8634,7 +9784,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$168,"prassi di cantiere")</f>
+        <f>COUNTIF(Voci!$G$3:$G$193,"prassi di cantiere")</f>
         <v/>
       </c>
     </row>
@@ -8645,7 +9795,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTA(Voci!$A$3:$A$168)</f>
+        <f>COUNTA(Voci!$A$3:$A$193)</f>
         <v/>
       </c>
     </row>
@@ -8663,7 +9813,7 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$168,"conforme")</f>
+        <f>COUNTIF(Voci!$I$3:$I$193,"conforme")</f>
         <v/>
       </c>
     </row>
@@ -8674,7 +9824,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$168,"diverso")</f>
+        <f>COUNTIF(Voci!$I$3:$I$193,"diverso")</f>
         <v/>
       </c>
     </row>
@@ -8685,7 +9835,7 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$168,"non applicabile")</f>
+        <f>COUNTIF(Voci!$I$3:$I$193,"non applicabile")</f>
         <v/>
       </c>
     </row>
@@ -8696,14 +9846,14 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>COUNTBLANK(Voci!$I$3:$I$168)</f>
+        <f>COUNTBLANK(Voci!$I$3:$I$193)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Conteggi sulle righe 3–168 del foglio «Voci» (la riga 2 è l'esempio).</t>
+          <t>Conteggi sulle righe 3–193 del foglio «Voci» (la riga 2 è l'esempio).</t>
         </is>
       </c>
     </row>

--- a/liftpilot/docs/lista-verifica-normativa.xlsx
+++ b/liftpilot/docs/lista-verifica-normativa.xlsx
@@ -943,7 +943,7 @@
       <c r="M3" s="11" t="n"/>
       <c r="N3" s="11" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="43" customHeight="1">
       <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
@@ -969,7 +969,7 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>BS EN 81-50:2020, estratto pubblico del testo, p. 50</t>
+          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 42</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
@@ -989,7 +989,7 @@
       <c r="M4" s="11" t="n"/>
       <c r="N4" s="11" t="n"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="69" customHeight="1">
       <c r="A5" s="10" t="n">
         <v>3</v>
       </c>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>BS EN 81-50:2020, estratto pubblico del testo, p. 50 (v_f: velocità delle funi alla velocità nominale della cabina)</t>
+          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 42 (v_f: velocità delle funi alla velocità nominale della cabina)</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -1035,7 +1035,7 @@
       <c r="M5" s="11" t="n"/>
       <c r="N5" s="11" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="43" customHeight="1">
       <c r="A6" s="10" t="n">
         <v>4</v>
       </c>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>BS EN 81-50:2020, estratto pubblico del testo, p. 50</t>
+          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 42</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.3</t>
+          <t>UNI EN 81-50:2020, 5.11.2.2.1 e 5.11.3</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>BS EN 81-50:2020, estratto pubblico del testo, p. 52 (al caricamento e con la cabina bloccata a = 0)</t>
+          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 40 e 44 (al caricamento e con la cabina bloccata a = 0)</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Forza massima al volantino — Il mezzo meccanico è ammesso solo se la forza per portare la cabina a una fermata non supera 150 N (5.9.2.3.1 a)): non verificato dal software.</t>
+          <t>Forza massima al volantino — Il software verifica i 400 N; i 150 N del mezzo meccanico (5.9.2.3.1 a)) non sono verificati: sono nella lista da verificare.</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>≤ 400 N, altrimenti manovra elettrica di emergenza</t>
+          <t>≤ 400 N per far salire la cabina con la portata, altrimenti manovra elettrica di emergenza; il mezzo meccanico è ammesso se per portare la cabina a una fermata bastano 150 N</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">

--- a/liftpilot/docs/lista-verifica-normativa.xlsx
+++ b/liftpilot/docs/lista-verifica-normativa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Riepilogo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$206</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Voci'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N193"/>
+  <dimension ref="A1:N206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -897,7 +897,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="147" customHeight="1">
       <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
@@ -908,7 +908,7 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Aderenza: tre condizioni di Euler-Eytelwein</t>
+          <t>Aderenza: tre condizioni di Euler-Eytelwein — Con la cabina o il contrappeso bloccati la condizione serve quando è l'aderenza a impedire il sollevamento: la UNI EN 81-20:2020 (5.5.3 c)) ammette in alternativa un dispositivo elettrico di sicurezza; la UNI EN 81-1:2008 (9.3 c)) no. Il software verifica sempre la condizione: se c'è il dispositivo, lo decide l'ingegnere.</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 39–40</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 39–40</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 42</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 42</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 42 (v_f: velocità delle funi alla velocità nominale della cabina)</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 42 (v_f: velocità delle funi alla velocità nominale della cabina)</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 42</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 42</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 40 e 44 (al caricamento e con la cabina bloccata a = 0)</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 40 e 44 (al caricamento e con la cabina bloccata a = 0)</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 40</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 40</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Decelerazione della verifica di frenatura con ammortizzatori a corsa ridotta — La UNI EN 81-50:2020 non dà un numero: con ammortizzatori a corsa ridotta la decelerazione è la minima che porta cabina e contrappeso alla velocità di progetto degli ammortizzatori, mai sotto 0,5 m/s². Il software tiene 0,8 m/s², il valore della UNI EN 81-1: l'ingegnere lo sostituisce con quello calcolato dai dati degli ammortizzatori.</t>
+          <t>Decelerazione della verifica di frenatura con ammortizzatori a corsa ridotta — La UNI EN 81-50:2020 non dà un numero: con ammortizzatori a corsa ridotta la decelerazione è la minima che porta cabina e contrappeso alla velocità di progetto degli ammortizzatori, mai sotto 0,5 m/s². Il software tiene 0,8 m/s², il valore della UNI EN 81-1:2008: l'ingegnere lo sostituisce con quello calcolato dai dati degli ammortizzatori.</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-1:2008, testo della norma fornito dal cliente, letto il 2026-10-06, p. 167; UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 40</t>
+          <t>UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 167; UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 40</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 40</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 40</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 40–41</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 40–41</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 41</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 41</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Limite del sottosquadro — fino alla versione 1.1.0 del motore il limite era 106°, il valore raccomandato della UNI EN 81-1 (M.2.2.1)</t>
+          <t>Limite del sottosquadro — fino alla versione 1.1.0 del motore il limite era 106°, il valore raccomandato della UNI EN 81-1:2008 (M.2.2.1.1)</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 40–41</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 40–41</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -1541,7 +1541,7 @@
       <c r="M16" s="11" t="n"/>
       <c r="N16" s="11" t="n"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="43" customHeight="1">
       <c r="A17" s="10" t="n">
         <v>15</v>
       </c>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 41; Montanari consiglia 35–40°</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 41; Montanari consiglia 35–40°</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 40–41</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 40–41</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 74</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 74</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -1679,7 +1679,7 @@
       <c r="M19" s="11" t="n"/>
       <c r="N19" s="11" t="n"/>
     </row>
-    <row r="20" ht="82" customHeight="1">
+    <row r="20" ht="108" customHeight="1">
       <c r="A20" s="10" t="n">
         <v>18</v>
       </c>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Rapporto D/d delle pulegge di rinvio</t>
+          <t>Rapporto D/d delle pulegge di rinvio — Il limite vale per ogni puleggia (5.5.2.1), mentre Dp è uno solo e nel calcolo di N_equiv(p) è la media delle pulegge di rinvio (UNI EN 81-50:2020, 5.12.2.3): con pulegge di diametro diverso si controlla la più piccola.</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 74; UNI 10411-1:2024, testo della norma fornito dal cliente, letto il 2026-10-06, p. 14</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 74; UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 14</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Numero minimo di funi</t>
+          <t>Numero minimo di funi — Con 2 sole funi la UNI EN 81-20:2020 (5.5.5.3 a)) chiede anche un dispositivo elettrico di sicurezza contro l'allungamento anomalo di una fune rispetto all'altra; il software non lo verifica.</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 74</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 74</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 74–75; UNI 10411-1:2024, testo della norma fornito dal cliente, letto il 2026-10-06, p. 13</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 74–75; UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 13</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -1863,7 +1863,7 @@
       <c r="M23" s="11" t="n"/>
       <c r="N23" s="11" t="n"/>
     </row>
-    <row r="24" ht="43" customHeight="1">
+    <row r="24" ht="69" customHeight="1">
       <c r="A24" s="10" t="n">
         <v>22</v>
       </c>
@@ -1884,12 +1884,12 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12 (ex EN 81-1 Allegato N)</t>
+          <t>UNI EN 81-50:2020, 5.12.3 (ex UNI EN 81-1:2008, appendice N)</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>riprodotto su due casi pubblicati (liftdesign.it S_f 16,69; Mellor)</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 46; riprodotto anche su due casi pubblicati (liftdesign.it S_f 16,69; Mellor)</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -1909,7 +1909,7 @@
       <c r="M24" s="11" t="n"/>
       <c r="N24" s="11" t="n"/>
     </row>
-    <row r="25" ht="121" customHeight="1">
+    <row r="25" ht="108" customHeight="1">
       <c r="A25" s="10" t="n">
         <v>23</v>
       </c>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>N_equiv delle pulegge — D è il diametro della puleggia di frizione, Dp la media delle altre pulegge. La flessione è inversa solo tra due pulegge consecutive ad assi fissi, con i punti di contatto a meno di 200·d e i piani di flessione ruotati di oltre 120°: la classifica il progettista.</t>
+          <t>N_equiv delle pulegge — D: diametro della puleggia di trazione; Dp: media delle altre pulegge. La flessione è inversa solo tra due pulegge consecutive ad assi fissi, con i punti di contatto a meno di 200·d e i piani di flessione ruotati di oltre 120°: la classifica il progettista.</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 46</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 46</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -1955,7 +1955,7 @@
       <c r="M25" s="11" t="n"/>
       <c r="N25" s="11" t="n"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="82" customHeight="1">
       <c r="A26" s="10" t="n">
         <v>24</v>
       </c>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>N_equiv(t) della gola</t>
+          <t>N_equiv(t) della gola — Il prospetto non ha una riga per la gola a V con sottosquadro: il software prende il maggiore tra il valore di β (riga a U) e quello di γ (riga a V), dal lato della sicurezza.</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12.2.2, tabella 2</t>
+          <t>UNI EN 81-50:2020, 5.12.2.2, prospetto 2</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>BS EN 81-50:2020, estratto pubblico del testo, p. 55 (i valori della gola a V differiscono da quelli della EN 81-1)</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 46 (i valori della gola a V differiscono da quelli della UNI EN 81-1:2008, prospetto N.1)</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -2001,7 +2001,7 @@
       <c r="M26" s="11" t="n"/>
       <c r="N26" s="11" t="n"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="43" customHeight="1">
       <c r="A27" s="10" t="n">
         <v>25</v>
       </c>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>BS EN 81-50:2020, estratto pubblico del testo, p. 55 (la norma consente l'interpolazione lineare)</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 46</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 74–75</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 74–75</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
@@ -2185,7 +2185,7 @@
       <c r="M30" s="11" t="n"/>
       <c r="N30" s="11" t="n"/>
     </row>
-    <row r="31" ht="82" customHeight="1">
+    <row r="31" ht="69" customHeight="1">
       <c r="A31" s="10" t="n">
         <v>29</v>
       </c>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 100; UNI 10411-1:2024, testo della norma fornito dal cliente, letto il 2026-10-06, p. 13</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 100; UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 13</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 100</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 100</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -2277,7 +2277,7 @@
       <c r="M32" s="11" t="n"/>
       <c r="N32" s="11" t="n"/>
     </row>
-    <row r="33" ht="82" customHeight="1">
+    <row r="33" ht="95" customHeight="1">
       <c r="A33" s="10" t="n">
         <v>31</v>
       </c>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Freno, un solo gruppo — La UNI 10411-1:2024 (11.1.4) e la UNI EN 81-1 chiedono a un solo gruppo di rallentare la cabina carica in discesa; il software applica la richiesta più completa della UNI EN 81-20.</t>
+          <t>Freno, un solo gruppo — La UNI 10411-1:2024 (11.1.4) e la UNI EN 81-1:2008 (12.4.2.1) chiedono a un solo gruppo di rallentare la cabina carica in discesa; il software applica la richiesta più completa della UNI EN 81-20.</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 100; UNI 10411-1:2024, testo della norma fornito dal cliente, letto il 2026-10-06, p. 13</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 100; UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 13</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.9.2.2.2.1 (non oltre il paracadute o l'urto sugli ammortizzatori); 1 gn in 5.6.2.1.3 e 5.8.2</t>
+          <t>UNI EN 81-20:2020, 5.9.2.2.2.1 (non oltre il paracadute o l'urto sugli ammortizzatori); 1 gn in 5.6.2.1.3 e 5.8.2; con il freno come organo d'arresto, 1 gn anche in 5.6.6.3 (ACOP) e 5.6.7.6 (UCM)</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 81, 98–100</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 81, 98–100</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
@@ -2645,7 +2645,7 @@
       <c r="M40" s="11" t="n"/>
       <c r="N40" s="11" t="n"/>
     </row>
-    <row r="41" ht="82" customHeight="1">
+    <row r="41" ht="147" customHeight="1">
       <c r="A41" s="10" t="n">
         <v>39</v>
       </c>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Tolleranza tra velocità reale e nominale — Con la UNI 10411-1:2024 (15.1) una velocità oltre il 5 % sopra quella originale è un aumento della velocità nominale (punti 15.2–15.15).</t>
+          <t>Tolleranza tra velocità reale e nominale — Con la UNI 10411-1:2024 (15.1) una velocità oltre il 5 % sopra la maggiore tra quella del libretto e quella dopo il passaggio a 50 Hz è un aumento della velocità nominale (punti 15.2–15.15). Con la UNI 10411-11:2024 (15) ogni cambio della velocità nominale, in più o in meno, porta ai punti 15 a)–k) e alla valutazione 4.3.</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 102; UNI 10411-1:2024, testo della norma fornito dal cliente, letto il 2026-10-06, p. 14</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 102; UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 14</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 101–102</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 101–102</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -2875,7 +2875,7 @@
       <c r="M45" s="11" t="n"/>
       <c r="N45" s="11" t="n"/>
     </row>
-    <row r="46" ht="212" customHeight="1">
+    <row r="46" ht="225" customHeight="1">
       <c r="A46" s="10" t="n">
         <v>44</v>
       </c>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, punto 14: macchina secondo la UNI EN 81-20 (5.9.1 e 5.9.2, freno in due gruppi) o la UNI EN 81-1:2010, con aderenza e coefficiente di sicurezza delle funi (14.1); D/d ≥ 40 (14.3); temporizzatore della UNI EN 81-20 (5.9.2.7), arresto prima che la cabina in salita tocchi la velocità di intervento del limitatore, ACOP e UCM esistenti che funzionano ancora, arresto vicino alla macchina, pulegge secondo la 5.5.7, interruzione se il freno non si apre (14.4 a)–g)). UNI 10411-11:2024, punto 14: macchina come l'originale, altrimenti UNI EN 81-20 5.9.1–5.9.2 con le verifiche della norma di origine o della UNI EN 81-20 e la valutazione 4.3 (14.1); UCM esistenti che funzionano ancora e interruzione se il freno non si apre (14.3)</t>
+          <t>UNI 10411-1:2024, punto 14: macchina secondo la UNI EN 81-20 (5.9.1 e 5.9.2, freno in due gruppi) o la UNI EN 81-1:2010, con aderenza e coefficiente di sicurezza delle funi (14.1); D/d ≥ 40 (14.3); temporizzatore della UNI EN 81-20 (5.9.2.7), arresto prima che la cabina in salita tocchi la velocità di intervento del limitatore, ACOP e UCM esistenti che funzionano ancora, arresto vicino alla macchina, pulegge secondo la 5.5.7, interruzione se il freno non si apre (14.4 a)–g)). UNI 10411-11:2024, punto 14: macchina come l'originale, altrimenti UNI EN 81-20 5.9.1–5.9.2 con le verifiche della norma di origine o della UNI EN 81-20 e la valutazione 4.3 (14.1); UCM esistenti che funzionano ancora e, senza UCM conforme alla 5.6.7 e con il rallentamento controllato, interruzione se il freno non si apre (14.3)</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 13–14; UNI 10411-11:2024, testo della norma fornito dal cliente, letto il 2026-10-06, p. 12</t>
+          <t>UNI 10411-1:2024, testo della norma, letto il 2026-10-06, pp. 13–14; UNI 10411-11:2024, testo della norma, letto il 2026-10-06, p. 12</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 27</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 27</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 43–44</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 43–44</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
@@ -3059,7 +3059,7 @@
       <c r="M49" s="11" t="n"/>
       <c r="N49" s="11" t="n"/>
     </row>
-    <row r="50" ht="30" customHeight="1">
+    <row r="50" ht="69" customHeight="1">
       <c r="A50" s="10" t="n">
         <v>48</v>
       </c>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Compensazione e cavo flessibile</t>
+          <t>Compensazione e cavo flessibile — Nella 5.11.3 la massa della compensazione e del cavo dipende dalla posizione della cabina; il software la tiene costante dentro P.</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 63–64</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 63–64</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 66</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 66</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -3243,7 +3243,7 @@
       <c r="M53" s="11" t="n"/>
       <c r="N53" s="11" t="n"/>
     </row>
-    <row r="54" ht="108" customHeight="1">
+    <row r="54" ht="186" customHeight="1">
       <c r="A54" s="10" t="n">
         <v>52</v>
       </c>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Parete del vano di fronte all'entrata della cabina — le deroghe della norma (fino a 0,20 m per un tratto alto non più di 0,50 m o con porte verticali di ascensori per merci; nessun limite con la porta di cabina bloccata meccanicamente) non sono usate: la verifica è più severa</t>
+          <t>Parete del vano di fronte all'entrata della cabina — le deroghe della norma (fino a 0,20 m per un tratto alto non più di 0,50 m o con porte verticali di ascensori per merci; nessun limite con la porta di cabina bloccata meccanicamente) non sono usate: la verifica è più severa. Il software misura fino alla soglia; la figura 3 della norma porta il limite anche al telaio e al bordo di chiusura delle ante di cabina: con la porta scelta lo verifica l'ingegnere sui dati del fornitore.</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 33</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 33</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -3289,7 +3289,7 @@
       <c r="M54" s="11" t="n"/>
       <c r="N54" s="11" t="n"/>
     </row>
-    <row r="55" ht="43" customHeight="1">
+    <row r="55" ht="95" customHeight="1">
       <c r="A55" s="10" t="n">
         <v>53</v>
       </c>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Gioco tra soglia di cabina e soglia di piano</t>
+          <t>Gioco tra soglia di cabina e soglia di piano — Non calcolato: tra il bordo d'attacco delle ante di cabina e le porte di piano al massimo 0,12 m (5.3.4.2; 11.2.3 nella UNI EN 81-1:2008), dato del fornitore delle porte.</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 50</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 50</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 35</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 35</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 49</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 49</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Imbotti della porta di piano (sostituzione con una luce più piccola)</t>
+          <t>Imbotti della porta di piano (sostituzione con una luce più piccola) — Montanti e pannelli accanto alla porta più larghi di 150 mm che chiudono l'apertura vanno con la prova del pendolo della porta (UNI EN 81-20:2020, 5.3.5.3.4): la copre il fornitore.</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 37–40</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 37–40</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 36</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 36</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 38</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 38</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 38</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 38</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 40–41, 69</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 40–41, 69</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 70–72</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 70–72</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
@@ -4531,7 +4531,7 @@
       <c r="M81" s="11" t="n"/>
       <c r="N81" s="11" t="n"/>
     </row>
-    <row r="82" ht="56" customHeight="1">
+    <row r="82" ht="121" customHeight="1">
       <c r="A82" s="10" t="n">
         <v>80</v>
       </c>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Superficie dove una persona può stare sul tetto di cabina</t>
+          <t>Superficie dove una persona può stare sul tetto di cabina — Nella 5.2.5.7.3 lo 0,12 m² è la soglia da cui un'area conta come posto in piedi, sopra la quale serve l'altezza del rifugio; che un'area simile debba esserci lo chiedeva la UNI EN 81-1:2008 (8.13.2). Il software verifica l'area disegnata.</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 39</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 39</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 49, 63; 2 m anche in DM 587/1987 (UNI EN 81-1), 7.3.1, 8.1.1 e 8.1.2</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 49, 63; 2 m anche in DM 587/1987 (UNI EN 81-1), 7.3.1, 8.1.1 e 8.1.2</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
@@ -4623,7 +4623,7 @@
       <c r="M83" s="11" t="n"/>
       <c r="N83" s="11" t="n"/>
     </row>
-    <row r="84" ht="108" customHeight="1">
+    <row r="84" ht="160" customHeight="1">
       <c r="A84" s="10" t="n">
         <v>82</v>
       </c>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Corsa guidata del contrappeso in testata</t>
+          <t>Corsa guidata in testata (contrappeso e cabina)</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>con la cabina sugli ammortizzatori completamente compressi le guide del contrappeso lo guidano ancora per almeno 0,1 + 0,035·v² m (v velocità nominale): dalla sommità del contrappeso, salito della corsa sotto la cabina (extracorsa e corsa degli ammortizzatori), alla sommità delle guide, che il software pone 50 mm sotto la soletta (voce foglio.stime)</t>
+          <t>con la cabina sugli ammortizzatori completamente compressi le guide del contrappeso lo guidano ancora per almeno 0,1 + 0,035·v² m (v velocità nominale): dalla sommità del contrappeso, salito della corsa sotto la cabina (extracorsa e corsa degli ammortizzatori), alla sommità delle guide, che il software pone 50 mm sotto la soletta (voce foglio.stime); la cabina nella sua posizione più alta (salto compreso) ha ancora almeno 0,1 m di guida sopra la sommità dell'arcata, dove il software mette i pattini superiori (avviso: l'altezza reale dei pattini è del fornitore)</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 36; UNI EN 81-1:2008, testo della norma fornito dal cliente, letto il 2026-10-06, p. 27</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 36; UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 27</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>corsa guidata del contrappeso in testata</t>
+          <t>corsa guidata del contrappeso in testata; corsa guidata della cabina in testata</t>
         </is>
       </c>
       <c r="I84" s="11" t="n"/>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 35</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 35</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 98, 131</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 98, 131</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
@@ -4761,7 +4761,7 @@
       <c r="M86" s="11" t="n"/>
       <c r="N86" s="11" t="n"/>
     </row>
-    <row r="87" ht="134" customHeight="1">
+    <row r="87" ht="121" customHeight="1">
       <c r="A87" s="10" t="n">
         <v>85</v>
       </c>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 98–99; UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 24; il tampone tipico dai cataloghi P+S Diepocell (wwlift.de) e ACLA AUTAN XL (acla.de), estratti di ricerca del 1° ottobre 2026</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 98–99; UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 24; il tampone tipico dai cataloghi P+S Diepocell (wwlift.de) e ACLA AUTAN XL (acla.de), estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 99; gli ammortizzatori tipici dal catalogo Oleo LSB e SEB (oleo.co.uk), estratti di ricerca del 1° ottobre 2026</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 99; gli ammortizzatori tipici dal catalogo Oleo LSB e SEB (oleo.co.uk), estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
@@ -4853,7 +4853,7 @@
       <c r="M88" s="11" t="n"/>
       <c r="N88" s="11" t="n"/>
     </row>
-    <row r="89" ht="121" customHeight="1">
+    <row r="89" ht="134" customHeight="1">
       <c r="A89" s="10" t="n">
         <v>87</v>
       </c>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario — non verificati: i percorsi larghi almeno 0,50 m e lo spazio di 0,30 m sopra le parti rotanti (5.2.6.3.2.2)</t>
+          <t>Locale del macchinario — davanti al quadro il software verifica la profondità libera e che la parete sia lunga almeno quanto il maggiore tra 500 mm e il quadro; non verificati: la macchina o altro dentro quella superficie, i percorsi larghi almeno 0,50 m (5.2.6.3.2.2) e lo spazio di 0,30 m sopra le parti rotanti (5.2.6.3.2.3)</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 29, 43; le superfici libere anche in UNI EN 81-1:1999, 6.3.2.1 (edizione 2008: 6.3.3.1)</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 29, 43; le superfici libere anche in UNI EN 81-1:1999, 6.3.2.1 (edizione 2008: 6.3.3.1)</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>vano: illuminazione fissa di almeno 50 lux a 1 m sopra il tetto della cabina e sopra il pavimento della fossa, 20 lux altrove; locale del macchinario: almeno 200 lux al pavimento nelle zone di lavoro</t>
+          <t>vano: luce fissa, almeno 50 lux a un metro dal tetto di cabina e dal fondo della fossa, 20 lux nel resto; locale del macchinario: almeno 200 lux al pavimento dove si lavora e 50 lux sui percorsi; 50 lux anche sull'accesso al macchinario</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.4.1 a)–c) e 5.2.1.4.2</t>
+          <t>UNI EN 81-20:2020, 5.2.1.4.1 a)–c), 5.2.1.4.2 e 5.2.2.2</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 25</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 25</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 14</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 14</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
@@ -5267,7 +5267,7 @@
       <c r="M97" s="11" t="n"/>
       <c r="N97" s="11" t="n"/>
     </row>
-    <row r="98" ht="108" customHeight="1">
+    <row r="98" ht="134" customHeight="1">
       <c r="A98" s="10" t="n">
         <v>96</v>
       </c>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Carichi sul pavimento della fossa — non calcolato: con spazi accessibili sotto il vano (5.2.5.4) il contrappeso ha il paracadute, sotto le sue guide va anche k1·g·M_cw/n e il fondo della fossa regge almeno 5000 N/m²</t>
+          <t>Carichi sul pavimento della fossa — non calcolato: con spazi accessibili sotto il vano (5.2.5.4) il contrappeso ha il paracadute, sotto le sue guide va anche k1·g·M_cw/n e il fondo della fossa regge almeno 5000 N/m². P è la cabina vuota: la quota del cavo flessibile e della compensazione, che la 5.2.1.8.5 conta in P, va aggiunta dall'ingegnere</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 27, 94–96</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 27, 94–96</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 77–79; UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 94–96</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 77–79; UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 94–96</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
@@ -5543,7 +5543,7 @@
       <c r="M103" s="11" t="n"/>
       <c r="N103" s="11" t="n"/>
     </row>
-    <row r="104" ht="290" customHeight="1">
+    <row r="104" ht="342" customHeight="1">
       <c r="A104" s="10" t="n">
         <v>102</v>
       </c>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Verifica delle guide di cabina — Confermati sul testo i coefficienti, le formule e i limiti. Da verificare il carico al piano: la UNI EN 81-20:2020 (5.7.2.3.6) lo lega al tipo di ascensore, 0,4·g·Q per persone, 0,6·g·Q per merci, 0,85·g·Q con dispositivi di movimentazione pesanti; il software usa la regola della UNI EN 81-1 (0,6·g·Q da 2500 kg, appendice G.2.5) perché il tipo di ascensore non è tra i dati. La formula di ω per Rm 370 è data da λ 20 a 250: sotto 20 il software usa la stessa formula. Non contate: la spinta di scorrimento delle staffe (assestamento dell'edificio), le apparecchiature appese alle guide, le frecce di staffe ed edificio (la norma vuole la somma entro il limite) e le guide del contrappeso</t>
+          <t>Verifica delle guide di cabina — Confermati sul testo i coefficienti, le formule e i limiti. Da verificare il carico al piano: la UNI EN 81-20:2020 (5.7.2.3.6) lo lega al tipo di ascensore, 0,4·g·Q per persone, 0,6·g·Q per merci, 0,85·g·Q con dispositivi di movimentazione pesanti; il software usa la regola della UNI EN 81-1:2008 (0,6·g·Q da 2500 kg, appendice G.2.5) perché il tipo di ascensore non è tra i dati. La formula di ω per Rm 370 è data da λ 20 a 250: sotto 20 il software usa ω di λ 20 (dal lato della sicurezza). Non contate: la spinta di scorrimento delle staffe (assestamento dell'edificio), le apparecchiature appese alle guide, le frecce di staffe ed edificio (la norma vuole la somma entro il limite) e le guide del contrappeso. La flessione della suola è quella dei pattini a rotelle (5.10.5 ha una formula a parte per quelli a scorrimento; il tipo di pattino non è un dato del software).</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 35–39; UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 94–97; Rm 370 è scelta del software (il valore più basso)</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 35–39; UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 94–97; Rm 370 è scelta del software (il valore più basso)</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
@@ -5635,7 +5635,7 @@
       <c r="M105" s="11" t="n"/>
       <c r="N105" s="11" t="n"/>
     </row>
-    <row r="106" ht="82" customHeight="1">
+    <row r="106" ht="69" customHeight="1">
       <c r="A106" s="10" t="n">
         <v>104</v>
       </c>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, p. 81; UNI EN 81-1:2008, testo della norma fornito dal cliente, letto il 2026-10-06, p. 58</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 81; UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 58</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
@@ -5819,7 +5819,7 @@
       <c r="M109" s="11" t="n"/>
       <c r="N109" s="11" t="n"/>
     </row>
-    <row r="110" ht="186" customHeight="1">
+    <row r="110" ht="238" customHeight="1">
       <c r="A110" s="10" t="n">
         <v>108</v>
       </c>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>da fare a parte, con i dati dei fornitori: sollecitazioni e frecce delle staffe e delle guide del contrappeso (UNI EN 81-50:2020, 5.10: il software verifica le guide di cabina, sul foglio 1 delle tavole); puleggia del contrappeso in taglia 2:1 sotto il soffitto; paracadute del contrappeso con spazi accessibili sotto il vano; distanza tra le parti fisse più alte della fossa e quelle più basse della cabina sugli ammortizzatori; sporgenze nel vano oltre 150 mm senza balaustra; locale della macchina in basso (dimensioni e spazi di manovra: il software non lo disegna); movimento incontrollato della cabina (UCM) e velocità eccessiva in salita con la nuova macchina</t>
+          <t>da fare a parte, con i dati dei fornitori: sollecitazioni e frecce delle staffe e delle guide del contrappeso (UNI EN 81-50:2020, 5.10: il software verifica le guide di cabina, sul foglio 1 delle tavole); puleggia del contrappeso in taglia 2:1 sotto il soffitto; paracadute del contrappeso con spazi accessibili sotto il vano; distanza tra le parti fisse più alte della fossa e quelle più basse della cabina sugli ammortizzatori; sporgenze nel vano oltre 150 mm senza balaustra; locale della macchina in basso (dimensioni e spazi di manovra: il software non lo disegna); movimento incontrollato della cabina (UCM) e velocità eccessiva in salita con la nuova macchina; muro sotto la soglia di piano (5.2.5.3.2 a)); le soluzioni della UNI EN 81-21:2022 per testata, fossa, locale e porte ridotti (le verifiche in sezione seguono solo la UNI EN 81-20:2020)</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 31–43, 89–97; analisi delle lacune del 2026-10-03</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 31–43, 89–97; analisi delle lacune del 2026-10-03</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
@@ -5911,7 +5911,7 @@
       <c r="M111" s="11" t="n"/>
       <c r="N111" s="11" t="n"/>
     </row>
-    <row r="112" ht="56" customHeight="1">
+    <row r="112" ht="121" customHeight="1">
       <c r="A112" s="10" t="n">
         <v>110</v>
       </c>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Portata e velocità</t>
+          <t>Portata e velocità — In una modifica la UNI 10411-1:2024 (6.1, prospetto 1) tratta come aumento della portata oltre il 10 % (Q fino a 500 kg) o il 5 % (oltre) e del carico totale oltre il 15 % o il 10 %; la UNI 10411-11:2024 (6.1) ogni aumento del carico totale: il confronto con la portata originale lo fa l'ingegnere.</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 5, 13–14; UNI 10411-11:2024, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 5, 12; schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); ricerca, capitoli 2.4 e 6.6</t>
+          <t>UNI 10411-1:2024, testo della norma, letto il 2026-10-06, pp. 5, 13–14; UNI 10411-11:2024, testo della norma, letto il 2026-10-06, pp. 5, 12; schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); ricerca, capitoli 2.4 e 6.6</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
@@ -6003,7 +6003,7 @@
       <c r="M113" s="11" t="n"/>
       <c r="N113" s="11" t="n"/>
     </row>
-    <row r="114" ht="160" customHeight="1">
+    <row r="114" ht="264" customHeight="1">
       <c r="A114" s="10" t="n">
         <v>112</v>
       </c>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Rifacimento con l'arcata esistente — il DPR 162/1999 elenca le modifiche costruttive ma non dice quando l'insieme diventa una sostituzione completa: la qualificazione dell'intervento la conferma il tecnico incaricato con il soggetto che esegue la verifica straordinaria</t>
+          <t>Rifacimento con l'arcata esistente — il DPR 162/1999 elenca le modifiche costruttive senza dire quando l'insieme diventa una sostituzione completa; la UNI 10411-1/-11:2024 (21.1) chiama modifica sostanziale il cambio insieme di quadro, macchina, almeno una porta di piano, cabina e arcata, con il risultato secondo la UNI EN 81-20:2020: tenendo l'arcata il 21.1 non si applica. Una cabina nuova nell'arcata esistente segue la UNI EN 81-20 5.4.1–5.4.10 (UNI 10411-1:2024, 22; con porte di cabina a battente fino a +0,10 m² di superficie senza cambiare la portata, 22 f)). La qualificazione dell'intervento la conferma il tecnico incaricato con il soggetto che esegue la verifica straordinaria</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso — la EN 81-20 non ammette più il pilastro pieno fino al terreno — (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori</t>
+          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso — la EN 81-20 non ammette più il pilastro pieno fino al terreno — (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori; in una modifica la UNI 10411-1:2024 (6.14) accetta al posto del paracadute un pilastro esistente fino al terreno, verificato per i nuovi carichi</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
@@ -6325,7 +6325,7 @@
       <c r="M120" s="11" t="n"/>
       <c r="N120" s="11" t="n"/>
     </row>
-    <row r="121" ht="238" customHeight="1">
+    <row r="121" ht="251" customHeight="1">
       <c r="A121" s="10" t="n">
         <v>119</v>
       </c>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta dal catalogo di un costruttore — la tolleranza sul rapporto è una scelta del software: la velocità reale con l'inverter deve restare entro il 5 % sopra la nominale (UNI EN 81-20:2020, 5.9.2.4); i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
+          <t>Macchina proposta dal catalogo di un costruttore — la tolleranza sul rapporto è una scelta del software: la velocità reale con l'inverter deve restare entro il 5 % sopra la nominale (UNI EN 81-20:2020, 5.9.2.4; buona pratica non oltre l'8 % sotto); i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.2</t>
+          <t>UNI EN 81-50:2020, 5.11.1 e 5.11.2.3.2 (μ della frenatura)</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
@@ -6555,7 +6555,7 @@
       <c r="M125" s="11" t="n"/>
       <c r="N125" s="11" t="n"/>
     </row>
-    <row r="126" ht="43" customHeight="1">
+    <row r="126" ht="108" customHeight="1">
       <c r="A126" s="10" t="n">
         <v>124</v>
       </c>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Tempi delle porte</t>
+          <t>Tempi delle porte — La norma non dà tempi: per le porte automatiche orizzontali dà l'energia cinetica (≤ 10 J, ≤ 4 J con il dispositivo di protezione escluso) e la forza contro la chiusura (≤ 150 N) (UNI EN 81-20:2020, 5.3.6.2.2.1), dati del fornitore delle porte.</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
@@ -6601,7 +6601,7 @@
       <c r="M126" s="11" t="n"/>
       <c r="N126" s="11" t="n"/>
     </row>
-    <row r="127" ht="108" customHeight="1">
+    <row r="127" ht="212" customHeight="1">
       <c r="A127" s="10" t="n">
         <v>125</v>
       </c>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione</t>
+          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione. Le decelerazioni mostrate non sono una verifica: per i tamponi non lineari la norma vuole media ≤ 1 gn, oltre 2,5 gn per non più di 0,04 s, picco ≤ 6 gn e rimbalzo ≤ 1 m/s (5.8.2.1.2.1), per gli idraulici media ≤ 1 gn e oltre 2,5 gn per non più di 0,04 s (5.8.2.2.3); si provano per tipo (certificato del fornitore)</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma fornito dal cliente, letto il 2026-10-06, pp. 98–99</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 98–99</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
@@ -6647,7 +6647,7 @@
       <c r="M127" s="11" t="n"/>
       <c r="N127" s="11" t="n"/>
     </row>
-    <row r="128" ht="56" customHeight="1">
+    <row r="128" ht="82" customHeight="1">
       <c r="A128" s="10" t="n">
         <v>126</v>
       </c>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Cabina bloccata: rotazione in salita</t>
+          <t>Cabina bloccata: rotazione in salita — La simulazione mostra il contrappeso sugli ammortizzatori con la cabina in alto; la norma chiede anche la cabina vuota in basso, che il calcolo verifica (tr_stall).</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2</t>
+          <t>UNI EN 81-50:2020, 5.11.2.2.3</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
@@ -6796,17 +6796,17 @@
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 6-bis e 7 c.3</t>
+          <t>DPR 162/1999 e s.m.i., artt. 6-bis e 7 c.3</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>procedura con un organismo notificato (All. V, VIII, X, XI o XII); marcatura CE in cabina con il numero dell'organismo</t>
+          <t>procedura con un organismo notificato (ascensore modello con esame UE del tipo, All. IV B, più All. V, X o XII; oppure All. VIII o XI); marcatura CE in cabina con il numero dell'organismo</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 6-bis e 7 c.3</t>
+          <t>DPR 162/1999 e s.m.i., artt. 6-bis e 7 c.3</t>
         </is>
       </c>
       <c r="F131" s="10" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.1–3</t>
+          <t>DPR 162/1999 e s.m.i., art. 12 c.1–3</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.1–3</t>
+          <t>DPR 162/1999 e s.m.i., art. 12 c.1–3</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
@@ -7061,7 +7061,7 @@
       <c r="M136" s="11" t="n"/>
       <c r="N136" s="11" t="n"/>
     </row>
-    <row r="137" ht="56" customHeight="1">
+    <row r="137" ht="69" customHeight="1">
       <c r="A137" s="10" t="n">
         <v>135</v>
       </c>
@@ -7072,17 +7072,17 @@
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 14 c.3</t>
+          <t>DPR 162/1999 e s.m.i., art. 14 c.3; schema ICIM SCI 162 rev. 02</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>verifica straordinaria da uno dei soggetti dell'art. 13 c.1, di norma limitata ai controlli sulle modifiche, con la documentazione delle modifiche e dei componenti sostituiti</t>
+          <t>verifica straordinaria da uno dei soggetti dell'art. 13 c.1 (la legge); secondo lo schema ICIM è di norma limitata ai controlli sulle modifiche, con la documentazione delle modifiche e dei componenti sostituiti</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 14 c.3</t>
+          <t>DPR 162/1999 e s.m.i., art. 14 c.3; schema ICIM SCI 162 rev. 02</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
@@ -7107,33 +7107,33 @@
       <c r="M137" s="11" t="n"/>
       <c r="N137" s="11" t="n"/>
     </row>
-    <row r="138" ht="56" customHeight="1">
+    <row r="138" ht="82" customHeight="1">
       <c r="A138" s="10" t="n">
         <v>136</v>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
+          <t>UNI 10411-1:2024 e UNI 10411-11:2024, 25</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>prove dell'organismo notificato: funzionamento a vuoto e a pieno carico, in mancanza di energia, prova statica a 1,25 volte la portata e controllo che non restino deformazioni</t>
+          <t>documentazione della modifica (App. C della -1, App. A della -11): il proprietario la tiene per chi esegue la verifica straordinaria e la allega alla dichiarazione di conformità (DM 37/2008); manuali della macchina, del quadro e dei nuovi componenti di sicurezza consegnati al proprietario</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
+          <t>UNI 10411-1:2024 e UNI 10411-11:2024, 25</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G138" s="10" t="inlineStr">
@@ -7164,17 +7164,17 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
+          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>documentazione tecnica con i risultati dei calcoli di progetto, le relazioni sulle prove e l'elenco delle norme armonizzate applicate, anche in parte</t>
+          <t>prove dell'organismo notificato: funzionamento a vuoto e a pieno carico, in mancanza di energia, prova statica a 1,25 volte la portata e controllo che non restino deformazioni</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
+          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
         </is>
       </c>
       <c r="F139" s="10" t="inlineStr">
@@ -7210,17 +7210,17 @@
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
+          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>per gli ascensori dichiarati conformi dal 20/01/2027: requisiti dell'All. III del Regolamento macchine (tra cui 1.1.9 e 1.2.1), con una valutazione aggiuntiva per i requisiti nuovi o cambiati</t>
+          <t>documentazione tecnica con i risultati dei calcoli di progetto, le relazioni sulle prove e l'elenco delle norme armonizzate applicate, anche in parte</t>
         </is>
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
+          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
         </is>
       </c>
       <c r="F140" s="10" t="inlineStr">
@@ -7245,7 +7245,7 @@
       <c r="M140" s="11" t="n"/>
       <c r="N140" s="11" t="n"/>
     </row>
-    <row r="141" ht="82" customHeight="1">
+    <row r="141" ht="56" customHeight="1">
       <c r="A141" s="10" t="n">
         <v>139</v>
       </c>
@@ -7256,17 +7256,17 @@
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12.1 e 5.12.2.1</t>
+          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>il metodo del coefficiente di sicurezza delle funi vale solo per pulegge di acciaio o ghisa e funi d'acciaio secondo EN 12385-5; la flessione è semplice se il raggio della gola non supera 0,53 volte il diametro della fune: rilevare il materiale della puleggia e il raggio delle gole</t>
+          <t>per gli ascensori dichiarati conformi dal 20/01/2027: requisiti dell'All. III del Regolamento macchine (tra cui 1.1.9 e 1.2.1), con una valutazione aggiuntiva per i requisiti nuovi o cambiati</t>
         </is>
       </c>
       <c r="E141" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12.1 e 5.12.2.1</t>
+          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
         </is>
       </c>
       <c r="F141" s="10" t="inlineStr">
@@ -7291,7 +7291,7 @@
       <c r="M141" s="11" t="n"/>
       <c r="N141" s="11" t="n"/>
     </row>
-    <row r="142" ht="43" customHeight="1">
+    <row r="142" ht="82" customHeight="1">
       <c r="A142" s="10" t="n">
         <v>140</v>
       </c>
@@ -7302,22 +7302,22 @@
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.6.2.2.1.2</t>
+          <t>UNI EN 81-50:2020, 5.12.1 e 5.12.2.1</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>tempo di risposta del limitatore di velocità: i suoi punti d'intervento distano al massimo 250 mm di corsa della fune del limitatore</t>
+          <t>il metodo del coefficiente di sicurezza delle funi vale solo per pulegge di acciaio o ghisa e funi d'acciaio secondo EN 12385-5; la flessione è semplice se il raggio della gola non supera 0,53 volte il diametro della fune: rilevare il materiale della puleggia e il raggio delle gole</t>
         </is>
       </c>
       <c r="E142" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.6.2.2.1.2</t>
+          <t>UNI EN 81-50:2020, 5.12.1 e 5.12.2.1</t>
         </is>
       </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G142" s="10" t="inlineStr">
@@ -7337,7 +7337,7 @@
       <c r="M142" s="11" t="n"/>
       <c r="N142" s="11" t="n"/>
     </row>
-    <row r="143" ht="56" customHeight="1">
+    <row r="143" ht="43" customHeight="1">
       <c r="A143" s="10" t="n">
         <v>141</v>
       </c>
@@ -7348,22 +7348,22 @@
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2.1.2.1 e 5.8.2.2.3</t>
+          <t>UNI EN 81-20:2020, 5.6.2.2.1.2</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>ammortizzatori (dato del fornitore): decelerazione non oltre 1 gn, sopra 2,5 gn al massimo per 0,04 s; per quelli ad accumulo non lineari anche picco non oltre 6 gn e rimbalzo non oltre 1 m/s</t>
+          <t>tempo di risposta del limitatore di velocità: i suoi punti d'intervento distano al massimo 250 mm di corsa della fune del limitatore</t>
         </is>
       </c>
       <c r="E143" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2.1.2.1 e 5.8.2.2.3</t>
+          <t>UNI EN 81-20:2020, 5.6.2.2.1.2</t>
         </is>
       </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G143" s="10" t="inlineStr">
@@ -7383,7 +7383,7 @@
       <c r="M143" s="11" t="n"/>
       <c r="N143" s="11" t="n"/>
     </row>
-    <row r="144" ht="69" customHeight="1">
+    <row r="144" ht="56" customHeight="1">
       <c r="A144" s="10" t="n">
         <v>142</v>
       </c>
@@ -7394,22 +7394,22 @@
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1</t>
+          <t>UNI EN 81-20:2020, 5.8.2.1.2.1 e 5.8.2.2.3</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>cartello sopra o accanto allo schermo del contrappeso (5.2.5.5.1) con il gioco massimo ammesso tra contrappeso e ammortizzatore con la cabina al piano più alto, per conservare gli spazi in testata</t>
+          <t>ammortizzatori (dato del fornitore): decelerazione non oltre 1 gn, sopra 2,5 gn al massimo per 0,04 s; per quelli ad accumulo non lineari anche picco non oltre 6 gn e rimbalzo non oltre 1 m/s</t>
         </is>
       </c>
       <c r="E144" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1</t>
+          <t>UNI EN 81-20:2020, 5.8.2.1.2.1 e 5.8.2.2.3</t>
         </is>
       </c>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G144" s="10" t="inlineStr">
@@ -7429,7 +7429,7 @@
       <c r="M144" s="11" t="n"/>
       <c r="N144" s="11" t="n"/>
     </row>
-    <row r="145" ht="43" customHeight="1">
+    <row r="145" ht="69" customHeight="1">
       <c r="A145" s="10" t="n">
         <v>143</v>
       </c>
@@ -7440,22 +7440,22 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.2.4</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>fossa più profonda di 2,50 m: porta di accesso; fino a 2,50 m porta di accesso oppure scala dentro il vano (appendice F)</t>
+          <t>cartello sopra o accanto allo schermo del contrappeso (5.2.5.5.1) con il gioco massimo ammesso tra contrappeso e ammortizzatore con la cabina al piano più alto, per conservare gli spazi in testata</t>
         </is>
       </c>
       <c r="E145" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.2.4</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1</t>
         </is>
       </c>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G145" s="10" t="inlineStr">
@@ -7486,22 +7486,22 @@
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.5.1 b)</t>
+          <t>UNI EN 81-20:2020, 5.2.2.4</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>in fossa un commutatore di ispezione fisso, manovrabile da non oltre 0,30 m da uno spazio di rifugio</t>
+          <t>fossa più profonda di 2,50 m: porta di accesso; fino a 2,50 m porta di accesso oppure scala dentro il vano (appendice F)</t>
         </is>
       </c>
       <c r="E146" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.5.1 b)</t>
+          <t>UNI EN 81-20:2020, 5.2.2.4</t>
         </is>
       </c>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G146" s="10" t="inlineStr">
@@ -7532,22 +7532,22 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1</t>
+          <t>UNI EN 81-20:2020, 5.2.1.5.1 b)</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>uno spazio di rifugio per ogni persona, tutti dello stesso tipo e senza sovrapposizioni; cartello con il numero di persone ammesse e la postura</t>
+          <t>in fossa un commutatore di ispezione fisso, manovrabile da non oltre 0,30 m da uno spazio di rifugio</t>
         </is>
       </c>
       <c r="E147" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1</t>
+          <t>UNI EN 81-20:2020, 5.2.1.5.1 b)</t>
         </is>
       </c>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G147" s="10" t="inlineStr">
@@ -7567,7 +7567,7 @@
       <c r="M147" s="11" t="n"/>
       <c r="N147" s="11" t="n"/>
     </row>
-    <row r="148" ht="69" customHeight="1">
+    <row r="148" ht="43" customHeight="1">
       <c r="A148" s="10" t="n">
         <v>146</v>
       </c>
@@ -7578,22 +7578,22 @@
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.4.1</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>illuminazione del vano: almeno 50 lux a 1 m sopra il tetto della cabina nella sua proiezione e a 1 m sopra il fondo della fossa dove si sta, si lavora o si passa tra le zone di lavoro; almeno 20 lux altrove</t>
+          <t>uno spazio di rifugio per ogni persona, tutti dello stesso tipo e senza sovrapposizioni; cartello con il numero di persone ammesse e la postura</t>
         </is>
       </c>
       <c r="E148" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.4.1</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1</t>
         </is>
       </c>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G148" s="10" t="inlineStr">
@@ -7613,7 +7613,7 @@
       <c r="M148" s="11" t="n"/>
       <c r="N148" s="11" t="n"/>
     </row>
-    <row r="149" ht="56" customHeight="1">
+    <row r="149" ht="69" customHeight="1">
       <c r="A149" s="10" t="n">
         <v>147</v>
       </c>
@@ -7624,22 +7624,22 @@
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.10.1 e 5.4.10.4</t>
+          <t>UNI EN 81-20:2020, 5.2.1.4.1</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>luce in cabina almeno 100 lux sui comandi e a 1 m dal pavimento; luce di emergenza di almeno 5 lux per un'ora presso gli allarmi in cabina e sul tetto e al centro di cabina e tetto, a 1 m</t>
+          <t>illuminazione del vano: almeno 50 lux a 1 m sopra il tetto della cabina nella sua proiezione e a 1 m sopra il fondo della fossa dove si sta, si lavora o si passa tra le zone di lavoro; almeno 20 lux altrove</t>
         </is>
       </c>
       <c r="E149" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.10.1 e 5.4.10.4</t>
+          <t>UNI EN 81-20:2020, 5.2.1.4.1</t>
         </is>
       </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G149" s="10" t="inlineStr">
@@ -7659,7 +7659,7 @@
       <c r="M149" s="11" t="n"/>
       <c r="N149" s="11" t="n"/>
     </row>
-    <row r="150" ht="43" customHeight="1">
+    <row r="150" ht="56" customHeight="1">
       <c r="A150" s="10" t="n">
         <v>148</v>
       </c>
@@ -7670,22 +7670,22 @@
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.4</t>
+          <t>UNI EN 81-20:2020, 5.4.10.1 e 5.4.10.4</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>materiali della cabina secondo EN 13501-1: pavimento Cfl-s2, pareti C-s2,d1, soffitto C-s2,d0</t>
+          <t>luce in cabina almeno 100 lux sui comandi e a 1 m dal pavimento; luce di emergenza di almeno 5 lux per un'ora presso gli allarmi in cabina e sul tetto e al centro di cabina e tetto, a 1 m</t>
         </is>
       </c>
       <c r="E150" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.4</t>
+          <t>UNI EN 81-20:2020, 5.4.10.1 e 5.4.10.4</t>
         </is>
       </c>
       <c r="F150" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G150" s="10" t="inlineStr">
@@ -7705,7 +7705,7 @@
       <c r="M150" s="11" t="n"/>
       <c r="N150" s="11" t="n"/>
     </row>
-    <row r="151" ht="108" customHeight="1">
+    <row r="151" ht="43" customHeight="1">
       <c r="A151" s="10" t="n">
         <v>149</v>
       </c>
@@ -7716,22 +7716,22 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.3.5.3.2, 5.3.5.3.4, 5.3.6.2.2.1 b) e 5.3.15.2 b)</t>
+          <t>UNI EN 81-20:2020, 5.4.4</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>pannelli delle porte con i dispositivi di ritenuta e le prove a pendolo (morbido da 800 mm; rigido da 500 mm sui pannelli in vetro); sulle porte automatiche un dispositivo di protezione che copre da 25 a 1600 mm sopra la soglia e rileva ostacoli di 50 mm; fuori dalla zona di sbloccaggio la porta di cabina, spinta con 1000 N, non si apre più di 50 mm</t>
+          <t>materiali della cabina secondo EN 13501-1: pavimento Cfl-s2, pareti C-s2,d1, soffitto C-s2,d0</t>
         </is>
       </c>
       <c r="E151" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.3.5.3.2, 5.3.5.3.4, 5.3.6.2.2.1 b) e 5.3.15.2 b)</t>
+          <t>UNI EN 81-20:2020, 5.4.4</t>
         </is>
       </c>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G151" s="10" t="inlineStr">
@@ -7751,33 +7751,33 @@
       <c r="M151" s="11" t="n"/>
       <c r="N151" s="11" t="n"/>
     </row>
-    <row r="152" ht="56" customHeight="1">
+    <row r="152" ht="95" customHeight="1">
       <c r="A152" s="10" t="n">
         <v>150</v>
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-1:2024</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, scopo</t>
+          <t>UNI EN 81-20:2020, 6.3.1</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>ascensori elettrici a frizione non conformi alla 95/16/CE né alla 2014/33/UE; esclude le modifiche che cambiano le misure antincendio (valgono il DM 15/09/2005 o il Codice V.3)</t>
+          <t>prova del freno: da solo ferma la cabina che scende a velocità nominale con il 125 % della portata; con un gruppo fuori servizio rallenta la cabina con la portata in discesa; con il carico tra (q − 0,1)·Q e (q + 0,1)·Q lo sblocco manuale fa partire la cabina da sola, altrimenti servono i mezzi della 5.9.2.2.2.9 b)</t>
         </is>
       </c>
       <c r="E152" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, scopo</t>
+          <t>UNI EN 81-20:2020, 6.3.1</t>
         </is>
       </c>
       <c r="F152" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G152" s="10" t="inlineStr">
@@ -7797,33 +7797,33 @@
       <c r="M152" s="11" t="n"/>
       <c r="N152" s="11" t="n"/>
     </row>
-    <row r="153" ht="56" customHeight="1">
+    <row r="153" ht="69" customHeight="1">
       <c r="A153" s="10" t="n">
         <v>151</v>
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-11:2024</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, scopo</t>
+          <t>UNI EN 81-20:2020, 6.3.2</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>ascensori elettrici a frizione conformi alla Direttiva Ascensori; esclude le modifiche che cambiano le misure antincendio (valgono il DM 15/09/2005 o il Codice V.3)</t>
+          <t>impianto elettrico: esame a vista, continuità dei conduttori di protezione, isolamento circuito per circuito con l'elettronica scollegata, efficacia dell'interruzione automatica in caso di guasto</t>
         </is>
       </c>
       <c r="E153" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, scopo</t>
+          <t>UNI EN 81-20:2020, 6.3.2</t>
         </is>
       </c>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G153" s="10" t="inlineStr">
@@ -7843,33 +7843,33 @@
       <c r="M153" s="11" t="n"/>
       <c r="N153" s="11" t="n"/>
     </row>
-    <row r="154" ht="108" customHeight="1">
+    <row r="154" ht="82" customHeight="1">
       <c r="A154" s="10" t="n">
         <v>152</v>
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-11:2024</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, 14.3 a) e App. A (14); UNI EN 81-20:2020, 5.6.6.2 e 5.6.7.3</t>
+          <t>UNI EN 81-20:2020, 6.3.3</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>cambiando la macchina con protezioni ACOP o UCM esistenti: la modifica ne deve garantire il funzionamento, con una relazione sulla compatibilità della nuova macchina, oppure nuovi dispositivi con certificato di esame di tipo e dichiarazione di conformità; il freno della macchina vale come organo d'arresto solo se ridondante e autocontrollato</t>
+          <t>aderenza: arresti con la frenatura più severa, in salita a cabina vuota nella parte alta e in discesa con il 125 % della portata verso il basso; con il contrappeso sugli ammortizzatori e la macchina in moto le funi slittano oppure la cabina non sale; bilanciamento come dichiarato</t>
         </is>
       </c>
       <c r="E154" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, 14.3 a) e App. A (14); UNI EN 81-20:2020, 5.6.6.2 e 5.6.7.3</t>
+          <t>UNI EN 81-20:2020, 6.3.3</t>
         </is>
       </c>
       <c r="F154" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G154" s="10" t="inlineStr">
@@ -7889,33 +7889,33 @@
       <c r="M154" s="11" t="n"/>
       <c r="N154" s="11" t="n"/>
     </row>
-    <row r="155" ht="69" customHeight="1">
+    <row r="155" ht="121" customHeight="1">
       <c r="A155" s="10" t="n">
         <v>153</v>
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-21:2022, 1</t>
+          <t>UNI EN 81-20:2020, 6.3.4, 6.3.5 e 6.3.7</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>ascensori installati in un edificio esistente quando vincoli dell'edificio impediscono di soddisfare alcuni requisiti della UNI EN 81-20:2020; non si applica agli ascensori installati prima della sua pubblicazione</t>
+          <t>paracadute di cabina in discesa (istantaneo con la portata a velocità nominale; progressivo, negli impianti a frizione, con il 125 % della portata a velocità nominale o inferiore), del contrappeso a cabina vuota; ammortizzatori ad accumulo compressi dalla cabina con la portata, a dissipazione provati alla velocità nominale (o a quella usata per la corsa ridotta); dopo, nessun danno all'esame a vista</t>
         </is>
       </c>
       <c r="E155" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-21:2022, 1</t>
+          <t>UNI EN 81-20:2020, 6.3.4, 6.3.5 e 6.3.7</t>
         </is>
       </c>
       <c r="F155" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G155" s="10" t="inlineStr">
@@ -7935,33 +7935,33 @@
       <c r="M155" s="11" t="n"/>
       <c r="N155" s="11" t="n"/>
     </row>
-    <row r="156" ht="82" customHeight="1">
+    <row r="156" ht="108" customHeight="1">
       <c r="A156" s="10" t="n">
         <v>154</v>
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
+          <t>UNI EN 81-20:2020, 6.3.11, 6.3.12 e 6.3.13</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>spazi di rifugio ridotti solo con l'accordo preventivo: in edificio esistente PEC al Ministero con la certificazione dell'organismo prima dell'installazione (Procedura 2: dichiarazione dei punti della EN 81-21 applicati); la EN 81-21 da sola non giustifica la deroga</t>
+          <t>ACOP: cabina vuota in salita a velocità non inferiore alla nominale, frenata solo dal dispositivo; livellamento verificato a ogni fermata e, al piano più sfavorevole, durante carico e scarico; UCM: cabina vuota verso l'alto e piena verso il basso a una velocità prestabilita, con il movimento entro il limite della 5.6.7.5 e l'autosorveglianza dove richiesta</t>
         </is>
       </c>
       <c r="E156" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
+          <t>UNI EN 81-20:2020, 6.3.11, 6.3.12 e 6.3.13</t>
         </is>
       </c>
       <c r="F156" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G156" s="10" t="inlineStr">
@@ -7981,38 +7981,38 @@
       <c r="M156" s="11" t="n"/>
       <c r="N156" s="11" t="n"/>
     </row>
-    <row r="157" ht="69" customHeight="1">
+    <row r="157" ht="43" customHeight="1">
       <c r="A157" s="10" t="n">
         <v>155</v>
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-28:2022</t>
+          <t>UNI EN 81-20:2020, 6.3.14</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>teleallarme verso un servizio di soccorso: requisiti da verificare sul testo della norma (la UNI EN 81-28:2004 letta si applica agli impianti montati dopo la sua pubblicazione e vale da riferimento per gli esistenti, punto 1)</t>
+          <t>cabina fuori dalla zona di sbloccaggio e porta di piano tenuta aperta di 100 mm: lasciata, la porta si richiude e si blocca</t>
         </is>
       </c>
       <c r="E157" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-28:2022</t>
+          <t>UNI EN 81-20:2020, 6.3.14</t>
         </is>
       </c>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G157" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H157" s="10" t="inlineStr">
@@ -8027,33 +8027,33 @@
       <c r="M157" s="11" t="n"/>
       <c r="N157" s="11" t="n"/>
     </row>
-    <row r="158" ht="69" customHeight="1">
+    <row r="158" ht="43" customHeight="1">
       <c r="A158" s="10" t="n">
         <v>156</v>
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-58:2022 (resistenza al fuoco delle porte di piano)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
+          <t>UNI EN 81-20:2020, C.2 e 7.3.2</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>porte di piano resistenti al fuoco (classi E, EI, EW) provate secondo la norma, quando fanno parte della compartimentazione del vano; sostituirle con modelli diversi è una modifica sostanziale ai fini antincendio</t>
+          <t>la sostituzione della macchina o della puleggia di trazione è una trasformazione importante: si annota nel registro dell'impianto, da aggiornare</t>
         </is>
       </c>
       <c r="E158" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
+          <t>UNI EN 81-20:2020, C.2 e 7.3.2</t>
         </is>
       </c>
       <c r="F158" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G158" s="10" t="inlineStr">
@@ -8073,38 +8073,38 @@
       <c r="M158" s="11" t="n"/>
       <c r="N158" s="11" t="n"/>
     </row>
-    <row r="159" ht="95" customHeight="1">
+    <row r="159" ht="108" customHeight="1">
       <c r="A159" s="10" t="n">
         <v>157</v>
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.1</t>
+          <t>UNI EN 81-20:2020, 5.3.5.3.2, 5.3.5.3.4, 5.3.6.2.2.1 b) e 5.3.15.2 b)</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>tipi di cabina (larghezza × profondità, luce della porta): 1) 1000 × 1300, 800; 2) 1100 × 1400, 900; 3) 1100 × 2100, 900; 4) 1600 × 1400 o 1400 × 1600, 900; 5) 2000 × 1400 o 1400 × 2000, 1100 mm (la UNI EN 81-70:2005 letta, Prospetto 1, ha tre tipi: 1000 × 1250, 1100 × 1400 e 2000 × 1400 mm)</t>
+          <t>pannelli delle porte con i dispositivi di ritenuta e le prove a pendolo (morbido da 800 mm; rigido da 500 mm sui pannelli in vetro); sulle porte automatiche un dispositivo di protezione che copre da 25 a 1600 mm sopra la soglia e rileva ostacoli di 50 mm; fuori dalla zona di sbloccaggio la porta di cabina, spinta con 1000 N, non si apre più di 50 mm</t>
         </is>
       </c>
       <c r="E159" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.1</t>
+          <t>UNI EN 81-20:2020, 5.3.5.3.2, 5.3.5.3.4, 5.3.6.2.2.1 b) e 5.3.15.2 b)</t>
         </is>
       </c>
       <c r="F159" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G159" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H159" s="10" t="inlineStr">
@@ -8119,38 +8119,38 @@
       <c r="M159" s="11" t="n"/>
       <c r="N159" s="11" t="n"/>
     </row>
-    <row r="160" ht="95" customHeight="1">
+    <row r="160" ht="56" customHeight="1">
       <c r="A160" s="10" t="n">
         <v>158</v>
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+          <t>Collaudo: UNI 10411-1:2024</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
+          <t>UNI 10411-1:2024, scopo</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>specchio nei tipi 1–3; finiture che riducono le misure nominali al massimo di 15 mm per parete; segnale acustico regolabile 35–65 dB(A), fino a 80 in ambienti rumorosi; contrasto di Michelson con la A1:2022 (nella UNI EN 81-70:2005 letta: specchio nei tipi 1 e 2, 15 mm, 35–65 dB(A); non ci sono gli 80 dB(A) né il contrasto di Michelson)</t>
+          <t>impianti elettrici a frizione fuori dalla 95/16/CE e dalla 2014/33/UE; esclude le modifiche che cambiano le misure antincendio (per queste, a nostro giudizio, il DM 15/09/2005 o il Codice V.3)</t>
         </is>
       </c>
       <c r="E160" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
+          <t>UNI 10411-1:2024, scopo</t>
         </is>
       </c>
       <c r="F160" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G160" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H160" s="10" t="inlineStr">
@@ -8165,33 +8165,33 @@
       <c r="M160" s="11" t="n"/>
       <c r="N160" s="11" t="n"/>
     </row>
-    <row r="161" ht="43" customHeight="1">
+    <row r="161" ht="121" customHeight="1">
       <c r="A161" s="10" t="n">
         <v>159</v>
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+          <t>Collaudo: UNI 10411-1:2024</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, scopo</t>
+          <t>UNI 10411-1:2024, 14.4 a)–g)</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>si usa con la UNI EN 81-20:2020; per gli impianti esistenti vale la UNI EN 81-82</t>
+          <t>con la macchina nuova: temporizzatore del motore (EN 81-20 5.9.2.7); arresto in salita prima della velocità d'intervento del limitatore; protezioni ACOP e UCM esistenti che continuano a funzionare; dispositivo d'arresto presso la macchina (5.12.1.11.1 e)); pulegge nel locale secondo la 5.5.7; senza UCM e con la regolazione di velocità, macchinario senza alimentazione se il freno non si apre, con ripristino solo manuale</t>
         </is>
       </c>
       <c r="E161" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, scopo</t>
+          <t>UNI 10411-1:2024, 14.4 a)–g)</t>
         </is>
       </c>
       <c r="F161" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G161" s="10" t="inlineStr">
@@ -8211,33 +8211,33 @@
       <c r="M161" s="11" t="n"/>
       <c r="N161" s="11" t="n"/>
     </row>
-    <row r="162" ht="43" customHeight="1">
+    <row r="162" ht="56" customHeight="1">
       <c r="A162" s="10" t="n">
         <v>160</v>
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-71 (ascensori antivandalo)</t>
+          <t>Collaudo: UNI 10411-11:2024</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-71</t>
+          <t>UNI 10411-11:2024, scopo</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>categoria antivandalo da concordare con il committente; per la presunzione di conformità vale l'edizione 2005+A1:2006</t>
+          <t>impianti elettrici a frizione marcati CE secondo la Direttiva; esclude le modifiche che cambiano le misure antincendio (per queste, a nostro giudizio, il DM 15/09/2005 o il Codice V.3)</t>
         </is>
       </c>
       <c r="E162" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-71</t>
+          <t>UNI 10411-11:2024, scopo</t>
         </is>
       </c>
       <c r="F162" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G162" s="10" t="inlineStr">
@@ -8263,27 +8263,27 @@
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+          <t>Collaudo: UNI 10411-11:2024</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 7; Codice V.3.3.4</t>
+          <t>UNI 10411-11:2024, 14.3 a) e App. A (14); UNI EN 81-20:2020, 5.6.6.2 e 5.6.7.3</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>ascensore antincendio: tutti i piani serviti; vano e porte di piano almeno REI 60; cabina interna almeno 1,10 × 2,10 m con accesso sul lato corto; botola sul tetto almeno 0,50 × 0,70 m; area dedicata almeno 5 m² a ogni piano; luce d'emergenza almeno 5 lux con 1 h di autonomia; IPX3 dove arriva l'acqua; linea dedicata con alimentazione di sicurezza</t>
+          <t>cambiando la macchina: le protezioni UCM esistenti devono continuare a funzionare (14.3 a)); per l'ACOP esistente l'App. A (14) chiede una relazione sulla compatibilità della nuova macchina, oppure nuovi dispositivi con certificato di esame di tipo e dichiarazione di conformità; il freno della macchina vale come organo d'arresto solo se ridondante e autocontrollato</t>
         </is>
       </c>
       <c r="E163" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 7; Codice V.3.3.4</t>
+          <t>UNI 10411-11:2024, 14.3 a) e App. A (14); UNI EN 81-20:2020, 5.6.6.2 e 5.6.7.3</t>
         </is>
       </c>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G163" s="10" t="inlineStr">
@@ -8309,27 +8309,27 @@
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+          <t>Collaudo: UNI 10411-11:2024</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>Codice S.10, Tab. S.10-2</t>
+          <t>UNI 10411-11:2024, 14.3 b)</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>alimentazione di sicurezza dell'ascensore antincendio: interruzione al massimo 15 s, autonomia oltre 30 min</t>
+          <t>senza UCM conforme alla 5.6.7 e con il rallentamento controllato: macchinario senza alimentazione se il freno non si apre, al più tardi all'arrivo al piano, con ripristino solo manuale</t>
         </is>
       </c>
       <c r="E164" s="10" t="inlineStr">
         <is>
-          <t>Codice S.10, Tab. S.10-2</t>
+          <t>UNI 10411-11:2024, 14.3 b)</t>
         </is>
       </c>
       <c r="F164" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G164" s="10" t="inlineStr">
@@ -8355,32 +8355,32 @@
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-72:2020</t>
+          <t>UNI EN 81-21:2022, 1</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>requisiti propri della norma (cabina, tempi, protezione dall'acqua) da verificare sul testo</t>
+          <t>ascensori nuovi in un edificio esistente, dove l'edificio non permette di rispettare tutta la UNI EN 81-20:2020; esclusi gli impianti montati prima della sua pubblicazione</t>
         </is>
       </c>
       <c r="E165" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-72:2020</t>
+          <t>UNI EN 81-21:2022, 1</t>
         </is>
       </c>
       <c r="F165" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G165" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H165" s="10" t="inlineStr">
@@ -8395,33 +8395,33 @@
       <c r="M165" s="11" t="n"/>
       <c r="N165" s="11" t="n"/>
     </row>
-    <row r="166" ht="56" customHeight="1">
+    <row r="166" ht="95" customHeight="1">
       <c r="A166" s="10" t="n">
         <v>164</v>
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
+          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
+          <t>UNI EN 81-21:2022, 6.2 e 7.1</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>su comando della rivelazione incendio la cabina va al piano prestabilito e lascia uscire i passeggeri; con il Codice l'ascensore «dovrebbe» essere conforme alla UNI EN 81-73</t>
+          <t>oltre alle prove della EN 81-20 6.3: arresti mobili e sistema di arresto preattivato provati in moto a velocità nominale (in testata a cabina vuota, in fossa con il carico nominale), corsa dei loro ammortizzatori e distanza di frenatura; nelle istruzioni: quanto frena il sistema, col valore nominale e i due limiti</t>
         </is>
       </c>
       <c r="E166" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
+          <t>UNI EN 81-21:2022, 6.2 e 7.1</t>
         </is>
       </c>
       <c r="F166" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G166" s="10" t="inlineStr">
@@ -8441,28 +8441,28 @@
       <c r="M166" s="11" t="n"/>
       <c r="N166" s="11" t="n"/>
     </row>
-    <row r="167" ht="56" customHeight="1">
+    <row r="167" ht="82" customHeight="1">
       <c r="A167" s="10" t="n">
         <v>165</v>
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
+          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-73:2020</t>
+          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>segnali e comportamento della manovra da verificare sul testo; la norma serve anche da base per migliorare gli esistenti (così la UNI EN 81-73:2005 letta, punto 1)</t>
+          <t>spazi di rifugio ridotti solo con l'accordo preventivo: in edificio esistente PEC al Ministero con la certificazione dell'organismo prima dell'installazione (Procedura 2: dichiarazione dei punti della EN 81-21 applicati); la EN 81-21 da sola non giustifica la deroga</t>
         </is>
       </c>
       <c r="E167" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-73:2020</t>
+          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
         </is>
       </c>
       <c r="F167" s="10" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="G167" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H167" s="10" t="inlineStr">
@@ -8487,38 +8487,38 @@
       <c r="M167" s="11" t="n"/>
       <c r="N167" s="11" t="n"/>
     </row>
-    <row r="168" ht="69" customHeight="1">
+    <row r="168" ht="82" customHeight="1">
       <c r="A168" s="10" t="n">
         <v>166</v>
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-76:2025 (evacuazione delle persone con disabilità)</t>
+          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-76:2025</t>
+          <t>UNI EN 81-20:2020, 5.12.3.1; UNI EN 81-28:2004, 4.1.3, 4.2.1 e 7</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>evacuazione delle persone con disabilità con l'ascensore: requisiti aggiuntivi alla EN 81-20 (manovra, alimentazione) da verificare sul testo</t>
+          <t>la EN 81-20 richiama con data la EN 81-28:2003 (UNI EN 81-28:2004): prova automatica del collegamento almeno ogni 3 giorni; con alimentazione a batteria, avviso al servizio di soccorso quando l'autonomia residua scende sotto 1 h; pulsante d'allarme giallo con il simbolo della campana</t>
         </is>
       </c>
       <c r="E168" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-76:2025</t>
+          <t>UNI EN 81-20:2020, 5.12.3.1; UNI EN 81-28:2004, 4.1.3, 4.2.1 e 7</t>
         </is>
       </c>
       <c r="F168" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G168" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H168" s="10" t="inlineStr">
@@ -8539,22 +8539,22 @@
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 1</t>
+          <t>UNI EN 81-28:2022</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>con accelerazione di progetto a_d fino a 1 m/s² nessuna prescrizione specifica; a_d e la posizione dei rilevatori si concordano con il progettista dell'edificio</t>
+          <t>requisiti dell'edizione citata in GUUE da verificare sul testo; nelle modifiche la UNI 10411-1/-11:2024 (punto 23) ammette l'allarme nuovo secondo la EN 81-20 5.12.3.1 o la UNI EN 81-28:2022</t>
         </is>
       </c>
       <c r="E169" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 1</t>
+          <t>UNI EN 81-28:2022</t>
         </is>
       </c>
       <c r="F169" s="10" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="G169" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H169" s="10" t="inlineStr">
@@ -8585,22 +8585,22 @@
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-58:2022 (resistenza al fuoco delle porte di piano)</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
+          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>oltre 1 m/s²: massa della cabina nei calcoli (5.4.1), ritegni della cabina (5.4.2) e del contrappeso (5.5), protezione delle pulegge (5.6.1), tensioni e frecce delle guide (5.8.2, All. D), rilevazione e modo sismico (5.10.3, 5.10.4); soglie delle categorie dell'All. A da verificare sul testo</t>
+          <t>porte di piano resistenti al fuoco (classi E, EI, EW) provate secondo la norma, quando fanno parte della compartimentazione del vano; sostituirle con modelli diversi è una modifica sostanziale ai fini antincendio (la UNI EN 81-20:2020, 5.3.5.2, richiama con data la EN 81-58:2003: quale certificato accettare lo decide l'organismo)</t>
         </is>
       </c>
       <c r="E170" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
+          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
         </is>
       </c>
       <c r="F170" s="10" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="G170" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H170" s="10" t="inlineStr">
@@ -8625,28 +8625,28 @@
       <c r="M170" s="11" t="n"/>
       <c r="N170" s="11" t="n"/>
     </row>
-    <row r="171" ht="43" customHeight="1">
+    <row r="171" ht="95" customHeight="1">
       <c r="A171" s="10" t="n">
         <v>169</v>
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 0.3</t>
+          <t>UNI EN 81-70:2022, 5.3.1</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>non si applica agli impianti installati prima della sua pubblicazione</t>
+          <t>tipi di cabina (larghezza × profondità, luce della porta): 1) 1000 × 1300, 800; 2) 1100 × 1400, 900; 3) 1100 × 2100, 900; 4) 1600 × 1400 o 1400 × 1600, 900; 5) 2000 × 1400 o 1400 × 2000, 1100 mm (la UNI EN 81-70:2005 letta, Prospetto 1, ha tre tipi: 1000 × 1250, 1100 × 1400 e 2000 × 1400 mm)</t>
         </is>
       </c>
       <c r="E171" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 0.3</t>
+          <t>UNI EN 81-70:2022, 5.3.1</t>
         </is>
       </c>
       <c r="F171" s="10" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="G171" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H171" s="10" t="inlineStr">
@@ -8671,28 +8671,28 @@
       <c r="M171" s="11" t="n"/>
       <c r="N171" s="11" t="n"/>
     </row>
-    <row r="172" ht="69" customHeight="1">
+    <row r="172" ht="95" customHeight="1">
       <c r="A172" s="10" t="n">
         <v>170</v>
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-80:2019</t>
+          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>analisi dei rischi dell'impianto esistente e piano di miglioramento per priorità, scelta volontaria del proprietario (così le UNI EN 81-80:2004 e 2009 lette, punto 1 e appendice A)</t>
+          <t>specchio nei tipi 1–3; finiture che riducono le misure nominali al massimo di 15 mm per parete; segnale acustico regolabile 35–65 dB(A), fino a 80 in ambienti rumorosi; contrasto di Michelson con la A1:2022 (nella UNI EN 81-70:2005 letta: specchio nei tipi 1 e 2, 15 mm, 35–65 dB(A); non ci sono gli 80 dB(A) né il contrasto di Michelson)</t>
         </is>
       </c>
       <c r="E172" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-80:2019</t>
+          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
         </is>
       </c>
       <c r="F172" s="10" t="inlineStr">
@@ -8717,28 +8717,28 @@
       <c r="M172" s="11" t="n"/>
       <c r="N172" s="11" t="n"/>
     </row>
-    <row r="173" ht="56" customHeight="1">
+    <row r="173" ht="43" customHeight="1">
       <c r="A173" s="10" t="n">
         <v>171</v>
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-82:2026 (accessibilità degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
         </is>
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-82:2026</t>
+          <t>UNI EN 81-70:2022, scopo</t>
         </is>
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>miglioramento dell'accessibilità di un impianto esistente secondo i requisiti della EN 81-70</t>
+          <t>si usa con la UNI EN 81-20:2020; per gli impianti esistenti vale la UNI EN 81-82</t>
         </is>
       </c>
       <c r="E173" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-82:2026</t>
+          <t>UNI EN 81-70:2022, scopo</t>
         </is>
       </c>
       <c r="F173" s="10" t="inlineStr">
@@ -8763,28 +8763,28 @@
       <c r="M173" s="11" t="n"/>
       <c r="N173" s="11" t="n"/>
     </row>
-    <row r="174" ht="56" customHeight="1">
+    <row r="174" ht="43" customHeight="1">
       <c r="A174" s="10" t="n">
         <v>172</v>
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-83:2026 (antivandalo degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-71 (ascensori antivandalo)</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-83:2026</t>
+          <t>UNI EN 81-71</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>miglioramento della resistenza agli atti vandalici di un impianto esistente secondo la EN 81-71:2022 (voce 1.2 della Tab. A.1 della EN 81-80)</t>
+          <t>categoria antivandalo da concordare con il committente; per la presunzione di conformità vale l'edizione 2005+A1:2006</t>
         </is>
       </c>
       <c r="E174" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-83:2026</t>
+          <t>UNI EN 81-71</t>
         </is>
       </c>
       <c r="F174" s="10" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="G174" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H174" s="10" t="inlineStr">
@@ -8809,28 +8809,28 @@
       <c r="M174" s="11" t="n"/>
       <c r="N174" s="11" t="n"/>
     </row>
-    <row r="175" ht="56" customHeight="1">
+    <row r="175" ht="108" customHeight="1">
       <c r="A175" s="10" t="n">
         <v>173</v>
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>DM 15/09/2005, punto 7 (valori); Codice V.3.3.4</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>piattaforma di distribuzione davanti alla porta di cabina: 1,50 × 1,50 m negli edifici nuovi, 1,40 × 1,40 m nell'adeguamento (fuori dal vano: in sito)</t>
+          <t>ascensore antincendio: tutti i piani serviti; vano e porte di piano almeno REI 60; cabina interna almeno 1,10 × 2,10 m con accesso sul lato corto; botola sul tetto almeno 0,50 × 0,70 m; area dedicata almeno 5 m² a ogni piano; luce d'emergenza almeno 5 lux con 1 h di autonomia; IPX3 dove arriva l'acqua; linea dedicata con alimentazione di sicurezza</t>
         </is>
       </c>
       <c r="E175" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>DM 15/09/2005, punto 7 (valori); Codice V.3.3.4</t>
         </is>
       </c>
       <c r="F175" s="10" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H175" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I175" s="11" t="n"/>
@@ -8861,22 +8861,22 @@
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>Codice S.10, Tab. S.10-2</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>porte di cabina e di piano a scorrimento automatico (nell'adeguamento la porta di piano può essere a battente se ad apertura automatica); porte aperte almeno 8 s, chiusura in almeno 4 s</t>
+          <t>alimentazione di sicurezza dell'ascensore antincendio: interruzione al massimo 15 s, autonomia oltre 30 min</t>
         </is>
       </c>
       <c r="E176" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>Codice S.10, Tab. S.10-2</t>
         </is>
       </c>
       <c r="F176" s="10" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="H176" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I176" s="11" t="n"/>
@@ -8901,28 +8901,28 @@
       <c r="M176" s="11" t="n"/>
       <c r="N176" s="11" t="n"/>
     </row>
-    <row r="177" ht="43" customHeight="1">
+    <row r="177" ht="56" customHeight="1">
       <c r="A177" s="10" t="n">
         <v>175</v>
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-72:2020</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>arresto ai piani con autolivellamento entro ± 2 cm; sosta ai piani con le porte chiuse</t>
+          <t>requisiti propri della norma (cabina, tempi, protezione dall'acqua) da verificare sul testo</t>
         </is>
       </c>
       <c r="E177" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-72:2020</t>
         </is>
       </c>
       <c r="F177" s="10" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="G177" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H177" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I177" s="11" t="n"/>
@@ -8947,28 +8947,28 @@
       <c r="M177" s="11" t="n"/>
       <c r="N177" s="11" t="n"/>
     </row>
-    <row r="178" ht="56" customHeight="1">
+    <row r="178" ht="69" customHeight="1">
       <c r="A178" s="10" t="n">
         <v>176</v>
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>pulsanti di cabina e di piano: il più alto tra 1,10 e 1,40 m, misurato all'asse del comando; bottoniera di cabina su una parete laterale ad almeno 0,35 m dalla porta</t>
+          <t>quando la compartimentazione lo richiede, su comando della rivelazione incendio la cabina va al piano prestabilito e lascia uscire i passeggeri; con il Codice l'ascensore «dovrebbe» essere conforme alla UNI EN 81-73</t>
         </is>
       </c>
       <c r="E178" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
         </is>
       </c>
       <c r="F178" s="10" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="H178" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I178" s="11" t="n"/>
@@ -8993,28 +8993,28 @@
       <c r="M178" s="11" t="n"/>
       <c r="N178" s="11" t="n"/>
     </row>
-    <row r="179" ht="95" customHeight="1">
+    <row r="179" ht="56" customHeight="1">
       <c r="A179" s="10" t="n">
         <v>177</v>
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
+          <t>UNI EN 81-73:2020</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>citofono in cabina tra 1,10 e 1,30 m; luce d'emergenza con almeno 3 h di autonomia; campanello d'allarme e segnale luminoso di allarme ricevuto; arresto e inversione della chiusura; segnale acustico d'arrivo; numeri in rilievo e Braille, targa Braille di piano; sedile ribaltabile dove possibile</t>
+          <t>segnali e comportamento della manovra da verificare sul testo; la norma serve anche da base per migliorare gli esistenti (così la UNI EN 81-73:2005 letta, punto 1)</t>
         </is>
       </c>
       <c r="E179" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
+          <t>UNI EN 81-73:2020</t>
         </is>
       </c>
       <c r="F179" s="10" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="G179" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H179" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I179" s="11" t="n"/>
@@ -9039,28 +9039,28 @@
       <c r="M179" s="11" t="n"/>
       <c r="N179" s="11" t="n"/>
     </row>
-    <row r="180" ht="56" customHeight="1">
+    <row r="180" ht="69" customHeight="1">
       <c r="A180" s="10" t="n">
         <v>178</v>
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-76:2025 (evacuazione delle persone con disabilità)</t>
         </is>
       </c>
       <c r="C180" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
+          <t>UNI EN 81-76:2025</t>
         </is>
       </c>
       <c r="D180" s="10" t="inlineStr">
         <is>
-          <t>ascensore obbligatorio oltre il terzo livello (contati interrati e porticati); negli immobili con più di tre livelli fuori terra un ascensore per ogni scala principale</t>
+          <t>evacuazione delle persone con disabilità con l'ascensore: requisiti aggiuntivi alla EN 81-20 (manovra, alimentazione) da verificare sul testo</t>
         </is>
       </c>
       <c r="E180" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
+          <t>UNI EN 81-76:2025</t>
         </is>
       </c>
       <c r="F180" s="10" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="G180" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H180" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I180" s="11" t="n"/>
@@ -9091,22 +9091,22 @@
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+          <t>UNI EN 81-77:2022, 1</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>nelle ristrutturazioni deroghe per impossibilità tecnica strutturale o impiantistica (privati: concesse dal Sindaco); edifici vincolati: deroga se le opere pregiudicano il bene</t>
+          <t>con accelerazione di progetto a_d fino a 1 m/s² nessuna prescrizione specifica; a_d e la posizione dei rilevatori si concordano con il progettista dell'edificio</t>
         </is>
       </c>
       <c r="E181" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+          <t>UNI EN 81-77:2022, 1</t>
         </is>
       </c>
       <c r="F181" s="10" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="H181" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I181" s="11" t="n"/>
@@ -9131,28 +9131,28 @@
       <c r="M181" s="11" t="n"/>
       <c r="N181" s="11" t="n"/>
     </row>
-    <row r="182" ht="69" customHeight="1">
+    <row r="182" ht="95" customHeight="1">
       <c r="A182" s="10" t="n">
         <v>180</v>
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
         </is>
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
         </is>
       </c>
       <c r="D182" s="10" t="inlineStr">
         <is>
-          <t>il progettista applica il DM 15/09/2005 oppure la RTV V.3 del Codice: dove si usa il Codice il DM 2005 non si applica</t>
+          <t>oltre 1 m/s²: massa della cabina nei calcoli (5.4.1), ritegni della cabina (5.4.2) e del contrappeso (5.5), protezione delle pulegge (5.6.1), tensioni e frecce delle guide (5.8.2, All. D), rilevazione e modo sismico (5.10.3, 5.10.4); soglie delle categorie dell'All. A da verificare sul testo</t>
         </is>
       </c>
       <c r="E182" s="10" t="inlineStr">
         <is>
-          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
         </is>
       </c>
       <c r="F182" s="10" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="G182" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H182" s="10" t="inlineStr">
@@ -9177,28 +9177,28 @@
       <c r="M182" s="11" t="n"/>
       <c r="N182" s="11" t="n"/>
     </row>
-    <row r="183" ht="95" customHeight="1">
+    <row r="183" ht="43" customHeight="1">
       <c r="A183" s="10" t="n">
         <v>181</v>
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, art. 1 c.2</t>
+          <t>UNI EN 81-77:2022, 0.3</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>sugli impianti esistenti vale per le modifiche sostanziali: nuovo impianto; più fermate o altro azionamento; pareti del vano, porte di piano, locale macchine o pulegge sostituiti con materiali, modelli, dimensioni o criteri diversi; solai o scale rifatti che coinvolgono l'impianto; sopraelevazione; cambio di destinazione d'uso</t>
+          <t>non si applica agli impianti installati prima della sua pubblicazione</t>
         </is>
       </c>
       <c r="E183" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, art. 1 c.2</t>
+          <t>UNI EN 81-77:2022, 0.3</t>
         </is>
       </c>
       <c r="F183" s="10" t="inlineStr">
@@ -9229,27 +9229,27 @@
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
         </is>
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+          <t>UNI EN 81-80:2004 e 2009, 1 e appendice A</t>
         </is>
       </c>
       <c r="D184" s="10" t="inlineStr">
         <is>
-          <t>tipo di vano: aperto, protetto o a prova di fumo (Codice: classi da SA a SE)</t>
+          <t>analisi dei rischi dell'impianto esistente e piano di miglioramento per priorità; quali misure e in che tempi lo decide la legislazione nazionale, non la norma</t>
         </is>
       </c>
       <c r="E184" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+          <t>UNI EN 81-80:2004 e 2009, 1 e appendice A</t>
         </is>
       </c>
       <c r="F184" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G184" s="10" t="inlineStr">
@@ -9275,22 +9275,22 @@
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
         </is>
       </c>
       <c r="C185" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 2</t>
+          <t>UNI EN 81-80:2019</t>
         </is>
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>pareti del vano, locale macchine e pulegge, setti e arcata non combustibili; pareti, pavimento e tetto della cabina in classe di reazione al fuoco non oltre 1</t>
+          <t>la stessa analisi nell'edizione in vigore, con una struttura diversa: da verificare sul testo</t>
         </is>
       </c>
       <c r="E185" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 2</t>
+          <t>UNI EN 81-80:2019</t>
         </is>
       </c>
       <c r="F185" s="10" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="G185" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H185" s="10" t="inlineStr">
@@ -9315,28 +9315,28 @@
       <c r="M185" s="11" t="n"/>
       <c r="N185" s="11" t="n"/>
     </row>
-    <row r="186" ht="82" customHeight="1">
+    <row r="186" ht="56" customHeight="1">
       <c r="A186" s="10" t="n">
         <v>184</v>
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: UNI EN 81-82:2026 (accessibilità degli esistenti)</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 5</t>
+          <t>UNI EN 81-82:2026</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>aerazione permanente in alto verso spazi scoperti di almeno il 3 % della pianta (vano almeno 0,20 m², locale macchine o pulegge almeno 0,05 m²), con una protezione che non lascia passare una sfera oltre 15 mm; non serve se il vano è aperto su spazi scoperti</t>
+          <t>miglioramento dell'accessibilità di un impianto esistente secondo i requisiti della EN 81-70</t>
         </is>
       </c>
       <c r="E186" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 5</t>
+          <t>UNI EN 81-82:2026</t>
         </is>
       </c>
       <c r="F186" s="10" t="inlineStr">
@@ -9361,28 +9361,28 @@
       <c r="M186" s="11" t="n"/>
       <c r="N186" s="11" t="n"/>
     </row>
-    <row r="187" ht="69" customHeight="1">
+    <row r="187" ht="56" customHeight="1">
       <c r="A187" s="10" t="n">
         <v>185</v>
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: UNI EN 81-83:2026 (antivandalo degli esistenti)</t>
         </is>
       </c>
       <c r="C187" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+          <t>UNI EN 81-83:2026</t>
         </is>
       </c>
       <c r="D187" s="10" t="inlineStr">
         <is>
-          <t>estintore 21A89BC vicino all'accesso al macchinario; richiamo della cabina al piano prestabilito su comando della rivelazione quando la compartimentazione lo richiede</t>
+          <t>miglioramento della resistenza agli atti vandalici di un impianto esistente secondo la EN 81-71:2022 (voce 1.2 della Tab. A.1 della EN 81-80)</t>
         </is>
       </c>
       <c r="E187" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+          <t>UNI EN 81-83:2026</t>
         </is>
       </c>
       <c r="F187" s="10" t="inlineStr">
@@ -9407,33 +9407,33 @@
       <c r="M187" s="11" t="n"/>
       <c r="N187" s="11" t="n"/>
     </row>
-    <row r="188" ht="69" customHeight="1">
+    <row r="188" ht="56" customHeight="1">
       <c r="A188" s="10" t="n">
         <v>186</v>
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>Codice S.9, Tab. S.9-3</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>piani tra 32 e 54 m: almeno un ascensore antincendio; oltre 54 m: almeno uno di soccorso; interrati tra −10 e −15 m: antincendio; sotto −15 m: soccorso</t>
+          <t>piattaforma di distribuzione davanti alla porta di cabina: 1,50 × 1,50 m negli edifici nuovi, 1,40 × 1,40 m nell'adeguamento (fuori dal vano: in sito)</t>
         </is>
       </c>
       <c r="E188" s="10" t="inlineStr">
         <is>
-          <t>Codice S.9, Tab. S.9-3</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F188" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989</t>
         </is>
       </c>
       <c r="G188" s="10" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="H188" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I188" s="11" t="n"/>
@@ -9453,33 +9453,33 @@
       <c r="M188" s="11" t="n"/>
       <c r="N188" s="11" t="n"/>
     </row>
-    <row r="189" ht="43" customHeight="1">
+    <row r="189" ht="56" customHeight="1">
       <c r="A189" s="10" t="n">
         <v>187</v>
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §3.1.4</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>carichi del macchinario valutati caso per caso sui massimi prevedibili e riportati nel progetto e nel collaudo statico</t>
+          <t>porte di cabina e di piano a scorrimento automatico (nell'adeguamento la porta di piano può essere a battente se ad apertura automatica); porte aperte almeno 8 s, chiusura in almeno 4 s</t>
         </is>
       </c>
       <c r="E189" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §3.1.4</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F189" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989</t>
         </is>
       </c>
       <c r="G189" s="10" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="H189" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I189" s="11" t="n"/>
@@ -9505,27 +9505,27 @@
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §8.4.1</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>su un edificio esistente l'intervento è locale: verifica limitata alle parti interessate, senza ridurre la sicurezza preesistente</t>
+          <t>arresto ai piani con autolivellamento entro ± 2 cm; sosta ai piani con le porte chiuse</t>
         </is>
       </c>
       <c r="E190" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §8.4.1</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F190" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989</t>
         </is>
       </c>
       <c r="G190" s="10" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="H190" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I190" s="11" t="n"/>
@@ -9545,33 +9545,33 @@
       <c r="M190" s="11" t="n"/>
       <c r="N190" s="11" t="n"/>
     </row>
-    <row r="191" ht="43" customHeight="1">
+    <row r="191" ht="56" customHeight="1">
       <c r="A191" s="10" t="n">
         <v>189</v>
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §11.4.1</t>
+          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>ancoranti per uso strutturale qualificati; con azioni sismiche categoria C2 per tutte le classi d'uso</t>
+          <t>pulsanti di cabina e di piano: il più alto tra 1,10 e 1,40 m, misurato all'asse del comando; bottoniera di cabina su una parete laterale ad almeno 0,35 m dalla porta</t>
         </is>
       </c>
       <c r="E191" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §11.4.1</t>
+          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
         </is>
       </c>
       <c r="F191" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989</t>
         </is>
       </c>
       <c r="G191" s="10" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H191" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I191" s="11" t="n"/>
@@ -9591,33 +9591,33 @@
       <c r="M191" s="11" t="n"/>
       <c r="N191" s="11" t="n"/>
     </row>
-    <row r="192" ht="108" customHeight="1">
+    <row r="192" ht="95" customHeight="1">
       <c r="A192" s="10" t="n">
         <v>190</v>
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §7.2.3–7.2.4</t>
+          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>forza sismica sull'elemento non strutturale Fa = Sa·Wa/qa; nessun vincolo ad attrito; studio specifico oltre il 30 % del carico permanente del solaio o il 10 % di quello dell'intera struttura; progetto antisismico dell'impianto del produttore, dei collegamenti dell'installatore, dei solai e delle pareti d'ancoraggio del progettista strutturale</t>
+          <t>citofono in cabina tra 1,10 e 1,30 m; luce d'emergenza con almeno 3 h di autonomia; campanello d'allarme e segnale luminoso di allarme ricevuto; arresto e inversione della chiusura; segnale acustico d'arrivo; numeri in rilievo e Braille, targa Braille di piano; sedile ribaltabile dove possibile</t>
         </is>
       </c>
       <c r="E192" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §7.2.3–7.2.4</t>
+          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
         </is>
       </c>
       <c r="F192" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989</t>
         </is>
       </c>
       <c r="G192" s="10" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="H192" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I192" s="11" t="n"/>
@@ -9637,33 +9637,33 @@
       <c r="M192" s="11" t="n"/>
       <c r="N192" s="11" t="n"/>
     </row>
-    <row r="193" ht="43" customHeight="1">
+    <row r="193" ht="56" customHeight="1">
       <c r="A193" s="10" t="n">
         <v>191</v>
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
         </is>
       </c>
       <c r="D193" s="10" t="inlineStr">
         <is>
-          <t>impianti: stabilità allo SLV per tutte le classi d'uso; nelle classi III e IV anche funzionamento allo SLO</t>
+          <t>ascensore obbligatorio oltre il terzo livello (contati interrati e porticati); negli immobili con più di tre livelli fuori terra un ascensore per ogni scala principale</t>
         </is>
       </c>
       <c r="E193" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
         </is>
       </c>
       <c r="F193" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989; L. 13/1989: ricerca, cap. 16</t>
         </is>
       </c>
       <c r="G193" s="10" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="H193" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I193" s="11" t="n"/>
@@ -9683,10 +9683,608 @@
       <c r="M193" s="11" t="n"/>
       <c r="N193" s="11" t="n"/>
     </row>
+    <row r="194" ht="56" customHeight="1">
+      <c r="A194" s="10" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+        </is>
+      </c>
+      <c r="C194" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+        </is>
+      </c>
+      <c r="D194" s="10" t="inlineStr">
+        <is>
+          <t>nelle ristrutturazioni deroghe per impossibilità tecnica strutturale o impiantistica (privati: concesse dal Sindaco); edifici vincolati: deroga se le opere pregiudicano il bene</t>
+        </is>
+      </c>
+      <c r="E194" s="10" t="inlineStr">
+        <is>
+          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+        </is>
+      </c>
+      <c r="F194" s="10" t="inlineStr">
+        <is>
+          <t>testo ufficiale del DM 236/1989; DPR 503/1996: ricerca, cap. 16</t>
+        </is>
+      </c>
+      <c r="G194" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H194" s="10" t="inlineStr">
+        <is>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+        </is>
+      </c>
+      <c r="I194" s="11" t="n"/>
+      <c r="J194" s="11" t="n"/>
+      <c r="K194" s="11" t="n"/>
+      <c r="L194" s="11" t="n"/>
+      <c r="M194" s="11" t="n"/>
+      <c r="N194" s="11" t="n"/>
+    </row>
+    <row r="195" ht="69" customHeight="1">
+      <c r="A195" s="10" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C195" s="10" t="inlineStr">
+        <is>
+          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+        </is>
+      </c>
+      <c r="D195" s="10" t="inlineStr">
+        <is>
+          <t>il progettista applica il DM 15/09/2005 oppure la RTV V.3 del Codice: dove si usa il Codice il DM 2005 non si applica</t>
+        </is>
+      </c>
+      <c r="E195" s="10" t="inlineStr">
+        <is>
+          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+        </is>
+      </c>
+      <c r="F195" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G195" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H195" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I195" s="11" t="n"/>
+      <c r="J195" s="11" t="n"/>
+      <c r="K195" s="11" t="n"/>
+      <c r="L195" s="11" t="n"/>
+      <c r="M195" s="11" t="n"/>
+      <c r="N195" s="11" t="n"/>
+    </row>
+    <row r="196" ht="95" customHeight="1">
+      <c r="A196" s="10" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C196" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, art. 1 c.2</t>
+        </is>
+      </c>
+      <c r="D196" s="10" t="inlineStr">
+        <is>
+          <t>sugli impianti esistenti vale per le modifiche sostanziali: nuovo impianto; più fermate o altro azionamento; pareti del vano, porte di piano, locale macchine o pulegge sostituiti con materiali, modelli, dimensioni o criteri diversi; solai o scale rifatti che coinvolgono l'impianto; sopraelevazione; cambio di destinazione d'uso</t>
+        </is>
+      </c>
+      <c r="E196" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, art. 1 c.2</t>
+        </is>
+      </c>
+      <c r="F196" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G196" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H196" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I196" s="11" t="n"/>
+      <c r="J196" s="11" t="n"/>
+      <c r="K196" s="11" t="n"/>
+      <c r="L196" s="11" t="n"/>
+      <c r="M196" s="11" t="n"/>
+      <c r="N196" s="11" t="n"/>
+    </row>
+    <row r="197" ht="69" customHeight="1">
+      <c r="A197" s="10" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C197" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+        </is>
+      </c>
+      <c r="D197" s="10" t="inlineStr">
+        <is>
+          <t>tipo di vano: aperto, protetto o a prova di fumo (Codice: classi da SA a SE)</t>
+        </is>
+      </c>
+      <c r="E197" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+        </is>
+      </c>
+      <c r="F197" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G197" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H197" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I197" s="11" t="n"/>
+      <c r="J197" s="11" t="n"/>
+      <c r="K197" s="11" t="n"/>
+      <c r="L197" s="11" t="n"/>
+      <c r="M197" s="11" t="n"/>
+      <c r="N197" s="11" t="n"/>
+    </row>
+    <row r="198" ht="69" customHeight="1">
+      <c r="A198" s="10" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C198" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 2</t>
+        </is>
+      </c>
+      <c r="D198" s="10" t="inlineStr">
+        <is>
+          <t>pareti del vano, locale macchine e pulegge, setti e arcata non combustibili; pareti, pavimento e tetto della cabina in classe di reazione al fuoco non oltre 1</t>
+        </is>
+      </c>
+      <c r="E198" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 2</t>
+        </is>
+      </c>
+      <c r="F198" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G198" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H198" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I198" s="11" t="n"/>
+      <c r="J198" s="11" t="n"/>
+      <c r="K198" s="11" t="n"/>
+      <c r="L198" s="11" t="n"/>
+      <c r="M198" s="11" t="n"/>
+      <c r="N198" s="11" t="n"/>
+    </row>
+    <row r="199" ht="82" customHeight="1">
+      <c r="A199" s="10" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C199" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 5</t>
+        </is>
+      </c>
+      <c r="D199" s="10" t="inlineStr">
+        <is>
+          <t>aerazione permanente in alto verso spazi scoperti di almeno il 3 % della pianta (vano almeno 0,20 m², locale macchine o pulegge almeno 0,05 m²), con una protezione che non lascia passare una sfera oltre 15 mm; non serve se il vano è aperto su spazi scoperti</t>
+        </is>
+      </c>
+      <c r="E199" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 5</t>
+        </is>
+      </c>
+      <c r="F199" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G199" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H199" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I199" s="11" t="n"/>
+      <c r="J199" s="11" t="n"/>
+      <c r="K199" s="11" t="n"/>
+      <c r="L199" s="11" t="n"/>
+      <c r="M199" s="11" t="n"/>
+      <c r="N199" s="11" t="n"/>
+    </row>
+    <row r="200" ht="69" customHeight="1">
+      <c r="A200" s="10" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C200" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+        </is>
+      </c>
+      <c r="D200" s="10" t="inlineStr">
+        <is>
+          <t>estintore 21A89BC vicino all'accesso al macchinario; richiamo della cabina al piano prestabilito su comando della rivelazione quando la compartimentazione lo richiede</t>
+        </is>
+      </c>
+      <c r="E200" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+        </is>
+      </c>
+      <c r="F200" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G200" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H200" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I200" s="11" t="n"/>
+      <c r="J200" s="11" t="n"/>
+      <c r="K200" s="11" t="n"/>
+      <c r="L200" s="11" t="n"/>
+      <c r="M200" s="11" t="n"/>
+      <c r="N200" s="11" t="n"/>
+    </row>
+    <row r="201" ht="69" customHeight="1">
+      <c r="A201" s="10" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C201" s="10" t="inlineStr">
+        <is>
+          <t>Codice S.9, Tab. S.9-3</t>
+        </is>
+      </c>
+      <c r="D201" s="10" t="inlineStr">
+        <is>
+          <t>piani tra 32 e 54 m: almeno un ascensore antincendio; oltre 54 m: almeno uno di soccorso; interrati tra −10 e −15 m: antincendio; sotto −15 m: soccorso</t>
+        </is>
+      </c>
+      <c r="E201" s="10" t="inlineStr">
+        <is>
+          <t>Codice S.9, Tab. S.9-3</t>
+        </is>
+      </c>
+      <c r="F201" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G201" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H201" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I201" s="11" t="n"/>
+      <c r="J201" s="11" t="n"/>
+      <c r="K201" s="11" t="n"/>
+      <c r="L201" s="11" t="n"/>
+      <c r="M201" s="11" t="n"/>
+      <c r="N201" s="11" t="n"/>
+    </row>
+    <row r="202" ht="43" customHeight="1">
+      <c r="A202" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C202" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §3.1.4</t>
+        </is>
+      </c>
+      <c r="D202" s="10" t="inlineStr">
+        <is>
+          <t>carichi del macchinario valutati caso per caso sui massimi prevedibili e riportati nel progetto e nel collaudo statico</t>
+        </is>
+      </c>
+      <c r="E202" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §3.1.4</t>
+        </is>
+      </c>
+      <c r="F202" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G202" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H202" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I202" s="11" t="n"/>
+      <c r="J202" s="11" t="n"/>
+      <c r="K202" s="11" t="n"/>
+      <c r="L202" s="11" t="n"/>
+      <c r="M202" s="11" t="n"/>
+      <c r="N202" s="11" t="n"/>
+    </row>
+    <row r="203" ht="43" customHeight="1">
+      <c r="A203" s="10" t="n">
+        <v>201</v>
+      </c>
+      <c r="B203" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C203" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §8.4.1</t>
+        </is>
+      </c>
+      <c r="D203" s="10" t="inlineStr">
+        <is>
+          <t>su un edificio esistente l'intervento è locale: verifica limitata alle parti interessate, senza ridurre la sicurezza preesistente</t>
+        </is>
+      </c>
+      <c r="E203" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §8.4.1</t>
+        </is>
+      </c>
+      <c r="F203" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G203" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H203" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I203" s="11" t="n"/>
+      <c r="J203" s="11" t="n"/>
+      <c r="K203" s="11" t="n"/>
+      <c r="L203" s="11" t="n"/>
+      <c r="M203" s="11" t="n"/>
+      <c r="N203" s="11" t="n"/>
+    </row>
+    <row r="204" ht="43" customHeight="1">
+      <c r="A204" s="10" t="n">
+        <v>202</v>
+      </c>
+      <c r="B204" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C204" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §11.4.1</t>
+        </is>
+      </c>
+      <c r="D204" s="10" t="inlineStr">
+        <is>
+          <t>ancoranti per uso strutturale qualificati; con azioni sismiche categoria C2 per tutte le classi d'uso</t>
+        </is>
+      </c>
+      <c r="E204" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §11.4.1</t>
+        </is>
+      </c>
+      <c r="F204" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G204" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H204" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I204" s="11" t="n"/>
+      <c r="J204" s="11" t="n"/>
+      <c r="K204" s="11" t="n"/>
+      <c r="L204" s="11" t="n"/>
+      <c r="M204" s="11" t="n"/>
+      <c r="N204" s="11" t="n"/>
+    </row>
+    <row r="205" ht="108" customHeight="1">
+      <c r="A205" s="10" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C205" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §7.2.3–7.2.4</t>
+        </is>
+      </c>
+      <c r="D205" s="10" t="inlineStr">
+        <is>
+          <t>forza sismica sull'elemento non strutturale Fa = Sa·Wa/qa; nessun vincolo ad attrito; studio specifico oltre il 30 % del carico permanente del solaio o il 10 % di quello dell'intera struttura; progetto antisismico dell'impianto del produttore, dei collegamenti dell'installatore, dei solai e delle pareti d'ancoraggio del progettista strutturale</t>
+        </is>
+      </c>
+      <c r="E205" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §7.2.3–7.2.4</t>
+        </is>
+      </c>
+      <c r="F205" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G205" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H205" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I205" s="11" t="n"/>
+      <c r="J205" s="11" t="n"/>
+      <c r="K205" s="11" t="n"/>
+      <c r="L205" s="11" t="n"/>
+      <c r="M205" s="11" t="n"/>
+      <c r="N205" s="11" t="n"/>
+    </row>
+    <row r="206" ht="43" customHeight="1">
+      <c r="A206" s="10" t="n">
+        <v>204</v>
+      </c>
+      <c r="B206" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C206" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+        </is>
+      </c>
+      <c r="D206" s="10" t="inlineStr">
+        <is>
+          <t>impianti: stabilità allo SLV per tutte le classi d'uso; nelle classi III e IV anche funzionamento allo SLO</t>
+        </is>
+      </c>
+      <c r="E206" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+        </is>
+      </c>
+      <c r="F206" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G206" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H206" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I206" s="11" t="n"/>
+      <c r="J206" s="11" t="n"/>
+      <c r="K206" s="11" t="n"/>
+      <c r="L206" s="11" t="n"/>
+      <c r="M206" s="11" t="n"/>
+      <c r="N206" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N193"/>
+  <autoFilter ref="A1:N206"/>
   <dataValidations count="1">
-    <dataValidation sqref="I3:I193" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
+    <dataValidation sqref="I3:I206" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
       <formula1>"conforme,diverso,non applicabile"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9729,7 +10327,7 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$193,"da verificare")</f>
+        <f>COUNTIF(Voci!$G$3:$G$206,"da verificare")</f>
         <v/>
       </c>
     </row>
@@ -9740,7 +10338,7 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$193,"confermato")</f>
+        <f>COUNTIF(Voci!$G$3:$G$206,"confermato")</f>
         <v/>
       </c>
     </row>
@@ -9751,7 +10349,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$193,"scelta del software")</f>
+        <f>COUNTIF(Voci!$G$3:$G$206,"scelta del software")</f>
         <v/>
       </c>
     </row>
@@ -9762,7 +10360,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$193,"stima")</f>
+        <f>COUNTIF(Voci!$G$3:$G$206,"stima")</f>
         <v/>
       </c>
     </row>
@@ -9773,7 +10371,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$193,"derivazione")</f>
+        <f>COUNTIF(Voci!$G$3:$G$206,"derivazione")</f>
         <v/>
       </c>
     </row>
@@ -9784,7 +10382,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$193,"prassi di cantiere")</f>
+        <f>COUNTIF(Voci!$G$3:$G$206,"prassi di cantiere")</f>
         <v/>
       </c>
     </row>
@@ -9795,7 +10393,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTA(Voci!$A$3:$A$193)</f>
+        <f>COUNTA(Voci!$A$3:$A$206)</f>
         <v/>
       </c>
     </row>
@@ -9813,7 +10411,7 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$193,"conforme")</f>
+        <f>COUNTIF(Voci!$I$3:$I$206,"conforme")</f>
         <v/>
       </c>
     </row>
@@ -9824,7 +10422,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$193,"diverso")</f>
+        <f>COUNTIF(Voci!$I$3:$I$206,"diverso")</f>
         <v/>
       </c>
     </row>
@@ -9835,7 +10433,7 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$193,"non applicabile")</f>
+        <f>COUNTIF(Voci!$I$3:$I$206,"non applicabile")</f>
         <v/>
       </c>
     </row>
@@ -9846,14 +10444,14 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>COUNTBLANK(Voci!$I$3:$I$193)</f>
+        <f>COUNTBLANK(Voci!$I$3:$I$206)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Conteggi sulle righe 3–193 del foglio «Voci» (la riga 2 è l'esempio).</t>
+          <t>Conteggi sulle righe 3–206 del foglio «Voci» (la riga 2 è l'esempio).</t>
         </is>
       </c>
     </row>

--- a/liftpilot/docs/lista-verifica-normativa.xlsx
+++ b/liftpilot/docs/lista-verifica-normativa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Riepilogo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$215</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Voci'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N206"/>
+  <dimension ref="A1:N215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -897,7 +897,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="147" customHeight="1">
+    <row r="3" ht="121" customHeight="1">
       <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
@@ -908,7 +908,7 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Aderenza: tre condizioni di Euler-Eytelwein — Con la cabina o il contrappeso bloccati la condizione serve quando è l'aderenza a impedire il sollevamento: la UNI EN 81-20:2020 (5.5.3 c)) ammette in alternativa un dispositivo elettrico di sicurezza; la UNI EN 81-1:2008 (9.3 c)) no. Il software verifica sempre la condizione: se c'è il dispositivo, lo decide l'ingegnere.</t>
+          <t>Aderenza: tre condizioni di Euler-Eytelwein — Con la cabina o il contrappeso bloccati la condizione serve quando è l'aderenza a impedire il sollevamento: la UNI EN 81-20:2020 (5.5.3 c)) ammette in alternativa un dispositivo elettrico di sicurezza (voce trazione.bloccata.dispositivo); la UNI EN 81-1:2008 (9.3 c)) no.</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -943,7 +943,7 @@
       <c r="M3" s="11" t="n"/>
       <c r="N3" s="11" t="n"/>
     </row>
-    <row r="4" ht="43" customHeight="1">
+    <row r="4" ht="134" customHeight="1">
       <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
@@ -954,22 +954,22 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Coefficiente di attrito, caricamento</t>
+          <t>Cabina o contrappeso bloccati: dispositivo al posto dello slittamento — La norma non dice quale dispositivo: deve accorgersi del blocco e fermare la macchina prima di un sollevamento pericoloso. Il temporizzatore della 5.9.2.7 è un obbligo distinto. Con la UNI 10411-11:2024 vale solo se la macchina è verificata secondo la UNI EN 81-20.</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>μ = 0,1</t>
+          <t>con la macchina secondo la UNI EN 81-20:2020 e un dispositivo elettrico di sicurezza (5.11.2) che arresta la macchina, la verifica con cabina o contrappeso bloccati non superata è «Attenzione» (verifica sostituita da dispositivo, da documentare), mai OK; con la macchina secondo la UNI EN 81-1 resta KO</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.3.2</t>
+          <t>UNI EN 81-20:2020, 5.5.3 c) 2); UNI EN 81-1:2008, 9.3 c); UNI 10411-1:2024, 14.1 a)–b)</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 42</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 75; UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 55; UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 13</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>aderenza al caricamento</t>
+          <t>cabina bloccata</t>
         </is>
       </c>
       <c r="I4" s="11" t="n"/>
@@ -989,7 +989,7 @@
       <c r="M4" s="11" t="n"/>
       <c r="N4" s="11" t="n"/>
     </row>
-    <row r="5" ht="69" customHeight="1">
+    <row r="5" ht="43" customHeight="1">
       <c r="A5" s="10" t="n">
         <v>3</v>
       </c>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Coefficiente di attrito, frenatura di emergenza</t>
+          <t>Coefficiente di attrito, caricamento</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>μ = 0,1 / (1 + v_f/10), v_f = velocità delle funi</t>
+          <t>μ = 0,1</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 42 (v_f: velocità delle funi alla velocità nominale della cabina)</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 42</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>aderenza in frenatura, in discesa; aderenza in frenatura, in salita; aderenza alla decelerazione reale (avviso)</t>
+          <t>aderenza al caricamento</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
@@ -1035,7 +1035,7 @@
       <c r="M5" s="11" t="n"/>
       <c r="N5" s="11" t="n"/>
     </row>
-    <row r="6" ht="43" customHeight="1">
+    <row r="6" ht="69" customHeight="1">
       <c r="A6" s="10" t="n">
         <v>4</v>
       </c>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Coefficiente di attrito, contrappeso o cabina bloccati</t>
+          <t>Coefficiente di attrito, frenatura di emergenza</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>μ = 0,2</t>
+          <t>μ = 0,1 / (1 + v_f/10), v_f = velocità delle funi</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 42</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 42 (v_f: velocità delle funi alla velocità nominale della cabina)</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>cabina bloccata</t>
+          <t>aderenza in frenatura, in discesa; aderenza in frenatura, in salita; aderenza alla decelerazione reale (avviso)</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
@@ -1081,7 +1081,7 @@
       <c r="M6" s="11" t="n"/>
       <c r="N6" s="11" t="n"/>
     </row>
-    <row r="7" ht="95" customHeight="1">
+    <row r="7" ht="43" customHeight="1">
       <c r="A7" s="10" t="n">
         <v>5</v>
       </c>
@@ -1092,22 +1092,22 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Carico della verifica di caricamento — La norma aggiunge il peso dei dispositivi di movimentazione, dove usati negli ascensori per merci e persone: non modellato. Le due posizioni della cabina sono quelle più sfavorevoli che il software verifica.</t>
+          <t>Coefficiente di attrito, contrappeso o cabina bloccati</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1,25·Q, cabina in basso e in alto</t>
+          <t>μ = 0,2</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.2.1 e 5.11.3</t>
+          <t>UNI EN 81-50:2020, 5.11.2.3.2</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 40 e 44 (al caricamento e con la cabina bloccata a = 0)</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 42</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>aderenza al caricamento</t>
+          <t>cabina bloccata</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
@@ -1127,7 +1127,7 @@
       <c r="M7" s="11" t="n"/>
       <c r="N7" s="11" t="n"/>
     </row>
-    <row r="8" ht="43" customHeight="1">
+    <row r="8" ht="95" customHeight="1">
       <c r="A8" s="10" t="n">
         <v>6</v>
       </c>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Decelerazione della verifica di frenatura</t>
+          <t>Carico della verifica di caricamento — La norma aggiunge il peso dei dispositivi di movimentazione, dove usati negli ascensori per merci e persone: non modellato. Le due posizioni della cabina sono quelle più sfavorevoli che il software verifica.</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>almeno 0,5 m/s²</t>
+          <t>1,25·Q, cabina in basso e in alto</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.2.2</t>
+          <t>UNI EN 81-50:2020, 5.11.2.2.1 e 5.11.3</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 40</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 40 e 44 (al caricamento e con la cabina bloccata a = 0)</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>aderenza in frenatura, in discesa; aderenza in frenatura, in salita</t>
+          <t>aderenza al caricamento</t>
         </is>
       </c>
       <c r="I8" s="11" t="n"/>
@@ -1173,7 +1173,7 @@
       <c r="M8" s="11" t="n"/>
       <c r="N8" s="11" t="n"/>
     </row>
-    <row r="9" ht="160" customHeight="1">
+    <row r="9" ht="43" customHeight="1">
       <c r="A9" s="10" t="n">
         <v>7</v>
       </c>
@@ -1184,27 +1184,27 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Decelerazione della verifica di frenatura con ammortizzatori a corsa ridotta — La UNI EN 81-50:2020 non dà un numero: con ammortizzatori a corsa ridotta la decelerazione è la minima che porta cabina e contrappeso alla velocità di progetto degli ammortizzatori, mai sotto 0,5 m/s². Il software tiene 0,8 m/s², il valore della UNI EN 81-1:2008: l'ingegnere lo sostituisce con quello calcolato dai dati degli ammortizzatori.</t>
+          <t>Decelerazione della verifica di frenatura</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>0,8 m/s²</t>
+          <t>almeno 0,5 m/s²</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-1:2008, M.2.1.2; UNI EN 81-50:2020, 5.11.2.2.2</t>
+          <t>UNI EN 81-50:2020, 5.11.2.2.2</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 167; UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 40</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 40</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -1219,7 +1219,7 @@
       <c r="M9" s="11" t="n"/>
       <c r="N9" s="11" t="n"/>
     </row>
-    <row r="10" ht="43" customHeight="1">
+    <row r="10" ht="160" customHeight="1">
       <c r="A10" s="10" t="n">
         <v>8</v>
       </c>
@@ -1230,22 +1230,22 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Combinazioni della frenatura di emergenza</t>
+          <t>Decelerazione della verifica di frenatura con ammortizzatori a corsa ridotta — La UNI EN 81-50:2020 non dà un numero: con ammortizzatori a corsa ridotta la decelerazione è la minima che porta cabina e contrappeso alla velocità di progetto degli ammortizzatori, mai sotto 0,5 m/s². Il software tiene 0,8 m/s², il valore della UNI EN 81-1:2008: l'ingegnere lo sostituisce con quello calcolato dai dati degli ammortizzatori.</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>cabina vuota e con portata × in discesa e in salita × in basso e in alto; conta la peggiore per verso</t>
+          <t>0,8 m/s²</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.2.2</t>
+          <t>UNI EN 81-1:2008, M.2.1.2; UNI EN 81-50:2020, 5.11.2.2.2</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>derivazione (copertura completa dei casi)</t>
+          <t>UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 167; UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 40</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -1265,7 +1265,7 @@
       <c r="M10" s="11" t="n"/>
       <c r="N10" s="11" t="n"/>
     </row>
-    <row r="11" ht="121" customHeight="1">
+    <row r="11" ht="43" customHeight="1">
       <c r="A11" s="10" t="n">
         <v>9</v>
       </c>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Aderenza alla decelerazione reale del freno — La norma vuole ogni massa in moto con la sua accelerazione e una decelerazione di calcolo mai sotto 0,5 m/s²; non dice con quanti gruppi del freno. Se contarla come esito lo decide l'ingegnere: nell'esempio B del capitolo 7 l'utilizzo passa da 1,005 a 4,17.</t>
+          <t>Combinazioni della frenatura di emergenza</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Seconda verifica con la decelerazione data dal freno (tutti i gruppi, mai sotto il minimo); oggi solo avviso</t>
+          <t>cabina vuota e con portata × in discesa e in salita × in basso e in alto; conta la peggiore per verso</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 40</t>
+          <t>derivazione (copertura completa dei casi)</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>aderenza alla decelerazione reale (avviso)</t>
+          <t>aderenza in frenatura, in discesa; aderenza in frenatura, in salita</t>
         </is>
       </c>
       <c r="I11" s="11" t="n"/>
@@ -1311,7 +1311,7 @@
       <c r="M11" s="11" t="n"/>
       <c r="N11" s="11" t="n"/>
     </row>
-    <row r="12" ht="69" customHeight="1">
+    <row r="12" ht="121" customHeight="1">
       <c r="A12" s="10" t="n">
         <v>10</v>
       </c>
@@ -1322,22 +1322,22 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Soglia di attenzione sull'utilizzo dell'aderenza</t>
+          <t>Aderenza alla decelerazione reale del freno — La norma vuole ogni massa in moto con la sua accelerazione e una decelerazione di calcolo mai sotto 0,5 m/s²; non dice con quanti gruppi del freno. Se contarla come esito lo decide l'ingegnere: nell'esempio B del capitolo 7 l'utilizzo passa da 1,005 a 4,17.</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>utilizzo &gt; 0,97 → «Attenzione»</t>
+          <t>Seconda verifica con la decelerazione data dal freno (tutti i gruppi, mai sotto il minimo); oggi solo avviso</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.2.2.2</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (margine per incertezza su masse e bilanciamento)</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 40</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>aderenza al caricamento; aderenza in frenatura, in discesa; aderenza in frenatura, in salita; aderenza alla decelerazione reale (avviso)</t>
+          <t>aderenza alla decelerazione reale (avviso)</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -1357,43 +1357,43 @@
       <c r="M12" s="11" t="n"/>
       <c r="N12" s="11" t="n"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="69" customHeight="1">
       <c r="A13" s="10" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Gole</t>
+          <t>Aderenza</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Fattore di gola, semicircolare con o senza sottosquadro</t>
+          <t>Soglia di attenzione sull'utilizzo dell'aderenza</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>f = μ·4·(cos(γ/2) − sin(β/2)) / (π − β − γ − sin β + sin γ); senza sottosquadro β = 0</t>
+          <t>utilizzo &gt; 0,97 → «Attenzione»</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.3.1.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 40–41</t>
+          <t>scelta del software (margine per incertezza su masse e bilanciamento)</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>aderenza al caricamento; aderenza in frenatura, in discesa; aderenza in frenatura, in salita; cabina bloccata</t>
+          <t>aderenza al caricamento; aderenza in frenatura, in discesa; aderenza in frenatura, in salita; aderenza alla decelerazione reale (avviso)</t>
         </is>
       </c>
       <c r="I13" s="11" t="n"/>
@@ -1403,7 +1403,7 @@
       <c r="M13" s="11" t="n"/>
       <c r="N13" s="11" t="n"/>
     </row>
-    <row r="14" ht="69" customHeight="1">
+    <row r="14" ht="56" customHeight="1">
       <c r="A14" s="10" t="n">
         <v>12</v>
       </c>
@@ -1414,22 +1414,22 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Fattore di gola a V — la norma dà f = μ / sin(γ/2) per il contrappeso bloccato; il software la usa anche per la cabina bloccata nella posizione più bassa (5.11.2.2.3)</t>
+          <t>Fattore di gola, semicircolare con o senza sottosquadro</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>non temprata, al caricamento e in frenatura: f = μ·4·(1 − sin(β/2)) / (π − β − sin β); temprata, e ogni gola a V con il contrappeso o la cabina bloccati: f = μ / sin(γ/2)</t>
+          <t>f = μ·4·(cos(γ/2) − sin(β/2)) / (π − β − γ − sin β + sin γ); senza sottosquadro β = 0</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.3.1.2</t>
+          <t>UNI EN 81-50:2020, 5.11.2.3.1.1</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 41</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 40–41</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -1449,7 +1449,7 @@
       <c r="M14" s="11" t="n"/>
       <c r="N14" s="11" t="n"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="69" customHeight="1">
       <c r="A15" s="10" t="n">
         <v>13</v>
       </c>
@@ -1460,22 +1460,22 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Limite del sottosquadro — fino alla versione 1.1.0 del motore il limite era 106°, il valore raccomandato della UNI EN 81-1:2008 (M.2.2.1.1)</t>
+          <t>Fattore di gola a V — la norma dà f = μ / sin(γ/2) per il contrappeso bloccato; il software la usa anche per la cabina bloccata nella posizione più bassa (5.11.2.2.3)</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>β ≤ 105° (1,83 rad; oltre: KO)</t>
+          <t>non temprata, al caricamento e in frenatura: f = μ·4·(1 − sin(β/2)) / (π − β − sin β); temprata, e ogni gola a V con il contrappeso o la cabina bloccati: f = μ / sin(γ/2)</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.3.1.1 e 5.11.2.3.1.2</t>
+          <t>UNI EN 81-50:2020, 5.11.2.3.1.2</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 40–41</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 41</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>geometria della gola</t>
+          <t>aderenza al caricamento; aderenza in frenatura, in discesa; aderenza in frenatura, in salita; cabina bloccata</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -1495,7 +1495,7 @@
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="11" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="56" customHeight="1">
       <c r="A16" s="10" t="n">
         <v>14</v>
       </c>
@@ -1506,27 +1506,27 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Sottosquadro raccomandato</t>
+          <t>Limite del sottosquadro — fino alla versione 1.1.0 del motore il limite era 106°, il valore raccomandato della UNI EN 81-1:2008 (M.2.2.1.1)</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>β ≤ 90° (oltre: «Attenzione»)</t>
+          <t>β ≤ 105° (1,83 rad; oltre: KO)</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.2.3.1.1 e 5.11.2.3.1.2</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>Montanari, documento tecnico del costruttore</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 40–41</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -1541,7 +1541,7 @@
       <c r="M16" s="11" t="n"/>
       <c r="N16" s="11" t="n"/>
     </row>
-    <row r="17" ht="43" customHeight="1">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="10" t="n">
         <v>15</v>
       </c>
@@ -1552,27 +1552,27 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Angolo minimo della gola a V</t>
+          <t>Sottosquadro raccomandato</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>γ ≥ 35° (sotto: KO)</t>
+          <t>β ≤ 90° (oltre: «Attenzione»)</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.3.1.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 41; Montanari consiglia 35–40°</t>
+          <t>Montanari, documento tecnico del costruttore</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
@@ -1598,22 +1598,22 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Angolo minimo della gola semicircolare</t>
+          <t>Angolo minimo della gola a V</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>γ ≥ 25° (0,44 rad; sotto: «Attenzione»: la norma lo raccomanda, non lo impone)</t>
+          <t>γ ≥ 35° (sotto: KO)</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.3.1.1</t>
+          <t>UNI EN 81-50:2020, 5.11.2.3.1.2</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 40–41</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 41; Montanari consiglia 35–40°</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -1639,27 +1639,27 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Funi</t>
+          <t>Gole</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Rapporto D/d della puleggia di trazione</t>
+          <t>Angolo minimo della gola semicircolare</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>D/d ≥ 40</t>
+          <t>γ ≥ 25° (0,44 rad; sotto: «Attenzione»: la norma lo raccomanda, non lo impone)</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.5.2.1</t>
+          <t>UNI EN 81-50:2020, 5.11.2.3.1.1</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 74</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 40–41</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>D/d della puleggia</t>
+          <t>geometria della gola</t>
         </is>
       </c>
       <c r="I19" s="11" t="n"/>
@@ -1679,7 +1679,7 @@
       <c r="M19" s="11" t="n"/>
       <c r="N19" s="11" t="n"/>
     </row>
-    <row r="20" ht="108" customHeight="1">
+    <row r="20" ht="43" customHeight="1">
       <c r="A20" s="10" t="n">
         <v>18</v>
       </c>
@@ -1690,22 +1690,22 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Rapporto D/d delle pulegge di rinvio — Il limite vale per ogni puleggia (5.5.2.1), mentre Dp è uno solo e nel calcolo di N_equiv(p) è la media delle pulegge di rinvio (UNI EN 81-50:2020, 5.12.2.3): con pulegge di diametro diverso si controlla la più piccola.</t>
+          <t>Rapporto D/d della puleggia di trazione</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Dp/d ≥ 40</t>
+          <t>D/d ≥ 40</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.5.2.1; UNI 10411-1:2024, 14.3</t>
+          <t>UNI EN 81-20:2020, 5.5.2.1</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 74; UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 14</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 74</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Dp/d dei rinvii</t>
+          <t>D/d della puleggia</t>
         </is>
       </c>
       <c r="I20" s="11" t="n"/>
@@ -1725,7 +1725,7 @@
       <c r="M20" s="11" t="n"/>
       <c r="N20" s="11" t="n"/>
     </row>
-    <row r="21" ht="95" customHeight="1">
+    <row r="21" ht="108" customHeight="1">
       <c r="A21" s="10" t="n">
         <v>19</v>
       </c>
@@ -1736,22 +1736,22 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Numero minimo di funi — Con 2 sole funi la UNI EN 81-20:2020 (5.5.5.3 a)) chiede anche un dispositivo elettrico di sicurezza contro l'allungamento anomalo di una fune rispetto all'altra; il software non lo verifica.</t>
+          <t>Rapporto D/d delle pulegge di rinvio — Il limite vale per ogni puleggia (5.5.2.1), mentre Dp è uno solo e nel calcolo di N_equiv(p) è la media delle pulegge di rinvio (UNI EN 81-50:2020, 5.12.2.3): con pulegge di diametro diverso si controlla la più piccola.</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>almeno 2 funi indipendenti, ciascuna con il suo attacco</t>
+          <t>Dp/d ≥ 40</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. I 1.3 (Direttiva 2014/33/UE, All. I); UNI EN 81-20:2020, 5.5</t>
+          <t>UNI EN 81-20:2020, 5.5.2.1; UNI 10411-1:2024, 14.3</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 consolidato (Normattiva), letto il 2026-10-02, e Direttiva 2014/33/UE nel testo ufficiale italiano (EUR-Lex, fornito dal cliente), letto il 2026-10-04 (ricerca, cap. 16): All. I 1.3</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 74; UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 14</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>numero e diametro delle funi</t>
+          <t>Dp/d dei rinvii</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
@@ -1771,7 +1771,7 @@
       <c r="M21" s="11" t="n"/>
       <c r="N21" s="11" t="n"/>
     </row>
-    <row r="22" ht="43" customHeight="1">
+    <row r="22" ht="95" customHeight="1">
       <c r="A22" s="10" t="n">
         <v>20</v>
       </c>
@@ -1782,22 +1782,22 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Diametro nominale minimo</t>
+          <t>Numero minimo di funi — Con 2 sole funi serve anche il dispositivo contro l'allungamento anomalo (voce funi.due): il software lo ricorda, non lo verifica.</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>d ≥ 8 mm</t>
+          <t>almeno 2 funi indipendenti, ciascuna con il suo attacco</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.5.1.2 a)</t>
+          <t>DPR 162/1999, All. I 1.3 (Direttiva 2014/33/UE, All. I); UNI EN 81-20:2020, 5.5</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 74</t>
+          <t>DPR 162/1999 consolidato (Normattiva), letto il 2026-10-02, e Direttiva 2014/33/UE nel testo ufficiale italiano (EUR-Lex, fornito dal cliente), letto il 2026-10-04 (ricerca, cap. 16): All. I 1.3</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -1817,7 +1817,7 @@
       <c r="M22" s="11" t="n"/>
       <c r="N22" s="11" t="n"/>
     </row>
-    <row r="23" ht="108" customHeight="1">
+    <row r="23" ht="69" customHeight="1">
       <c r="A23" s="10" t="n">
         <v>21</v>
       </c>
@@ -1828,22 +1828,22 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Coefficiente di sicurezza minimo — Con la trazione vale anche il valore calcolato secondo la UNI EN 81-50:2020, 5.12 (il maggiore dei due). Con la UNI 10411-1:2024 (14.1) 12 e 16 possono sostituire quel calcolo solo con la verifica della pressione nelle gole (appendice D.2).</t>
+          <t>Cabina appesa a due funi</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>12 con tre o più funi; 16 con due funi</t>
+          <t>con 2 funi un dispositivo elettrico di sicurezza (5.11.2) ferma la macchina se una fune si allunga in modo anomalo rispetto all'altra (informazione)</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.5.2.2 a)–b); UNI 10411-1:2024, 14.1 c)–d)</t>
+          <t>UNI EN 81-20:2020, 5.5.5.3 a); UNI EN 81-1:2008, 9.5.3</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 74–75; UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 13</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 76; UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 56</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>coefficiente di sicurezza delle funi</t>
+          <t>cabina appesa a due funi</t>
         </is>
       </c>
       <c r="I23" s="11" t="n"/>
@@ -1863,7 +1863,7 @@
       <c r="M23" s="11" t="n"/>
       <c r="N23" s="11" t="n"/>
     </row>
-    <row r="24" ht="69" customHeight="1">
+    <row r="24" ht="82" customHeight="1">
       <c r="A24" s="10" t="n">
         <v>22</v>
       </c>
@@ -1874,22 +1874,22 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Coefficiente di sicurezza richiesto S_f</t>
+          <t>Funi trattenute nelle gole</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>S_f = 10^[2,6834 − log10(695,85·10^6·N_equiv/(D/d)^8,567) / log10(77,09·(D/d)^−2,894)]</t>
+          <t>un fermo dove le funi entrano ed escono dalla puleggia e almeno uno intermedio se più di 60° dell'arco di avvolgimento sono sotto l'orizzontale per l'asse e l'avvolgimento supera 120°: con la macchina in basso le funi avvolgono la puleggia da sotto (informazione)</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12.3 (ex UNI EN 81-1:2008, appendice N)</t>
+          <t>UNI EN 81-20:2020, 5.5.7.2</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 46; riprodotto anche su due casi pubblicati (liftdesign.it S_f 16,69; Mellor)</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 77–78</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>coefficiente di sicurezza delle funi</t>
+          <t>funi trattenute nelle gole</t>
         </is>
       </c>
       <c r="I24" s="11" t="n"/>
@@ -1909,7 +1909,7 @@
       <c r="M24" s="11" t="n"/>
       <c r="N24" s="11" t="n"/>
     </row>
-    <row r="25" ht="108" customHeight="1">
+    <row r="25" ht="43" customHeight="1">
       <c r="A25" s="10" t="n">
         <v>23</v>
       </c>
@@ -1920,22 +1920,22 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>N_equiv delle pulegge — D: diametro della puleggia di trazione; Dp: media delle altre pulegge. La flessione è inversa solo tra due pulegge consecutive ad assi fissi, con i punti di contatto a meno di 200·d e i piani di flessione ruotati di oltre 120°: la classifica il progettista.</t>
+          <t>Diametro nominale minimo</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>N_equiv(p) = K_p·(N_ps + 4·N_pr), K_p = (D/Dp)^4</t>
+          <t>d ≥ 8 mm</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12.2.3</t>
+          <t>UNI EN 81-20:2020, 5.5.1.2 a)</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 46</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 74</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>coefficiente di sicurezza delle funi</t>
+          <t>numero e diametro delle funi</t>
         </is>
       </c>
       <c r="I25" s="11" t="n"/>
@@ -1955,7 +1955,7 @@
       <c r="M25" s="11" t="n"/>
       <c r="N25" s="11" t="n"/>
     </row>
-    <row r="26" ht="82" customHeight="1">
+    <row r="26" ht="108" customHeight="1">
       <c r="A26" s="10" t="n">
         <v>24</v>
       </c>
@@ -1966,22 +1966,22 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>N_equiv(t) della gola — Il prospetto non ha una riga per la gola a V con sottosquadro: il software prende il maggiore tra il valore di β (riga a U) e quello di γ (riga a V), dal lato della sicurezza.</t>
+          <t>Coefficiente di sicurezza minimo — Con la trazione vale anche il valore calcolato secondo la UNI EN 81-50:2020, 5.12 (il maggiore dei due). Con la UNI 10411-1:2024 (14.1) 12 e 16 possono sostituire quel calcolo solo con la verifica della pressione nelle gole (appendice D.2).</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>U senza sottosquadro 1 · U con sottosquadro: β 75° 2,5; 80° 3,0; 85° 3,8; 90° 5,0; 95° 6,7; 100° 10,0; 105° 15,2 · V: γ 35° 18,5; 36° 16,0; 38° 12,0; 40° 10,0; 42° 8,0; 45° 6,5; 50° 5,0</t>
+          <t>12 con tre o più funi; 16 con due funi</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12.2.2, prospetto 2</t>
+          <t>UNI EN 81-20:2020, 5.5.2.2 a)–b); UNI 10411-1:2024, 14.1 c)–d)</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 46 (i valori della gola a V differiscono da quelli della UNI EN 81-1:2008, prospetto N.1)</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 74–75; UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 13</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -2001,7 +2001,7 @@
       <c r="M26" s="11" t="n"/>
       <c r="N26" s="11" t="n"/>
     </row>
-    <row r="27" ht="43" customHeight="1">
+    <row r="27" ht="69" customHeight="1">
       <c r="A27" s="10" t="n">
         <v>25</v>
       </c>
@@ -2012,22 +2012,22 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Angoli tra i punti della tabella di N_equiv(t)</t>
+          <t>Coefficiente di sicurezza richiesto S_f</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>interpolazione lineare tra i due punti vicini</t>
+          <t>S_f = 10^[2,6834 − log10(695,85·10^6·N_equiv/(D/d)^8,567) / log10(77,09·(D/d)^−2,894)]</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12.2.2</t>
+          <t>UNI EN 81-50:2020, 5.12.3 (ex UNI EN 81-1:2008, appendice N)</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 46</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 46; riprodotto anche su due casi pubblicati (liftdesign.it S_f 16,69; Mellor)</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -2047,7 +2047,7 @@
       <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
     </row>
-    <row r="28" ht="82" customHeight="1">
+    <row r="28" ht="108" customHeight="1">
       <c r="A28" s="10" t="n">
         <v>26</v>
       </c>
@@ -2058,27 +2058,27 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Angoli fuori dalla tabella di N_equiv(t)</t>
+          <t>N_equiv delle pulegge — D: diametro della puleggia di trazione; Dp: media delle altre pulegge. La flessione è inversa solo tra due pulegge consecutive ad assi fissi, con i punti di contatto a meno di 200·d e i piani di flessione ruotati di oltre 120°: la classifica il progettista.</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>U: sotto 75° il valore di 75°, oltre 105° estrapolazione dall'ultimo tratto, segnalata · V: oltre 50° il valore di 50°</t>
+          <t>N_equiv(p) = K_p·(N_ps + 4·N_pr), K_p = (D/Dp)^4</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12.2.2</t>
+          <t>UNI EN 81-50:2020, 5.12.2.3</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>scelta prudente del software (la tabella si ferma a quegli angoli; N_equiv cresce con β e cala con γ, quindi il valore dell'estremo sta dal lato della sicurezza)</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 46</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
@@ -2093,7 +2093,7 @@
       <c r="M28" s="11" t="n"/>
       <c r="N28" s="11" t="n"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="69" customHeight="1">
       <c r="A29" s="10" t="n">
         <v>27</v>
       </c>
@@ -2104,22 +2104,22 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Tiro massimo per fune — Con la macchina in basso il tiro sul primo tratto verso la testata è una derivazione del software.</t>
+          <t>N_equiv(t) della gola</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>cabina con portata ferma al piano più basso; con la macchina in basso sul primo tratto verso la testata</t>
+          <t>U senza sottosquadro 1 · U con sottosquadro: β 75° 2,5; 80° 3,0; 85° 3,8; 90° 5,0; 95° 6,7; 100° 10,0; 105° 15,2 · V: γ 35° 18,5; 36° 16,0; 38° 12,0; 40° 10,0; 42° 8,0; 45° 6,5; 50° 5,0</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.5.2.2 (definizione); UNI EN 81-50:2020, 5.12.1</t>
+          <t>UNI EN 81-50:2020, 5.12.2.2, prospetto 2</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 74–75</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 46 (i valori della gola a V differiscono da quelli della UNI EN 81-1:2008, prospetto N.1)</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
@@ -2139,7 +2139,7 @@
       <c r="M29" s="11" t="n"/>
       <c r="N29" s="11" t="n"/>
     </row>
-    <row r="30" ht="43" customHeight="1">
+    <row r="30" ht="95" customHeight="1">
       <c r="A30" s="10" t="n">
         <v>28</v>
       </c>
@@ -2150,32 +2150,32 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Stima di carico di rottura e massa delle funi</t>
+          <t>N_equiv(t) della gola a V con sottosquadro — Scelta dal lato della sicurezza; la UNI EN 81-1:2008 (prospetto N.1) intitola la riga con sottosquadro «U/V»: con una macchina secondo quella norma l'ingegnere può prendere il valore di β.</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>8×19 Seale anima tessile 1570 N/mm²: 8 mm = 30,4 kN e 0,215 kg/m, poi in proporzione a d²</t>
+          <t>il maggiore tra il valore per β (riga a U con sottosquadro) e quello per γ (riga a V)</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.12.2.2, prospetto 2</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>tabella Pfeifer 8×19S NFC; usata solo con il pulsante di stima e nella proposta libera</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 46 (il prospetto non ha una riga per questa gola)</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>coefficiente di sicurezza delle funi</t>
         </is>
       </c>
       <c r="I30" s="11" t="n"/>
@@ -2185,33 +2185,33 @@
       <c r="M30" s="11" t="n"/>
       <c r="N30" s="11" t="n"/>
     </row>
-    <row r="31" ht="69" customHeight="1">
+    <row r="31" ht="43" customHeight="1">
       <c r="A31" s="10" t="n">
         <v>29</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Freno</t>
+          <t>Funi</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Gruppi meccanici del freno</t>
+          <t>Angoli tra i punti della tabella di N_equiv(t)</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>almeno 2</t>
+          <t>interpolazione lineare tra i due punti vicini</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.9.2.2.2.1; UNI 10411-1:2024, 14.1 a)</t>
+          <t>UNI EN 81-50:2020, 5.12.2.2</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 100; UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 13</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 46</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>gruppi del freno</t>
+          <t>coefficiente di sicurezza delle funi</t>
         </is>
       </c>
       <c r="I31" s="11" t="n"/>
@@ -2231,43 +2231,43 @@
       <c r="M31" s="11" t="n"/>
       <c r="N31" s="11" t="n"/>
     </row>
-    <row r="32" ht="43" customHeight="1">
+    <row r="32" ht="82" customHeight="1">
       <c r="A32" s="10" t="n">
         <v>30</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Freno</t>
+          <t>Funi</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Freno, tutti i gruppi</t>
+          <t>Angoli fuori dalla tabella di N_equiv(t)</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>arresta la cabina in discesa a velocità nominale con 1,25·Q</t>
+          <t>U: sotto 75° il valore di 75°, oltre 105° estrapolazione dall'ultimo tratto, segnalata · V: oltre 50° il valore di 50°</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.9.2.2.2.1</t>
+          <t>UNI EN 81-50:2020, 5.12.2.2</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 100</t>
+          <t>scelta prudente del software (la tabella si ferma a quegli angoli; N_equiv cresce con β e cala con γ, quindi il valore dell'estremo sta dal lato della sicurezza)</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>freno, tutti i gruppi</t>
+          <t>coefficiente di sicurezza delle funi</t>
         </is>
       </c>
       <c r="I32" s="11" t="n"/>
@@ -2277,33 +2277,33 @@
       <c r="M32" s="11" t="n"/>
       <c r="N32" s="11" t="n"/>
     </row>
-    <row r="33" ht="95" customHeight="1">
+    <row r="33" ht="56" customHeight="1">
       <c r="A33" s="10" t="n">
         <v>31</v>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Freno</t>
+          <t>Funi</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Freno, un solo gruppo — La UNI 10411-1:2024 (11.1.4) e la UNI EN 81-1:2008 (12.4.2.1) chiedono a un solo gruppo di rallentare la cabina carica in discesa; il software applica la richiesta più completa della UNI EN 81-20.</t>
+          <t>Tiro massimo per fune — Con la macchina in basso il tiro sul primo tratto verso la testata è una derivazione del software.</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>rallenta, arresta e tiene la cabina con portata in discesa e la cabina vuota in salita</t>
+          <t>cabina con portata ferma al piano più basso; con la macchina in basso sul primo tratto verso la testata</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.9.2.2.2.1; UNI 10411-1:2024, 14.1 a)</t>
+          <t>UNI EN 81-20:2020, 5.5.2.2 (definizione); UNI EN 81-50:2020, 5.12.1</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 100; UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 13</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 74–75</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>freno, un gruppo in discesa; freno, un gruppo a vuoto in salita</t>
+          <t>coefficiente di sicurezza delle funi</t>
         </is>
       </c>
       <c r="I33" s="11" t="n"/>
@@ -2329,17 +2329,17 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Freno</t>
+          <t>Funi</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Attrito del riduttore nel fabbisogno del freno</t>
+          <t>Stima di carico di rottura e massa delle funi</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>non conteggiato (η_i = 1): a favore di sicurezza</t>
+          <t>8×19 Seale anima tessile 1570 N/mm²: 8 mm = 30,4 kN e 0,215 kg/m, poi in proporzione a d²</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -2349,17 +2349,17 @@
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>scelta prudente del software</t>
+          <t>tabella Pfeifer 8×19S NFC; usata solo con il pulsante di stima e nella proposta libera</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>freno, tutti i gruppi; freno, un gruppo in discesa; freno, un gruppo a vuoto in salita</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I34" s="11" t="n"/>
@@ -2369,7 +2369,7 @@
       <c r="M34" s="11" t="n"/>
       <c r="N34" s="11" t="n"/>
     </row>
-    <row r="35" ht="108" customHeight="1">
+    <row r="35" ht="69" customHeight="1">
       <c r="A35" s="10" t="n">
         <v>33</v>
       </c>
@@ -2380,32 +2380,32 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Decelerazione massima del freno — La norma non dà un numero per il freno: ne confronta la decelerazione media con quella del paracadute e dell'urto sugli ammortizzatori, che hanno 1 gn come limite. Il confronto vero è con i dati dei componenti montati.</t>
+          <t>Gruppi meccanici del freno</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>≤ 1 g (oltre: «Attenzione»), da confrontare con paracadute e ammortizzatori</t>
+          <t>almeno 2</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.9.2.2.2.1 (non oltre il paracadute o l'urto sugli ammortizzatori); 1 gn in 5.6.2.1.3 e 5.8.2; con il freno come organo d'arresto, 1 gn anche in 5.6.6.3 (ACOP) e 5.6.7.6 (UCM)</t>
+          <t>UNI EN 81-20:2020, 5.9.2.2.2.1; UNI 10411-1:2024, 14.1 a)</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 81, 98–100</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 100; UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 13</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>decelerazione massima del freno</t>
+          <t>gruppi del freno</t>
         </is>
       </c>
       <c r="I35" s="11" t="n"/>
@@ -2415,43 +2415,43 @@
       <c r="M35" s="11" t="n"/>
       <c r="N35" s="11" t="n"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="43" customHeight="1">
       <c r="A36" s="10" t="n">
         <v>34</v>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Riduttore e motore</t>
+          <t>Freno</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Rendimento inverso del riduttore se non dato — Da sostituire con il valore del costruttore: la decelerazione reale del freno ne dipende molto.</t>
+          <t>Freno, tutti i gruppi</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>η_i ≈ 2 − 1/η_d (0 = irreversibile)</t>
+          <t>arresta la cabina in discesa a velocità nominale con 1,25·Q</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.9.2.2.2.1</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>approssimazione della teoria della vite senza fine</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 100</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>aderenza alla decelerazione reale (avviso); decelerazione massima del freno</t>
+          <t>freno, tutti i gruppi</t>
         </is>
       </c>
       <c r="I36" s="11" t="n"/>
@@ -2461,43 +2461,43 @@
       <c r="M36" s="11" t="n"/>
       <c r="N36" s="11" t="n"/>
     </row>
-    <row r="37" ht="43" customHeight="1">
+    <row r="37" ht="95" customHeight="1">
       <c r="A37" s="10" t="n">
         <v>35</v>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Riduttore e motore</t>
+          <t>Freno</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Coppia di accelerazione</t>
+          <t>Freno, un solo gruppo — La UNI 10411-1:2024 (11.1.4) e la UNI EN 81-1:2008 (12.4.2.1) chiedono a un solo gruppo di rallentare la cabina carica in discesa; il software applica la richiesta più completa della UNI EN 81-20.</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>≤ 2 volte la coppia nominale (oltre: «Attenzione»; nella proposta: criterio di scelta del motore)</t>
+          <t>rallenta, arresta e tiene la cabina con portata in discesa e la cabina vuota in salita</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.9.2.2.2.1; UNI 10411-1:2024, 14.1 a)</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>scelta del software; il limite vero è quello di motore e inverter</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 100; UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 13</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>coppia di accelerazione</t>
+          <t>freno, un gruppo in discesa; freno, un gruppo a vuoto in salita</t>
         </is>
       </c>
       <c r="I37" s="11" t="n"/>
@@ -2507,23 +2507,23 @@
       <c r="M37" s="11" t="n"/>
       <c r="N37" s="11" t="n"/>
     </row>
-    <row r="38" ht="30" customHeight="1">
+    <row r="38" ht="43" customHeight="1">
       <c r="A38" s="10" t="n">
         <v>36</v>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Riduttore e motore</t>
+          <t>Freno</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Soglia di attenzione sui limiti del costruttore</t>
+          <t>Attrito del riduttore nel fabbisogno del freno</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>oltre il 98% del limite di catalogo (albero, coppia in uscita) → «Attenzione»</t>
+          <t>non conteggiato (η_i = 1): a favore di sicurezza</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
@@ -2533,17 +2533,17 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
+          <t>scelta prudente del software</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
           <t>scelta del software</t>
         </is>
       </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>scelta del software</t>
-        </is>
-      </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>carico sull'albero; coppia in uscita</t>
+          <t>freno, tutti i gruppi; freno, un gruppo in discesa; freno, un gruppo a vuoto in salita</t>
         </is>
       </c>
       <c r="I38" s="11" t="n"/>
@@ -2553,43 +2553,43 @@
       <c r="M38" s="11" t="n"/>
       <c r="N38" s="11" t="n"/>
     </row>
-    <row r="39" ht="43" customHeight="1">
+    <row r="39" ht="108" customHeight="1">
       <c r="A39" s="10" t="n">
         <v>37</v>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Riduttore e motore</t>
+          <t>Freno</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Potenza statica del motore</t>
+          <t>Decelerazione massima del freno — La norma non dà un numero per il freno: ne confronta la decelerazione media con quella del paracadute e dell'urto sugli ammortizzatori, che hanno 1 gn come limite. Il confronto vero è con i dati dei componenti montati.</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>P_st = ΔF·v_f / (η_d·η_vano) ≤ P_n, con ΔF il maggiore tra cabina carica in salita dal basso e vuota in discesa dall'alto</t>
+          <t>≤ 1 g (oltre: «Attenzione»), da confrontare con paracadute e ammortizzatori</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.9.2.2.2.1 (non oltre il paracadute o l'urto sugli ammortizzatori); 1 gn in 5.6.2.1.3 e 5.8.2; con il freno come organo d'arresto, 1 gn anche in 5.6.6.3 (ACOP) e 5.6.7.6 (UCM)</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 81, 98–100</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
           <t>derivazione</t>
         </is>
       </c>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>derivazione</t>
-        </is>
-      </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>potenza del motore</t>
+          <t>decelerazione massima del freno</t>
         </is>
       </c>
       <c r="I39" s="11" t="n"/>
@@ -2599,7 +2599,7 @@
       <c r="M39" s="11" t="n"/>
       <c r="N39" s="11" t="n"/>
     </row>
-    <row r="40" ht="30" customHeight="1">
+    <row r="40" ht="56" customHeight="1">
       <c r="A40" s="10" t="n">
         <v>38</v>
       </c>
@@ -2610,32 +2610,32 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Coppia massima in uscita dal riduttore</t>
+          <t>Rendimento inverso del riduttore se non dato — Da sostituire con il valore del costruttore: la decelerazione reale del freno ne dipende molto.</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>M_p = ΔF·D/2 + J·i·α_m, confrontata con il valore di catalogo se inserito</t>
+          <t>η_i ≈ 2 − 1/η_d (0 = irreversibile)</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>dato del costruttore</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>approssimazione della teoria della vite senza fine</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>coppia in uscita</t>
+          <t>aderenza alla decelerazione reale (avviso); decelerazione massima del freno</t>
         </is>
       </c>
       <c r="I40" s="11" t="n"/>
@@ -2645,7 +2645,7 @@
       <c r="M40" s="11" t="n"/>
       <c r="N40" s="11" t="n"/>
     </row>
-    <row r="41" ht="147" customHeight="1">
+    <row r="41" ht="43" customHeight="1">
       <c r="A41" s="10" t="n">
         <v>39</v>
       </c>
@@ -2656,32 +2656,32 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Tolleranza tra velocità reale e nominale — Con la UNI 10411-1:2024 (15.1) una velocità oltre il 5 % sopra la maggiore tra quella del libretto e quella dopo il passaggio a 50 Hz è un aumento della velocità nominale (punti 15.2–15.15). Con la UNI 10411-11:2024 (15) ogni cambio della velocità nominale, in più o in meno, porta ai punti 15 a)–k) e alla valutazione 4.3.</t>
+          <t>Coppia di accelerazione</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>con metà portata a metà corsa, in salita e in discesa, non oltre il 5 % sopra la nominale (buona pratica: non oltre l'8 % sotto); non verificata: il software mostra la velocità reale e la frequenza per la nominale</t>
+          <t>≤ 2 volte la coppia nominale (oltre: «Attenzione»; nella proposta: criterio di scelta del motore)</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.9.2.4; UNI 10411-1:2024, 15.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 102; UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 14</t>
+          <t>scelta del software; il limite vero è quello di motore e inverter</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>coppia di accelerazione</t>
         </is>
       </c>
       <c r="I41" s="11" t="n"/>
@@ -2691,43 +2691,43 @@
       <c r="M41" s="11" t="n"/>
       <c r="N41" s="11" t="n"/>
     </row>
-    <row r="42" ht="69" customHeight="1">
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="10" t="n">
         <v>40</v>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Manovra di emergenza</t>
+          <t>Riduttore e motore</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Forza massima al volantino — Il software verifica i 400 N; i 150 N del mezzo meccanico (5.9.2.3.1 a)) non sono verificati: sono nella lista da verificare.</t>
+          <t>Soglia di attenzione sui limiti del costruttore</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>≤ 400 N per far salire la cabina con la portata, altrimenti manovra elettrica di emergenza; il mezzo meccanico è ammesso se per portare la cabina a una fermata bastano 150 N</t>
+          <t>oltre il 98% del limite di catalogo (albero, coppia in uscita) → «Attenzione»</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.9.2.3.3 (400 N) e 5.9.2.3.1 a) (150 N)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 101–102</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>forza al volantino</t>
+          <t>carico sull'albero; coppia in uscita</t>
         </is>
       </c>
       <c r="I42" s="11" t="n"/>
@@ -2737,33 +2737,33 @@
       <c r="M42" s="11" t="n"/>
       <c r="N42" s="11" t="n"/>
     </row>
-    <row r="43" ht="56" customHeight="1">
+    <row r="43" ht="43" customHeight="1">
       <c r="A43" s="10" t="n">
         <v>41</v>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Albero e ancoraggi</t>
+          <t>Riduttore e motore</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Carico sull'albero della puleggia</t>
+          <t>Potenza statica del motore</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>risultante dei tiri con 1,25·Q al piano più basso, confrontata con il limite del costruttore</t>
+          <t>P_st = ΔF·v_f / (η_d·η_vano) ≤ P_n, con ΔF il maggiore tra cabina carica in salita dal basso e vuota in discesa dall'alto</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>dato del costruttore; 1,25·Q come nella verifica di caricamento (UNI EN 81-50:2020, 5.11.2.2.1)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>derivazione; la definizione del carico va confermata con il costruttore</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>carico sull'albero</t>
+          <t>potenza del motore</t>
         </is>
       </c>
       <c r="I43" s="11" t="n"/>
@@ -2789,22 +2789,22 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Albero e ancoraggi</t>
+          <t>Riduttore e motore</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Sollevamento netto sugli ancoraggi (macchina in basso)</t>
+          <t>Coppia massima in uscita dal riduttore</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>carico verso l'alto meno la massa della macchina: da verificare con il progettista strutturale</t>
+          <t>M_p = ΔF·D/2 + J·i·α_m, confrontata con il valore di catalogo se inserito</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>dato del costruttore</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>sollevamento netto</t>
+          <t>coppia in uscita</t>
         </is>
       </c>
       <c r="I44" s="11" t="n"/>
@@ -2829,33 +2829,33 @@
       <c r="M44" s="11" t="n"/>
       <c r="N44" s="11" t="n"/>
     </row>
-    <row r="45" ht="69" customHeight="1">
+    <row r="45" ht="147" customHeight="1">
       <c r="A45" s="10" t="n">
         <v>43</v>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Sostituzione (Italia)</t>
+          <t>Riduttore e motore</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>La sostituzione del macchinario è una modifica costruttiva</t>
+          <t>Tolleranza tra velocità reale e nominale — Con la UNI 10411-1:2024 (15.1) una velocità oltre il 5 % sopra la maggiore tra quella del libretto e quella dopo il passaggio a 50 Hz è un aumento della velocità nominale (punti 15.2–15.15). Con la UNI 10411-11:2024 (15) ogni cambio della velocità nominale, in più o in meno, porta ai punti 15 a)–k) e alla valutazione 4.3.</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>modifica costruttiva (art. 2 c.1 lett. cc), n. 5): adeguamento della parte sostituita e delle altre parti interessate, comunicazione al Comune e al soggetto delle verifiche periodiche, verifica straordinaria prima del servizio</t>
+          <t>con metà portata a metà corsa, in salita e in discesa, non oltre il 5 % sopra la nominale (buona pratica: non oltre l'8 % sotto); non verificata: il software mostra la velocità reale e la frequenza per la nominale</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., art. 2 c.1 lett. cc), art. 12 c.4–5, art. 14 c.3</t>
+          <t>UNI EN 81-20:2020, 5.9.2.4; UNI 10411-1:2024, 15.1</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 consolidato (Normattiva), letto il 2026-10-02 (ricerca, cap. 16), §3.2</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 102; UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 14</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
@@ -2875,33 +2875,33 @@
       <c r="M45" s="11" t="n"/>
       <c r="N45" s="11" t="n"/>
     </row>
-    <row r="46" ht="225" customHeight="1">
+    <row r="46" ht="82" customHeight="1">
       <c r="A46" s="10" t="n">
         <v>44</v>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Sostituzione (Italia)</t>
+          <t>Manovra di emergenza</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Adeguamenti richiesti per la sostituzione del macchinario</t>
+          <t>Forza al volantino per far salire la cabina con la portata — La forza è quella per far salire la cabina con la portata dal piano più basso, con i rendimenti del riduttore (in avanti) e del vano.</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, punto 14: macchina secondo la UNI EN 81-20 (5.9.1 e 5.9.2, freno in due gruppi) o la UNI EN 81-1:2010, con aderenza e coefficiente di sicurezza delle funi (14.1); D/d ≥ 40 (14.3); temporizzatore della UNI EN 81-20 (5.9.2.7), arresto prima che la cabina in salita tocchi la velocità di intervento del limitatore, ACOP e UCM esistenti che funzionano ancora, arresto vicino alla macchina, pulegge secondo la 5.5.7, interruzione se il freno non si apre (14.4 a)–g)). UNI 10411-11:2024, punto 14: macchina come l'originale, altrimenti UNI EN 81-20 5.9.1–5.9.2 con le verifiche della norma di origine o della UNI EN 81-20 e la valutazione 4.3 (14.1); UCM esistenti che funzionano ancora e, senza UCM conforme alla 5.6.7 e con il rallentamento controllato, interruzione se il freno non si apre (14.3)</t>
+          <t>≤ 400 N, altrimenti manovra elettrica di emergenza: secondo la UNI EN 81-20:2020 quella della 5.12.1.6 (al massimo 0,30 m/s); secondo la UNI EN 81-1:2008 quella della 14.2.1.4 (al massimo 0,63 m/s)</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, 14.1–14.4; UNI 10411-11:2024, 14.1–14.3</t>
+          <t>UNI EN 81-20:2020, 5.9.2.3.3 e 5.12.1.6; UNI EN 81-1:2008, 12.5.1–12.5.2 e 14.2.1.4</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, testo della norma, letto il 2026-10-06, pp. 13–14; UNI 10411-11:2024, testo della norma, letto il 2026-10-06, p. 12</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 102 e 129; UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, pp. 69 e 89–90</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>gruppi del freno</t>
+          <t>forza al volantino</t>
         </is>
       </c>
       <c r="I46" s="11" t="n"/>
@@ -2921,43 +2921,43 @@
       <c r="M46" s="11" t="n"/>
       <c r="N46" s="11" t="n"/>
     </row>
-    <row r="47" ht="43" customHeight="1">
+    <row r="47" ht="121" customHeight="1">
       <c r="A47" s="10" t="n">
         <v>45</v>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Sostituzione (Italia)</t>
+          <t>Manovra di emergenza</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Funi nella sostituzione</t>
+          <t>Mezzo meccanico per la manovra di emergenza — Solo con la macchina secondo la UNI EN 81-20:2020: la UNI EN 81-1:2008 non ha la soglia dei 150 N né l'ora di autonomia. Il verso della forza non è dato dalla norma: il software prende il peggiore.</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>di norma funi nuove con lo stesso numero e diametro di quelle montate; la proposta le tiene fisse</t>
+          <t>ammesso se per portare la cabina a una fermata bastano 150 N con il carico tra (q − 0,1)·Q e (q + 0,1)·Q: il software prende la forza maggiore tra i due carichi, i due versi e le due posizioni estreme; oltre, mezzo elettrico (5.9.2.3.1 b)) con alimentazione indipendente dalla rete, che porta la cabina con qualsiasi carico alla fermata vicina entro 1 h, al massimo a 0,30 m/s, e manovra elettrica di emergenza (5.12.1.6)</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.9.2.2.2.9, 5.9.2.3.1 e 5.9.2.3.3</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>indicazione di Panev Ascensori (29 settembre 2026)</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 101–102</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>prassi di cantiere</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>forza al volantino fino a una fermata</t>
         </is>
       </c>
       <c r="I47" s="11" t="n"/>
@@ -2967,33 +2967,33 @@
       <c r="M47" s="11" t="n"/>
       <c r="N47" s="11" t="n"/>
     </row>
-    <row r="48" ht="43" customHeight="1">
+    <row r="48" ht="69" customHeight="1">
       <c r="A48" s="10" t="n">
         <v>46</v>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Modello di calcolo</t>
+          <t>Manovra di emergenza</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Accelerazione di gravità</t>
+          <t>Movimento per gravità con il freno aperto a mano — Il rendimento inverso η_i è quello inserito o la stima della voce azionamento.rendimento.inverso.</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>g = 9,81 m/s² (anche come limite di 1 g)</t>
+          <t>con il riduttore irreversibile (η_i = 0) la cabina non si muove aprendo il freno: servono i mezzi della 5.9.2.3 (informazione)</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.8.5 (g_n = 9,81 m/s²)</t>
+          <t>UNI EN 81-20:2020, 5.9.2.2.2.9</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 27</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 101</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>movimento per gravità</t>
         </is>
       </c>
       <c r="I48" s="11" t="n"/>
@@ -3013,43 +3013,43 @@
       <c r="M48" s="11" t="n"/>
       <c r="N48" s="11" t="n"/>
     </row>
-    <row r="49" ht="173" customHeight="1">
+    <row r="49" ht="56" customHeight="1">
       <c r="A49" s="10" t="n">
         <v>47</v>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Modello di calcolo</t>
+          <t>Albero e ancoraggi</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Tiri con il metodo del percorso della fune — Confermati sul testo: le masse per lato, il fattore (r² + 2)/3 delle funi, il termine delle pulegge di rinvio e l'attrito trascurato. Da verificare: in taglia 2:1 le pulegge di cabina e di contrappeso (termine III della norma) non sono contate; con la macchina in basso il tratto tra macchina e pulegge in testata usa r·a, dove il testo stampa a (la forma stampata coincide con quella fisica solo a 1:1).</t>
+          <t>Carico sull'albero della puleggia</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>masse e funi di ogni tratto, inerzia delle pulegge di rinvio; attrito di guide e pulegge trascurato in aderenza</t>
+          <t>risultante dei tiri con 1,25·Q al piano più basso, confrontata con il limite del costruttore</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.3</t>
+          <t>dato del costruttore; 1,25·Q come nella verifica di caricamento (UNI EN 81-50:2020, 5.11.2.2.1)</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 43–44</t>
+          <t>derivazione; la definizione del carico va confermata con il costruttore</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>aderenza al caricamento; aderenza in frenatura, in discesa; aderenza in frenatura, in salita; aderenza alla decelerazione reale (avviso); cabina bloccata</t>
+          <t>carico sull'albero</t>
         </is>
       </c>
       <c r="I49" s="11" t="n"/>
@@ -3059,43 +3059,43 @@
       <c r="M49" s="11" t="n"/>
       <c r="N49" s="11" t="n"/>
     </row>
-    <row r="50" ht="69" customHeight="1">
+    <row r="50" ht="30" customHeight="1">
       <c r="A50" s="10" t="n">
         <v>48</v>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Modello di calcolo</t>
+          <t>Albero e ancoraggi</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Compensazione e cavo flessibile — Nella 5.11.3 la massa della compensazione e del cavo dipende dalla posizione della cabina; il software la tiene costante dentro P.</t>
+          <t>Sollevamento netto sugli ancoraggi (macchina in basso)</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>non modellati a parte: la loro massa sul lato cabina entra in P</t>
+          <t>carico verso l'alto meno la massa della macchina: da verificare con il progettista strutturale</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>limite del modello attuale</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>sollevamento netto</t>
         </is>
       </c>
       <c r="I50" s="11" t="n"/>
@@ -3105,38 +3105,38 @@
       <c r="M50" s="11" t="n"/>
       <c r="N50" s="11" t="n"/>
     </row>
-    <row r="51" ht="30" customHeight="1">
+    <row r="51" ht="69" customHeight="1">
       <c r="A51" s="10" t="n">
         <v>49</v>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Modello di calcolo</t>
+          <t>Sostituzione (Italia)</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Analisi di sensibilità</t>
+          <t>La sostituzione del macchinario è una modifica costruttiva</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>P ±10%; k ±0,05 se il carico di equilibrio non è misurato</t>
+          <t>modifica costruttiva (art. 2 c.1 lett. cc), n. 5): adeguamento della parte sostituita e delle altre parti interessate, comunicazione al Comune e al soggetto delle verifiche periodiche, verifica straordinaria prima del servizio</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DPR 162/1999 e s.m.i., art. 2 c.1 lett. cc), art. 12 c.4–5, art. 14 c.3</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (incertezza tipica del rilievo)</t>
+          <t>DPR 162/1999 consolidato (Normattiva), letto il 2026-10-02 (ricerca, cap. 16), §3.2</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
@@ -3151,33 +3151,33 @@
       <c r="M51" s="11" t="n"/>
       <c r="N51" s="11" t="n"/>
     </row>
-    <row r="52" ht="134" customHeight="1">
+    <row r="52" ht="290" customHeight="1">
       <c r="A52" s="10" t="n">
         <v>50</v>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Vano: cabina e portata</t>
+          <t>Sostituzione (Italia)</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Superficie utile massima della cabina per portata — la norma misura la superficie a 1 m dal pavimento tra le pareti strutturali, senza finiture (5.4.2.1.2), conta le nicchie e conta per intero la rientranza dell'ingresso profonda più di 100 mm (5.4.2.1.3); il software usa larghezza × profondità interne: nicchie e rientranze vanno aggiunte a mano</t>
+          <t>Adeguamenti richiesti per la sostituzione del macchinario</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>100 kg 0,37 m²; 180 kg 0,58; 225 kg 0,70; 300 kg 0,90; 375 kg 1,10; 400 kg 1,17; 450 kg 1,30; 525 kg 1,45; 600 kg 1,60; 630 kg 1,66; 675 kg 1,75; 750 kg 1,90; 800 kg 2,00; 825 kg 2,05; 900 kg 2,20; 975 kg 2,35; 1000 kg 2,40; 1050 kg 2,50; 1125 kg 2,65; 1200 kg 2,80; 1250 kg 2,90; 1275 kg 2,95; 1350 kg 3,10; 1425 kg 3,25; 1500 kg 3,40; 1600 kg 3,56; 2000 kg 4,20; 2500 kg 5,00; oltre 2500 kg +0,16 m² ogni 100 kg; interpolazione lineare</t>
+          <t>UNI 10411-1:2024, punto 14: macchina secondo la UNI EN 81-20 (5.9.1 e 5.9.2, freno in due gruppi) o la UNI EN 81-1:2010, con aderenza e coefficiente di sicurezza delle funi (14.1); D/d ≥ 40 (14.3); temporizzatore della UNI EN 81-20 (5.9.2.7), arresto prima che la cabina in salita tocchi la velocità di intervento del limitatore, ACOP e UCM esistenti che funzionano ancora, arresto vicino alla macchina, pulegge secondo la 5.5.7, interruzione se il freno non si apre (14.4 a)–g)); valutazione della sicurezza su tre piani (4); con funi nuove, controllo degli attacchi d'estremità (17.1); documenti dell'appendice C (14) e manuali (25.5). UNI 10411-11:2024, punto 14: macchina come l'originale, altrimenti UNI EN 81-20 5.9.1–5.9.2 con le verifiche della norma di origine o della UNI EN 81-20 e la valutazione 4.3 (14.1); UCM esistenti che funzionano ancora e, senza UCM conforme alla 5.6.7 e con il rallentamento controllato, interruzione se il freno non si apre (14.3); funi nuove e attacchi come gli originali, altrimenti verificati con la valutazione 4.3 (17)</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.2.1.1 (Prospetto 6)</t>
+          <t>UNI 10411-1:2024, 4, 14.1–14.4, 17.1, 25.5, appendice C; UNI 10411-11:2024, 14.1–14.3, 17</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 63–64</t>
+          <t>UNI 10411-1:2024, testo della norma, letto il 2026-10-06, pp. 6, 13–14, 16, 21 e 30; UNI 10411-11:2024, testo della norma, letto il 2026-10-06, pp. 12 e 14</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>superficie della cabina per la portata</t>
+          <t>gruppi del freno</t>
         </is>
       </c>
       <c r="I52" s="11" t="n"/>
@@ -3197,38 +3197,38 @@
       <c r="M52" s="11" t="n"/>
       <c r="N52" s="11" t="n"/>
     </row>
-    <row r="53" ht="95" customHeight="1">
+    <row r="53" ht="43" customHeight="1">
       <c r="A53" s="10" t="n">
         <v>51</v>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Vano: cabina e portata</t>
+          <t>Sostituzione (Italia)</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Numero di passeggeri</t>
+          <t>Funi nella sostituzione</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>il minore tra Q/75 arrotondato per difetto e il numero ammesso dalla superficie: 1 persona 0,28 m²; 2 0,49; 3 0,60; 4 0,79; 5 0,98; 6 1,17; 7 1,31; 8 1,45; 9 1,59; 10 1,73; 11 1,87; 12 2,01; 13 2,15; 14 2,29; 15 2,43; 16 2,57; 17 2,71; 18 2,85; 19 2,99; 20 3,13; oltre 20 +0,115 m² per persona</t>
+          <t>di norma funi nuove con lo stesso numero e diametro di quelle montate; la proposta le tiene fisse</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.2.3.1 (Prospetto 8)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 66</t>
+          <t>indicazione di Panev Ascensori (29 settembre 2026)</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>prassi di cantiere</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
@@ -3243,33 +3243,33 @@
       <c r="M53" s="11" t="n"/>
       <c r="N53" s="11" t="n"/>
     </row>
-    <row r="54" ht="186" customHeight="1">
+    <row r="54" ht="43" customHeight="1">
       <c r="A54" s="10" t="n">
         <v>52</v>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Vano: distanze in pianta</t>
+          <t>Modello di calcolo</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Parete del vano di fronte all'entrata della cabina — le deroghe della norma (fino a 0,20 m per un tratto alto non più di 0,50 m o con porte verticali di ascensori per merci; nessun limite con la porta di cabina bloccata meccanicamente) non sono usate: la verifica è più severa. Il software misura fino alla soglia; la figura 3 della norma porta il limite anche al telaio e al bordo di chiusura delle ante di cabina: con la porta scelta lo verifica l'ingegnere sui dati del fornitore.</t>
+          <t>Accelerazione di gravità</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>distanza orizzontale dalla soglia o dal telaio della porta di cabina ≤ 150 mm (qui: profondità della porta di piano + gioco tra le soglie)</t>
+          <t>g = 9,81 m/s² (anche come limite di 1 g)</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.3.1</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8.5 (g_n = 9,81 m/s²)</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 33</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 27</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>parete di fronte all'entrata</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I54" s="11" t="n"/>
@@ -3289,33 +3289,33 @@
       <c r="M54" s="11" t="n"/>
       <c r="N54" s="11" t="n"/>
     </row>
-    <row r="55" ht="95" customHeight="1">
+    <row r="55" ht="69" customHeight="1">
       <c r="A55" s="10" t="n">
         <v>53</v>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Vano: distanze in pianta</t>
+          <t>Modello di calcolo</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Gioco tra soglia di cabina e soglia di piano — Non calcolato: tra il bordo d'attacco delle ante di cabina e le porte di piano al massimo 0,12 m (5.3.4.2; 11.2.3 nella UNI EN 81-1:2008), dato del fornitore delle porte.</t>
+          <t>Tiri con il metodo del percorso della fune — Il fattore (r² + 2)/3 vale esattamente r per le taglie 1:1 e 2:1, le sole del software.</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>distanza orizzontale ≤ 35 mm</t>
+          <t>masse per lato, funi di ogni tratto con il fattore (r² + 2)/3, inerzia delle pulegge di rinvio e, in taglia 2:1, delle pulegge di cabina e di contrappeso (termine III); attrito di guide e pulegge trascurato in aderenza</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.3.4.1 (figura 3); 11.2.2 nella UNI EN 81-1 (1999, 2008)</t>
+          <t>UNI EN 81-50:2020, 5.11.3</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 50</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 43–44</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>gioco tra le soglie</t>
+          <t>aderenza al caricamento; aderenza in frenatura, in discesa; aderenza in frenatura, in salita; aderenza alla decelerazione reale (avviso); cabina bloccata</t>
         </is>
       </c>
       <c r="I55" s="11" t="n"/>
@@ -3335,43 +3335,43 @@
       <c r="M55" s="11" t="n"/>
       <c r="N55" s="11" t="n"/>
     </row>
-    <row r="56" ht="69" customHeight="1">
+    <row r="56" ht="108" customHeight="1">
       <c r="A56" s="10" t="n">
         <v>54</v>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Vano: distanze in pianta</t>
+          <t>Modello di calcolo</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Distanza tra cabina e contrappeso — il software misura tra le sagome di cabina e contrappeso: pattini e staffe non sono nel modello della pianta</t>
+          <t>Pulegge di cabina e di contrappeso nella taglia 2:1 — La velocità della fune rispetto all'asse della puleggia di cabina è quella della cabina: la massa ridotta è J_p/R_p². Con più pulegge o pulegge diverse da quelle di rinvio, l'ingegnere inserisce l'inerzia equivalente.</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>≥ 50 mm tra la cabina con i suoi componenti e il contrappeso con i suoi</t>
+          <t>una puleggia per lato, con l'inerzia J_p e il diametro D_p delle pulegge di rinvio: massa ridotta J_p/R_p², con l'accelerazione della cabina divisa per r, nei tiri e nell'inerzia riportata al motore</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.5.1 h)</t>
+          <t>UNI EN 81-50:2020, 5.11.3 (termine III)</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 35</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 43–44; numero e inerzia delle pulegge: scelta del software</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>distanza cabina–contrappeso</t>
+          <t>aderenza in frenatura, in discesa; aderenza in frenatura, in salita; aderenza alla decelerazione reale (avviso)</t>
         </is>
       </c>
       <c r="I56" s="11" t="n"/>
@@ -3381,43 +3381,43 @@
       <c r="M56" s="11" t="n"/>
       <c r="N56" s="11" t="n"/>
     </row>
-    <row r="57" ht="199" customHeight="1">
+    <row r="57" ht="69" customHeight="1">
       <c r="A57" s="10" t="n">
         <v>55</v>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Vano: distanze in pianta</t>
+          <t>Modello di calcolo</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Pareti all'ultimo piano e in testata diverse dal piano principale</t>
+          <t>Macchina in basso: tratto tra la macchina e le pulegge in testata — Il testo stampa a in entrambe le edizioni; a 1:1 le due forme coincidono.</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>negli edifici esistenti le pareti del vano all'ultima fermata e in testata possono stare altrove che al piano principale: cabina, guide e contrappeso restano a piombo; la cabina con soglie e operatori delle porte e il contrappeso passano ad almeno 25 mm dalle pareti spostate (meno: «Attenzione»; dentro la parete: «Non conforme»); le porte di piano dell'ultima fermata restano in linea con la cabina e la parete non entra nel loro spessore, i piedi delle guide e la staffa a ponte non entrano nelle pareti; le staffe arrivano alla parete dove sta (le staffe Panev si verificano anche lì); la distanza dalla parete di fronte all'entrata (voce distanze.parete.entrata) vale anche in testata</t>
+          <t>con l'accelerazione a della cabina, come stampato nella norma; nella taglia 2:1 il software mostra anche l'esito con r·a, l'accelerazione fisica di quel tratto: «Attenzione» se supera il limite, mai KO</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.3.1 (parete di fronte all'entrata); il resto scelta del software</t>
+          <t>UNI EN 81-50:2020, 5.11.3 (MSR1)</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>scelta del software: il margine di marcia va confermato con l'installatore</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 44</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>pareti in testata diverse dal piano principale</t>
+          <t>aderenza in frenatura, in discesa; aderenza in frenatura, in salita; tratto macchina–testata a r·a (avviso)</t>
         </is>
       </c>
       <c r="I57" s="11" t="n"/>
@@ -3427,33 +3427,33 @@
       <c r="M57" s="11" t="n"/>
       <c r="N57" s="11" t="n"/>
     </row>
-    <row r="58" ht="56" customHeight="1">
+    <row r="58" ht="69" customHeight="1">
       <c r="A58" s="10" t="n">
         <v>56</v>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Vano: accessibilità (DM 236/1989)</t>
+          <t>Modello di calcolo</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Edifici residenziali nuovi: cabina e porta minime</t>
+          <t>Velocità nominale e compensazione</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>cabina larga 950 mm e profonda 1300 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (fuori dal vano: da verificare in sito)</t>
+          <t>oltre 1,75 m/s i mezzi di compensazione senza tensionamento vanno guidati vicino all'ansa («Attenzione»); oltre 3 m/s servono funi di compensazione con puleggia tenditrice, che il modello non contiene (KO: fuori dal campo del software)</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-20:2020, 5.5.6.1 a)–d)</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12, letto per intero su Normattiva il 2026-10-02 (ricerca, cap. 16, §4.1)</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 76</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>velocità e compensazione</t>
         </is>
       </c>
       <c r="I58" s="11" t="n"/>
@@ -3473,43 +3473,43 @@
       <c r="M58" s="11" t="n"/>
       <c r="N58" s="11" t="n"/>
     </row>
-    <row r="59" ht="56" customHeight="1">
+    <row r="59" ht="121" customHeight="1">
       <c r="A59" s="10" t="n">
         <v>57</v>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Vano: accessibilità (DM 236/1989)</t>
+          <t>Modello di calcolo</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Edifici non residenziali nuovi: cabina e porta minime</t>
+          <t>Compensazione e cavo flessibile — Nella 5.11.3 la massa della compensazione (0,5·H ± y) e del cavo (0,25·H ± 0,5·y) dipende dalla posizione della cabina e c'è anche sul lato del contrappeso; il software la tiene costante dentro P. Con catene o funi di compensazione il modello non vale.</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>cabina larga 1100 mm e profonda 1400 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (fuori dal vano: da verificare in sito)</t>
+          <t>non modellati a parte: la loro massa sul lato cabina entra in P</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-50:2020, 5.11.3</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12, letto per intero su Normattiva il 2026-10-02 (ricerca, cap. 16, §4.1)</t>
+          <t>limite del modello attuale</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I59" s="11" t="n"/>
@@ -3519,43 +3519,43 @@
       <c r="M59" s="11" t="n"/>
       <c r="N59" s="11" t="n"/>
     </row>
-    <row r="60" ht="56" customHeight="1">
+    <row r="60" ht="30" customHeight="1">
       <c r="A60" s="10" t="n">
         <v>58</v>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Vano: accessibilità (DM 236/1989)</t>
+          <t>Modello di calcolo</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Adeguamento di edifici esistenti: cabina e porta minime</t>
+          <t>Analisi di sensibilità</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>cabina larga 800 mm e profonda 1200 mm, porta di 750 mm sul lato corto; piattaforma davanti alla porta 1,40 × 1,40 m (fuori dal vano: da verificare in sito)</t>
+          <t>P ±10%; k ±0,05 se il carico di equilibrio non è misurato</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12, letto per intero su Normattiva il 2026-10-02 (ricerca, cap. 16, §4.1)</t>
+          <t>scelta del software (incertezza tipica del rilievo)</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I60" s="11" t="n"/>
@@ -3565,43 +3565,43 @@
       <c r="M60" s="11" t="n"/>
       <c r="N60" s="11" t="n"/>
     </row>
-    <row r="61" ht="43" customHeight="1">
+    <row r="61" ht="134" customHeight="1">
       <c r="A61" s="10" t="n">
         <v>59</v>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Vano: porte</t>
+          <t>Vano: cabina e portata</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Ingombro della porta di piano lungo la parete del vano</t>
+          <t>Superficie utile massima della cabina per portata — la norma misura la superficie a 1 m dal pavimento tra le pareti strutturali, senza finiture (5.4.2.1.2), conta le nicchie e conta per intero la rientranza dell'ingresso profonda più di 100 mm (5.4.2.1.3); il software usa larghezza × profondità interne: nicchie e rientranze vanno aggiunte a mano</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>telescopica a 2 ante: 1,5·L + 110 mm; centrale a 2 ante: 2·L + 110 mm (L = luce netta)</t>
+          <t>100 kg 0,37 m²; 180 kg 0,58; 225 kg 0,70; 300 kg 0,90; 375 kg 1,10; 400 kg 1,17; 450 kg 1,30; 525 kg 1,45; 600 kg 1,60; 630 kg 1,66; 675 kg 1,75; 750 kg 1,90; 800 kg 2,00; 825 kg 2,05; 900 kg 2,20; 975 kg 2,35; 1000 kg 2,40; 1050 kg 2,50; 1125 kg 2,65; 1200 kg 2,80; 1250 kg 2,90; 1275 kg 2,95; 1350 kg 3,10; 1425 kg 3,25; 1500 kg 3,40; 1600 kg 3,56; 2000 kg 4,20; 2500 kg 5,00; oltre 2500 kg +0,16 m² ogni 100 kg; interpolazione lineare</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>dato del fornitore delle porte</t>
+          <t>UNI EN 81-20:2020, 5.4.2.1.1 (Prospetto 6)</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>valori tipici: scelta del software da confermare con il fornitore</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 63–64</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>ingombro della porta di piano</t>
+          <t>superficie della cabina per la portata</t>
         </is>
       </c>
       <c r="I61" s="11" t="n"/>
@@ -3611,43 +3611,43 @@
       <c r="M61" s="11" t="n"/>
       <c r="N61" s="11" t="n"/>
     </row>
-    <row r="62" ht="30" customHeight="1">
+    <row r="62" ht="95" customHeight="1">
       <c r="A62" s="10" t="n">
         <v>60</v>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Vano: porte</t>
+          <t>Vano: cabina e portata</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Larghezza della cabina rispetto alla porta</t>
+          <t>Numero di passeggeri</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>larghezza interna ≥ luce della porta + 50 mm; profondità interna ≥ 800 mm</t>
+          <t>il minore tra Q/75 arrotondato per difetto e il numero ammesso dalla superficie: 1 persona 0,28 m²; 2 0,49; 3 0,60; 4 0,79; 5 0,98; 6 1,17; 7 1,31; 8 1,45; 9 1,59; 10 1,73; 11 1,87; 12 2,01; 13 2,15; 14 2,29; 15 2,43; 16 2,57; 17 2,71; 18 2,85; 19 2,99; 20 3,13; oltre 20 +0,115 m² per persona</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.4.2.3.1 (Prospetto 8)</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 66</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>la cabina entra nel vano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I62" s="11" t="n"/>
@@ -3657,43 +3657,43 @@
       <c r="M62" s="11" t="n"/>
       <c r="N62" s="11" t="n"/>
     </row>
-    <row r="63" ht="342" customHeight="1">
+    <row r="63" ht="186" customHeight="1">
       <c r="A63" s="10" t="n">
         <v>61</v>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Vano: porte</t>
+          <t>Vano: distanze in pianta</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Vano porta di piano e operatore della porta di cabina</t>
+          <t>Parete del vano di fronte all'entrata della cabina — le deroghe della norma (fino a 0,20 m per un tratto alto non più di 0,50 m o con porte verticali di ascensori per merci; nessun limite con la porta di cabina bloccata meccanicamente) non sono usate: la verifica è più severa. Il software misura fino alla soglia; la figura 3 della norma porta il limite anche al telaio e al bordo di chiusura delle ante di cabina: con la porta scelta lo verifica l'ingegnere sui dati del fornitore.</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>vano nel muro: luce netta + 2 × 50 mm di portale; operatore della porta di cabina lungo 1,5·L + 50 mm con porta telescopica (il lato di chiusura 25 mm oltre la luce) e 2·L + 60 mm con porta centrale, profondo 220 mm, dentro il vano; con il fornitore scelto: 2SG FLY/LIKE 1,5·L + 40 mm (telescopica) e 2·L + 20 mm (centrale), profondo 220 mm; Fermator 40/10 1,5·L + 50 mm e 2·L + 50 mm, profondo 144 mm; Dapa LOWER 1,5·L + 47 mm e 2·L + 50 mm, profondo 217 mm; con due accessi adiacenti gli operatori non devono sovrapporsi all'angolo tra le porte (altrimenti «Attenzione»: operatori da scegliere con il fornitore)</t>
+          <t>distanza orizzontale dalla soglia o dal telaio della porta di cabina ≤ 150 mm (qui: profondità della porta di piano + gioco tra le soglie)</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>dato del fornitore delle porte</t>
+          <t>UNI EN 81-20:2020, 5.2.5.3.1</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>schede PDF 2SG FLY 2AT (ingombro massimo 1,5·A + 10; soglia 1,5·A + 20, + 40 con l'extracorsa: presa la più lunga) e 2AO (2·A + 20), profondità 220 letta sul disegno; catalogo tecnico Dapa LOWER (1,5·AP + 47, 2·AP + 50, profondità 217); Fermator 40/10 PM in copie presso terzi (1,5·PL + 50 e 2·PL + 50, le soglie + 40; profondità 120–144 sul disegno, con le staffe 183–280; chiusura a 15 mm dalla luce, il software ne tiene 25); Wittur Hydra Plus da una copia del catalogo Selcom (1,5·PL + 25 e 2·PL + 50, profondo 200); letti il 2 ottobre 2026 (research/argano-geared/18-porte-limitatori-tenditori-tutti.md). Il generico è l'inviluppo: il più lungo (Fermator, Dapa) e il più profondo (2SG FLY). Hydra Plus può superarlo dove la sua quota GM supera la GW; Prisma e CMM: lunghezza e profondità non trovate</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 33</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>ingombro della porta di piano; ingombro della seconda porta di piano; operatori delle porte adiacenti</t>
+          <t>parete di fronte all'entrata</t>
         </is>
       </c>
       <c r="I63" s="11" t="n"/>
@@ -3703,33 +3703,33 @@
       <c r="M63" s="11" t="n"/>
       <c r="N63" s="11" t="n"/>
     </row>
-    <row r="64" ht="134" customHeight="1">
+    <row r="64" ht="95" customHeight="1">
       <c r="A64" s="10" t="n">
         <v>62</v>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Vano: porte</t>
+          <t>Vano: distanze in pianta</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Porta di piano spostata rispetto alla porta di cabina (disassamento) — nel 3D la leva della serratura con i rulli resta in linea con l'accoppiatore della porta di cabina: con il disassamento va montata spostata sull'anta della porta di piano (da concordare con il fornitore delle porte)</t>
+          <t>Gioco tra soglia di cabina e soglia di piano — Non calcolato: tra il bordo d'attacco delle ante di cabina e le porte di piano al massimo 0,12 m (5.3.4.2; 11.2.3 nella UNI EN 81-1:2008), dato del fornitore delle porte.</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>la luce netta della porta di piano sporge al massimo 50 mm per lato oltre quella della porta di cabina: con la stessa luce, disassamento ≤ 50 mm (oltre: «Non conforme»); lo stesso spostamento a tutti i piani, per ciascun accesso, con il vano nel muro, il portale, gli imbotti, la soglia sulle staffe e la bottoniera della porta di piano; il passaggio libero è la parte comune delle due luci (luce − disassamento), ed è quello verificato per l'accessibilità (DM 236/1989)</t>
+          <t>distanza orizzontale ≤ 35 mm</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.3.2.2</t>
+          <t>UNI EN 81-20:2020, 5.3.4.1 (figura 3); 11.2.2 nella UNI EN 81-1 (1999, 2008)</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 49</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 50</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>disassamento della porta di piano A; disassamento della porta di piano B</t>
+          <t>gioco tra le soglie</t>
         </is>
       </c>
       <c r="I64" s="11" t="n"/>
@@ -3749,43 +3749,43 @@
       <c r="M64" s="11" t="n"/>
       <c r="N64" s="11" t="n"/>
     </row>
-    <row r="65" ht="95" customHeight="1">
+    <row r="65" ht="69" customHeight="1">
       <c r="A65" s="10" t="n">
         <v>63</v>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Vano: porte</t>
+          <t>Vano: distanze in pianta</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Bottoniera di piano</t>
+          <t>Distanza tra cabina e contrappeso — il software misura tra le sagome di cabina e contrappeso: pattini e staffe non sono nel modello della pianta</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>accanto a ogni porta di piano, sul pianerottolo: per default a destra guardando la porta, il centro della pulsantiera a 150 mm dal vano della porta e i pulsanti a 1100 mm dal pavimento; pulsantiera di 120 × 300 mm, sporgente 15 mm dal muro; lato, distanza e altezza modificabili su ogni progetto</t>
+          <t>≥ 50 mm tra la cabina con i suoi componenti e il contrappeso con i suoi</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>altezze e distanze dagli angoli per l'accessibilità da verificare (DM 236/1989, UNI EN 81-70)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.5.1 h)</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 35</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>distanza cabina–contrappeso</t>
         </is>
       </c>
       <c r="I65" s="11" t="n"/>
@@ -3795,43 +3795,43 @@
       <c r="M65" s="11" t="n"/>
       <c r="N65" s="11" t="n"/>
     </row>
-    <row r="66" ht="186" customHeight="1">
+    <row r="66" ht="199" customHeight="1">
       <c r="A66" s="10" t="n">
         <v>64</v>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Vano: porte</t>
+          <t>Vano: distanze in pianta</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Imbotti della porta di piano (sostituzione con una luce più piccola) — Montanti e pannelli accanto alla porta più larghi di 150 mm che chiudono l'apertura vanno con la prova del pendolo della porta (UNI EN 81-20:2020, 5.3.5.3.4): la copre il fornitore.</t>
+          <t>Pareti all'ultimo piano e in testata diverse dal piano principale</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>quando la porta nuova ha una luce più piccola del vano esistente tra i marmi, gli imbotti laterali (a sinistra e a destra guardando la porta dal pianerottolo) e quello superiore coprono la differenza: distanza tra i marmi = imbotto sinistro + luce + 2 × 50 mm di portale + imbotto destro; altezza sotto il marmo superiore = altezza della luce + 60 mm di architrave del portale + imbotto superiore (con il telaio proprio della porta, i suoi montanti e il suo frontalino al posto del portale); gli stessi imbotti per tutte le porte di piano, in lamiera sul filo del muro verso il pianerottolo, disegnati in pianta, in sezione e nel 3D</t>
+          <t>negli edifici esistenti le pareti del vano all'ultima fermata e in testata possono stare altrove che al piano principale: cabina, guide e contrappeso restano a piombo; la cabina con soglie e operatori delle porte e il contrappeso passano ad almeno 25 mm dalle pareti spostate (meno: «Attenzione»; dentro la parete: «Non conforme»); le porte di piano dell'ultima fermata restano in linea con la cabina e la parete non entra nel loro spessore, i piedi delle guide e la staffa a ponte non entrano nelle pareti; le staffe arrivano alla parete dove sta (le staffe Panev si verificano anche lì); la distanza dalla parete di fronte all'entrata (voce distanze.parete.entrata) vale anche in testata</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>dato del fornitore delle porte (imbotti su misura)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.3.1 (parete di fronte all'entrata); il resto scelta del software</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
+          <t>scelta del software: il margine di marcia va confermato con l'installatore</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
           <t>scelta del software</t>
         </is>
       </c>
-      <c r="G66" s="10" t="inlineStr">
-        <is>
-          <t>scelta del software</t>
-        </is>
-      </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>pareti in testata diverse dal piano principale</t>
         </is>
       </c>
       <c r="I66" s="11" t="n"/>
@@ -3841,43 +3841,43 @@
       <c r="M66" s="11" t="n"/>
       <c r="N66" s="11" t="n"/>
     </row>
-    <row r="67" ht="316" customHeight="1">
+    <row r="67" ht="56" customHeight="1">
       <c r="A67" s="10" t="n">
         <v>65</v>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Vano: porte</t>
+          <t>Vano: accessibilità (DM 236/1989)</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Telaio proprio delle porte di piano</t>
+          <t>Edifici residenziali nuovi: cabina e porta minime</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>a scelta del progettista, al posto del portale (2 × 50 mm, architrave 60 mm): il telaio della porta, uguale a tutti i piani, per default il telaio standard con montanti da 120 mm a tutta altezza, frontalino da 220 mm sopra la luce tra i montanti e spessore 50 mm; montanti, frontalino e spessore modificabili su ogni progetto, montanti e frontalino da 25 mm (telai su misura). Il telaio sta tutto nel vano di corsa, contro la parete e sulla soglia: soglia e sospensione della porta sono fissate al telaio e le coppie Panev (sotto la soglia e sopra la sospensione) lo tengono alla parete; il vano nel muro è il suo ingombro esterno (luce + 2 montanti, altezza della luce + frontalino), gli imbotti stanno sul pavimento del pianerottolo. Lo spessore del telaio è dentro la profondità della porta di piano: le ante scorrono dietro il telaio, il binario più vicino alla parete (68 mm prima del bordo della soglia nelle porte telescopiche, 30 mm nelle centrali) almeno a filo del telaio, altrimenti «Attenzione» (si aumenta la profondità della porta di piano). Disegnato in pianta, in sezione e nel 3D; la bottoniera si misura dal bordo del vano nel muro</t>
+          <t>cabina larga 950 mm e profonda 1300 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (fuori dal vano: da verificare in sito)</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>dato del fornitore delle porte</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>2SG, pagina del telaio standard (montanti 120, frontalino 220, spessore 50; lamiera autoportante 1/1,2 mm; montaggio sul pavimento finito, staffe e tasselli per il muro) e disegno del telaio (larghezza luce + 240) letti il 2 ottobre 2026; telai di dimensioni speciali con montanti e frontalino da 25 mm (research/argano-geared/14-porte-e-soglie.md, 18-porte-limitatori-tenditori-tutti.md). Il telaio nel vano di corsa con soglia e sospensione fissate, tenuto dalle coppie Panev, il vano nel muro della misura del telaio, lo spessore dentro la profondità della porta e gli imbotti sul pavimento del pianerottolo: indicazione del cliente (4 ottobre 2026)</t>
+          <t>DM 236/1989, 8.1.12, letto per intero su Normattiva il 2026-10-02 (ricerca, cap. 16, §4.1)</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>le ante della porta di piano dietro il suo telaio</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I67" s="11" t="n"/>
@@ -3887,43 +3887,43 @@
       <c r="M67" s="11" t="n"/>
       <c r="N67" s="11" t="n"/>
     </row>
-    <row r="68" ht="199" customHeight="1">
+    <row r="68" ht="56" customHeight="1">
       <c r="A68" s="10" t="n">
         <v>66</v>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Vano: ingombri tipici</t>
+          <t>Vano: accessibilità (DM 236/1989)</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Ingombri tipici nel vano (modificabili su ogni progetto) — pacchetto porta di catalogo (porta di cabina + gioco tra le soglie + porta di piano), da wittur.com: Hydra 210 mm a 2 ante telescopiche e 180 mm a 2 ante centrali, Hydra 3000 180 e 130, Augusta EVO 190 e 110, Sematic 2000 C-MOD 185 e 117, Fineline 115 e 85; Sematic 2000 B 255 e 165 (cabina 90 e 45, gioco 30, piano 135 e 90, da una copia della brochure). Con le porte scelte, i tre ingombri vanno portati alla somma del fornitore (oggi 80 + 30 + 80 = 190 mm)</t>
+          <t>Edifici non residenziali nuovi: cabina e porta minime</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>profondità della porta di piano 80 mm; gioco tra le soglie 30 mm; porta di cabina 80 mm; pareti della cabina 35 mm; guide e staffe della cabina 165 mm per lato; cabina–contrappeso 60 mm; spessore del contrappeso 140 mm; guide e staffe del contrappeso 80 mm; cabina–parete di fondo 60 mm; punta della guida–cabina 30 mm; contrappeso laterale–piede della guida di cabina 85 mm</t>
+          <t>cabina larga 1100 mm e profonda 1400 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (fuori dal vano: da verificare in sito)</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>dati del costruttore di guide, porte e cabina</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>valori tipici: scelta del software</t>
+          <t>DM 236/1989, 8.1.12, letto per intero su Normattiva il 2026-10-02 (ricerca, cap. 16, §4.1)</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>la cabina entra nel vano</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I68" s="11" t="n"/>
@@ -3933,43 +3933,43 @@
       <c r="M68" s="11" t="n"/>
       <c r="N68" s="11" t="n"/>
     </row>
-    <row r="69" ht="108" customHeight="1">
+    <row r="69" ht="56" customHeight="1">
       <c r="A69" s="10" t="n">
         <v>67</v>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Vano: ingombri tipici</t>
+          <t>Vano: accessibilità (DM 236/1989)</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Contrappeso laterale</t>
+          <t>Adeguamento di edifici esistenti: cabina e porta minime</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>tra la parete e la guida della cabina, centrato sull'asse delle guide di cabina, con le sue guide alle estremità (pattini 20 mm) e la guida di cabina su una staffa a ponte; a 40 mm dalle zone delle porte; lunghezza in pianta da 400 a 900 mm (sotto 400 mm: «Attenzione»); con il contrappeso sul fondo, al massimo la larghezza tra le guide della cabina</t>
+          <t>cabina larga 800 mm e profonda 1200 mm, porta di 750 mm sul lato corto; piattaforma davanti alla porta 1,40 × 1,40 m (fuori dal vano: da verificare in sito)</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>DM 236/1989, 8.1.12, letto per intero su Normattiva il 2026-10-02 (ricerca, cap. 16, §4.1)</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>lunghezza del contrappeso</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I69" s="11" t="n"/>
@@ -3979,33 +3979,33 @@
       <c r="M69" s="11" t="n"/>
       <c r="N69" s="11" t="n"/>
     </row>
-    <row r="70" ht="147" customHeight="1">
+    <row r="70" ht="43" customHeight="1">
       <c r="A70" s="10" t="n">
         <v>68</v>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Vano: ingombri tipici</t>
+          <t>Vano: porte</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Arcata a zaino (due accessi adiacenti a 90°)</t>
+          <t>Ingombro della porta di piano lungo la parete del vano</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>entrambe le guide di cabina sulla parete opposta all'accesso laterale, con le lame affacciate lungo la parete (il momento della cabina a sbalzo va sulle facce delle lame); piedi delle guide a 20 mm dentro la profondità della piattaforma; contrappeso tra le guide, contro la parete, con le sue guide alle estremità e i piedi a 70 mm da quelli delle guide di cabina (staffe); la cabina a 10 mm dalle bride che tengono i piedi delle guide sulle staffe (bride forgiate della misura della guida, con la piastra oltre il piede)</t>
+          <t>telescopica a 2 ante: 1,5·L + 110 mm; centrale a 2 ante: 2·L + 110 mm (L = luce netta)</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>dato del fornitore delle porte</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (principio: cataloghi di arcate a zaino); disposizione da confermare con il fornitore dell'arcata</t>
+          <t>valori tipici: scelta del software da confermare con il fornitore</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ingombro della porta di piano</t>
         </is>
       </c>
       <c r="I70" s="11" t="n"/>
@@ -4025,23 +4025,23 @@
       <c r="M70" s="11" t="n"/>
       <c r="N70" s="11" t="n"/>
     </row>
-    <row r="71" ht="212" customHeight="1">
+    <row r="71" ht="30" customHeight="1">
       <c r="A71" s="10" t="n">
         <v>69</v>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Vano: ingombri tipici</t>
+          <t>Vano: porte</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Nicchie nelle pareti del vano</t>
+          <t>Larghezza della cabina rispetto alla porta</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>contrappeso in nicchia: il contrappeso con le sue guide sta nella nicchia della parete su cui corre, con almeno 20 mm tra le guide e i fianchi della nicchia (con le staffe Panev, lo spazio della piastra del supporto dietro il piede di ogni guida); la distanza dalla parete si misura dal fondo della nicchia e la cabina guadagna la sua profondità, senza scendere sotto gli ingombri delle guide; luce del vano in nicchia: una nicchia alta 400 mm per lampada, le lampade 1500 mm sopra ogni piano e l'ultima a 80 mm sotto il solaio; canalina in nicchia: dal fondo della fossa al solaio; ogni nicchia dentro la sua parete, fuori dai telai delle porte di piano e dalle altre nicchie, con almeno 50 mm di muro dietro; altrimenti «Non conforme»</t>
+          <t>larghezza interna ≥ luce della porta + 50 mm; profondità interna ≥ 800 mm</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>scelta del software; la resistenza della parete con la nicchia va verificata dal progettista</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>nicchie nelle pareti</t>
+          <t>la cabina entra nel vano</t>
         </is>
       </c>
       <c r="I71" s="11" t="n"/>
@@ -4071,43 +4071,43 @@
       <c r="M71" s="11" t="n"/>
       <c r="N71" s="11" t="n"/>
     </row>
-    <row r="72" ht="329" customHeight="1">
+    <row r="72" ht="342" customHeight="1">
       <c r="A72" s="10" t="n">
         <v>70</v>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Vano: ingombri tipici</t>
+          <t>Vano: porte</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Staffe delle guide del contrappeso (catalogo Panev)</t>
+          <t>Vano porta di piano e operatore della porta di cabina</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>per default il supporto Panev SU o SD con la guida SG, la guida serrata sulla flangia della SG da due bride N1: il supporto più corto il cui campo stampato prende la distanza della guida dalla parete (o dal fondo della nicchia) e la cui piastra sta sulla parete: SU, SD 150 e SD 220 lunghi 160 mm da 45 a 155 mm (SD 220 da 50), lunghi 180 mm da 45 a 195 mm, lunghi 200 mm da 45 a 215 mm; quando nessuno sta, vicino a un angolo, il supporto scorrevole SC sulla parete dietro il piede della guida con la SG lungo la parete: la flangia della SG da 2 mm oltre il bordo dell'SC fino a 70, 88, 130 e 140 mm dalla parete per SC 50, 60, 80 e 90, l'asse della guida entro il campo stampato da un'estremità dell'SC (lunghi 200 mm: 210, 213, 215 e 215 mm; lunghi 220 mm: 235, 235, 255 e 235 mm), fuori dai telai delle porte e dalle nicchie. Il progettista può scegliere l'articolo a mano (se non prende la guida: «Non conforme») o una soluzione su disegno esecutivo, SC 50 170 + SG 225 50 a misura o SN 60 65 + SN 65 200 + BRACCIO 160 190 all'angolo del vano: «Da verificare» sul disegno; nessuno adatto: «Non conforme» (si possono scegliere staffe generiche, da dimensionare a parte)</t>
+          <t>vano nel muro: luce netta + 2 × 50 mm di portale; operatore della porta di cabina lungo 1,5·L + 50 mm con porta telescopica (il lato di chiusura 25 mm oltre la luce) e 2·L + 60 mm con porta centrale, profondo 220 mm, dentro il vano; con il fornitore scelto: 2SG FLY/LIKE 1,5·L + 40 mm (telescopica) e 2·L + 20 mm (centrale), profondo 220 mm; Fermator 40/10 1,5·L + 50 mm e 2·L + 50 mm, profondo 144 mm; Dapa LOWER 1,5·L + 47 mm e 2·L + 50 mm, profondo 217 mm; con due accessi adiacenti gli operatori non devono sovrapporsi all'angolo tra le porte (altrimenti «Attenzione»: operatori da scegliere con il fornitore)</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>catalogo staffe Panev 2026, pp. 20-62</t>
+          <t>dato del fornitore delle porte</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>catalogo del costruttore (panev/docs/catalogo-staffe-panev-2026.pdf); le corse dell'SC lontano dalla parete lette sui disegni di montaggio (pp. 41-55)</t>
+          <t>schede PDF 2SG FLY 2AT (ingombro massimo 1,5·A + 10; soglia 1,5·A + 20, + 40 con l'extracorsa: presa la più lunga) e 2AO (2·A + 20), profondità 220 letta sul disegno; catalogo tecnico Dapa LOWER (1,5·AP + 47, 2·AP + 50, profondità 217); Fermator 40/10 PM in copie presso terzi (1,5·PL + 50 e 2·PL + 50, le soglie + 40; profondità 120–144 sul disegno, con le staffe 183–280; chiusura a 15 mm dalla luce, il software ne tiene 25); Wittur Hydra Plus da una copia del catalogo Selcom (1,5·PL + 25 e 2·PL + 50, profondo 200); letti il 2 ottobre 2026 (research/argano-geared/18-porte-limitatori-tenditori-tutti.md). Il generico è l'inviluppo: il più lungo (Fermator, Dapa) e il più profondo (2SG FLY). Hydra Plus può superarlo dove la sua quota GM supera la GW; Prisma e CMM: lunghezza e profondità non trovate</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>staffe del catalogo per le guide del contrappeso</t>
+          <t>ingombro della porta di piano; ingombro della seconda porta di piano; operatori delle porte adiacenti</t>
         </is>
       </c>
       <c r="I72" s="11" t="n"/>
@@ -4117,43 +4117,43 @@
       <c r="M72" s="11" t="n"/>
       <c r="N72" s="11" t="n"/>
     </row>
-    <row r="73" ht="407" customHeight="1">
+    <row r="73" ht="134" customHeight="1">
       <c r="A73" s="10" t="n">
         <v>71</v>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Vano: ingombri tipici</t>
+          <t>Vano: porte</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Staffe delle porte di piano (catalogo Panev)</t>
+          <t>Porta di piano spostata rispetto alla porta di cabina (disassamento) — nel 3D la leva della serratura con i rulli resta in linea con l'accoppiatore della porta di cabina: con il disassamento va montata spostata sull'anta della porta di piano (da concordare con il fornitore delle porte)</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>sotto ogni soglia di piano la coppia A + B della stessa sezione (65, 45 o 37 mm: le serie non sono intercambiabili): per default A 65 170 7 + B 65 320 (5 mm, regolazione ±8°), oppure quella scelta dal progettista; la piastra A tagliata alla profondità della soglia, 4 mm prima del suo bordo (se la piastra è più corta della soglia: da verificare); una coppia ogni 400 mm della luce, almeno tre, le estreme a 10 mm dai bordi della luce. Sopra ogni porta di piano la stessa coppia capovolta: B sulla parete sopra il vano con lo snodo in basso, la sospensione della porta appesa sotto la piattaforma di A con bulloni nei suoi fori, A tagliata come sotto la soglia; una coppia ogni 400 mm lungo la sospensione (la corsa delle ante e 30 mm per parte), almeno tre, le estreme a 10 mm dalle sue estremità; se le coppie della soglia del piano sopra arrivano alla stessa altezza, quella che cadrebbe su una di esse si sposta accanto (la faccia di B e 10 mm), dentro la sospensione. Con il telaio proprio della porta le coppie tengono il telaio, a cui sono fissate soglia e sospensione (porte.telaio). B vuole il muro dalla sommità della sospensione (230 mm sopra la luce) in su: se il vano nel muro (telaio o marmi) sale più in alto, o la coppia arriva alla soglia del piano sopra, a quel piano le coppie sopra la porta non sono poste né contate, e la verifica lo segnala come «Attenzione» (il fissaggio della sospensione va definito con il costruttore della porta)</t>
+          <t>la luce netta della porta di piano sporge al massimo 50 mm per lato oltre quella della porta di cabina: con la stessa luce, disassamento ≤ 50 mm (oltre: «Non conforme»); lo stesso spostamento a tutti i piani, per ciascun accesso, con il vano nel muro, il portale, gli imbotti, la soglia sulle staffe e la bottoniera della porta di piano; il passaggio libero è la parte comune delle due luci (luce − disassamento), ed è quello verificato per l'accessibilità (DM 236/1989)</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>catalogo staffe Panev 2026, pp. 14-18 (coppie), p. 05 (taglio della piastra) e p. 04 (soglia o elemento portante della porta di piano)</t>
+          <t>UNI EN 81-20:2020, 5.3.2.2</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>catalogo del costruttore (panev/docs/catalogo-staffe-panev-2026.pdf); il passo, il numero minimo, il montaggio capovolto sopra la porta e lo spostamento sono scelta del software (il montaggio sopra la porta va confermato con il costruttore della porta)</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 49</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>staffe Panev sopra le porte di piano: muro tra il vano della porta e la soglia del piano sopra</t>
+          <t>disassamento della porta di piano A; disassamento della porta di piano B</t>
         </is>
       </c>
       <c r="I73" s="11" t="n"/>
@@ -4163,38 +4163,38 @@
       <c r="M73" s="11" t="n"/>
       <c r="N73" s="11" t="n"/>
     </row>
-    <row r="74" ht="355" customHeight="1">
+    <row r="74" ht="95" customHeight="1">
       <c r="A74" s="10" t="n">
         <v>72</v>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>Vano: ingombri tipici</t>
+          <t>Vano: porte</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Limitatore di velocità e tenditore (pianta, locale macchina, 3D) — il disegno unico delle LK200–LK315 dà due altezze non spiegate (230 e 415 mm; un rivenditore scrive 370): è presa la maggiore. Per Bode la velocità nominale massima è nostra: la velocità di scatto massima diviso 1,15 (scatto ≥ 115 % della nominale), del GB 8 con 1,49 m/s del disegno invece dei 2,04 della brochure. Per le RQ-A e le RC Montanari 0,15–3,0 e 1,60–4,2 m/s sono i campi della famiglia: il limite di ogni taglia va letto sul manuale. Delle basi pubblicate non sempre è detto quale lato stia nel piano della puleggia (il lato lungo è disegnato in quel piano, come nel LK200). Tenditore a leva: lungo 700 mm (quota «A» del PFB R4KE per LK200 in un listino di rivenditore, senza definizione), puleggia a 255 mm dalla cerniera e blocco di 150 × 185 mm: scelte del software; le masse di 22 e 44 kg sono quelle delle tabelle PFB (tenditori R4K e R4R per LK200, confermate dalla brochure)</t>
+          <t>Bottoniera di piano</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>per velocità il più piccolo PFB che la regge: LK200 (Ø 200, fune 6) fino a 1,48 m/s, LK250 fino a 1,74, LK300 fino a 2,93, R12BF fino a 4,00; oppure il modello scelto se regge la velocità: PFB (LX, LK, R1, R3LR, R5, R6, R10BF), Bode (GB 7 fino a 2,98 m/s, GB 8 fino a 1,29), Dynatech (VEGA 200 fino a 2,40), Wittur (OL20 fino a 1,75, OL35 fino a 3,00, EOS fino a 2,50, OL100 fino a 10,00) o Montanari (RQ-A 200, 250 e 300, RC 200 e 300, NOR fino a 1,50 m/s, RG 200 fino a 0,30). Con le quote dei disegni dei costruttori (altezza totale, tra parentesi l'asse dalla base): LK200, LK250, LK300 e LK315 415 (165) su base 220 × 165 (LK315 220 × 130); LX120 178 (70,5), LK120 270 (71), LX150 274 (86), LX180 322 (107), LX200 349 (110); R1 344 (190,5) su base 285 × 80; R3LR 348 (157); R5 261 (120); R6 335 (168); R10BF 488 (303) su base 460 × 196; R12BF 524 (337) su base 520 × 116; Bode GB 7 360 (205) e GB 8 315 (205); Dynatech VEGA 200 332 (199,5); Wittur e Montanari nelle proporzioni del software (Ø 200: alto 370, asse a 240). Tenditore in fossa sulla guida di cabina: a leva con 22 kg (come PFB R4K) o verticale con 44 kg (come PFB R4R)</t>
+          <t>accanto a ogni porta di piano, sul pianerottolo: per default a destra guardando la porta, il centro della pulsantiera a 150 mm dal vano della porta e i pulsanti a 1100 mm dal pavimento; pulsantiera di 120 × 300 mm, sporgente 15 mm dal muro; lato, distanza e altezza modificabili su ogni progetto</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>dati del fornitore del limitatore; dalla norma solo lo scatto ≥ 115 % della velocità nominale (UNI EN 81-20:2020, 5.6.2.2.1.1 a))</t>
+          <t>altezze e distanze dagli angoli per l'accessibilità da verificare (DM 236/1989, UNI EN 81-70)</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>manuali d'uso PFB con i disegni quotati (download.pfb.it), brochure Bode e Wittur, manuale Dynatech VEGA e disegni Bode in copia presso un rivenditore (elevatorequipment.co.uk), letti il 2 ottobre 2026; basi delle LK da un listino di rivenditore; Montanari da estratti di ricerca del 1° ottobre 2026 (research/argano-geared/18-porte-limitatori-tenditori-tutti.md)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
@@ -4209,43 +4209,43 @@
       <c r="M74" s="11" t="n"/>
       <c r="N74" s="11" t="n"/>
     </row>
-    <row r="75" ht="82" customHeight="1">
+    <row r="75" ht="186" customHeight="1">
       <c r="A75" s="10" t="n">
         <v>73</v>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: porte</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Spazi di rifugio sul tetto di cabina e in fossa</t>
+          <t>Imbotti della porta di piano (sostituzione con una luce più piccola) — Montanti e pannelli accanto alla porta più larghi di 150 mm che chiudono l'apertura vanno con la prova del pendolo della porta (UNI EN 81-20:2020, 5.3.5.3.4): la copre il fornitore.</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>tipo 1 (in piedi) 400 × 500 mm in pianta, alto 2000 mm; tipo 2 (accucciato) 500 × 700 mm, alto 1000 mm; tipo 3 (disteso, solo in fossa) 700 × 1000 mm, alto 500 mm; in testata con la cabina nella posizione più alta, in fossa con la cabina sugli ammortizzatori compressi</t>
+          <t>quando la porta nuova ha una luce più piccola del vano esistente tra i marmi, gli imbotti laterali (a sinistra e a destra guardando la porta dal pianerottolo) e quello superiore coprono la differenza: distanza tra i marmi = imbotto sinistro + luce + 2 × 50 mm di portale + imbotto destro; altezza sotto il marmo superiore = altezza della luce + 60 mm di architrave del portale + imbotto superiore (con il telaio proprio della porta, i suoi montanti e il suo frontalino al posto del portale); gli stessi imbotti per tutte le porte di piano, in lamiera sul filo del muro verso il pianerottolo, disegnati in pianta, in sezione e nel 3D</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1 (Prospetto 3) e 5.2.5.8.1 (Prospetto 4)</t>
+          <t>dato del fornitore delle porte (imbotti su misura)</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 37–40</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>spazio di rifugio in testata; spazio di rifugio in fossa</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I75" s="11" t="n"/>
@@ -4255,43 +4255,43 @@
       <c r="M75" s="11" t="n"/>
       <c r="N75" s="11" t="n"/>
     </row>
-    <row r="76" ht="95" customHeight="1">
+    <row r="76" ht="316" customHeight="1">
       <c r="A76" s="10" t="n">
         <v>74</v>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: porte</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Posizione più alta della cabina — vale per gli ascensori a frizione; le riduzioni di 5.2.5.6.1.2 (rallentamento controllato) e 5.2.5.6.1.3 (puleggia tenditrice con antirimbalzo) non sono usate: la verifica è più severa</t>
+          <t>Telaio proprio delle porte di piano</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>contrappeso sugli ammortizzatori completamente compressi, più il salto 0,035·v² m (v velocità nominale)</t>
+          <t>a scelta del progettista, al posto del portale (2 × 50 mm, architrave 60 mm): il telaio della porta, uguale a tutti i piani, per default il telaio standard con montanti da 120 mm a tutta altezza, frontalino da 220 mm sopra la luce tra i montanti e spessore 50 mm; montanti, frontalino e spessore modificabili su ogni progetto, montanti e frontalino da 25 mm (telai su misura). Il telaio sta tutto nel vano di corsa, contro la parete e sulla soglia: soglia e sospensione della porta sono fissate al telaio e le coppie Panev (sotto la soglia e sopra la sospensione) lo tengono alla parete; il vano nel muro è il suo ingombro esterno (luce + 2 montanti, altezza della luce + frontalino), gli imbotti stanno sul pavimento del pianerottolo. Lo spessore del telaio è dentro la profondità della porta di piano: le ante scorrono dietro il telaio, il binario più vicino alla parete (68 mm prima del bordo della soglia nelle porte telescopiche, 30 mm nelle centrali) almeno a filo del telaio, altrimenti «Attenzione» (si aumenta la profondità della porta di piano). Disegnato in pianta, in sezione e nel 3D; la bottoniera si misura dal bordo del vano nel muro</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.6.1.1 (Prospetto 2)</t>
+          <t>dato del fornitore delle porte</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 36</t>
+          <t>2SG, pagina del telaio standard (montanti 120, frontalino 220, spessore 50; lamiera autoportante 1/1,2 mm; montaggio sul pavimento finito, staffe e tasselli per il muro) e disegno del telaio (larghezza luce + 240) letti il 2 ottobre 2026; telai di dimensioni speciali con montanti e frontalino da 25 mm (research/argano-geared/14-porte-e-soglie.md, 18-porte-limitatori-tenditori-tutti.md). Il telaio nel vano di corsa con soglia e sospensione fissate, tenuto dalle coppie Panev, il vano nel muro della misura del telaio, lo spessore dentro la profondità della porta e gli imbotti sul pavimento del pianerottolo: indicazione del cliente (4 ottobre 2026)</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>spazio di rifugio in testata; distanze libere dal soffitto</t>
+          <t>le ante della porta di piano dietro il suo telaio</t>
         </is>
       </c>
       <c r="I76" s="11" t="n"/>
@@ -4301,43 +4301,43 @@
       <c r="M76" s="11" t="n"/>
       <c r="N76" s="11" t="n"/>
     </row>
-    <row r="77" ht="147" customHeight="1">
+    <row r="77" ht="199" customHeight="1">
       <c r="A77" s="10" t="n">
         <v>75</v>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Distanze libere dal soffitto con la cabina nella posizione più alta — I valori 500, 100 e 300 mm sono confermati. Da concordare con l'organismo: il software dà alla traversa dell'arcata i 100 mm di b) (il testo nomina traversa o architrave e parti di porte verticali; se non vale per l'arcata servono i 500 mm di a)); non verifica i 500 mm in obliquo oltre i 400 mm dal corrimano (c) 2)).</t>
+          <t>Ingombri tipici nel vano (modificabili su ogni progetto) — pacchetto porta di catalogo (porta di cabina + gioco tra le soglie + porta di piano), da wittur.com: Hydra 210 mm a 2 ante telescopiche e 180 mm a 2 ante centrali, Hydra 3000 180 e 130, Augusta EVO 190 e 110, Sematic 2000 C-MOD 185 e 117, Fineline 115 e 85; Sematic 2000 B 255 e 165 (cabina 90 e 45, gioco 30, piano 135 e 90, da una copia della brochure). Con le porte scelte, i tre ingombri vanno portati alla somma del fornitore (oggi 80 + 30 + 80 = 190 mm)</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>≥ 500 mm sopra le apparecchiature sul tetto di cabina (operatore); ≥ 100 mm sopra pattini, attacchi delle funi e traversa dell'arcata; ≥ 300 mm sopra il corrimano della balaustra</t>
+          <t>profondità della porta di piano 80 mm; gioco tra le soglie 30 mm; porta di cabina 80 mm; pareti della cabina 35 mm; guide e staffe della cabina 165 mm per lato; cabina–contrappeso 60 mm; spessore del contrappeso 140 mm; guide e staffe del contrappeso 80 mm; cabina–parete di fondo 60 mm; punta della guida–cabina 30 mm; contrappeso laterale–piede della guida di cabina 85 mm</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.2 a)–c)</t>
+          <t>dati del costruttore di guide, porte e cabina</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 38</t>
+          <t>valori tipici: scelta del software</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>distanze libere dal soffitto</t>
+          <t>la cabina entra nel vano</t>
         </is>
       </c>
       <c r="I77" s="11" t="n"/>
@@ -4353,37 +4353,37 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Parte più alta della cabina sotto ciò che pende sopra — fino alla versione 1.17.0 del motore del progetto la puleggia di cabina era verificata a 100 mm; i 100 mm della traversa sono la stessa lettura di spazi.testata.parti</t>
+          <t>Contrappeso laterale</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>con la cabina nella posizione più alta: a 2:1 la puleggia di cabina (Dp + 30 mm sopra la traversa) è un'apparecchiatura sul tetto, distanza libera ≥ 500 mm dal soffitto o dalle pulegge appese; a 1:1 con la macchina in basso la traversa sotto le pulegge appese al solaio (asse a Dp/2 + 120 mm sotto il soffitto), distanza libera ≥ 100 mm, quella della traversa</t>
+          <t>tra la parete e la guida della cabina, centrato sull'asse delle guide di cabina, con le sue guide alle estremità (pattini 20 mm) e la guida di cabina su una staffa a ponte; a 40 mm dalle zone delle porte; lunghezza in pianta da 400 a 900 mm (sotto 400 mm: «Attenzione»); con il contrappeso sul fondo, al massimo la larghezza tra le guide della cabina</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.2 a) e b)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 38</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>parte più alta della cabina sotto ciò che pende sopra</t>
+          <t>lunghezza del contrappeso</t>
         </is>
       </c>
       <c r="I78" s="11" t="n"/>
@@ -4393,33 +4393,33 @@
       <c r="M78" s="11" t="n"/>
       <c r="N78" s="11" t="n"/>
     </row>
-    <row r="79" ht="134" customHeight="1">
+    <row r="79" ht="147" customHeight="1">
       <c r="A79" s="10" t="n">
         <v>77</v>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori e spazio di rifugio in fossa, in pianta</t>
+          <t>Arcata a zaino (due accessi adiacenti a 90°)</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>lo spazio di rifugio in fossa resta libero dagli ammortizzatori di cabina: il software lo mette sotto il centro della cabina o, se un piatto vi entra, nel posto libero più vicino sotto l'interno della cabina; due o più ammortizzatori di cabina a 160 mm dai fianchi della piattaforma, più in fuori finché i piatti escono dalla pianta del rifugio, sempre sotto la piattaforma; la verifica vale anche per quelli messi dal software (margine ≥ 0)</t>
+          <t>entrambe le guide di cabina sulla parete opposta all'accesso laterale, con le lame affacciate lungo la parete (il momento della cabina a sbalzo va sulle facce delle lame); piedi delle guide a 20 mm dentro la profondità della piattaforma; contrappeso tra le guide, contro la parete, con le sue guide alle estremità e i piedi a 70 mm da quelli delle guide di cabina (staffe); la cabina a 10 mm dalle bride che tengono i piedi delle guide sulle staffe (bride forgiate della misura della guida, con la piastra oltre il piede)</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.8.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>scelta del software sul modello della fossa (posizioni tipiche, da confermare con i dati del fornitore degli ammortizzatori)</t>
+          <t>scelta del software (principio: cataloghi di arcate a zaino); disposizione da confermare con il fornitore dell'arcata</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="11" t="n"/>
@@ -4439,43 +4439,43 @@
       <c r="M79" s="11" t="n"/>
       <c r="N79" s="11" t="n"/>
     </row>
-    <row r="80" ht="82" customHeight="1">
+    <row r="80" ht="212" customHeight="1">
       <c r="A80" s="10" t="n">
         <v>78</v>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Distanze in fossa con la cabina sugli ammortizzatori compressi</t>
+          <t>Nicchie nelle pareti del vano</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>≥ 500 mm dal pavimento della fossa alle parti più basse della cabina; grembiule sotto la soglia di cabina: tratto verticale ≥ 750 mm, poi uno smusso a ≥ 60° sull'orizzontale con proiezione orizzontale ≥ 20 mm (circa 35 mm più in basso), con ≥ 100 mm liberi dal pavimento della fossa</t>
+          <t>contrappeso in nicchia: il contrappeso con le sue guide sta nella nicchia della parete su cui corre, con almeno 20 mm tra le guide e i fianchi della nicchia (con le staffe Panev, lo spazio della piastra del supporto dietro il piede di ogni guida); la distanza dalla parete si misura dal fondo della nicchia e la cabina guadagna la sua profondità, senza scendere sotto gli ingombri delle guide; luce del vano in nicchia: una nicchia alta 400 mm per lampada, le lampade 1500 mm sopra ogni piano e l'ultima a 80 mm sotto il solaio; canalina in nicchia: dal fondo della fossa al solaio; ogni nicchia dentro la sua parete, fuori dai telai delle porte di piano e dalle altre nicchie, con almeno 50 mm di muro dietro; altrimenti «Non conforme»</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.8.2 a) e 5.4.5.1–5.4.5.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 40–41, 69</t>
+          <t>scelta del software; la resistenza della parete con la nicchia va verificata dal progettista</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>spazio di rifugio in fossa; grembiule sugli ammortizzatori compressi</t>
+          <t>nicchie nelle pareti</t>
         </is>
       </c>
       <c r="I80" s="11" t="n"/>
@@ -4485,33 +4485,33 @@
       <c r="M80" s="11" t="n"/>
       <c r="N80" s="11" t="n"/>
     </row>
-    <row r="81" ht="108" customHeight="1">
+    <row r="81" ht="329" customHeight="1">
       <c r="A81" s="10" t="n">
         <v>79</v>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Balaustra sul tetto di cabina — fino alla versione 2.12.0 del motore del vano il software misurava i 500 mm dal bordo del tetto; la norma vuole la balaustra entro 150 mm dal bordo: se è più interna, la distanza cresce e può servire l'altezza maggiore</t>
+          <t>Staffe delle guide del contrappeso (catalogo Panev)</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>richiesta se dal bordo esterno del tetto alla parete ci sono più di 300 mm; alta 700 mm se dal bordo interno del corrimano alla parete ci sono fino a 500 mm, 1100 mm oltre; il corrimano (30 mm) con la faccia esterna a 100 mm dal bordo del tetto, come nel 3D</t>
+          <t>per default il supporto Panev SU o SD con la guida SG, la guida serrata sulla flangia della SG da due bride N1: il supporto più corto il cui campo stampato prende la distanza della guida dalla parete (o dal fondo della nicchia) e la cui piastra sta sulla parete: SU, SD 150 e SD 220 lunghi 160 mm da 45 a 155 mm (SD 220 da 50), lunghi 180 mm da 45 a 195 mm, lunghi 200 mm da 45 a 215 mm; quando nessuno sta, vicino a un angolo, il supporto scorrevole SC sulla parete dietro il piede della guida con la SG lungo la parete: la flangia della SG da 2 mm oltre il bordo dell'SC fino a 70, 88, 130 e 140 mm dalla parete per SC 50, 60, 80 e 90, l'asse della guida entro il campo stampato da un'estremità dell'SC (lunghi 200 mm: 210, 213, 215 e 215 mm; lunghi 220 mm: 235, 235, 255 e 235 mm), fuori dai telai delle porte e dalle nicchie. Il progettista può scegliere l'articolo a mano (se non prende la guida: «Non conforme») o una soluzione su disegno esecutivo, SC 50 170 + SG 225 50 a misura o SN 60 65 + SN 65 200 + BRACCIO 160 190 all'angolo del vano: «Da verificare» sul disegno; nessuno adatto: «Non conforme» (si possono scegliere staffe generiche, da dimensionare a parte)</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.7.2 b) e 5.4.7.4 b)–c)</t>
+          <t>catalogo staffe Panev 2026, pp. 20-62</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 70–72</t>
+          <t>catalogo del costruttore (panev/docs/catalogo-staffe-panev-2026.pdf); le corse dell'SC lontano dalla parete lette sui disegni di montaggio (pp. 41-55)</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>balaustra sul tetto di cabina</t>
+          <t>staffe del catalogo per le guide del contrappeso</t>
         </is>
       </c>
       <c r="I81" s="11" t="n"/>
@@ -4531,43 +4531,43 @@
       <c r="M81" s="11" t="n"/>
       <c r="N81" s="11" t="n"/>
     </row>
-    <row r="82" ht="121" customHeight="1">
+    <row r="82" ht="407" customHeight="1">
       <c r="A82" s="10" t="n">
         <v>80</v>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Superficie dove una persona può stare sul tetto di cabina — Nella 5.2.5.7.3 lo 0,12 m² è la soglia da cui un'area conta come posto in piedi, sopra la quale serve l'altezza del rifugio; che un'area simile debba esserci lo chiedeva la UNI EN 81-1:2008 (8.13.2). Il software verifica l'area disegnata.</t>
+          <t>Staffe delle porte di piano (catalogo Panev)</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>area continua ≥ 0,12 m² con il lato minore oltre 250 mm (disegnata 400 × 300 mm, modificabile sulla pianta in testata); sopra di essa deve esserci l'altezza dello spazio di rifugio</t>
+          <t>sotto ogni soglia di piano la coppia A + B della stessa sezione (65, 45 o 37 mm: le serie non sono intercambiabili): per default A 65 170 7 + B 65 320 (5 mm, regolazione ±8°), oppure quella scelta dal progettista; la piastra A tagliata alla profondità della soglia, 4 mm prima del suo bordo (se la piastra è più corta della soglia: da verificare); una coppia ogni 400 mm della luce, almeno tre, le estreme a 10 mm dai bordi della luce. Sopra ogni porta di piano la stessa coppia capovolta: B sulla parete sopra il vano con lo snodo in basso, la sospensione della porta appesa sotto la piattaforma di A con bulloni nei suoi fori, A tagliata come sotto la soglia; una coppia ogni 400 mm lungo la sospensione (la corsa delle ante e 30 mm per parte), almeno tre, le estreme a 10 mm dalle sue estremità; se le coppie della soglia del piano sopra arrivano alla stessa altezza, quella che cadrebbe su una di esse si sposta accanto (la faccia di B e 10 mm), dentro la sospensione. Con il telaio proprio della porta le coppie tengono il telaio, a cui sono fissate soglia e sospensione (porte.telaio). B vuole il muro dalla sommità della sospensione (230 mm sopra la luce) in su: se il vano nel muro (telaio o marmi) sale più in alto, o la coppia arriva alla soglia del piano sopra, a quel piano le coppie sopra la porta non sono poste né contate, e la verifica lo segnala come «Attenzione» (il fissaggio della sospensione va definito con il costruttore della porta)</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.3</t>
+          <t>catalogo staffe Panev 2026, pp. 14-18 (coppie), p. 05 (taglio della piastra) e p. 04 (soglia o elemento portante della porta di piano)</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 39</t>
+          <t>catalogo del costruttore (panev/docs/catalogo-staffe-panev-2026.pdf); il passo, il numero minimo, il montaggio capovolto sopra la porta e lo spostamento sono scelta del software (il montaggio sopra la porta va confermato con il costruttore della porta)</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>superficie per stare sul tetto di cabina</t>
+          <t>staffe Panev sopra le porte di piano: muro tra il vano della porta e la soglia del piano sopra</t>
         </is>
       </c>
       <c r="I82" s="11" t="n"/>
@@ -4577,43 +4577,43 @@
       <c r="M82" s="11" t="n"/>
       <c r="N82" s="11" t="n"/>
     </row>
-    <row r="83" ht="212" customHeight="1">
+    <row r="83" ht="355" customHeight="1">
       <c r="A83" s="10" t="n">
         <v>81</v>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Altezza libera degli accessi e della cabina — negli impianti esistenti (DPR 1497/1963, artt. 24, 27 e 29, non riletto) le porte possono essere alte 1,90 m e la cabina 2,00 m; con la sola sostituzione della macchina le altezze restano (parti esistenti); la UNI 10411-1:2024 ammette porte di piano nuove non più basse delle esistenti (19.1), una cabina nuova sotto 2 m se non più bassa dell'esistente e mai sotto 1,90 m (22 m)) e accessi di cabina mai sotto 1,80 m (22 n)), con avvertimenti: il software non conosce le esistenti e segnala ogni porta sotto 2000 mm</t>
+          <t>Limitatore di velocità e tenditore (pianta, locale macchina, 3D) — il disegno unico delle LK200–LK315 dà due altezze non spiegate (230 e 415 mm; un rivenditore scrive 370): è presa la maggiore. Per Bode la velocità nominale massima è nostra: la velocità di scatto massima diviso 1,15 (scatto ≥ 115 % della nominale), del GB 8 con 1,49 m/s del disegno invece dei 2,04 della brochure. Per le RQ-A e le RC Montanari 0,15–3,0 e 1,60–4,2 m/s sono i campi della famiglia: il limite di ogni taglia va letto sul manuale. Delle basi pubblicate non sempre è detto quale lato stia nel piano della puleggia (il lato lungo è disegnato in quel piano, come nel LK200). Tenditore a leva: lungo 700 mm (quota «A» del PFB R4KE per LK200 in un listino di rivenditore, senza definizione), puleggia a 255 mm dalla cerniera e blocco di 150 × 185 mm: scelte del software; le masse di 22 e 44 kg sono quelle delle tabelle PFB (tenditori R4K e R4R per LK200, confermate dalla brochure)</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>luce netta in altezza delle porte di piano e di cabina ≥ 2000 mm; altezza libera interna della cabina ≥ 2000 mm</t>
+          <t>per velocità il più piccolo PFB che la regge: LK200 (Ø 200, fune 6) fino a 1,48 m/s, LK250 fino a 1,74, LK300 fino a 2,93, R12BF fino a 4,00; oppure il modello scelto se regge la velocità: PFB (LX, LK, R1, R3LR, R5, R6, R10BF), Bode (GB 7 fino a 2,98 m/s, GB 8 fino a 1,29), Dynatech (VEGA 200 fino a 2,40), Wittur (OL20 fino a 1,75, OL35 fino a 3,00, EOS fino a 2,50, OL100 fino a 10,00) o Montanari (RQ-A 200, 250 e 300, RC 200 e 300, NOR fino a 1,50 m/s, RG 200 fino a 0,30). Con le quote dei disegni dei costruttori (altezza totale, tra parentesi l'asse dalla base): LK200, LK250, LK300 e LK315 415 (165) su base 220 × 165 (LK315 220 × 130); LX120 178 (70,5), LK120 270 (71), LX150 274 (86), LX180 322 (107), LX200 349 (110); R1 344 (190,5) su base 285 × 80; R3LR 348 (157); R5 261 (120); R6 335 (168); R10BF 488 (303) su base 460 × 196; R12BF 524 (337) su base 520 × 116; Bode GB 7 360 (205) e GB 8 315 (205); Dynatech VEGA 200 332 (199,5); Wittur e Montanari nelle proporzioni del software (Ø 200: alto 370, asse a 240). Tenditore in fossa sulla guida di cabina: a leva con 22 kg (come PFB R4K) o verticale con 44 kg (come PFB R4R)</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.3.2.1 e 5.4.1</t>
+          <t>dati del fornitore del limitatore; dalla norma solo lo scatto ≥ 115 % della velocità nominale (UNI EN 81-20:2020, 5.6.2.2.1.1 a))</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 49, 63; 2 m anche in DM 587/1987 (UNI EN 81-1), 7.3.1, 8.1.1 e 8.1.2</t>
+          <t>manuali d'uso PFB con i disegni quotati (download.pfb.it), brochure Bode e Wittur, manuale Dynatech VEGA e disegni Bode in copia presso un rivenditore (elevatorequipment.co.uk), letti il 2 ottobre 2026; basi delle LK da un listino di rivenditore; Montanari da estratti di ricerca del 1° ottobre 2026 (research/argano-geared/18-porte-limitatori-tenditori-tutti.md)</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>altezza libera degli accessi; altezza libera interna della cabina</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I83" s="11" t="n"/>
@@ -4623,7 +4623,7 @@
       <c r="M83" s="11" t="n"/>
       <c r="N83" s="11" t="n"/>
     </row>
-    <row r="84" ht="160" customHeight="1">
+    <row r="84" ht="82" customHeight="1">
       <c r="A84" s="10" t="n">
         <v>82</v>
       </c>
@@ -4634,22 +4634,22 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Corsa guidata in testata (contrappeso e cabina)</t>
+          <t>Spazi di rifugio sul tetto di cabina e in fossa</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>con la cabina sugli ammortizzatori completamente compressi le guide del contrappeso lo guidano ancora per almeno 0,1 + 0,035·v² m (v velocità nominale): dalla sommità del contrappeso, salito della corsa sotto la cabina (extracorsa e corsa degli ammortizzatori), alla sommità delle guide, che il software pone 50 mm sotto la soletta (voce foglio.stime); la cabina nella sua posizione più alta (salto compreso) ha ancora almeno 0,1 m di guida sopra la sommità dell'arcata, dove il software mette i pattini superiori (avviso: l'altezza reale dei pattini è del fornitore)</t>
+          <t>tipo 1 (in piedi) 400 × 500 mm in pianta, alto 2000 mm; tipo 2 (accucciato) 500 × 700 mm, alto 1000 mm; tipo 3 (disteso, solo in fossa) 700 × 1000 mm, alto 500 mm; in testata con la cabina nella posizione più alta, in fossa con la cabina sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.6.2 e 5.2.5.6.1.1 (Prospetto 2: cabina sugli ammortizzatori compressi più 0,035·v²); stesso valore in UNI EN 81-1 (1999, 2008), 5.7.1.2</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1 (Prospetto 3) e 5.2.5.8.1 (Prospetto 4)</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 36; UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 27</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 37–40</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>corsa guidata del contrappeso in testata; corsa guidata della cabina in testata</t>
+          <t>spazio di rifugio in testata; spazio di rifugio in fossa</t>
         </is>
       </c>
       <c r="I84" s="11" t="n"/>
@@ -4680,22 +4680,22 @@
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Schermo del contrappeso in fossa — non verificati: il bordo inferiore dello schermo a non più di 300 mm dal fondo della fossa (5.2.5.5.1 c)) e la protezione dello spazio oltre 300 mm tra guide del contrappeso e parete (e))</t>
+          <t>Posizione più alta della cabina — vale per gli ascensori a frizione; le riduzioni di 5.2.5.6.1.2 (rallentamento controllato) e 5.2.5.6.1.3 (puleggia tenditrice con antirimbalzo) non sono usate: la verifica è più severa</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>dal punto più basso del contrappeso sugli ammortizzatori compressi fino ad almeno 2000 mm sopra il pavimento della fossa (altezza dello schermo modificabile sul progetto, mai sotto questo valore)</t>
+          <t>contrappeso sugli ammortizzatori completamente compressi, più il salto 0,035·v² m (v velocità nominale)</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.5.1 b)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.6.1.1 (Prospetto 2)</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 35</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 36</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>protezione del contrappeso in fossa</t>
+          <t>spazio di rifugio in testata; distanze libere dal soffitto</t>
         </is>
       </c>
       <c r="I85" s="11" t="n"/>
@@ -4715,7 +4715,7 @@
       <c r="M85" s="11" t="n"/>
       <c r="N85" s="11" t="n"/>
     </row>
-    <row r="86" ht="95" customHeight="1">
+    <row r="86" ht="147" customHeight="1">
       <c r="A86" s="10" t="n">
         <v>84</v>
       </c>
@@ -4726,32 +4726,32 @@
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori ad accumulo di energia lineari (molle)</t>
+          <t>Distanze libere dal soffitto con la cabina nella posizione più alta — I valori 500, 100 e 300 mm sono confermati. Da concordare con l'organismo: il software dà alla traversa dell'arcata i 100 mm di b) (il testo nomina traversa o architrave e parti di porte verticali; se non vale per l'arcata servono i 500 mm di a)); non verifica i 500 mm in obliquo oltre i 400 mm dal corrimano (c) 2)).</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>ammessi fino a 1 m/s; corsa ≥ 0,135·v² m e comunque ≥ 65 mm; extracorsa della cabina e del contrappeso ≥ 0 (nessun minimo nella norma)</t>
+          <t>≥ 500 mm sopra le apparecchiature sul tetto di cabina (operatore); ≥ 100 mm sopra pattini, attacchi delle funi e traversa dell'arcata; ≥ 300 mm sopra il corrimano della balaustra</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.1.5 (fino a 1 m/s) e 5.8.2.1.1.1 (corsa); nessuna extracorsa minima in metri: l'interruttore di extracorsa interviene prima che la cabina o il contrappeso tocchino gli ammortizzatori (5.12.2.1)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.2 a)–c)</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 98, 131</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 38</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso; extracorsa di cabina e contrappeso</t>
+          <t>distanze libere dal soffitto</t>
         </is>
       </c>
       <c r="I86" s="11" t="n"/>
@@ -4761,7 +4761,7 @@
       <c r="M86" s="11" t="n"/>
       <c r="N86" s="11" t="n"/>
     </row>
-    <row r="87" ht="121" customHeight="1">
+    <row r="87" ht="108" customHeight="1">
       <c r="A87" s="10" t="n">
         <v>85</v>
       </c>
@@ -4772,22 +4772,22 @@
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori ad accumulo di energia non lineari (tamponi in poliuretano) — il tampone tipico alto 80 mm è un dato di catalogo, non della norma: va sostituito con quello montato</t>
+          <t>Parte più alta della cabina sotto ciò che pende sopra — fino alla versione 1.17.0 del motore del progetto la puleggia di cabina era verificata a 100 mm; i 100 mm della traversa sono la stessa lettura di spazi.testata.parti</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>ammessi fino a 1 m/s come le molle; nessuna corsa minima da formula: il campo di masse del certificato di esame di tipo per la velocità deve comprendere, per ogni tampone, la cabina vuota e a pieno carico (o il contrappeso); «completamente compresso» vuol dire compresso del 90 % dell'altezza, quindi la corsa è 0,9·H negli spazi in fossa e in testata; tampone tipico alti 80 mm (P+S Diepocell D, Ø da 80 a 220 mm; ACLA AUTAN XL)</t>
+          <t>con la cabina nella posizione più alta: a 2:1 la puleggia di cabina (Dp + 30 mm sopra la traversa) è un'apparecchiatura sul tetto, distanza libera ≥ 500 mm dal soffitto o dalle pulegge appese; a 1:1 con la macchina in basso la traversa sotto le pulegge appese al solaio (asse a Dp/2 + 120 mm sotto il soffitto), distanza libera ≥ 100 mm, quella della traversa</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.1.5, 5.8.1.7, 5.8.2.1.2.1 e 5.8.2.1.2.2 (compresso al 90 %); UNI EN 81-50:2020, 5.5.4 (esame di tipo)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.2 a) e b)</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 98–99; UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 24; il tampone tipico dai cataloghi P+S Diepocell (wwlift.de) e ACLA AUTAN XL (acla.de), estratti di ricerca del 1° ottobre 2026</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 38</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso</t>
+          <t>parte più alta della cabina sotto ciò che pende sopra</t>
         </is>
       </c>
       <c r="I87" s="11" t="n"/>
@@ -4807,7 +4807,7 @@
       <c r="M87" s="11" t="n"/>
       <c r="N87" s="11" t="n"/>
     </row>
-    <row r="88" ht="95" customHeight="1">
+    <row r="88" ht="134" customHeight="1">
       <c r="A88" s="10" t="n">
         <v>86</v>
       </c>
@@ -4818,32 +4818,32 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori a dissipazione di energia (idraulici) — gli ammortizzatori Oleo sono dati di catalogo, non della norma: vanno sostituiti con quelli montati</t>
+          <t>Ammortizzatori e spazio di rifugio in fossa, in pianta</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>a ogni velocità; corsa ≥ 0,0674·v² m (arresto per gravità al 115 % della velocità nominale); la corsa ridotta con il controllo del rallentamento non è considerata; ammortizzatori tipici: Oleo LSB10 fino a 1 m/s, alto 222,2 mm con corsa 73,4 mm; LSB16 fino a 1,6 m/s, alto 485,5 mm con corsa 173,5 mm</t>
+          <t>lo spazio di rifugio in fossa resta libero dagli ammortizzatori di cabina: il software lo mette sotto il centro della cabina o, se un piatto vi entra, nel posto libero più vicino sotto l'interno della cabina; due o più ammortizzatori di cabina a 160 mm dai fianchi della piattaforma, più in fuori finché i piatti escono dalla pianta del rifugio, sempre sotto la piattaforma; la verifica vale anche per quelli messi dal software (margine ≥ 0)</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.1.6 e 5.8.2.2.1 (corsa); la corsa ridotta di 5.8.2.2.2 non è usata</t>
+          <t>UNI EN 81-20:2020, 5.2.5.8.1</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 99; gli ammortizzatori tipici dal catalogo Oleo LSB e SEB (oleo.co.uk), estratti di ricerca del 1° ottobre 2026</t>
+          <t>scelta del software sul modello della fossa (posizioni tipiche, da confermare con i dati del fornitore degli ammortizzatori)</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso</t>
+          <t>ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
         </is>
       </c>
       <c r="I88" s="11" t="n"/>
@@ -4853,33 +4853,33 @@
       <c r="M88" s="11" t="n"/>
       <c r="N88" s="11" t="n"/>
     </row>
-    <row r="89" ht="134" customHeight="1">
+    <row r="89" ht="82" customHeight="1">
       <c r="A89" s="10" t="n">
         <v>87</v>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario — davanti al quadro il software verifica la profondità libera e che la parete sia lunga almeno quanto il maggiore tra 500 mm e il quadro; non verificati: la macchina o altro dentro quella superficie, i percorsi larghi almeno 0,50 m (5.2.6.3.2.2) e lo spazio di 0,30 m sopra le parti rotanti (5.2.6.3.2.3)</t>
+          <t>Distanze in fossa con la cabina sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>altezza libera delle zone di lavoro ≥ 2100 mm (1800 mm sui percorsi); davanti al quadro una superficie libera profonda ≥ 700 mm e larga ≥ 500 mm o quanto il quadro; per la manutenzione delle parti in movimento e la manovra di emergenza una superficie libera di almeno 500 × 600 mm (il software la cerca accanto all'argano, sul lato più libero, fino a muri e quadro); porta di accesso ≥ 600 × 2000 mm</t>
+          <t>≥ 500 mm dal pavimento della fossa alle parti più basse della cabina; grembiule sotto la soglia di cabina: tratto verticale ≥ 750 mm, poi uno smusso a ≥ 60° sull'orizzontale con proiezione orizzontale ≥ 20 mm (circa 35 mm più in basso), con ≥ 100 mm liberi dal pavimento della fossa</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.6.3.2.1 (2,10 m e superfici libere), 5.2.6.3.2.2 (1,80 m sui percorsi) e 5.2.3.2 a) (porta)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.8.2 a) e 5.4.5.1–5.4.5.2</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 29, 43; le superfici libere anche in UNI EN 81-1:1999, 6.3.2.1 (edizione 2008: 6.3.3.1)</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 40–41, 69</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>altezza del locale macchina; superficie libera davanti al quadro; superficie libera accanto all'argano; porta del locale macchina</t>
+          <t>spazio di rifugio in fossa; grembiule sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="I89" s="11" t="n"/>
@@ -4899,33 +4899,33 @@
       <c r="M89" s="11" t="n"/>
       <c r="N89" s="11" t="n"/>
     </row>
-    <row r="90" ht="69" customHeight="1">
+    <row r="90" ht="108" customHeight="1">
       <c r="A90" s="10" t="n">
         <v>88</v>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Illuminazione del vano e del locale del macchinario</t>
+          <t>Balaustra sul tetto di cabina — fino alla versione 2.12.0 del motore del vano il software misurava i 500 mm dal bordo del tetto; la norma vuole la balaustra entro 150 mm dal bordo: se è più interna, la distanza cresce e può servire l'altezza maggiore</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>vano: luce fissa, almeno 50 lux a un metro dal tetto di cabina e dal fondo della fossa, 20 lux nel resto; locale del macchinario: almeno 200 lux al pavimento dove si lavora e 50 lux sui percorsi; 50 lux anche sull'accesso al macchinario</t>
+          <t>richiesta se dal bordo esterno del tetto alla parete ci sono più di 300 mm; alta 700 mm se dal bordo interno del corrimano alla parete ci sono fino a 500 mm, 1100 mm oltre; il corrimano (30 mm) con la faccia esterna a 100 mm dal bordo del tetto, come nel 3D</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.4.1 a)–c), 5.2.1.4.2 e 5.2.2.2</t>
+          <t>UNI EN 81-20:2020, 5.4.7.2 b) e 5.4.7.4 b)–c)</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 25</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 70–72</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>balaustra sul tetto di cabina</t>
         </is>
       </c>
       <c r="I90" s="11" t="n"/>
@@ -4945,33 +4945,33 @@
       <c r="M90" s="11" t="n"/>
       <c r="N90" s="11" t="n"/>
     </row>
-    <row r="91" ht="43" customHeight="1">
+    <row r="91" ht="121" customHeight="1">
       <c r="A91" s="10" t="n">
         <v>89</v>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Temperatura dei locali del macchinario e degli armadi</t>
+          <t>Superficie dove una persona può stare sul tetto di cabina — Nella 5.2.5.7.3 lo 0,12 m² è la soglia da cui un'area conta come posto in piedi, sopra la quale serve l'altezza del rifugio; che un'area simile debba esserci lo chiedeva la UNI EN 81-1:2008 (8.13.2). Il software verifica l'area disegnata.</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>temperatura ambiente mantenuta tra +5 °C e +40 °C: ipotesi della norma, da garantire nell'edificio</t>
+          <t>area continua ≥ 0,12 m² con il lato minore oltre 250 mm (disegnata 400 × 300 mm, modificabile sulla pianta in testata); sopra di essa deve esserci l'altezza dello spazio di rifugio</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 0.4.16 (ipotesi della norma, vale anche per il vano)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.3</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 14</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 39</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>superficie per stare sul tetto di cabina</t>
         </is>
       </c>
       <c r="I91" s="11" t="n"/>
@@ -4991,43 +4991,43 @@
       <c r="M91" s="11" t="n"/>
       <c r="N91" s="11" t="n"/>
     </row>
-    <row r="92" ht="225" customHeight="1">
+    <row r="92" ht="212" customHeight="1">
       <c r="A92" s="10" t="n">
         <v>90</v>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Basamento dell'argano</t>
+          <t>Altezza libera degli accessi e della cabina — negli impianti esistenti (DPR 1497/1963, artt. 24, 27 e 29, non riletto) le porte possono essere alte 1,90 m e la cabina 2,00 m; con la sola sostituzione della macchina le altezze restano (parti esistenti); la UNI 10411-1:2024 ammette porte di piano nuove non più basse delle esistenti (19.1), una cabina nuova sotto 2 m se non più bassa dell'esistente e mai sotto 1,90 m (22 m)) e accessi di cabina mai sotto 1,80 m (22 n)), con avvertimenti: il software non conosce le esistenti e segnala ogni porta sotto 2000 mm</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>su spessori di livellamento sotto gli appoggi (l'asse della puleggia dove lo mette il software), su telaio di due profilati sul pavimento (tipico UPN 200, alto quanto il profilato come i telai bassi universali), su due putrelle da muro a muro che possono stare sollevate dal pavimento (tipiche IPE 200, appoggio nei muri 150 mm), su piastre d'acciaio sotto gli appoggi (tipiche 20 mm) o su plinto in calcestruzzo (tipico 250 mm), o — con un rinvio — sul telaio con rinvio (locale.rinvio); tamponi antivibranti di 30 mm sotto gli appoggi, salvo sugli spessori e sul telaio con rinvio (antivibranti sotto le gambe); telaio e plinto 100 mm oltre il telaio dell'argano a ogni estremità; l'altezza del basamento porta l'asse della puleggia, che il calcolo (tratto di fune oltre la corsa) e il 3D seguono</t>
+          <t>luce netta in altezza delle porte di piano e di cabina ≥ 2000 mm; altezza libera interna della cabina ≥ 2000 mm</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio); scelta del costruttore</t>
+          <t>UNI EN 81-20:2020, 5.3.2.1 e 5.4.1</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>telaio basso universale per argano alto 200 mm (lift-store.it); tamponi antivibranti 25–30 mm (catalogo Donati); piastre di 20 mm e plinto di 250–300 mm nella pratica di installazione (fonti estere, da confermare); estratti di ricerca del 1° ottobre 2026</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 49, 63; 2 m anche in DM 587/1987 (UNI EN 81-1), 7.3.1, 8.1.1 e 8.1.2</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>altezza libera degli accessi; altezza libera interna della cabina</t>
         </is>
       </c>
       <c r="I92" s="11" t="n"/>
@@ -5037,43 +5037,43 @@
       <c r="M92" s="11" t="n"/>
       <c r="N92" s="11" t="n"/>
     </row>
-    <row r="93" ht="147" customHeight="1">
+    <row r="93" ht="160" customHeight="1">
       <c r="A93" s="10" t="n">
         <v>91</v>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Telaio sotto l'argano di un costruttore</t>
+          <t>Corsa guidata in testata (contrappeso e cabina)</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>l'argano di catalogo poggia con i suoi piedi su un telaio di due travi sotto le file di fori, con antivibranti alle estremità e 40 mm oltre l'argano a ogni estremità; il telaio è alto quanto serve per tenere l'asse della puleggia dove lo tiene l'argano generico del software, almeno 80 mm e con il bordo della puleggia 30 mm sopra il suo piano d'appoggio (gli argani compatti hanno la puleggia a sbalzo, sotto il piano dei piedi); se l'argano non lo permette l'asse sale e il calcolo segue</t>
+          <t>con la cabina sugli ammortizzatori completamente compressi le guide del contrappeso lo guidano ancora per almeno 0,1 + 0,035·v² m (v velocità nominale): dalla sommità del contrappeso, salito della corsa sotto la cabina (extracorsa e corsa degli ammortizzatori), alla sommità delle guide, che il software pone 50 mm sotto la soletta (voce foglio.stime); la cabina nella sua posizione più alta (salto compreso) ha ancora almeno 0,1 m di guida sopra la sommità dell'arcata, dove il software mette i pattini superiori (avviso: l'altezza reale dei pattini è del fornitore)</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.2.5.6.2 e 5.2.5.6.1.1 (Prospetto 2: cabina sugli ammortizzatori compressi più 0,035·v²); stesso valore in UNI EN 81-1 (1999, 2008), 5.7.1.2</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>quote dei piedi, dei fori e dell'asse della puleggia dalle schede tecniche del costruttore; altezza del telaio scelta dal software, da adattare al telaio fornito</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 36; UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 27</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>corsa guidata del contrappeso in testata; corsa guidata della cabina in testata</t>
         </is>
       </c>
       <c r="I93" s="11" t="n"/>
@@ -5083,43 +5083,43 @@
       <c r="M93" s="11" t="n"/>
       <c r="N93" s="11" t="n"/>
     </row>
-    <row r="94" ht="303" customHeight="1">
+    <row r="94" ht="95" customHeight="1">
       <c r="A94" s="10" t="n">
         <v>92</v>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Puleggia di rinvio nel locale del macchinario</t>
+          <t>Schermo del contrappeso in fossa — non verificati: il bordo inferiore dello schermo a non più di 300 mm dal fondo della fossa (5.2.5.5.1 c)) e la protezione dello spazio oltre 300 mm tra guide del contrappeso e parete (e))</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>con l'argano in alto il rinvio sta sempre nel locale del macchinario, mai nel vano: nel telaio dell'argano (il basamento che il software prende quando c'è un rinvio), con l'asse del rinvio a 320 mm dal pavimento (il bordo almeno 60 mm sopra il pavimento: Dp/2 + 60 oltre Ø 520), il piano del telaio a 736 mm (almeno 176 mm sopra il rinvio), gambe di tubo quadro da 80 mm su antivibranti da 28 mm, travi UPN 160, 100 mm oltre l'argano e il rinvio a ogni estremità, largo almeno 655 mm; con un argano SICOR che ha il suo telaio a catalogo (SV110 e SH110B XTE0517/XTE0516, SH130 e SH130G XTE3022/XTE3023, SH140 XTE6026/XTE6027, SH160 XTE5708, SH190 XTE3988) le quote del costruttore: asse del rinvio, asse della puleggia (A), piano del telaio (A − B), calata del contrappeso entro L max dall'asse della puleggia (verifica di avvertimento: oltre, telaio su misura); h del calcolo = asse della puleggia − asse del rinvio, dx dalla pianta; con un altro basamento scelto il rinvio sta su un supporto proprio sul pavimento, alla stessa altezza; una h inserita a mano che porta il rinvio sotto il pavimento è segnalata</t>
+          <t>dal punto più basso del contrappeso sugli ammortizzatori compressi fino ad almeno 2000 mm sopra il pavimento della fossa (altezza dello schermo modificabile sul progetto, mai sotto questo valore)</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>regola del committente (Panev): il rinvio sta nel telaio del locale macchine, mai nel vano; UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.5.1 b)</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>brochure Geared SICOR, aprile 2026, pp. 16, 23, 41, 47, 58, 68 e 80 (telai «top machine with diverting pulley for CSW wrapping»), letta il 2 ottobre 2026; i telai «corti» MR21, MR26 e MR35 portano il rinvio sotto il pavimento (Hmin = Dt/2 + 75) e non sono usati; le quote del telaio del software sono quelle dei telai SICOR, da adattare al telaio fornito</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 35</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>calata del contrappeso nel telaio con rinvio del costruttore</t>
+          <t>protezione del contrappeso in fossa</t>
         </is>
       </c>
       <c r="I94" s="11" t="n"/>
@@ -5129,43 +5129,43 @@
       <c r="M94" s="11" t="n"/>
       <c r="N94" s="11" t="n"/>
     </row>
-    <row r="95" ht="134" customHeight="1">
+    <row r="95" ht="95" customHeight="1">
       <c r="A95" s="10" t="n">
         <v>93</v>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>L'argano dentro il locale del macchinario</t>
+          <t>Ammortizzatori ad accumulo di energia lineari (molle)</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>l'argano sul suo basamento — con il telaio del rinvio o con il supporto del rinvio — sta dentro il locale in pianta e sotto il soffitto: la distanza minima dai muri e dal soffitto non è negativa; ingombri dalle quote del costruttore per gli argani disegnati com'è, dall'argano generico del software (scalato alla puleggia) per gli altri; la puleggia di rinvio sul suo supporto sotto l'argano libera il basamento dell'argano sopra di essa (solo le putrelle sollevate la scavalcano)</t>
+          <t>ammessi fino a 1 m/s; corsa ≥ 0,135·v² m e comunque ≥ 65 mm; extracorsa della cabina e del contrappeso ≥ 0 (nessun minimo nella norma)</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.8.1.5 (fino a 1 m/s) e 5.8.2.1.1.1 (corsa); nessuna extracorsa minima in metri: l'interruttore di extracorsa interviene prima che la cabina o il contrappeso tocchino gli ammortizzatori (5.12.2.1)</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>geometria del progetto: la pianta e l'altezza del locale inserite, gli ingombri dell'argano e del basamento</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 98, 131</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>argano dentro il locale (muri e soffitto); puleggia di rinvio sul suo supporto sotto l'argano</t>
+          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso; extracorsa di cabina e contrappeso</t>
         </is>
       </c>
       <c r="I95" s="11" t="n"/>
@@ -5175,43 +5175,43 @@
       <c r="M95" s="11" t="n"/>
       <c r="N95" s="11" t="n"/>
     </row>
-    <row r="96" ht="134" customHeight="1">
+    <row r="96" ht="121" customHeight="1">
       <c r="A96" s="10" t="n">
         <v>94</v>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
+          <t>Ammortizzatori ad accumulo di energia non lineari (tamponi in poliuretano) — il tampone tipico alto 80 mm è un dato di catalogo, non della norma: va sostituito con quello montato</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
+          <t>ammessi fino a 1 m/s come le molle; nessuna corsa minima da formula: il campo di masse del certificato di esame di tipo per la velocità deve comprendere, per ogni tampone, la cabina vuota e a pieno carico (o il contrappeso); «completamente compresso» vuol dire compresso del 90 % dell'altezza, quindi la corsa è 0,9·H negli spazi in fossa e in testata; tampone tipico alti 80 mm (P+S Diepocell D, Ø da 80 a 220 mm; ACLA AUTAN XL)</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E), §3.1.4 (carichi del macchinario); DPR 1497/1963, art. 5.1–5.2 (carichi fissi più 1,5 volte il carico statico delle funi, sicurezza ≥ 6, freccia ≤ 1/1500 della luce libera: regola storica degli impianti esistenti, letta su Normattiva)</t>
+          <t>UNI EN 81-20:2020, 5.8.1.5, 5.8.1.7, 5.8.2.1.2.1 e 5.8.2.1.2.2 (compresso al 90 %); UNI EN 81-50:2020, 5.5.4 (esame di tipo)</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 98–99; UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 24; il tampone tipico dai cataloghi P+S Diepocell (wwlift.de) e ACLA AUTAN XL (acla.de), estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso</t>
         </is>
       </c>
       <c r="I96" s="11" t="n"/>
@@ -5221,43 +5221,43 @@
       <c r="M96" s="11" t="n"/>
       <c r="N96" s="11" t="n"/>
     </row>
-    <row r="97" ht="147" customHeight="1">
+    <row r="97" ht="95" customHeight="1">
       <c r="A97" s="10" t="n">
         <v>95</v>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Sostituzione dell'argano: calate esistenti e calate della nuova macchina</t>
+          <t>Ammortizzatori a dissipazione di energia (idraulici) — gli ammortizzatori Oleo sono dati di catalogo, non della norma: vanno sostituiti con quelli montati</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>nella sola sostituzione dell'argano la cabina e il contrappeso restano dove sono: le funi della nuova macchina devono scendere sulle calate esistenti, rilevate nel locale dall'angolo interno del vano. La distanza tra le calate data dal calcolo (rinvio: D/2 + dx ± Dp/2, più Dp in taglia 2:1; tiro diretto: il diametro della puleggia esistente, se inserita, altrimenti della nuova, più Dp in taglia 2:1) e quella misurata differiscono al più di 10 mm; oltre, il calcolo va ripetuto con la geometria misurata (dx, puleggia esistente)</t>
+          <t>a ogni velocità; corsa ≥ 0,0674·v² m (arresto per gravità al 115 % della velocità nominale); la corsa ridotta con il controllo del rallentamento non è considerata; ammortizzatori tipici: Oleo LSB10 fino a 1 m/s, alto 222,2 mm con corsa 73,4 mm; LSB16 fino a 1,6 m/s, alto 485,5 mm con corsa 173,5 mm</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.8.1.6 e 5.8.2.2.1 (corsa); la corsa ridotta di 5.8.2.2.2 non è usata</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>tolleranza scelta dal software per il rilievo in sito (le funi a qualche metro dal basamento): da confermare con l'installatore</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 99; gli ammortizzatori tipici dal catalogo Oleo LSB e SEB (oleo.co.uk), estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>sostituzione: calate della nuova macchina sulle calate esistenti</t>
+          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso</t>
         </is>
       </c>
       <c r="I97" s="11" t="n"/>
@@ -5273,27 +5273,27 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Carichi sul pavimento della fossa — non calcolato: con spazi accessibili sotto il vano (5.2.5.4) il contrappeso ha il paracadute, sotto le sue guide va anche k1·g·M_cw/n e il fondo della fossa regge almeno 5000 N/m². P è la cabina vuota: la quota del cavo flessibile e della compensazione, che la 5.2.1.8.5 conta in P, va aggiunta dall'ingegnere</t>
+          <t>Locale del macchinario — davanti al quadro il software verifica la profondità libera e che la parete sia lunga almeno quanto il maggiore tra 500 mm e il quadro; non verificati: la macchina o altro dentro quella superficie, i percorsi larghi almeno 0,50 m (5.2.6.3.2.2) e lo spazio di 0,30 m sopra le parti rotanti (5.2.6.3.2.3)</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
+          <t>altezza libera delle zone di lavoro ≥ 2100 mm (1800 mm sui percorsi); davanti al quadro una superficie libera profonda ≥ 700 mm e larga ≥ 500 mm o quanto il quadro; per la manutenzione delle parti in movimento e la manovra di emergenza una superficie libera di almeno 500 × 600 mm (il software la cerca accanto all'argano, sul lato più libero, fino a muri e quadro); porta di accesso ≥ 600 × 2000 mm</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.8.4–5.2.1.8.6, 5.7.2.3.5 e Prospetto 14 (k1)</t>
+          <t>UNI EN 81-20:2020, 5.2.6.3.2.1 (2,10 m e superfici libere), 5.2.6.3.2.2 (1,80 m sui percorsi) e 5.2.3.2 a) (porta)</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 27, 94–96</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 29, 43; le superfici libere anche in UNI EN 81-1:1999, 6.3.2.1 (edizione 2008: 6.3.3.1)</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>altezza del locale macchina; superficie libera davanti al quadro; superficie libera accanto all'argano; porta del locale macchina</t>
         </is>
       </c>
       <c r="I98" s="11" t="n"/>
@@ -5313,33 +5313,33 @@
       <c r="M98" s="11" t="n"/>
       <c r="N98" s="11" t="n"/>
     </row>
-    <row r="99" ht="108" customHeight="1">
+    <row r="99" ht="69" customHeight="1">
       <c r="A99" s="10" t="n">
         <v>97</v>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Spinte sulle guide di cabina — h, la distanza tra i pattini, è una stima del software (l'ingombro verticale dell'arcata)</t>
+          <t>Illuminazione del vano e del locale del macchinario</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
+          <t>vano: luce fissa, almeno 50 lux a un metro dal tetto di cabina e dal fondo della fossa, 20 lux nel resto; locale del macchinario: almeno 200 lux al pavimento dove si lavora e 50 lux sui percorsi; 50 lux anche sull'accesso al macchinario</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, appendice C (informativa), C.2.1.1 e C.2.2.1; UNI EN 81-20:2020, 5.7.2.3.4 (portata su 3/4 della superficie: 1/8) e Prospetto 14 (k1; k2 = 1,2)</t>
+          <t>UNI EN 81-20:2020, 5.2.1.4.1 a)–c), 5.2.1.4.2 e 5.2.2.2</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 77–79; UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 94–96</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 25</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
@@ -5359,38 +5359,38 @@
       <c r="M99" s="11" t="n"/>
       <c r="N99" s="11" t="n"/>
     </row>
-    <row r="100" ht="82" customHeight="1">
+    <row r="100" ht="43" customHeight="1">
       <c r="A100" s="10" t="n">
         <v>98</v>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Carico della macchina sulla soletta</t>
+          <t>Temperatura dei locali del macchinario e degli armadi</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
+          <t>temperatura ambiente mantenuta tra +5 °C e +40 °C: ipotesi della norma, da garantire nell'edificio</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 0.4.16 (ipotesi della norma, vale anche per il vano)</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 14</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>prassi di cantiere</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H100" s="10" t="inlineStr">
@@ -5405,38 +5405,38 @@
       <c r="M100" s="11" t="n"/>
       <c r="N100" s="11" t="n"/>
     </row>
-    <row r="101" ht="43" customHeight="1">
+    <row r="101" ht="225" customHeight="1">
       <c r="A101" s="10" t="n">
         <v>99</v>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Massa dei cavi flessibili</t>
+          <t>Basamento dell'argano</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
+          <t>su spessori di livellamento sotto gli appoggi (l'asse della puleggia dove lo mette il software), su telaio di due profilati sul pavimento (tipico UPN 200, alto quanto il profilato come i telai bassi universali), su due putrelle da muro a muro che possono stare sollevate dal pavimento (tipiche IPE 200, appoggio nei muri 150 mm), su piastre d'acciaio sotto gli appoggi (tipiche 20 mm) o su plinto in calcestruzzo (tipico 250 mm), o — con un rinvio — sul telaio con rinvio (locale.rinvio); tamponi antivibranti di 30 mm sotto gli appoggi, salvo sugli spessori e sul telaio con rinvio (antivibranti sotto le gambe); telaio e plinto 100 mm oltre il telaio dell'argano a ogni estremità; l'altezza del basamento porta l'asse della puleggia, che il calcolo (tratto di fune oltre la corsa) e il 3D seguono</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio); scelta del costruttore</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
+          <t>telaio basso universale per argano alto 200 mm (lift-store.it); tamponi antivibranti 25–30 mm (catalogo Donati); piastre di 20 mm e plinto di 250–300 mm nella pratica di installazione (fonti estere, da confermare); estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H101" s="10" t="inlineStr">
@@ -5451,33 +5451,33 @@
       <c r="M101" s="11" t="n"/>
       <c r="N101" s="11" t="n"/>
     </row>
-    <row r="102" ht="121" customHeight="1">
+    <row r="102" ht="147" customHeight="1">
       <c r="A102" s="10" t="n">
         <v>100</v>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
+          <t>Telaio sotto l'argano di un costruttore</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
+          <t>l'argano di catalogo poggia con i suoi piedi su un telaio di due travi sotto le file di fori, con antivibranti alle estremità e 40 mm oltre l'argano a ogni estremità; il telaio è alto quanto serve per tenere l'asse della puleggia dove lo tiene l'argano generico del software, almeno 80 mm e con il bordo della puleggia 30 mm sopra il suo piano d'appoggio (gli argani compatti hanno la puleggia a sbalzo, sotto il piano dei piedi); se l'argano non lo permette l'asse sale e il calcolo segue</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>regola di montaggio indicata dal committente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>scelta del committente</t>
+          <t>quote dei piedi, dei fori e dell'asse della puleggia dalle schede tecniche del costruttore; altezza del telaio scelta dal software, da adattare al telaio fornito</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
@@ -5497,43 +5497,43 @@
       <c r="M102" s="11" t="n"/>
       <c r="N102" s="11" t="n"/>
     </row>
-    <row r="103" ht="82" customHeight="1">
+    <row r="103" ht="303" customHeight="1">
       <c r="A103" s="10" t="n">
         <v>101</v>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Lunghezze stimate nel foglio dei dati</t>
+          <t>Puleggia di rinvio nel locale del macchinario</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
+          <t>con l'argano in alto il rinvio sta sempre nel locale del macchinario, mai nel vano: nel telaio dell'argano (il basamento che il software prende quando c'è un rinvio), con l'asse del rinvio a 320 mm dal pavimento (il bordo almeno 60 mm sopra il pavimento: Dp/2 + 60 oltre Ø 520), il piano del telaio a 736 mm (almeno 176 mm sopra il rinvio), gambe di tubo quadro da 80 mm su antivibranti da 28 mm, travi UPN 160, 100 mm oltre l'argano e il rinvio a ogni estremità, largo almeno 655 mm; con un argano SICOR che ha il suo telaio a catalogo (SV110 e SH110B XTE0517/XTE0516, SH130 e SH130G XTE3022/XTE3023, SH140 XTE6026/XTE6027, SH160 XTE5708, SH190 XTE3988) le quote del costruttore: asse del rinvio, asse della puleggia (A), piano del telaio (A − B), calata del contrappeso entro L max dall'asse della puleggia (verifica di avvertimento: oltre, telaio su misura); h del calcolo = asse della puleggia − asse del rinvio, dx dalla pianta; con un altro basamento scelto il rinvio sta su un supporto proprio sul pavimento, alla stessa altezza; una h inserita a mano che porta il rinvio sotto il pavimento è segnalata</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>regola del committente (Panev): il rinvio sta nel telaio del locale macchine, mai nel vano; UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio)</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>stima del software, da sostituire con le misure di cantiere</t>
+          <t>brochure Geared SICOR, aprile 2026, pp. 16, 23, 41, 47, 58, 68 e 80 (telai «top machine with diverting pulley for CSW wrapping»), letta il 2 ottobre 2026; i telai «corti» MR21, MR26 e MR35 portano il rinvio sotto il pavimento (Hmin = Dt/2 + 75) e non sono usati; le quote del telaio del software sono quelle dei telai SICOR, da adattare al telaio fornito</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>calata del contrappeso nel telaio con rinvio del costruttore</t>
         </is>
       </c>
       <c r="I103" s="11" t="n"/>
@@ -5543,43 +5543,43 @@
       <c r="M103" s="11" t="n"/>
       <c r="N103" s="11" t="n"/>
     </row>
-    <row r="104" ht="342" customHeight="1">
+    <row r="104" ht="134" customHeight="1">
       <c r="A104" s="10" t="n">
         <v>102</v>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Verifica delle guide di cabina — Confermati sul testo i coefficienti, le formule e i limiti. Da verificare il carico al piano: la UNI EN 81-20:2020 (5.7.2.3.6) lo lega al tipo di ascensore, 0,4·g·Q per persone, 0,6·g·Q per merci, 0,85·g·Q con dispositivi di movimentazione pesanti; il software usa la regola della UNI EN 81-1:2008 (0,6·g·Q da 2500 kg, appendice G.2.5) perché il tipo di ascensore non è tra i dati. La formula di ω per Rm 370 è data da λ 20 a 250: sotto 20 il software usa ω di λ 20 (dal lato della sicurezza). Non contate: la spinta di scorrimento delle staffe (assestamento dell'edificio), le apparecchiature appese alle guide, le frecce di staffe ed edificio (la norma vuole la somma entro il limite) e le guide del contrappeso. La flessione della suola è quella dei pattini a rotelle (5.10.5 ha una formula a parte per quelli a scorrimento; il tipo di pattino non è un dato del software).</t>
+          <t>L'argano dentro il locale del macchinario</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>tra due staffe (l = distanza massima tra le staffe della guida) con le spinte della voce guide.spinte, portata spostata di 1/8 della cabina in un senso e poi nell'altro: flessione M = 3·F·l/16, σm = σx + σy; intervento del paracadute: forza verticale Fv = k1·g·(P+Q)/n più il peso della guida, carico di punta con il metodo omega (λ = l/i con il raggio d'inerzia minore √(I/A), λ ≤ 250; acciaio Rm 370: ω = 0,0001292·λ^1,89 + 1 fino a λ 60, 0,00004627·λ^2,14 + 1 fino a 85, 0,00001711·λ^2,35 + 1,04 fino a 115, 0,00016887·λ^2 fino a 250), σ = σm + Fv/A e σc = σk + 0,9·σm; marcia: k2 = 1,2 e il peso della guida; carico al piano: cabina vuota e Fs = 0,4·g·Q (0,6·g·Q da 2500 kg) al centro della soglia di cabina, a ogni accesso; flessione della suola σF = 1,85·Fx/c² (pattini a rotelle); frecce δx = 0,7·Fx·l³/(48·E·Iy) e δy = 0,7·Fy·l³/(48·E·Ix) ≤ 5 mm. Tensione ammissibile Rm/St con St = 2,25 in marcia e al carico, 1,8 all'intervento del paracadute (allungamento A5 &gt; 12 %): con Rm 370 N/mm², 164,4 e 205,6 N/mm²</t>
+          <t>l'argano sul suo basamento — con il telaio del rinvio o con il supporto del rinvio — sta dentro il locale in pianta e sotto il soffitto: la distanza minima dai muri e dal soffitto non è negativa; ingombri dalle quote del costruttore per gli argani disegnati com'è, dall'argano generico del software (scalato alla puleggia) per gli altri; la puleggia di rinvio sul suo supporto sotto l'argano libera il basamento dell'argano sopra di essa (solo le putrelle sollevate la scavalcano)</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.10.2–5.10.6; UNI EN 81-20:2020, 5.7.2.3.5, 5.7.2.3.6, 5.7.4.5 (Prospetto 15), 5.7.4.6 e Prospetto 14</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 35–39; UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 94–97; Rm 370 è scelta del software (il valore più basso)</t>
+          <t>geometria del progetto: la pianta e l'altezza del locale inserite, gli ingombri dell'argano e del basamento</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>tensioni nelle guide di cabina; flessione della suola delle guide di cabina; frecce delle guide di cabina</t>
+          <t>argano dentro il locale (muri e soffitto); puleggia di rinvio sul suo supporto sotto l'argano</t>
         </is>
       </c>
       <c r="I104" s="11" t="n"/>
@@ -5589,33 +5589,33 @@
       <c r="M104" s="11" t="n"/>
       <c r="N104" s="11" t="n"/>
     </row>
-    <row r="105" ht="147" customHeight="1">
+    <row r="105" ht="134" customHeight="1">
       <c r="A105" s="10" t="n">
         <v>103</v>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Sezioni delle guide di cabina</t>
+          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>area, momenti d'inerzia e moduli di resistenza minimi attorno all'asse parallelo alla suola (x) e all'asse di simmetria (y), spessore c del collo tra lama e suola, per ogni profilo del software; raggi d'inerzia calcolati come √(I/A)</t>
+          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
         </is>
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>ISO 7465:2007 (ora ISO 8100-33:2022); EN 10055:1995 per il T 70×70×8 laminato</t>
+          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E), §3.1.4 (carichi del macchinario); DPR 1497/1963, art. 5.1–5.2 (carichi fissi più 1,5 volte il carico statico delle funi, sicurezza ≥ 6, freccia ≤ 1/1500 della luce libera: regola storica degli impianti esistenti, letta su Normattiva)</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>tabella ISO 7465:2007 stampata da Savera (Standard Savera Guide, Rev 03/10; assi e c dalla Rev 08.26), anteprime ISO 7465:1997 e ISO 8100-33:2022 (correzione dei raggi del T127-1/B, stampati nel 2007 uguali ai moduli), EN 10055:1995, Tabella 1. La EN 10055 non ha il T 45: al T 45×45×5 il software dà la sezione del T45/A, delle stesse misure</t>
+          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
         </is>
       </c>
       <c r="I105" s="11" t="n"/>
@@ -5635,43 +5635,43 @@
       <c r="M105" s="11" t="n"/>
       <c r="N105" s="11" t="n"/>
     </row>
-    <row r="106" ht="69" customHeight="1">
+    <row r="106" ht="147" customHeight="1">
       <c r="A106" s="10" t="n">
         <v>104</v>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Tipo di paracadute per la velocità nominale</t>
+          <t>Sostituzione dell'argano: calate esistenti e calate della nuova macchina</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>istantaneo (anche a rulli imprigionati) fino a 0,63 m/s; oltre, progressivo (la UNI EN 81-20 non ha più l'istantaneo con effetto ammortizzato fino a 1 m/s); il tipo viene dai dati dell'impianto (se manca: progressivo, con la nota sul foglio)</t>
+          <t>nella sola sostituzione dell'argano la cabina e il contrappeso restano dove sono: le funi della nuova macchina devono scendere sulle calate esistenti, rilevate nel locale dall'angolo interno del vano. La distanza tra le calate data dal calcolo (rinvio: D/2 + dx ± Dp/2, più Dp in taglia 2:1; tiro diretto: il diametro della puleggia esistente, se inserita, altrimenti della nuova, più Dp in taglia 2:1) e quella misurata differiscono al più di 10 mm; oltre, il calcolo va ripetuto con la geometria misurata (dx, puleggia esistente)</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.6.2.1.2.1; la regola precedente in UNI EN 81-1 (1999, 2008), 9.8.2.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 81; UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 58</t>
+          <t>tolleranza scelta dal software per il rilievo in sito (le funi a qualche metro dal basamento): da confermare con l'installatore</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>tipo di paracadute per la velocità</t>
+          <t>sostituzione: calate della nuova macchina sulle calate esistenti</t>
         </is>
       </c>
       <c r="I106" s="11" t="n"/>
@@ -5681,38 +5681,38 @@
       <c r="M106" s="11" t="n"/>
       <c r="N106" s="11" t="n"/>
     </row>
-    <row r="107" ht="43" customHeight="1">
+    <row r="107" ht="134" customHeight="1">
       <c r="A107" s="10" t="n">
         <v>105</v>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Dimensioni proposte della cabina</t>
+          <t>Carichi sul pavimento della fossa — non calcolato: con spazi accessibili sotto il vano (5.2.5.4) il contrappeso ha il paracadute, sotto le sue guide va anche k1·g·M_cw/n e il fondo della fossa regge almeno 5000 N/m². P è la cabina vuota: la quota del cavo flessibile e della compensazione, che la 5.2.1.8.5 conta in P, va aggiunta dall'ingegnere</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
+          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8.4–5.2.1.8.6, 5.7.2.3.5 e Prospetto 14 (k1)</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 27, 94–96</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
@@ -5727,43 +5727,43 @@
       <c r="M107" s="11" t="n"/>
       <c r="N107" s="11" t="n"/>
     </row>
-    <row r="108" ht="225" customHeight="1">
+    <row r="108" ht="108" customHeight="1">
       <c r="A108" s="10" t="n">
         <v>106</v>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Quote della pianta fissate a mano</t>
+          <t>Spinte sulle guide di cabina — h, la distanza tra i pattini, è una stima del software (l'ingombro verticale dell'arcata)</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8.1), quello del contrappeso dentro la lunghezza del contrappeso (la stessa verifica vale per quelli messi dal software: ammortizzatori.posizione)</t>
+          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, appendice C (informativa), C.2.1.1 e C.2.2.1; UNI EN 81-20:2020, 5.7.2.3.4 (portata su 3/4 della superficie: 1/8) e Prospetto 14 (k1; k2 = 1,2)</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 77–79; UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 94–96</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H108" s="10" t="inlineStr">
         <is>
-          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I108" s="11" t="n"/>
@@ -5779,17 +5779,17 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Limiti del modello del vano</t>
+          <t>Carico della macchina sulla soletta</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
+          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
         </is>
       </c>
       <c r="E109" s="10" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>limite del modello attuale</t>
+          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>prassi di cantiere</t>
         </is>
       </c>
       <c r="H109" s="10" t="inlineStr">
@@ -5819,38 +5819,38 @@
       <c r="M109" s="11" t="n"/>
       <c r="N109" s="11" t="n"/>
     </row>
-    <row r="110" ht="238" customHeight="1">
+    <row r="110" ht="43" customHeight="1">
       <c r="A110" s="10" t="n">
         <v>108</v>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Verifiche che il software non calcola</t>
+          <t>Massa dei cavi flessibili</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>da fare a parte, con i dati dei fornitori: sollecitazioni e frecce delle staffe e delle guide del contrappeso (UNI EN 81-50:2020, 5.10: il software verifica le guide di cabina, sul foglio 1 delle tavole); puleggia del contrappeso in taglia 2:1 sotto il soffitto; paracadute del contrappeso con spazi accessibili sotto il vano; distanza tra le parti fisse più alte della fossa e quelle più basse della cabina sugli ammortizzatori; sporgenze nel vano oltre 150 mm senza balaustra; locale della macchina in basso (dimensioni e spazi di manovra: il software non lo disegna); movimento incontrollato della cabina (UCM) e velocità eccessiva in salita con la nuova macchina; muro sotto la soglia di piano (5.2.5.3.2 a)); le soluzioni della UNI EN 81-21:2022 per testata, fossa, locale e porte ridotti (le verifiche in sezione seguono solo la UNI EN 81-20:2020)</t>
+          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020: guide e staffe 5.7.2–5.7.4 (con UNI EN 81-50:2020, 5.10); distanze in testata 5.2.5.7.2; spazi accessibili sotto il vano 5.2.5.4; parti fisse in fossa 5.2.5.8.2; sporgenze oltre 0,15 m 5.2.5.2.2.2; locale del macchinario 5.2.6.3; velocità eccessiva in salita 5.6.6; movimento incontrollato 5.6.7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 31–43, 89–97; analisi delle lacune del 2026-10-03</t>
+          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
@@ -5865,38 +5865,38 @@
       <c r="M110" s="11" t="n"/>
       <c r="N110" s="11" t="n"/>
     </row>
-    <row r="111" ht="56" customHeight="1">
+    <row r="111" ht="121" customHeight="1">
       <c r="A111" s="10" t="n">
         <v>109</v>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Corsa</t>
+          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
+          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>regola di montaggio indicata dal committente</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>dati dei piani inseriti</t>
+          <t>scelta del committente</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H111" s="10" t="inlineStr">
@@ -5911,38 +5911,38 @@
       <c r="M111" s="11" t="n"/>
       <c r="N111" s="11" t="n"/>
     </row>
-    <row r="112" ht="121" customHeight="1">
+    <row r="112" ht="82" customHeight="1">
       <c r="A112" s="10" t="n">
         <v>110</v>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Portata e velocità — In una modifica la UNI 10411-1:2024 (6.1, prospetto 1) tratta come aumento della portata oltre il 10 % (Q fino a 500 kg) o il 5 % (oltre) e del carico totale oltre il 15 % o il 10 %; la UNI 10411-11:2024 (6.1) ogni aumento del carico totale: il confronto con la portata originale lo fa l'ingegnere.</t>
+          <t>Lunghezze stimate nel foglio dei dati</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
+          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.2.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>progetto del vano</t>
+          <t>stima del software, da sostituire con le misure di cantiere</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
@@ -5957,43 +5957,43 @@
       <c r="M112" s="11" t="n"/>
       <c r="N112" s="11" t="n"/>
     </row>
-    <row r="113" ht="316" customHeight="1">
+    <row r="113" ht="342" customHeight="1">
       <c r="A113" s="10" t="n">
         <v>111</v>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Normativa di collaudo e parti sostituite o modificate — lo scopo delle due UNI 10411 e i requisiti per la sostituzione del macchinario (punto 14) sono letti sul testo (voce sostituzione.adeguamenti); quali verifiche riguardano ciascuna parte e la matrice delle norme compatibili sono una lettura del software, da approvare dall'ingegnere</t>
+          <t>Verifica delle guide di cabina — Confermati sul testo i coefficienti, le formule e i limiti. Da verificare il carico al piano: la UNI EN 81-20:2020 (5.7.2.3.6) lo lega al tipo di ascensore, 0,4·g·Q per persone, 0,6·g·Q per merci, 0,85·g·Q con dispositivi di movimentazione pesanti; il software usa la regola della UNI EN 81-1:2008 (0,6·g·Q da 2500 kg, appendice G.2.5) perché il tipo di ascensore non è tra i dati. La formula di ω per Rm 370 è data da λ 20 a 250: sotto 20 il software usa ω di λ 20 (dal lato della sicurezza). Non contate: la spinta di scorrimento delle staffe (assestamento dell'edificio), le apparecchiature appese alle guide, le frecce di staffe ed edificio (la norma vuole la somma entro il limite) e le guide del contrappeso. La flessione della suola è quella dei pattini a rotelle (5.10.5 ha una formula a parte per quelli a scorrimento; il tipo di pattino non è un dato del software).</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico a frizione non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (a frizione, conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software. Alla norma base si aggiungono le norme compatibili (matrice della ricerca, cap. 16 §5.2): sull'impianto nuovo le EN 81 supplementari (21, 28, 58, 70, 71, 72, 73, 76, 77), sulla modifica la EN 81-20/50 intera, le EN 81-28, 58, 73 e il miglioramento (80, 82, 83), su entrambi DM 236/1989, antincendio (DM 15/09/2005 o Codice V.3) e NTC 2018 (con le verifiche delle putrelle). Ogni norma ha il suo esito («non calcolata» se il software non ne calcola verifiche) e i suoi punti da verificare in sito nella relazione, con gli adempimenti del DPR 162/1999</t>
+          <t>tra due staffe (l = distanza massima tra le staffe della guida) con le spinte della voce guide.spinte, portata spostata di 1/8 della cabina in un senso e poi nell'altro: flessione M = 3·F·l/16, σm = σx + σy; intervento del paracadute: forza verticale Fv = k1·g·(P+Q)/n più il peso della guida, carico di punta con il metodo omega (λ = l/i con il raggio d'inerzia minore √(I/A), λ ≤ 250; acciaio Rm 370: ω = 0,0001292·λ^1,89 + 1 fino a λ 60, 0,00004627·λ^2,14 + 1 fino a 85, 0,00001711·λ^2,35 + 1,04 fino a 115, 0,00016887·λ^2 fino a 250), σ = σm + Fv/A e σc = σk + 0,9·σm; marcia: k2 = 1,2 e il peso della guida; carico al piano: cabina vuota e Fs = 0,4·g·Q (0,6·g·Q da 2500 kg) al centro della soglia di cabina, a ogni accesso; flessione della suola σF = 1,85·Fx/c² (pattini a rotelle); frecce δx = 0,7·Fx·l³/(48·E·Iy) e δy = 0,7·Fy·l³/(48·E·Ix) ≤ 5 mm. Tensione ammissibile Rm/St con St = 2,25 in marcia e al carico, 1,8 all'intervento del paracadute (allungamento A5 &gt; 12 %): con Rm 370 N/mm², 164,4 e 205,6 N/mm²</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
+          <t>UNI EN 81-50:2020, 5.10.2–5.10.6; UNI EN 81-20:2020, 5.7.2.3.5, 5.7.2.3.6, 5.7.4.5 (Prospetto 15), 5.7.4.6 e Prospetto 14</t>
         </is>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, testo della norma, letto il 2026-10-06, pp. 5, 13–14; UNI 10411-11:2024, testo della norma, letto il 2026-10-06, pp. 5, 12; schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); ricerca, capitoli 2.4 e 6.6</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 35–39; UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 94–97; Rm 370 è scelta del software (il valore più basso)</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tensioni nelle guide di cabina; flessione della suola delle guide di cabina; frecce delle guide di cabina</t>
         </is>
       </c>
       <c r="I113" s="11" t="n"/>
@@ -6003,38 +6003,38 @@
       <c r="M113" s="11" t="n"/>
       <c r="N113" s="11" t="n"/>
     </row>
-    <row r="114" ht="264" customHeight="1">
+    <row r="114" ht="147" customHeight="1">
       <c r="A114" s="10" t="n">
         <v>112</v>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Rifacimento con l'arcata esistente — il DPR 162/1999 elenca le modifiche costruttive senza dire quando l'insieme diventa una sostituzione completa; la UNI 10411-1/-11:2024 (21.1) chiama modifica sostanziale il cambio insieme di quadro, macchina, almeno una porta di piano, cabina e arcata, con il risultato secondo la UNI EN 81-20:2020: tenendo l'arcata il 21.1 non si applica. Una cabina nuova nell'arcata esistente segue la UNI EN 81-20 5.4.1–5.4.10 (UNI 10411-1:2024, 22; con porte di cabina a battente fino a +0,10 m² di superficie senza cambiare la portata, 22 f)). La qualificazione dell'intervento la conferma il tecnico incaricato con il soggetto che esegue la verifica straordinaria</t>
+          <t>Sezioni delle guide di cabina</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>si sostituiscono tutte le parti tranne l'arcata, che resta: le sostituzioni sono modifiche costruttive dell'impianto esistente, che si collauda secondo UNI 10411-1:2024 o UNI 10411-11:2024 e non come impianto nuovo; le verifiche che riguardano solo l'arcata (il tipo di paracadute, se la velocità non cambia) sono riportate come «esistente». La sostituzione completa dell'ascensore, arcata compresa, si collauda come impianto nuovo (UNI EN 81-20:2020 e UNI EN 81-50:2020; negli edifici esistenti anche la UNI EN 81-21:2022, supplementare)</t>
+          <t>area, momenti d'inerzia e moduli di resistenza minimi attorno all'asse parallelo alla suola (x) e all'asse di simmetria (y), spessore c del collo tra lama e suola, per ogni profilo del software; raggi d'inerzia calcolati come √(I/A)</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., art. 2 c.1 lett. cc), art. 12 c.4, art. 14 c.3; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-21:2022 (scopo)</t>
+          <t>ISO 7465:2007 (ora ISO 8100-33:2022); EN 10055:1995 per il T 70×70×8 laminato</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>indicazione del cliente (5 ottobre 2026): prassi di lasciare l'arcata; ricerca, capitolo 16 §3.2 e §5.3</t>
+          <t>tabella ISO 7465:2007 stampata da Savera (Standard Savera Guide, Rev 03/10; assi e c dalla Rev 08.26), anteprime ISO 7465:1997 e ISO 8100-33:2022 (correzione dei raggi del T127-1/B, stampati nel 2007 uguali ai moduli), EN 10055:1995, Tabella 1. La EN 10055 non ha il T 45: al T 45×45×5 il software dà la sezione del T45/A, delle stesse misure</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>prassi di cantiere</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
@@ -6055,37 +6055,37 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
+          <t>Tipo di paracadute per la velocità nominale</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
+          <t>istantaneo (anche a rulli imprigionati) fino a 0,63 m/s; oltre, progressivo (la UNI EN 81-20 non ha più l'istantaneo con effetto ammortizzato fino a 1 m/s); il tipo viene dai dati dell'impianto (se manca: progressivo, con la nota sul foglio)</t>
         </is>
       </c>
       <c r="E115" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
+          <t>UNI EN 81-20:2020, 5.6.2.1.2.1; la regola precedente in UNI EN 81-1 (1999, 2008), 9.8.2.1</t>
         </is>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>scelta del software, senza fonte</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 81; UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 58</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tipo di paracadute per la velocità</t>
         </is>
       </c>
       <c r="I115" s="11" t="n"/>
@@ -6095,23 +6095,23 @@
       <c r="M115" s="11" t="n"/>
       <c r="N115" s="11" t="n"/>
     </row>
-    <row r="116" ht="108" customHeight="1">
+    <row r="116" ht="43" customHeight="1">
       <c r="A116" s="10" t="n">
         <v>114</v>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Fune oltre la corsa (L0)</t>
+          <t>Dimensioni proposte della cabina</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale; con la puleggia di rinvio, l'asse sul basamento o sul telaio che la porta (voce locale.rinvio); macchina in basso o senza locale: fino al soffitto del vano</t>
+          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G116" s="10" t="inlineStr">
@@ -6141,43 +6141,43 @@
       <c r="M116" s="11" t="n"/>
       <c r="N116" s="11" t="n"/>
     </row>
-    <row r="117" ht="147" customHeight="1">
+    <row r="117" ht="225" customHeight="1">
       <c r="A117" s="10" t="n">
         <v>115</v>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
+          <t>Quote della pianta fissate a mano</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
+          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8.1), quello del contrappeso dentro la lunghezza del contrappeso (la stessa verifica vale per quelli messi dal software: ammortizzatori.posizione)</t>
         </is>
       </c>
       <c r="E117" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t>pianta del vano</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G117" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
         </is>
       </c>
       <c r="I117" s="11" t="n"/>
@@ -6187,38 +6187,38 @@
       <c r="M117" s="11" t="n"/>
       <c r="N117" s="11" t="n"/>
     </row>
-    <row r="118" ht="160" customHeight="1">
+    <row r="118" ht="82" customHeight="1">
       <c r="A118" s="10" t="n">
         <v>116</v>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
+          <t>Limiti del modello del vano</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
+          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>geometria delle funi</t>
+          <t>limite del modello attuale</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H118" s="10" t="inlineStr">
@@ -6233,38 +6233,38 @@
       <c r="M118" s="11" t="n"/>
       <c r="N118" s="11" t="n"/>
     </row>
-    <row r="119" ht="56" customHeight="1">
+    <row r="119" ht="238" customHeight="1">
       <c r="A119" s="10" t="n">
         <v>117</v>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
+          <t>Verifiche che il software non calcola</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
+          <t>da fare a parte, con i dati dei fornitori: sollecitazioni e frecce delle staffe e delle guide del contrappeso (UNI EN 81-50:2020, 5.10: il software verifica le guide di cabina, sul foglio 1 delle tavole); puleggia del contrappeso in taglia 2:1 sotto il soffitto; paracadute del contrappeso con spazi accessibili sotto il vano; distanza tra le parti fisse più alte della fossa e quelle più basse della cabina sugli ammortizzatori; sporgenze nel vano oltre 150 mm senza balaustra; locale della macchina in basso (dimensioni e spazi di manovra: il software non lo disegna); movimento incontrollato della cabina (UCM) e velocità eccessiva in salita con la nuova macchina; muro sotto la soglia di piano (5.2.5.3.2 a)); le soluzioni della UNI EN 81-21:2022 per testata, fossa, locale e porte ridotti (le verifiche in sezione seguono solo la UNI EN 81-20:2020)</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
+          <t>UNI EN 81-20:2020: guide e staffe 5.7.2–5.7.4 (con UNI EN 81-50:2020, 5.10); distanze in testata 5.2.5.7.2; spazi accessibili sotto il vano 5.2.5.4; parti fisse in fossa 5.2.5.8.2; sporgenze oltre 0,15 m 5.2.5.2.2.2; locale del macchinario 5.2.6.3; velocità eccessiva in salita 5.6.6; movimento incontrollato 5.6.7</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 31–43, 89–97; analisi delle lacune del 2026-10-03</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H119" s="10" t="inlineStr">
@@ -6279,7 +6279,7 @@
       <c r="M119" s="11" t="n"/>
       <c r="N119" s="11" t="n"/>
     </row>
-    <row r="120" ht="238" customHeight="1">
+    <row r="120" ht="56" customHeight="1">
       <c r="A120" s="10" t="n">
         <v>118</v>
       </c>
@@ -6290,27 +6290,27 @@
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso — la EN 81-20 non ammette più il pilastro pieno fino al terreno — (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori; in una modifica la UNI 10411-1:2024 (6.14) accetta al posto del paracadute un pilastro esistente fino al terreno, verificato per i nuovi carichi</t>
+          <t>Corsa</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
+          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>geometria ricostruita dal software</t>
+          <t>dati dei piani inseriti</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H120" s="10" t="inlineStr">
@@ -6325,7 +6325,7 @@
       <c r="M120" s="11" t="n"/>
       <c r="N120" s="11" t="n"/>
     </row>
-    <row r="121" ht="251" customHeight="1">
+    <row r="121" ht="121" customHeight="1">
       <c r="A121" s="10" t="n">
         <v>119</v>
       </c>
@@ -6336,27 +6336,27 @@
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta dal catalogo di un costruttore — la tolleranza sul rapporto è una scelta del software: la velocità reale con l'inverter deve restare entro il 5 % sopra la nominale (UNI EN 81-20:2020, 5.9.2.4; buona pratica non oltre l'8 % sotto); i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
+          <t>Portata e velocità — In una modifica la UNI 10411-1:2024 (6.1, prospetto 1) tratta come aumento della portata oltre il 10 % (Q fino a 500 kg) o il 5 % (oltre) e del carico totale oltre il 15 % o il 10 %; la UNI 10411-11:2024 (6.1) ogni aumento del carico totale: il confronto con la portata originale lo fa l'ingegnere.</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo; i disegni e il 3D mostrano l'argano SICOR com'è (ingombri, piedi e fori, asse della puleggia, P ed E della scheda), sul telaio del software</t>
+          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
         </is>
       </c>
       <c r="E121" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
+          <t>UNI EN 81-20:2020, 5.4.2.1</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>SICOR: schede tecniche 2025 e modelli CAD scaricati da sicoritaly.com il 2 ottobre 2026 (solo le quote); Sassi, Montanari, GEM, FAER: estratti delle pagine dei costruttori e dei rivenditori, 1° ottobre 2026</t>
+          <t>progetto del vano</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H121" s="10" t="inlineStr">
@@ -6371,7 +6371,7 @@
       <c r="M121" s="11" t="n"/>
       <c r="N121" s="11" t="n"/>
     </row>
-    <row r="122" ht="134" customHeight="1">
+    <row r="122" ht="316" customHeight="1">
       <c r="A122" s="10" t="n">
         <v>120</v>
       </c>
@@ -6382,22 +6382,22 @@
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
+          <t>Normativa di collaudo e parti sostituite o modificate — lo scopo delle due UNI 10411 e i requisiti per la sostituzione del macchinario (punto 14) sono letti sul testo (voce sostituzione.adeguamenti); quali verifiche riguardano ciascuna parte e la matrice delle norme compatibili sono una lettura del software, da approvare dall'ingegnere</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
+          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico a frizione non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (a frizione, conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software. Alla norma base si aggiungono le norme compatibili (matrice della ricerca, cap. 16 §5.2): sull'impianto nuovo le EN 81 supplementari (21, 28, 58, 70, 71, 72, 73, 76, 77), sulla modifica la EN 81-20/50 intera, le EN 81-28, 58, 73 e il miglioramento (80, 82, 83), su entrambi DM 236/1989, antincendio (DM 15/09/2005 o Codice V.3) e NTC 2018 (con le verifiche delle putrelle). Ogni norma ha il suo esito («non calcolata» se il software non ne calcola verifiche) e i suoi punti da verificare in sito nella relazione, con gli adempimenti del DPR 162/1999</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 8</t>
+          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo</t>
+          <t>UNI 10411-1:2024, testo della norma, letto il 2026-10-06, pp. 5, 13–14; UNI 10411-11:2024, testo della norma, letto il 2026-10-06, pp. 5, 12; schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); ricerca, capitoli 2.4 e 6.6</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
@@ -6417,38 +6417,38 @@
       <c r="M122" s="11" t="n"/>
       <c r="N122" s="11" t="n"/>
     </row>
-    <row r="123" ht="69" customHeight="1">
+    <row r="123" ht="264" customHeight="1">
       <c r="A123" s="10" t="n">
         <v>121</v>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
+          <t>Rifacimento con l'arcata esistente — il DPR 162/1999 elenca le modifiche costruttive senza dire quando l'insieme diventa una sostituzione completa; la UNI 10411-1/-11:2024 (21.1) chiama modifica sostanziale il cambio insieme di quadro, macchina, almeno una porta di piano, cabina e arcata, con il risultato secondo la UNI EN 81-20:2020: tenendo l'arcata il 21.1 non si applica. Una cabina nuova nell'arcata esistente segue la UNI EN 81-20 5.4.1–5.4.10 (UNI 10411-1:2024, 22; con porte di cabina a battente fino a +0,10 m² di superficie senza cambiare la portata, 22 f)). La qualificazione dell'intervento la conferma il tecnico incaricato con il soggetto che esegue la verifica straordinaria</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
+          <t>si sostituiscono tutte le parti tranne l'arcata, che resta: le sostituzioni sono modifiche costruttive dell'impianto esistente, che si collauda secondo UNI 10411-1:2024 o UNI 10411-11:2024 e non come impianto nuovo; le verifiche che riguardano solo l'arcata (il tipo di paracadute, se la velocità non cambia) sono riportate come «esistente». La sostituzione completa dell'ascensore, arcata compresa, si collauda come impianto nuovo (UNI EN 81-20:2020 e UNI EN 81-50:2020; negli edifici esistenti anche la UNI EN 81-21:2022, supplementare)</t>
         </is>
       </c>
       <c r="E123" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
+          <t>DPR 162/1999 e s.m.i., art. 2 c.1 lett. cc), art. 12 c.4, art. 14 c.3; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-21:2022 (scopo)</t>
         </is>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo (src/calc/model.ts)</t>
+          <t>indicazione del cliente (5 ottobre 2026): prassi di lasciare l'arcata; ricerca, capitolo 16 §3.2 e §5.3</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>prassi di cantiere</t>
         </is>
       </c>
       <c r="H123" s="10" t="inlineStr">
@@ -6463,38 +6463,38 @@
       <c r="M123" s="11" t="n"/>
       <c r="N123" s="11" t="n"/>
     </row>
-    <row r="124" ht="56" customHeight="1">
+    <row r="124" ht="69" customHeight="1">
       <c r="A124" s="10" t="n">
         <v>122</v>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
+          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
+          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
+          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>scelta del software, senza fonte</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H124" s="10" t="inlineStr">
@@ -6509,33 +6509,33 @@
       <c r="M124" s="11" t="n"/>
       <c r="N124" s="11" t="n"/>
     </row>
-    <row r="125" ht="69" customHeight="1">
+    <row r="125" ht="108" customHeight="1">
       <c r="A125" s="10" t="n">
         <v>123</v>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Limite di aderenza mostrato durante la marcia</t>
+          <t>Fune oltre la corsa (L0)</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
+          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale; con la puleggia di rinvio, l'asse sul basamento o sul telaio che la porta (voce locale.rinvio); macchina in basso o senza locale: fino al soffitto del vano</t>
         </is>
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.1 e 5.11.2.3.2 (μ della frenatura)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
@@ -6555,38 +6555,38 @@
       <c r="M125" s="11" t="n"/>
       <c r="N125" s="11" t="n"/>
     </row>
-    <row r="126" ht="108" customHeight="1">
+    <row r="126" ht="147" customHeight="1">
       <c r="A126" s="10" t="n">
         <v>124</v>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Tempi delle porte — La norma non dà tempi: per le porte automatiche orizzontali dà l'energia cinetica (≤ 10 J, ≤ 4 J con il dispositivo di protezione escluso) e la forza contro la chiusura (≤ 150 N) (UNI EN 81-20:2020, 5.3.6.2.2.1), dati del fornitore delle porte.</t>
+          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
+          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ricerca, capitolo 5.3</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (solo animazione)</t>
+          <t>pianta del vano</t>
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H126" s="10" t="inlineStr">
@@ -6601,38 +6601,38 @@
       <c r="M126" s="11" t="n"/>
       <c r="N126" s="11" t="n"/>
     </row>
-    <row r="127" ht="212" customHeight="1">
+    <row r="127" ht="160" customHeight="1">
       <c r="A127" s="10" t="n">
         <v>125</v>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione. Le decelerazioni mostrate non sono una verifica: per i tamponi non lineari la norma vuole media ≤ 1 gn, oltre 2,5 gn per non più di 0,04 s, picco ≤ 6 gn e rimbalzo ≤ 1 m/s (5.8.2.1.2.1), per gli idraulici media ≤ 1 gn e oltre 2,5 gn per non più di 0,04 s (5.8.2.2.3); si provano per tipo (certificato del fornitore)</t>
+          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
+          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2.1.1.1–5.8.2.1.1.2 (urto al 115 %; corsa piena con un carico statico tra 2,5 e 4 volte: il software prende 4), 5.8.2.1.2.2 (90 %), 5.8.2.2.1 e 5.8.2.2.3 a)</t>
+          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 98–99</t>
+          <t>geometria delle funi</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H127" s="10" t="inlineStr">
@@ -6647,38 +6647,38 @@
       <c r="M127" s="11" t="n"/>
       <c r="N127" s="11" t="n"/>
     </row>
-    <row r="128" ht="82" customHeight="1">
+    <row r="128" ht="56" customHeight="1">
       <c r="A128" s="10" t="n">
         <v>126</v>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Cabina bloccata: rotazione in salita — La simulazione mostra il contrappeso sugli ammortizzatori con la cabina in alto; la norma chiede anche la cabina vuota in basso, che il calcolo verifica (tr_stall).</t>
+          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
+          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.2.3</t>
+          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo; velocità scelta dal software</t>
+          <t>dati verticali del vano</t>
         </is>
       </c>
       <c r="G128" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H128" s="10" t="inlineStr">
@@ -6693,33 +6693,33 @@
       <c r="M128" s="11" t="n"/>
       <c r="N128" s="11" t="n"/>
     </row>
-    <row r="129" ht="43" customHeight="1">
+    <row r="129" ht="238" customHeight="1">
       <c r="A129" s="10" t="n">
         <v>127</v>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Passo di campionamento</t>
+          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso — la EN 81-20 non ammette più il pilastro pieno fino al terreno — (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori; in una modifica la UNI 10411-1:2024 (6.14) accetta al posto del paracadute un pilastro esistente fino al terreno, verificato per i nuovi carichi</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
+          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
         </is>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>geometria ricostruita dal software</t>
         </is>
       </c>
       <c r="G129" s="10" t="inlineStr">
@@ -6739,38 +6739,38 @@
       <c r="M129" s="11" t="n"/>
       <c r="N129" s="11" t="n"/>
     </row>
-    <row r="130" ht="56" customHeight="1">
+    <row r="130" ht="251" customHeight="1">
       <c r="A130" s="10" t="n">
         <v>128</v>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 4-bis</t>
+          <t>Macchina proposta dal catalogo di un costruttore — la tolleranza sul rapporto è una scelta del software: la velocità reale con l'inverter deve restare entro il 5 % sopra la nominale (UNI EN 81-20:2020, 5.9.2.4; buona pratica non oltre l'8 % sotto); i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>progetto, fabbricazione, installazione e prove conformi all'All. I; documentazione tecnica e dichiarazione di conformità conservate per 10 anni</t>
+          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo; i disegni e il 3D mostrano l'argano SICOR com'è (ingombri, piedi e fori, asse della puleggia, P ed E della scheda), sul telaio del software</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 4-bis</t>
+          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>SICOR: schede tecniche 2025 e modelli CAD scaricati da sicoritaly.com il 2 ottobre 2026 (solo le quote); Sassi, Montanari, GEM, FAER: estratti delle pagine dei costruttori e dei rivenditori, 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G130" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H130" s="10" t="inlineStr">
@@ -6785,38 +6785,38 @@
       <c r="M130" s="11" t="n"/>
       <c r="N130" s="11" t="n"/>
     </row>
-    <row r="131" ht="56" customHeight="1">
+    <row r="131" ht="134" customHeight="1">
       <c r="A131" s="10" t="n">
         <v>129</v>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., artt. 6-bis e 7 c.3</t>
+          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>procedura con un organismo notificato (ascensore modello con esame UE del tipo, All. IV B, più All. V, X o XII; oppure All. VIII o XI); marcatura CE in cabina con il numero dell'organismo</t>
+          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., artt. 6-bis e 7 c.3</t>
+          <t>ricerca, capitolo 8</t>
         </is>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>motore di calcolo</t>
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H131" s="10" t="inlineStr">
@@ -6831,38 +6831,38 @@
       <c r="M131" s="11" t="n"/>
       <c r="N131" s="11" t="n"/>
     </row>
-    <row r="132" ht="56" customHeight="1">
+    <row r="132" ht="69" customHeight="1">
       <c r="A132" s="10" t="n">
         <v>130</v>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., art. 12 c.1–3</t>
+          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>comunicazione al Comune entro 60 giorni dalla dichiarazione di conformità (oltre: con il verbale di una verifica straordinaria di attivazione); matricola entro 30 giorni</t>
+          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., art. 12 c.1–3</t>
+          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>motore di calcolo (src/calc/model.ts)</t>
         </is>
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H132" s="10" t="inlineStr">
@@ -6883,32 +6883,32 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
+          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>verifiche periodiche ogni 2 anni; controllo dei dispositivi di sicurezza, delle funi e dell'isolamento almeno ogni 6 mesi; targa in cabina</t>
+          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
+          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
         </is>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H133" s="10" t="inlineStr">
@@ -6923,38 +6923,38 @@
       <c r="M133" s="11" t="n"/>
       <c r="N133" s="11" t="n"/>
     </row>
-    <row r="134" ht="43" customHeight="1">
+    <row r="134" ht="69" customHeight="1">
       <c r="A134" s="10" t="n">
         <v>132</v>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
+          <t>Limite di aderenza mostrato durante la marcia</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>la modifica è costruttiva: la sostituzione del macchinario ne è il caso n. 5)</t>
+          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
+          <t>UNI EN 81-50:2020, 5.11.1 e 5.11.2.3.2 (μ della frenatura)</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G134" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H134" s="10" t="inlineStr">
@@ -6969,38 +6969,38 @@
       <c r="M134" s="11" t="n"/>
       <c r="N134" s="11" t="n"/>
     </row>
-    <row r="135" ht="43" customHeight="1">
+    <row r="135" ht="108" customHeight="1">
       <c r="A135" s="10" t="n">
         <v>133</v>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4</t>
+          <t>Tempi delle porte — La norma non dà tempi: per le porte automatiche orizzontali dà l'energia cinetica (≤ 10 J, ≤ 4 J con il dispositivo di protezione escluso) e la forza contro la chiusura (≤ 150 N) (UNI EN 81-20:2020, 5.3.6.2.2.1), dati del fornitore delle porte.</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>prima della comunicazione, adeguamento della parte modificata o sostituita e delle altre parti interessate</t>
+          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>scelta del software (solo animazione)</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H135" s="10" t="inlineStr">
@@ -7015,38 +7015,38 @@
       <c r="M135" s="11" t="n"/>
       <c r="N135" s="11" t="n"/>
     </row>
-    <row r="136" ht="43" customHeight="1">
+    <row r="136" ht="212" customHeight="1">
       <c r="A136" s="10" t="n">
         <v>134</v>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4–5</t>
+          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione. Le decelerazioni mostrate non sono una verifica: per i tamponi non lineari la norma vuole media ≤ 1 gn, oltre 2,5 gn per non più di 0,04 s, picco ≤ 6 gn e rimbalzo ≤ 1 m/s (5.8.2.1.2.1), per gli idraulici media ≤ 1 gn e oltre 2,5 gn per non più di 0,04 s (5.8.2.2.3); si provano per tipo (certificato del fornitore)</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>comunicazione al Comune e al soggetto delle verifiche periodiche; l'impianto non resta in esercizio senza le comunicazioni aggiornate</t>
+          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4–5</t>
+          <t>UNI EN 81-20:2020, 5.8.2.1.1.1–5.8.2.1.1.2 (urto al 115 %; corsa piena con un carico statico tra 2,5 e 4 volte: il software prende 4), 5.8.2.1.2.2 (90 %), 5.8.2.2.1 e 5.8.2.2.3 a)</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 98–99</t>
         </is>
       </c>
       <c r="G136" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H136" s="10" t="inlineStr">
@@ -7061,38 +7061,38 @@
       <c r="M136" s="11" t="n"/>
       <c r="N136" s="11" t="n"/>
     </row>
-    <row r="137" ht="69" customHeight="1">
+    <row r="137" ht="82" customHeight="1">
       <c r="A137" s="10" t="n">
         <v>135</v>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., art. 14 c.3; schema ICIM SCI 162 rev. 02</t>
+          <t>Cabina bloccata: rotazione in salita — La simulazione mostra il contrappeso sugli ammortizzatori con la cabina in alto; la norma chiede anche la cabina vuota in basso, che il calcolo verifica (tr_stall).</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>verifica straordinaria da uno dei soggetti dell'art. 13 c.1 (la legge); secondo lo schema ICIM è di norma limitata ai controlli sulle modifiche, con la documentazione delle modifiche e dei componenti sostituiti</t>
+          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., art. 14 c.3; schema ICIM SCI 162 rev. 02</t>
+          <t>UNI EN 81-50:2020, 5.11.2.2.3</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>motore di calcolo; velocità scelta dal software</t>
         </is>
       </c>
       <c r="G137" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H137" s="10" t="inlineStr">
@@ -7107,38 +7107,38 @@
       <c r="M137" s="11" t="n"/>
       <c r="N137" s="11" t="n"/>
     </row>
-    <row r="138" ht="82" customHeight="1">
+    <row r="138" ht="43" customHeight="1">
       <c r="A138" s="10" t="n">
         <v>136</v>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024 e UNI 10411-11:2024, 25</t>
+          <t>Passo di campionamento</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>documentazione della modifica (App. C della -1, App. A della -11): il proprietario la tiene per chi esegue la verifica straordinaria e la allega alla dichiarazione di conformità (DM 37/2008); manuali della macchina, del quadro e dei nuovi componenti di sicurezza consegnati al proprietario</t>
+          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024 e UNI 10411-11:2024, 25</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G138" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H138" s="10" t="inlineStr">
@@ -7159,22 +7159,22 @@
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
+          <t>DPR 162/1999, art. 4-bis</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>prove dell'organismo notificato: funzionamento a vuoto e a pieno carico, in mancanza di energia, prova statica a 1,25 volte la portata e controllo che non restino deformazioni</t>
+          <t>progetto, fabbricazione, installazione e prove conformi all'All. I; documentazione tecnica e dichiarazione di conformità conservate per 10 anni</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
+          <t>DPR 162/1999, art. 4-bis</t>
         </is>
       </c>
       <c r="F139" s="10" t="inlineStr">
@@ -7205,22 +7205,22 @@
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
+          <t>DPR 162/1999 e s.m.i., artt. 6-bis e 7 c.3</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>documentazione tecnica con i risultati dei calcoli di progetto, le relazioni sulle prove e l'elenco delle norme armonizzate applicate, anche in parte</t>
+          <t>procedura con un organismo notificato (ascensore modello con esame UE del tipo, All. IV B, più All. V, X o XII; oppure All. VIII o XI); marcatura CE in cabina con il numero dell'organismo</t>
         </is>
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
+          <t>DPR 162/1999 e s.m.i., artt. 6-bis e 7 c.3</t>
         </is>
       </c>
       <c r="F140" s="10" t="inlineStr">
@@ -7251,22 +7251,22 @@
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
+          <t>DPR 162/1999 e s.m.i., art. 12 c.1–3</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>per gli ascensori dichiarati conformi dal 20/01/2027: requisiti dell'All. III del Regolamento macchine (tra cui 1.1.9 e 1.2.1), con una valutazione aggiuntiva per i requisiti nuovi o cambiati</t>
+          <t>comunicazione al Comune entro 60 giorni dalla dichiarazione di conformità (oltre: con il verbale di una verifica straordinaria di attivazione); matricola entro 30 giorni</t>
         </is>
       </c>
       <c r="E141" s="10" t="inlineStr">
         <is>
-          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
+          <t>DPR 162/1999 e s.m.i., art. 12 c.1–3</t>
         </is>
       </c>
       <c r="F141" s="10" t="inlineStr">
@@ -7291,33 +7291,33 @@
       <c r="M141" s="11" t="n"/>
       <c r="N141" s="11" t="n"/>
     </row>
-    <row r="142" ht="82" customHeight="1">
+    <row r="142" ht="56" customHeight="1">
       <c r="A142" s="10" t="n">
         <v>140</v>
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12.1 e 5.12.2.1</t>
+          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>il metodo del coefficiente di sicurezza delle funi vale solo per pulegge di acciaio o ghisa e funi d'acciaio secondo EN 12385-5; la flessione è semplice se il raggio della gola non supera 0,53 volte il diametro della fune: rilevare il materiale della puleggia e il raggio delle gole</t>
+          <t>verifiche periodiche ogni 2 anni; controllo dei dispositivi di sicurezza, delle funi e dell'isolamento almeno ogni 6 mesi; targa in cabina</t>
         </is>
       </c>
       <c r="E142" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12.1 e 5.12.2.1</t>
+          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
         </is>
       </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G142" s="10" t="inlineStr">
@@ -7343,27 +7343,27 @@
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.6.2.2.1.2</t>
+          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>tempo di risposta del limitatore di velocità: i suoi punti d'intervento distano al massimo 250 mm di corsa della fune del limitatore</t>
+          <t>la modifica è costruttiva: la sostituzione del macchinario ne è il caso n. 5)</t>
         </is>
       </c>
       <c r="E143" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.6.2.2.1.2</t>
+          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
         </is>
       </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G143" s="10" t="inlineStr">
@@ -7383,33 +7383,33 @@
       <c r="M143" s="11" t="n"/>
       <c r="N143" s="11" t="n"/>
     </row>
-    <row r="144" ht="56" customHeight="1">
+    <row r="144" ht="43" customHeight="1">
       <c r="A144" s="10" t="n">
         <v>142</v>
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2.1.2.1 e 5.8.2.2.3</t>
+          <t>DPR 162/1999, art. 12 c.4</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>ammortizzatori (dato del fornitore): decelerazione non oltre 1 gn, sopra 2,5 gn al massimo per 0,04 s; per quelli ad accumulo non lineari anche picco non oltre 6 gn e rimbalzo non oltre 1 m/s</t>
+          <t>prima della comunicazione, adeguamento della parte modificata o sostituita e delle altre parti interessate</t>
         </is>
       </c>
       <c r="E144" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2.1.2.1 e 5.8.2.2.3</t>
+          <t>DPR 162/1999, art. 12 c.4</t>
         </is>
       </c>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G144" s="10" t="inlineStr">
@@ -7429,33 +7429,33 @@
       <c r="M144" s="11" t="n"/>
       <c r="N144" s="11" t="n"/>
     </row>
-    <row r="145" ht="69" customHeight="1">
+    <row r="145" ht="43" customHeight="1">
       <c r="A145" s="10" t="n">
         <v>143</v>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1</t>
+          <t>DPR 162/1999, art. 12 c.4–5</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>cartello sopra o accanto allo schermo del contrappeso (5.2.5.5.1) con il gioco massimo ammesso tra contrappeso e ammortizzatore con la cabina al piano più alto, per conservare gli spazi in testata</t>
+          <t>comunicazione al Comune e al soggetto delle verifiche periodiche; l'impianto non resta in esercizio senza le comunicazioni aggiornate</t>
         </is>
       </c>
       <c r="E145" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1</t>
+          <t>DPR 162/1999, art. 12 c.4–5</t>
         </is>
       </c>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G145" s="10" t="inlineStr">
@@ -7475,33 +7475,33 @@
       <c r="M145" s="11" t="n"/>
       <c r="N145" s="11" t="n"/>
     </row>
-    <row r="146" ht="43" customHeight="1">
+    <row r="146" ht="69" customHeight="1">
       <c r="A146" s="10" t="n">
         <v>144</v>
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.2.4</t>
+          <t>DPR 162/1999 e s.m.i., art. 14 c.3; schema ICIM SCI 162 rev. 02</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>fossa più profonda di 2,50 m: porta di accesso; fino a 2,50 m porta di accesso oppure scala dentro il vano (appendice F)</t>
+          <t>verifica straordinaria da uno dei soggetti dell'art. 13 c.1 (la legge); secondo lo schema ICIM è di norma limitata ai controlli sulle modifiche, con la documentazione delle modifiche e dei componenti sostituiti</t>
         </is>
       </c>
       <c r="E146" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.2.4</t>
+          <t>DPR 162/1999 e s.m.i., art. 14 c.3; schema ICIM SCI 162 rev. 02</t>
         </is>
       </c>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G146" s="10" t="inlineStr">
@@ -7521,28 +7521,28 @@
       <c r="M146" s="11" t="n"/>
       <c r="N146" s="11" t="n"/>
     </row>
-    <row r="147" ht="43" customHeight="1">
+    <row r="147" ht="82" customHeight="1">
       <c r="A147" s="10" t="n">
         <v>145</v>
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.5.1 b)</t>
+          <t>UNI 10411-1:2024 e UNI 10411-11:2024, 25</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>in fossa un commutatore di ispezione fisso, manovrabile da non oltre 0,30 m da uno spazio di rifugio</t>
+          <t>documentazione della modifica (App. C della -1, App. A della -11): il proprietario la tiene per chi esegue la verifica straordinaria e la allega alla dichiarazione di conformità (DM 37/2008); manuali della macchina, del quadro e dei nuovi componenti di sicurezza consegnati al proprietario</t>
         </is>
       </c>
       <c r="E147" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.5.1 b)</t>
+          <t>UNI 10411-1:2024 e UNI 10411-11:2024, 25</t>
         </is>
       </c>
       <c r="F147" s="10" t="inlineStr">
@@ -7567,7 +7567,7 @@
       <c r="M147" s="11" t="n"/>
       <c r="N147" s="11" t="n"/>
     </row>
-    <row r="148" ht="43" customHeight="1">
+    <row r="148" ht="56" customHeight="1">
       <c r="A148" s="10" t="n">
         <v>146</v>
       </c>
@@ -7578,22 +7578,22 @@
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1</t>
+          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>uno spazio di rifugio per ogni persona, tutti dello stesso tipo e senza sovrapposizioni; cartello con il numero di persone ammesse e la postura</t>
+          <t>prove dell'organismo notificato: funzionamento a vuoto e a pieno carico, in mancanza di energia, prova statica a 1,25 volte la portata e controllo che non restino deformazioni</t>
         </is>
       </c>
       <c r="E148" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1</t>
+          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
         </is>
       </c>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G148" s="10" t="inlineStr">
@@ -7613,7 +7613,7 @@
       <c r="M148" s="11" t="n"/>
       <c r="N148" s="11" t="n"/>
     </row>
-    <row r="149" ht="69" customHeight="1">
+    <row r="149" ht="56" customHeight="1">
       <c r="A149" s="10" t="n">
         <v>147</v>
       </c>
@@ -7624,22 +7624,22 @@
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.4.1</t>
+          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>illuminazione del vano: almeno 50 lux a 1 m sopra il tetto della cabina nella sua proiezione e a 1 m sopra il fondo della fossa dove si sta, si lavora o si passa tra le zone di lavoro; almeno 20 lux altrove</t>
+          <t>documentazione tecnica con i risultati dei calcoli di progetto, le relazioni sulle prove e l'elenco delle norme armonizzate applicate, anche in parte</t>
         </is>
       </c>
       <c r="E149" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.4.1</t>
+          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
         </is>
       </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G149" s="10" t="inlineStr">
@@ -7670,22 +7670,22 @@
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.10.1 e 5.4.10.4</t>
+          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>luce in cabina almeno 100 lux sui comandi e a 1 m dal pavimento; luce di emergenza di almeno 5 lux per un'ora presso gli allarmi in cabina e sul tetto e al centro di cabina e tetto, a 1 m</t>
+          <t>per gli ascensori dichiarati conformi dal 20/01/2027: requisiti dell'All. III del Regolamento macchine (tra cui 1.1.9 e 1.2.1), con una valutazione aggiuntiva per i requisiti nuovi o cambiati</t>
         </is>
       </c>
       <c r="E150" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.10.1 e 5.4.10.4</t>
+          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
         </is>
       </c>
       <c r="F150" s="10" t="inlineStr">
         <is>
-          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G150" s="10" t="inlineStr">
@@ -7705,7 +7705,7 @@
       <c r="M150" s="11" t="n"/>
       <c r="N150" s="11" t="n"/>
     </row>
-    <row r="151" ht="43" customHeight="1">
+    <row r="151" ht="82" customHeight="1">
       <c r="A151" s="10" t="n">
         <v>149</v>
       </c>
@@ -7716,17 +7716,17 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.4</t>
+          <t>UNI EN 81-50:2020, 5.12.1 e 5.12.2.1</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>materiali della cabina secondo EN 13501-1: pavimento Cfl-s2, pareti C-s2,d1, soffitto C-s2,d0</t>
+          <t>il metodo del coefficiente di sicurezza delle funi vale solo per pulegge di acciaio o ghisa e funi d'acciaio secondo EN 12385-5; la flessione è semplice se il raggio della gola non supera 0,53 volte il diametro della fune: rilevare il materiale della puleggia e il raggio delle gole</t>
         </is>
       </c>
       <c r="E151" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.4</t>
+          <t>UNI EN 81-50:2020, 5.12.1 e 5.12.2.1</t>
         </is>
       </c>
       <c r="F151" s="10" t="inlineStr">
@@ -7751,7 +7751,7 @@
       <c r="M151" s="11" t="n"/>
       <c r="N151" s="11" t="n"/>
     </row>
-    <row r="152" ht="95" customHeight="1">
+    <row r="152" ht="43" customHeight="1">
       <c r="A152" s="10" t="n">
         <v>150</v>
       </c>
@@ -7762,17 +7762,17 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.1</t>
+          <t>UNI EN 81-20:2020, 5.6.2.2.1.2</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>prova del freno: da solo ferma la cabina che scende a velocità nominale con il 125 % della portata; con un gruppo fuori servizio rallenta la cabina con la portata in discesa; con il carico tra (q − 0,1)·Q e (q + 0,1)·Q lo sblocco manuale fa partire la cabina da sola, altrimenti servono i mezzi della 5.9.2.2.2.9 b)</t>
+          <t>tempo di risposta del limitatore di velocità: i suoi punti d'intervento distano al massimo 250 mm di corsa della fune del limitatore</t>
         </is>
       </c>
       <c r="E152" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.1</t>
+          <t>UNI EN 81-20:2020, 5.6.2.2.1.2</t>
         </is>
       </c>
       <c r="F152" s="10" t="inlineStr">
@@ -7797,7 +7797,7 @@
       <c r="M152" s="11" t="n"/>
       <c r="N152" s="11" t="n"/>
     </row>
-    <row r="153" ht="69" customHeight="1">
+    <row r="153" ht="56" customHeight="1">
       <c r="A153" s="10" t="n">
         <v>151</v>
       </c>
@@ -7808,17 +7808,17 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.2</t>
+          <t>UNI EN 81-20:2020, 5.8.2.1.2.1 e 5.8.2.2.3</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>impianto elettrico: esame a vista, continuità dei conduttori di protezione, isolamento circuito per circuito con l'elettronica scollegata, efficacia dell'interruzione automatica in caso di guasto</t>
+          <t>ammortizzatori (dato del fornitore): decelerazione non oltre 1 gn, sopra 2,5 gn al massimo per 0,04 s; per quelli ad accumulo non lineari anche picco non oltre 6 gn e rimbalzo non oltre 1 m/s</t>
         </is>
       </c>
       <c r="E153" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.2</t>
+          <t>UNI EN 81-20:2020, 5.8.2.1.2.1 e 5.8.2.2.3</t>
         </is>
       </c>
       <c r="F153" s="10" t="inlineStr">
@@ -7843,7 +7843,7 @@
       <c r="M153" s="11" t="n"/>
       <c r="N153" s="11" t="n"/>
     </row>
-    <row r="154" ht="82" customHeight="1">
+    <row r="154" ht="69" customHeight="1">
       <c r="A154" s="10" t="n">
         <v>152</v>
       </c>
@@ -7854,17 +7854,17 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.3</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>aderenza: arresti con la frenatura più severa, in salita a cabina vuota nella parte alta e in discesa con il 125 % della portata verso il basso; con il contrappeso sugli ammortizzatori e la macchina in moto le funi slittano oppure la cabina non sale; bilanciamento come dichiarato</t>
+          <t>cartello sopra o accanto allo schermo del contrappeso (5.2.5.5.1) con il gioco massimo ammesso tra contrappeso e ammortizzatore con la cabina al piano più alto, per conservare gli spazi in testata</t>
         </is>
       </c>
       <c r="E154" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.3</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1</t>
         </is>
       </c>
       <c r="F154" s="10" t="inlineStr">
@@ -7889,7 +7889,7 @@
       <c r="M154" s="11" t="n"/>
       <c r="N154" s="11" t="n"/>
     </row>
-    <row r="155" ht="121" customHeight="1">
+    <row r="155" ht="43" customHeight="1">
       <c r="A155" s="10" t="n">
         <v>153</v>
       </c>
@@ -7900,17 +7900,17 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.4, 6.3.5 e 6.3.7</t>
+          <t>UNI EN 81-20:2020, 5.2.2.4</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>paracadute di cabina in discesa (istantaneo con la portata a velocità nominale; progressivo, negli impianti a frizione, con il 125 % della portata a velocità nominale o inferiore), del contrappeso a cabina vuota; ammortizzatori ad accumulo compressi dalla cabina con la portata, a dissipazione provati alla velocità nominale (o a quella usata per la corsa ridotta); dopo, nessun danno all'esame a vista</t>
+          <t>fossa più profonda di 2,50 m: porta di accesso; fino a 2,50 m porta di accesso oppure scala dentro il vano (appendice F)</t>
         </is>
       </c>
       <c r="E155" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.4, 6.3.5 e 6.3.7</t>
+          <t>UNI EN 81-20:2020, 5.2.2.4</t>
         </is>
       </c>
       <c r="F155" s="10" t="inlineStr">
@@ -7935,7 +7935,7 @@
       <c r="M155" s="11" t="n"/>
       <c r="N155" s="11" t="n"/>
     </row>
-    <row r="156" ht="108" customHeight="1">
+    <row r="156" ht="43" customHeight="1">
       <c r="A156" s="10" t="n">
         <v>154</v>
       </c>
@@ -7946,17 +7946,17 @@
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.11, 6.3.12 e 6.3.13</t>
+          <t>UNI EN 81-20:2020, 5.2.1.5.1 b)</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>ACOP: cabina vuota in salita a velocità non inferiore alla nominale, frenata solo dal dispositivo; livellamento verificato a ogni fermata e, al piano più sfavorevole, durante carico e scarico; UCM: cabina vuota verso l'alto e piena verso il basso a una velocità prestabilita, con il movimento entro il limite della 5.6.7.5 e l'autosorveglianza dove richiesta</t>
+          <t>in fossa un commutatore di ispezione fisso, manovrabile da non oltre 0,30 m da uno spazio di rifugio</t>
         </is>
       </c>
       <c r="E156" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.11, 6.3.12 e 6.3.13</t>
+          <t>UNI EN 81-20:2020, 5.2.1.5.1 b)</t>
         </is>
       </c>
       <c r="F156" s="10" t="inlineStr">
@@ -7992,17 +7992,17 @@
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.14</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>cabina fuori dalla zona di sbloccaggio e porta di piano tenuta aperta di 100 mm: lasciata, la porta si richiude e si blocca</t>
+          <t>uno spazio di rifugio per ogni persona, tutti dello stesso tipo e senza sovrapposizioni; cartello con il numero di persone ammesse e la postura</t>
         </is>
       </c>
       <c r="E157" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.14</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1</t>
         </is>
       </c>
       <c r="F157" s="10" t="inlineStr">
@@ -8027,7 +8027,7 @@
       <c r="M157" s="11" t="n"/>
       <c r="N157" s="11" t="n"/>
     </row>
-    <row r="158" ht="43" customHeight="1">
+    <row r="158" ht="69" customHeight="1">
       <c r="A158" s="10" t="n">
         <v>156</v>
       </c>
@@ -8038,17 +8038,17 @@
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, C.2 e 7.3.2</t>
+          <t>UNI EN 81-20:2020, 5.2.1.4.1</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>la sostituzione della macchina o della puleggia di trazione è una trasformazione importante: si annota nel registro dell'impianto, da aggiornare</t>
+          <t>illuminazione del vano: almeno 50 lux a 1 m sopra il tetto della cabina nella sua proiezione e a 1 m sopra il fondo della fossa dove si sta, si lavora o si passa tra le zone di lavoro; almeno 20 lux altrove</t>
         </is>
       </c>
       <c r="E158" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, C.2 e 7.3.2</t>
+          <t>UNI EN 81-20:2020, 5.2.1.4.1</t>
         </is>
       </c>
       <c r="F158" s="10" t="inlineStr">
@@ -8073,7 +8073,7 @@
       <c r="M158" s="11" t="n"/>
       <c r="N158" s="11" t="n"/>
     </row>
-    <row r="159" ht="108" customHeight="1">
+    <row r="159" ht="56" customHeight="1">
       <c r="A159" s="10" t="n">
         <v>157</v>
       </c>
@@ -8084,17 +8084,17 @@
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.3.5.3.2, 5.3.5.3.4, 5.3.6.2.2.1 b) e 5.3.15.2 b)</t>
+          <t>UNI EN 81-20:2020, 5.4.10.1 e 5.4.10.4</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>pannelli delle porte con i dispositivi di ritenuta e le prove a pendolo (morbido da 800 mm; rigido da 500 mm sui pannelli in vetro); sulle porte automatiche un dispositivo di protezione che copre da 25 a 1600 mm sopra la soglia e rileva ostacoli di 50 mm; fuori dalla zona di sbloccaggio la porta di cabina, spinta con 1000 N, non si apre più di 50 mm</t>
+          <t>luce in cabina almeno 100 lux sui comandi e a 1 m dal pavimento; luce di emergenza di almeno 5 lux per un'ora presso gli allarmi in cabina e sul tetto e al centro di cabina e tetto, a 1 m</t>
         </is>
       </c>
       <c r="E159" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.3.5.3.2, 5.3.5.3.4, 5.3.6.2.2.1 b) e 5.3.15.2 b)</t>
+          <t>UNI EN 81-20:2020, 5.4.10.1 e 5.4.10.4</t>
         </is>
       </c>
       <c r="F159" s="10" t="inlineStr">
@@ -8119,28 +8119,28 @@
       <c r="M159" s="11" t="n"/>
       <c r="N159" s="11" t="n"/>
     </row>
-    <row r="160" ht="56" customHeight="1">
+    <row r="160" ht="43" customHeight="1">
       <c r="A160" s="10" t="n">
         <v>158</v>
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-1:2024</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, scopo</t>
+          <t>UNI EN 81-20:2020, 5.4.4</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>impianti elettrici a frizione fuori dalla 95/16/CE e dalla 2014/33/UE; esclude le modifiche che cambiano le misure antincendio (per queste, a nostro giudizio, il DM 15/09/2005 o il Codice V.3)</t>
+          <t>materiali della cabina secondo EN 13501-1: pavimento Cfl-s2, pareti C-s2,d1, soffitto C-s2,d0</t>
         </is>
       </c>
       <c r="E160" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, scopo</t>
+          <t>UNI EN 81-20:2020, 5.4.4</t>
         </is>
       </c>
       <c r="F160" s="10" t="inlineStr">
@@ -8165,28 +8165,28 @@
       <c r="M160" s="11" t="n"/>
       <c r="N160" s="11" t="n"/>
     </row>
-    <row r="161" ht="121" customHeight="1">
+    <row r="161" ht="95" customHeight="1">
       <c r="A161" s="10" t="n">
         <v>159</v>
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-1:2024</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, 14.4 a)–g)</t>
+          <t>UNI EN 81-20:2020, 6.3.1</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>con la macchina nuova: temporizzatore del motore (EN 81-20 5.9.2.7); arresto in salita prima della velocità d'intervento del limitatore; protezioni ACOP e UCM esistenti che continuano a funzionare; dispositivo d'arresto presso la macchina (5.12.1.11.1 e)); pulegge nel locale secondo la 5.5.7; senza UCM e con la regolazione di velocità, macchinario senza alimentazione se il freno non si apre, con ripristino solo manuale</t>
+          <t>prova del freno: da solo ferma la cabina che scende a velocità nominale con il 125 % della portata; con un gruppo fuori servizio rallenta la cabina con la portata in discesa; con il carico tra (q − 0,1)·Q e (q + 0,1)·Q lo sblocco manuale fa partire la cabina da sola, altrimenti servono i mezzi della 5.9.2.2.2.9 b)</t>
         </is>
       </c>
       <c r="E161" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, 14.4 a)–g)</t>
+          <t>UNI EN 81-20:2020, 6.3.1</t>
         </is>
       </c>
       <c r="F161" s="10" t="inlineStr">
@@ -8211,28 +8211,28 @@
       <c r="M161" s="11" t="n"/>
       <c r="N161" s="11" t="n"/>
     </row>
-    <row r="162" ht="56" customHeight="1">
+    <row r="162" ht="69" customHeight="1">
       <c r="A162" s="10" t="n">
         <v>160</v>
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-11:2024</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, scopo</t>
+          <t>UNI EN 81-20:2020, 6.3.2</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>impianti elettrici a frizione marcati CE secondo la Direttiva; esclude le modifiche che cambiano le misure antincendio (per queste, a nostro giudizio, il DM 15/09/2005 o il Codice V.3)</t>
+          <t>impianto elettrico: esame a vista, continuità dei conduttori di protezione, isolamento circuito per circuito con l'elettronica scollegata, efficacia dell'interruzione automatica in caso di guasto</t>
         </is>
       </c>
       <c r="E162" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, scopo</t>
+          <t>UNI EN 81-20:2020, 6.3.2</t>
         </is>
       </c>
       <c r="F162" s="10" t="inlineStr">
@@ -8257,28 +8257,28 @@
       <c r="M162" s="11" t="n"/>
       <c r="N162" s="11" t="n"/>
     </row>
-    <row r="163" ht="108" customHeight="1">
+    <row r="163" ht="82" customHeight="1">
       <c r="A163" s="10" t="n">
         <v>161</v>
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-11:2024</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, 14.3 a) e App. A (14); UNI EN 81-20:2020, 5.6.6.2 e 5.6.7.3</t>
+          <t>UNI EN 81-20:2020, 6.3.3</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>cambiando la macchina: le protezioni UCM esistenti devono continuare a funzionare (14.3 a)); per l'ACOP esistente l'App. A (14) chiede una relazione sulla compatibilità della nuova macchina, oppure nuovi dispositivi con certificato di esame di tipo e dichiarazione di conformità; il freno della macchina vale come organo d'arresto solo se ridondante e autocontrollato</t>
+          <t>aderenza: arresti con la frenatura più severa, in salita a cabina vuota nella parte alta e in discesa con il 125 % della portata verso il basso; con il contrappeso sugli ammortizzatori e la macchina in moto le funi slittano oppure la cabina non sale; bilanciamento come dichiarato</t>
         </is>
       </c>
       <c r="E163" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, 14.3 a) e App. A (14); UNI EN 81-20:2020, 5.6.6.2 e 5.6.7.3</t>
+          <t>UNI EN 81-20:2020, 6.3.3</t>
         </is>
       </c>
       <c r="F163" s="10" t="inlineStr">
@@ -8303,28 +8303,28 @@
       <c r="M163" s="11" t="n"/>
       <c r="N163" s="11" t="n"/>
     </row>
-    <row r="164" ht="56" customHeight="1">
+    <row r="164" ht="121" customHeight="1">
       <c r="A164" s="10" t="n">
         <v>162</v>
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-11:2024</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, 14.3 b)</t>
+          <t>UNI EN 81-20:2020, 6.3.4, 6.3.5 e 6.3.7</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>senza UCM conforme alla 5.6.7 e con il rallentamento controllato: macchinario senza alimentazione se il freno non si apre, al più tardi all'arrivo al piano, con ripristino solo manuale</t>
+          <t>paracadute di cabina in discesa (istantaneo con la portata a velocità nominale; progressivo, negli impianti a frizione, con il 125 % della portata a velocità nominale o inferiore), del contrappeso a cabina vuota; ammortizzatori ad accumulo compressi dalla cabina con la portata, a dissipazione provati alla velocità nominale (o a quella usata per la corsa ridotta); dopo, nessun danno all'esame a vista</t>
         </is>
       </c>
       <c r="E164" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, 14.3 b)</t>
+          <t>UNI EN 81-20:2020, 6.3.4, 6.3.5 e 6.3.7</t>
         </is>
       </c>
       <c r="F164" s="10" t="inlineStr">
@@ -8349,28 +8349,28 @@
       <c r="M164" s="11" t="n"/>
       <c r="N164" s="11" t="n"/>
     </row>
-    <row r="165" ht="56" customHeight="1">
+    <row r="165" ht="108" customHeight="1">
       <c r="A165" s="10" t="n">
         <v>163</v>
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-21:2022, 1</t>
+          <t>UNI EN 81-20:2020, 6.3.11, 6.3.12 e 6.3.13</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>ascensori nuovi in un edificio esistente, dove l'edificio non permette di rispettare tutta la UNI EN 81-20:2020; esclusi gli impianti montati prima della sua pubblicazione</t>
+          <t>ACOP: cabina vuota in salita a velocità non inferiore alla nominale, frenata solo dal dispositivo; livellamento verificato a ogni fermata e, al piano più sfavorevole, durante carico e scarico; UCM: cabina vuota verso l'alto e piena verso il basso a una velocità prestabilita, con il movimento entro il limite della 5.6.7.5 e l'autosorveglianza dove richiesta</t>
         </is>
       </c>
       <c r="E165" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-21:2022, 1</t>
+          <t>UNI EN 81-20:2020, 6.3.11, 6.3.12 e 6.3.13</t>
         </is>
       </c>
       <c r="F165" s="10" t="inlineStr">
@@ -8395,28 +8395,28 @@
       <c r="M165" s="11" t="n"/>
       <c r="N165" s="11" t="n"/>
     </row>
-    <row r="166" ht="95" customHeight="1">
+    <row r="166" ht="43" customHeight="1">
       <c r="A166" s="10" t="n">
         <v>164</v>
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-21:2022, 6.2 e 7.1</t>
+          <t>UNI EN 81-20:2020, 6.3.14</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>oltre alle prove della EN 81-20 6.3: arresti mobili e sistema di arresto preattivato provati in moto a velocità nominale (in testata a cabina vuota, in fossa con il carico nominale), corsa dei loro ammortizzatori e distanza di frenatura; nelle istruzioni: quanto frena il sistema, col valore nominale e i due limiti</t>
+          <t>cabina fuori dalla zona di sbloccaggio e porta di piano tenuta aperta di 100 mm: lasciata, la porta si richiude e si blocca</t>
         </is>
       </c>
       <c r="E166" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-21:2022, 6.2 e 7.1</t>
+          <t>UNI EN 81-20:2020, 6.3.14</t>
         </is>
       </c>
       <c r="F166" s="10" t="inlineStr">
@@ -8441,33 +8441,33 @@
       <c r="M166" s="11" t="n"/>
       <c r="N166" s="11" t="n"/>
     </row>
-    <row r="167" ht="82" customHeight="1">
+    <row r="167" ht="43" customHeight="1">
       <c r="A167" s="10" t="n">
         <v>165</v>
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
+          <t>UNI EN 81-20:2020, C.2 e 7.3.2</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>spazi di rifugio ridotti solo con l'accordo preventivo: in edificio esistente PEC al Ministero con la certificazione dell'organismo prima dell'installazione (Procedura 2: dichiarazione dei punti della EN 81-21 applicati); la EN 81-21 da sola non giustifica la deroga</t>
+          <t>la sostituzione della macchina o della puleggia di trazione è una trasformazione importante: si annota nel registro dell'impianto, da aggiornare</t>
         </is>
       </c>
       <c r="E167" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
+          <t>UNI EN 81-20:2020, C.2 e 7.3.2</t>
         </is>
       </c>
       <c r="F167" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G167" s="10" t="inlineStr">
@@ -8487,28 +8487,28 @@
       <c r="M167" s="11" t="n"/>
       <c r="N167" s="11" t="n"/>
     </row>
-    <row r="168" ht="82" customHeight="1">
+    <row r="168" ht="108" customHeight="1">
       <c r="A168" s="10" t="n">
         <v>166</v>
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.12.3.1; UNI EN 81-28:2004, 4.1.3, 4.2.1 e 7</t>
+          <t>UNI EN 81-20:2020, 5.3.5.3.2, 5.3.5.3.4, 5.3.6.2.2.1 b) e 5.3.15.2 b)</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>la EN 81-20 richiama con data la EN 81-28:2003 (UNI EN 81-28:2004): prova automatica del collegamento almeno ogni 3 giorni; con alimentazione a batteria, avviso al servizio di soccorso quando l'autonomia residua scende sotto 1 h; pulsante d'allarme giallo con il simbolo della campana</t>
+          <t>pannelli delle porte con i dispositivi di ritenuta e le prove a pendolo (morbido da 800 mm; rigido da 500 mm sui pannelli in vetro); sulle porte automatiche un dispositivo di protezione che copre da 25 a 1600 mm sopra la soglia e rileva ostacoli di 50 mm; fuori dalla zona di sbloccaggio la porta di cabina, spinta con 1000 N, non si apre più di 50 mm</t>
         </is>
       </c>
       <c r="E168" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.12.3.1; UNI EN 81-28:2004, 4.1.3, 4.2.1 e 7</t>
+          <t>UNI EN 81-20:2020, 5.3.5.3.2, 5.3.5.3.4, 5.3.6.2.2.1 b) e 5.3.15.2 b)</t>
         </is>
       </c>
       <c r="F168" s="10" t="inlineStr">
@@ -8539,32 +8539,32 @@
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
+          <t>Collaudo: UNI 10411-1:2024</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-28:2022</t>
+          <t>UNI 10411-1:2024, scopo</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>requisiti dell'edizione citata in GUUE da verificare sul testo; nelle modifiche la UNI 10411-1/-11:2024 (punto 23) ammette l'allarme nuovo secondo la EN 81-20 5.12.3.1 o la UNI EN 81-28:2022</t>
+          <t>impianti elettrici a frizione fuori dalla 95/16/CE e dalla 2014/33/UE; esclude le modifiche che cambiano le misure antincendio (per queste, a nostro giudizio, il DM 15/09/2005 o il Codice V.3)</t>
         </is>
       </c>
       <c r="E169" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-28:2022</t>
+          <t>UNI 10411-1:2024, scopo</t>
         </is>
       </c>
       <c r="F169" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G169" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H169" s="10" t="inlineStr">
@@ -8579,33 +8579,33 @@
       <c r="M169" s="11" t="n"/>
       <c r="N169" s="11" t="n"/>
     </row>
-    <row r="170" ht="95" customHeight="1">
+    <row r="170" ht="121" customHeight="1">
       <c r="A170" s="10" t="n">
         <v>168</v>
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-58:2022 (resistenza al fuoco delle porte di piano)</t>
+          <t>Collaudo: UNI 10411-1:2024</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
+          <t>UNI 10411-1:2024, 14.4 a)–g)</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>porte di piano resistenti al fuoco (classi E, EI, EW) provate secondo la norma, quando fanno parte della compartimentazione del vano; sostituirle con modelli diversi è una modifica sostanziale ai fini antincendio (la UNI EN 81-20:2020, 5.3.5.2, richiama con data la EN 81-58:2003: quale certificato accettare lo decide l'organismo)</t>
+          <t>con la macchina nuova: temporizzatore del motore (EN 81-20 5.9.2.7); arresto in salita prima della velocità d'intervento del limitatore; protezioni ACOP e UCM esistenti che continuano a funzionare; dispositivo d'arresto presso la macchina (5.12.1.11.1 e)); pulegge nel locale secondo la 5.5.7; senza UCM e con la regolazione di velocità, macchinario senza alimentazione se il freno non si apre, con ripristino solo manuale</t>
         </is>
       </c>
       <c r="E170" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
+          <t>UNI 10411-1:2024, 14.4 a)–g)</t>
         </is>
       </c>
       <c r="F170" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G170" s="10" t="inlineStr">
@@ -8625,38 +8625,38 @@
       <c r="M170" s="11" t="n"/>
       <c r="N170" s="11" t="n"/>
     </row>
-    <row r="171" ht="95" customHeight="1">
+    <row r="171" ht="56" customHeight="1">
       <c r="A171" s="10" t="n">
         <v>169</v>
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+          <t>Collaudo: UNI 10411-11:2024</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.1</t>
+          <t>UNI 10411-11:2024, scopo</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>tipi di cabina (larghezza × profondità, luce della porta): 1) 1000 × 1300, 800; 2) 1100 × 1400, 900; 3) 1100 × 2100, 900; 4) 1600 × 1400 o 1400 × 1600, 900; 5) 2000 × 1400 o 1400 × 2000, 1100 mm (la UNI EN 81-70:2005 letta, Prospetto 1, ha tre tipi: 1000 × 1250, 1100 × 1400 e 2000 × 1400 mm)</t>
+          <t>impianti elettrici a frizione marcati CE secondo la Direttiva; esclude le modifiche che cambiano le misure antincendio (per queste, a nostro giudizio, il DM 15/09/2005 o il Codice V.3)</t>
         </is>
       </c>
       <c r="E171" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.1</t>
+          <t>UNI 10411-11:2024, scopo</t>
         </is>
       </c>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G171" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H171" s="10" t="inlineStr">
@@ -8671,38 +8671,38 @@
       <c r="M171" s="11" t="n"/>
       <c r="N171" s="11" t="n"/>
     </row>
-    <row r="172" ht="95" customHeight="1">
+    <row r="172" ht="108" customHeight="1">
       <c r="A172" s="10" t="n">
         <v>170</v>
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+          <t>Collaudo: UNI 10411-11:2024</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
+          <t>UNI 10411-11:2024, 14.3 a) e App. A (14); UNI EN 81-20:2020, 5.6.6.2 e 5.6.7.3</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>specchio nei tipi 1–3; finiture che riducono le misure nominali al massimo di 15 mm per parete; segnale acustico regolabile 35–65 dB(A), fino a 80 in ambienti rumorosi; contrasto di Michelson con la A1:2022 (nella UNI EN 81-70:2005 letta: specchio nei tipi 1 e 2, 15 mm, 35–65 dB(A); non ci sono gli 80 dB(A) né il contrasto di Michelson)</t>
+          <t>cambiando la macchina: le protezioni UCM esistenti devono continuare a funzionare (14.3 a)); per l'ACOP esistente l'App. A (14) chiede una relazione sulla compatibilità della nuova macchina, oppure nuovi dispositivi con certificato di esame di tipo e dichiarazione di conformità; il freno della macchina vale come organo d'arresto solo se ridondante e autocontrollato</t>
         </is>
       </c>
       <c r="E172" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
+          <t>UNI 10411-11:2024, 14.3 a) e App. A (14); UNI EN 81-20:2020, 5.6.6.2 e 5.6.7.3</t>
         </is>
       </c>
       <c r="F172" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G172" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H172" s="10" t="inlineStr">
@@ -8717,33 +8717,33 @@
       <c r="M172" s="11" t="n"/>
       <c r="N172" s="11" t="n"/>
     </row>
-    <row r="173" ht="43" customHeight="1">
+    <row r="173" ht="56" customHeight="1">
       <c r="A173" s="10" t="n">
         <v>171</v>
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+          <t>Collaudo: UNI 10411-11:2024</t>
         </is>
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, scopo</t>
+          <t>UNI 10411-11:2024, 14.3 b)</t>
         </is>
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>si usa con la UNI EN 81-20:2020; per gli impianti esistenti vale la UNI EN 81-82</t>
+          <t>senza UCM conforme alla 5.6.7 e con il rallentamento controllato: macchinario senza alimentazione se il freno non si apre, al più tardi all'arrivo al piano, con ripristino solo manuale</t>
         </is>
       </c>
       <c r="E173" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, scopo</t>
+          <t>UNI 10411-11:2024, 14.3 b)</t>
         </is>
       </c>
       <c r="F173" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G173" s="10" t="inlineStr">
@@ -8763,38 +8763,38 @@
       <c r="M173" s="11" t="n"/>
       <c r="N173" s="11" t="n"/>
     </row>
-    <row r="174" ht="43" customHeight="1">
+    <row r="174" ht="56" customHeight="1">
       <c r="A174" s="10" t="n">
         <v>172</v>
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-71 (ascensori antivandalo)</t>
+          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-71</t>
+          <t>UNI EN 81-21:2022, 1</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>categoria antivandalo da concordare con il committente; per la presunzione di conformità vale l'edizione 2005+A1:2006</t>
+          <t>ascensori nuovi in un edificio esistente, dove l'edificio non permette di rispettare tutta la UNI EN 81-20:2020; esclusi gli impianti montati prima della sua pubblicazione</t>
         </is>
       </c>
       <c r="E174" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-71</t>
+          <t>UNI EN 81-21:2022, 1</t>
         </is>
       </c>
       <c r="F174" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G174" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H174" s="10" t="inlineStr">
@@ -8809,33 +8809,33 @@
       <c r="M174" s="11" t="n"/>
       <c r="N174" s="11" t="n"/>
     </row>
-    <row r="175" ht="108" customHeight="1">
+    <row r="175" ht="95" customHeight="1">
       <c r="A175" s="10" t="n">
         <v>173</v>
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 7 (valori); Codice V.3.3.4</t>
+          <t>UNI EN 81-21:2022, 6.2 e 7.1</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>ascensore antincendio: tutti i piani serviti; vano e porte di piano almeno REI 60; cabina interna almeno 1,10 × 2,10 m con accesso sul lato corto; botola sul tetto almeno 0,50 × 0,70 m; area dedicata almeno 5 m² a ogni piano; luce d'emergenza almeno 5 lux con 1 h di autonomia; IPX3 dove arriva l'acqua; linea dedicata con alimentazione di sicurezza</t>
+          <t>oltre alle prove della EN 81-20 6.3: arresti mobili e sistema di arresto preattivato provati in moto a velocità nominale (in testata a cabina vuota, in fossa con il carico nominale), corsa dei loro ammortizzatori e distanza di frenatura; nelle istruzioni: quanto frena il sistema, col valore nominale e i due limiti</t>
         </is>
       </c>
       <c r="E175" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 7 (valori); Codice V.3.3.4</t>
+          <t>UNI EN 81-21:2022, 6.2 e 7.1</t>
         </is>
       </c>
       <c r="F175" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G175" s="10" t="inlineStr">
@@ -8855,28 +8855,28 @@
       <c r="M175" s="11" t="n"/>
       <c r="N175" s="11" t="n"/>
     </row>
-    <row r="176" ht="56" customHeight="1">
+    <row r="176" ht="82" customHeight="1">
       <c r="A176" s="10" t="n">
         <v>174</v>
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>Codice S.10, Tab. S.10-2</t>
+          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>alimentazione di sicurezza dell'ascensore antincendio: interruzione al massimo 15 s, autonomia oltre 30 min</t>
+          <t>spazi di rifugio ridotti solo con l'accordo preventivo: in edificio esistente PEC al Ministero con la certificazione dell'organismo prima dell'installazione (Procedura 2: dichiarazione dei punti della EN 81-21 applicati); la EN 81-21 da sola non giustifica la deroga</t>
         </is>
       </c>
       <c r="E176" s="10" t="inlineStr">
         <is>
-          <t>Codice S.10, Tab. S.10-2</t>
+          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
         </is>
       </c>
       <c r="F176" s="10" t="inlineStr">
@@ -8901,38 +8901,38 @@
       <c r="M176" s="11" t="n"/>
       <c r="N176" s="11" t="n"/>
     </row>
-    <row r="177" ht="56" customHeight="1">
+    <row r="177" ht="82" customHeight="1">
       <c r="A177" s="10" t="n">
         <v>175</v>
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-72:2020</t>
+          <t>UNI EN 81-20:2020, 5.12.3.1; UNI EN 81-28:2004, 4.1.3, 4.2.1 e 7</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>requisiti propri della norma (cabina, tempi, protezione dall'acqua) da verificare sul testo</t>
+          <t>la EN 81-20 richiama con data la EN 81-28:2003 (UNI EN 81-28:2004): prova automatica del collegamento almeno ogni 3 giorni; con alimentazione a batteria, avviso al servizio di soccorso quando l'autonomia residua scende sotto 1 h; pulsante d'allarme giallo con il simbolo della campana</t>
         </is>
       </c>
       <c r="E177" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-72:2020</t>
+          <t>UNI EN 81-20:2020, 5.12.3.1; UNI EN 81-28:2004, 4.1.3, 4.2.1 e 7</t>
         </is>
       </c>
       <c r="F177" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G177" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H177" s="10" t="inlineStr">
@@ -8947,28 +8947,28 @@
       <c r="M177" s="11" t="n"/>
       <c r="N177" s="11" t="n"/>
     </row>
-    <row r="178" ht="69" customHeight="1">
+    <row r="178" ht="56" customHeight="1">
       <c r="A178" s="10" t="n">
         <v>176</v>
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
+          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
+          <t>UNI EN 81-28:2022</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>quando la compartimentazione lo richiede, su comando della rivelazione incendio la cabina va al piano prestabilito e lascia uscire i passeggeri; con il Codice l'ascensore «dovrebbe» essere conforme alla UNI EN 81-73</t>
+          <t>requisiti dell'edizione citata in GUUE da verificare sul testo; nelle modifiche la UNI 10411-1/-11:2024 (punto 23) ammette l'allarme nuovo secondo la EN 81-20 5.12.3.1 o la UNI EN 81-28:2022</t>
         </is>
       </c>
       <c r="E178" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
+          <t>UNI EN 81-28:2022</t>
         </is>
       </c>
       <c r="F178" s="10" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="G178" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H178" s="10" t="inlineStr">
@@ -8993,28 +8993,28 @@
       <c r="M178" s="11" t="n"/>
       <c r="N178" s="11" t="n"/>
     </row>
-    <row r="179" ht="56" customHeight="1">
+    <row r="179" ht="95" customHeight="1">
       <c r="A179" s="10" t="n">
         <v>177</v>
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
+          <t>Collaudo: UNI EN 81-58:2022 (resistenza al fuoco delle porte di piano)</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-73:2020</t>
+          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>segnali e comportamento della manovra da verificare sul testo; la norma serve anche da base per migliorare gli esistenti (così la UNI EN 81-73:2005 letta, punto 1)</t>
+          <t>porte di piano resistenti al fuoco (classi E, EI, EW) provate secondo la norma, quando fanno parte della compartimentazione del vano; sostituirle con modelli diversi è una modifica sostanziale ai fini antincendio (la UNI EN 81-20:2020, 5.3.5.2, richiama con data la EN 81-58:2003: quale certificato accettare lo decide l'organismo)</t>
         </is>
       </c>
       <c r="E179" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-73:2020</t>
+          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
         </is>
       </c>
       <c r="F179" s="10" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="G179" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H179" s="10" t="inlineStr">
@@ -9039,28 +9039,28 @@
       <c r="M179" s="11" t="n"/>
       <c r="N179" s="11" t="n"/>
     </row>
-    <row r="180" ht="69" customHeight="1">
+    <row r="180" ht="95" customHeight="1">
       <c r="A180" s="10" t="n">
         <v>178</v>
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-76:2025 (evacuazione delle persone con disabilità)</t>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
         </is>
       </c>
       <c r="C180" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-76:2025</t>
+          <t>UNI EN 81-70:2022, 5.3.1</t>
         </is>
       </c>
       <c r="D180" s="10" t="inlineStr">
         <is>
-          <t>evacuazione delle persone con disabilità con l'ascensore: requisiti aggiuntivi alla EN 81-20 (manovra, alimentazione) da verificare sul testo</t>
+          <t>tipi di cabina (larghezza × profondità, luce della porta): 1) 1000 × 1300, 800; 2) 1100 × 1400, 900; 3) 1100 × 2100, 900; 4) 1600 × 1400 o 1400 × 1600, 900; 5) 2000 × 1400 o 1400 × 2000, 1100 mm (la UNI EN 81-70:2005 letta, Prospetto 1, ha tre tipi: 1000 × 1250, 1100 × 1400 e 2000 × 1400 mm)</t>
         </is>
       </c>
       <c r="E180" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-76:2025</t>
+          <t>UNI EN 81-70:2022, 5.3.1</t>
         </is>
       </c>
       <c r="F180" s="10" t="inlineStr">
@@ -9085,28 +9085,28 @@
       <c r="M180" s="11" t="n"/>
       <c r="N180" s="11" t="n"/>
     </row>
-    <row r="181" ht="56" customHeight="1">
+    <row r="181" ht="95" customHeight="1">
       <c r="A181" s="10" t="n">
         <v>179</v>
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 1</t>
+          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>con accelerazione di progetto a_d fino a 1 m/s² nessuna prescrizione specifica; a_d e la posizione dei rilevatori si concordano con il progettista dell'edificio</t>
+          <t>specchio nei tipi 1–3; finiture che riducono le misure nominali al massimo di 15 mm per parete; segnale acustico regolabile 35–65 dB(A), fino a 80 in ambienti rumorosi; contrasto di Michelson con la A1:2022 (nella UNI EN 81-70:2005 letta: specchio nei tipi 1 e 2, 15 mm, 35–65 dB(A); non ci sono gli 80 dB(A) né il contrasto di Michelson)</t>
         </is>
       </c>
       <c r="E181" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 1</t>
+          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
         </is>
       </c>
       <c r="F181" s="10" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="G181" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H181" s="10" t="inlineStr">
@@ -9131,28 +9131,28 @@
       <c r="M181" s="11" t="n"/>
       <c r="N181" s="11" t="n"/>
     </row>
-    <row r="182" ht="95" customHeight="1">
+    <row r="182" ht="43" customHeight="1">
       <c r="A182" s="10" t="n">
         <v>180</v>
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
         </is>
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
+          <t>UNI EN 81-70:2022, scopo</t>
         </is>
       </c>
       <c r="D182" s="10" t="inlineStr">
         <is>
-          <t>oltre 1 m/s²: massa della cabina nei calcoli (5.4.1), ritegni della cabina (5.4.2) e del contrappeso (5.5), protezione delle pulegge (5.6.1), tensioni e frecce delle guide (5.8.2, All. D), rilevazione e modo sismico (5.10.3, 5.10.4); soglie delle categorie dell'All. A da verificare sul testo</t>
+          <t>si usa con la UNI EN 81-20:2020; per gli impianti esistenti vale la UNI EN 81-82</t>
         </is>
       </c>
       <c r="E182" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
+          <t>UNI EN 81-70:2022, scopo</t>
         </is>
       </c>
       <c r="F182" s="10" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="G182" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H182" s="10" t="inlineStr">
@@ -9183,22 +9183,22 @@
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-71 (ascensori antivandalo)</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 0.3</t>
+          <t>UNI EN 81-71</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>non si applica agli impianti installati prima della sua pubblicazione</t>
+          <t>categoria antivandalo da concordare con il committente; per la presunzione di conformità vale l'edizione 2005+A1:2006</t>
         </is>
       </c>
       <c r="E183" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 0.3</t>
+          <t>UNI EN 81-71</t>
         </is>
       </c>
       <c r="F183" s="10" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="G183" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H183" s="10" t="inlineStr">
@@ -9223,33 +9223,33 @@
       <c r="M183" s="11" t="n"/>
       <c r="N183" s="11" t="n"/>
     </row>
-    <row r="184" ht="69" customHeight="1">
+    <row r="184" ht="108" customHeight="1">
       <c r="A184" s="10" t="n">
         <v>182</v>
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
         </is>
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-80:2004 e 2009, 1 e appendice A</t>
+          <t>DM 15/09/2005, punto 7 (valori); Codice V.3.3.4</t>
         </is>
       </c>
       <c r="D184" s="10" t="inlineStr">
         <is>
-          <t>analisi dei rischi dell'impianto esistente e piano di miglioramento per priorità; quali misure e in che tempi lo decide la legislazione nazionale, non la norma</t>
+          <t>ascensore antincendio: tutti i piani serviti; vano e porte di piano almeno REI 60; cabina interna almeno 1,10 × 2,10 m con accesso sul lato corto; botola sul tetto almeno 0,50 × 0,70 m; area dedicata almeno 5 m² a ogni piano; luce d'emergenza almeno 5 lux con 1 h di autonomia; IPX3 dove arriva l'acqua; linea dedicata con alimentazione di sicurezza</t>
         </is>
       </c>
       <c r="E184" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-80:2004 e 2009, 1 e appendice A</t>
+          <t>DM 15/09/2005, punto 7 (valori); Codice V.3.3.4</t>
         </is>
       </c>
       <c r="F184" s="10" t="inlineStr">
         <is>
-          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G184" s="10" t="inlineStr">
@@ -9269,28 +9269,28 @@
       <c r="M184" s="11" t="n"/>
       <c r="N184" s="11" t="n"/>
     </row>
-    <row r="185" ht="69" customHeight="1">
+    <row r="185" ht="56" customHeight="1">
       <c r="A185" s="10" t="n">
         <v>183</v>
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
         </is>
       </c>
       <c r="C185" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-80:2019</t>
+          <t>Codice S.10, Tab. S.10-2</t>
         </is>
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>la stessa analisi nell'edizione in vigore, con una struttura diversa: da verificare sul testo</t>
+          <t>alimentazione di sicurezza dell'ascensore antincendio: interruzione al massimo 15 s, autonomia oltre 30 min</t>
         </is>
       </c>
       <c r="E185" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-80:2019</t>
+          <t>Codice S.10, Tab. S.10-2</t>
         </is>
       </c>
       <c r="F185" s="10" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="G185" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H185" s="10" t="inlineStr">
@@ -9321,22 +9321,22 @@
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-82:2026 (accessibilità degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-82:2026</t>
+          <t>UNI EN 81-72:2020</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>miglioramento dell'accessibilità di un impianto esistente secondo i requisiti della EN 81-70</t>
+          <t>requisiti propri della norma (cabina, tempi, protezione dall'acqua) da verificare sul testo</t>
         </is>
       </c>
       <c r="E186" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-82:2026</t>
+          <t>UNI EN 81-72:2020</t>
         </is>
       </c>
       <c r="F186" s="10" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="G186" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H186" s="10" t="inlineStr">
@@ -9361,28 +9361,28 @@
       <c r="M186" s="11" t="n"/>
       <c r="N186" s="11" t="n"/>
     </row>
-    <row r="187" ht="56" customHeight="1">
+    <row r="187" ht="69" customHeight="1">
       <c r="A187" s="10" t="n">
         <v>185</v>
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-83:2026 (antivandalo degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
         </is>
       </c>
       <c r="C187" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-83:2026</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
         </is>
       </c>
       <c r="D187" s="10" t="inlineStr">
         <is>
-          <t>miglioramento della resistenza agli atti vandalici di un impianto esistente secondo la EN 81-71:2022 (voce 1.2 della Tab. A.1 della EN 81-80)</t>
+          <t>quando la compartimentazione lo richiede, su comando della rivelazione incendio la cabina va al piano prestabilito e lascia uscire i passeggeri; con il Codice l'ascensore «dovrebbe» essere conforme alla UNI EN 81-73</t>
         </is>
       </c>
       <c r="E187" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-83:2026</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
         </is>
       </c>
       <c r="F187" s="10" t="inlineStr">
@@ -9413,37 +9413,37 @@
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-73:2020</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>piattaforma di distribuzione davanti alla porta di cabina: 1,50 × 1,50 m negli edifici nuovi, 1,40 × 1,40 m nell'adeguamento (fuori dal vano: in sito)</t>
+          <t>segnali e comportamento della manovra da verificare sul testo; la norma serve anche da base per migliorare gli esistenti (così la UNI EN 81-73:2005 letta, punto 1)</t>
         </is>
       </c>
       <c r="E188" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-73:2020</t>
         </is>
       </c>
       <c r="F188" s="10" t="inlineStr">
         <is>
-          <t>testo ufficiale del DM 236/1989</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G188" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H188" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I188" s="11" t="n"/>
@@ -9453,43 +9453,43 @@
       <c r="M188" s="11" t="n"/>
       <c r="N188" s="11" t="n"/>
     </row>
-    <row r="189" ht="56" customHeight="1">
+    <row r="189" ht="69" customHeight="1">
       <c r="A189" s="10" t="n">
         <v>187</v>
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-76:2025 (evacuazione delle persone con disabilità)</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-76:2025</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>porte di cabina e di piano a scorrimento automatico (nell'adeguamento la porta di piano può essere a battente se ad apertura automatica); porte aperte almeno 8 s, chiusura in almeno 4 s</t>
+          <t>evacuazione delle persone con disabilità con l'ascensore: requisiti aggiuntivi alla EN 81-20 (manovra, alimentazione) da verificare sul testo</t>
         </is>
       </c>
       <c r="E189" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-76:2025</t>
         </is>
       </c>
       <c r="F189" s="10" t="inlineStr">
         <is>
-          <t>testo ufficiale del DM 236/1989</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G189" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H189" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I189" s="11" t="n"/>
@@ -9499,33 +9499,33 @@
       <c r="M189" s="11" t="n"/>
       <c r="N189" s="11" t="n"/>
     </row>
-    <row r="190" ht="43" customHeight="1">
+    <row r="190" ht="56" customHeight="1">
       <c r="A190" s="10" t="n">
         <v>188</v>
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-77:2022, 1</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>arresto ai piani con autolivellamento entro ± 2 cm; sosta ai piani con le porte chiuse</t>
+          <t>con accelerazione di progetto a_d fino a 1 m/s² nessuna prescrizione specifica; a_d e la posizione dei rilevatori si concordano con il progettista dell'edificio</t>
         </is>
       </c>
       <c r="E190" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-77:2022, 1</t>
         </is>
       </c>
       <c r="F190" s="10" t="inlineStr">
         <is>
-          <t>testo ufficiale del DM 236/1989</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G190" s="10" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="H190" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I190" s="11" t="n"/>
@@ -9545,43 +9545,43 @@
       <c r="M190" s="11" t="n"/>
       <c r="N190" s="11" t="n"/>
     </row>
-    <row r="191" ht="56" customHeight="1">
+    <row r="191" ht="95" customHeight="1">
       <c r="A191" s="10" t="n">
         <v>189</v>
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
+          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>pulsanti di cabina e di piano: il più alto tra 1,10 e 1,40 m, misurato all'asse del comando; bottoniera di cabina su una parete laterale ad almeno 0,35 m dalla porta</t>
+          <t>oltre 1 m/s²: massa della cabina nei calcoli (5.4.1), ritegni della cabina (5.4.2) e del contrappeso (5.5), protezione delle pulegge (5.6.1), tensioni e frecce delle guide (5.8.2, All. D), rilevazione e modo sismico (5.10.3, 5.10.4); soglie delle categorie dell'All. A da verificare sul testo</t>
         </is>
       </c>
       <c r="E191" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
+          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
         </is>
       </c>
       <c r="F191" s="10" t="inlineStr">
         <is>
-          <t>testo ufficiale del DM 236/1989</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G191" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H191" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I191" s="11" t="n"/>
@@ -9591,33 +9591,33 @@
       <c r="M191" s="11" t="n"/>
       <c r="N191" s="11" t="n"/>
     </row>
-    <row r="192" ht="95" customHeight="1">
+    <row r="192" ht="43" customHeight="1">
       <c r="A192" s="10" t="n">
         <v>190</v>
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
+          <t>UNI EN 81-77:2022, 0.3</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>citofono in cabina tra 1,10 e 1,30 m; luce d'emergenza con almeno 3 h di autonomia; campanello d'allarme e segnale luminoso di allarme ricevuto; arresto e inversione della chiusura; segnale acustico d'arrivo; numeri in rilievo e Braille, targa Braille di piano; sedile ribaltabile dove possibile</t>
+          <t>non si applica agli impianti installati prima della sua pubblicazione</t>
         </is>
       </c>
       <c r="E192" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
+          <t>UNI EN 81-77:2022, 0.3</t>
         </is>
       </c>
       <c r="F192" s="10" t="inlineStr">
         <is>
-          <t>testo ufficiale del DM 236/1989</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G192" s="10" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="H192" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I192" s="11" t="n"/>
@@ -9637,33 +9637,33 @@
       <c r="M192" s="11" t="n"/>
       <c r="N192" s="11" t="n"/>
     </row>
-    <row r="193" ht="56" customHeight="1">
+    <row r="193" ht="69" customHeight="1">
       <c r="A193" s="10" t="n">
         <v>191</v>
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
+          <t>UNI EN 81-80:2004 e 2009, 1 e appendice A</t>
         </is>
       </c>
       <c r="D193" s="10" t="inlineStr">
         <is>
-          <t>ascensore obbligatorio oltre il terzo livello (contati interrati e porticati); negli immobili con più di tre livelli fuori terra un ascensore per ogni scala principale</t>
+          <t>analisi dei rischi dell'impianto esistente e piano di miglioramento per priorità; quali misure e in che tempi lo decide la legislazione nazionale, non la norma</t>
         </is>
       </c>
       <c r="E193" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
+          <t>UNI EN 81-80:2004 e 2009, 1 e appendice A</t>
         </is>
       </c>
       <c r="F193" s="10" t="inlineStr">
         <is>
-          <t>testo ufficiale del DM 236/1989; L. 13/1989: ricerca, cap. 16</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G193" s="10" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="H193" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I193" s="11" t="n"/>
@@ -9683,43 +9683,43 @@
       <c r="M193" s="11" t="n"/>
       <c r="N193" s="11" t="n"/>
     </row>
-    <row r="194" ht="56" customHeight="1">
+    <row r="194" ht="69" customHeight="1">
       <c r="A194" s="10" t="n">
         <v>192</v>
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
         </is>
       </c>
       <c r="C194" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+          <t>UNI EN 81-80:2019</t>
         </is>
       </c>
       <c r="D194" s="10" t="inlineStr">
         <is>
-          <t>nelle ristrutturazioni deroghe per impossibilità tecnica strutturale o impiantistica (privati: concesse dal Sindaco); edifici vincolati: deroga se le opere pregiudicano il bene</t>
+          <t>la stessa analisi nell'edizione in vigore, con una struttura diversa: da verificare sul testo</t>
         </is>
       </c>
       <c r="E194" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+          <t>UNI EN 81-80:2019</t>
         </is>
       </c>
       <c r="F194" s="10" t="inlineStr">
         <is>
-          <t>testo ufficiale del DM 236/1989; DPR 503/1996: ricerca, cap. 16</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G194" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H194" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I194" s="11" t="n"/>
@@ -9729,28 +9729,28 @@
       <c r="M194" s="11" t="n"/>
       <c r="N194" s="11" t="n"/>
     </row>
-    <row r="195" ht="69" customHeight="1">
+    <row r="195" ht="56" customHeight="1">
       <c r="A195" s="10" t="n">
         <v>193</v>
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: UNI EN 81-82:2026 (accessibilità degli esistenti)</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+          <t>UNI EN 81-82:2026</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>il progettista applica il DM 15/09/2005 oppure la RTV V.3 del Codice: dove si usa il Codice il DM 2005 non si applica</t>
+          <t>miglioramento dell'accessibilità di un impianto esistente secondo i requisiti della EN 81-70</t>
         </is>
       </c>
       <c r="E195" s="10" t="inlineStr">
         <is>
-          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+          <t>UNI EN 81-82:2026</t>
         </is>
       </c>
       <c r="F195" s="10" t="inlineStr">
@@ -9775,28 +9775,28 @@
       <c r="M195" s="11" t="n"/>
       <c r="N195" s="11" t="n"/>
     </row>
-    <row r="196" ht="95" customHeight="1">
+    <row r="196" ht="56" customHeight="1">
       <c r="A196" s="10" t="n">
         <v>194</v>
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: UNI EN 81-83:2026 (antivandalo degli esistenti)</t>
         </is>
       </c>
       <c r="C196" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, art. 1 c.2</t>
+          <t>UNI EN 81-83:2026</t>
         </is>
       </c>
       <c r="D196" s="10" t="inlineStr">
         <is>
-          <t>sugli impianti esistenti vale per le modifiche sostanziali: nuovo impianto; più fermate o altro azionamento; pareti del vano, porte di piano, locale macchine o pulegge sostituiti con materiali, modelli, dimensioni o criteri diversi; solai o scale rifatti che coinvolgono l'impianto; sopraelevazione; cambio di destinazione d'uso</t>
+          <t>miglioramento della resistenza agli atti vandalici di un impianto esistente secondo la EN 81-71:2022 (voce 1.2 della Tab. A.1 della EN 81-80)</t>
         </is>
       </c>
       <c r="E196" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, art. 1 c.2</t>
+          <t>UNI EN 81-83:2026</t>
         </is>
       </c>
       <c r="F196" s="10" t="inlineStr">
@@ -9821,33 +9821,33 @@
       <c r="M196" s="11" t="n"/>
       <c r="N196" s="11" t="n"/>
     </row>
-    <row r="197" ht="69" customHeight="1">
+    <row r="197" ht="56" customHeight="1">
       <c r="A197" s="10" t="n">
         <v>195</v>
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C197" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="D197" s="10" t="inlineStr">
         <is>
-          <t>tipo di vano: aperto, protetto o a prova di fumo (Codice: classi da SA a SE)</t>
+          <t>piattaforma di distribuzione davanti alla porta di cabina: 1,50 × 1,50 m negli edifici nuovi, 1,40 × 1,40 m nell'adeguamento (fuori dal vano: in sito)</t>
         </is>
       </c>
       <c r="E197" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F197" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989</t>
         </is>
       </c>
       <c r="G197" s="10" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="H197" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I197" s="11" t="n"/>
@@ -9867,33 +9867,33 @@
       <c r="M197" s="11" t="n"/>
       <c r="N197" s="11" t="n"/>
     </row>
-    <row r="198" ht="69" customHeight="1">
+    <row r="198" ht="56" customHeight="1">
       <c r="A198" s="10" t="n">
         <v>196</v>
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C198" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 2</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="D198" s="10" t="inlineStr">
         <is>
-          <t>pareti del vano, locale macchine e pulegge, setti e arcata non combustibili; pareti, pavimento e tetto della cabina in classe di reazione al fuoco non oltre 1</t>
+          <t>porte di cabina e di piano a scorrimento automatico (nell'adeguamento la porta di piano può essere a battente se ad apertura automatica); porte aperte almeno 8 s, chiusura in almeno 4 s</t>
         </is>
       </c>
       <c r="E198" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 2</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F198" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989</t>
         </is>
       </c>
       <c r="G198" s="10" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="H198" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I198" s="11" t="n"/>
@@ -9913,33 +9913,33 @@
       <c r="M198" s="11" t="n"/>
       <c r="N198" s="11" t="n"/>
     </row>
-    <row r="199" ht="82" customHeight="1">
+    <row r="199" ht="43" customHeight="1">
       <c r="A199" s="10" t="n">
         <v>197</v>
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C199" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 5</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="D199" s="10" t="inlineStr">
         <is>
-          <t>aerazione permanente in alto verso spazi scoperti di almeno il 3 % della pianta (vano almeno 0,20 m², locale macchine o pulegge almeno 0,05 m²), con una protezione che non lascia passare una sfera oltre 15 mm; non serve se il vano è aperto su spazi scoperti</t>
+          <t>arresto ai piani con autolivellamento entro ± 2 cm; sosta ai piani con le porte chiuse</t>
         </is>
       </c>
       <c r="E199" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 5</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F199" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989</t>
         </is>
       </c>
       <c r="G199" s="10" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="H199" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I199" s="11" t="n"/>
@@ -9959,33 +9959,33 @@
       <c r="M199" s="11" t="n"/>
       <c r="N199" s="11" t="n"/>
     </row>
-    <row r="200" ht="69" customHeight="1">
+    <row r="200" ht="56" customHeight="1">
       <c r="A200" s="10" t="n">
         <v>198</v>
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
         <is>
-          <t>estintore 21A89BC vicino all'accesso al macchinario; richiamo della cabina al piano prestabilito su comando della rivelazione quando la compartimentazione lo richiede</t>
+          <t>pulsanti di cabina e di piano: il più alto tra 1,10 e 1,40 m, misurato all'asse del comando; bottoniera di cabina su una parete laterale ad almeno 0,35 m dalla porta</t>
         </is>
       </c>
       <c r="E200" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
         </is>
       </c>
       <c r="F200" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989</t>
         </is>
       </c>
       <c r="G200" s="10" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="H200" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I200" s="11" t="n"/>
@@ -10005,33 +10005,33 @@
       <c r="M200" s="11" t="n"/>
       <c r="N200" s="11" t="n"/>
     </row>
-    <row r="201" ht="69" customHeight="1">
+    <row r="201" ht="95" customHeight="1">
       <c r="A201" s="10" t="n">
         <v>199</v>
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
         <is>
-          <t>Codice S.9, Tab. S.9-3</t>
+          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>piani tra 32 e 54 m: almeno un ascensore antincendio; oltre 54 m: almeno uno di soccorso; interrati tra −10 e −15 m: antincendio; sotto −15 m: soccorso</t>
+          <t>citofono in cabina tra 1,10 e 1,30 m; luce d'emergenza con almeno 3 h di autonomia; campanello d'allarme e segnale luminoso di allarme ricevuto; arresto e inversione della chiusura; segnale acustico d'arrivo; numeri in rilievo e Braille, targa Braille di piano; sedile ribaltabile dove possibile</t>
         </is>
       </c>
       <c r="E201" s="10" t="inlineStr">
         <is>
-          <t>Codice S.9, Tab. S.9-3</t>
+          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
         </is>
       </c>
       <c r="F201" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989</t>
         </is>
       </c>
       <c r="G201" s="10" t="inlineStr">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="H201" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I201" s="11" t="n"/>
@@ -10051,33 +10051,33 @@
       <c r="M201" s="11" t="n"/>
       <c r="N201" s="11" t="n"/>
     </row>
-    <row r="202" ht="43" customHeight="1">
+    <row r="202" ht="56" customHeight="1">
       <c r="A202" s="10" t="n">
         <v>200</v>
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C202" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §3.1.4</t>
+          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
         </is>
       </c>
       <c r="D202" s="10" t="inlineStr">
         <is>
-          <t>carichi del macchinario valutati caso per caso sui massimi prevedibili e riportati nel progetto e nel collaudo statico</t>
+          <t>ascensore obbligatorio oltre il terzo livello (contati interrati e porticati); negli immobili con più di tre livelli fuori terra un ascensore per ogni scala principale</t>
         </is>
       </c>
       <c r="E202" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §3.1.4</t>
+          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
         </is>
       </c>
       <c r="F202" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989; L. 13/1989: ricerca, cap. 16</t>
         </is>
       </c>
       <c r="G202" s="10" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="H202" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I202" s="11" t="n"/>
@@ -10097,33 +10097,33 @@
       <c r="M202" s="11" t="n"/>
       <c r="N202" s="11" t="n"/>
     </row>
-    <row r="203" ht="43" customHeight="1">
+    <row r="203" ht="56" customHeight="1">
       <c r="A203" s="10" t="n">
         <v>201</v>
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §8.4.1</t>
+          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
         </is>
       </c>
       <c r="D203" s="10" t="inlineStr">
         <is>
-          <t>su un edificio esistente l'intervento è locale: verifica limitata alle parti interessate, senza ridurre la sicurezza preesistente</t>
+          <t>nelle ristrutturazioni deroghe per impossibilità tecnica strutturale o impiantistica (privati: concesse dal Sindaco); edifici vincolati: deroga se le opere pregiudicano il bene</t>
         </is>
       </c>
       <c r="E203" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §8.4.1</t>
+          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
         </is>
       </c>
       <c r="F203" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989; DPR 503/1996: ricerca, cap. 16</t>
         </is>
       </c>
       <c r="G203" s="10" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="H203" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
         </is>
       </c>
       <c r="I203" s="11" t="n"/>
@@ -10143,28 +10143,28 @@
       <c r="M203" s="11" t="n"/>
       <c r="N203" s="11" t="n"/>
     </row>
-    <row r="204" ht="43" customHeight="1">
+    <row r="204" ht="69" customHeight="1">
       <c r="A204" s="10" t="n">
         <v>202</v>
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §11.4.1</t>
+          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
         </is>
       </c>
       <c r="D204" s="10" t="inlineStr">
         <is>
-          <t>ancoranti per uso strutturale qualificati; con azioni sismiche categoria C2 per tutte le classi d'uso</t>
+          <t>il progettista applica il DM 15/09/2005 oppure la RTV V.3 del Codice: dove si usa il Codice il DM 2005 non si applica</t>
         </is>
       </c>
       <c r="E204" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §11.4.1</t>
+          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
         </is>
       </c>
       <c r="F204" s="10" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="H204" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I204" s="11" t="n"/>
@@ -10189,28 +10189,28 @@
       <c r="M204" s="11" t="n"/>
       <c r="N204" s="11" t="n"/>
     </row>
-    <row r="205" ht="108" customHeight="1">
+    <row r="205" ht="95" customHeight="1">
       <c r="A205" s="10" t="n">
         <v>203</v>
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
         </is>
       </c>
       <c r="C205" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §7.2.3–7.2.4</t>
+          <t>DM 15/09/2005, art. 1 c.2</t>
         </is>
       </c>
       <c r="D205" s="10" t="inlineStr">
         <is>
-          <t>forza sismica sull'elemento non strutturale Fa = Sa·Wa/qa; nessun vincolo ad attrito; studio specifico oltre il 30 % del carico permanente del solaio o il 10 % di quello dell'intera struttura; progetto antisismico dell'impianto del produttore, dei collegamenti dell'installatore, dei solai e delle pareti d'ancoraggio del progettista strutturale</t>
+          <t>sugli impianti esistenti vale per le modifiche sostanziali: nuovo impianto; più fermate o altro azionamento; pareti del vano, porte di piano, locale macchine o pulegge sostituiti con materiali, modelli, dimensioni o criteri diversi; solai o scale rifatti che coinvolgono l'impianto; sopraelevazione; cambio di destinazione d'uso</t>
         </is>
       </c>
       <c r="E205" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §7.2.3–7.2.4</t>
+          <t>DM 15/09/2005, art. 1 c.2</t>
         </is>
       </c>
       <c r="F205" s="10" t="inlineStr">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="H205" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I205" s="11" t="n"/>
@@ -10235,28 +10235,28 @@
       <c r="M205" s="11" t="n"/>
       <c r="N205" s="11" t="n"/>
     </row>
-    <row r="206" ht="43" customHeight="1">
+    <row r="206" ht="69" customHeight="1">
       <c r="A206" s="10" t="n">
         <v>204</v>
       </c>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
         </is>
       </c>
       <c r="C206" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
         </is>
       </c>
       <c r="D206" s="10" t="inlineStr">
         <is>
-          <t>impianti: stabilità allo SLV per tutte le classi d'uso; nelle classi III e IV anche funzionamento allo SLO</t>
+          <t>tipo di vano: aperto, protetto o a prova di fumo (Codice: classi da SA a SE)</t>
         </is>
       </c>
       <c r="E206" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
         </is>
       </c>
       <c r="F206" s="10" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="H206" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I206" s="11" t="n"/>
@@ -10281,10 +10281,424 @@
       <c r="M206" s="11" t="n"/>
       <c r="N206" s="11" t="n"/>
     </row>
+    <row r="207" ht="69" customHeight="1">
+      <c r="A207" s="10" t="n">
+        <v>205</v>
+      </c>
+      <c r="B207" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C207" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 2</t>
+        </is>
+      </c>
+      <c r="D207" s="10" t="inlineStr">
+        <is>
+          <t>pareti del vano, locale macchine e pulegge, setti e arcata non combustibili; pareti, pavimento e tetto della cabina in classe di reazione al fuoco non oltre 1</t>
+        </is>
+      </c>
+      <c r="E207" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 2</t>
+        </is>
+      </c>
+      <c r="F207" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G207" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H207" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I207" s="11" t="n"/>
+      <c r="J207" s="11" t="n"/>
+      <c r="K207" s="11" t="n"/>
+      <c r="L207" s="11" t="n"/>
+      <c r="M207" s="11" t="n"/>
+      <c r="N207" s="11" t="n"/>
+    </row>
+    <row r="208" ht="82" customHeight="1">
+      <c r="A208" s="10" t="n">
+        <v>206</v>
+      </c>
+      <c r="B208" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C208" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 5</t>
+        </is>
+      </c>
+      <c r="D208" s="10" t="inlineStr">
+        <is>
+          <t>aerazione permanente in alto verso spazi scoperti di almeno il 3 % della pianta (vano almeno 0,20 m², locale macchine o pulegge almeno 0,05 m²), con una protezione che non lascia passare una sfera oltre 15 mm; non serve se il vano è aperto su spazi scoperti</t>
+        </is>
+      </c>
+      <c r="E208" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 5</t>
+        </is>
+      </c>
+      <c r="F208" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G208" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H208" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I208" s="11" t="n"/>
+      <c r="J208" s="11" t="n"/>
+      <c r="K208" s="11" t="n"/>
+      <c r="L208" s="11" t="n"/>
+      <c r="M208" s="11" t="n"/>
+      <c r="N208" s="11" t="n"/>
+    </row>
+    <row r="209" ht="69" customHeight="1">
+      <c r="A209" s="10" t="n">
+        <v>207</v>
+      </c>
+      <c r="B209" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C209" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+        </is>
+      </c>
+      <c r="D209" s="10" t="inlineStr">
+        <is>
+          <t>estintore 21A89BC vicino all'accesso al macchinario; richiamo della cabina al piano prestabilito su comando della rivelazione quando la compartimentazione lo richiede</t>
+        </is>
+      </c>
+      <c r="E209" s="10" t="inlineStr">
+        <is>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+        </is>
+      </c>
+      <c r="F209" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G209" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H209" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I209" s="11" t="n"/>
+      <c r="J209" s="11" t="n"/>
+      <c r="K209" s="11" t="n"/>
+      <c r="L209" s="11" t="n"/>
+      <c r="M209" s="11" t="n"/>
+      <c r="N209" s="11" t="n"/>
+    </row>
+    <row r="210" ht="69" customHeight="1">
+      <c r="A210" s="10" t="n">
+        <v>208</v>
+      </c>
+      <c r="B210" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+        </is>
+      </c>
+      <c r="C210" s="10" t="inlineStr">
+        <is>
+          <t>Codice S.9, Tab. S.9-3</t>
+        </is>
+      </c>
+      <c r="D210" s="10" t="inlineStr">
+        <is>
+          <t>piani tra 32 e 54 m: almeno un ascensore antincendio; oltre 54 m: almeno uno di soccorso; interrati tra −10 e −15 m: antincendio; sotto −15 m: soccorso</t>
+        </is>
+      </c>
+      <c r="E210" s="10" t="inlineStr">
+        <is>
+          <t>Codice S.9, Tab. S.9-3</t>
+        </is>
+      </c>
+      <c r="F210" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G210" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H210" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I210" s="11" t="n"/>
+      <c r="J210" s="11" t="n"/>
+      <c r="K210" s="11" t="n"/>
+      <c r="L210" s="11" t="n"/>
+      <c r="M210" s="11" t="n"/>
+      <c r="N210" s="11" t="n"/>
+    </row>
+    <row r="211" ht="43" customHeight="1">
+      <c r="A211" s="10" t="n">
+        <v>209</v>
+      </c>
+      <c r="B211" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C211" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §3.1.4</t>
+        </is>
+      </c>
+      <c r="D211" s="10" t="inlineStr">
+        <is>
+          <t>carichi del macchinario valutati caso per caso sui massimi prevedibili e riportati nel progetto e nel collaudo statico</t>
+        </is>
+      </c>
+      <c r="E211" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §3.1.4</t>
+        </is>
+      </c>
+      <c r="F211" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G211" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H211" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I211" s="11" t="n"/>
+      <c r="J211" s="11" t="n"/>
+      <c r="K211" s="11" t="n"/>
+      <c r="L211" s="11" t="n"/>
+      <c r="M211" s="11" t="n"/>
+      <c r="N211" s="11" t="n"/>
+    </row>
+    <row r="212" ht="43" customHeight="1">
+      <c r="A212" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="B212" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C212" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §8.4.1</t>
+        </is>
+      </c>
+      <c r="D212" s="10" t="inlineStr">
+        <is>
+          <t>su un edificio esistente l'intervento è locale: verifica limitata alle parti interessate, senza ridurre la sicurezza preesistente</t>
+        </is>
+      </c>
+      <c r="E212" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §8.4.1</t>
+        </is>
+      </c>
+      <c r="F212" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G212" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H212" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I212" s="11" t="n"/>
+      <c r="J212" s="11" t="n"/>
+      <c r="K212" s="11" t="n"/>
+      <c r="L212" s="11" t="n"/>
+      <c r="M212" s="11" t="n"/>
+      <c r="N212" s="11" t="n"/>
+    </row>
+    <row r="213" ht="43" customHeight="1">
+      <c r="A213" s="10" t="n">
+        <v>211</v>
+      </c>
+      <c r="B213" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C213" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §11.4.1</t>
+        </is>
+      </c>
+      <c r="D213" s="10" t="inlineStr">
+        <is>
+          <t>ancoranti per uso strutturale qualificati; con azioni sismiche categoria C2 per tutte le classi d'uso</t>
+        </is>
+      </c>
+      <c r="E213" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §11.4.1</t>
+        </is>
+      </c>
+      <c r="F213" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G213" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H213" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I213" s="11" t="n"/>
+      <c r="J213" s="11" t="n"/>
+      <c r="K213" s="11" t="n"/>
+      <c r="L213" s="11" t="n"/>
+      <c r="M213" s="11" t="n"/>
+      <c r="N213" s="11" t="n"/>
+    </row>
+    <row r="214" ht="108" customHeight="1">
+      <c r="A214" s="10" t="n">
+        <v>212</v>
+      </c>
+      <c r="B214" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C214" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §7.2.3–7.2.4</t>
+        </is>
+      </c>
+      <c r="D214" s="10" t="inlineStr">
+        <is>
+          <t>forza sismica sull'elemento non strutturale Fa = Sa·Wa/qa; nessun vincolo ad attrito; studio specifico oltre il 30 % del carico permanente del solaio o il 10 % di quello dell'intera struttura; progetto antisismico dell'impianto del produttore, dei collegamenti dell'installatore, dei solai e delle pareti d'ancoraggio del progettista strutturale</t>
+        </is>
+      </c>
+      <c r="E214" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §7.2.3–7.2.4</t>
+        </is>
+      </c>
+      <c r="F214" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G214" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H214" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I214" s="11" t="n"/>
+      <c r="J214" s="11" t="n"/>
+      <c r="K214" s="11" t="n"/>
+      <c r="L214" s="11" t="n"/>
+      <c r="M214" s="11" t="n"/>
+      <c r="N214" s="11" t="n"/>
+    </row>
+    <row r="215" ht="43" customHeight="1">
+      <c r="A215" s="10" t="n">
+        <v>213</v>
+      </c>
+      <c r="B215" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C215" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+        </is>
+      </c>
+      <c r="D215" s="10" t="inlineStr">
+        <is>
+          <t>impianti: stabilità allo SLV per tutte le classi d'uso; nelle classi III e IV anche funzionamento allo SLO</t>
+        </is>
+      </c>
+      <c r="E215" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+        </is>
+      </c>
+      <c r="F215" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G215" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H215" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I215" s="11" t="n"/>
+      <c r="J215" s="11" t="n"/>
+      <c r="K215" s="11" t="n"/>
+      <c r="L215" s="11" t="n"/>
+      <c r="M215" s="11" t="n"/>
+      <c r="N215" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N206"/>
+  <autoFilter ref="A1:N215"/>
   <dataValidations count="1">
-    <dataValidation sqref="I3:I206" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
+    <dataValidation sqref="I3:I215" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
       <formula1>"conforme,diverso,non applicabile"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10327,7 +10741,7 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$206,"da verificare")</f>
+        <f>COUNTIF(Voci!$G$3:$G$215,"da verificare")</f>
         <v/>
       </c>
     </row>
@@ -10338,7 +10752,7 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$206,"confermato")</f>
+        <f>COUNTIF(Voci!$G$3:$G$215,"confermato")</f>
         <v/>
       </c>
     </row>
@@ -10349,7 +10763,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$206,"scelta del software")</f>
+        <f>COUNTIF(Voci!$G$3:$G$215,"scelta del software")</f>
         <v/>
       </c>
     </row>
@@ -10360,7 +10774,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$206,"stima")</f>
+        <f>COUNTIF(Voci!$G$3:$G$215,"stima")</f>
         <v/>
       </c>
     </row>
@@ -10371,7 +10785,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$206,"derivazione")</f>
+        <f>COUNTIF(Voci!$G$3:$G$215,"derivazione")</f>
         <v/>
       </c>
     </row>
@@ -10382,7 +10796,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$206,"prassi di cantiere")</f>
+        <f>COUNTIF(Voci!$G$3:$G$215,"prassi di cantiere")</f>
         <v/>
       </c>
     </row>
@@ -10393,7 +10807,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTA(Voci!$A$3:$A$206)</f>
+        <f>COUNTA(Voci!$A$3:$A$215)</f>
         <v/>
       </c>
     </row>
@@ -10411,7 +10825,7 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$206,"conforme")</f>
+        <f>COUNTIF(Voci!$I$3:$I$215,"conforme")</f>
         <v/>
       </c>
     </row>
@@ -10422,7 +10836,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$206,"diverso")</f>
+        <f>COUNTIF(Voci!$I$3:$I$215,"diverso")</f>
         <v/>
       </c>
     </row>
@@ -10433,7 +10847,7 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$206,"non applicabile")</f>
+        <f>COUNTIF(Voci!$I$3:$I$215,"non applicabile")</f>
         <v/>
       </c>
     </row>
@@ -10444,14 +10858,14 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>COUNTBLANK(Voci!$I$3:$I$206)</f>
+        <f>COUNTBLANK(Voci!$I$3:$I$215)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Conteggi sulle righe 3–206 del foglio «Voci» (la riga 2 è l'esempio).</t>
+          <t>Conteggi sulle righe 3–215 del foglio «Voci» (la riga 2 è l'esempio).</t>
         </is>
       </c>
     </row>

--- a/liftpilot/docs/lista-verifica-normativa.xlsx
+++ b/liftpilot/docs/lista-verifica-normativa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Riepilogo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$215</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$220</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Voci'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N215"/>
+  <dimension ref="A1:N220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3841,7 +3841,7 @@
       <c r="M66" s="11" t="n"/>
       <c r="N66" s="11" t="n"/>
     </row>
-    <row r="67" ht="56" customHeight="1">
+    <row r="67" ht="69" customHeight="1">
       <c r="A67" s="10" t="n">
         <v>65</v>
       </c>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>cabina larga 950 mm e profonda 1300 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (fuori dal vano: da verificare in sito)</t>
+          <t>cabina larga 950 mm e profonda 1300 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (fuori dal vano: da verificare in sito); pulsanti più alti delle bottoniere tra 1100 e 1400 mm dal pavimento</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto; pulsanti più alti delle bottoniere (DM 236/1989)</t>
         </is>
       </c>
       <c r="I67" s="11" t="n"/>
@@ -3887,7 +3887,7 @@
       <c r="M67" s="11" t="n"/>
       <c r="N67" s="11" t="n"/>
     </row>
-    <row r="68" ht="56" customHeight="1">
+    <row r="68" ht="69" customHeight="1">
       <c r="A68" s="10" t="n">
         <v>66</v>
       </c>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>cabina larga 1100 mm e profonda 1400 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (fuori dal vano: da verificare in sito)</t>
+          <t>cabina larga 1100 mm e profonda 1400 mm, porta di 800 mm sul lato corto; piattaforma davanti alla porta 1,50 × 1,50 m (fuori dal vano: da verificare in sito); pulsanti più alti delle bottoniere tra 1100 e 1400 mm dal pavimento</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto; pulsanti più alti delle bottoniere (DM 236/1989)</t>
         </is>
       </c>
       <c r="I68" s="11" t="n"/>
@@ -3933,7 +3933,7 @@
       <c r="M68" s="11" t="n"/>
       <c r="N68" s="11" t="n"/>
     </row>
-    <row r="69" ht="56" customHeight="1">
+    <row r="69" ht="134" customHeight="1">
       <c r="A69" s="10" t="n">
         <v>67</v>
       </c>
@@ -3944,17 +3944,17 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Adeguamento di edifici esistenti: cabina e porta minime</t>
+          <t>Adeguamento di edifici esistenti: cabina e porta minime — Per un ascensore nuovo in un edificio esistente il caso è a) o b) secondo la destinazione; il c) è l'eccezione, scelta dal progettista.</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>cabina larga 800 mm e profonda 1200 mm, porta di 750 mm sul lato corto; piattaforma davanti alla porta 1,40 × 1,40 m (fuori dal vano: da verificare in sito)</t>
+          <t>cabina larga 800 mm e profonda 1200 mm, porta di 750 mm sul lato corto; piattaforma davanti alla porta 1,40 × 1,40 m (fuori dal vano: da verificare in sito); pulsanti più alti delle bottoniere tra 1100 e 1400 mm dal pavimento; solo se l'edificio esistente non consente una cabina più grande: una cabina sotto le misure del caso b) (larga 950 mm, profonda 1300 mm, porta di 800 mm) chiede la motivazione scritta nel progetto («Attenzione» se manca)</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>DM 236/1989, 8.1.12 c)</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto; motivazione del caso c) (DM 236/1989); pulsanti più alti delle bottoniere (DM 236/1989)</t>
         </is>
       </c>
       <c r="I69" s="11" t="n"/>
@@ -4163,7 +4163,7 @@
       <c r="M73" s="11" t="n"/>
       <c r="N73" s="11" t="n"/>
     </row>
-    <row r="74" ht="95" customHeight="1">
+    <row r="74" ht="108" customHeight="1">
       <c r="A74" s="10" t="n">
         <v>72</v>
       </c>
@@ -4179,12 +4179,12 @@
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>accanto a ogni porta di piano, sul pianerottolo: per default a destra guardando la porta, il centro della pulsantiera a 150 mm dal vano della porta e i pulsanti a 1100 mm dal pavimento; pulsantiera di 120 × 300 mm, sporgente 15 mm dal muro; lato, distanza e altezza modificabili su ogni progetto</t>
+          <t>accanto a ogni porta di piano, sul pianerottolo: per default a destra guardando la porta, il centro della pulsantiera a 150 mm dal vano della porta e il centro del pulsante più alto a 1100 mm dal pavimento; pulsantiera di 120 × 300 mm, sporgente 15 mm dal muro; lato, distanza e altezza modificabili su ogni progetto</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>altezze e distanze dagli angoli per l'accessibilità da verificare (DM 236/1989, UNI EN 81-70)</t>
+          <t>DM 236/1989, 8.1.12 (pulsanti più alti tra 1,10 e 1,40 m); UNI EN 81-70:2005, prospetto 2 (sul pianerottolo il pulsante più alto a non oltre 1,10 m, ogni pulsante ad almeno 0,90 m e ad almeno 0,50 m da un angolo fra pareti: da verificare in sito)</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Distanze libere dal soffitto con la cabina nella posizione più alta — I valori 500, 100 e 300 mm sono confermati. Da concordare con l'organismo: il software dà alla traversa dell'arcata i 100 mm di b) (il testo nomina traversa o architrave e parti di porte verticali; se non vale per l'arcata servono i 500 mm di a)); non verifica i 500 mm in obliquo oltre i 400 mm dal corrimano (c) 2)).</t>
+          <t>Distanze libere dal soffitto con la cabina nella posizione più alta — I valori 500, 100 e 300 mm sono confermati. Il software dà alla traversa dell'arcata i 100 mm di b) e avvisa sotto i 500 mm di a) (voce spazi.testata.traversa). Con il soffitto piano, 300 mm sopra il corrimano danno anche i 500 mm in obliquo oltre i 400 mm (c) 2)); sotto pulegge o travi appese no.</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
@@ -4761,7 +4761,7 @@
       <c r="M86" s="11" t="n"/>
       <c r="N86" s="11" t="n"/>
     </row>
-    <row r="87" ht="108" customHeight="1">
+    <row r="87" ht="82" customHeight="1">
       <c r="A87" s="10" t="n">
         <v>85</v>
       </c>
@@ -4772,32 +4772,32 @@
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Parte più alta della cabina sotto ciò che pende sopra — fino alla versione 1.17.0 del motore del progetto la puleggia di cabina era verificata a 100 mm; i 100 mm della traversa sono la stessa lettura di spazi.testata.parti</t>
+          <t>Traversa dell'arcata sotto il soffitto — La b) nomina la traversa delle porte e le parti delle porte a scorrimento verticale; quella dell'arcata non è nominata. Da concordare con l'organismo.</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>con la cabina nella posizione più alta: a 2:1 la puleggia di cabina (Dp + 30 mm sopra la traversa) è un'apparecchiatura sul tetto, distanza libera ≥ 500 mm dal soffitto o dalle pulegge appese; a 1:1 con la macchina in basso la traversa sotto le pulegge appese al solaio (asse a Dp/2 + 120 mm sotto il soffitto), distanza libera ≥ 100 mm, quella della traversa</t>
+          <t>≥ 100 mm come parte di b); sotto 500 mm «Attenzione»: se l'organismo la considera un'apparecchiatura vale a) (500 mm)</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.2 a) e b)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.2 a)–b); UNI EN 81-1:2008, 5.7.1.1 c)</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 38</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 38; UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 26</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>parte più alta della cabina sotto ciò che pende sopra</t>
+          <t>traversa dell'arcata sotto il soffitto</t>
         </is>
       </c>
       <c r="I87" s="11" t="n"/>
@@ -4807,7 +4807,7 @@
       <c r="M87" s="11" t="n"/>
       <c r="N87" s="11" t="n"/>
     </row>
-    <row r="88" ht="134" customHeight="1">
+    <row r="88" ht="108" customHeight="1">
       <c r="A88" s="10" t="n">
         <v>86</v>
       </c>
@@ -4818,32 +4818,32 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori e spazio di rifugio in fossa, in pianta</t>
+          <t>Parte più alta della cabina sotto ciò che pende sopra — fino alla versione 1.17.0 del motore del progetto la puleggia di cabina era verificata a 100 mm; i 100 mm della traversa sono la stessa lettura di spazi.testata.parti</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>lo spazio di rifugio in fossa resta libero dagli ammortizzatori di cabina: il software lo mette sotto il centro della cabina o, se un piatto vi entra, nel posto libero più vicino sotto l'interno della cabina; due o più ammortizzatori di cabina a 160 mm dai fianchi della piattaforma, più in fuori finché i piatti escono dalla pianta del rifugio, sempre sotto la piattaforma; la verifica vale anche per quelli messi dal software (margine ≥ 0)</t>
+          <t>con la cabina nella posizione più alta: a 2:1 la puleggia di cabina (Dp + 30 mm sopra la traversa) è un'apparecchiatura sul tetto, distanza libera ≥ 500 mm dal soffitto o dalle pulegge appese; a 1:1 con la macchina in basso la traversa sotto le pulegge appese al solaio (asse a Dp/2 + 120 mm sotto il soffitto), distanza libera ≥ 100 mm, quella della traversa</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.8.1</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.2 a) e b)</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>scelta del software sul modello della fossa (posizioni tipiche, da confermare con i dati del fornitore degli ammortizzatori)</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 38</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
+          <t>parte più alta della cabina sotto ciò che pende sopra</t>
         </is>
       </c>
       <c r="I88" s="11" t="n"/>
@@ -4853,7 +4853,7 @@
       <c r="M88" s="11" t="n"/>
       <c r="N88" s="11" t="n"/>
     </row>
-    <row r="89" ht="82" customHeight="1">
+    <row r="89" ht="134" customHeight="1">
       <c r="A89" s="10" t="n">
         <v>87</v>
       </c>
@@ -4864,32 +4864,32 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Distanze in fossa con la cabina sugli ammortizzatori compressi</t>
+          <t>Ammortizzatori e spazio di rifugio in fossa, in pianta</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>≥ 500 mm dal pavimento della fossa alle parti più basse della cabina; grembiule sotto la soglia di cabina: tratto verticale ≥ 750 mm, poi uno smusso a ≥ 60° sull'orizzontale con proiezione orizzontale ≥ 20 mm (circa 35 mm più in basso), con ≥ 100 mm liberi dal pavimento della fossa</t>
+          <t>lo spazio di rifugio in fossa resta libero dagli ammortizzatori di cabina: il software lo mette sotto il centro della cabina o, se un piatto vi entra, nel posto libero più vicino sotto l'interno della cabina; due o più ammortizzatori di cabina a 160 mm dai fianchi della piattaforma, più in fuori finché i piatti escono dalla pianta del rifugio, sempre sotto la piattaforma; la verifica vale anche per quelli messi dal software (margine ≥ 0)</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.8.2 a) e 5.4.5.1–5.4.5.2</t>
+          <t>UNI EN 81-20:2020, 5.2.5.8.1</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 40–41, 69</t>
+          <t>scelta del software sul modello della fossa (posizioni tipiche, da confermare con i dati del fornitore degli ammortizzatori)</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>spazio di rifugio in fossa; grembiule sugli ammortizzatori compressi</t>
+          <t>ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
         </is>
       </c>
       <c r="I89" s="11" t="n"/>
@@ -4899,7 +4899,7 @@
       <c r="M89" s="11" t="n"/>
       <c r="N89" s="11" t="n"/>
     </row>
-    <row r="90" ht="108" customHeight="1">
+    <row r="90" ht="82" customHeight="1">
       <c r="A90" s="10" t="n">
         <v>88</v>
       </c>
@@ -4910,22 +4910,22 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Balaustra sul tetto di cabina — fino alla versione 2.12.0 del motore del vano il software misurava i 500 mm dal bordo del tetto; la norma vuole la balaustra entro 150 mm dal bordo: se è più interna, la distanza cresce e può servire l'altezza maggiore</t>
+          <t>Distanze in fossa con la cabina sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>richiesta se dal bordo esterno del tetto alla parete ci sono più di 300 mm; alta 700 mm se dal bordo interno del corrimano alla parete ci sono fino a 500 mm, 1100 mm oltre; il corrimano (30 mm) con la faccia esterna a 100 mm dal bordo del tetto, come nel 3D</t>
+          <t>≥ 500 mm dal pavimento della fossa alle parti più basse della cabina; grembiule sotto la soglia di cabina: tratto verticale ≥ 750 mm, poi uno smusso a ≥ 60° sull'orizzontale con proiezione orizzontale ≥ 20 mm (circa 35 mm più in basso), con ≥ 100 mm liberi dal pavimento della fossa</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.7.2 b) e 5.4.7.4 b)–c)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.8.2 a) e 5.4.5.1–5.4.5.2</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 70–72</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 40–41, 69</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>balaustra sul tetto di cabina</t>
+          <t>spazio di rifugio in fossa; grembiule sugli ammortizzatori compressi</t>
         </is>
       </c>
       <c r="I90" s="11" t="n"/>
@@ -4945,7 +4945,7 @@
       <c r="M90" s="11" t="n"/>
       <c r="N90" s="11" t="n"/>
     </row>
-    <row r="91" ht="121" customHeight="1">
+    <row r="91" ht="108" customHeight="1">
       <c r="A91" s="10" t="n">
         <v>89</v>
       </c>
@@ -4956,22 +4956,22 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Superficie dove una persona può stare sul tetto di cabina — Nella 5.2.5.7.3 lo 0,12 m² è la soglia da cui un'area conta come posto in piedi, sopra la quale serve l'altezza del rifugio; che un'area simile debba esserci lo chiedeva la UNI EN 81-1:2008 (8.13.2). Il software verifica l'area disegnata.</t>
+          <t>Balaustra sul tetto di cabina — fino alla versione 2.12.0 del motore del vano il software misurava i 500 mm dal bordo del tetto; la norma vuole la balaustra entro 150 mm dal bordo: se è più interna, la distanza cresce e può servire l'altezza maggiore</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>area continua ≥ 0,12 m² con il lato minore oltre 250 mm (disegnata 400 × 300 mm, modificabile sulla pianta in testata); sopra di essa deve esserci l'altezza dello spazio di rifugio</t>
+          <t>richiesta se dal bordo esterno del tetto alla parete ci sono più di 300 mm; alta 700 mm se dal bordo interno del corrimano alla parete ci sono fino a 500 mm, 1100 mm oltre; il corrimano (30 mm) con la faccia esterna a 100 mm dal bordo del tetto, come nel 3D</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.3</t>
+          <t>UNI EN 81-20:2020, 5.4.7.2 b) e 5.4.7.4 b)–c)</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 39</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 70–72</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>superficie per stare sul tetto di cabina</t>
+          <t>balaustra sul tetto di cabina</t>
         </is>
       </c>
       <c r="I91" s="11" t="n"/>
@@ -4991,7 +4991,7 @@
       <c r="M91" s="11" t="n"/>
       <c r="N91" s="11" t="n"/>
     </row>
-    <row r="92" ht="212" customHeight="1">
+    <row r="92" ht="121" customHeight="1">
       <c r="A92" s="10" t="n">
         <v>90</v>
       </c>
@@ -5002,22 +5002,22 @@
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Altezza libera degli accessi e della cabina — negli impianti esistenti (DPR 1497/1963, artt. 24, 27 e 29, non riletto) le porte possono essere alte 1,90 m e la cabina 2,00 m; con la sola sostituzione della macchina le altezze restano (parti esistenti); la UNI 10411-1:2024 ammette porte di piano nuove non più basse delle esistenti (19.1), una cabina nuova sotto 2 m se non più bassa dell'esistente e mai sotto 1,90 m (22 m)) e accessi di cabina mai sotto 1,80 m (22 n)), con avvertimenti: il software non conosce le esistenti e segnala ogni porta sotto 2000 mm</t>
+          <t>Spazio di rifugio e posti in piedi sul tetto di cabina — L'operatore delle porte sul tetto è profondo meno di 250 mm (cataloghi): non è un posto in piedi e conta come apparecchiatura (500 mm, h_clear). La UNI EN 81-1:2008 (8.13.2) chiedeva un'area ≥ 0,12 m² con il lato minore ≥ 0,25 m.</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>luce netta in altezza delle porte di piano e di cabina ≥ 2000 mm; altezza libera interna della cabina ≥ 2000 mm</t>
+          <t>sul tetto c'è posto per la pianta del rifugio scelto (tipo 1: 400 × 500 mm; tipo 2: 500 × 700 mm), in un verso o nell'altro; ogni area continua ≥ 0,12 m² con il lato minore oltre 250 mm (anche su un apparecchio) è un posto in piedi e sopra di essa serve l'altezza del rifugio (h_refuge per il tetto); l'area disegnata (400 × 300 mm) indica dove stare</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.3.2.1 e 5.4.1</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1 (prospetto 3) e 5.2.5.7.3; UNI EN 81-1:2008, 8.13.2</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 49, 63; 2 m anche in DM 587/1987 (UNI EN 81-1), 7.3.1, 8.1.1 e 8.1.2</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 38–39; UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 52</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>altezza libera degli accessi; altezza libera interna della cabina</t>
+          <t>spazio di rifugio sul tetto di cabina; spazio di rifugio in testata</t>
         </is>
       </c>
       <c r="I92" s="11" t="n"/>
@@ -5037,7 +5037,7 @@
       <c r="M92" s="11" t="n"/>
       <c r="N92" s="11" t="n"/>
     </row>
-    <row r="93" ht="160" customHeight="1">
+    <row r="93" ht="212" customHeight="1">
       <c r="A93" s="10" t="n">
         <v>91</v>
       </c>
@@ -5048,22 +5048,22 @@
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Corsa guidata in testata (contrappeso e cabina)</t>
+          <t>Altezza libera degli accessi e della cabina — negli impianti esistenti (DPR 1497/1963, artt. 24, 27 e 29, non riletto) le porte possono essere alte 1,90 m e la cabina 2,00 m; con la sola sostituzione della macchina le altezze restano (parti esistenti); la UNI 10411-1:2024 ammette porte di piano nuove non più basse delle esistenti (19.1), una cabina nuova sotto 2 m se non più bassa dell'esistente e mai sotto 1,90 m (22 m)) e accessi di cabina mai sotto 1,80 m (22 n)), con avvertimenti: il software non conosce le esistenti e segnala ogni porta sotto 2000 mm</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>con la cabina sugli ammortizzatori completamente compressi le guide del contrappeso lo guidano ancora per almeno 0,1 + 0,035·v² m (v velocità nominale): dalla sommità del contrappeso, salito della corsa sotto la cabina (extracorsa e corsa degli ammortizzatori), alla sommità delle guide, che il software pone 50 mm sotto la soletta (voce foglio.stime); la cabina nella sua posizione più alta (salto compreso) ha ancora almeno 0,1 m di guida sopra la sommità dell'arcata, dove il software mette i pattini superiori (avviso: l'altezza reale dei pattini è del fornitore)</t>
+          <t>luce netta in altezza delle porte di piano e di cabina ≥ 2000 mm; altezza libera interna della cabina ≥ 2000 mm</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.6.2 e 5.2.5.6.1.1 (Prospetto 2: cabina sugli ammortizzatori compressi più 0,035·v²); stesso valore in UNI EN 81-1 (1999, 2008), 5.7.1.2</t>
+          <t>UNI EN 81-20:2020, 5.3.2.1 e 5.4.1</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 36; UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 27</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 49, 63; 2 m anche in DM 587/1987 (UNI EN 81-1), 7.3.1, 8.1.1 e 8.1.2</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>corsa guidata del contrappeso in testata; corsa guidata della cabina in testata</t>
+          <t>altezza libera degli accessi; altezza libera interna della cabina</t>
         </is>
       </c>
       <c r="I93" s="11" t="n"/>
@@ -5083,7 +5083,7 @@
       <c r="M93" s="11" t="n"/>
       <c r="N93" s="11" t="n"/>
     </row>
-    <row r="94" ht="95" customHeight="1">
+    <row r="94" ht="160" customHeight="1">
       <c r="A94" s="10" t="n">
         <v>92</v>
       </c>
@@ -5094,22 +5094,22 @@
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Schermo del contrappeso in fossa — non verificati: il bordo inferiore dello schermo a non più di 300 mm dal fondo della fossa (5.2.5.5.1 c)) e la protezione dello spazio oltre 300 mm tra guide del contrappeso e parete (e))</t>
+          <t>Corsa guidata in testata (contrappeso e cabina)</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>dal punto più basso del contrappeso sugli ammortizzatori compressi fino ad almeno 2000 mm sopra il pavimento della fossa (altezza dello schermo modificabile sul progetto, mai sotto questo valore)</t>
+          <t>con la cabina sugli ammortizzatori completamente compressi le guide del contrappeso lo guidano ancora per almeno 0,1 + 0,035·v² m (v velocità nominale): dalla sommità del contrappeso, salito della corsa sotto la cabina (extracorsa e corsa degli ammortizzatori), alla sommità delle guide, che il software pone 50 mm sotto la soletta (voce foglio.stime); la cabina nella sua posizione più alta (salto compreso) ha ancora almeno 0,1 m di guida sopra la sommità dell'arcata, dove il software mette i pattini superiori (avviso: l'altezza reale dei pattini è del fornitore)</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.5.1 b)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.6.2 e 5.2.5.6.1.1 (Prospetto 2: cabina sugli ammortizzatori compressi più 0,035·v²); stesso valore in UNI EN 81-1 (1999, 2008), 5.7.1.2</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 35</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 36; UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 27</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>protezione del contrappeso in fossa</t>
+          <t>corsa guidata del contrappeso in testata; corsa guidata della cabina in testata</t>
         </is>
       </c>
       <c r="I94" s="11" t="n"/>
@@ -5140,22 +5140,22 @@
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori ad accumulo di energia lineari (molle)</t>
+          <t>Schermo del contrappeso in fossa — non verificati: il bordo inferiore dello schermo a non più di 300 mm dal fondo della fossa (5.2.5.5.1 c)) e la protezione dello spazio oltre 300 mm tra guide del contrappeso e parete (e))</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>ammessi fino a 1 m/s; corsa ≥ 0,135·v² m e comunque ≥ 65 mm; extracorsa della cabina e del contrappeso ≥ 0 (nessun minimo nella norma)</t>
+          <t>dal punto più basso del contrappeso sugli ammortizzatori compressi fino ad almeno 2000 mm sopra il pavimento della fossa (altezza dello schermo modificabile sul progetto, mai sotto questo valore)</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.1.5 (fino a 1 m/s) e 5.8.2.1.1.1 (corsa); nessuna extracorsa minima in metri: l'interruttore di extracorsa interviene prima che la cabina o il contrappeso tocchino gli ammortizzatori (5.12.2.1)</t>
+          <t>UNI EN 81-20:2020, 5.2.5.5.1 b)</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 98, 131</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 35</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso; extracorsa di cabina e contrappeso</t>
+          <t>protezione del contrappeso in fossa</t>
         </is>
       </c>
       <c r="I95" s="11" t="n"/>
@@ -5175,7 +5175,7 @@
       <c r="M95" s="11" t="n"/>
       <c r="N95" s="11" t="n"/>
     </row>
-    <row r="96" ht="121" customHeight="1">
+    <row r="96" ht="95" customHeight="1">
       <c r="A96" s="10" t="n">
         <v>94</v>
       </c>
@@ -5186,22 +5186,22 @@
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori ad accumulo di energia non lineari (tamponi in poliuretano) — il tampone tipico alto 80 mm è un dato di catalogo, non della norma: va sostituito con quello montato</t>
+          <t>Ammortizzatori ad accumulo di energia lineari (molle)</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>ammessi fino a 1 m/s come le molle; nessuna corsa minima da formula: il campo di masse del certificato di esame di tipo per la velocità deve comprendere, per ogni tampone, la cabina vuota e a pieno carico (o il contrappeso); «completamente compresso» vuol dire compresso del 90 % dell'altezza, quindi la corsa è 0,9·H negli spazi in fossa e in testata; tampone tipico alti 80 mm (P+S Diepocell D, Ø da 80 a 220 mm; ACLA AUTAN XL)</t>
+          <t>ammessi fino a 1 m/s; corsa ≥ 0,135·v² m e comunque ≥ 65 mm; extracorsa della cabina e del contrappeso ≥ 0 (nessun minimo nella norma)</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.1.5, 5.8.1.7, 5.8.2.1.2.1 e 5.8.2.1.2.2 (compresso al 90 %); UNI EN 81-50:2020, 5.5.4 (esame di tipo)</t>
+          <t>UNI EN 81-20:2020, 5.8.1.5 (fino a 1 m/s) e 5.8.2.1.1.1 (corsa); nessuna extracorsa minima in metri: l'interruttore di extracorsa interviene prima che la cabina o il contrappeso tocchino gli ammortizzatori (5.12.2.1)</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 98–99; UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 24; il tampone tipico dai cataloghi P+S Diepocell (wwlift.de) e ACLA AUTAN XL (acla.de), estratti di ricerca del 1° ottobre 2026</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 98, 131</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso</t>
+          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso; extracorsa di cabina e contrappeso</t>
         </is>
       </c>
       <c r="I96" s="11" t="n"/>
@@ -5221,7 +5221,7 @@
       <c r="M96" s="11" t="n"/>
       <c r="N96" s="11" t="n"/>
     </row>
-    <row r="97" ht="95" customHeight="1">
+    <row r="97" ht="121" customHeight="1">
       <c r="A97" s="10" t="n">
         <v>95</v>
       </c>
@@ -5232,22 +5232,22 @@
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Ammortizzatori a dissipazione di energia (idraulici) — gli ammortizzatori Oleo sono dati di catalogo, non della norma: vanno sostituiti con quelli montati</t>
+          <t>Ammortizzatori ad accumulo di energia non lineari (tamponi in poliuretano) — il tampone tipico alto 80 mm è un dato di catalogo, non della norma: va sostituito con quello montato</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>a ogni velocità; corsa ≥ 0,0674·v² m (arresto per gravità al 115 % della velocità nominale); la corsa ridotta con il controllo del rallentamento non è considerata; ammortizzatori tipici: Oleo LSB10 fino a 1 m/s, alto 222,2 mm con corsa 73,4 mm; LSB16 fino a 1,6 m/s, alto 485,5 mm con corsa 173,5 mm</t>
+          <t>ammessi fino a 1 m/s come le molle; nessuna corsa minima da formula: il campo di masse del certificato di esame di tipo per la velocità deve comprendere, per ogni tampone, la cabina vuota e a pieno carico (o il contrappeso); «completamente compresso» vuol dire compresso del 90 % dell'altezza, quindi la corsa è 0,9·H negli spazi in fossa e in testata; tampone tipico alti 80 mm (P+S Diepocell D, Ø da 80 a 220 mm; ACLA AUTAN XL)</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.1.6 e 5.8.2.2.1 (corsa); la corsa ridotta di 5.8.2.2.2 non è usata</t>
+          <t>UNI EN 81-20:2020, 5.8.1.5, 5.8.1.7, 5.8.2.1.2.1 e 5.8.2.1.2.2 (compresso al 90 %); UNI EN 81-50:2020, 5.5.4 (esame di tipo)</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 99; gli ammortizzatori tipici dal catalogo Oleo LSB e SEB (oleo.co.uk), estratti di ricerca del 1° ottobre 2026</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 98–99; UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, p. 24; il tampone tipico dai cataloghi P+S Diepocell (wwlift.de) e ACLA AUTAN XL (acla.de), estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
@@ -5267,33 +5267,33 @@
       <c r="M97" s="11" t="n"/>
       <c r="N97" s="11" t="n"/>
     </row>
-    <row r="98" ht="134" customHeight="1">
+    <row r="98" ht="95" customHeight="1">
       <c r="A98" s="10" t="n">
         <v>96</v>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario</t>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Locale del macchinario — davanti al quadro il software verifica la profondità libera e che la parete sia lunga almeno quanto il maggiore tra 500 mm e il quadro; non verificati: la macchina o altro dentro quella superficie, i percorsi larghi almeno 0,50 m (5.2.6.3.2.2) e lo spazio di 0,30 m sopra le parti rotanti (5.2.6.3.2.3)</t>
+          <t>Ammortizzatori a dissipazione di energia (idraulici) — gli ammortizzatori Oleo sono dati di catalogo, non della norma: vanno sostituiti con quelli montati</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>altezza libera delle zone di lavoro ≥ 2100 mm (1800 mm sui percorsi); davanti al quadro una superficie libera profonda ≥ 700 mm e larga ≥ 500 mm o quanto il quadro; per la manutenzione delle parti in movimento e la manovra di emergenza una superficie libera di almeno 500 × 600 mm (il software la cerca accanto all'argano, sul lato più libero, fino a muri e quadro); porta di accesso ≥ 600 × 2000 mm</t>
+          <t>a ogni velocità; corsa ≥ 0,0674·v² m (arresto per gravità al 115 % della velocità nominale); la corsa ridotta con il controllo del rallentamento non è considerata; ammortizzatori tipici: Oleo LSB10 fino a 1 m/s, alto 222,2 mm con corsa 73,4 mm; LSB16 fino a 1,6 m/s, alto 485,5 mm con corsa 173,5 mm</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.6.3.2.1 (2,10 m e superfici libere), 5.2.6.3.2.2 (1,80 m sui percorsi) e 5.2.3.2 a) (porta)</t>
+          <t>UNI EN 81-20:2020, 5.8.1.6 e 5.8.2.2.1 (corsa); la corsa ridotta di 5.8.2.2.2 non è usata</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 29, 43; le superfici libere anche in UNI EN 81-1:1999, 6.3.2.1 (edizione 2008: 6.3.3.1)</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 99; gli ammortizzatori tipici dal catalogo Oleo LSB e SEB (oleo.co.uk), estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>altezza del locale macchina; superficie libera davanti al quadro; superficie libera accanto all'argano; porta del locale macchina</t>
+          <t>tipo di ammortizzatori per la velocità; corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso</t>
         </is>
       </c>
       <c r="I98" s="11" t="n"/>
@@ -5313,7 +5313,7 @@
       <c r="M98" s="11" t="n"/>
       <c r="N98" s="11" t="n"/>
     </row>
-    <row r="99" ht="69" customHeight="1">
+    <row r="99" ht="134" customHeight="1">
       <c r="A99" s="10" t="n">
         <v>97</v>
       </c>
@@ -5324,22 +5324,22 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Illuminazione del vano e del locale del macchinario</t>
+          <t>Locale del macchinario — davanti al quadro il software verifica la profondità libera e che la parete sia lunga almeno quanto il maggiore tra 500 mm e il quadro; non verificati: la macchina o altro dentro quella superficie, i percorsi larghi almeno 0,50 m (5.2.6.3.2.2) e lo spazio di 0,30 m sopra le parti rotanti (5.2.6.3.2.3)</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>vano: luce fissa, almeno 50 lux a un metro dal tetto di cabina e dal fondo della fossa, 20 lux nel resto; locale del macchinario: almeno 200 lux al pavimento dove si lavora e 50 lux sui percorsi; 50 lux anche sull'accesso al macchinario</t>
+          <t>altezza libera delle zone di lavoro ≥ 2100 mm (1800 mm sui percorsi); davanti al quadro una superficie libera profonda ≥ 700 mm e larga ≥ 500 mm o quanto il quadro; per la manutenzione delle parti in movimento e la manovra di emergenza una superficie libera di almeno 500 × 600 mm (il software la cerca accanto all'argano, sul lato più libero, fino a muri e quadro); porta di accesso ≥ 600 × 2000 mm</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.4.1 a)–c), 5.2.1.4.2 e 5.2.2.2</t>
+          <t>UNI EN 81-20:2020, 5.2.6.3.2.1 (2,10 m e superfici libere), 5.2.6.3.2.2 (1,80 m sui percorsi) e 5.2.3.2 a) (porta)</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 25</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 29, 43; le superfici libere anche in UNI EN 81-1:1999, 6.3.2.1 (edizione 2008: 6.3.3.1)</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>altezza del locale macchina; superficie libera davanti al quadro; superficie libera accanto all'argano; porta del locale macchina</t>
         </is>
       </c>
       <c r="I99" s="11" t="n"/>
@@ -5359,7 +5359,7 @@
       <c r="M99" s="11" t="n"/>
       <c r="N99" s="11" t="n"/>
     </row>
-    <row r="100" ht="43" customHeight="1">
+    <row r="100" ht="69" customHeight="1">
       <c r="A100" s="10" t="n">
         <v>98</v>
       </c>
@@ -5370,22 +5370,22 @@
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Temperatura dei locali del macchinario e degli armadi</t>
+          <t>Illuminazione del vano e del locale del macchinario</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>temperatura ambiente mantenuta tra +5 °C e +40 °C: ipotesi della norma, da garantire nell'edificio</t>
+          <t>vano: luce fissa, almeno 50 lux a un metro dal tetto di cabina e dal fondo della fossa, 20 lux nel resto; locale del macchinario: almeno 200 lux al pavimento dove si lavora e 50 lux sui percorsi; 50 lux anche sull'accesso al macchinario</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 0.4.16 (ipotesi della norma, vale anche per il vano)</t>
+          <t>UNI EN 81-20:2020, 5.2.1.4.1 a)–c), 5.2.1.4.2 e 5.2.2.2</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 14</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 25</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
@@ -5405,7 +5405,7 @@
       <c r="M100" s="11" t="n"/>
       <c r="N100" s="11" t="n"/>
     </row>
-    <row r="101" ht="225" customHeight="1">
+    <row r="101" ht="43" customHeight="1">
       <c r="A101" s="10" t="n">
         <v>99</v>
       </c>
@@ -5416,27 +5416,27 @@
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Basamento dell'argano</t>
+          <t>Temperatura dei locali del macchinario e degli armadi</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>su spessori di livellamento sotto gli appoggi (l'asse della puleggia dove lo mette il software), su telaio di due profilati sul pavimento (tipico UPN 200, alto quanto il profilato come i telai bassi universali), su due putrelle da muro a muro che possono stare sollevate dal pavimento (tipiche IPE 200, appoggio nei muri 150 mm), su piastre d'acciaio sotto gli appoggi (tipiche 20 mm) o su plinto in calcestruzzo (tipico 250 mm), o — con un rinvio — sul telaio con rinvio (locale.rinvio); tamponi antivibranti di 30 mm sotto gli appoggi, salvo sugli spessori e sul telaio con rinvio (antivibranti sotto le gambe); telaio e plinto 100 mm oltre il telaio dell'argano a ogni estremità; l'altezza del basamento porta l'asse della puleggia, che il calcolo (tratto di fune oltre la corsa) e il 3D seguono</t>
+          <t>temperatura ambiente mantenuta tra +5 °C e +40 °C: ipotesi della norma, da garantire nell'edificio</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio); scelta del costruttore</t>
+          <t>UNI EN 81-20:2020, 0.4.16 (ipotesi della norma, vale anche per il vano)</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>telaio basso universale per argano alto 200 mm (lift-store.it); tamponi antivibranti 25–30 mm (catalogo Donati); piastre di 20 mm e plinto di 250–300 mm nella pratica di installazione (fonti estere, da confermare); estratti di ricerca del 1° ottobre 2026</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 14</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H101" s="10" t="inlineStr">
@@ -5451,7 +5451,7 @@
       <c r="M101" s="11" t="n"/>
       <c r="N101" s="11" t="n"/>
     </row>
-    <row r="102" ht="147" customHeight="1">
+    <row r="102" ht="225" customHeight="1">
       <c r="A102" s="10" t="n">
         <v>100</v>
       </c>
@@ -5462,22 +5462,22 @@
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Telaio sotto l'argano di un costruttore</t>
+          <t>Basamento dell'argano</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>l'argano di catalogo poggia con i suoi piedi su un telaio di due travi sotto le file di fori, con antivibranti alle estremità e 40 mm oltre l'argano a ogni estremità; il telaio è alto quanto serve per tenere l'asse della puleggia dove lo tiene l'argano generico del software, almeno 80 mm e con il bordo della puleggia 30 mm sopra il suo piano d'appoggio (gli argani compatti hanno la puleggia a sbalzo, sotto il piano dei piedi); se l'argano non lo permette l'asse sale e il calcolo segue</t>
+          <t>su spessori di livellamento sotto gli appoggi (l'asse della puleggia dove lo mette il software), su telaio di due profilati sul pavimento (tipico UPN 200, alto quanto il profilato come i telai bassi universali), su due putrelle da muro a muro che possono stare sollevate dal pavimento (tipiche IPE 200, appoggio nei muri 150 mm), su piastre d'acciaio sotto gli appoggi (tipiche 20 mm) o su plinto in calcestruzzo (tipico 250 mm), o — con un rinvio — sul telaio con rinvio (locale.rinvio); tamponi antivibranti di 30 mm sotto gli appoggi, salvo sugli spessori e sul telaio con rinvio (antivibranti sotto le gambe); telaio e plinto 100 mm oltre il telaio dell'argano a ogni estremità; l'altezza del basamento porta l'asse della puleggia, che il calcolo (tratto di fune oltre la corsa) e il 3D seguono</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio); scelta del costruttore</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>quote dei piedi, dei fori e dell'asse della puleggia dalle schede tecniche del costruttore; altezza del telaio scelta dal software, da adattare al telaio fornito</t>
+          <t>telaio basso universale per argano alto 200 mm (lift-store.it); tamponi antivibranti 25–30 mm (catalogo Donati); piastre di 20 mm e plinto di 250–300 mm nella pratica di installazione (fonti estere, da confermare); estratti di ricerca del 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
@@ -5497,7 +5497,7 @@
       <c r="M102" s="11" t="n"/>
       <c r="N102" s="11" t="n"/>
     </row>
-    <row r="103" ht="303" customHeight="1">
+    <row r="103" ht="147" customHeight="1">
       <c r="A103" s="10" t="n">
         <v>101</v>
       </c>
@@ -5508,22 +5508,22 @@
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Puleggia di rinvio nel locale del macchinario</t>
+          <t>Telaio sotto l'argano di un costruttore</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>con l'argano in alto il rinvio sta sempre nel locale del macchinario, mai nel vano: nel telaio dell'argano (il basamento che il software prende quando c'è un rinvio), con l'asse del rinvio a 320 mm dal pavimento (il bordo almeno 60 mm sopra il pavimento: Dp/2 + 60 oltre Ø 520), il piano del telaio a 736 mm (almeno 176 mm sopra il rinvio), gambe di tubo quadro da 80 mm su antivibranti da 28 mm, travi UPN 160, 100 mm oltre l'argano e il rinvio a ogni estremità, largo almeno 655 mm; con un argano SICOR che ha il suo telaio a catalogo (SV110 e SH110B XTE0517/XTE0516, SH130 e SH130G XTE3022/XTE3023, SH140 XTE6026/XTE6027, SH160 XTE5708, SH190 XTE3988) le quote del costruttore: asse del rinvio, asse della puleggia (A), piano del telaio (A − B), calata del contrappeso entro L max dall'asse della puleggia (verifica di avvertimento: oltre, telaio su misura); h del calcolo = asse della puleggia − asse del rinvio, dx dalla pianta; con un altro basamento scelto il rinvio sta su un supporto proprio sul pavimento, alla stessa altezza; una h inserita a mano che porta il rinvio sotto il pavimento è segnalata</t>
+          <t>l'argano di catalogo poggia con i suoi piedi su un telaio di due travi sotto le file di fori, con antivibranti alle estremità e 40 mm oltre l'argano a ogni estremità; il telaio è alto quanto serve per tenere l'asse della puleggia dove lo tiene l'argano generico del software, almeno 80 mm e con il bordo della puleggia 30 mm sopra il suo piano d'appoggio (gli argani compatti hanno la puleggia a sbalzo, sotto il piano dei piedi); se l'argano non lo permette l'asse sale e il calcolo segue</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>regola del committente (Panev): il rinvio sta nel telaio del locale macchine, mai nel vano; UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>brochure Geared SICOR, aprile 2026, pp. 16, 23, 41, 47, 58, 68 e 80 (telai «top machine with diverting pulley for CSW wrapping»), letta il 2 ottobre 2026; i telai «corti» MR21, MR26 e MR35 portano il rinvio sotto il pavimento (Hmin = Dt/2 + 75) e non sono usati; le quote del telaio del software sono quelle dei telai SICOR, da adattare al telaio fornito</t>
+          <t>quote dei piedi, dei fori e dell'asse della puleggia dalle schede tecniche del costruttore; altezza del telaio scelta dal software, da adattare al telaio fornito</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>calata del contrappeso nel telaio con rinvio del costruttore</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I103" s="11" t="n"/>
@@ -5543,7 +5543,7 @@
       <c r="M103" s="11" t="n"/>
       <c r="N103" s="11" t="n"/>
     </row>
-    <row r="104" ht="134" customHeight="1">
+    <row r="104" ht="303" customHeight="1">
       <c r="A104" s="10" t="n">
         <v>102</v>
       </c>
@@ -5554,32 +5554,32 @@
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>L'argano dentro il locale del macchinario</t>
+          <t>Puleggia di rinvio nel locale del macchinario</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>l'argano sul suo basamento — con il telaio del rinvio o con il supporto del rinvio — sta dentro il locale in pianta e sotto il soffitto: la distanza minima dai muri e dal soffitto non è negativa; ingombri dalle quote del costruttore per gli argani disegnati com'è, dall'argano generico del software (scalato alla puleggia) per gli altri; la puleggia di rinvio sul suo supporto sotto l'argano libera il basamento dell'argano sopra di essa (solo le putrelle sollevate la scavalcano)</t>
+          <t>con l'argano in alto il rinvio sta sempre nel locale del macchinario, mai nel vano: nel telaio dell'argano (il basamento che il software prende quando c'è un rinvio), con l'asse del rinvio a 320 mm dal pavimento (il bordo almeno 60 mm sopra il pavimento: Dp/2 + 60 oltre Ø 520), il piano del telaio a 736 mm (almeno 176 mm sopra il rinvio), gambe di tubo quadro da 80 mm su antivibranti da 28 mm, travi UPN 160, 100 mm oltre l'argano e il rinvio a ogni estremità, largo almeno 655 mm; con un argano SICOR che ha il suo telaio a catalogo (SV110 e SH110B XTE0517/XTE0516, SH130 e SH130G XTE3022/XTE3023, SH140 XTE6026/XTE6027, SH160 XTE5708, SH190 XTE3988) le quote del costruttore: asse del rinvio, asse della puleggia (A), piano del telaio (A − B), calata del contrappeso entro L max dall'asse della puleggia (verifica di avvertimento: oltre, telaio su misura); h del calcolo = asse della puleggia − asse del rinvio, dx dalla pianta; con un altro basamento scelto il rinvio sta su un supporto proprio sul pavimento, alla stessa altezza; una h inserita a mano che porta il rinvio sotto il pavimento è segnalata</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>regola del committente (Panev): il rinvio sta nel telaio del locale macchine, mai nel vano; UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio)</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>geometria del progetto: la pianta e l'altezza del locale inserite, gli ingombri dell'argano e del basamento</t>
+          <t>brochure Geared SICOR, aprile 2026, pp. 16, 23, 41, 47, 58, 68 e 80 (telai «top machine with diverting pulley for CSW wrapping»), letta il 2 ottobre 2026; i telai «corti» MR21, MR26 e MR35 portano il rinvio sotto il pavimento (Hmin = Dt/2 + 75) e non sono usati; le quote del telaio del software sono quelle dei telai SICOR, da adattare al telaio fornito</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>argano dentro il locale (muri e soffitto); puleggia di rinvio sul suo supporto sotto l'argano</t>
+          <t>calata del contrappeso nel telaio con rinvio del costruttore</t>
         </is>
       </c>
       <c r="I104" s="11" t="n"/>
@@ -5600,32 +5600,32 @@
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
+          <t>L'argano dentro il locale del macchinario</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
+          <t>l'argano sul suo basamento — con il telaio del rinvio o con il supporto del rinvio — sta dentro il locale in pianta e sotto il soffitto: la distanza minima dai muri e dal soffitto non è negativa; ingombri dalle quote del costruttore per gli argani disegnati com'è, dall'argano generico del software (scalato alla puleggia) per gli altri; la puleggia di rinvio sul suo supporto sotto l'argano libera il basamento dell'argano sopra di essa (solo le putrelle sollevate la scavalcano)</t>
         </is>
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E), §3.1.4 (carichi del macchinario); DPR 1497/1963, art. 5.1–5.2 (carichi fissi più 1,5 volte il carico statico delle funi, sicurezza ≥ 6, freccia ≤ 1/1500 della luce libera: regola storica degli impianti esistenti, letta su Normattiva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
+          <t>geometria del progetto: la pianta e l'altezza del locale inserite, gli ingombri dell'argano e del basamento</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>argano dentro il locale (muri e soffitto); puleggia di rinvio sul suo supporto sotto l'argano</t>
         </is>
       </c>
       <c r="I105" s="11" t="n"/>
@@ -5635,7 +5635,7 @@
       <c r="M105" s="11" t="n"/>
       <c r="N105" s="11" t="n"/>
     </row>
-    <row r="106" ht="147" customHeight="1">
+    <row r="106" ht="134" customHeight="1">
       <c r="A106" s="10" t="n">
         <v>104</v>
       </c>
@@ -5646,32 +5646,32 @@
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Sostituzione dell'argano: calate esistenti e calate della nuova macchina</t>
+          <t>Verifica delle putrelle sotto l'argano — verifica semplice a carico concentrato in mezzeria su trave appoggiata; gli appoggi nei muri e la muratura vanno verificati dal progettista</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>nella sola sostituzione dell'argano la cabina e il contrappeso restano dove sono: le funi della nuova macchina devono scendere sulle calate esistenti, rilevate nel locale dall'angolo interno del vano. La distanza tra le calate data dal calcolo (rinvio: D/2 + dx ± Dp/2, più Dp in taglia 2:1; tiro diretto: il diametro della puleggia esistente, se inserita, altrimenti della nuova, più Dp in taglia 2:1) e quella misurata differiscono al più di 10 mm; oltre, il calcolo va ripetuto con la geometria misurata (dx, puleggia esistente)</t>
+          <t>ognuna delle due putrelle porta metà del carico dell'argano (il suo peso più il carico statico sull'asse per il coefficiente dinamico) come forza concentrata in mezzeria, più il proprio peso, sulla luce tra i centri degli appoggi nei muri (luce libera più 150 mm): σ = M/Wel,y ≤ fyk/γM0 con acciaio S275 (fyk 275 MPa) e γM0 = 1,05; freccia elastica f = F·L³/(48·E·I) + 5·q·L⁴/(384·E·I) ≤ 1/1500 della luce libera con E = 210000 MPa; proprietà dei profili EN 10365</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NTC 2018, §4.2.4.1.1 (γM0), Tab. 11.3.IX (S275), §11.3.4.1 (E), §3.1.4 (carichi del macchinario); DPR 1497/1963, art. 5.1–5.2 (carichi fissi più 1,5 volte il carico statico delle funi, sicurezza ≥ 6, freccia ≤ 1/1500 della luce libera: regola storica degli impianti esistenti, letta su Normattiva)</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>tolleranza scelta dal software per il rilievo in sito (le funi a qualche metro dal basamento): da confermare con l'installatore</t>
+          <t>NTC 2018 (DM 17/01/2018); catalogo dei profilati ArcelorMittal (EN 10365) confrontato con due tabelle indipendenti; DPR 1497/1963 letto per intero (research/argano-geared, cap. 15, §1.1)</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>sostituzione: calate della nuova macchina sulle calate esistenti</t>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
         </is>
       </c>
       <c r="I106" s="11" t="n"/>
@@ -5681,43 +5681,43 @@
       <c r="M106" s="11" t="n"/>
       <c r="N106" s="11" t="n"/>
     </row>
-    <row r="107" ht="134" customHeight="1">
+    <row r="107" ht="147" customHeight="1">
       <c r="A107" s="10" t="n">
         <v>105</v>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>Carichi sull'edificio e spinte sulle guide</t>
+          <t>Locale del macchinario</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Carichi sul pavimento della fossa — non calcolato: con spazi accessibili sotto il vano (5.2.5.4) il contrappeso ha il paracadute, sotto le sue guide va anche k1·g·M_cw/n e il fondo della fossa regge almeno 5000 N/m². P è la cabina vuota: la quota del cavo flessibile e della compensazione, che la 5.2.1.8.5 conta in P, va aggiunta dall'ingegnere</t>
+          <t>Sostituzione dell'argano: calate esistenti e calate della nuova macchina</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
+          <t>nella sola sostituzione dell'argano la cabina e il contrappeso restano dove sono: le funi della nuova macchina devono scendere sulle calate esistenti, rilevate nel locale dall'angolo interno del vano. La distanza tra le calate data dal calcolo (rinvio: D/2 + dx ± Dp/2, più Dp in taglia 2:1; tiro diretto: il diametro della puleggia esistente, se inserita, altrimenti della nuova, più Dp in taglia 2:1) e quella misurata differiscono al più di 10 mm; oltre, il calcolo va ripetuto con la geometria misurata (dx, puleggia esistente)</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.8.4–5.2.1.8.6, 5.7.2.3.5 e Prospetto 14 (k1)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 27, 94–96</t>
+          <t>tolleranza scelta dal software per il rilievo in sito (le funi a qualche metro dal basamento): da confermare con l'installatore</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>sostituzione: calate della nuova macchina sulle calate esistenti</t>
         </is>
       </c>
       <c r="I107" s="11" t="n"/>
@@ -5727,7 +5727,7 @@
       <c r="M107" s="11" t="n"/>
       <c r="N107" s="11" t="n"/>
     </row>
-    <row r="108" ht="108" customHeight="1">
+    <row r="108" ht="147" customHeight="1">
       <c r="A108" s="10" t="n">
         <v>106</v>
       </c>
@@ -5738,22 +5738,22 @@
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Spinte sulle guide di cabina — h, la distanza tra i pattini, è una stima del software (l'ingombro verticale dell'arcata)</t>
+          <t>Carichi sul pavimento della fossa — non calcolato: con spazi accessibili sotto il vano (5.2.5.4) il contrappeso ha il paracadute, sotto le sue guide va anche k1·g·M_cw/n e il fondo della fossa regge almeno 5000 N/m². In P il software conta anche il cavo flessibile (metà corsa + 3 m, come sull'asse della macchina), come vuole la 5.2.1.8.5; la compensazione, se c'è, la aggiunge l'ingegnere</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
+          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, appendice C (informativa), C.2.1.1 e C.2.2.1; UNI EN 81-20:2020, 5.7.2.3.4 (portata su 3/4 della superficie: 1/8) e Prospetto 14 (k1; k2 = 1,2)</t>
+          <t>UNI EN 81-20:2020, 5.2.1.8.4–5.2.1.8.6, 5.7.2.3.5 e Prospetto 14 (k1)</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 77–79; UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 94–96</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 27, 94–96</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
@@ -5773,7 +5773,7 @@
       <c r="M108" s="11" t="n"/>
       <c r="N108" s="11" t="n"/>
     </row>
-    <row r="109" ht="82" customHeight="1">
+    <row r="109" ht="108" customHeight="1">
       <c r="A109" s="10" t="n">
         <v>107</v>
       </c>
@@ -5784,27 +5784,27 @@
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Carico della macchina sulla soletta</t>
+          <t>Spinte sulle guide di cabina — h, la distanza tra i pattini, è una stima del software (l'ingombro verticale dell'arcata)</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
+          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
         </is>
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, appendice C (informativa), C.2.1.1 e C.2.2.1; UNI EN 81-20:2020, 5.7.2.3.4 (portata su 3/4 della superficie: 1/8) e Prospetto 14 (k1; k2 = 1,2)</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 77–79; UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 94–96</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>prassi di cantiere</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H109" s="10" t="inlineStr">
@@ -5819,7 +5819,7 @@
       <c r="M109" s="11" t="n"/>
       <c r="N109" s="11" t="n"/>
     </row>
-    <row r="110" ht="43" customHeight="1">
+    <row r="110" ht="82" customHeight="1">
       <c r="A110" s="10" t="n">
         <v>108</v>
       </c>
@@ -5830,12 +5830,12 @@
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Massa dei cavi flessibili</t>
+          <t>Carico della macchina sulla soletta</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
+          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
+          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>prassi di cantiere</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
@@ -5865,7 +5865,7 @@
       <c r="M110" s="11" t="n"/>
       <c r="N110" s="11" t="n"/>
     </row>
-    <row r="111" ht="121" customHeight="1">
+    <row r="111" ht="43" customHeight="1">
       <c r="A111" s="10" t="n">
         <v>109</v>
       </c>
@@ -5876,27 +5876,27 @@
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
+          <t>Massa dei cavi flessibili</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
+          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>regola di montaggio indicata dal committente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>scelta del committente</t>
+          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H111" s="10" t="inlineStr">
@@ -5911,7 +5911,7 @@
       <c r="M111" s="11" t="n"/>
       <c r="N111" s="11" t="n"/>
     </row>
-    <row r="112" ht="82" customHeight="1">
+    <row r="112" ht="121" customHeight="1">
       <c r="A112" s="10" t="n">
         <v>110</v>
       </c>
@@ -5922,27 +5922,27 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Lunghezze stimate nel foglio dei dati</t>
+          <t>Numero e posizione delle staffe delle guide — il passo delle staffe va confermato con la verifica delle guide (UNI EN 81-50:2020, 5.10), che usa la distanza tra le staffe</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
+          <t>una staffa ogni 2000 mm di guida, più una all'inizio e una alla fine: per guida ⌊L / 2000⌋ + 2 (L la lunghezza della guida); la prima a 600 mm dal piede della guida, l'ultima a 200 mm dalla sua sommità, le altre a passo uguale tra le due; una staffa che cadrebbe sulla piastra di una giunzione (guide da 5 m dal fondo della fossa) si sposta appena oltre la piastra. Il passo inserito nei dati dell'impianto sostituisce i 2000 mm</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>regola di montaggio indicata dal committente</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>stima del software, da sostituire con le misure di cantiere</t>
+          <t>scelta del committente</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
@@ -5957,7 +5957,7 @@
       <c r="M112" s="11" t="n"/>
       <c r="N112" s="11" t="n"/>
     </row>
-    <row r="113" ht="342" customHeight="1">
+    <row r="113" ht="82" customHeight="1">
       <c r="A113" s="10" t="n">
         <v>111</v>
       </c>
@@ -5968,32 +5968,32 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Verifica delle guide di cabina — Confermati sul testo i coefficienti, le formule e i limiti. Da verificare il carico al piano: la UNI EN 81-20:2020 (5.7.2.3.6) lo lega al tipo di ascensore, 0,4·g·Q per persone, 0,6·g·Q per merci, 0,85·g·Q con dispositivi di movimentazione pesanti; il software usa la regola della UNI EN 81-1:2008 (0,6·g·Q da 2500 kg, appendice G.2.5) perché il tipo di ascensore non è tra i dati. La formula di ω per Rm 370 è data da λ 20 a 250: sotto 20 il software usa ω di λ 20 (dal lato della sicurezza). Non contate: la spinta di scorrimento delle staffe (assestamento dell'edificio), le apparecchiature appese alle guide, le frecce di staffe ed edificio (la norma vuole la somma entro il limite) e le guide del contrappeso. La flessione della suola è quella dei pattini a rotelle (5.10.5 ha una formula a parte per quelli a scorrimento; il tipo di pattino non è un dato del software).</t>
+          <t>Lunghezze stimate nel foglio dei dati</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>tra due staffe (l = distanza massima tra le staffe della guida) con le spinte della voce guide.spinte, portata spostata di 1/8 della cabina in un senso e poi nell'altro: flessione M = 3·F·l/16, σm = σx + σy; intervento del paracadute: forza verticale Fv = k1·g·(P+Q)/n più il peso della guida, carico di punta con il metodo omega (λ = l/i con il raggio d'inerzia minore √(I/A), λ ≤ 250; acciaio Rm 370: ω = 0,0001292·λ^1,89 + 1 fino a λ 60, 0,00004627·λ^2,14 + 1 fino a 85, 0,00001711·λ^2,35 + 1,04 fino a 115, 0,00016887·λ^2 fino a 250), σ = σm + Fv/A e σc = σk + 0,9·σm; marcia: k2 = 1,2 e il peso della guida; carico al piano: cabina vuota e Fs = 0,4·g·Q (0,6·g·Q da 2500 kg) al centro della soglia di cabina, a ogni accesso; flessione della suola σF = 1,85·Fx/c² (pattini a rotelle); frecce δx = 0,7·Fx·l³/(48·E·Iy) e δy = 0,7·Fy·l³/(48·E·Ix) ≤ 5 mm. Tensione ammissibile Rm/St con St = 2,25 in marcia e al carico, 1,8 all'intervento del paracadute (allungamento A5 &gt; 12 %): con Rm 370 N/mm², 164,4 e 205,6 N/mm²</t>
+          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.10.2–5.10.6; UNI EN 81-20:2020, 5.7.2.3.5, 5.7.2.3.6, 5.7.4.5 (Prospetto 15), 5.7.4.6 e Prospetto 14</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 35–39; UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 94–97; Rm 370 è scelta del software (il valore più basso)</t>
+          <t>stima del software, da sostituire con le misure di cantiere</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>tensioni nelle guide di cabina; flessione della suola delle guide di cabina; frecce delle guide di cabina</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I113" s="11" t="n"/>
@@ -6003,7 +6003,7 @@
       <c r="M113" s="11" t="n"/>
       <c r="N113" s="11" t="n"/>
     </row>
-    <row r="114" ht="147" customHeight="1">
+    <row r="114" ht="329" customHeight="1">
       <c r="A114" s="10" t="n">
         <v>112</v>
       </c>
@@ -6014,32 +6014,32 @@
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Sezioni delle guide di cabina</t>
+          <t>Verifica delle guide di cabina — Confermati sul testo i coefficienti, le formule e i limiti, e il carico al piano per uso (UNI EN 81-20:2020, 5.7.2.3.6). Senza l'uso nei dati dell'impianto vale la regola per portata della UNI EN 81-1:2008 (G.2.5), che per un ascensore per persone da 2500 kg in su è dal lato della sicurezza. La formula di ω per Rm 370 è data da λ 20 a 250: sotto 20 il software usa ω di λ 20 (dal lato della sicurezza). Non contate: la spinta di scorrimento delle staffe (assestamento dell'edificio), le apparecchiature appese alle guide, le frecce di staffe ed edificio (la norma vuole la somma entro il limite) e le guide del contrappeso. La flessione della suola è quella dei pattini a rotelle (5.10.5 ha una formula a parte per quelli a scorrimento; il tipo di pattino non è un dato del software).</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>area, momenti d'inerzia e moduli di resistenza minimi attorno all'asse parallelo alla suola (x) e all'asse di simmetria (y), spessore c del collo tra lama e suola, per ogni profilo del software; raggi d'inerzia calcolati come √(I/A)</t>
+          <t>tra due staffe (l = distanza massima tra le staffe della guida) con le spinte della voce guide.spinte, portata spostata di 1/8 della cabina in un senso e poi nell'altro: flessione M = 3·F·l/16, σm = σx + σy; intervento del paracadute: forza verticale Fv = k1·g·(P+Q)/n più il peso della guida, carico di punta con il metodo omega (λ = l/i con il raggio d'inerzia minore √(I/A), λ ≤ 250; acciaio Rm 370: ω = 0,0001292·λ^1,89 + 1 fino a λ 60, 0,00004627·λ^2,14 + 1 fino a 85, 0,00001711·λ^2,35 + 1,04 fino a 115, 0,00016887·λ^2 fino a 250), σ = σm + Fv/A e σc = σk + 0,9·σm; marcia: k2 = 1,2 e il peso della guida; carico al piano: cabina vuota e Fs al centro della soglia di cabina, a ogni accesso, secondo l'uso indicato nei dati dell'impianto: persone 0,4·g·Q, merci accompagnate 0,6·g·Q, con mezzi di carico pesanti fuori portata 0,85·g·Q (senza l'uso: secondo la portata, 0,6·g·Q da 2500 kg); flessione della suola σF = 1,85·Fx/c² (pattini a rotelle); frecce δx = 0,7·Fx·l³/(48·E·Iy) e δy = 0,7·Fy·l³/(48·E·Ix) ≤ 5 mm. Tensione ammissibile Rm/St con St = 2,25 in marcia e al carico, 1,8 all'intervento del paracadute (allungamento A5 &gt; 12 %): con Rm 370 N/mm², 164,4 e 205,6 N/mm²</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>ISO 7465:2007 (ora ISO 8100-33:2022); EN 10055:1995 per il T 70×70×8 laminato</t>
+          <t>UNI EN 81-50:2020, 5.10.2–5.10.6; UNI EN 81-20:2020, 5.7.2.3.5, 5.7.2.3.6, 5.7.4.5 (Prospetto 15), 5.7.4.6 e Prospetto 14; UNI EN 81-1:2008, G.2.5 (l'uso non indicato)</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>tabella ISO 7465:2007 stampata da Savera (Standard Savera Guide, Rev 03/10; assi e c dalla Rev 08.26), anteprime ISO 7465:1997 e ISO 8100-33:2022 (correzione dei raggi del T127-1/B, stampati nel 2007 uguali ai moduli), EN 10055:1995, Tabella 1. La EN 10055 non ha il T 45: al T 45×45×5 il software dà la sezione del T45/A, delle stesse misure</t>
+          <t>UNI EN 81-50:2020, testo della norma, letto il 2026-10-06, pp. 35–39; UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 94–97; Rm 370 è scelta del software (il valore più basso)</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tensioni nelle guide di cabina; flessione della suola delle guide di cabina; frecce delle guide di cabina</t>
         </is>
       </c>
       <c r="I114" s="11" t="n"/>
@@ -6049,7 +6049,7 @@
       <c r="M114" s="11" t="n"/>
       <c r="N114" s="11" t="n"/>
     </row>
-    <row r="115" ht="69" customHeight="1">
+    <row r="115" ht="147" customHeight="1">
       <c r="A115" s="10" t="n">
         <v>113</v>
       </c>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Tipo di paracadute per la velocità nominale</t>
+          <t>Sezioni delle guide di cabina</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>istantaneo (anche a rulli imprigionati) fino a 0,63 m/s; oltre, progressivo (la UNI EN 81-20 non ha più l'istantaneo con effetto ammortizzato fino a 1 m/s); il tipo viene dai dati dell'impianto (se manca: progressivo, con la nota sul foglio)</t>
+          <t>area, momenti d'inerzia e moduli di resistenza minimi attorno all'asse parallelo alla suola (x) e all'asse di simmetria (y), spessore c del collo tra lama e suola, per ogni profilo del software; raggi d'inerzia calcolati come √(I/A)</t>
         </is>
       </c>
       <c r="E115" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.6.2.1.2.1; la regola precedente in UNI EN 81-1 (1999, 2008), 9.8.2.1</t>
+          <t>ISO 7465:2007 (ora ISO 8100-33:2022); EN 10055:1995 per il T 70×70×8 laminato</t>
         </is>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 81; UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 58</t>
+          <t>tabella ISO 7465:2007 stampata da Savera (Standard Savera Guide, Rev 03/10; assi e c dalla Rev 08.26), anteprime ISO 7465:1997 e ISO 8100-33:2022 (correzione dei raggi del T127-1/B, stampati nel 2007 uguali ai moduli), EN 10055:1995, Tabella 1. La EN 10055 non ha il T 45: al T 45×45×5 il software dà la sezione del T45/A, delle stesse misure</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>tipo di paracadute per la velocità</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I115" s="11" t="n"/>
@@ -6095,43 +6095,43 @@
       <c r="M115" s="11" t="n"/>
       <c r="N115" s="11" t="n"/>
     </row>
-    <row r="116" ht="43" customHeight="1">
+    <row r="116" ht="69" customHeight="1">
       <c r="A116" s="10" t="n">
         <v>114</v>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Dimensioni proposte della cabina</t>
+          <t>Tipo di paracadute per la velocità nominale</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
+          <t>istantaneo (anche a rulli imprigionati) fino a 0,63 m/s; oltre, progressivo (la UNI EN 81-20 non ha più l'istantaneo con effetto ammortizzato fino a 1 m/s); il tipo viene dai dati dell'impianto (se manca: progressivo, con la nota sul foglio)</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020, 5.6.2.1.2.1; la regola precedente in UNI EN 81-1 (1999, 2008), 9.8.2.1</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, p. 81; UNI EN 81-1:2008, testo della norma, letto il 2026-10-06, p. 58</t>
         </is>
       </c>
       <c r="G116" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tipo di paracadute per la velocità</t>
         </is>
       </c>
       <c r="I116" s="11" t="n"/>
@@ -6141,7 +6141,7 @@
       <c r="M116" s="11" t="n"/>
       <c r="N116" s="11" t="n"/>
     </row>
-    <row r="117" ht="225" customHeight="1">
+    <row r="117" ht="43" customHeight="1">
       <c r="A117" s="10" t="n">
         <v>115</v>
       </c>
@@ -6152,12 +6152,12 @@
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Quote della pianta fissate a mano</t>
+          <t>Dimensioni proposte della cabina</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8.1), quello del contrappeso dentro la lunghezza del contrappeso (la stessa verifica vale per quelli messi dal software: ammortizzatori.posizione)</t>
+          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
         </is>
       </c>
       <c r="E117" s="10" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I117" s="11" t="n"/>
@@ -6187,7 +6187,7 @@
       <c r="M117" s="11" t="n"/>
       <c r="N117" s="11" t="n"/>
     </row>
-    <row r="118" ht="82" customHeight="1">
+    <row r="118" ht="225" customHeight="1">
       <c r="A118" s="10" t="n">
         <v>116</v>
       </c>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>Limiti del modello del vano</t>
+          <t>Quote della pianta fissate a mano</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
+          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme». Anche gli ammortizzatori si possono spostare: quelli di cabina restano con il piatto sotto la piattaforma e fuori dalla pianta dello spazio di rifugio in fossa (UNI EN 81-20, 5.2.5.8.1), quello del contrappeso dentro la lunghezza del contrappeso (la stessa verifica vale per quelli messi dal software: ammortizzatori.posizione)</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>limite del modello attuale</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina; ammortizzatori fissati a mano: sotto cabina e contrappeso, fuori dal rifugio</t>
         </is>
       </c>
       <c r="I118" s="11" t="n"/>
@@ -6233,7 +6233,7 @@
       <c r="M118" s="11" t="n"/>
       <c r="N118" s="11" t="n"/>
     </row>
-    <row r="119" ht="238" customHeight="1">
+    <row r="119" ht="82" customHeight="1">
       <c r="A119" s="10" t="n">
         <v>117</v>
       </c>
@@ -6244,22 +6244,22 @@
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>Verifiche che il software non calcola</t>
+          <t>Limiti del modello del vano</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>da fare a parte, con i dati dei fornitori: sollecitazioni e frecce delle staffe e delle guide del contrappeso (UNI EN 81-50:2020, 5.10: il software verifica le guide di cabina, sul foglio 1 delle tavole); puleggia del contrappeso in taglia 2:1 sotto il soffitto; paracadute del contrappeso con spazi accessibili sotto il vano; distanza tra le parti fisse più alte della fossa e quelle più basse della cabina sugli ammortizzatori; sporgenze nel vano oltre 150 mm senza balaustra; locale della macchina in basso (dimensioni e spazi di manovra: il software non lo disegna); movimento incontrollato della cabina (UCM) e velocità eccessiva in salita con la nuova macchina; muro sotto la soglia di piano (5.2.5.3.2 a)); le soluzioni della UNI EN 81-21:2022 per testata, fossa, locale e porte ridotti (le verifiche in sezione seguono solo la UNI EN 81-20:2020)</t>
+          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020: guide e staffe 5.7.2–5.7.4 (con UNI EN 81-50:2020, 5.10); distanze in testata 5.2.5.7.2; spazi accessibili sotto il vano 5.2.5.4; parti fisse in fossa 5.2.5.8.2; sporgenze oltre 0,15 m 5.2.5.2.2.2; locale del macchinario 5.2.6.3; velocità eccessiva in salita 5.6.6; movimento incontrollato 5.6.7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 31–43, 89–97; analisi delle lacune del 2026-10-03</t>
+          <t>limite del modello attuale</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
@@ -6279,38 +6279,38 @@
       <c r="M119" s="11" t="n"/>
       <c r="N119" s="11" t="n"/>
     </row>
-    <row r="120" ht="56" customHeight="1">
+    <row r="120" ht="238" customHeight="1">
       <c r="A120" s="10" t="n">
         <v>118</v>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Corsa</t>
+          <t>Verifiche che il software non calcola</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
+          <t>da fare a parte, con i dati dei fornitori: sollecitazioni e frecce delle staffe e delle guide del contrappeso (UNI EN 81-50:2020, 5.10: il software verifica le guide di cabina, sul foglio 1 delle tavole); puleggia del contrappeso in taglia 2:1 sotto il soffitto; paracadute del contrappeso con spazi accessibili sotto il vano; distanza tra le parti fisse più alte della fossa e quelle più basse della cabina sugli ammortizzatori; sporgenze nel vano oltre 150 mm senza balaustra; locale della macchina in basso (dimensioni e spazi di manovra: il software non lo disegna); movimento incontrollato della cabina (UCM) e velocità eccessiva in salita con la nuova macchina; muro sotto la soglia di piano (5.2.5.3.2 a)); le soluzioni della UNI EN 81-21:2022 per testata, fossa, locale e porte ridotti (le verifiche in sezione seguono solo la UNI EN 81-20:2020)</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-20:2020: guide e staffe 5.7.2–5.7.4 (con UNI EN 81-50:2020, 5.10); distanze in testata 5.2.5.7.2; spazi accessibili sotto il vano 5.2.5.4; parti fisse in fossa 5.2.5.8.2; sporgenze oltre 0,15 m 5.2.5.2.2.2; locale del macchinario 5.2.6.3; velocità eccessiva in salita 5.6.6; movimento incontrollato 5.6.7</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>dati dei piani inseriti</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 31–43, 89–97; analisi delle lacune del 2026-10-03</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H120" s="10" t="inlineStr">
@@ -6325,7 +6325,7 @@
       <c r="M120" s="11" t="n"/>
       <c r="N120" s="11" t="n"/>
     </row>
-    <row r="121" ht="121" customHeight="1">
+    <row r="121" ht="56" customHeight="1">
       <c r="A121" s="10" t="n">
         <v>119</v>
       </c>
@@ -6336,22 +6336,22 @@
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Portata e velocità — In una modifica la UNI 10411-1:2024 (6.1, prospetto 1) tratta come aumento della portata oltre il 10 % (Q fino a 500 kg) o il 5 % (oltre) e del carico totale oltre il 15 % o il 10 %; la UNI 10411-11:2024 (6.1) ogni aumento del carico totale: il confronto con la portata originale lo fa l'ingegnere.</t>
+          <t>Corsa</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
+          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
         </is>
       </c>
       <c r="E121" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.2.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>progetto del vano</t>
+          <t>dati dei piani inseriti</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -6371,7 +6371,7 @@
       <c r="M121" s="11" t="n"/>
       <c r="N121" s="11" t="n"/>
     </row>
-    <row r="122" ht="316" customHeight="1">
+    <row r="122" ht="56" customHeight="1">
       <c r="A122" s="10" t="n">
         <v>120</v>
       </c>
@@ -6382,27 +6382,27 @@
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Normativa di collaudo e parti sostituite o modificate — lo scopo delle due UNI 10411 e i requisiti per la sostituzione del macchinario (punto 14) sono letti sul testo (voce sostituzione.adeguamenti); quali verifiche riguardano ciascuna parte e la matrice delle norme compatibili sono una lettura del software, da approvare dall'ingegnere</t>
+          <t>Portata e velocità — In una modifica il confronto con i carichi documentati è nella voce impianto.variazione.carico.</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico a frizione non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (a frizione, conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software. Alla norma base si aggiungono le norme compatibili (matrice della ricerca, cap. 16 §5.2): sull'impianto nuovo le EN 81 supplementari (21, 28, 58, 70, 71, 72, 73, 76, 77), sulla modifica la EN 81-20/50 intera, le EN 81-28, 58, 73 e il miglioramento (80, 82, 83), su entrambi DM 236/1989, antincendio (DM 15/09/2005 o Codice V.3) e NTC 2018 (con le verifiche delle putrelle). Ogni norma ha il suo esito («non calcolata» se il software non ne calcola verifiche) e i suoi punti da verificare in sito nella relazione, con gli adempimenti del DPR 162/1999</t>
+          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
+          <t>UNI EN 81-20:2020, 5.4.2.1</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, testo della norma, letto il 2026-10-06, pp. 5, 13–14; UNI 10411-11:2024, testo della norma, letto il 2026-10-06, pp. 5, 12; schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); ricerca, capitoli 2.4 e 6.6</t>
+          <t>progetto del vano</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H122" s="10" t="inlineStr">
@@ -6417,7 +6417,7 @@
       <c r="M122" s="11" t="n"/>
       <c r="N122" s="11" t="n"/>
     </row>
-    <row r="123" ht="264" customHeight="1">
+    <row r="123" ht="212" customHeight="1">
       <c r="A123" s="10" t="n">
         <v>121</v>
       </c>
@@ -6428,27 +6428,27 @@
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Rifacimento con l'arcata esistente — il DPR 162/1999 elenca le modifiche costruttive senza dire quando l'insieme diventa una sostituzione completa; la UNI 10411-1/-11:2024 (21.1) chiama modifica sostanziale il cambio insieme di quadro, macchina, almeno una porta di piano, cabina e arcata, con il risultato secondo la UNI EN 81-20:2020: tenendo l'arcata il 21.1 non si applica. Una cabina nuova nell'arcata esistente segue la UNI EN 81-20 5.4.1–5.4.10 (UNI 10411-1:2024, 22; con porte di cabina a battente fino a +0,10 m² di superficie senza cambiare la portata, 22 f)). La qualificazione dell'intervento la conferma il tecnico incaricato con il soggetto che esegue la verifica straordinaria</t>
+          <t>Modifica: variazione dei carichi rispetto allo stato documentato — T* della norma non comprende funi e cavi: P del calcolo comprende la quota del cavo flessibile, che si annulla nel confronto se resta la stessa. Quale portata decide la riga del prospetto non è detto nel testo (scelta prudente del software); con la -11 il 10 % si somma alle modifiche precedenti: lo stato documentato è quello dell'impianto originale</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>si sostituiscono tutte le parti tranne l'arcata, che resta: le sostituzioni sono modifiche costruttive dell'impianto esistente, che si collauda secondo UNI 10411-1:2024 o UNI 10411-11:2024 e non come impianto nuovo; le verifiche che riguardano solo l'arcata (il tipo di paracadute, se la velocità non cambia) sono riportate come «esistente». La sostituzione completa dell'ascensore, arcata compresa, si collauda come impianto nuovo (UNI EN 81-20:2020 e UNI EN 81-50:2020; negli edifici esistenti anche la UNI EN 81-21:2022, supplementare)</t>
+          <t>con i carichi dell'ultimo verbale (collaudo o verifica straordinaria) — portata, cabina vuota completa P, contrappeso — e quelli del progetto, T* = P + Q: con la UNI 10411-1 le verifiche del carico entrano nell'esito se la portata cresce oltre il 10 % o T* oltre il 15 % (portata fino a 500 kg; oltre: 5 % e 10 %, prospetto 1) o se il contrappeso cresce oltre il 25 % della portata (oltre 500 kg: 10 %, prospetto 2); con la UNI 10411-11 a ogni aumento, e oltre il 10 % anche le strutture (punto 5, escluse fino a lì dal 6.2); un carico che diminuisce le porta anch'esso (ammortizzatori, paracadute progressivo). Con le due portate a cavallo di 500 kg vale la riga più severa, e la quota del contrappeso si misura sulla portata minore</t>
         </is>
       </c>
       <c r="E123" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., art. 2 c.1 lett. cc), art. 12 c.4, art. 14 c.3; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-21:2022 (scopo)</t>
+          <t>UNI 10411-1:2024, 6.1 (prospetti 1 e 2); UNI 10411-11:2024, 6.1 e 6.2</t>
         </is>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>indicazione del cliente (5 ottobre 2026): prassi di lasciare l'arcata; ricerca, capitolo 16 §3.2 e §5.3</t>
+          <t>UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 7; UNI 10411-11:2024, testo della norma, letto il 2026-10-06, pp. 7–8</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
         <is>
-          <t>prassi di cantiere</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H123" s="10" t="inlineStr">
@@ -6463,7 +6463,7 @@
       <c r="M123" s="11" t="n"/>
       <c r="N123" s="11" t="n"/>
     </row>
-    <row r="124" ht="69" customHeight="1">
+    <row r="124" ht="108" customHeight="1">
       <c r="A124" s="10" t="n">
         <v>122</v>
       </c>
@@ -6474,27 +6474,27 @@
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
+          <t>Modifica: UNI 10411-1 o UNI 10411-11 — la data dal DPR 162/1999 è una lettura dell'articolo 19 (messa in servizio secondo le regole precedenti fino al 30 giugno 1999)</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
+          <t>dalla marcatura CE dell'impianto — dichiarazione di conformità CE/UE nel libretto e marcatura nella cabina —: presente UNI 10411-11, assente UNI 10411-1; non nota, dalla data di messa in servizio: fino al 30 giugno 1999 UNI 10411-1, dal 01/07/1999 UNI 10411-11, da confermare con il libretto (la relazione lo riporta). La targa dell'impianto non lo dice</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
+          <t>UNI 10411-11:2024, 1 e 3.3–3.4; UNI 10411-1:2024, 1; DPR 162/1999, art. 7 c.2, art. 16 c.1 e c.3, art. 19 c.1</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>scelta del software, senza fonte</t>
+          <t>UNI 10411-1:2024, testo della norma, letto il 2026-10-06, p. 5; UNI 10411-11:2024, testo della norma, letto il 2026-10-06, pp. 5–6; DPR 162/1999 (testo su Normattiva)</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H124" s="10" t="inlineStr">
@@ -6509,7 +6509,7 @@
       <c r="M124" s="11" t="n"/>
       <c r="N124" s="11" t="n"/>
     </row>
-    <row r="125" ht="108" customHeight="1">
+    <row r="125" ht="316" customHeight="1">
       <c r="A125" s="10" t="n">
         <v>123</v>
       </c>
@@ -6520,22 +6520,22 @@
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Fune oltre la corsa (L0)</t>
+          <t>Normativa di collaudo e parti sostituite o modificate — lo scopo delle due UNI 10411 e i requisiti per la sostituzione del macchinario (punto 14) sono letti sul testo (voce sostituzione.adeguamenti); quali verifiche riguardano ciascuna parte e la matrice delle norme compatibili sono una lettura del software, da approvare dall'ingegnere</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale; con la puleggia di rinvio, l'asse sul basamento o sul telaio che la porta (voce locale.rinvio); macchina in basso o senza locale: fino al soffitto del vano</t>
+          <t>impianto nuovo: UNI EN 81-20:2020 e UNI EN 81-50:2020, ogni verifica entra nell'esito; modifica di un impianto esistente: UNI 10411-1:2024 (ascensore elettrico a frizione non conforme alla Direttiva Ascensori) o UNI 10411-11:2024 (a frizione, conforme alla 95/16/CE o alla 2014/33/UE), a scelta dell'utente: entrano nell'esito le verifiche che riguardano le parti sostituite o modificate (comprese le variazioni di velocità, portata e corsa), le altre sono riportate come «esistente» con il valore calcolato. Quali parti riguarda ciascuna verifica è una lettura del software. Alla norma base si aggiungono le norme compatibili (matrice della ricerca, cap. 16 §5.2): sull'impianto nuovo le EN 81 supplementari (21, 28, 58, 70, 71, 72, 73, 76, 77), sulla modifica la EN 81-20/50 intera, le EN 81-28, 58, 73 e il miglioramento (80, 82, 83), su entrambi DM 236/1989, antincendio (DM 15/09/2005 o Codice V.3) e NTC 2018 (con le verifiche delle putrelle). Ogni norma ha il suo esito («non calcolata» se il software non ne calcola verifiche) e i suoi punti da verificare in sito nella relazione, con gli adempimenti del DPR 162/1999</t>
         </is>
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DPR 162/1999 e s.m.i.; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-20:2020; UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
+          <t>UNI 10411-1:2024, testo della norma, letto il 2026-10-06, pp. 5, 13–14; UNI 10411-11:2024, testo della norma, letto il 2026-10-06, pp. 5, 12; schema ICIM delle verifiche (la verifica straordinaria si limita di norma alle modifiche); ricerca, capitoli 2.4 e 6.6</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
@@ -6555,7 +6555,7 @@
       <c r="M125" s="11" t="n"/>
       <c r="N125" s="11" t="n"/>
     </row>
-    <row r="126" ht="147" customHeight="1">
+    <row r="126" ht="264" customHeight="1">
       <c r="A126" s="10" t="n">
         <v>124</v>
       </c>
@@ -6566,27 +6566,27 @@
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
+          <t>Rifacimento con l'arcata esistente — il DPR 162/1999 elenca le modifiche costruttive senza dire quando l'insieme diventa una sostituzione completa; la UNI 10411-1/-11:2024 (21.1) chiama modifica sostanziale il cambio insieme di quadro, macchina, almeno una porta di piano, cabina e arcata, con il risultato secondo la UNI EN 81-20:2020: tenendo l'arcata il 21.1 non si applica. Una cabina nuova nell'arcata esistente segue la UNI EN 81-20 5.4.1–5.4.10 (UNI 10411-1:2024, 22; con porte di cabina a battente fino a +0,10 m² di superficie senza cambiare la portata, 22 f)). La qualificazione dell'intervento la conferma il tecnico incaricato con il soggetto che esegue la verifica straordinaria</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
+          <t>si sostituiscono tutte le parti tranne l'arcata, che resta: le sostituzioni sono modifiche costruttive dell'impianto esistente, che si collauda secondo UNI 10411-1:2024 o UNI 10411-11:2024 e non come impianto nuovo; le verifiche che riguardano solo l'arcata (il tipo di paracadute, se la velocità non cambia) sono riportate come «esistente». La sostituzione completa dell'ascensore, arcata compresa, si collauda come impianto nuovo (UNI EN 81-20:2020 e UNI EN 81-50:2020; negli edifici esistenti anche la UNI EN 81-21:2022, supplementare)</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3</t>
+          <t>DPR 162/1999 e s.m.i., art. 2 c.1 lett. cc), art. 12 c.4, art. 14 c.3; UNI 10411-1:2024; UNI 10411-11:2024; UNI EN 81-21:2022 (scopo)</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>pianta del vano</t>
+          <t>indicazione del cliente (5 ottobre 2026): prassi di lasciare l'arcata; ricerca, capitolo 16 §3.2 e §5.3</t>
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>prassi di cantiere</t>
         </is>
       </c>
       <c r="H126" s="10" t="inlineStr">
@@ -6601,7 +6601,7 @@
       <c r="M126" s="11" t="n"/>
       <c r="N126" s="11" t="n"/>
     </row>
-    <row r="127" ht="160" customHeight="1">
+    <row r="127" ht="69" customHeight="1">
       <c r="A127" s="10" t="n">
         <v>125</v>
       </c>
@@ -6612,27 +6612,27 @@
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
+          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
+          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
+          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>geometria delle funi</t>
+          <t>scelta del software, senza fonte</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H127" s="10" t="inlineStr">
@@ -6647,7 +6647,7 @@
       <c r="M127" s="11" t="n"/>
       <c r="N127" s="11" t="n"/>
     </row>
-    <row r="128" ht="56" customHeight="1">
+    <row r="128" ht="108" customHeight="1">
       <c r="A128" s="10" t="n">
         <v>126</v>
       </c>
@@ -6658,27 +6658,27 @@
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
+          <t>Fune oltre la corsa (L0)</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
+          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale; con la puleggia di rinvio, l'asse sul basamento o sul telaio che la porta (voce locale.rinvio); macchina in basso o senza locale: fino al soffitto del vano</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano</t>
+          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
         </is>
       </c>
       <c r="G128" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H128" s="10" t="inlineStr">
@@ -6693,7 +6693,7 @@
       <c r="M128" s="11" t="n"/>
       <c r="N128" s="11" t="n"/>
     </row>
-    <row r="129" ht="238" customHeight="1">
+    <row r="129" ht="147" customHeight="1">
       <c r="A129" s="10" t="n">
         <v>127</v>
       </c>
@@ -6704,27 +6704,27 @@
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso — la EN 81-20 non ammette più il pilastro pieno fino al terreno — (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori; in una modifica la UNI 10411-1:2024 (6.14) accetta al posto del paracadute un pilastro esistente fino al terreno, verificato per i nuovi carichi</t>
+          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
+          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
         <is>
-          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
+          <t>ricerca, capitolo 5.3</t>
         </is>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>geometria ricostruita dal software</t>
+          <t>pianta del vano</t>
         </is>
       </c>
       <c r="G129" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H129" s="10" t="inlineStr">
@@ -6739,7 +6739,7 @@
       <c r="M129" s="11" t="n"/>
       <c r="N129" s="11" t="n"/>
     </row>
-    <row r="130" ht="251" customHeight="1">
+    <row r="130" ht="160" customHeight="1">
       <c r="A130" s="10" t="n">
         <v>128</v>
       </c>
@@ -6750,27 +6750,27 @@
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta dal catalogo di un costruttore — la tolleranza sul rapporto è una scelta del software: la velocità reale con l'inverter deve restare entro il 5 % sopra la nominale (UNI EN 81-20:2020, 5.9.2.4; buona pratica non oltre l'8 % sotto); i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
+          <t>Tiro diretto (senza rinvio): calata uguale al diametro della puleggia — con un diametro diverso dalla calata le funi si inclinano verso gli attacchi: nella sostituzione con il confronto il calcolo ne tiene conto per la nuova puleggia; oltre pochi millimetri servono una puleggia di rinvio o il contrappeso spostato (quota «Calata» in pianta)</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo; i disegni e il 3D mostrano l'argano SICOR com'è (ingombri, piedi e fori, asse della puleggia, P ed E della scheda), sul telaio del software</t>
+          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
+          <t>ricerca, capitolo 5.3 (angolo di avvolgimento del tiro diretto)</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>SICOR: schede tecniche 2025 e modelli CAD scaricati da sicoritaly.com il 2 ottobre 2026 (solo le quote); Sassi, Montanari, GEM, FAER: estratti delle pagine dei costruttori e dei rivenditori, 1° ottobre 2026</t>
+          <t>geometria delle funi</t>
         </is>
       </c>
       <c r="G130" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H130" s="10" t="inlineStr">
@@ -6785,7 +6785,7 @@
       <c r="M130" s="11" t="n"/>
       <c r="N130" s="11" t="n"/>
     </row>
-    <row r="131" ht="134" customHeight="1">
+    <row r="131" ht="56" customHeight="1">
       <c r="A131" s="10" t="n">
         <v>129</v>
       </c>
@@ -6796,27 +6796,27 @@
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
+          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
+          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 8</t>
+          <t>ricerca, capitolo 5; funi con la macchina in basso, capitolo 2.6</t>
         </is>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo</t>
+          <t>dati verticali del vano</t>
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H131" s="10" t="inlineStr">
@@ -6831,38 +6831,38 @@
       <c r="M131" s="11" t="n"/>
       <c r="N131" s="11" t="n"/>
     </row>
-    <row r="132" ht="69" customHeight="1">
+    <row r="132" ht="238" customHeight="1">
       <c r="A132" s="10" t="n">
         <v>130</v>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
+          <t>Macchina in basso: schema delle funi — lo schema reale va rilevato sull'impianto; con la macchina sotto il vano lo spazio sotto la fossa è accessibile: paracadute del contrappeso — la EN 81-20 non ammette più il pilastro pieno fino al terreno — (UNI EN 81-20:2020, 5.2.5.4) e fondo della fossa per le reazioni degli ammortizzatori; in una modifica la UNI 10411-1:2024 (6.14) accetta al posto del paracadute un pilastro esistente fino al terreno, verificato per i nuovi carichi</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
+          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
+          <t>ricerca, funi con la macchina in basso, capitoli 2–5; DPR 1497/1963 artt. 5–9, 33</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo (src/calc/model.ts)</t>
+          <t>geometria ricostruita dal software</t>
         </is>
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H132" s="10" t="inlineStr">
@@ -6877,33 +6877,33 @@
       <c r="M132" s="11" t="n"/>
       <c r="N132" s="11" t="n"/>
     </row>
-    <row r="133" ht="56" customHeight="1">
+    <row r="133" ht="251" customHeight="1">
       <c r="A133" s="10" t="n">
         <v>131</v>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
+          <t>Macchina proposta dal catalogo di un costruttore — la tolleranza sul rapporto è una scelta del software: la velocità reale con l'inverter deve restare entro il 5 % sopra la nominale (UNI EN 81-20:2020, 5.9.2.4; buona pratica non oltre l'8 % sotto); i dati di Sassi, Montanari, GEM e FAER vengono da estratti dei motori di ricerca, non dai documenti; tutti vanno confermati sulla scheda del costruttore prima dell'ordine; per Montanari la massa è quella del riduttore (senza motore, puleggia e volano) e le pulegge sono quelle delle configurazioni tipiche; GEAT Elevators distribuisce argani Montanari, Sassi e FAER (P58F, P58S) e non ne costruisce</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
+          <t>tra le opzioni del dimensionamento solo quelle che un argano del costruttore scelto accetta: puleggia nella gamma del modello, carico statico sull'albero non oltre quello del catalogo, motore non oltre il più grande del catalogo, portata dichiarata; il rapporto è quello del catalogo più vicino al rapporto ideale, se la velocità che dà non si scosta da quella nominale più del 10 % (l'inverter adatta la frequenza); il calcolo usa quel rapporto, il carico statico ammesso e la massa del catalogo; i disegni e il 3D mostrano l'argano SICOR com'è (ingombri, piedi e fori, asse della puleggia, P ed E della scheda), sul telaio del software</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
         <is>
-          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
+          <t>ricerca, capitolo 12 (catalogo degli argani)</t>
         </is>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>SICOR: schede tecniche 2025 e modelli CAD scaricati da sicoritaly.com il 2 ottobre 2026 (solo le quote); Sassi, Montanari, GEM, FAER: estratti delle pagine dei costruttori e dei rivenditori, 1° ottobre 2026</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
@@ -6923,33 +6923,33 @@
       <c r="M133" s="11" t="n"/>
       <c r="N133" s="11" t="n"/>
     </row>
-    <row r="134" ht="69" customHeight="1">
+    <row r="134" ht="134" customHeight="1">
       <c r="A134" s="10" t="n">
         <v>132</v>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>Limite di aderenza mostrato durante la marcia</t>
+          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
+          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.1 e 5.11.2.3.2 (μ della frenatura)</t>
+          <t>ricerca, capitolo 8</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>motore di calcolo</t>
         </is>
       </c>
       <c r="G134" s="10" t="inlineStr">
@@ -6969,7 +6969,7 @@
       <c r="M134" s="11" t="n"/>
       <c r="N134" s="11" t="n"/>
     </row>
-    <row r="135" ht="108" customHeight="1">
+    <row r="135" ht="69" customHeight="1">
       <c r="A135" s="10" t="n">
         <v>133</v>
       </c>
@@ -6980,27 +6980,27 @@
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Tempi delle porte — La norma non dà tempi: per le porte automatiche orizzontali dà l'energia cinetica (≤ 10 J, ≤ 4 J con il dispositivo di protezione escluso) e la forza contro la chiusura (≤ 150 N) (UNI EN 81-20:2020, 5.3.6.2.2.1), dati del fornitore delle porte.</t>
+          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
+          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (solo animazione)</t>
+          <t>motore di calcolo (src/calc/model.ts)</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H135" s="10" t="inlineStr">
@@ -7015,7 +7015,7 @@
       <c r="M135" s="11" t="n"/>
       <c r="N135" s="11" t="n"/>
     </row>
-    <row r="136" ht="212" customHeight="1">
+    <row r="136" ht="56" customHeight="1">
       <c r="A136" s="10" t="n">
         <v>134</v>
       </c>
@@ -7026,22 +7026,22 @@
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione. Le decelerazioni mostrate non sono una verifica: per i tamponi non lineari la norma vuole media ≤ 1 gn, oltre 2,5 gn per non più di 0,04 s, picco ≤ 6 gn e rimbalzo ≤ 1 m/s (5.8.2.1.2.1), per gli idraulici media ≤ 1 gn e oltre 2,5 gn per non più di 0,04 s (5.8.2.2.3); si provano per tipo (certificato del fornitore)</t>
+          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
+          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2.1.1.1–5.8.2.1.1.2 (urto al 115 %; corsa piena con un carico statico tra 2,5 e 4 volte: il software prende 4), 5.8.2.1.2.2 (90 %), 5.8.2.2.1 e 5.8.2.2.3 a)</t>
+          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 98–99</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G136" s="10" t="inlineStr">
@@ -7061,7 +7061,7 @@
       <c r="M136" s="11" t="n"/>
       <c r="N136" s="11" t="n"/>
     </row>
-    <row r="137" ht="82" customHeight="1">
+    <row r="137" ht="69" customHeight="1">
       <c r="A137" s="10" t="n">
         <v>135</v>
       </c>
@@ -7072,22 +7072,22 @@
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Cabina bloccata: rotazione in salita — La simulazione mostra il contrappeso sugli ammortizzatori con la cabina in alto; la norma chiede anche la cabina vuota in basso, che il calcolo verifica (tr_stall).</t>
+          <t>Limite di aderenza mostrato durante la marcia</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
+          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.2.3</t>
+          <t>UNI EN 81-50:2020, 5.11.1 e 5.11.2.3.2 (μ della frenatura)</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo; velocità scelta dal software</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G137" s="10" t="inlineStr">
@@ -7107,7 +7107,7 @@
       <c r="M137" s="11" t="n"/>
       <c r="N137" s="11" t="n"/>
     </row>
-    <row r="138" ht="43" customHeight="1">
+    <row r="138" ht="108" customHeight="1">
       <c r="A138" s="10" t="n">
         <v>136</v>
       </c>
@@ -7118,12 +7118,12 @@
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Passo di campionamento</t>
+          <t>Tempi delle porte — La norma non dà tempi: per le porte automatiche orizzontali dà l'energia cinetica (≤ 10 J, ≤ 4 J con il dispositivo di protezione escluso) e la forza contro la chiusura (≤ 150 N) (UNI EN 81-20:2020, 5.3.6.2.2.1), dati del fornitore delle porte.</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
+          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>scelta del software (solo animazione)</t>
         </is>
       </c>
       <c r="G138" s="10" t="inlineStr">
@@ -7153,38 +7153,38 @@
       <c r="M138" s="11" t="n"/>
       <c r="N138" s="11" t="n"/>
     </row>
-    <row r="139" ht="56" customHeight="1">
+    <row r="139" ht="212" customHeight="1">
       <c r="A139" s="10" t="n">
         <v>137</v>
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 4-bis</t>
+          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa (il tampone in poliuretano reale non è lineare: valori indicativi); la verifica della corsa resta quella della sezione. Le decelerazioni mostrate non sono una verifica: per i tamponi non lineari la norma vuole media ≤ 1 gn, oltre 2,5 gn per non più di 0,04 s, picco ≤ 6 gn e rimbalzo ≤ 1 m/s (5.8.2.1.2.1), per gli idraulici media ≤ 1 gn e oltre 2,5 gn per non più di 0,04 s (5.8.2.2.3); si provano per tipo (certificato del fornitore)</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>progetto, fabbricazione, installazione e prove conformi all'All. I; documentazione tecnica e dichiarazione di conformità conservate per 10 anni</t>
+          <t>velocità d'urto 1,15 volte la nominale; molle e tamponi in poliuretano come ammortizzatori lineari con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa; per i tamponi la corsa utile è 0,9·H); ammortizzatori idraulici con decelerazione costante v₀²/(2·corsa) su tutta la corsa; la cabina e il contrappeso si separano all'urto</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 4-bis</t>
+          <t>UNI EN 81-20:2020, 5.8.2.1.1.1–5.8.2.1.1.2 (urto al 115 %; corsa piena con un carico statico tra 2,5 e 4 volte: il software prende 4), 5.8.2.1.2.2 (90 %), 5.8.2.2.1 e 5.8.2.2.3 a)</t>
         </is>
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>UNI EN 81-20:2020, testo della norma, letto il 2026-10-06, pp. 98–99</t>
         </is>
       </c>
       <c r="G139" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H139" s="10" t="inlineStr">
@@ -7199,38 +7199,38 @@
       <c r="M139" s="11" t="n"/>
       <c r="N139" s="11" t="n"/>
     </row>
-    <row r="140" ht="56" customHeight="1">
+    <row r="140" ht="82" customHeight="1">
       <c r="A140" s="10" t="n">
         <v>138</v>
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., artt. 6-bis e 7 c.3</t>
+          <t>Cabina bloccata: rotazione in salita — La simulazione mostra il contrappeso sugli ammortizzatori con la cabina in alto; la norma chiede anche la cabina vuota in basso, che il calcolo verifica (tr_stall).</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>procedura con un organismo notificato (ascensore modello con esame UE del tipo, All. IV B, più All. V, X o XII; oppure All. VIII o XI); marcatura CE in cabina con il numero dell'organismo</t>
+          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
         </is>
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., artt. 6-bis e 7 c.3</t>
+          <t>UNI EN 81-50:2020, 5.11.2.2.3</t>
         </is>
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>motore di calcolo; velocità scelta dal software</t>
         </is>
       </c>
       <c r="G140" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H140" s="10" t="inlineStr">
@@ -7245,38 +7245,38 @@
       <c r="M140" s="11" t="n"/>
       <c r="N140" s="11" t="n"/>
     </row>
-    <row r="141" ht="56" customHeight="1">
+    <row r="141" ht="43" customHeight="1">
       <c r="A141" s="10" t="n">
         <v>139</v>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
+          <t>Simulazione nel tempo (3D e grafici)</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., art. 12 c.1–3</t>
+          <t>Passo di campionamento</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>comunicazione al Comune entro 60 giorni dalla dichiarazione di conformità (oltre: con il verbale di una verifica straordinaria di attivazione); matricola entro 30 giorni</t>
+          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
         </is>
       </c>
       <c r="E141" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., art. 12 c.1–3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G141" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H141" s="10" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
+          <t>DPR 162/1999, art. 4-bis</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>verifiche periodiche ogni 2 anni; controllo dei dispositivi di sicurezza, delle funi e dell'isolamento almeno ogni 6 mesi; targa in cabina</t>
+          <t>progetto, fabbricazione, installazione e prove conformi all'All. I; documentazione tecnica e dichiarazione di conformità conservate per 10 anni</t>
         </is>
       </c>
       <c r="E142" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
+          <t>DPR 162/1999, art. 4-bis</t>
         </is>
       </c>
       <c r="F142" s="10" t="inlineStr">
@@ -7337,28 +7337,28 @@
       <c r="M142" s="11" t="n"/>
       <c r="N142" s="11" t="n"/>
     </row>
-    <row r="143" ht="43" customHeight="1">
+    <row r="143" ht="56" customHeight="1">
       <c r="A143" s="10" t="n">
         <v>141</v>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
+          <t>DPR 162/1999 e s.m.i., artt. 6-bis e 7 c.3</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>la modifica è costruttiva: la sostituzione del macchinario ne è il caso n. 5)</t>
+          <t>procedura con un organismo notificato (ascensore modello con esame UE del tipo, All. IV B, più All. V, X o XII; oppure All. VIII o XI); marcatura CE in cabina con il numero dell'organismo</t>
         </is>
       </c>
       <c r="E143" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
+          <t>DPR 162/1999 e s.m.i., artt. 6-bis e 7 c.3</t>
         </is>
       </c>
       <c r="F143" s="10" t="inlineStr">
@@ -7383,28 +7383,28 @@
       <c r="M143" s="11" t="n"/>
       <c r="N143" s="11" t="n"/>
     </row>
-    <row r="144" ht="43" customHeight="1">
+    <row r="144" ht="56" customHeight="1">
       <c r="A144" s="10" t="n">
         <v>142</v>
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4</t>
+          <t>DPR 162/1999 e s.m.i., art. 12 c.1–3</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>prima della comunicazione, adeguamento della parte modificata o sostituita e delle altre parti interessate</t>
+          <t>comunicazione al Comune entro 60 giorni dalla dichiarazione di conformità (oltre: con il verbale di una verifica straordinaria di attivazione); matricola entro 30 giorni</t>
         </is>
       </c>
       <c r="E144" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4</t>
+          <t>DPR 162/1999 e s.m.i., art. 12 c.1–3</t>
         </is>
       </c>
       <c r="F144" s="10" t="inlineStr">
@@ -7429,28 +7429,28 @@
       <c r="M144" s="11" t="n"/>
       <c r="N144" s="11" t="n"/>
     </row>
-    <row r="145" ht="43" customHeight="1">
+    <row r="145" ht="56" customHeight="1">
       <c r="A145" s="10" t="n">
         <v>143</v>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (impianto nuovo)</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4–5</t>
+          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>comunicazione al Comune e al soggetto delle verifiche periodiche; l'impianto non resta in esercizio senza le comunicazioni aggiornate</t>
+          <t>verifiche periodiche ogni 2 anni; controllo dei dispositivi di sicurezza, delle funi e dell'isolamento almeno ogni 6 mesi; targa in cabina</t>
         </is>
       </c>
       <c r="E145" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 12 c.4–5</t>
+          <t>DPR 162/1999, artt. 13, 15 c.4 e 16 c.3</t>
         </is>
       </c>
       <c r="F145" s="10" t="inlineStr">
@@ -7475,7 +7475,7 @@
       <c r="M145" s="11" t="n"/>
       <c r="N145" s="11" t="n"/>
     </row>
-    <row r="146" ht="69" customHeight="1">
+    <row r="146" ht="43" customHeight="1">
       <c r="A146" s="10" t="n">
         <v>144</v>
       </c>
@@ -7486,17 +7486,17 @@
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., art. 14 c.3; schema ICIM SCI 162 rev. 02</t>
+          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>verifica straordinaria da uno dei soggetti dell'art. 13 c.1 (la legge); secondo lo schema ICIM è di norma limitata ai controlli sulle modifiche, con la documentazione delle modifiche e dei componenti sostituiti</t>
+          <t>la modifica è costruttiva: la sostituzione del macchinario ne è il caso n. 5)</t>
         </is>
       </c>
       <c r="E146" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999 e s.m.i., art. 14 c.3; schema ICIM SCI 162 rev. 02</t>
+          <t>DPR 162/1999, art. 2 c.1 lett. cc)</t>
         </is>
       </c>
       <c r="F146" s="10" t="inlineStr">
@@ -7521,7 +7521,7 @@
       <c r="M146" s="11" t="n"/>
       <c r="N146" s="11" t="n"/>
     </row>
-    <row r="147" ht="82" customHeight="1">
+    <row r="147" ht="43" customHeight="1">
       <c r="A147" s="10" t="n">
         <v>145</v>
       </c>
@@ -7532,22 +7532,22 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024 e UNI 10411-11:2024, 25</t>
+          <t>DPR 162/1999, art. 12 c.4</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>documentazione della modifica (App. C della -1, App. A della -11): il proprietario la tiene per chi esegue la verifica straordinaria e la allega alla dichiarazione di conformità (DM 37/2008); manuali della macchina, del quadro e dei nuovi componenti di sicurezza consegnati al proprietario</t>
+          <t>prima della comunicazione, adeguamento della parte modificata o sostituita e delle altre parti interessate</t>
         </is>
       </c>
       <c r="E147" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024 e UNI 10411-11:2024, 25</t>
+          <t>DPR 162/1999, art. 12 c.4</t>
         </is>
       </c>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G147" s="10" t="inlineStr">
@@ -7567,28 +7567,28 @@
       <c r="M147" s="11" t="n"/>
       <c r="N147" s="11" t="n"/>
     </row>
-    <row r="148" ht="56" customHeight="1">
+    <row r="148" ht="43" customHeight="1">
       <c r="A148" s="10" t="n">
         <v>146</v>
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
+          <t>DPR 162/1999, art. 12 c.4–5</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>prove dell'organismo notificato: funzionamento a vuoto e a pieno carico, in mancanza di energia, prova statica a 1,25 volte la portata e controllo che non restino deformazioni</t>
+          <t>comunicazione al Comune e al soggetto delle verifiche periodiche; l'impianto non resta in esercizio senza le comunicazioni aggiornate</t>
         </is>
       </c>
       <c r="E148" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
+          <t>DPR 162/1999, art. 12 c.4–5</t>
         </is>
       </c>
       <c r="F148" s="10" t="inlineStr">
@@ -7613,28 +7613,28 @@
       <c r="M148" s="11" t="n"/>
       <c r="N148" s="11" t="n"/>
     </row>
-    <row r="149" ht="56" customHeight="1">
+    <row r="149" ht="69" customHeight="1">
       <c r="A149" s="10" t="n">
         <v>147</v>
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
+          <t>DPR 162/1999 e s.m.i., art. 14 c.3; schema ICIM SCI 162 rev. 02</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>documentazione tecnica con i risultati dei calcoli di progetto, le relazioni sulle prove e l'elenco delle norme armonizzate applicate, anche in parte</t>
+          <t>verifica straordinaria da uno dei soggetti dell'art. 13 c.1 (la legge); secondo lo schema ICIM è di norma limitata ai controlli sulle modifiche, con la documentazione delle modifiche e dei componenti sostituiti</t>
         </is>
       </c>
       <c r="E149" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
+          <t>DPR 162/1999 e s.m.i., art. 14 c.3; schema ICIM SCI 162 rev. 02</t>
         </is>
       </c>
       <c r="F149" s="10" t="inlineStr">
@@ -7659,33 +7659,33 @@
       <c r="M149" s="11" t="n"/>
       <c r="N149" s="11" t="n"/>
     </row>
-    <row r="150" ht="56" customHeight="1">
+    <row r="150" ht="82" customHeight="1">
       <c r="A150" s="10" t="n">
         <v>148</v>
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
+          <t>Collaudo: adempimenti del DPR 162/1999 (modifica)</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
+          <t>UNI 10411-1:2024 e UNI 10411-11:2024, 25</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>per gli ascensori dichiarati conformi dal 20/01/2027: requisiti dell'All. III del Regolamento macchine (tra cui 1.1.9 e 1.2.1), con una valutazione aggiuntiva per i requisiti nuovi o cambiati</t>
+          <t>documentazione della modifica (App. C della -1, App. A della -11): il proprietario la tiene per chi esegue la verifica straordinaria e la allega alla dichiarazione di conformità (DM 37/2008); manuali della macchina, del quadro e dei nuovi componenti di sicurezza consegnati al proprietario</t>
         </is>
       </c>
       <c r="E150" s="10" t="inlineStr">
         <is>
-          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
+          <t>UNI 10411-1:2024 e UNI 10411-11:2024, 25</t>
         </is>
       </c>
       <c r="F150" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G150" s="10" t="inlineStr">
@@ -7705,7 +7705,7 @@
       <c r="M150" s="11" t="n"/>
       <c r="N150" s="11" t="n"/>
     </row>
-    <row r="151" ht="82" customHeight="1">
+    <row r="151" ht="56" customHeight="1">
       <c r="A151" s="10" t="n">
         <v>149</v>
       </c>
@@ -7716,22 +7716,22 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12.1 e 5.12.2.1</t>
+          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>il metodo del coefficiente di sicurezza delle funi vale solo per pulegge di acciaio o ghisa e funi d'acciaio secondo EN 12385-5; la flessione è semplice se il raggio della gola non supera 0,53 volte il diametro della fune: rilevare il materiale della puleggia e il raggio delle gole</t>
+          <t>prove dell'organismo notificato: funzionamento a vuoto e a pieno carico, in mancanza di energia, prova statica a 1,25 volte la portata e controllo che non restino deformazioni</t>
         </is>
       </c>
       <c r="E151" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.12.1 e 5.12.2.1</t>
+          <t>DPR 162/1999, All. V 3.3 (All. VIII 4)</t>
         </is>
       </c>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G151" s="10" t="inlineStr">
@@ -7751,7 +7751,7 @@
       <c r="M151" s="11" t="n"/>
       <c r="N151" s="11" t="n"/>
     </row>
-    <row r="152" ht="43" customHeight="1">
+    <row r="152" ht="56" customHeight="1">
       <c r="A152" s="10" t="n">
         <v>150</v>
       </c>
@@ -7762,22 +7762,22 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.6.2.2.1.2</t>
+          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>tempo di risposta del limitatore di velocità: i suoi punti d'intervento distano al massimo 250 mm di corsa della fune del limitatore</t>
+          <t>documentazione tecnica con i risultati dei calcoli di progetto, le relazioni sulle prove e l'elenco delle norme armonizzate applicate, anche in parte</t>
         </is>
       </c>
       <c r="E152" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.6.2.2.1.2</t>
+          <t>DPR 162/1999, All. VIII 3 e), g), h)</t>
         </is>
       </c>
       <c r="F152" s="10" t="inlineStr">
         <is>
-          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G152" s="10" t="inlineStr">
@@ -7808,22 +7808,22 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2.1.2.1 e 5.8.2.2.3</t>
+          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>ammortizzatori (dato del fornitore): decelerazione non oltre 1 gn, sopra 2,5 gn al massimo per 0,04 s; per quelli ad accumulo non lineari anche picco non oltre 6 gn e rimbalzo non oltre 1 m/s</t>
+          <t>per gli ascensori dichiarati conformi dal 20/01/2027: requisiti dell'All. III del Regolamento macchine (tra cui 1.1.9 e 1.2.1), con una valutazione aggiuntiva per i requisiti nuovi o cambiati</t>
         </is>
       </c>
       <c r="E153" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2.1.2.1 e 5.8.2.2.3</t>
+          <t>Regolamento (UE) 2023/1230, art. 51 par. 2</t>
         </is>
       </c>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G153" s="10" t="inlineStr">
@@ -7843,7 +7843,7 @@
       <c r="M153" s="11" t="n"/>
       <c r="N153" s="11" t="n"/>
     </row>
-    <row r="154" ht="69" customHeight="1">
+    <row r="154" ht="82" customHeight="1">
       <c r="A154" s="10" t="n">
         <v>152</v>
       </c>
@@ -7854,17 +7854,17 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1</t>
+          <t>UNI EN 81-50:2020, 5.12.1 e 5.12.2.1</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>cartello sopra o accanto allo schermo del contrappeso (5.2.5.5.1) con il gioco massimo ammesso tra contrappeso e ammortizzatore con la cabina al piano più alto, per conservare gli spazi in testata</t>
+          <t>il metodo del coefficiente di sicurezza delle funi vale solo per pulegge di acciaio o ghisa e funi d'acciaio secondo EN 12385-5; la flessione è semplice se il raggio della gola non supera 0,53 volte il diametro della fune: rilevare il materiale della puleggia e il raggio delle gole</t>
         </is>
       </c>
       <c r="E154" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1</t>
+          <t>UNI EN 81-50:2020, 5.12.1 e 5.12.2.1</t>
         </is>
       </c>
       <c r="F154" s="10" t="inlineStr">
@@ -7900,17 +7900,17 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.2.4</t>
+          <t>UNI EN 81-20:2020, 5.6.2.2.1.2</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>fossa più profonda di 2,50 m: porta di accesso; fino a 2,50 m porta di accesso oppure scala dentro il vano (appendice F)</t>
+          <t>tempo di risposta del limitatore di velocità: i suoi punti d'intervento distano al massimo 250 mm di corsa della fune del limitatore</t>
         </is>
       </c>
       <c r="E155" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.2.4</t>
+          <t>UNI EN 81-20:2020, 5.6.2.2.1.2</t>
         </is>
       </c>
       <c r="F155" s="10" t="inlineStr">
@@ -7935,7 +7935,7 @@
       <c r="M155" s="11" t="n"/>
       <c r="N155" s="11" t="n"/>
     </row>
-    <row r="156" ht="43" customHeight="1">
+    <row r="156" ht="56" customHeight="1">
       <c r="A156" s="10" t="n">
         <v>154</v>
       </c>
@@ -7946,17 +7946,17 @@
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.5.1 b)</t>
+          <t>UNI EN 81-20:2020, 5.8.2.1.2.1 e 5.8.2.2.3</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>in fossa un commutatore di ispezione fisso, manovrabile da non oltre 0,30 m da uno spazio di rifugio</t>
+          <t>ammortizzatori (dato del fornitore): decelerazione non oltre 1 gn, sopra 2,5 gn al massimo per 0,04 s; per quelli ad accumulo non lineari anche picco non oltre 6 gn e rimbalzo non oltre 1 m/s</t>
         </is>
       </c>
       <c r="E156" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.5.1 b)</t>
+          <t>UNI EN 81-20:2020, 5.8.2.1.2.1 e 5.8.2.2.3</t>
         </is>
       </c>
       <c r="F156" s="10" t="inlineStr">
@@ -7981,7 +7981,7 @@
       <c r="M156" s="11" t="n"/>
       <c r="N156" s="11" t="n"/>
     </row>
-    <row r="157" ht="43" customHeight="1">
+    <row r="157" ht="69" customHeight="1">
       <c r="A157" s="10" t="n">
         <v>155</v>
       </c>
@@ -7992,17 +7992,17 @@
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>uno spazio di rifugio per ogni persona, tutti dello stesso tipo e senza sovrapposizioni; cartello con il numero di persone ammesse e la postura</t>
+          <t>cartello sopra o accanto allo schermo del contrappeso (5.2.5.5.1) con il gioco massimo ammesso tra contrappeso e ammortizzatore con la cabina al piano più alto, per conservare gli spazi in testata</t>
         </is>
       </c>
       <c r="E157" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1</t>
         </is>
       </c>
       <c r="F157" s="10" t="inlineStr">
@@ -8027,7 +8027,7 @@
       <c r="M157" s="11" t="n"/>
       <c r="N157" s="11" t="n"/>
     </row>
-    <row r="158" ht="69" customHeight="1">
+    <row r="158" ht="43" customHeight="1">
       <c r="A158" s="10" t="n">
         <v>156</v>
       </c>
@@ -8038,17 +8038,17 @@
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.4.1</t>
+          <t>UNI EN 81-20:2020, 5.2.2.4</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>illuminazione del vano: almeno 50 lux a 1 m sopra il tetto della cabina nella sua proiezione e a 1 m sopra il fondo della fossa dove si sta, si lavora o si passa tra le zone di lavoro; almeno 20 lux altrove</t>
+          <t>fossa più profonda di 2,50 m: porta di accesso; fino a 2,50 m porta di accesso oppure scala dentro il vano (appendice F)</t>
         </is>
       </c>
       <c r="E158" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.1.4.1</t>
+          <t>UNI EN 81-20:2020, 5.2.2.4</t>
         </is>
       </c>
       <c r="F158" s="10" t="inlineStr">
@@ -8073,7 +8073,7 @@
       <c r="M158" s="11" t="n"/>
       <c r="N158" s="11" t="n"/>
     </row>
-    <row r="159" ht="56" customHeight="1">
+    <row r="159" ht="43" customHeight="1">
       <c r="A159" s="10" t="n">
         <v>157</v>
       </c>
@@ -8084,17 +8084,17 @@
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.10.1 e 5.4.10.4</t>
+          <t>UNI EN 81-20:2020, 5.2.1.5.1 b)</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>luce in cabina almeno 100 lux sui comandi e a 1 m dal pavimento; luce di emergenza di almeno 5 lux per un'ora presso gli allarmi in cabina e sul tetto e al centro di cabina e tetto, a 1 m</t>
+          <t>in fossa un commutatore di ispezione fisso, manovrabile da non oltre 0,30 m da uno spazio di rifugio</t>
         </is>
       </c>
       <c r="E159" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.10.1 e 5.4.10.4</t>
+          <t>UNI EN 81-20:2020, 5.2.1.5.1 b)</t>
         </is>
       </c>
       <c r="F159" s="10" t="inlineStr">
@@ -8130,17 +8130,17 @@
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.4</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>materiali della cabina secondo EN 13501-1: pavimento Cfl-s2, pareti C-s2,d1, soffitto C-s2,d0</t>
+          <t>uno spazio di rifugio per ogni persona, tutti dello stesso tipo e senza sovrapposizioni; cartello con il numero di persone ammesse e la postura</t>
         </is>
       </c>
       <c r="E160" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.4</t>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1</t>
         </is>
       </c>
       <c r="F160" s="10" t="inlineStr">
@@ -8165,7 +8165,7 @@
       <c r="M160" s="11" t="n"/>
       <c r="N160" s="11" t="n"/>
     </row>
-    <row r="161" ht="95" customHeight="1">
+    <row r="161" ht="69" customHeight="1">
       <c r="A161" s="10" t="n">
         <v>159</v>
       </c>
@@ -8176,17 +8176,17 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.1</t>
+          <t>UNI EN 81-20:2020, 5.2.1.4.1</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>prova del freno: da solo ferma la cabina che scende a velocità nominale con il 125 % della portata; con un gruppo fuori servizio rallenta la cabina con la portata in discesa; con il carico tra (q − 0,1)·Q e (q + 0,1)·Q lo sblocco manuale fa partire la cabina da sola, altrimenti servono i mezzi della 5.9.2.2.2.9 b)</t>
+          <t>illuminazione del vano: almeno 50 lux a 1 m sopra il tetto della cabina nella sua proiezione e a 1 m sopra il fondo della fossa dove si sta, si lavora o si passa tra le zone di lavoro; almeno 20 lux altrove</t>
         </is>
       </c>
       <c r="E161" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.1</t>
+          <t>UNI EN 81-20:2020, 5.2.1.4.1</t>
         </is>
       </c>
       <c r="F161" s="10" t="inlineStr">
@@ -8211,7 +8211,7 @@
       <c r="M161" s="11" t="n"/>
       <c r="N161" s="11" t="n"/>
     </row>
-    <row r="162" ht="69" customHeight="1">
+    <row r="162" ht="56" customHeight="1">
       <c r="A162" s="10" t="n">
         <v>160</v>
       </c>
@@ -8222,17 +8222,17 @@
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.2</t>
+          <t>UNI EN 81-20:2020, 5.4.10.1 e 5.4.10.4</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>impianto elettrico: esame a vista, continuità dei conduttori di protezione, isolamento circuito per circuito con l'elettronica scollegata, efficacia dell'interruzione automatica in caso di guasto</t>
+          <t>luce in cabina almeno 100 lux sui comandi e a 1 m dal pavimento; luce di emergenza di almeno 5 lux per un'ora presso gli allarmi in cabina e sul tetto e al centro di cabina e tetto, a 1 m</t>
         </is>
       </c>
       <c r="E162" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.2</t>
+          <t>UNI EN 81-20:2020, 5.4.10.1 e 5.4.10.4</t>
         </is>
       </c>
       <c r="F162" s="10" t="inlineStr">
@@ -8257,7 +8257,7 @@
       <c r="M162" s="11" t="n"/>
       <c r="N162" s="11" t="n"/>
     </row>
-    <row r="163" ht="82" customHeight="1">
+    <row r="163" ht="43" customHeight="1">
       <c r="A163" s="10" t="n">
         <v>161</v>
       </c>
@@ -8268,17 +8268,17 @@
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.3</t>
+          <t>UNI EN 81-20:2020, 5.4.4</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>aderenza: arresti con la frenatura più severa, in salita a cabina vuota nella parte alta e in discesa con il 125 % della portata verso il basso; con il contrappeso sugli ammortizzatori e la macchina in moto le funi slittano oppure la cabina non sale; bilanciamento come dichiarato</t>
+          <t>materiali della cabina secondo EN 13501-1: pavimento Cfl-s2, pareti C-s2,d1, soffitto C-s2,d0</t>
         </is>
       </c>
       <c r="E163" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.3</t>
+          <t>UNI EN 81-20:2020, 5.4.4</t>
         </is>
       </c>
       <c r="F163" s="10" t="inlineStr">
@@ -8303,7 +8303,7 @@
       <c r="M163" s="11" t="n"/>
       <c r="N163" s="11" t="n"/>
     </row>
-    <row r="164" ht="121" customHeight="1">
+    <row r="164" ht="95" customHeight="1">
       <c r="A164" s="10" t="n">
         <v>162</v>
       </c>
@@ -8314,17 +8314,17 @@
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.4, 6.3.5 e 6.3.7</t>
+          <t>UNI EN 81-20:2020, 6.3.1</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>paracadute di cabina in discesa (istantaneo con la portata a velocità nominale; progressivo, negli impianti a frizione, con il 125 % della portata a velocità nominale o inferiore), del contrappeso a cabina vuota; ammortizzatori ad accumulo compressi dalla cabina con la portata, a dissipazione provati alla velocità nominale (o a quella usata per la corsa ridotta); dopo, nessun danno all'esame a vista</t>
+          <t>prova del freno: da solo ferma la cabina che scende a velocità nominale con il 125 % della portata; con un gruppo fuori servizio rallenta la cabina con la portata in discesa; con il carico tra (q − 0,1)·Q e (q + 0,1)·Q lo sblocco manuale fa partire la cabina da sola, altrimenti servono i mezzi della 5.9.2.2.2.9 b)</t>
         </is>
       </c>
       <c r="E164" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.4, 6.3.5 e 6.3.7</t>
+          <t>UNI EN 81-20:2020, 6.3.1</t>
         </is>
       </c>
       <c r="F164" s="10" t="inlineStr">
@@ -8349,7 +8349,7 @@
       <c r="M164" s="11" t="n"/>
       <c r="N164" s="11" t="n"/>
     </row>
-    <row r="165" ht="108" customHeight="1">
+    <row r="165" ht="69" customHeight="1">
       <c r="A165" s="10" t="n">
         <v>163</v>
       </c>
@@ -8360,17 +8360,17 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.11, 6.3.12 e 6.3.13</t>
+          <t>UNI EN 81-20:2020, 6.3.2</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>ACOP: cabina vuota in salita a velocità non inferiore alla nominale, frenata solo dal dispositivo; livellamento verificato a ogni fermata e, al piano più sfavorevole, durante carico e scarico; UCM: cabina vuota verso l'alto e piena verso il basso a una velocità prestabilita, con il movimento entro il limite della 5.6.7.5 e l'autosorveglianza dove richiesta</t>
+          <t>impianto elettrico: esame a vista, continuità dei conduttori di protezione, isolamento circuito per circuito con l'elettronica scollegata, efficacia dell'interruzione automatica in caso di guasto</t>
         </is>
       </c>
       <c r="E165" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.11, 6.3.12 e 6.3.13</t>
+          <t>UNI EN 81-20:2020, 6.3.2</t>
         </is>
       </c>
       <c r="F165" s="10" t="inlineStr">
@@ -8395,7 +8395,7 @@
       <c r="M165" s="11" t="n"/>
       <c r="N165" s="11" t="n"/>
     </row>
-    <row r="166" ht="43" customHeight="1">
+    <row r="166" ht="82" customHeight="1">
       <c r="A166" s="10" t="n">
         <v>164</v>
       </c>
@@ -8406,17 +8406,17 @@
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.14</t>
+          <t>UNI EN 81-20:2020, 6.3.3</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>cabina fuori dalla zona di sbloccaggio e porta di piano tenuta aperta di 100 mm: lasciata, la porta si richiude e si blocca</t>
+          <t>aderenza: arresti con la frenatura più severa, in salita a cabina vuota nella parte alta e in discesa con il 125 % della portata verso il basso; con il contrappeso sugli ammortizzatori e la macchina in moto le funi slittano oppure la cabina non sale; bilanciamento come dichiarato</t>
         </is>
       </c>
       <c r="E166" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 6.3.14</t>
+          <t>UNI EN 81-20:2020, 6.3.3</t>
         </is>
       </c>
       <c r="F166" s="10" t="inlineStr">
@@ -8441,7 +8441,7 @@
       <c r="M166" s="11" t="n"/>
       <c r="N166" s="11" t="n"/>
     </row>
-    <row r="167" ht="43" customHeight="1">
+    <row r="167" ht="121" customHeight="1">
       <c r="A167" s="10" t="n">
         <v>165</v>
       </c>
@@ -8452,17 +8452,17 @@
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, C.2 e 7.3.2</t>
+          <t>UNI EN 81-20:2020, 6.3.4, 6.3.5 e 6.3.7</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>la sostituzione della macchina o della puleggia di trazione è una trasformazione importante: si annota nel registro dell'impianto, da aggiornare</t>
+          <t>paracadute di cabina in discesa (istantaneo con la portata a velocità nominale; progressivo, negli impianti a frizione, con il 125 % della portata a velocità nominale o inferiore), del contrappeso a cabina vuota; ammortizzatori ad accumulo compressi dalla cabina con la portata, a dissipazione provati alla velocità nominale (o a quella usata per la corsa ridotta); dopo, nessun danno all'esame a vista</t>
         </is>
       </c>
       <c r="E167" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, C.2 e 7.3.2</t>
+          <t>UNI EN 81-20:2020, 6.3.4, 6.3.5 e 6.3.7</t>
         </is>
       </c>
       <c r="F167" s="10" t="inlineStr">
@@ -8498,17 +8498,17 @@
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.3.5.3.2, 5.3.5.3.4, 5.3.6.2.2.1 b) e 5.3.15.2 b)</t>
+          <t>UNI EN 81-20:2020, 6.3.11, 6.3.12 e 6.3.13</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>pannelli delle porte con i dispositivi di ritenuta e le prove a pendolo (morbido da 800 mm; rigido da 500 mm sui pannelli in vetro); sulle porte automatiche un dispositivo di protezione che copre da 25 a 1600 mm sopra la soglia e rileva ostacoli di 50 mm; fuori dalla zona di sbloccaggio la porta di cabina, spinta con 1000 N, non si apre più di 50 mm</t>
+          <t>ACOP: cabina vuota in salita a velocità non inferiore alla nominale, frenata solo dal dispositivo; livellamento verificato a ogni fermata e, al piano più sfavorevole, durante carico e scarico; UCM: cabina vuota verso l'alto e piena verso il basso a una velocità prestabilita, con il movimento entro il limite della 5.6.7.5 e l'autosorveglianza dove richiesta</t>
         </is>
       </c>
       <c r="E168" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.3.5.3.2, 5.3.5.3.4, 5.3.6.2.2.1 b) e 5.3.15.2 b)</t>
+          <t>UNI EN 81-20:2020, 6.3.11, 6.3.12 e 6.3.13</t>
         </is>
       </c>
       <c r="F168" s="10" t="inlineStr">
@@ -8533,28 +8533,28 @@
       <c r="M168" s="11" t="n"/>
       <c r="N168" s="11" t="n"/>
     </row>
-    <row r="169" ht="56" customHeight="1">
+    <row r="169" ht="43" customHeight="1">
       <c r="A169" s="10" t="n">
         <v>167</v>
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-1:2024</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, scopo</t>
+          <t>UNI EN 81-20:2020, 6.3.14</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>impianti elettrici a frizione fuori dalla 95/16/CE e dalla 2014/33/UE; esclude le modifiche che cambiano le misure antincendio (per queste, a nostro giudizio, il DM 15/09/2005 o il Codice V.3)</t>
+          <t>cabina fuori dalla zona di sbloccaggio e porta di piano tenuta aperta di 100 mm: lasciata, la porta si richiude e si blocca</t>
         </is>
       </c>
       <c r="E169" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, scopo</t>
+          <t>UNI EN 81-20:2020, 6.3.14</t>
         </is>
       </c>
       <c r="F169" s="10" t="inlineStr">
@@ -8579,28 +8579,28 @@
       <c r="M169" s="11" t="n"/>
       <c r="N169" s="11" t="n"/>
     </row>
-    <row r="170" ht="121" customHeight="1">
+    <row r="170" ht="43" customHeight="1">
       <c r="A170" s="10" t="n">
         <v>168</v>
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-1:2024</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, 14.4 a)–g)</t>
+          <t>UNI EN 81-20:2020, C.2 e 7.3.2</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>con la macchina nuova: temporizzatore del motore (EN 81-20 5.9.2.7); arresto in salita prima della velocità d'intervento del limitatore; protezioni ACOP e UCM esistenti che continuano a funzionare; dispositivo d'arresto presso la macchina (5.12.1.11.1 e)); pulegge nel locale secondo la 5.5.7; senza UCM e con la regolazione di velocità, macchinario senza alimentazione se il freno non si apre, con ripristino solo manuale</t>
+          <t>la sostituzione della macchina o della puleggia di trazione è una trasformazione importante: si annota nel registro dell'impianto, da aggiornare</t>
         </is>
       </c>
       <c r="E170" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, 14.4 a)–g)</t>
+          <t>UNI EN 81-20:2020, C.2 e 7.3.2</t>
         </is>
       </c>
       <c r="F170" s="10" t="inlineStr">
@@ -8625,28 +8625,28 @@
       <c r="M170" s="11" t="n"/>
       <c r="N170" s="11" t="n"/>
     </row>
-    <row r="171" ht="56" customHeight="1">
+    <row r="171" ht="108" customHeight="1">
       <c r="A171" s="10" t="n">
         <v>169</v>
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-11:2024</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, scopo</t>
+          <t>UNI EN 81-20:2020, 5.3.5.3.2, 5.3.5.3.4, 5.3.6.2.2.1 b) e 5.3.15.2 b)</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>impianti elettrici a frizione marcati CE secondo la Direttiva; esclude le modifiche che cambiano le misure antincendio (per queste, a nostro giudizio, il DM 15/09/2005 o il Codice V.3)</t>
+          <t>pannelli delle porte con i dispositivi di ritenuta e le prove a pendolo (morbido da 800 mm; rigido da 500 mm sui pannelli in vetro); sulle porte automatiche un dispositivo di protezione che copre da 25 a 1600 mm sopra la soglia e rileva ostacoli di 50 mm; fuori dalla zona di sbloccaggio la porta di cabina, spinta con 1000 N, non si apre più di 50 mm</t>
         </is>
       </c>
       <c r="E171" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, scopo</t>
+          <t>UNI EN 81-20:2020, 5.3.5.3.2, 5.3.5.3.4, 5.3.6.2.2.1 b) e 5.3.15.2 b)</t>
         </is>
       </c>
       <c r="F171" s="10" t="inlineStr">
@@ -8671,28 +8671,28 @@
       <c r="M171" s="11" t="n"/>
       <c r="N171" s="11" t="n"/>
     </row>
-    <row r="172" ht="108" customHeight="1">
+    <row r="172" ht="121" customHeight="1">
       <c r="A172" s="10" t="n">
         <v>170</v>
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-11:2024</t>
+          <t>Collaudo: UNI EN 81-20:2020 e UNI EN 81-50:2020</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, 14.3 a) e App. A (14); UNI EN 81-20:2020, 5.6.6.2 e 5.6.7.3</t>
+          <t>UNI EN 81-20:2020, 5.3.6.2.2.1 a)–d)</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>cambiando la macchina: le protezioni UCM esistenti devono continuare a funzionare (14.3 a)); per l'ACOP esistente l'App. A (14) chiede una relazione sulla compatibilità della nuova macchina, oppure nuovi dispositivi con certificato di esame di tipo e dichiarazione di conformità; il freno della macchina vale come organo d'arresto solo se ridondante e autocontrollato</t>
+          <t>porte scorrevoli automatiche: energia cinetica in chiusura non oltre 10 J alla velocità media (corsa senza 25 mm per estremità sulle porte centrali, 50 mm sulle laterali); con il dispositivo di protezione guasto o escluso e l'impianto in servizio non oltre 4 J, con un segnale acustico a ogni chiusura; forza per trattenere la porta in chiusura non oltre 150 N fuori dal primo terzo della corsa, e la porta trattenuta si riapre</t>
         </is>
       </c>
       <c r="E172" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, 14.3 a) e App. A (14); UNI EN 81-20:2020, 5.6.6.2 e 5.6.7.3</t>
+          <t>UNI EN 81-20:2020, 5.3.6.2.2.1 a)–d)</t>
         </is>
       </c>
       <c r="F172" s="10" t="inlineStr">
@@ -8723,22 +8723,22 @@
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI 10411-11:2024</t>
+          <t>Collaudo: UNI 10411-1:2024</t>
         </is>
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, 14.3 b)</t>
+          <t>UNI 10411-1:2024, scopo</t>
         </is>
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>senza UCM conforme alla 5.6.7 e con il rallentamento controllato: macchinario senza alimentazione se il freno non si apre, al più tardi all'arrivo al piano, con ripristino solo manuale</t>
+          <t>impianti elettrici a frizione fuori dalla 95/16/CE e dalla 2014/33/UE; esclude le modifiche che cambiano le misure antincendio (per queste, a nostro giudizio, il DM 15/09/2005 o il Codice V.3)</t>
         </is>
       </c>
       <c r="E173" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-11:2024, 14.3 b)</t>
+          <t>UNI 10411-1:2024, scopo</t>
         </is>
       </c>
       <c r="F173" s="10" t="inlineStr">
@@ -8763,28 +8763,28 @@
       <c r="M173" s="11" t="n"/>
       <c r="N173" s="11" t="n"/>
     </row>
-    <row r="174" ht="56" customHeight="1">
+    <row r="174" ht="121" customHeight="1">
       <c r="A174" s="10" t="n">
         <v>172</v>
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
+          <t>Collaudo: UNI 10411-1:2024</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-21:2022, 1</t>
+          <t>UNI 10411-1:2024, 14.4 a)–g)</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>ascensori nuovi in un edificio esistente, dove l'edificio non permette di rispettare tutta la UNI EN 81-20:2020; esclusi gli impianti montati prima della sua pubblicazione</t>
+          <t>con la macchina nuova: temporizzatore del motore (EN 81-20 5.9.2.7); arresto in salita prima della velocità d'intervento del limitatore; protezioni ACOP e UCM esistenti che continuano a funzionare; dispositivo d'arresto presso la macchina (5.12.1.11.1 e)); pulegge nel locale secondo la 5.5.7; senza UCM e con la regolazione di velocità, macchinario senza alimentazione se il freno non si apre, con ripristino solo manuale</t>
         </is>
       </c>
       <c r="E174" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-21:2022, 1</t>
+          <t>UNI 10411-1:2024, 14.4 a)–g)</t>
         </is>
       </c>
       <c r="F174" s="10" t="inlineStr">
@@ -8809,28 +8809,28 @@
       <c r="M174" s="11" t="n"/>
       <c r="N174" s="11" t="n"/>
     </row>
-    <row r="175" ht="95" customHeight="1">
+    <row r="175" ht="56" customHeight="1">
       <c r="A175" s="10" t="n">
         <v>173</v>
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
+          <t>Collaudo: UNI 10411-11:2024</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-21:2022, 6.2 e 7.1</t>
+          <t>UNI 10411-11:2024, scopo</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>oltre alle prove della EN 81-20 6.3: arresti mobili e sistema di arresto preattivato provati in moto a velocità nominale (in testata a cabina vuota, in fossa con il carico nominale), corsa dei loro ammortizzatori e distanza di frenatura; nelle istruzioni: quanto frena il sistema, col valore nominale e i due limiti</t>
+          <t>impianti elettrici a frizione marcati CE secondo la Direttiva; esclude le modifiche che cambiano le misure antincendio (per queste, a nostro giudizio, il DM 15/09/2005 o il Codice V.3)</t>
         </is>
       </c>
       <c r="E175" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-21:2022, 6.2 e 7.1</t>
+          <t>UNI 10411-11:2024, scopo</t>
         </is>
       </c>
       <c r="F175" s="10" t="inlineStr">
@@ -8855,33 +8855,33 @@
       <c r="M175" s="11" t="n"/>
       <c r="N175" s="11" t="n"/>
     </row>
-    <row r="176" ht="82" customHeight="1">
+    <row r="176" ht="108" customHeight="1">
       <c r="A176" s="10" t="n">
         <v>174</v>
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
+          <t>Collaudo: UNI 10411-11:2024</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
+          <t>UNI 10411-11:2024, 14.3 a) e App. A (14); UNI EN 81-20:2020, 5.6.6.2 e 5.6.7.3</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>spazi di rifugio ridotti solo con l'accordo preventivo: in edificio esistente PEC al Ministero con la certificazione dell'organismo prima dell'installazione (Procedura 2: dichiarazione dei punti della EN 81-21 applicati); la EN 81-21 da sola non giustifica la deroga</t>
+          <t>cambiando la macchina: le protezioni UCM esistenti devono continuare a funzionare (14.3 a)); per l'ACOP esistente l'App. A (14) chiede una relazione sulla compatibilità della nuova macchina, oppure nuovi dispositivi con certificato di esame di tipo e dichiarazione di conformità; il freno della macchina vale come organo d'arresto solo se ridondante e autocontrollato</t>
         </is>
       </c>
       <c r="E176" s="10" t="inlineStr">
         <is>
-          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
+          <t>UNI 10411-11:2024, 14.3 a) e App. A (14); UNI EN 81-20:2020, 5.6.6.2 e 5.6.7.3</t>
         </is>
       </c>
       <c r="F176" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G176" s="10" t="inlineStr">
@@ -8901,28 +8901,28 @@
       <c r="M176" s="11" t="n"/>
       <c r="N176" s="11" t="n"/>
     </row>
-    <row r="177" ht="82" customHeight="1">
+    <row r="177" ht="56" customHeight="1">
       <c r="A177" s="10" t="n">
         <v>175</v>
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
+          <t>Collaudo: UNI 10411-11:2024</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.12.3.1; UNI EN 81-28:2004, 4.1.3, 4.2.1 e 7</t>
+          <t>UNI 10411-11:2024, 14.3 b)</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>la EN 81-20 richiama con data la EN 81-28:2003 (UNI EN 81-28:2004): prova automatica del collegamento almeno ogni 3 giorni; con alimentazione a batteria, avviso al servizio di soccorso quando l'autonomia residua scende sotto 1 h; pulsante d'allarme giallo con il simbolo della campana</t>
+          <t>senza UCM conforme alla 5.6.7 e con il rallentamento controllato: macchinario senza alimentazione se il freno non si apre, al più tardi all'arrivo al piano, con ripristino solo manuale</t>
         </is>
       </c>
       <c r="E177" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.12.3.1; UNI EN 81-28:2004, 4.1.3, 4.2.1 e 7</t>
+          <t>UNI 10411-11:2024, 14.3 b)</t>
         </is>
       </c>
       <c r="F177" s="10" t="inlineStr">
@@ -8953,32 +8953,32 @@
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
+          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-28:2022</t>
+          <t>UNI EN 81-21:2022, 1</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>requisiti dell'edizione citata in GUUE da verificare sul testo; nelle modifiche la UNI 10411-1/-11:2024 (punto 23) ammette l'allarme nuovo secondo la EN 81-20 5.12.3.1 o la UNI EN 81-28:2022</t>
+          <t>ascensori nuovi in un edificio esistente, dove l'edificio non permette di rispettare tutta la UNI EN 81-20:2020; esclusi gli impianti montati prima della sua pubblicazione</t>
         </is>
       </c>
       <c r="E178" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-28:2022</t>
+          <t>UNI EN 81-21:2022, 1</t>
         </is>
       </c>
       <c r="F178" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G178" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H178" s="10" t="inlineStr">
@@ -8999,27 +8999,27 @@
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-58:2022 (resistenza al fuoco delle porte di piano)</t>
+          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
+          <t>UNI EN 81-21:2022, 6.2 e 7.1</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>porte di piano resistenti al fuoco (classi E, EI, EW) provate secondo la norma, quando fanno parte della compartimentazione del vano; sostituirle con modelli diversi è una modifica sostanziale ai fini antincendio (la UNI EN 81-20:2020, 5.3.5.2, richiama con data la EN 81-58:2003: quale certificato accettare lo decide l'organismo)</t>
+          <t>oltre alle prove della EN 81-20 6.3: arresti mobili e sistema di arresto preattivato provati in moto a velocità nominale (in testata a cabina vuota, in fossa con il carico nominale), corsa dei loro ammortizzatori e distanza di frenatura; nelle istruzioni: quanto frena il sistema, col valore nominale e i due limiti</t>
         </is>
       </c>
       <c r="E179" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
+          <t>UNI EN 81-21:2022, 6.2 e 7.1</t>
         </is>
       </c>
       <c r="F179" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G179" s="10" t="inlineStr">
@@ -9039,28 +9039,28 @@
       <c r="M179" s="11" t="n"/>
       <c r="N179" s="11" t="n"/>
     </row>
-    <row r="180" ht="95" customHeight="1">
+    <row r="180" ht="82" customHeight="1">
       <c r="A180" s="10" t="n">
         <v>178</v>
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+          <t>Collaudo: UNI EN 81-21:2022 (ascensori nuovi in edifici esistenti)</t>
         </is>
       </c>
       <c r="C180" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.1</t>
+          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
         </is>
       </c>
       <c r="D180" s="10" t="inlineStr">
         <is>
-          <t>tipi di cabina (larghezza × profondità, luce della porta): 1) 1000 × 1300, 800; 2) 1100 × 1400, 900; 3) 1100 × 2100, 900; 4) 1600 × 1400 o 1400 × 1600, 900; 5) 2000 × 1400 o 1400 × 2000, 1100 mm (la UNI EN 81-70:2005 letta, Prospetto 1, ha tre tipi: 1000 × 1250, 1100 × 1400 e 2000 × 1400 mm)</t>
+          <t>spazi di rifugio ridotti solo con l'accordo preventivo: in edificio esistente PEC al Ministero con la certificazione dell'organismo prima dell'installazione (Procedura 2: dichiarazione dei punti della EN 81-21 applicati); la EN 81-21 da sola non giustifica la deroga</t>
         </is>
       </c>
       <c r="E180" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.1</t>
+          <t>DPR 162/1999, art. 17-bis; DM 19/03/2015; linee guida MIMIT 2022</t>
         </is>
       </c>
       <c r="F180" s="10" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="G180" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H180" s="10" t="inlineStr">
@@ -9085,38 +9085,38 @@
       <c r="M180" s="11" t="n"/>
       <c r="N180" s="11" t="n"/>
     </row>
-    <row r="181" ht="95" customHeight="1">
+    <row r="181" ht="82" customHeight="1">
       <c r="A181" s="10" t="n">
         <v>179</v>
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
+          <t>UNI EN 81-20:2020, 5.12.3.1; UNI EN 81-28:2004, 4.1.3, 4.2.1 e 7</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>specchio nei tipi 1–3; finiture che riducono le misure nominali al massimo di 15 mm per parete; segnale acustico regolabile 35–65 dB(A), fino a 80 in ambienti rumorosi; contrasto di Michelson con la A1:2022 (nella UNI EN 81-70:2005 letta: specchio nei tipi 1 e 2, 15 mm, 35–65 dB(A); non ci sono gli 80 dB(A) né il contrasto di Michelson)</t>
+          <t>la EN 81-20 richiama con data la EN 81-28:2003 (UNI EN 81-28:2004): prova automatica del collegamento almeno ogni 3 giorni; con alimentazione a batteria, avviso al servizio di soccorso quando l'autonomia residua scende sotto 1 h; pulsante d'allarme giallo con il simbolo della campana</t>
         </is>
       </c>
       <c r="E181" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
+          <t>UNI EN 81-20:2020, 5.12.3.1; UNI EN 81-28:2004, 4.1.3, 4.2.1 e 7</t>
         </is>
       </c>
       <c r="F181" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G181" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H181" s="10" t="inlineStr">
@@ -9131,28 +9131,28 @@
       <c r="M181" s="11" t="n"/>
       <c r="N181" s="11" t="n"/>
     </row>
-    <row r="182" ht="43" customHeight="1">
+    <row r="182" ht="56" customHeight="1">
       <c r="A182" s="10" t="n">
         <v>180</v>
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
+          <t>Collaudo: UNI EN 81-28:2022 (teleallarme)</t>
         </is>
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, scopo</t>
+          <t>UNI EN 81-28:2022</t>
         </is>
       </c>
       <c r="D182" s="10" t="inlineStr">
         <is>
-          <t>si usa con la UNI EN 81-20:2020; per gli impianti esistenti vale la UNI EN 81-82</t>
+          <t>requisiti dell'edizione citata in GUUE da verificare sul testo; nelle modifiche la UNI 10411-1/-11:2024 (punto 23) ammette l'allarme nuovo secondo la EN 81-20 5.12.3.1 o la UNI EN 81-28:2022</t>
         </is>
       </c>
       <c r="E182" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-70:2022, scopo</t>
+          <t>UNI EN 81-28:2022</t>
         </is>
       </c>
       <c r="F182" s="10" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="G182" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H182" s="10" t="inlineStr">
@@ -9177,28 +9177,28 @@
       <c r="M182" s="11" t="n"/>
       <c r="N182" s="11" t="n"/>
     </row>
-    <row r="183" ht="43" customHeight="1">
+    <row r="183" ht="95" customHeight="1">
       <c r="A183" s="10" t="n">
         <v>181</v>
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-71 (ascensori antivandalo)</t>
+          <t>Collaudo: UNI EN 81-58:2022 (resistenza al fuoco delle porte di piano)</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-71</t>
+          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>categoria antivandalo da concordare con il committente; per la presunzione di conformità vale l'edizione 2005+A1:2006</t>
+          <t>porte di piano resistenti al fuoco (classi E, EI, EW) provate secondo la norma, quando fanno parte della compartimentazione del vano; sostituirle con modelli diversi è una modifica sostanziale ai fini antincendio (la UNI EN 81-20:2020, 5.3.5.2, richiama con data la EN 81-58:2003: quale certificato accettare lo decide l'organismo)</t>
         </is>
       </c>
       <c r="E183" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-71</t>
+          <t>UNI EN 81-58:2022; DM 15/09/2005, 3.2–3.3 e art. 1 c.2 lett. c)</t>
         </is>
       </c>
       <c r="F183" s="10" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="G183" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H183" s="10" t="inlineStr">
@@ -9223,28 +9223,28 @@
       <c r="M183" s="11" t="n"/>
       <c r="N183" s="11" t="n"/>
     </row>
-    <row r="184" ht="108" customHeight="1">
+    <row r="184" ht="95" customHeight="1">
       <c r="A184" s="10" t="n">
         <v>182</v>
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
         </is>
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 7 (valori); Codice V.3.3.4</t>
+          <t>UNI EN 81-70:2022, 5.3.1</t>
         </is>
       </c>
       <c r="D184" s="10" t="inlineStr">
         <is>
-          <t>ascensore antincendio: tutti i piani serviti; vano e porte di piano almeno REI 60; cabina interna almeno 1,10 × 2,10 m con accesso sul lato corto; botola sul tetto almeno 0,50 × 0,70 m; area dedicata almeno 5 m² a ogni piano; luce d'emergenza almeno 5 lux con 1 h di autonomia; IPX3 dove arriva l'acqua; linea dedicata con alimentazione di sicurezza</t>
+          <t>tipi di cabina (larghezza × profondità, luce della porta): 1) 1000 × 1300, 800; 2) 1100 × 1400, 900; 3) 1100 × 2100, 900; 4) 1600 × 1400 o 1400 × 1600, 900; 5) 2000 × 1400 o 1400 × 2000, 1100 mm (la UNI EN 81-70:2005 letta, Prospetto 1, ha tre tipi: 1000 × 1250, 1100 × 1400 e 2000 × 1400 mm)</t>
         </is>
       </c>
       <c r="E184" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 7 (valori); Codice V.3.3.4</t>
+          <t>UNI EN 81-70:2022, 5.3.1</t>
         </is>
       </c>
       <c r="F184" s="10" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="G184" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H184" s="10" t="inlineStr">
@@ -9269,28 +9269,28 @@
       <c r="M184" s="11" t="n"/>
       <c r="N184" s="11" t="n"/>
     </row>
-    <row r="185" ht="56" customHeight="1">
+    <row r="185" ht="95" customHeight="1">
       <c r="A185" s="10" t="n">
         <v>183</v>
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
         </is>
       </c>
       <c r="C185" s="10" t="inlineStr">
         <is>
-          <t>Codice S.10, Tab. S.10-2</t>
+          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
         </is>
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>alimentazione di sicurezza dell'ascensore antincendio: interruzione al massimo 15 s, autonomia oltre 30 min</t>
+          <t>specchio nei tipi 1–3; finiture che riducono le misure nominali al massimo di 15 mm per parete; segnale acustico regolabile 35–65 dB(A), fino a 80 in ambienti rumorosi; contrasto di Michelson con la A1:2022 (nella UNI EN 81-70:2005 letta: specchio nei tipi 1 e 2, 15 mm, 35–65 dB(A); non ci sono gli 80 dB(A) né il contrasto di Michelson)</t>
         </is>
       </c>
       <c r="E185" s="10" t="inlineStr">
         <is>
-          <t>Codice S.10, Tab. S.10-2</t>
+          <t>UNI EN 81-70:2022, 5.3.2 e 5.4</t>
         </is>
       </c>
       <c r="F185" s="10" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="G185" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H185" s="10" t="inlineStr">
@@ -9315,28 +9315,28 @@
       <c r="M185" s="11" t="n"/>
       <c r="N185" s="11" t="n"/>
     </row>
-    <row r="186" ht="56" customHeight="1">
+    <row r="186" ht="43" customHeight="1">
       <c r="A186" s="10" t="n">
         <v>184</v>
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
+          <t>Collaudo: UNI EN 81-70:2022 (accessibilità)</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-72:2020</t>
+          <t>UNI EN 81-70:2022, scopo</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>requisiti propri della norma (cabina, tempi, protezione dall'acqua) da verificare sul testo</t>
+          <t>si usa con la UNI EN 81-20:2020; per gli impianti esistenti vale la UNI EN 81-82</t>
         </is>
       </c>
       <c r="E186" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-72:2020</t>
+          <t>UNI EN 81-70:2022, scopo</t>
         </is>
       </c>
       <c r="F186" s="10" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="G186" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H186" s="10" t="inlineStr">
@@ -9361,28 +9361,28 @@
       <c r="M186" s="11" t="n"/>
       <c r="N186" s="11" t="n"/>
     </row>
-    <row r="187" ht="69" customHeight="1">
+    <row r="187" ht="43" customHeight="1">
       <c r="A187" s="10" t="n">
         <v>185</v>
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
+          <t>Collaudo: UNI EN 81-71 (ascensori antivandalo)</t>
         </is>
       </c>
       <c r="C187" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
+          <t>UNI EN 81-71</t>
         </is>
       </c>
       <c r="D187" s="10" t="inlineStr">
         <is>
-          <t>quando la compartimentazione lo richiede, su comando della rivelazione incendio la cabina va al piano prestabilito e lascia uscire i passeggeri; con il Codice l'ascensore «dovrebbe» essere conforme alla UNI EN 81-73</t>
+          <t>categoria antivandalo da concordare con il committente; per la presunzione di conformità vale l'edizione 2005+A1:2006</t>
         </is>
       </c>
       <c r="E187" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
+          <t>UNI EN 81-71</t>
         </is>
       </c>
       <c r="F187" s="10" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="G187" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H187" s="10" t="inlineStr">
@@ -9407,28 +9407,28 @@
       <c r="M187" s="11" t="n"/>
       <c r="N187" s="11" t="n"/>
     </row>
-    <row r="188" ht="56" customHeight="1">
+    <row r="188" ht="108" customHeight="1">
       <c r="A188" s="10" t="n">
         <v>186</v>
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-73:2020</t>
+          <t>DM 15/09/2005, punto 7 (valori); Codice V.3.3.4</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>segnali e comportamento della manovra da verificare sul testo; la norma serve anche da base per migliorare gli esistenti (così la UNI EN 81-73:2005 letta, punto 1)</t>
+          <t>ascensore antincendio: tutti i piani serviti; vano e porte di piano almeno REI 60; cabina interna almeno 1,10 × 2,10 m con accesso sul lato corto; botola sul tetto almeno 0,50 × 0,70 m; area dedicata almeno 5 m² a ogni piano; luce d'emergenza almeno 5 lux con 1 h di autonomia; IPX3 dove arriva l'acqua; linea dedicata con alimentazione di sicurezza</t>
         </is>
       </c>
       <c r="E188" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-73:2020</t>
+          <t>DM 15/09/2005, punto 7 (valori); Codice V.3.3.4</t>
         </is>
       </c>
       <c r="F188" s="10" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="G188" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H188" s="10" t="inlineStr">
@@ -9453,28 +9453,28 @@
       <c r="M188" s="11" t="n"/>
       <c r="N188" s="11" t="n"/>
     </row>
-    <row r="189" ht="69" customHeight="1">
+    <row r="189" ht="56" customHeight="1">
       <c r="A189" s="10" t="n">
         <v>187</v>
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-76:2025 (evacuazione delle persone con disabilità)</t>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-76:2025</t>
+          <t>Codice S.10, Tab. S.10-2</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>evacuazione delle persone con disabilità con l'ascensore: requisiti aggiuntivi alla EN 81-20 (manovra, alimentazione) da verificare sul testo</t>
+          <t>alimentazione di sicurezza dell'ascensore antincendio: interruzione al massimo 15 s, autonomia oltre 30 min</t>
         </is>
       </c>
       <c r="E189" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-76:2025</t>
+          <t>Codice S.10, Tab. S.10-2</t>
         </is>
       </c>
       <c r="F189" s="10" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="G189" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H189" s="10" t="inlineStr">
@@ -9505,22 +9505,22 @@
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-72:2020 (ascensori antincendio)</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 1</t>
+          <t>UNI EN 81-72:2020</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>con accelerazione di progetto a_d fino a 1 m/s² nessuna prescrizione specifica; a_d e la posizione dei rilevatori si concordano con il progettista dell'edificio</t>
+          <t>requisiti propri della norma (cabina, tempi, protezione dall'acqua) da verificare sul testo</t>
         </is>
       </c>
       <c r="E190" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 1</t>
+          <t>UNI EN 81-72:2020</t>
         </is>
       </c>
       <c r="F190" s="10" t="inlineStr">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="G190" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H190" s="10" t="inlineStr">
@@ -9545,28 +9545,28 @@
       <c r="M190" s="11" t="n"/>
       <c r="N190" s="11" t="n"/>
     </row>
-    <row r="191" ht="95" customHeight="1">
+    <row r="191" ht="69" customHeight="1">
       <c r="A191" s="10" t="n">
         <v>189</v>
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>oltre 1 m/s²: massa della cabina nei calcoli (5.4.1), ritegni della cabina (5.4.2) e del contrappeso (5.5), protezione delle pulegge (5.6.1), tensioni e frecce delle guide (5.8.2, All. D), rilevazione e modo sismico (5.10.3, 5.10.4); soglie delle categorie dell'All. A da verificare sul testo</t>
+          <t>quando la compartimentazione lo richiede, su comando della rivelazione incendio la cabina va al piano prestabilito e lascia uscire i passeggeri; con il Codice l'ascensore «dovrebbe» essere conforme alla UNI EN 81-73</t>
         </is>
       </c>
       <c r="E191" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1</t>
         </is>
       </c>
       <c r="F191" s="10" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="G191" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H191" s="10" t="inlineStr">
@@ -9591,28 +9591,28 @@
       <c r="M191" s="11" t="n"/>
       <c r="N191" s="11" t="n"/>
     </row>
-    <row r="192" ht="43" customHeight="1">
+    <row r="192" ht="56" customHeight="1">
       <c r="A192" s="10" t="n">
         <v>190</v>
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
+          <t>Collaudo: UNI EN 81-73:2020 (comportamento in caso d'incendio)</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 0.3</t>
+          <t>UNI EN 81-73:2020</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>non si applica agli impianti installati prima della sua pubblicazione</t>
+          <t>segnali e comportamento della manovra da verificare sul testo; la norma serve anche da base per migliorare gli esistenti (così la UNI EN 81-73:2005 letta, punto 1)</t>
         </is>
       </c>
       <c r="E192" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-77:2022, 0.3</t>
+          <t>UNI EN 81-73:2020</t>
         </is>
       </c>
       <c r="F192" s="10" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="G192" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H192" s="10" t="inlineStr">
@@ -9643,32 +9643,32 @@
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-76:2025 (evacuazione delle persone con disabilità)</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-80:2004 e 2009, 1 e appendice A</t>
+          <t>UNI EN 81-76:2025</t>
         </is>
       </c>
       <c r="D193" s="10" t="inlineStr">
         <is>
-          <t>analisi dei rischi dell'impianto esistente e piano di miglioramento per priorità; quali misure e in che tempi lo decide la legislazione nazionale, non la norma</t>
+          <t>evacuazione delle persone con disabilità con l'ascensore: requisiti aggiuntivi alla EN 81-20 (manovra, alimentazione) da verificare sul testo</t>
         </is>
       </c>
       <c r="E193" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-80:2004 e 2009, 1 e appendice A</t>
+          <t>UNI EN 81-76:2025</t>
         </is>
       </c>
       <c r="F193" s="10" t="inlineStr">
         <is>
-          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G193" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H193" s="10" t="inlineStr">
@@ -9683,28 +9683,28 @@
       <c r="M193" s="11" t="n"/>
       <c r="N193" s="11" t="n"/>
     </row>
-    <row r="194" ht="69" customHeight="1">
+    <row r="194" ht="56" customHeight="1">
       <c r="A194" s="10" t="n">
         <v>192</v>
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
         </is>
       </c>
       <c r="C194" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-80:2019</t>
+          <t>UNI EN 81-77:2022, 1</t>
         </is>
       </c>
       <c r="D194" s="10" t="inlineStr">
         <is>
-          <t>la stessa analisi nell'edizione in vigore, con una struttura diversa: da verificare sul testo</t>
+          <t>con accelerazione di progetto a_d fino a 1 m/s² nessuna prescrizione specifica; a_d e la posizione dei rilevatori si concordano con il progettista dell'edificio</t>
         </is>
       </c>
       <c r="E194" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-80:2019</t>
+          <t>UNI EN 81-77:2022, 1</t>
         </is>
       </c>
       <c r="F194" s="10" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="G194" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>confermato</t>
         </is>
       </c>
       <c r="H194" s="10" t="inlineStr">
@@ -9729,28 +9729,28 @@
       <c r="M194" s="11" t="n"/>
       <c r="N194" s="11" t="n"/>
     </row>
-    <row r="195" ht="56" customHeight="1">
+    <row r="195" ht="95" customHeight="1">
       <c r="A195" s="10" t="n">
         <v>193</v>
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-82:2026 (accessibilità degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-82:2026</t>
+          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>miglioramento dell'accessibilità di un impianto esistente secondo i requisiti della EN 81-70</t>
+          <t>oltre 1 m/s²: massa della cabina nei calcoli (5.4.1), ritegni della cabina (5.4.2) e del contrappeso (5.5), protezione delle pulegge (5.6.1), tensioni e frecce delle guide (5.8.2, All. D), rilevazione e modo sismico (5.10.3, 5.10.4); soglie delle categorie dell'All. A da verificare sul testo</t>
         </is>
       </c>
       <c r="E195" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-82:2026</t>
+          <t>UNI EN 81-77:2022, 5.4–5.10, All. A, B, D</t>
         </is>
       </c>
       <c r="F195" s="10" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="G195" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H195" s="10" t="inlineStr">
@@ -9775,28 +9775,28 @@
       <c r="M195" s="11" t="n"/>
       <c r="N195" s="11" t="n"/>
     </row>
-    <row r="196" ht="56" customHeight="1">
+    <row r="196" ht="43" customHeight="1">
       <c r="A196" s="10" t="n">
         <v>194</v>
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: UNI EN 81-83:2026 (antivandalo degli esistenti)</t>
+          <t>Collaudo: UNI EN 81-77:2022 (azioni sismiche)</t>
         </is>
       </c>
       <c r="C196" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-83:2026</t>
+          <t>UNI EN 81-77:2022, 0.3</t>
         </is>
       </c>
       <c r="D196" s="10" t="inlineStr">
         <is>
-          <t>miglioramento della resistenza agli atti vandalici di un impianto esistente secondo la EN 81-71:2022 (voce 1.2 della Tab. A.1 della EN 81-80)</t>
+          <t>non si applica agli impianti installati prima della sua pubblicazione</t>
         </is>
       </c>
       <c r="E196" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-83:2026</t>
+          <t>UNI EN 81-77:2022, 0.3</t>
         </is>
       </c>
       <c r="F196" s="10" t="inlineStr">
@@ -9821,33 +9821,33 @@
       <c r="M196" s="11" t="n"/>
       <c r="N196" s="11" t="n"/>
     </row>
-    <row r="197" ht="56" customHeight="1">
+    <row r="197" ht="69" customHeight="1">
       <c r="A197" s="10" t="n">
         <v>195</v>
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
         </is>
       </c>
       <c r="C197" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-80:2004 e 2009, 1 e appendice A</t>
         </is>
       </c>
       <c r="D197" s="10" t="inlineStr">
         <is>
-          <t>piattaforma di distribuzione davanti alla porta di cabina: 1,50 × 1,50 m negli edifici nuovi, 1,40 × 1,40 m nell'adeguamento (fuori dal vano: in sito)</t>
+          <t>analisi dei rischi dell'impianto esistente e piano di miglioramento per priorità; quali misure e in che tempi lo decide la legislazione nazionale, non la norma</t>
         </is>
       </c>
       <c r="E197" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-80:2004 e 2009, 1 e appendice A</t>
         </is>
       </c>
       <c r="F197" s="10" t="inlineStr">
         <is>
-          <t>testo ufficiale del DM 236/1989</t>
+          <t>testo della norma, letto il 2026-10-06 (punti e valori con parole nostre)</t>
         </is>
       </c>
       <c r="G197" s="10" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="H197" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I197" s="11" t="n"/>
@@ -9867,43 +9867,43 @@
       <c r="M197" s="11" t="n"/>
       <c r="N197" s="11" t="n"/>
     </row>
-    <row r="198" ht="56" customHeight="1">
+    <row r="198" ht="69" customHeight="1">
       <c r="A198" s="10" t="n">
         <v>196</v>
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-80:2019 (miglioramento della sicurezza degli esistenti)</t>
         </is>
       </c>
       <c r="C198" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-80:2019</t>
         </is>
       </c>
       <c r="D198" s="10" t="inlineStr">
         <is>
-          <t>porte di cabina e di piano a scorrimento automatico (nell'adeguamento la porta di piano può essere a battente se ad apertura automatica); porte aperte almeno 8 s, chiusura in almeno 4 s</t>
+          <t>la stessa analisi nell'edizione in vigore, con una struttura diversa: da verificare sul testo</t>
         </is>
       </c>
       <c r="E198" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-80:2019</t>
         </is>
       </c>
       <c r="F198" s="10" t="inlineStr">
         <is>
-          <t>testo ufficiale del DM 236/1989</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G198" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H198" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I198" s="11" t="n"/>
@@ -9913,33 +9913,33 @@
       <c r="M198" s="11" t="n"/>
       <c r="N198" s="11" t="n"/>
     </row>
-    <row r="199" ht="43" customHeight="1">
+    <row r="199" ht="56" customHeight="1">
       <c r="A199" s="10" t="n">
         <v>197</v>
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-82:2026 (accessibilità degli esistenti)</t>
         </is>
       </c>
       <c r="C199" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-82:2026</t>
         </is>
       </c>
       <c r="D199" s="10" t="inlineStr">
         <is>
-          <t>arresto ai piani con autolivellamento entro ± 2 cm; sosta ai piani con le porte chiuse</t>
+          <t>miglioramento dell'accessibilità di un impianto esistente secondo i requisiti della EN 81-70</t>
         </is>
       </c>
       <c r="E199" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12</t>
+          <t>UNI EN 81-82:2026</t>
         </is>
       </c>
       <c r="F199" s="10" t="inlineStr">
         <is>
-          <t>testo ufficiale del DM 236/1989</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G199" s="10" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="H199" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I199" s="11" t="n"/>
@@ -9965,27 +9965,27 @@
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
+          <t>Collaudo: UNI EN 81-83:2026 (antivandalo degli esistenti)</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
+          <t>UNI EN 81-83:2026</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
         <is>
-          <t>pulsanti di cabina e di piano: il più alto tra 1,10 e 1,40 m, misurato all'asse del comando; bottoniera di cabina su una parete laterale ad almeno 0,35 m dalla porta</t>
+          <t>miglioramento della resistenza agli atti vandalici di un impianto esistente secondo la EN 81-71:2022 (voce 1.2 della Tab. A.1 della EN 81-80)</t>
         </is>
       </c>
       <c r="E200" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
+          <t>UNI EN 81-83:2026</t>
         </is>
       </c>
       <c r="F200" s="10" t="inlineStr">
         <is>
-          <t>testo ufficiale del DM 236/1989</t>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
         </is>
       </c>
       <c r="G200" s="10" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="H200" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I200" s="11" t="n"/>
@@ -10005,7 +10005,7 @@
       <c r="M200" s="11" t="n"/>
       <c r="N200" s="11" t="n"/>
     </row>
-    <row r="201" ht="95" customHeight="1">
+    <row r="201" ht="82" customHeight="1">
       <c r="A201" s="10" t="n">
         <v>199</v>
       </c>
@@ -10016,17 +10016,17 @@
       </c>
       <c r="C201" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>citofono in cabina tra 1,10 e 1,30 m; luce d'emergenza con almeno 3 h di autonomia; campanello d'allarme e segnale luminoso di allarme ricevuto; arresto e inversione della chiusura; segnale acustico d'arrivo; numeri in rilievo e Braille, targa Braille di piano; sedile ribaltabile dove possibile</t>
+          <t>piattaforma di distribuzione davanti alla porta di cabina: 1,50 × 1,50 m negli edifici nuovi, 1,40 × 1,40 m nell'adeguamento (fuori dal vano: in sito)</t>
         </is>
       </c>
       <c r="E201" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F201" s="10" t="inlineStr">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="H201" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto; motivazione del caso c) (DM 236/1989); pulsanti più alti delle bottoniere (DM 236/1989)</t>
         </is>
       </c>
       <c r="I201" s="11" t="n"/>
@@ -10051,7 +10051,7 @@
       <c r="M201" s="11" t="n"/>
       <c r="N201" s="11" t="n"/>
     </row>
-    <row r="202" ht="56" customHeight="1">
+    <row r="202" ht="82" customHeight="1">
       <c r="A202" s="10" t="n">
         <v>200</v>
       </c>
@@ -10062,22 +10062,22 @@
       </c>
       <c r="C202" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="D202" s="10" t="inlineStr">
         <is>
-          <t>ascensore obbligatorio oltre il terzo livello (contati interrati e porticati); negli immobili con più di tre livelli fuori terra un ascensore per ogni scala principale</t>
+          <t>porte di cabina e di piano a scorrimento automatico (nell'adeguamento la porta di piano può essere a battente se ad apertura automatica); porte aperte almeno 8 s, chiusura in almeno 4 s</t>
         </is>
       </c>
       <c r="E202" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F202" s="10" t="inlineStr">
         <is>
-          <t>testo ufficiale del DM 236/1989; L. 13/1989: ricerca, cap. 16</t>
+          <t>testo ufficiale del DM 236/1989</t>
         </is>
       </c>
       <c r="G202" s="10" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="H202" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto; motivazione del caso c) (DM 236/1989); pulsanti più alti delle bottoniere (DM 236/1989)</t>
         </is>
       </c>
       <c r="I202" s="11" t="n"/>
@@ -10097,7 +10097,7 @@
       <c r="M202" s="11" t="n"/>
       <c r="N202" s="11" t="n"/>
     </row>
-    <row r="203" ht="56" customHeight="1">
+    <row r="203" ht="82" customHeight="1">
       <c r="A203" s="10" t="n">
         <v>201</v>
       </c>
@@ -10108,22 +10108,22 @@
       </c>
       <c r="C203" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="D203" s="10" t="inlineStr">
         <is>
-          <t>nelle ristrutturazioni deroghe per impossibilità tecnica strutturale o impiantistica (privati: concesse dal Sindaco); edifici vincolati: deroga se le opere pregiudicano il bene</t>
+          <t>arresto ai piani con autolivellamento entro ± 2 cm; sosta ai piani con le porte chiuse</t>
         </is>
       </c>
       <c r="E203" s="10" t="inlineStr">
         <is>
-          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
+          <t>DM 236/1989, 8.1.12</t>
         </is>
       </c>
       <c r="F203" s="10" t="inlineStr">
         <is>
-          <t>testo ufficiale del DM 236/1989; DPR 503/1996: ricerca, cap. 16</t>
+          <t>testo ufficiale del DM 236/1989</t>
         </is>
       </c>
       <c r="G203" s="10" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="H203" s="10" t="inlineStr">
         <is>
-          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto; motivazione del caso c) (DM 236/1989); pulsanti più alti delle bottoniere (DM 236/1989)</t>
         </is>
       </c>
       <c r="I203" s="11" t="n"/>
@@ -10143,33 +10143,33 @@
       <c r="M203" s="11" t="n"/>
       <c r="N203" s="11" t="n"/>
     </row>
-    <row r="204" ht="69" customHeight="1">
+    <row r="204" ht="82" customHeight="1">
       <c r="A204" s="10" t="n">
         <v>202</v>
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
         <is>
-          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
         </is>
       </c>
       <c r="D204" s="10" t="inlineStr">
         <is>
-          <t>il progettista applica il DM 15/09/2005 oppure la RTV V.3 del Codice: dove si usa il Codice il DM 2005 non si applica</t>
+          <t>pulsanti di cabina e di piano: il più alto tra 1,10 e 1,40 m, misurato all'asse del comando; bottoniera di cabina su una parete laterale ad almeno 0,35 m dalla porta</t>
         </is>
       </c>
       <c r="E204" s="10" t="inlineStr">
         <is>
-          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
+          <t>DM 236/1989, 8.1.12 e 8.0.1</t>
         </is>
       </c>
       <c r="F204" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989</t>
         </is>
       </c>
       <c r="G204" s="10" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="H204" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto; motivazione del caso c) (DM 236/1989); pulsanti più alti delle bottoniere (DM 236/1989)</t>
         </is>
       </c>
       <c r="I204" s="11" t="n"/>
@@ -10195,27 +10195,27 @@
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C205" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, art. 1 c.2</t>
+          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
         </is>
       </c>
       <c r="D205" s="10" t="inlineStr">
         <is>
-          <t>sugli impianti esistenti vale per le modifiche sostanziali: nuovo impianto; più fermate o altro azionamento; pareti del vano, porte di piano, locale macchine o pulegge sostituiti con materiali, modelli, dimensioni o criteri diversi; solai o scale rifatti che coinvolgono l'impianto; sopraelevazione; cambio di destinazione d'uso</t>
+          <t>citofono in cabina tra 1,10 e 1,30 m; luce d'emergenza con almeno 3 h di autonomia; campanello d'allarme e segnale luminoso di allarme ricevuto; arresto e inversione della chiusura; segnale acustico d'arrivo; numeri in rilievo e Braille, targa Braille di piano; sedile ribaltabile dove possibile</t>
         </is>
       </c>
       <c r="E205" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, art. 1 c.2</t>
+          <t>DM 236/1989, 8.1.12 e 4.1.12</t>
         </is>
       </c>
       <c r="F205" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989</t>
         </is>
       </c>
       <c r="G205" s="10" t="inlineStr">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="H205" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto; motivazione del caso c) (DM 236/1989); pulsanti più alti delle bottoniere (DM 236/1989)</t>
         </is>
       </c>
       <c r="I205" s="11" t="n"/>
@@ -10235,33 +10235,33 @@
       <c r="M205" s="11" t="n"/>
       <c r="N205" s="11" t="n"/>
     </row>
-    <row r="206" ht="69" customHeight="1">
+    <row r="206" ht="82" customHeight="1">
       <c r="A206" s="10" t="n">
         <v>204</v>
       </c>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C206" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
         </is>
       </c>
       <c r="D206" s="10" t="inlineStr">
         <is>
-          <t>tipo di vano: aperto, protetto o a prova di fumo (Codice: classi da SA a SE)</t>
+          <t>ascensore obbligatorio oltre il terzo livello (contati interrati e porticati); negli immobili con più di tre livelli fuori terra un ascensore per ogni scala principale</t>
         </is>
       </c>
       <c r="E206" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
+          <t>DM 236/1989, 3.2; L. 13/1989, art. 1 c.3 lett. d)</t>
         </is>
       </c>
       <c r="F206" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989; L. 13/1989: ricerca, cap. 16</t>
         </is>
       </c>
       <c r="G206" s="10" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="H206" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto; motivazione del caso c) (DM 236/1989); pulsanti più alti delle bottoniere (DM 236/1989)</t>
         </is>
       </c>
       <c r="I206" s="11" t="n"/>
@@ -10281,33 +10281,33 @@
       <c r="M206" s="11" t="n"/>
       <c r="N206" s="11" t="n"/>
     </row>
-    <row r="207" ht="69" customHeight="1">
+    <row r="207" ht="82" customHeight="1">
       <c r="A207" s="10" t="n">
         <v>205</v>
       </c>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
+          <t>Collaudo: DM 236/1989 (barriere architettoniche)</t>
         </is>
       </c>
       <c r="C207" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 2</t>
+          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
         </is>
       </c>
       <c r="D207" s="10" t="inlineStr">
         <is>
-          <t>pareti del vano, locale macchine e pulegge, setti e arcata non combustibili; pareti, pavimento e tetto della cabina in classe di reazione al fuoco non oltre 1</t>
+          <t>nelle ristrutturazioni deroghe per impossibilità tecnica strutturale o impiantistica (privati: concesse dal Sindaco); edifici vincolati: deroga se le opere pregiudicano il bene</t>
         </is>
       </c>
       <c r="E207" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 2</t>
+          <t>DM 236/1989, 7.5; DPR 503/1996, art. 19</t>
         </is>
       </c>
       <c r="F207" s="10" t="inlineStr">
         <is>
-          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+          <t>testo ufficiale del DM 236/1989; DPR 503/1996: ricerca, cap. 16</t>
         </is>
       </c>
       <c r="G207" s="10" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="H207" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cabina minima (DM 236/1989); porta minima (DM 236/1989); porta sul lato corto; motivazione del caso c) (DM 236/1989); pulsanti più alti delle bottoniere (DM 236/1989)</t>
         </is>
       </c>
       <c r="I207" s="11" t="n"/>
@@ -10327,7 +10327,7 @@
       <c r="M207" s="11" t="n"/>
       <c r="N207" s="11" t="n"/>
     </row>
-    <row r="208" ht="82" customHeight="1">
+    <row r="208" ht="69" customHeight="1">
       <c r="A208" s="10" t="n">
         <v>206</v>
       </c>
@@ -10338,17 +10338,17 @@
       </c>
       <c r="C208" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 5</t>
+          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
         </is>
       </c>
       <c r="D208" s="10" t="inlineStr">
         <is>
-          <t>aerazione permanente in alto verso spazi scoperti di almeno il 3 % della pianta (vano almeno 0,20 m², locale macchine o pulegge almeno 0,05 m²), con una protezione che non lascia passare una sfera oltre 15 mm; non serve se il vano è aperto su spazi scoperti</t>
+          <t>il progettista applica il DM 15/09/2005 oppure la RTV V.3 del Codice: dove si usa il Codice il DM 2005 non si applica</t>
         </is>
       </c>
       <c r="E208" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 5</t>
+          <t>DM 3/8/2015, art. 5 c.1-bis lett. e)</t>
         </is>
       </c>
       <c r="F208" s="10" t="inlineStr">
@@ -10373,7 +10373,7 @@
       <c r="M208" s="11" t="n"/>
       <c r="N208" s="11" t="n"/>
     </row>
-    <row r="209" ht="69" customHeight="1">
+    <row r="209" ht="95" customHeight="1">
       <c r="A209" s="10" t="n">
         <v>207</v>
       </c>
@@ -10384,17 +10384,17 @@
       </c>
       <c r="C209" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+          <t>DM 15/09/2005, art. 1 c.2</t>
         </is>
       </c>
       <c r="D209" s="10" t="inlineStr">
         <is>
-          <t>estintore 21A89BC vicino all'accesso al macchinario; richiamo della cabina al piano prestabilito su comando della rivelazione quando la compartimentazione lo richiede</t>
+          <t>sugli impianti esistenti vale per le modifiche sostanziali: nuovo impianto; più fermate o altro azionamento; pareti del vano, porte di piano, locale macchine o pulegge sostituiti con materiali, modelli, dimensioni o criteri diversi; solai o scale rifatti che coinvolgono l'impianto; sopraelevazione; cambio di destinazione d'uso</t>
         </is>
       </c>
       <c r="E209" s="10" t="inlineStr">
         <is>
-          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
+          <t>DM 15/09/2005, art. 1 c.2</t>
         </is>
       </c>
       <c r="F209" s="10" t="inlineStr">
@@ -10430,17 +10430,17 @@
       </c>
       <c r="C210" s="10" t="inlineStr">
         <is>
-          <t>Codice S.9, Tab. S.9-3</t>
+          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
         </is>
       </c>
       <c r="D210" s="10" t="inlineStr">
         <is>
-          <t>piani tra 32 e 54 m: almeno un ascensore antincendio; oltre 54 m: almeno uno di soccorso; interrati tra −10 e −15 m: antincendio; sotto −15 m: soccorso</t>
+          <t>tipo di vano: aperto, protetto o a prova di fumo (Codice: classi da SA a SE)</t>
         </is>
       </c>
       <c r="E210" s="10" t="inlineStr">
         <is>
-          <t>Codice S.9, Tab. S.9-3</t>
+          <t>DM 15/09/2005, 3.1–3.3; Codice V.3.2</t>
         </is>
       </c>
       <c r="F210" s="10" t="inlineStr">
@@ -10465,28 +10465,28 @@
       <c r="M210" s="11" t="n"/>
       <c r="N210" s="11" t="n"/>
     </row>
-    <row r="211" ht="43" customHeight="1">
+    <row r="211" ht="69" customHeight="1">
       <c r="A211" s="10" t="n">
         <v>209</v>
       </c>
       <c r="B211" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §3.1.4</t>
+          <t>DM 15/09/2005, punto 2</t>
         </is>
       </c>
       <c r="D211" s="10" t="inlineStr">
         <is>
-          <t>carichi del macchinario valutati caso per caso sui massimi prevedibili e riportati nel progetto e nel collaudo statico</t>
+          <t>pareti del vano, locale macchine e pulegge, setti e arcata non combustibili; pareti, pavimento e tetto della cabina in classe di reazione al fuoco non oltre 1</t>
         </is>
       </c>
       <c r="E211" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §3.1.4</t>
+          <t>DM 15/09/2005, punto 2</t>
         </is>
       </c>
       <c r="F211" s="10" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="H211" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I211" s="11" t="n"/>
@@ -10511,28 +10511,28 @@
       <c r="M211" s="11" t="n"/>
       <c r="N211" s="11" t="n"/>
     </row>
-    <row r="212" ht="43" customHeight="1">
+    <row r="212" ht="108" customHeight="1">
       <c r="A212" s="10" t="n">
         <v>210</v>
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §8.4.1</t>
+          <t>DM 15/03/2005 (tabella di confronto); UNI EN 81-20:2020, 5.4.4</t>
         </is>
       </c>
       <c r="D212" s="10" t="inlineStr">
         <is>
-          <t>su un edificio esistente l'intervento è locale: verifica limitata alle parti interessate, senza ridurre la sicurezza preesistente</t>
+          <t>le classi minime della EN 81-20 per la cabina (pavimento Cfl-s2, pareti C-s2,d1, soffitto C-s2,d0) corrispondono alla classe italiana 2; la classe 1 vuole pareti in A2 o B (fumo s1–s2, gocce d0–d1), soffitto in A2 o B-s1/s2,d0, pavimento in A2fl o Bfl (corrispondenza letta su una scheda commerciale del decreto, da confermare sul testo ufficiale)</t>
         </is>
       </c>
       <c r="E212" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §8.4.1</t>
+          <t>DM 15/03/2005 (tabella di confronto); UNI EN 81-20:2020, 5.4.4</t>
         </is>
       </c>
       <c r="F212" s="10" t="inlineStr">
@@ -10542,12 +10542,12 @@
       </c>
       <c r="G212" s="10" t="inlineStr">
         <is>
-          <t>confermato</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H212" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I212" s="11" t="n"/>
@@ -10557,28 +10557,28 @@
       <c r="M212" s="11" t="n"/>
       <c r="N212" s="11" t="n"/>
     </row>
-    <row r="213" ht="43" customHeight="1">
+    <row r="213" ht="82" customHeight="1">
       <c r="A213" s="10" t="n">
         <v>211</v>
       </c>
       <c r="B213" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §11.4.1</t>
+          <t>DM 15/09/2005, punto 5</t>
         </is>
       </c>
       <c r="D213" s="10" t="inlineStr">
         <is>
-          <t>ancoranti per uso strutturale qualificati; con azioni sismiche categoria C2 per tutte le classi d'uso</t>
+          <t>aerazione permanente in alto verso spazi scoperti di almeno il 3 % della pianta (vano almeno 0,20 m², locale macchine o pulegge almeno 0,05 m²), con una protezione che non lascia passare una sfera oltre 15 mm; non serve se il vano è aperto su spazi scoperti</t>
         </is>
       </c>
       <c r="E213" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §11.4.1</t>
+          <t>DM 15/09/2005, punto 5</t>
         </is>
       </c>
       <c r="F213" s="10" t="inlineStr">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="H213" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I213" s="11" t="n"/>
@@ -10603,28 +10603,28 @@
       <c r="M213" s="11" t="n"/>
       <c r="N213" s="11" t="n"/>
     </row>
-    <row r="214" ht="108" customHeight="1">
+    <row r="214" ht="69" customHeight="1">
       <c r="A214" s="10" t="n">
         <v>212</v>
       </c>
       <c r="B214" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
         </is>
       </c>
       <c r="C214" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §7.2.3–7.2.4</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
         </is>
       </c>
       <c r="D214" s="10" t="inlineStr">
         <is>
-          <t>forza sismica sull'elemento non strutturale Fa = Sa·Wa/qa; nessun vincolo ad attrito; studio specifico oltre il 30 % del carico permanente del solaio o il 10 % di quello dell'intera struttura; progetto antisismico dell'impianto del produttore, dei collegamenti dell'installatore, dei solai e delle pareti d'ancoraggio del progettista strutturale</t>
+          <t>estintore 21A89BC vicino all'accesso al macchinario; richiamo della cabina al piano prestabilito su comando della rivelazione quando la compartimentazione lo richiede</t>
         </is>
       </c>
       <c r="E214" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, §7.2.3–7.2.4</t>
+          <t>DM 15/09/2005, punto 6; Codice V.3.3.1 c.5</t>
         </is>
       </c>
       <c r="F214" s="10" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="H214" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I214" s="11" t="n"/>
@@ -10649,28 +10649,28 @@
       <c r="M214" s="11" t="n"/>
       <c r="N214" s="11" t="n"/>
     </row>
-    <row r="215" ht="43" customHeight="1">
+    <row r="215" ht="69" customHeight="1">
       <c r="A215" s="10" t="n">
         <v>213</v>
       </c>
       <c r="B215" s="10" t="inlineStr">
         <is>
-          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+          <t>Collaudo: DM 15/09/2005 o Codice di prevenzione incendi, RTV V.3 (antincendio)</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+          <t>Codice S.9, Tab. S.9-3</t>
         </is>
       </c>
       <c r="D215" s="10" t="inlineStr">
         <is>
-          <t>impianti: stabilità allo SLV per tutte le classi d'uso; nelle classi III e IV anche funzionamento allo SLO</t>
+          <t>piani tra 32 e 54 m: almeno un ascensore antincendio; oltre 54 m: almeno uno di soccorso; interrati tra −10 e −15 m: antincendio; sotto −15 m: soccorso</t>
         </is>
       </c>
       <c r="E215" s="10" t="inlineStr">
         <is>
-          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+          <t>Codice S.9, Tab. S.9-3</t>
         </is>
       </c>
       <c r="F215" s="10" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="H215" s="10" t="inlineStr">
         <is>
-          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I215" s="11" t="n"/>
@@ -10695,10 +10695,240 @@
       <c r="M215" s="11" t="n"/>
       <c r="N215" s="11" t="n"/>
     </row>
+    <row r="216" ht="43" customHeight="1">
+      <c r="A216" s="10" t="n">
+        <v>214</v>
+      </c>
+      <c r="B216" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C216" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §3.1.4</t>
+        </is>
+      </c>
+      <c r="D216" s="10" t="inlineStr">
+        <is>
+          <t>carichi del macchinario valutati caso per caso sui massimi prevedibili e riportati nel progetto e nel collaudo statico</t>
+        </is>
+      </c>
+      <c r="E216" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §3.1.4</t>
+        </is>
+      </c>
+      <c r="F216" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G216" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H216" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I216" s="11" t="n"/>
+      <c r="J216" s="11" t="n"/>
+      <c r="K216" s="11" t="n"/>
+      <c r="L216" s="11" t="n"/>
+      <c r="M216" s="11" t="n"/>
+      <c r="N216" s="11" t="n"/>
+    </row>
+    <row r="217" ht="43" customHeight="1">
+      <c r="A217" s="10" t="n">
+        <v>215</v>
+      </c>
+      <c r="B217" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C217" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §8.4.1</t>
+        </is>
+      </c>
+      <c r="D217" s="10" t="inlineStr">
+        <is>
+          <t>su un edificio esistente l'intervento è locale: verifica limitata alle parti interessate, senza ridurre la sicurezza preesistente</t>
+        </is>
+      </c>
+      <c r="E217" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §8.4.1</t>
+        </is>
+      </c>
+      <c r="F217" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G217" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H217" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I217" s="11" t="n"/>
+      <c r="J217" s="11" t="n"/>
+      <c r="K217" s="11" t="n"/>
+      <c r="L217" s="11" t="n"/>
+      <c r="M217" s="11" t="n"/>
+      <c r="N217" s="11" t="n"/>
+    </row>
+    <row r="218" ht="43" customHeight="1">
+      <c r="A218" s="10" t="n">
+        <v>216</v>
+      </c>
+      <c r="B218" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C218" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §11.4.1</t>
+        </is>
+      </c>
+      <c r="D218" s="10" t="inlineStr">
+        <is>
+          <t>ancoranti per uso strutturale qualificati; con azioni sismiche categoria C2 per tutte le classi d'uso</t>
+        </is>
+      </c>
+      <c r="E218" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §11.4.1</t>
+        </is>
+      </c>
+      <c r="F218" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G218" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H218" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I218" s="11" t="n"/>
+      <c r="J218" s="11" t="n"/>
+      <c r="K218" s="11" t="n"/>
+      <c r="L218" s="11" t="n"/>
+      <c r="M218" s="11" t="n"/>
+      <c r="N218" s="11" t="n"/>
+    </row>
+    <row r="219" ht="108" customHeight="1">
+      <c r="A219" s="10" t="n">
+        <v>217</v>
+      </c>
+      <c r="B219" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C219" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §7.2.3–7.2.4</t>
+        </is>
+      </c>
+      <c r="D219" s="10" t="inlineStr">
+        <is>
+          <t>forza sismica sull'elemento non strutturale Fa = Sa·Wa/qa; nessun vincolo ad attrito; studio specifico oltre il 30 % del carico permanente del solaio o il 10 % di quello dell'intera struttura; progetto antisismico dell'impianto del produttore, dei collegamenti dell'installatore, dei solai e delle pareti d'ancoraggio del progettista strutturale</t>
+        </is>
+      </c>
+      <c r="E219" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, §7.2.3–7.2.4</t>
+        </is>
+      </c>
+      <c r="F219" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G219" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H219" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I219" s="11" t="n"/>
+      <c r="J219" s="11" t="n"/>
+      <c r="K219" s="11" t="n"/>
+      <c r="L219" s="11" t="n"/>
+      <c r="M219" s="11" t="n"/>
+      <c r="N219" s="11" t="n"/>
+    </row>
+    <row r="220" ht="43" customHeight="1">
+      <c r="A220" s="10" t="n">
+        <v>218</v>
+      </c>
+      <c r="B220" s="10" t="inlineStr">
+        <is>
+          <t>Collaudo: NTC 2018 (strutture e azioni sismiche)</t>
+        </is>
+      </c>
+      <c r="C220" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+        </is>
+      </c>
+      <c r="D220" s="10" t="inlineStr">
+        <is>
+          <t>impianti: stabilità allo SLV per tutte le classi d'uso; nelle classi III e IV anche funzionamento allo SLO</t>
+        </is>
+      </c>
+      <c r="E220" s="10" t="inlineStr">
+        <is>
+          <t>NTC 2018, Tab. 7.3.III e §7.3.6.3</t>
+        </is>
+      </c>
+      <c r="F220" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, cap. 16 (testi ufficiali e schede UNI, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="G220" s="10" t="inlineStr">
+        <is>
+          <t>confermato</t>
+        </is>
+      </c>
+      <c r="H220" s="10" t="inlineStr">
+        <is>
+          <t>tensione nelle putrelle sotto l'argano; freccia delle putrelle sotto l'argano</t>
+        </is>
+      </c>
+      <c r="I220" s="11" t="n"/>
+      <c r="J220" s="11" t="n"/>
+      <c r="K220" s="11" t="n"/>
+      <c r="L220" s="11" t="n"/>
+      <c r="M220" s="11" t="n"/>
+      <c r="N220" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N215"/>
+  <autoFilter ref="A1:N220"/>
   <dataValidations count="1">
-    <dataValidation sqref="I3:I215" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
+    <dataValidation sqref="I3:I220" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
       <formula1>"conforme,diverso,non applicabile"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10741,7 +10971,7 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$215,"da verificare")</f>
+        <f>COUNTIF(Voci!$G$3:$G$220,"da verificare")</f>
         <v/>
       </c>
     </row>
@@ -10752,7 +10982,7 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$215,"confermato")</f>
+        <f>COUNTIF(Voci!$G$3:$G$220,"confermato")</f>
         <v/>
       </c>
     </row>
@@ -10763,7 +10993,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$215,"scelta del software")</f>
+        <f>COUNTIF(Voci!$G$3:$G$220,"scelta del software")</f>
         <v/>
       </c>
     </row>
@@ -10774,7 +11004,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$215,"stima")</f>
+        <f>COUNTIF(Voci!$G$3:$G$220,"stima")</f>
         <v/>
       </c>
     </row>
@@ -10785,7 +11015,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$215,"derivazione")</f>
+        <f>COUNTIF(Voci!$G$3:$G$220,"derivazione")</f>
         <v/>
       </c>
     </row>
@@ -10796,7 +11026,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$215,"prassi di cantiere")</f>
+        <f>COUNTIF(Voci!$G$3:$G$220,"prassi di cantiere")</f>
         <v/>
       </c>
     </row>
@@ -10807,7 +11037,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTA(Voci!$A$3:$A$215)</f>
+        <f>COUNTA(Voci!$A$3:$A$220)</f>
         <v/>
       </c>
     </row>
@@ -10825,7 +11055,7 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$215,"conforme")</f>
+        <f>COUNTIF(Voci!$I$3:$I$220,"conforme")</f>
         <v/>
       </c>
     </row>
@@ -10836,7 +11066,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$215,"diverso")</f>
+        <f>COUNTIF(Voci!$I$3:$I$220,"diverso")</f>
         <v/>
       </c>
     </row>
@@ -10847,7 +11077,7 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$215,"non applicabile")</f>
+        <f>COUNTIF(Voci!$I$3:$I$220,"non applicabile")</f>
         <v/>
       </c>
     </row>
@@ -10858,14 +11088,14 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>COUNTBLANK(Voci!$I$3:$I$215)</f>
+        <f>COUNTBLANK(Voci!$I$3:$I$220)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Conteggi sulle righe 3–215 del foglio «Voci» (la riga 2 è l'esempio).</t>
+          <t>Conteggi sulle righe 3–220 del foglio «Voci» (la riga 2 è l'esempio).</t>
         </is>
       </c>
     </row>

--- a/liftpilot/docs/lista-verifica-normativa.xlsx
+++ b/liftpilot/docs/lista-verifica-normativa.xlsx
@@ -6831,7 +6831,7 @@
       <c r="M131" s="11" t="n"/>
       <c r="N131" s="11" t="n"/>
     </row>
-    <row r="132" ht="238" customHeight="1">
+    <row r="132" ht="316" customHeight="1">
       <c r="A132" s="10" t="n">
         <v>130</v>
       </c>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
+          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. Il locale della macchina accanto al vano è lungo 2200 mm oltre la parete, largo 2600 mm e alto 2400 mm, con la porta sul fianco e il quadro sulla parete di fondo; quello sotto il vano è grande quanto il vano. Tutti e due si allargano dove la macchina ne esce, fino a 500 mm oltre il suo ingombro. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">

--- a/liftpilot/docs/lista-verifica-normativa.xlsx
+++ b/liftpilot/docs/lista-verifica-normativa.xlsx
@@ -959,7 +959,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>con la macchina secondo la UNI EN 81-20:2020 e un dispositivo elettrico di sicurezza (5.11.2) che arresta la macchina, la verifica con cabina o contrappeso bloccati non superata è «Attenzione» (verifica sostituita da dispositivo, da documentare), mai OK; con la macchina secondo la UNI EN 81-1 resta KO</t>
+          <t>con la macchina secondo la UNI EN 81-20:2020 e un dispositivo elettrico di sicurezza (5.11.2) che arresta la macchina, la verifica con cabina o contrappeso bloccati non superata è «Attenzione» (verifica sostituita da dispositivo, da documentare), mai OK; con la macchina secondo la UNI EN 81-1 resta «Non soddisfatta»</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>β ≤ 105° (1,83 rad; oltre: KO)</t>
+          <t>β ≤ 105° (1,83 rad; oltre: «Non soddisfatta»)</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>γ ≥ 35° (sotto: KO)</t>
+          <t>γ ≥ 35° (sotto: «Non soddisfatta»)</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Rapporto D/d della puleggia di trazione</t>
+          <t>Rapporto D/d della puleggia di frizione</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>N_equiv delle pulegge — D: diametro della puleggia di trazione; Dp: media delle altre pulegge. La flessione è inversa solo tra due pulegge consecutive ad assi fissi, con i punti di contatto a meno di 200·d e i piani di flessione ruotati di oltre 120°: la classifica il progettista.</t>
+          <t>N_equiv delle pulegge — D: diametro della puleggia di frizione; Dp: media delle altre pulegge. La flessione è inversa solo tra due pulegge consecutive ad assi fissi, con i punti di contatto a meno di 200·d e i piani di flessione ruotati di oltre 120°: la classifica il progettista.</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>con l'accelerazione a della cabina, come stampato nella norma; nella taglia 2:1 il software mostra anche l'esito con r·a, l'accelerazione fisica di quel tratto: «Attenzione» se supera il limite, mai KO</t>
+          <t>con l'accelerazione a della cabina, come stampato nella norma; nella taglia 2:1 il software mostra anche l'esito con r·a, l'accelerazione fisica di quel tratto: «Attenzione» se supera il limite, mai «Non soddisfatta»</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
@@ -3427,7 +3427,7 @@
       <c r="M57" s="11" t="n"/>
       <c r="N57" s="11" t="n"/>
     </row>
-    <row r="58" ht="69" customHeight="1">
+    <row r="58" ht="82" customHeight="1">
       <c r="A58" s="10" t="n">
         <v>56</v>
       </c>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>oltre 1,75 m/s i mezzi di compensazione senza tensionamento vanno guidati vicino all'ansa («Attenzione»); oltre 3 m/s servono funi di compensazione con puleggia tenditrice, che il modello non contiene (KO: fuori dal campo del software)</t>
+          <t>oltre 1,75 m/s i mezzi di compensazione senza tensionamento vanno guidati vicino all'ansa («Attenzione»); oltre 3 m/s servono funi di compensazione con puleggia tenditrice, che il modello non contiene («Non soddisfatta»: fuori dal campo del software)</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>contrappeso in nicchia: il contrappeso con le sue guide sta nella nicchia della parete su cui corre, con almeno 20 mm tra le guide e i fianchi della nicchia (con le staffe Panev, lo spazio della piastra del supporto dietro il piede di ogni guida); la distanza dalla parete si misura dal fondo della nicchia e la cabina guadagna la sua profondità, senza scendere sotto gli ingombri delle guide; luce del vano in nicchia: una nicchia alta 400 mm per lampada, le lampade 1500 mm sopra ogni piano e l'ultima a 80 mm sotto il solaio; canalina in nicchia: dal fondo della fossa al solaio; ogni nicchia dentro la sua parete, fuori dai telai delle porte di piano e dalle altre nicchie, con almeno 50 mm di muro dietro; altrimenti «Non conforme»</t>
+          <t>contrappeso in nicchia: il contrappeso con le sue guide sta nella nicchia della parete su cui corre, con almeno 20 mm tra le guide e i fianchi della nicchia (con le staffe Panev, lo spazio della piastra del supporto dietro il piede di ogni guida); la distanza dalla parete si misura dal fondo della nicchia e la cabina guadagna la sua profondità, senza scendere sotto gli ingombri delle guide; luce del vano in nicchia: una nicchia alta 400 mm per lampada, le lampade 1500 mm sopra ogni piano e l'ultima a 80 mm sotto la soletta; canalina in nicchia: dal fondo della fossa alla soletta; ogni nicchia dentro la sua parete, fuori dai telai delle porte di piano e dalle altre nicchie, con almeno 50 mm di muro dietro; altrimenti «Non conforme»</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>con la cabina nella posizione più alta: a 2:1 la puleggia di cabina (Dp + 30 mm sopra la traversa) è un'apparecchiatura sul tetto, distanza libera ≥ 500 mm dal soffitto o dalle pulegge appese; a 1:1 con la macchina in basso la traversa sotto le pulegge appese al solaio (asse a Dp/2 + 120 mm sotto il soffitto), distanza libera ≥ 100 mm, quella della traversa</t>
+          <t>con la cabina nella posizione più alta: a 2:1 la puleggia di cabina (Dp + 30 mm sopra la traversa) è un'apparecchiatura sul tetto, distanza libera ≥ 500 mm dal soffitto o dalle pulegge appese; a 1:1 con la macchina in basso la traversa sotto le pulegge appese alla soletta (asse a Dp/2 + 120 mm sotto il soffitto), distanza libera ≥ 100 mm, quella della traversa</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>regola del committente (Panev): il rinvio sta nel telaio del locale macchine, mai nel vano; UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio)</t>
+          <t>regola del committente (Panev): il rinvio sta nel telaio del locale macchina, mai nel vano; UNI EN 81-20:2020, 5.2.1.8 (carichi sull'edificio)</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
+          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di sospensione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale; con la puleggia di rinvio, l'asse sul basamento o sul telaio che la porta (voce locale.rinvio); macchina in basso o senza locale: fino al soffitto del vano</t>
+          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + soletta del locale + asse della puleggia a 0,9·D sul pavimento del locale; con la puleggia di rinvio, l'asse sul basamento o sul telaio che la porta (voce locale.rinvio); macchina in basso o senza locale: fino al soffitto del vano</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
+          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di frizione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>senza rinvio le due calate scendono dai due lati della puleggia di trazione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
+          <t>senza rinvio le due calate scendono dai due lati della puleggia di frizione: la loro distanza in pianta (dall'asse della cabina a quello del contrappeso, meno Dp con la taglia 2:1) è il diametro primitivo D. La macchina proposta ha la puleggia di diametro uguale alla calata della pianta, se è nella gamma del calcolo (da 320 a 800 mm); una macchina inserita a mano, o nella sostituzione con il confronto la macchina esistente (i suoi attacchi restano), con un diametro che si scosta dalla calata più di 1 mm è segnalata e il progetto non si salva</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>dall'asse dei rinvii in testata all'asse della puleggia di trazione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
+          <t>dall'asse dei rinvii in testata all'asse della puleggia di frizione, secondo lo schema delle funi (impianto.basso.schema); la puleggia ha l'asse a 0,9·D sul pavimento del suo locale</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>tre schemi: rinvii appesi sotto il solaio del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra il solaio (assi a 450 mm sul pavimento del locale, solaio di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto il solaio. Il locale della macchina accanto al vano è lungo 2200 mm oltre la parete, largo 2600 mm e alto 2400 mm, con la porta sul fianco e il quadro sulla parete di fondo; quello sotto il vano è grande quanto il vano. Tutti e due si allargano dove la macchina ne esce, fino a 500 mm oltre il suo ingombro. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
+          <t>tre schemi: rinvii appesi sotto la soletta del vano (assi a Dp/2 + 120 mm sotto il soffitto), macchina nel locale al piano più basso oltre la parete del contrappeso con la puleggia nel vano; locale pulegge sopra la soletta (assi a 450 mm sul pavimento del locale, soletta di 250 mm se il locale non è progettato), macchina come sopra; macchina sotto il vano, in un locale alto 2400 mm sotto la soletta della fossa di 300 mm, rinvii sotto la soletta. Il locale della macchina accanto al vano è lungo 2200 mm oltre la parete, largo 2600 mm e alto 2400 mm, con la porta sul fianco e il quadro sulla parete di fondo; quello sotto il vano è grande quanto il vano. Tutti e due si allargano dove la macchina ne esce, fino a 500 mm oltre il suo ingombro. I due rami alla macchina salgono dietro il contrappeso a 50 mm dalla parete e dal contrappeso, la puleggia con il piano parallelo alla parete; per lato un rinvio a 180° se il ramo dista dalla calata in pianta non più di Dp, altrimenti due rinvii a 90° con un tratto orizzontale. Il calcolo conta due rinvii per la macchina in basso: gli altri entrano come flessioni semplici aggiuntive (nps)</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>la sostituzione della macchina o della puleggia di trazione è una trasformazione importante: si annota nel registro dell'impianto, da aggiornare</t>
+          <t>la sostituzione della macchina o della puleggia di frizione è una trasformazione importante: si annota nel registro dell'impianto, da aggiornare</t>
         </is>
       </c>
       <c r="E170" s="10" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="D209" s="10" t="inlineStr">
         <is>
-          <t>sugli impianti esistenti vale per le modifiche sostanziali: nuovo impianto; più fermate o altro azionamento; pareti del vano, porte di piano, locale macchine o pulegge sostituiti con materiali, modelli, dimensioni o criteri diversi; solai o scale rifatti che coinvolgono l'impianto; sopraelevazione; cambio di destinazione d'uso</t>
+          <t>sugli impianti esistenti vale per le modifiche sostanziali: nuovo impianto; più fermate o altro azionamento; pareti del vano, porte di piano, locale macchina o pulegge sostituiti con materiali, modelli, dimensioni o criteri diversi; solai o scale rifatti che coinvolgono l'impianto; sopraelevazione; cambio di destinazione d'uso</t>
         </is>
       </c>
       <c r="E209" s="10" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="D211" s="10" t="inlineStr">
         <is>
-          <t>pareti del vano, locale macchine e pulegge, setti e arcata non combustibili; pareti, pavimento e tetto della cabina in classe di reazione al fuoco non oltre 1</t>
+          <t>pareti del vano, locale macchina e pulegge, setti e arcata non combustibili; pareti, pavimento e tetto della cabina in classe di reazione al fuoco non oltre 1</t>
         </is>
       </c>
       <c r="E211" s="10" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="D213" s="10" t="inlineStr">
         <is>
-          <t>aerazione permanente in alto verso spazi scoperti di almeno il 3 % della pianta (vano almeno 0,20 m², locale macchine o pulegge almeno 0,05 m²), con una protezione che non lascia passare una sfera oltre 15 mm; non serve se il vano è aperto su spazi scoperti</t>
+          <t>aerazione permanente in alto verso spazi scoperti di almeno il 3 % della pianta (vano almeno 0,20 m², locale macchina o pulegge almeno 0,05 m²), con una protezione che non lascia passare una sfera oltre 15 mm; non serve se il vano è aperto su spazi scoperti</t>
         </is>
       </c>
       <c r="E213" s="10" t="inlineStr">

--- a/liftpilot/docs/lista-verifica-normativa.xlsx
+++ b/liftpilot/docs/lista-verifica-normativa.xlsx
@@ -527,7 +527,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Italia — sostituzione dell'argano su impianto esistente</t>
+          <t>Italia — sostituzione dell’argano su impianto esistente</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Aderenza: tre condizioni di Euler-Eytelwein — Con la cabina o il contrappeso bloccati la condizione serve quando è l'aderenza a impedire il sollevamento: la UNI EN 81-20:2020 (5.5.3 c)) ammette in alternativa un dispositivo elettrico di sicurezza (voce trazione.bloccata.dispositivo); la UNI EN 81-1:2008 (9.3 c)) no.</t>
+          <t>Aderenza: tre condizioni di Euler-Eytelwein — Con la cabina o il contrappeso bloccati la condizione serve quando è l’aderenza a impedire il sollevamento: la UNI EN 81-20:2020 (5.5.3 c)) ammette in alternativa un dispositivo elettrico di sicurezza (voce trazione.bloccata.dispositivo); la UNI EN 81-1:2008 (9.3 c)) no.</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Decelerazione della verifica di frenatura con ammortizzatori a corsa ridotta — La UNI EN 81-50:2020 non dà un numero: con ammortizzatori a corsa ridotta la decelerazione è la minima che porta cabina e contrappeso alla velocità di progetto degli ammortizzatori, mai sotto 0,5 m/s². Il software tiene 0,8 m/s², il valore della UNI EN 81-1:2008: l'ingegnere lo sostituisce con quello calcolato dai dati degli ammortizzatori.</t>
+          <t>Decelerazione della verifica di frenatura con ammortizzatori a corsa ridotta — La UNI EN 81-50:2020 non dà un numero: con ammortizzatori a corsa ridotta la decelerazione è la minima che porta cabina e contrappeso alla velocità di progetto degli ammortizzatori, mai sotto 0,5 m/s². Il software tiene 0,8 m/s², il valore della UNI EN 81-1:2008: l’ingegnere lo sostituisce con quello calcolato dai dati degli ammortizzatori.</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Aderenza alla decelerazione reale del freno — La norma vuole ogni massa in moto con la sua accelerazione e una decelerazione di calcolo mai sotto 0,5 m/s²; non dice con quanti gruppi del freno. Se contarla come esito lo decide l'ingegnere: nell'esempio B del capitolo 7 l'utilizzo passa da 1,005 a 4,17.</t>
+          <t>Aderenza alla decelerazione reale del freno — La norma vuole ogni massa in moto con la sua accelerazione e una decelerazione di calcolo mai sotto 0,5 m/s²; non dice con quanti gruppi del freno. Se contarla come esito lo decide l’ingegnere: nell’esempio B del capitolo 7 l’utilizzo passa da 1,005 a 4,17.</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Soglia di attenzione sull'utilizzo dell'aderenza</t>
+          <t>Soglia di attenzione sull’utilizzo dell’aderenza</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Numero minimo di funi — Con 2 sole funi serve anche il dispositivo contro l'allungamento anomalo (voce funi.due): il software lo ricorda, non lo verifica.</t>
+          <t>Numero minimo di funi — Con 2 sole funi serve anche il dispositivo contro l’allungamento anomalo (voce funi.due): il software lo ricorda, non lo verifica.</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>con 2 funi un dispositivo elettrico di sicurezza (5.11.2) ferma la macchina se una fune si allunga in modo anomalo rispetto all'altra (informazione)</t>
+          <t>con 2 funi un dispositivo elettrico di sicurezza (5.11.2) ferma la macchina se una fune si allunga in modo anomalo rispetto all’altra (informazione)</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>un fermo dove le funi entrano ed escono dalla puleggia e almeno uno intermedio se più di 60° dell'arco di avvolgimento sono sotto l'orizzontale per l'asse e l'avvolgimento supera 120°: con la macchina in basso le funi avvolgono la puleggia da sotto (informazione)</t>
+          <t>un fermo dove le funi entrano ed escono dalla puleggia e almeno uno intermedio se più di 60° dell’arco di avvolgimento sono sotto l’orizzontale per l’asse e l’avvolgimento supera 120°: con la macchina in basso le funi avvolgono la puleggia da sotto (informazione)</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>N_equiv(t) della gola a V con sottosquadro — Scelta dal lato della sicurezza; la UNI EN 81-1:2008 (prospetto N.1) intitola la riga con sottosquadro «U/V»: con una macchina secondo quella norma l'ingegnere può prendere il valore di β.</t>
+          <t>N_equiv(t) della gola a V con sottosquadro — Scelta dal lato della sicurezza; la UNI EN 81-1:2008 (prospetto N.1) intitola la riga con sottosquadro «U/V»: con una macchina secondo quella norma l’ingegnere può prendere il valore di β.</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>U: sotto 75° il valore di 75°, oltre 105° estrapolazione dall'ultimo tratto, segnalata · V: oltre 50° il valore di 50°</t>
+          <t>U: sotto 75° il valore di 75°, oltre 105° estrapolazione dall’ultimo tratto, segnalata · V: oltre 50° il valore di 50°</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>scelta prudente del software (la tabella si ferma a quegli angoli; N_equiv cresce con β e cala con γ, quindi il valore dell'estremo sta dal lato della sicurezza)</t>
+          <t>scelta prudente del software (la tabella si ferma a quegli angoli; N_equiv cresce con β e cala con γ, quindi il valore dell’estremo sta dal lato della sicurezza)</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Decelerazione massima del freno — La norma non dà un numero per il freno: ne confronta la decelerazione media con quella del paracadute e dell'urto sugli ammortizzatori, che hanno 1 gn come limite. Il confronto vero è con i dati dei componenti montati.</t>
+          <t>Decelerazione massima del freno — La norma non dà un numero per il freno: ne confronta la decelerazione media con quella del paracadute e dell’urto sugli ammortizzatori, che hanno 1 gn come limite. Il confronto vero è con i dati dei componenti montati.</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.9.2.2.2.1 (non oltre il paracadute o l'urto sugli ammortizzatori); 1 gn in 5.6.2.1.3 e 5.8.2; con il freno come organo d'arresto, 1 gn anche in 5.6.6.3 (ACOP) e 5.6.7.6 (UCM)</t>
+          <t>UNI EN 81-20:2020, 5.9.2.2.2.1 (non oltre il paracadute o l’urto sugli ammortizzatori); 1 gn in 5.6.2.1.3 e 5.8.2; con il freno come organo d’arresto, 1 gn anche in 5.6.6.3 (ACOP) e 5.6.7.6 (UCM)</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>carico sull'albero; coppia in uscita</t>
+          <t>carico sull’albero; coppia in uscita</t>
         </is>
       </c>
       <c r="I42" s="11" t="n"/>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>P_st = ΔF·v_f / (η_d·η_vano) ≤ P_n, con ΔF il maggiore tra cabina carica in salita dal basso e vuota in discesa dall'alto</t>
+          <t>P_st = ΔF·v_f / (η_d·η_vano) ≤ P_n, con ΔF il maggiore tra cabina carica in salita dal basso e vuota in discesa dall’alto</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Mezzo meccanico per la manovra di emergenza — Solo con la macchina secondo la UNI EN 81-20:2020: la UNI EN 81-1:2008 non ha la soglia dei 150 N né l'ora di autonomia. Il verso della forza non è dato dalla norma: il software prende il peggiore.</t>
+          <t>Mezzo meccanico per la manovra di emergenza — Solo con la macchina secondo la UNI EN 81-20:2020: la UNI EN 81-1:2008 non ha la soglia dei 150 N né l’ora di autonomia. Il verso della forza non è dato dalla norma: il software prende il peggiore.</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Carico sull'albero della puleggia</t>
+          <t>Carico sull’albero della puleggia</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>carico sull'albero</t>
+          <t>carico sull’albero</t>
         </is>
       </c>
       <c r="I49" s="11" t="n"/>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>carico verso l'alto meno la massa della macchina: da verificare con il progettista strutturale</t>
+          <t>carico verso l’alto meno la massa della macchina: da verificare con il progettista strutturale</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>UNI 10411-1:2024, punto 14: macchina secondo la UNI EN 81-20 (5.9.1 e 5.9.2, freno in due gruppi) o la UNI EN 81-1:2010, con aderenza e coefficiente di sicurezza delle funi (14.1); D/d ≥ 40 (14.3); temporizzatore della UNI EN 81-20 (5.9.2.7), arresto prima che la cabina in salita tocchi la velocità di intervento del limitatore, ACOP e UCM esistenti che funzionano ancora, arresto vicino alla macchina, pulegge secondo la 5.5.7, interruzione se il freno non si apre (14.4 a)–g)); valutazione della sicurezza su tre piani (4); con funi nuove, controllo degli attacchi d'estremità (17.1); documenti dell'appendice C (14) e manuali (25.5). UNI 10411-11:2024, punto 14: macchina come l'originale, altrimenti UNI EN 81-20 5.9.1–5.9.2 con le verifiche della norma di origine o della UNI EN 81-20 e la valutazione 4.3 (14.1); UCM esistenti che funzionano ancora e, senza UCM conforme alla 5.6.7 e con il rallentamento controllato, interruzione se il freno non si apre (14.3); funi nuove e attacchi come gli originali, altrimenti verificati con la valutazione 4.3 (17)</t>
+          <t>UNI 10411-1:2024, punto 14: macchina secondo la UNI EN 81-20 (5.9.1 e 5.9.2, freno in due gruppi) o la UNI EN 81-1:2010, con aderenza e coefficiente di sicurezza delle funi (14.1); D/d ≥ 40 (14.3); temporizzatore della UNI EN 81-20 (5.9.2.7), arresto prima che la cabina in salita tocchi la velocità di intervento del limitatore, ACOP e UCM esistenti che funzionano ancora, arresto vicino alla macchina, pulegge secondo la 5.5.7, interruzione se il freno non si apre (14.4 a)–g)); valutazione della sicurezza su tre piani (4); con funi nuove, controllo degli attacchi d’estremità (17.1); documenti dell’appendice C (14) e manuali (25.5). UNI 10411-11:2024, punto 14: macchina come l’originale, altrimenti UNI EN 81-20 5.9.1–5.9.2 con le verifiche della norma di origine o della UNI EN 81-20 e la valutazione 4.3 (14.1); UCM esistenti che funzionano ancora e, senza UCM conforme alla 5.6.7 e con il rallentamento controllato, interruzione se il freno non si apre (14.3); funi nuove e attacchi come gli originali, altrimenti verificati con la valutazione 4.3 (17)</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Pulegge di cabina e di contrappeso nella taglia 2:1 — La velocità della fune rispetto all'asse della puleggia di cabina è quella della cabina: la massa ridotta è J_p/R_p². Con più pulegge o pulegge diverse da quelle di rinvio, l'ingegnere inserisce l'inerzia equivalente.</t>
+          <t>Pulegge di cabina e di contrappeso nella taglia 2:1 — La velocità della fune rispetto all’asse della puleggia di cabina è quella della cabina: la massa ridotta è J_p/R_p². Con più pulegge o pulegge diverse da quelle di rinvio, l’ingegnere inserisce l’inerzia equivalente.</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>una puleggia per lato, con l'inerzia J_p e il diametro D_p delle pulegge di rinvio: massa ridotta J_p/R_p², con l'accelerazione della cabina divisa per r, nei tiri e nell'inerzia riportata al motore</t>
+          <t>una puleggia per lato, con l’inerzia J_p e il diametro D_p delle pulegge di rinvio: massa ridotta J_p/R_p², con l’accelerazione della cabina divisa per r, nei tiri e nell’inerzia riportata al motore</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>con l'accelerazione a della cabina, come stampato nella norma; nella taglia 2:1 il software mostra anche l'esito con r·a, l'accelerazione fisica di quel tratto: «Attenzione» se supera il limite, mai «Non soddisfatta»</t>
+          <t>con l’accelerazione a della cabina, come stampato nella norma; nella taglia 2:1 il software mostra anche l’esito con r·a, l’accelerazione fisica di quel tratto: «Attenzione» se supera il limite, mai «Non soddisfatta»</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>oltre 1,75 m/s i mezzi di compensazione senza tensionamento vanno guidati vicino all'ansa («Attenzione»); oltre 3 m/s servono funi di compensazione con puleggia tenditrice, che il modello non contiene («Non soddisfatta»: fuori dal campo del software)</t>
+          <t>oltre 1,75 m/s i mezzi di compensazione senza tensionamento vanno guidati vicino all’ansa («Attenzione»); oltre 3 m/s servono funi di compensazione con puleggia tenditrice, che il modello non contiene («Non soddisfatta»: fuori dal campo del software)</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Compensazione e cavo flessibile — Nella 5.11.3 la massa della compensazione (0,5·H ± y) e del cavo (0,25·H ± 0,5·y) dipende dalla posizione della cabina e c'è anche sul lato del contrappeso; il software la tiene costante dentro P. Con catene o funi di compensazione il modello non vale.</t>
+          <t>Compensazione e cavo flessibile — Nella 5.11.3 la massa della compensazione (0,5·H ± y) e del cavo (0,25·H ± 0,5·y) dipende dalla posizione della cabina e c’è anche sul lato del contrappeso; il software la tiene costante dentro P. Con catene o funi di compensazione il modello non vale.</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Superficie utile massima della cabina per portata — la norma misura la superficie a 1 m dal pavimento tra le pareti strutturali, senza finiture (5.4.2.1.2), conta le nicchie e conta per intero la rientranza dell'ingresso profonda più di 100 mm (5.4.2.1.3); il software usa larghezza × profondità interne: nicchie e rientranze vanno aggiunte a mano</t>
+          <t>Superficie utile massima della cabina per portata — la norma misura la superficie a 1 m dal pavimento tra le pareti strutturali, senza finiture (5.4.2.1.2), conta le nicchie e conta per intero la rientranza dell’ingresso profonda più di 100 mm (5.4.2.1.3); il software usa larghezza × profondità interne: nicchie e rientranze vanno aggiunte a mano</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Parete del vano di fronte all'entrata della cabina — le deroghe della norma (fino a 0,20 m per un tratto alto non più di 0,50 m o con porte verticali di ascensori per merci; nessun limite con la porta di cabina bloccata meccanicamente) non sono usate: la verifica è più severa. Il software misura fino alla soglia; la figura 3 della norma porta il limite anche al telaio e al bordo di chiusura delle ante di cabina: con la porta scelta lo verifica l'ingegnere sui dati del fornitore.</t>
+          <t>Parete del vano di fronte all’entrata della cabina — le deroghe della norma (fino a 0,20 m per un tratto alto non più di 0,50 m o con porte verticali di ascensori per merci; nessun limite con la porta di cabina bloccata meccanicamente) non sono usate: la verifica è più severa. Il software misura fino alla soglia; la figura 3 della norma porta il limite anche al telaio e al bordo di chiusura delle ante di cabina: con la porta scelta lo verifica l’ingegnere sui dati del fornitore.</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>parete di fronte all'entrata</t>
+          <t>parete di fronte all’entrata</t>
         </is>
       </c>
       <c r="I63" s="11" t="n"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Gioco tra soglia di cabina e soglia di piano — Non calcolato: tra il bordo d'attacco delle ante di cabina e le porte di piano al massimo 0,12 m (5.3.4.2; 11.2.3 nella UNI EN 81-1:2008), dato del fornitore delle porte.</t>
+          <t>Gioco tra soglia di cabina e soglia di piano — Non calcolato: tra il bordo d’attacco delle ante di cabina e le porte di piano al massimo 0,12 m (5.3.4.2; 11.2.3 nella UNI EN 81-1:2008), dato del fornitore delle porte.</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Pareti all'ultimo piano e in testata diverse dal piano principale</t>
+          <t>Pareti all’ultimo piano e in testata diverse dal piano principale</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>negli edifici esistenti le pareti del vano all'ultima fermata e in testata possono stare altrove che al piano principale: cabina, guide e contrappeso restano a piombo; la cabina con soglie e operatori delle porte e il contrappeso passano ad almeno 25 mm dalle pareti spostate (meno: «Attenzione»; dentro la parete: «Non conforme»); le porte di piano dell'ultima fermata restano in linea con la cabina e la parete non entra nel loro spessore, i piedi delle guide e la staffa a ponte non entrano nelle pareti; le staffe arrivano alla parete dove sta (le staffe Panev si verificano anche lì); la distanza dalla parete di fronte all'entrata (voce distanze.parete.entrata) vale anche in testata</t>
+          <t>negli edifici esistenti le pareti del vano all’ultima fermata e in testata possono stare altrove che al piano principale: cabina, guide e contrappeso restano a piombo; la cabina con soglie e operatori delle porte e il contrappeso passano ad almeno 25 mm dalle pareti spostate (meno: «Attenzione»; dentro la parete: «Non conforme»); le porte di piano dell’ultima fermata restano in linea con la cabina e la parete non entra nel loro spessore, i piedi delle guide e la staffa a ponte non entrano nelle pareti; le staffe arrivano alla parete dove sta (le staffe Panev si verificano anche lì); la distanza dalla parete di fronte all’entrata (voce distanze.parete.entrata) vale anche in testata</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.3.1 (parete di fronte all'entrata); il resto scelta del software</t>
+          <t>UNI EN 81-20:2020, 5.2.5.3.1 (parete di fronte all’entrata); il resto scelta del software</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>scelta del software: il margine di marcia va confermato con l'installatore</t>
+          <t>scelta del software: il margine di marcia va confermato con l’installatore</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Adeguamento di edifici esistenti: cabina e porta minime — Per un ascensore nuovo in un edificio esistente il caso è a) o b) secondo la destinazione; il c) è l'eccezione, scelta dal progettista.</t>
+          <t>Adeguamento di edifici esistenti: cabina e porta minime — Per un ascensore nuovo in un edificio esistente il caso è a) o b) secondo la destinazione; il c) è l’eccezione, scelta dal progettista.</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>cabina larga 800 mm e profonda 1200 mm, porta di 750 mm sul lato corto; piattaforma davanti alla porta 1,40 × 1,40 m (fuori dal vano: da verificare in sito); pulsanti più alti delle bottoniere tra 1100 e 1400 mm dal pavimento; solo se l'edificio esistente non consente una cabina più grande: una cabina sotto le misure del caso b) (larga 950 mm, profonda 1300 mm, porta di 800 mm) chiede la motivazione scritta nel progetto («Attenzione» se manca)</t>
+          <t>cabina larga 800 mm e profonda 1200 mm, porta di 750 mm sul lato corto; piattaforma davanti alla porta 1,40 × 1,40 m (fuori dal vano: da verificare in sito); pulsanti più alti delle bottoniere tra 1100 e 1400 mm dal pavimento; solo se l’edificio esistente non consente una cabina più grande: una cabina sotto le misure del caso b) (larga 950 mm, profonda 1300 mm, porta di 800 mm) chiede la motivazione scritta nel progetto («Attenzione» se manca)</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>vano nel muro: luce netta + 2 × 50 mm di portale; operatore della porta di cabina lungo 1,5·L + 50 mm con porta telescopica (il lato di chiusura 25 mm oltre la luce) e 2·L + 60 mm con porta centrale, profondo 220 mm, dentro il vano; con il fornitore scelto: 2SG FLY/LIKE 1,5·L + 40 mm (telescopica) e 2·L + 20 mm (centrale), profondo 220 mm; Fermator 40/10 1,5·L + 50 mm e 2·L + 50 mm, profondo 144 mm; Dapa LOWER 1,5·L + 47 mm e 2·L + 50 mm, profondo 217 mm; con due accessi adiacenti gli operatori non devono sovrapporsi all'angolo tra le porte (altrimenti «Attenzione»: operatori da scegliere con il fornitore)</t>
+          <t>vano nel muro: luce netta + 2 × 50 mm di portale; operatore della porta di cabina lungo 1,5·L + 50 mm con porta telescopica (il lato di chiusura 25 mm oltre la luce) e 2·L + 60 mm con porta centrale, profondo 220 mm, dentro il vano; con il fornitore scelto: 2SG FLY/LIKE 1,5·L + 40 mm (telescopica) e 2·L + 20 mm (centrale), profondo 220 mm; Fermator 40/10 1,5·L + 50 mm e 2·L + 50 mm, profondo 144 mm; Dapa LOWER 1,5·L + 47 mm e 2·L + 50 mm, profondo 217 mm; con due accessi adiacenti gli operatori non devono sovrapporsi all’angolo tra le porte (altrimenti «Attenzione»: operatori da scegliere con il fornitore)</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>schede PDF 2SG FLY 2AT (ingombro massimo 1,5·A + 10; soglia 1,5·A + 20, + 40 con l'extracorsa: presa la più lunga) e 2AO (2·A + 20), profondità 220 letta sul disegno; catalogo tecnico Dapa LOWER (1,5·AP + 47, 2·AP + 50, profondità 217); Fermator 40/10 PM in copie presso terzi (1,5·PL + 50 e 2·PL + 50, le soglie + 40; profondità 120–144 sul disegno, con le staffe 183–280; chiusura a 15 mm dalla luce, il software ne tiene 25); Wittur Hydra Plus da una copia del catalogo Selcom (1,5·PL + 25 e 2·PL + 50, profondo 200); letti il 2 ottobre 2026 (research/argano-geared/18-porte-limitatori-tenditori-tutti.md). Il generico è l'inviluppo: il più lungo (Fermator, Dapa) e il più profondo (2SG FLY). Hydra Plus può superarlo dove la sua quota GM supera la GW; Prisma e CMM: lunghezza e profondità non trovate</t>
+          <t>schede PDF 2SG FLY 2AT (ingombro massimo 1,5·A + 10; soglia 1,5·A + 20, + 40 con l’extracorsa: presa la più lunga) e 2AO (2·A + 20), profondità 220 letta sul disegno; catalogo tecnico Dapa LOWER (1,5·AP + 47, 2·AP + 50, profondità 217); Fermator 40/10 PM in copie presso terzi (1,5·PL + 50 e 2·PL + 50, le soglie + 40; profondità 120–144 sul disegno, con le staffe 183–280; chiusura a 15 mm dalla luce, il software ne tiene 25); Wittur Hydra Plus da una copia del catalogo Selcom (1,5·PL + 25 e 2·PL + 50, profondo 200); letti il 2 ottobre 2026 (research/argano-geared/18-porte-limitatori-tenditori-tutti.md). Il generico è l’inviluppo: il più lungo (Fermator, Dapa) e il più profondo (2SG FLY). Hydra Plus può superarlo dove la sua quota GM supera la GW; Prisma e CMM: lunghezza e profondità non trovate</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
@@ -4128,12 +4128,12 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Porta di piano spostata rispetto alla porta di cabina (disassamento) — nel 3D la leva della serratura con i rulli resta in linea con l'accoppiatore della porta di cabina: con il disassamento va montata spostata sull'anta della porta di piano (da concordare con il fornitore delle porte)</t>
+          <t>Porta di piano spostata rispetto alla porta di cabina (disassamento) — nel 3D la leva della serratura con i rulli resta in linea con l’accoppiatore della porta di cabina: con il disassamento va montata spostata sull’anta della porta di piano (da concordare con il fornitore delle porte)</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>la luce netta della porta di piano sporge al massimo 50 mm per lato oltre quella della porta di cabina: con la stessa luce, disassamento ≤ 50 mm (oltre: «Non conforme»); lo stesso spostamento a tutti i piani, per ciascun accesso, con il vano nel muro, il portale, gli imbotti, la soglia sulle staffe e la bottoniera della porta di piano; il passaggio libero è la parte comune delle due luci (luce − disassamento), ed è quello verificato per l'accessibilità (DM 236/1989)</t>
+          <t>la luce netta della porta di piano sporge al massimo 50 mm per lato oltre quella della porta di cabina: con la stessa luce, disassamento ≤ 50 mm (oltre: «Non conforme»); lo stesso spostamento a tutti i piani, per ciascun accesso, con il vano nel muro, il portale, gli imbotti, la soglia sulle staffe e la bottoniera della porta di piano; il passaggio libero è la parte comune delle due luci (luce − disassamento), ed è quello verificato per l’accessibilità (DM 236/1989)</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Imbotti della porta di piano (sostituzione con una luce più piccola) — Montanti e pannelli accanto alla porta più larghi di 150 mm che chiudono l'apertura vanno con la prova del pendolo della porta (UNI EN 81-20:2020, 5.3.5.3.4): la copre il fornitore.</t>
+          <t>Imbotti della porta di piano (sostituzione con una luce più piccola) — Montanti e pannelli accanto alla porta più larghi di 150 mm che chiudono l’apertura vanno con la prova del pendolo della porta (UNI EN 81-20:2020, 5.3.5.3.4): la copre il fornitore.</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>tra la parete e la guida della cabina, centrato sull'asse delle guide di cabina, con le sue guide alle estremità (pattini 20 mm) e la guida di cabina su una staffa a ponte; a 40 mm dalle zone delle porte; lunghezza in pianta da 400 a 900 mm (sotto 400 mm: «Attenzione»); con il contrappeso sul fondo, al massimo la larghezza tra le guide della cabina</t>
+          <t>tra la parete e la guida della cabina, centrato sull’asse delle guide di cabina, con le sue guide alle estremità (pattini 20 mm) e la guida di cabina su una staffa a ponte; a 40 mm dalle zone delle porte; lunghezza in pianta da 400 a 900 mm (sotto 400 mm: «Attenzione»); con il contrappeso sul fondo, al massimo la larghezza tra le guide della cabina</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>entrambe le guide di cabina sulla parete opposta all'accesso laterale, con le lame affacciate lungo la parete (il momento della cabina a sbalzo va sulle facce delle lame); piedi delle guide a 20 mm dentro la profondità della piattaforma; contrappeso tra le guide, contro la parete, con le sue guide alle estremità e i piedi a 70 mm da quelli delle guide di cabina (staffe); la cabina a 10 mm dalle bride che tengono i piedi delle guide sulle staffe (bride forgiate della misura della guida, con la piastra oltre il piede)</t>
+          <t>entrambe le guide di cabina sulla parete opposta all’accesso laterale, con le lame affacciate lungo la parete (il momento della cabina a sbalzo va sulle facce delle lame); piedi delle guide a 20 mm dentro la profondità della piattaforma; contrappeso tra le guide, contro la parete, con le sue guide alle estremità e i piedi a 70 mm da quelli delle guide di cabina (staffe); la cabina a 10 mm dalle bride che tengono i piedi delle guide sulle staffe (bride forgiate della misura della guida, con la piastra oltre il piede)</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (principio: cataloghi di arcate a zaino); disposizione da confermare con il fornitore dell'arcata</t>
+          <t>scelta del software (principio: cataloghi di arcate a zaino); disposizione da confermare con il fornitore dell’arcata</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>contrappeso in nicchia: il contrappeso con le sue guide sta nella nicchia della parete su cui corre, con almeno 20 mm tra le guide e i fianchi della nicchia (con le staffe Panev, lo spazio della piastra del supporto dietro il piede di ogni guida); la distanza dalla parete si misura dal fondo della nicchia e la cabina guadagna la sua profondità, senza scendere sotto gli ingombri delle guide; luce del vano in nicchia: una nicchia alta 400 mm per lampada, le lampade 1500 mm sopra ogni piano e l'ultima a 80 mm sotto la soletta; canalina in nicchia: dal fondo della fossa alla soletta; ogni nicchia dentro la sua parete, fuori dai telai delle porte di piano e dalle altre nicchie, con almeno 50 mm di muro dietro; altrimenti «Non conforme»</t>
+          <t>contrappeso in nicchia: il contrappeso con le sue guide sta nella nicchia della parete su cui corre, con almeno 20 mm tra le guide e i fianchi della nicchia (con le staffe Panev, lo spazio della piastra del supporto dietro il piede di ogni guida); la distanza dalla parete si misura dal fondo della nicchia e la cabina guadagna la sua profondità, senza scendere sotto gli ingombri delle guide; luce del vano in nicchia: una nicchia alta 400 mm per lampada, le lampade 1500 mm sopra ogni piano e l’ultima a 80 mm sotto la soletta; canalina in nicchia: dal fondo della fossa alla soletta; ogni nicchia dentro la sua parete, fuori dai telai delle porte di piano e dalle altre nicchie, con almeno 50 mm di muro dietro; altrimenti «Non conforme»</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>per default il supporto Panev SU o SD con la guida SG, la guida serrata sulla flangia della SG da due bride N1: il supporto più corto il cui campo stampato prende la distanza della guida dalla parete (o dal fondo della nicchia) e la cui piastra sta sulla parete: SU, SD 150 e SD 220 lunghi 160 mm da 45 a 155 mm (SD 220 da 50), lunghi 180 mm da 45 a 195 mm, lunghi 200 mm da 45 a 215 mm; quando nessuno sta, vicino a un angolo, il supporto scorrevole SC sulla parete dietro il piede della guida con la SG lungo la parete: la flangia della SG da 2 mm oltre il bordo dell'SC fino a 70, 88, 130 e 140 mm dalla parete per SC 50, 60, 80 e 90, l'asse della guida entro il campo stampato da un'estremità dell'SC (lunghi 200 mm: 210, 213, 215 e 215 mm; lunghi 220 mm: 235, 235, 255 e 235 mm), fuori dai telai delle porte e dalle nicchie. Il progettista può scegliere l'articolo a mano (se non prende la guida: «Non conforme») o una soluzione su disegno esecutivo, SC 50 170 + SG 225 50 a misura o SN 60 65 + SN 65 200 + BRACCIO 160 190 all'angolo del vano: «Da verificare» sul disegno; nessuno adatto: «Non conforme» (si possono scegliere staffe generiche, da dimensionare a parte)</t>
+          <t>per default il supporto Panev SU o SD con la guida SG, la guida serrata sulla flangia della SG da due bride N1: il supporto più corto il cui campo stampato prende la distanza della guida dalla parete (o dal fondo della nicchia) e la cui piastra sta sulla parete: SU, SD 150 e SD 220 lunghi 160 mm da 45 a 155 mm (SD 220 da 50), lunghi 180 mm da 45 a 195 mm, lunghi 200 mm da 45 a 215 mm; quando nessuno sta, vicino a un angolo, il supporto scorrevole SC sulla parete dietro il piede della guida con la SG lungo la parete: la flangia della SG da 2 mm oltre il bordo dell’SC fino a 70, 88, 130 e 140 mm dalla parete per SC 50, 60, 80 e 90, l’asse della guida entro il campo stampato da un’estremità dell’SC (lunghi 200 mm: 210, 213, 215 e 215 mm; lunghi 220 mm: 235, 235, 255 e 235 mm), fuori dai telai delle porte e dalle nicchie. Il progettista può scegliere l’articolo a mano (se non prende la guida: «Non conforme») o una soluzione su disegno esecutivo, SC 50 170 + SG 225 50 a misura o SN 60 65 + SN 65 200 + BRACCIO 160 190 all’angolo del vano: «Da verificare» sul disegno; nessuno adatto: «Non conforme» (si possono scegliere staffe generiche, da dimensionare a parte)</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>catalogo del costruttore (panev/docs/catalogo-staffe-panev-2026.pdf); le corse dell'SC lontano dalla parete lette sui disegni di montaggio (pp. 41-55)</t>
+          <t>catalogo del costruttore (panev/docs/catalogo-staffe-panev-2026.pdf); le corse dell’SC lontano dalla parete lette sui disegni di montaggio (pp. 41-55)</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>per velocità il più piccolo PFB che la regge: LK200 (Ø 200, fune 6) fino a 1,48 m/s, LK250 fino a 1,74, LK300 fino a 2,93, R12BF fino a 4,00; oppure il modello scelto se regge la velocità: PFB (LX, LK, R1, R3LR, R5, R6, R10BF), Bode (GB 7 fino a 2,98 m/s, GB 8 fino a 1,29), Dynatech (VEGA 200 fino a 2,40), Wittur (OL20 fino a 1,75, OL35 fino a 3,00, EOS fino a 2,50, OL100 fino a 10,00) o Montanari (RQ-A 200, 250 e 300, RC 200 e 300, NOR fino a 1,50 m/s, RG 200 fino a 0,30). Con le quote dei disegni dei costruttori (altezza totale, tra parentesi l'asse dalla base): LK200, LK250, LK300 e LK315 415 (165) su base 220 × 165 (LK315 220 × 130); LX120 178 (70,5), LK120 270 (71), LX150 274 (86), LX180 322 (107), LX200 349 (110); R1 344 (190,5) su base 285 × 80; R3LR 348 (157); R5 261 (120); R6 335 (168); R10BF 488 (303) su base 460 × 196; R12BF 524 (337) su base 520 × 116; Bode GB 7 360 (205) e GB 8 315 (205); Dynatech VEGA 200 332 (199,5); Wittur e Montanari nelle proporzioni del software (Ø 200: alto 370, asse a 240). Tenditore in fossa sulla guida di cabina: a leva con 22 kg (come PFB R4K) o verticale con 44 kg (come PFB R4R)</t>
+          <t>per velocità il più piccolo PFB che la regge: LK200 (Ø 200, fune 6) fino a 1,48 m/s, LK250 fino a 1,74, LK300 fino a 2,93, R12BF fino a 4,00; oppure il modello scelto se regge la velocità: PFB (LX, LK, R1, R3LR, R5, R6, R10BF), Bode (GB 7 fino a 2,98 m/s, GB 8 fino a 1,29), Dynatech (VEGA 200 fino a 2,40), Wittur (OL20 fino a 1,75, OL35 fino a 3,00, EOS fino a 2,50, OL100 fino a 10,00) o Montanari (RQ-A 200, 250 e 300, RC 200 e 300, NOR fino a 1,50 m/s, RG 200 fino a 0,30). Con le quote dei disegni dei costruttori (altezza totale, tra parentesi l’asse dalla base): LK200, LK250, LK300 e LK315 415 (165) su base 220 × 165 (LK315 220 × 130); LX120 178 (70,5), LK120 270 (71), LX150 274 (86), LX180 322 (107), LX200 349 (110); R1 344 (190,5) su base 285 × 80; R3LR 348 (157); R5 261 (120); R6 335 (168); R10BF 488 (303) su base 460 × 196; R12BF 524 (337) su base 520 × 116; Bode GB 7 360 (205) e GB 8 315 (205); Dynatech VEGA 200 332 (199,5); Wittur e Montanari nelle proporzioni del software (Ø 200: alto 370, asse a 240). Tenditore in fossa sulla guida di cabina: a leva con 22 kg (come PFB R4K) o verticale con 44 kg (come PFB R4R)</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>manuali d'uso PFB con i disegni quotati (download.pfb.it), brochure Bode e Wittur, manuale Dynatech VEGA e disegni Bode in copia presso un rivenditore (elevatorequipment.co.uk), letti il 2 ottobre 2026; basi delle LK da un listino di rivenditore; Montanari da estratti di ricerca del 1° ottobre 2026 (research/argano-geared/18-porte-limitatori-tenditori-tutti.md)</t>
+          <t>manuali d’uso PFB con i disegni quotati (download.pfb.it), brochure Bode e Wittur, manuale Dynatech VEGA e disegni Bode in copia presso un rivenditore (elevatorequipment.co.uk), letti il 2 ottobre 2026; basi delle LK da un listino di rivenditore; Montanari da estratti di ricerca del 1° ottobre 2026 (research/argano-geared/18-porte-limitatori-tenditori-tutti.md)</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Distanze libere dal soffitto con la cabina nella posizione più alta — I valori 500, 100 e 300 mm sono confermati. Il software dà alla traversa dell'arcata i 100 mm di b) e avvisa sotto i 500 mm di a) (voce spazi.testata.traversa). Con il soffitto piano, 300 mm sopra il corrimano danno anche i 500 mm in obliquo oltre i 400 mm (c) 2)); sotto pulegge o travi appese no.</t>
+          <t>Distanze libere dal soffitto con la cabina nella posizione più alta — I valori 500, 100 e 300 mm sono confermati. Il software dà alla traversa dell’arcata i 100 mm di b) e avvisa sotto i 500 mm di a) (voce spazi.testata.traversa). Con il soffitto piano, 300 mm sopra il corrimano danno anche i 500 mm in obliquo oltre i 400 mm (c) 2)); sotto pulegge o travi appese no.</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>≥ 500 mm sopra le apparecchiature sul tetto di cabina (operatore); ≥ 100 mm sopra pattini, attacchi delle funi e traversa dell'arcata; ≥ 300 mm sopra il corrimano della balaustra</t>
+          <t>≥ 500 mm sopra le apparecchiature sul tetto di cabina (operatore); ≥ 100 mm sopra pattini, attacchi delle funi e traversa dell’arcata; ≥ 300 mm sopra il corrimano della balaustra</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Traversa dell'arcata sotto il soffitto — La b) nomina la traversa delle porte e le parti delle porte a scorrimento verticale; quella dell'arcata non è nominata. Da concordare con l'organismo.</t>
+          <t>Traversa dell’arcata sotto il soffitto — La b) nomina la traversa delle porte e le parti delle porte a scorrimento verticale; quella dell’arcata non è nominata. Da concordare con l’organismo.</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>≥ 100 mm come parte di b); sotto 500 mm «Attenzione»: se l'organismo la considera un'apparecchiatura vale a) (500 mm)</t>
+          <t>≥ 100 mm come parte di b); sotto 500 mm «Attenzione»: se l’organismo la considera un’apparecchiatura vale a) (500 mm)</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>traversa dell'arcata sotto il soffitto</t>
+          <t>traversa dell’arcata sotto il soffitto</t>
         </is>
       </c>
       <c r="I87" s="11" t="n"/>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>con la cabina nella posizione più alta: a 2:1 la puleggia di cabina (Dp + 30 mm sopra la traversa) è un'apparecchiatura sul tetto, distanza libera ≥ 500 mm dal soffitto o dalle pulegge appese; a 1:1 con la macchina in basso la traversa sotto le pulegge appese alla soletta (asse a Dp/2 + 120 mm sotto il soffitto), distanza libera ≥ 100 mm, quella della traversa</t>
+          <t>con la cabina nella posizione più alta: a 2:1 la puleggia di cabina (Dp + 30 mm sopra la traversa) è un’apparecchiatura sul tetto, distanza libera ≥ 500 mm dal soffitto o dalle pulegge appese; a 1:1 con la macchina in basso la traversa sotto le pulegge appese alla soletta (asse a Dp/2 + 120 mm sotto il soffitto), distanza libera ≥ 100 mm, quella della traversa</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>lo spazio di rifugio in fossa resta libero dagli ammortizzatori di cabina: il software lo mette sotto il centro della cabina o, se un piatto vi entra, nel posto libero più vicino sotto l'interno della cabina; due o più ammortizzatori di cabina a 160 mm dai fianchi della piattaforma, più in fuori finché i piatti escono dalla pianta del rifugio, sempre sotto la piattaforma; la verifica vale anche per quelli messi dal software (margine ≥ 0)</t>
+          <t>lo spazio di rifugio in fossa resta libero dagli ammortizzatori di cabina: il software lo mette sotto il centro della cabina o, se un piatto vi entra, nel posto libero più vicino sotto l’interno della cabina; due o più ammortizzatori di cabina a 160 mm dai fianchi della piattaforma, più in fuori finché i piatti escono dalla pianta del rifugio, sempre sotto la piattaforma; la verifica vale anche per quelli messi dal software (margine ≥ 0)</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>≥ 500 mm dal pavimento della fossa alle parti più basse della cabina; grembiule sotto la soglia di cabina: tratto verticale ≥ 750 mm, poi uno smusso a ≥ 60° sull'orizzontale con proiezione orizzontale ≥ 20 mm (circa 35 mm più in basso), con ≥ 100 mm liberi dal pavimento della fossa</t>
+          <t>≥ 500 mm dal pavimento della fossa alle parti più basse della cabina; grembiule sotto la soglia di cabina: tratto verticale ≥ 750 mm, poi uno smusso a ≥ 60° sull’orizzontale con proiezione orizzontale ≥ 20 mm (circa 35 mm più in basso), con ≥ 100 mm liberi dal pavimento della fossa</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Balaustra sul tetto di cabina — fino alla versione 2.12.0 del motore del vano il software misurava i 500 mm dal bordo del tetto; la norma vuole la balaustra entro 150 mm dal bordo: se è più interna, la distanza cresce e può servire l'altezza maggiore</t>
+          <t>Balaustra sul tetto di cabina — fino alla versione 2.12.0 del motore del vano il software misurava i 500 mm dal bordo del tetto; la norma vuole la balaustra entro 150 mm dal bordo: se è più interna, la distanza cresce e può servire l’altezza maggiore</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="C